--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -1275,39 +1275,39 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
         <v>60</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>25570</v>
+        <v>8457</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>24850 - 26290</t>
+          <t>8242 - 8672</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1321,15 +1321,15 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Above 200-DMA (+11.2%)</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>25570</v>
+        <v>25371</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 65; TORNTPHARM: 78, CIPLA: 73, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 80; FORTIS: 72, MAXHEALTH: 70, METROPOLIS: 64</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.6%) • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1368,39 +1368,39 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
         <v>60</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2357.8</v>
+        <v>364.6</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2298 - 2418</t>
+          <t>354 - 375</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1414,15 +1414,15 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+9.3%)</t>
+          <t>Above 200-DMA (+2.7%)</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -1435,22 +1435,22 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>33009</v>
+        <v>17136</v>
       </c>
       <c r="T3" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="U3" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 71; TORNTPHARM: 78, CIPLA: 73, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 80; POWERGRID: 72, TATAPOWER: 68, CESC: 62</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+2.7%) • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -1461,39 +1461,39 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
         <v>60</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8457</v>
+        <v>821</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>8242 - 8672</t>
+          <t>801 - 841</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1507,15 +1507,15 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.2%)</t>
+          <t>Above 200-DMA (+8.5%)</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -1528,22 +1528,22 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>25371</v>
+        <v>27095</v>
       </c>
       <c r="T4" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="U4" t="n">
-        <v>10.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 80; FORTIS: 72, MAXHEALTH: 70, METROPOLIS: 64</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 72; NESTLEIND: 74, VBL: 58, TATACONSUM: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
@@ -1554,61 +1554,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="D5" t="n">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E5" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="G5" t="n">
         <v>60</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1901.6</v>
+        <v>291.9</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1851 - 1952</t>
+          <t>283 - 301</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.6%)</t>
+          <t>Above 200-DMA (+2.1%)</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -1621,65 +1621,65 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>30426</v>
+        <v>16349</v>
       </c>
       <c r="T5" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="U5" t="n">
-        <v>10.2</v>
+        <v>5.5</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 70; TATACOMM: 54, INDUSTOWER: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 72; NTPC: 80, TATAPOWER: 68, CESC: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+2.1%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="E6" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5241</v>
+        <v>2357.8</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>5103 - 5379</t>
+          <t>2298 - 2418</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1693,11 +1693,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.6%)</t>
+          <t>Above 200-DMA (+9.3%)</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1714,22 +1714,22 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>26205</v>
+        <v>33009</v>
       </c>
       <c r="T6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; NESTLEIND: 74, MARICO: 72, VBL: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 71; TORNTPHARM: 78, CIPLA: 73, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.3%) • sector strength 65/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1740,61 +1740,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>37</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>821</v>
+        <v>1901.6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>801 - 841</t>
+          <t>1851 - 1952</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3% to +15%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.5%)</t>
+          <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -1807,87 +1807,87 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>27095</v>
+        <v>30426</v>
       </c>
       <c r="T7" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="U7" t="n">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 72; NESTLEIND: 74, VBL: 58, TATACONSUM: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 70; TATACOMM: 54, INDUSTOWER: 52</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.5%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • sector strength 59/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="F8" t="n">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="G8" t="n">
         <v>60</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1309.5</v>
+        <v>25570</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1268 - 1351</t>
+          <t>24850 - 26290</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-1% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1900,22 +1900,22 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>22262</v>
+        <v>25570</v>
       </c>
       <c r="T8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>7.7</v>
+        <v>11.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 55; GAIL: 60, IGL: 52, PETRONET: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 65; TORNTPHARM: 78, CIPLA: 73, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.6%) • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
       </c>
     </row>
@@ -1926,16 +1926,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F9" t="n">
         <v>35</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1954,33 +1954,33 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1833.7</v>
+        <v>1338.3</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1782 - 1885</t>
+          <t>1300 - 1377</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.5%)</t>
+          <t>Below 200-DMA (-0.6%)</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>20171</v>
+        <v>17398</v>
       </c>
       <c r="T9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U9" t="n">
-        <v>7.1</v>
+        <v>5.9</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 59; AXISBANK: 62, ICICIBANK: 62, KOTAKBANK: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 62; AXISBANK: 62, KOTAKBANK: 62, LICI: 62</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.5%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -2019,16 +2019,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
         <v>35</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2047,33 +2047,33 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1338.3</v>
+        <v>1833.7</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1300 - 1377</t>
+          <t>1782 - 1885</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.6%)</t>
+          <t>Below 200-DMA (-2.5%)</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -2086,87 +2086,87 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>17398</v>
+        <v>20171</v>
       </c>
       <c r="T10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U10" t="n">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 62; AXISBANK: 62, KOTAKBANK: 62, LICI: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 59; AXISBANK: 62, ICICIBANK: 62, KOTAKBANK: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-0.6%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.5%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F11" t="n">
-        <v>88</v>
+        <v>18</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>364.6</v>
+        <v>1309.5</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>354 - 375</t>
+          <t>1268 - 1351</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1% to +7%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+2.7%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -2179,65 +2179,65 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>17136</v>
+        <v>22262</v>
       </c>
       <c r="T11" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="U11" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 80; POWERGRID: 72, TATAPOWER: 68, CESC: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 55; GAIL: 60, IGL: 52, PETRONET: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • above 200-dma (+2.7%) • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="E12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F12" t="n">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c r="G12" t="n">
         <v>60</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>291.9</v>
+        <v>5241</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>283 - 301</t>
+          <t>5103 - 5379</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2251,15 +2251,15 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+2.1%)</t>
+          <t>Below 200-DMA (-9.6%)</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -2272,22 +2272,22 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>16349</v>
+        <v>26205</v>
       </c>
       <c r="T12" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="U12" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 72; NTPC: 80, TATAPOWER: 68, CESC: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; NESTLEIND: 74, MARICO: 72, VBL: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • above 200-dma (+2.1%) • sector strength 88/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APOLLOHOSP (score 77)</t>
+          <t>APOLLOHOSP (score 78)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHREECEM (score 49)</t>
+          <t>SHREECEM (score 48)</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1389,105 +1389,130 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Score Breakdown</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Top Factor</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Weakest Factor</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>F: Historical</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>F: Technical/Trend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>F: Risk/Vol</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>F: Sector</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F: Regime</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Buy Range</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Expected Range (hist)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Prob +ve</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Rec Confidence %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Selected Because</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Not Evaluated</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Why This vs Alternatives</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1500,87 +1525,112 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
-      </c>
-      <c r="C2" t="n">
+        <v>78</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Risk/Vol +25 · Historical +19 · Trend/Tech +16 · Regime +9 · Sector +9 = 78</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>78</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>99</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>88</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>60</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>APOLLOHOSP</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>8592</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>8374 - 8810</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>78</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Above 200-DMA (+12.8%)</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>71</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="V2" t="n">
         <v>25776</v>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>3</v>
       </c>
-      <c r="U2" t="n">
+      <c r="X2" t="n">
         <v>9</v>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 77; FORTIS: 71, MAXHEALTH: 69, LALPATHLAB: 61</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Healthcare name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 78; FORTIS: 70, MAXHEALTH: 69, LALPATHLAB: 61</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Low-risk Healthcare holding (low vol) • above 200-dma (+12.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
@@ -1595,85 +1645,110 @@
       <c r="B3" t="n">
         <v>72</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +3 = 72</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>61</v>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="n">
         <v>84</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>100</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>29</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>60</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>MARICO</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>825.8</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>806 - 846</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>75</v>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>Above 200-DMA (+9.0%)</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>59</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="V3" t="n">
         <v>23948</v>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>29</v>
       </c>
-      <c r="U3" t="n">
+      <c r="X3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 72; NESTLEIND: 73, VBL: 61, UNITDSPR: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>Low-risk FMCG holding (low vol) • above 200-dma (+9.0%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
@@ -1686,89 +1761,114 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
-      </c>
-      <c r="C4" t="n">
-        <v>84</v>
-      </c>
-      <c r="D4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E4" t="n">
-        <v>93</v>
+        <v>71</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +19 · Trend/Tech +15 · Regime +9 · Sector +4 = 71</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
+        <v>75</v>
+      </c>
+      <c r="H4" t="n">
+        <v>94</v>
+      </c>
+      <c r="I4" t="n">
+        <v>35</v>
+      </c>
+      <c r="J4" t="n">
         <v>60</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Power</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>352</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>342 - 363</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>409</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>397 - 421</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>74</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-0.9%)</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="n">
+        <v>75</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Above 200-DMA (+0.7%)</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>81</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>23235</v>
-      </c>
-      <c r="T4" t="n">
-        <v>66</v>
-      </c>
-      <c r="U4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 70; POWERGRID: 62, CESC: 60, NHPC: 59</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.9%) • sector strength 76/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+      <c r="V4" t="n">
+        <v>17996</v>
+      </c>
+      <c r="W4" t="n">
+        <v>44</v>
+      </c>
+      <c r="X4" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 71; ICICIBANK: 72, AXISBANK: 62, SBIN: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+0.7%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -1781,87 +1881,112 @@
       <c r="B5" t="n">
         <v>70</v>
       </c>
-      <c r="C5" t="n">
-        <v>64</v>
-      </c>
-      <c r="D5" t="n">
-        <v>75</v>
-      </c>
-      <c r="E5" t="n">
-        <v>94</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Historical +25 · Risk/Vol +23 · Regime +9 · Sector +8 · Trend/Tech +5 = 70</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Trend/Tech</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
+        <v>24</v>
+      </c>
+      <c r="H5" t="n">
+        <v>93</v>
+      </c>
+      <c r="I5" t="n">
+        <v>76</v>
+      </c>
+      <c r="J5" t="n">
         <v>60</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>409</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>397 - 421</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>352</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>342 - 363</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>74</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Above 200-DMA (+0.7%)</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>81</v>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-0.9%)</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>41</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>17996</v>
-      </c>
-      <c r="T5" t="n">
-        <v>44</v>
-      </c>
-      <c r="U5" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 70; ICICIBANK: 71, AXISBANK: 62, FEDERALBNK: 61. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+0.7%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+      <c r="V5" t="n">
+        <v>23235</v>
+      </c>
+      <c r="W5" t="n">
+        <v>66</v>
+      </c>
+      <c r="X5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 70; POWERGRID: 62, CESC: 61, NHPC: 60</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.9%) • sector strength 76/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -1872,87 +1997,112 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
-      </c>
-      <c r="C6" t="n">
+        <v>69</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Risk/Vol +25 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +5 = 69</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>50</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>73</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>99</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>47</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>60</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>LUPIN</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>2343.5</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>2284 - 2403</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>71</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>Above 200-DMA (+8.4%)</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>65</v>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>35152</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>15</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>12.2</v>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 68; TORNTPHARM: 76, CIPLA: 71, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; TORNTPHARM: 77, CIPLA: 71, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.4%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
@@ -1965,87 +2115,112 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>67</v>
-      </c>
-      <c r="C7" t="n">
+        <v>66</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +23 · Regime +9 · Trend/Tech +6 · Sector +4 = 66</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>76</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>98</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>41</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>60</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>BHARTIARTL</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>1850.7</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1801 - 1900</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>-3% to +15%</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>69%</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>85</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>Below 200-DMA (-5.2%)</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>60</v>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>20358</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>7.1</v>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 67; TATACOMM: 52, INDUSTOWER: 50</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 66; TATACOMM: 53, INDUSTOWER: 50</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>Low-risk Telecom holding (low vol) • below 200-dma (-5.2%) • sector strength 41/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
@@ -2060,85 +2235,110 @@
       <c r="B8" t="n">
         <v>64</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +21 · Regime +9 · Trend/Tech +5 · Sector +5 = 64</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>70</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>27</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>97</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>47</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>60</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>ABBOTINDIA</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>25585</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>24868 - 26302</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>72</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Below 200-DMA (-8.3%)</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>42</v>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>25585</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>1</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>11.6</v>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 64; TORNTPHARM: 76, CIPLA: 71, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 64; TORNTPHARM: 77, CIPLA: 71, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.3%) • sector strength 47/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
@@ -2153,85 +2353,110 @@
       <c r="B9" t="n">
         <v>62</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Sector +8 · Trend/Tech +5 = 62</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Trend/Tech</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>56</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>27</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>92</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>76</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>60</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>POWERGRID</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Power</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>283.9</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>275 - 293</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>71</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Below 200-DMA (-0.8%)</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>47</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>19305</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>68</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>6.5</v>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 62; NTPC: 70, CESC: 60, NHPC: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 62; NTPC: 70, CESC: 61, NHPC: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>Low-risk Power holding (low vol) • below 200-dma (-0.8%) • sector strength 76/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
@@ -2244,87 +2469,112 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
-      </c>
-      <c r="C10" t="n">
+        <v>60</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +16 · Regime +9 · Trend/Tech +7 · Sector +4 = 60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>52</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
         <v>34</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>96</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>35</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>60</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>ICICIGI</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>1813.6</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1763 - 1865</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>70</v>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>Below 200-DMA (-3.6%)</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>57</v>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>27204</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>15</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>9.1</v>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 59; ICICIBANK: 71, KOTAKBANK: 70, AXISBANK: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 60; ICICIBANK: 72, KOTAKBANK: 71, AXISBANK: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>Low-risk Financials holding (low vol) • below 200-dma (-3.6%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
@@ -2339,85 +2589,110 @@
       <c r="B11" t="n">
         <v>54</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Risk/Vol +22 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +1 = 54</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>56</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="n">
         <v>25</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>90</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>12</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>60</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>1318.1</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1276 - 1360</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>-1% to +7%</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>62%</t>
         </is>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>72</v>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>Below 200-DMA (-7.2%)</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>57</v>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>25044</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>19</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>8.4</v>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 54; GAIL: 60, IGL: 51, PETRONET: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 54; GAIL: 59, IGL: 51, PETRONET: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>Low-risk Energy holding (low vol) • below 200-dma (-7.2%) • sector strength 12/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
@@ -2432,85 +2707,110 @@
       <c r="B12" t="n">
         <v>51</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +5 · Sector +3 = 51</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>32</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>25</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>98</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>29</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>60</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>BRITANNIA</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>FMCG</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>5237</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>5099 - 5375</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>66</v>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>Below 200-DMA (-9.6%)</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>62</v>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>15711</v>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>7</v>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; NESTLEIND: 73, MARICO: 72, VBL: 61. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
@@ -2523,87 +2823,112 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
-      </c>
-      <c r="C13" t="n">
+        <v>48</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Risk/Vol +22 · Regime +9 · Trend/Tech +8 · Historical +7 · Sector +2 = 48</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>24</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
         <v>41</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>90</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>18</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>60</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>SHREECEM</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Cement</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>25735</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>24925 - 26545</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>-11% to +3%</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>70</v>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>67</v>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>7.1</v>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 49; GRASIM: 75, ULTRACEMCO: 57, RAMCOCEM: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Regime strongest; chosen as a lowest-volatility Cement name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 48; GRASIM: 75, ULTRACEMCO: 57, RAMCOCEM: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>Low-risk Cement holding (low vol) • below 200-dma (-2.7%) • sector strength 18/100 • regime cautious (partial deploy) • 5 similar past recs: 40% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -531,24 +531,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Highest conviction</t>
+          <t>Best risk-fit (suitability)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APOLLOHOSP (score 78)</t>
+          <t>APOLLOHOSP (78)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Weakest holding</t>
+          <t>Weakest holding (suitability)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHREECEM (score 48)</t>
+          <t>SHREECEM (48)</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Score /100</t>
+          <t>Portfolio Suitability</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Score Breakdown</t>
+          <t>Suitability Breakdown</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -27972,12 +27972,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Factor breakdown (each 0-100)</t>
+          <t>Portfolio Suitability (0-100)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Every pick shows 5 sub-scores so you see WHY, not one opaque number: Historical (win rate + median, SHRUNK toward neutral when &lt;5 cases), Technical/Trend (200-DMA, relative strength, RSI), Risk/Vol (low volatility = high), Sector, Regime. Overall = 0.30 Historical + 0.25 Risk + 0.20 Technical + 0.10 Sector + 0.15 Regime.</t>
+          <t>HONEST NAMING: this score measures how well a stock FITS a risk-managed portfolio (risk-fit), NOT how likely it is to outperform. Its largest component is always Risk/Vol — AEGIS is a portfolio-allocation engine, not an alpha-discovery engine. Built from 5 sub-scores: Historical (win rate + median, shrunk toward neutral when &lt;5 cases), Technical/Trend (200-DMA, rel-strength, RSI), Risk/Vol (low volatility = high), Sector, Regime. Suitability = 0.30 Historical + 0.25 Risk + 0.20 Technical + 0.10 Sector + 0.15 Regime (the Score Breakdown column shows the exact additive parts).</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHREECEM (48)</t>
+          <t>SHREECEM (47)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -700,7 +700,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-26  /  2026-06-25</t>
+          <t>2026-06-29  /  2026-06-29</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1568,11 +1568,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8592</v>
+        <v>8717.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8374 - 8810</t>
+          <t>8497 - 8938</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+12.8%)</t>
+          <t>Above 200-DMA (+14.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1603,17 +1603,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>25776</v>
+        <v>26152</v>
       </c>
       <c r="W2" t="n">
         <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 78; FORTIS: 70, MAXHEALTH: 69, LALPATHLAB: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 78; FORTIS: 68, MAXHEALTH: 68, LALPATHLAB: 62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+12.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +3 = 72</t>
+          <t>Historical +25 · Risk/Vol +23 · Trend/Tech +13 · Regime +9 · Sector +7 = 77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1661,36 +1661,36 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>825.8</v>
+        <v>355.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>806 - 846</t>
+          <t>345 - 366</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1704,15 +1704,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+9.0%)</t>
+          <t>Above 200-DMA (+0.0%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23948</v>
+        <v>18133</v>
       </c>
       <c r="W3" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="X3" t="n">
-        <v>8.1</v>
+        <v>6.1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 72; NESTLEIND: 73, VBL: 61, UNITDSPR: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 77; POWERGRID: 61, JSWENERGY: 58, NHPC: 57</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+9.0%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+0.0%) • sector strength 71/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -1761,11 +1761,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +19 · Trend/Tech +15 · Regime +9 · Sector +4 = 71</t>
+          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +3 = 72</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1779,36 +1779,36 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>409</v>
+        <v>841.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>397 - 421</t>
+          <t>821 - 862</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1826,11 +1826,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+0.7%)</t>
+          <t>Above 200-DMA (+11.0%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1839,21 +1839,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>17996</v>
+        <v>25246</v>
       </c>
       <c r="W4" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="X4" t="n">
-        <v>6.1</v>
+        <v>8.6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1863,12 +1863,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 71; ICICIBANK: 72, AXISBANK: 62, SBIN: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 72; NESTLEIND: 73, VBL: 61, UNITDSPR: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+0.7%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+11.0%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
@@ -1879,76 +1879,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +23 · Regime +9 · Sector +8 · Trend/Tech +5 = 70</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +14 · Regime +9 · Sector +4 = 71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G5" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="H5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I5" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>352</v>
+        <v>1389.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>342 - 363</t>
+          <t>1349 - 1430</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.9%)</t>
+          <t>Above 200-DMA (+3.3%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>23235</v>
+        <v>13897</v>
       </c>
       <c r="W5" t="n">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="X5" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 70; POWERGRID: 62, CESC: 61, NHPC: 60</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; LICI: 64, AXISBANK: 63, KOTAKBANK: 62</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.9%) • sector strength 76/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.3%) • sector strength 41/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +5 = 69</t>
+          <t>Risk/Vol +25 · Historical +15 · Trend/Tech +13 · Regime +9 · Sector +6 = 68</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2018,13 +2018,13 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="H6" t="n">
         <v>99</v>
       </c>
       <c r="I6" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2040,11 +2040,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2343.5</v>
+        <v>2393.1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2284 - 2403</t>
+          <t>2332 - 2454</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2062,11 +2062,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.4%)</t>
+          <t>Above 200-DMA (+10.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2075,11 +2075,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>35152</v>
+        <v>35897</v>
       </c>
       <c r="W6" t="n">
         <v>15</v>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; TORNTPHARM: 77, CIPLA: 71, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 68; TORNTPHARM: 78, ZYDUSLIFE: 72, BIOCON: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.4%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.6%) • sector strength 59/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Regime +9 · Trend/Tech +6 · Sector +4 = 66</t>
+          <t>Risk/Vol +24 · Historical +21 · Regime +9 · Trend/Tech +6 · Sector +6 = 66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2133,58 +2133,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I7" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1850.7</v>
+        <v>25675</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1801 - 1900</t>
+          <t>24956 - 26394</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.2%)</t>
+          <t>Below 200-DMA (-7.9%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>20358</v>
+        <v>25675</v>
       </c>
       <c r="W7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>7.1</v>
+        <v>12.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2217,27 +2217,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 66; TATACOMM: 53, INDUSTOWER: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 66; TORNTPHARM: 78, ZYDUSLIFE: 72, BIOCON: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-5.2%) • sector strength 41/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-7.9%) • sector strength 59/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +21 · Regime +9 · Trend/Tech +5 · Sector +5 = 64</t>
+          <t>Risk/Vol +24 · Historical +23 · Regime +9 · Trend/Tech +6 · Sector +4 = 66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2251,58 +2251,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I8" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>25585</v>
+        <v>1845</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>24868 - 26302</t>
+          <t>1796 - 1894</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3% to +15%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.3%)</t>
+          <t>Below 200-DMA (-5.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>25585</v>
+        <v>33210</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="X8" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 64; TORNTPHARM: 77, CIPLA: 71, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 66; TATACOMM: 53, INDUSTOWER: 51</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-8.3%) • sector strength 47/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-5.5%) • sector strength 35/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -2351,11 +2351,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Sector +8 · Trend/Tech +5 = 62</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Sector +7 · Trend/Tech +5 = 61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2372,13 +2372,13 @@
         <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H9" t="n">
         <v>92</v>
       </c>
       <c r="I9" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2394,11 +2394,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>283.9</v>
+        <v>285.5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>275 - 293</t>
+          <t>277 - 294</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2412,15 +2412,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.8%)</t>
+          <t>Below 200-DMA (-0.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2429,17 +2429,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>19305</v>
+        <v>17130</v>
       </c>
       <c r="W9" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="X9" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2453,12 +2453,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 62; NTPC: 70, CESC: 61, NHPC: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 61; NTPC: 77, JSWENERGY: 58, NHPC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.8%) • sector strength 76/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.2%) • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2490,13 +2490,13 @@
         <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" t="n">
         <v>96</v>
       </c>
       <c r="I10" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1813.6</v>
+        <v>1799</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1763 - 1865</t>
+          <t>1748 - 1850</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2534,11 +2534,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.6%)</t>
+          <t>Below 200-DMA (-4.3%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2547,17 +2547,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>27204</v>
+        <v>17990</v>
       </c>
       <c r="W10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="X10" t="n">
-        <v>9.1</v>
+        <v>6.5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 60; ICICIBANK: 72, KOTAKBANK: 71, AXISBANK: 62. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 60; ICICIBANK: 71, LICI: 64, AXISBANK: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.6%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-4.3%) • sector strength 41/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +1 = 54</t>
+          <t>Risk/Vol +22 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2608,13 +2608,13 @@
         <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
         <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2630,11 +2630,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1318.1</v>
+        <v>1309.9</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1276 - 1360</t>
+          <t>1269 - 1351</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2652,11 +2652,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.2%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2665,17 +2665,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>25044</v>
+        <v>24888</v>
       </c>
       <c r="W11" t="n">
         <v>19</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 54; GAIL: 59, IGL: 51, PETRONET: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 54; GAIL: 60, IGL: 52, PETRONET: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.2%) • sector strength 12/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
         <v>98</v>
@@ -2748,11 +2748,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>5237</v>
+        <v>5229</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5099 - 5375</t>
+          <t>5091 - 5367</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2770,11 +2770,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.6%)</t>
+          <t>Below 200-DMA (-9.7%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2783,17 +2783,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>15711</v>
+        <v>26145</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>8.9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.6%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.7%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2823,11 +2823,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Regime +9 · Trend/Tech +8 · Historical +7 · Sector +2 = 48</t>
+          <t>Risk/Vol +23 · Regime +9 · Historical +7 · Trend/Tech +6 · Sector +2 = 47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2844,13 +2844,13 @@
         <v>24</v>
       </c>
       <c r="G13" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2866,11 +2866,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>25735</v>
+        <v>25600</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>24925 - 26545</t>
+          <t>24794 - 26406</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2884,15 +2884,15 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-3.1%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="V13" t="n">
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2925,12 +2925,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 48; GRASIM: 75, ULTRACEMCO: 57, RAMCOCEM: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 47; GRASIM: 75, ULTRACEMCO: 56, RAMCOCEM: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk Cement holding (low vol) • below 200-dma (-2.7%) • sector strength 18/100 • regime cautious (partial deploy) • 5 similar past recs: 40% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Cement holding (low vol) • below 200-dma (-3.1%) • sector strength 24/100 • regime cautious (partial deploy) • 5 similar past recs: 40% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27719,7 +27719,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27729,12 +27729,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27744,12 +27744,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27759,12 +27759,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27774,12 +27774,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27789,12 +27789,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27804,12 +27804,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27819,12 +27819,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APOLLOHOSP (78)</t>
+          <t>TORNTPHARM (82)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHREECEM (47)</t>
+          <t>ITC (55)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -700,7 +700,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-29  /  2026-06-29</t>
+          <t>2026-07-14  /  2026-07-14</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rs5L</t>
+          <t>Rs1L</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs300,000 (60%)</t>
+          <t>Rs60,000 (60%)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs200,000 (40%)</t>
+          <t>Rs40,000 (40%)</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs512,500</t>
+          <t>Rs102,500</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rs602,000</t>
+          <t>Rs120,400</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rs458,000</t>
+          <t>Rs91,600</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
+          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
+          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -1525,11 +1525,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +19 · Trend/Tech +16 · Regime +9 · Sector +9 = 78</t>
+          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +17 · Regime +9 · Sector +9 = 82</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1543,13 +1543,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="I2" t="n">
         <v>88</v>
@@ -1559,20 +1559,20 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>TORNTPHARM</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8717.5</v>
+        <v>4967.1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8497 - 8938</t>
+          <t>4830 - 5104</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1586,15 +1586,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+14.4%)</t>
+          <t>Above 200-DMA (+21.9%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1603,21 +1603,21 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>26152</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>10.1</v>
+        <v>7.9</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Healthcare name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 78; FORTIS: 68, MAXHEALTH: 68, LALPATHLAB: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TORNTPHARM: 82; SUNPHARMA: 78, CIPLA: 76, BIOCON: 74</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+21.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +6.2%</t>
         </is>
       </c>
     </row>
@@ -1643,16 +1643,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +23 · Trend/Tech +13 · Regime +9 · Sector +7 = 77</t>
+          <t>Risk/Vol +25 · Historical +19 · Trend/Tech +18 · Regime +9 · Sector +9 = 80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1661,36 +1661,36 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I3" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>355.5</v>
+        <v>8806</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>345 - 366</t>
+          <t>8591 - 9021</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1704,15 +1704,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+0.0%)</t>
+          <t>Above 200-DMA (+14.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1721,21 +1721,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>18133</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>6.1</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Healthcare name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 77; POWERGRID: 61, JSWENERGY: 58, NHPC: 57</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 80; FORTIS: 72, MAXHEALTH: 71, LALPATHLAB: 63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • above 200-dma (+0.0%) • sector strength 71/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.8%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1761,11 +1761,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +3 = 72</t>
+          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +6 = 75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1782,13 +1782,13 @@
         <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1804,11 +1804,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>841.5</v>
+        <v>845.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>821 - 862</t>
+          <t>825 - 865</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1822,15 +1822,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.0%)</t>
+          <t>Above 200-DMA (+10.5%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1839,17 +1839,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>25246</v>
+        <v>5917</v>
       </c>
       <c r="W4" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>8.6</v>
+        <v>10.4</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 72; NESTLEIND: 73, VBL: 61, UNITDSPR: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 75; NESTLEIND: 76, UNITDSPR: 66, TATACONSUM: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+11.0%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+10.5%) • outperforming Nifty • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
@@ -1879,11 +1879,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +14 · Regime +9 · Sector +4 = 71</t>
+          <t>Risk/Vol +25 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +9 = 73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1897,58 +1897,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I5" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1389.7</v>
+        <v>2488.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1349 - 1430</t>
+          <t>2427 - 2550</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+3.3%)</t>
+          <t>Above 200-DMA (+13.7%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1957,21 +1957,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>13897</v>
+        <v>4978</v>
       </c>
       <c r="W5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 71; LICI: 64, AXISBANK: 63, KOTAKBANK: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 73; TORNTPHARM: 82, SUNPHARMA: 78, CIPLA: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.3%) • sector strength 41/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+13.7%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1997,11 +1997,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +15 · Trend/Tech +13 · Regime +9 · Sector +6 = 68</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +4 = 73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2015,58 +2015,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="H6" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I6" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2393.1</v>
+        <v>1397.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2332 - 2454</t>
+          <t>1358 - 1438</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.6%)</t>
+          <t>Above 200-DMA (+3.9%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2075,21 +2075,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>35897</v>
+        <v>2795</v>
       </c>
       <c r="W6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>12.2</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 68; TORNTPHARM: 78, ZYDUSLIFE: 72, BIOCON: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 73; LICI: 64, SBIN: 64, FEDERALBNK: 62</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.6%) • sector strength 59/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.9%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -2115,11 +2115,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +21 · Regime +9 · Trend/Tech +6 · Sector +6 = 66</t>
+          <t>Risk/Vol +24 · Historical +23 · Regime +9 · Trend/Tech +8 · Sector +5 = 69</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2133,58 +2133,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H7" t="n">
         <v>97</v>
       </c>
       <c r="I7" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>25675</v>
+        <v>1905.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>24956 - 26394</t>
+          <t>1853 - 1958</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3% to +15%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.9%)</t>
+          <t>Below 200-DMA (-2.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2193,21 +2193,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>25675</v>
+        <v>5717</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X7" t="n">
-        <v>12.7</v>
+        <v>10.8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ABBOTINDIA: 66; TORNTPHARM: 78, ZYDUSLIFE: 72, BIOCON: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 69; INDUSTOWER: 55, TATACOMM: 51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-7.9%) • sector strength 59/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +24.6%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.3%) • sector strength 47/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -2233,76 +2233,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Regime +9 · Trend/Tech +6 · Sector +4 = 66</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +7 · Trend/Tech +4 = 69</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="H8" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1845</v>
+        <v>353</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1796 - 1894</t>
+          <t>343 - 363</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.5%)</t>
+          <t>Below 200-DMA (-1.0%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>33210</v>
+        <v>3530</v>
       </c>
       <c r="W8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="X8" t="n">
-        <v>11.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2335,27 +2335,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 66; TATACOMM: 53, INDUSTOWER: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 69; NHPC: 60, POWERGRID: 60, JSWENERGY: 59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-5.5%) • sector strength 35/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-1.0%) • sector strength 71/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Sector +7 · Trend/Tech +5 = 61</t>
+          <t>Risk/Vol +22 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +6 = 69</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2365,62 +2365,62 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G9" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>285.5</v>
+        <v>1568</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>277 - 294</t>
+          <t>1518 - 1618</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.2%)</t>
+          <t>Above 200-DMA (+7.0%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2429,21 +2429,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>17130</v>
+        <v>1568</v>
       </c>
       <c r="W9" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 61; NTPC: 77, JSWENERGY: 58, NHPC: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 69; NAVINFLUOR: 61, BALRAMCHIN: 59, DEEPAKNTR: 59</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.2%) • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+7.0%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +16 · Regime +9 · Trend/Tech +7 · Sector +4 = 60</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Sector +7 · Trend/Tech +4 = 60</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2483,40 +2483,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="H10" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I10" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1799</v>
+        <v>284.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1748 - 1850</t>
+          <t>276 - 293</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2534,11 +2534,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.3%)</t>
+          <t>Below 200-DMA (-0.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2547,21 +2547,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>17990</v>
+        <v>3131</v>
       </c>
       <c r="W10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X10" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2571,27 +2571,27 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 60; ICICIBANK: 71, LICI: 64, AXISBANK: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 60; NTPC: 69, NHPC: 60, JSWENERGY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-4.3%) • sector strength 41/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.5%) • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +2 = 54</t>
+          <t>Risk/Vol +24 · Historical +16 · Regime +9 · Trend/Tech +5 · Sector +4 = 58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2605,58 +2605,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I11" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1309.9</v>
+        <v>1763.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1269 - 1351</t>
+          <t>1714 - 1813</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-1% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-6.0%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2665,21 +2665,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>24888</v>
+        <v>5290</v>
       </c>
       <c r="W11" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="X11" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2689,27 +2689,27 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 54; GAIL: 60, IGL: 52, PETRONET: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 58; ICICIBANK: 73, LICI: 64, SBIN: 64. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.8%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-6.0%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +5 · Sector +3 = 51</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +1 = 56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2723,58 +2723,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="I12" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>5229</v>
+        <v>1295.2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5091 - 5367</t>
+          <t>1256 - 1334</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1% to +7%</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.7%)</t>
+          <t>Below 200-DMA (-8.5%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>67</v>
+        <v>44</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2783,21 +2783,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>26145</v>
+        <v>3886</v>
       </c>
       <c r="W12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X12" t="n">
-        <v>8.9</v>
+        <v>8.4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2807,27 +2807,27 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; NESTLEIND: 73, MARICO: 72, VBL: 61. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 56; GAIL: 60, ONGC: 48, IGL: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.7%) • sector strength 29/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.5%) • sector strength 12/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Regime +9 · Historical +7 · Trend/Tech +6 · Sector +2 = 47</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Sector +6 · Trend/Tech +3 = 55</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2837,62 +2837,62 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I13" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SHREECEM</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>25600</v>
+        <v>280.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>24794 - 26406</t>
+          <t>273 - 288</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-11% to +3%</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.1%)</t>
+          <t>Below 200-DMA (-17.9%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2901,21 +2901,21 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>5045</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="X13" t="n">
-        <v>4.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Risk/Vol + Regime strongest; chosen as a lowest-volatility Cement name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SHREECEM: 47; GRASIM: 75, ULTRACEMCO: 56, RAMCOCEM: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; NESTLEIND: 76, MARICO: 75, UNITDSPR: 66. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk Cement holding (low vol) • below 200-dma (-3.1%) • sector strength 24/100 • regime cautious (partial deploy) • 5 similar past recs: 40% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.9%) • sector strength 65/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -3030,10 +3030,10 @@
         <v>2021</v>
       </c>
       <c r="B2" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C2" t="n">
-        <v>542732</v>
+        <v>108546</v>
       </c>
       <c r="D2" t="n">
         <v>8.5</v>
@@ -3071,7 +3071,7 @@
         <v>-14.9</v>
       </c>
       <c r="O2" t="n">
-        <v>43738</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="3">
@@ -3079,10 +3079,10 @@
         <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C3" t="n">
-        <v>600703</v>
+        <v>120141</v>
       </c>
       <c r="D3" t="n">
         <v>20.1</v>
@@ -3120,7 +3120,7 @@
         <v>-19.8</v>
       </c>
       <c r="O3" t="n">
-        <v>93560</v>
+        <v>19532</v>
       </c>
     </row>
     <row r="4">
@@ -3128,10 +3128,10 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C4" t="n">
-        <v>722531</v>
+        <v>144506</v>
       </c>
       <c r="D4" t="n">
         <v>44.5</v>
@@ -3169,7 +3169,7 @@
         <v>-16.5</v>
       </c>
       <c r="O4" t="n">
-        <v>176947</v>
+        <v>30402</v>
       </c>
     </row>
     <row r="5">
@@ -3177,10 +3177,10 @@
         <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C5" t="n">
-        <v>551527</v>
+        <v>110305</v>
       </c>
       <c r="D5" t="n">
         <v>10.3</v>
@@ -3218,7 +3218,7 @@
         <v>-26</v>
       </c>
       <c r="O5" t="n">
-        <v>56158</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="6">
@@ -3226,10 +3226,10 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C6" t="n">
-        <v>531876</v>
+        <v>106375</v>
       </c>
       <c r="D6" t="n">
         <v>6.4</v>
@@ -3267,7 +3267,7 @@
         <v>-23.6</v>
       </c>
       <c r="O6" t="n">
-        <v>15954</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
@@ -3275,10 +3275,10 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C7" t="n">
-        <v>504000</v>
+        <v>100800</v>
       </c>
       <c r="D7" t="n">
         <v>0.8</v>
@@ -3316,7 +3316,7 @@
         <v>-16.7</v>
       </c>
       <c r="O7" t="n">
-        <v>7126</v>
+        <v>1322</v>
       </c>
     </row>
   </sheetData>
@@ -3468,16 +3468,16 @@
         <v>22031.2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>66945</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>88125</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>21180</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>31.64</v>
@@ -3549,16 +3549,16 @@
         <v>4737.4</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>32560</v>
+        <v>3618</v>
       </c>
       <c r="I3" t="n">
-        <v>42637</v>
+        <v>4737</v>
       </c>
       <c r="J3" t="n">
-        <v>10077</v>
+        <v>1120</v>
       </c>
       <c r="K3" t="n">
         <v>30.95</v>
@@ -3630,16 +3630,16 @@
         <v>675.9</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>16725</v>
+        <v>3136</v>
       </c>
       <c r="I4" t="n">
-        <v>21629</v>
+        <v>4055</v>
       </c>
       <c r="J4" t="n">
-        <v>4904</v>
+        <v>920</v>
       </c>
       <c r="K4" t="n">
         <v>29.32</v>
@@ -3711,16 +3711,16 @@
         <v>3990.05</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>32195</v>
+        <v>6439</v>
       </c>
       <c r="I5" t="n">
-        <v>39900</v>
+        <v>7980</v>
       </c>
       <c r="J5" t="n">
-        <v>7706</v>
+        <v>1541</v>
       </c>
       <c r="K5" t="n">
         <v>23.93</v>
@@ -3792,16 +3792,16 @@
         <v>1834.7</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>19162</v>
+        <v>3194</v>
       </c>
       <c r="I6" t="n">
-        <v>22016</v>
+        <v>3669</v>
       </c>
       <c r="J6" t="n">
-        <v>2854</v>
+        <v>476</v>
       </c>
       <c r="K6" t="n">
         <v>14.89</v>
@@ -3873,16 +3873,16 @@
         <v>3730.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>20049</v>
+        <v>3342</v>
       </c>
       <c r="I7" t="n">
-        <v>22381</v>
+        <v>3730</v>
       </c>
       <c r="J7" t="n">
-        <v>2332</v>
+        <v>389</v>
       </c>
       <c r="K7" t="n">
         <v>11.63</v>
@@ -3954,16 +3954,16 @@
         <v>1208.63</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>20607</v>
+        <v>3254</v>
       </c>
       <c r="I8" t="n">
-        <v>22964</v>
+        <v>3626</v>
       </c>
       <c r="J8" t="n">
-        <v>2357</v>
+        <v>372</v>
       </c>
       <c r="K8" t="n">
         <v>11.44</v>
@@ -4035,16 +4035,16 @@
         <v>3921.1</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>39554</v>
+        <v>7192</v>
       </c>
       <c r="I9" t="n">
-        <v>43132</v>
+        <v>7842</v>
       </c>
       <c r="J9" t="n">
-        <v>3578</v>
+        <v>651</v>
       </c>
       <c r="K9" t="n">
         <v>9.050000000000001</v>
@@ -4116,16 +4116,16 @@
         <v>9740.799999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>35809</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>38963</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3154</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>8.81</v>
@@ -4133,9 +4133,15 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>88</v>
+      </c>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -4191,16 +4197,16 @@
         <v>2321.6</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>34794</v>
+        <v>6524</v>
       </c>
       <c r="I11" t="n">
-        <v>37146</v>
+        <v>6965</v>
       </c>
       <c r="J11" t="n">
-        <v>2351</v>
+        <v>441</v>
       </c>
       <c r="K11" t="n">
         <v>6.76</v>
@@ -4272,16 +4278,16 @@
         <v>1665.15</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>20285</v>
+        <v>3121</v>
       </c>
       <c r="I12" t="n">
-        <v>21647</v>
+        <v>3330</v>
       </c>
       <c r="J12" t="n">
-        <v>1362</v>
+        <v>210</v>
       </c>
       <c r="K12" t="n">
         <v>6.71</v>
@@ -4353,16 +4359,16 @@
         <v>729.45</v>
       </c>
       <c r="G13" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>34973</v>
+        <v>6858</v>
       </c>
       <c r="I13" t="n">
-        <v>37202</v>
+        <v>7294</v>
       </c>
       <c r="J13" t="n">
-        <v>2229</v>
+        <v>437</v>
       </c>
       <c r="K13" t="n">
         <v>6.37</v>
@@ -4434,16 +4440,16 @@
         <v>1687.8</v>
       </c>
       <c r="G14" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>58079</v>
+        <v>10249</v>
       </c>
       <c r="I14" t="n">
-        <v>57385</v>
+        <v>10127</v>
       </c>
       <c r="J14" t="n">
-        <v>-694</v>
+        <v>-122</v>
       </c>
       <c r="K14" t="n">
         <v>-1.19</v>
@@ -4515,16 +4521,16 @@
         <v>178.85</v>
       </c>
       <c r="G15" t="n">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>20373</v>
+        <v>4002</v>
       </c>
       <c r="I15" t="n">
-        <v>20031</v>
+        <v>3935</v>
       </c>
       <c r="J15" t="n">
-        <v>-342</v>
+        <v>-67</v>
       </c>
       <c r="K15" t="n">
         <v>-1.68</v>
@@ -4596,16 +4602,16 @@
         <v>1928.9</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>29596</v>
+        <v>4228</v>
       </c>
       <c r="I16" t="n">
-        <v>27005</v>
+        <v>3858</v>
       </c>
       <c r="J16" t="n">
-        <v>-2591</v>
+        <v>-370</v>
       </c>
       <c r="K16" t="n">
         <v>-8.76</v>
@@ -4677,16 +4683,16 @@
         <v>1898.45</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>31638</v>
+        <v>4995</v>
       </c>
       <c r="I17" t="n">
-        <v>36071</v>
+        <v>5695</v>
       </c>
       <c r="J17" t="n">
-        <v>4433</v>
+        <v>700</v>
       </c>
       <c r="K17" t="n">
         <v>14.01</v>
@@ -4758,16 +4764,16 @@
         <v>30.95</v>
       </c>
       <c r="G18" t="n">
-        <v>799</v>
+        <v>159</v>
       </c>
       <c r="H18" t="n">
-        <v>22692</v>
+        <v>4516</v>
       </c>
       <c r="I18" t="n">
-        <v>24729</v>
+        <v>4921</v>
       </c>
       <c r="J18" t="n">
-        <v>2037</v>
+        <v>405</v>
       </c>
       <c r="K18" t="n">
         <v>8.98</v>
@@ -4839,16 +4845,16 @@
         <v>31.2</v>
       </c>
       <c r="G19" t="n">
-        <v>714</v>
+        <v>142</v>
       </c>
       <c r="H19" t="n">
-        <v>20777</v>
+        <v>4132</v>
       </c>
       <c r="I19" t="n">
-        <v>22277</v>
+        <v>4430</v>
       </c>
       <c r="J19" t="n">
-        <v>1499</v>
+        <v>298</v>
       </c>
       <c r="K19" t="n">
         <v>7.22</v>
@@ -4920,16 +4926,16 @@
         <v>1626.05</v>
       </c>
       <c r="G20" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>41588</v>
+        <v>7701</v>
       </c>
       <c r="I20" t="n">
-        <v>43903</v>
+        <v>8130</v>
       </c>
       <c r="J20" t="n">
-        <v>2316</v>
+        <v>429</v>
       </c>
       <c r="K20" t="n">
         <v>5.57</v>
@@ -5001,16 +5007,16 @@
         <v>1236.98</v>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>30216</v>
+        <v>6043</v>
       </c>
       <c r="I21" t="n">
-        <v>30924</v>
+        <v>6185</v>
       </c>
       <c r="J21" t="n">
-        <v>709</v>
+        <v>142</v>
       </c>
       <c r="K21" t="n">
         <v>2.35</v>
@@ -5082,16 +5088,16 @@
         <v>3817.75</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>26111</v>
+        <v>3730</v>
       </c>
       <c r="I22" t="n">
-        <v>26724</v>
+        <v>3818</v>
       </c>
       <c r="J22" t="n">
-        <v>613</v>
+        <v>88</v>
       </c>
       <c r="K22" t="n">
         <v>2.35</v>
@@ -5163,16 +5169,16 @@
         <v>1209.4</v>
       </c>
       <c r="G23" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>35062</v>
+        <v>6045</v>
       </c>
       <c r="I23" t="n">
-        <v>35073</v>
+        <v>6047</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>0.03</v>
@@ -5244,16 +5250,16 @@
         <v>1091.18</v>
       </c>
       <c r="G24" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>35513</v>
+        <v>6873</v>
       </c>
       <c r="I24" t="n">
-        <v>33827</v>
+        <v>6547</v>
       </c>
       <c r="J24" t="n">
-        <v>-1686</v>
+        <v>-326</v>
       </c>
       <c r="K24" t="n">
         <v>-4.75</v>
@@ -5325,16 +5331,16 @@
         <v>9043.200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>19482</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>18086</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-1395</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>-7.16</v>
@@ -5342,9 +5348,15 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-64</v>
+      </c>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5400,16 +5412,16 @@
         <v>3617.55</v>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>47053</v>
+        <v>7842</v>
       </c>
       <c r="I26" t="n">
-        <v>43411</v>
+        <v>7235</v>
       </c>
       <c r="J26" t="n">
-        <v>-3643</v>
+        <v>-607</v>
       </c>
       <c r="K26" t="n">
         <v>-7.74</v>
@@ -5481,16 +5493,16 @@
         <v>650.5</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>36472</v>
+        <v>7294</v>
       </c>
       <c r="I27" t="n">
-        <v>32525</v>
+        <v>6505</v>
       </c>
       <c r="J27" t="n">
-        <v>-3948</v>
+        <v>-790</v>
       </c>
       <c r="K27" t="n">
         <v>-10.82</v>
@@ -5562,16 +5574,16 @@
         <v>1917.45</v>
       </c>
       <c r="G28" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>37067</v>
+        <v>6541</v>
       </c>
       <c r="I28" t="n">
-        <v>32597</v>
+        <v>5752</v>
       </c>
       <c r="J28" t="n">
-        <v>-4470</v>
+        <v>-789</v>
       </c>
       <c r="K28" t="n">
         <v>-12.06</v>
@@ -5637,16 +5649,16 @@
         <v>2476.6</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>25632</v>
+        <v>2848</v>
       </c>
       <c r="I29" t="n">
-        <v>22289</v>
+        <v>2477</v>
       </c>
       <c r="J29" t="n">
-        <v>-3342</v>
+        <v>-371</v>
       </c>
       <c r="K29" t="n">
         <v>-13.04</v>
@@ -5718,16 +5730,16 @@
         <v>1463.8</v>
       </c>
       <c r="G30" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>43883</v>
+        <v>8439</v>
       </c>
       <c r="I30" t="n">
-        <v>38059</v>
+        <v>7319</v>
       </c>
       <c r="J30" t="n">
-        <v>-5824</v>
+        <v>-1120</v>
       </c>
       <c r="K30" t="n">
         <v>-13.27</v>
@@ -5799,16 +5811,16 @@
         <v>3277.1</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>26968</v>
+        <v>3853</v>
       </c>
       <c r="I31" t="n">
-        <v>22940</v>
+        <v>3277</v>
       </c>
       <c r="J31" t="n">
-        <v>-4028</v>
+        <v>-576</v>
       </c>
       <c r="K31" t="n">
         <v>-14.94</v>
@@ -5880,16 +5892,16 @@
         <v>3809.7</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>19663</v>
+        <v>3277</v>
       </c>
       <c r="I32" t="n">
-        <v>22858</v>
+        <v>3810</v>
       </c>
       <c r="J32" t="n">
-        <v>3196</v>
+        <v>533</v>
       </c>
       <c r="K32" t="n">
         <v>16.25</v>
@@ -5961,16 +5973,16 @@
         <v>1586.7</v>
       </c>
       <c r="G33" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>62943</v>
+        <v>11710</v>
       </c>
       <c r="I33" t="n">
-        <v>68228</v>
+        <v>12694</v>
       </c>
       <c r="J33" t="n">
-        <v>5285</v>
+        <v>983</v>
       </c>
       <c r="K33" t="n">
         <v>8.4</v>
@@ -6042,16 +6054,16 @@
         <v>804.13</v>
       </c>
       <c r="G34" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>43310</v>
+        <v>8358</v>
       </c>
       <c r="I34" t="n">
-        <v>45835</v>
+        <v>8845</v>
       </c>
       <c r="J34" t="n">
-        <v>2525</v>
+        <v>487</v>
       </c>
       <c r="K34" t="n">
         <v>5.83</v>
@@ -6123,16 +6135,16 @@
         <v>1253.83</v>
       </c>
       <c r="G35" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>44531</v>
+        <v>8659</v>
       </c>
       <c r="I35" t="n">
-        <v>45138</v>
+        <v>8777</v>
       </c>
       <c r="J35" t="n">
-        <v>607</v>
+        <v>118</v>
       </c>
       <c r="K35" t="n">
         <v>1.36</v>
@@ -6204,16 +6216,16 @@
         <v>3814.8</v>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>34360</v>
+        <v>3818</v>
       </c>
       <c r="I36" t="n">
-        <v>34333</v>
+        <v>3815</v>
       </c>
       <c r="J36" t="n">
-        <v>-27</v>
+        <v>-3</v>
       </c>
       <c r="K36" t="n">
         <v>-0.08</v>
@@ -6285,16 +6297,16 @@
         <v>1861.1</v>
       </c>
       <c r="G37" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>36071</v>
+        <v>5695</v>
       </c>
       <c r="I37" t="n">
-        <v>35361</v>
+        <v>5583</v>
       </c>
       <c r="J37" t="n">
-        <v>-710</v>
+        <v>-112</v>
       </c>
       <c r="K37" t="n">
         <v>-1.97</v>
@@ -6366,16 +6378,16 @@
         <v>1836.05</v>
       </c>
       <c r="G38" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>23074</v>
+        <v>3846</v>
       </c>
       <c r="I38" t="n">
-        <v>22033</v>
+        <v>3672</v>
       </c>
       <c r="J38" t="n">
-        <v>-1042</v>
+        <v>-174</v>
       </c>
       <c r="K38" t="n">
         <v>-4.51</v>
@@ -6447,16 +6459,16 @@
         <v>828.65</v>
       </c>
       <c r="G39" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>21024</v>
+        <v>3504</v>
       </c>
       <c r="I39" t="n">
-        <v>19888</v>
+        <v>3315</v>
       </c>
       <c r="J39" t="n">
-        <v>-1136</v>
+        <v>-189</v>
       </c>
       <c r="K39" t="n">
         <v>-5.41</v>
@@ -6528,16 +6540,16 @@
         <v>2332.25</v>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>22289</v>
+        <v>2477</v>
       </c>
       <c r="I40" t="n">
-        <v>20990</v>
+        <v>2332</v>
       </c>
       <c r="J40" t="n">
-        <v>-1299</v>
+        <v>-144</v>
       </c>
       <c r="K40" t="n">
         <v>-5.83</v>
@@ -6690,16 +6702,16 @@
         <v>1701.8</v>
       </c>
       <c r="G42" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>37115</v>
+        <v>7423</v>
       </c>
       <c r="I42" t="n">
-        <v>34036</v>
+        <v>6807</v>
       </c>
       <c r="J42" t="n">
-        <v>-3079</v>
+        <v>-616</v>
       </c>
       <c r="K42" t="n">
         <v>-8.300000000000001</v>
@@ -6771,16 +6783,16 @@
         <v>901.16</v>
       </c>
       <c r="G43" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>45259</v>
+        <v>8855</v>
       </c>
       <c r="I43" t="n">
-        <v>41453</v>
+        <v>8110</v>
       </c>
       <c r="J43" t="n">
-        <v>-3806</v>
+        <v>-745</v>
       </c>
       <c r="K43" t="n">
         <v>-8.41</v>
@@ -6852,16 +6864,16 @@
         <v>199.6</v>
       </c>
       <c r="G44" t="n">
-        <v>167</v>
+        <v>33</v>
       </c>
       <c r="H44" t="n">
-        <v>36540</v>
+        <v>7220</v>
       </c>
       <c r="I44" t="n">
-        <v>33333</v>
+        <v>6587</v>
       </c>
       <c r="J44" t="n">
-        <v>-3206</v>
+        <v>-634</v>
       </c>
       <c r="K44" t="n">
         <v>-8.779999999999999</v>
@@ -6933,16 +6945,16 @@
         <v>569.65</v>
       </c>
       <c r="G45" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>24068</v>
+        <v>4554</v>
       </c>
       <c r="I45" t="n">
-        <v>21077</v>
+        <v>3988</v>
       </c>
       <c r="J45" t="n">
-        <v>-2991</v>
+        <v>-566</v>
       </c>
       <c r="K45" t="n">
         <v>-12.43</v>
@@ -7014,16 +7026,16 @@
         <v>6726.15</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>15448</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>13452</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>-1996</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>-12.92</v>
@@ -7095,16 +7107,16 @@
         <v>2350.15</v>
       </c>
       <c r="G47" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>39141</v>
+        <v>6807</v>
       </c>
       <c r="I47" t="n">
-        <v>54053</v>
+        <v>9401</v>
       </c>
       <c r="J47" t="n">
-        <v>14912</v>
+        <v>2593</v>
       </c>
       <c r="K47" t="n">
         <v>38.1</v>
@@ -7176,16 +7188,16 @@
         <v>979.3</v>
       </c>
       <c r="G48" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>27194</v>
+        <v>4944</v>
       </c>
       <c r="I48" t="n">
-        <v>32317</v>
+        <v>5876</v>
       </c>
       <c r="J48" t="n">
-        <v>5123</v>
+        <v>932</v>
       </c>
       <c r="K48" t="n">
         <v>18.84</v>
@@ -7257,16 +7269,16 @@
         <v>220.95</v>
       </c>
       <c r="G49" t="n">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="H49" t="n">
-        <v>26347</v>
+        <v>5190</v>
       </c>
       <c r="I49" t="n">
-        <v>29165</v>
+        <v>5745</v>
       </c>
       <c r="J49" t="n">
-        <v>2818</v>
+        <v>555</v>
       </c>
       <c r="K49" t="n">
         <v>10.7</v>
@@ -7419,16 +7431,16 @@
         <v>919.4400000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>49564</v>
+        <v>9913</v>
       </c>
       <c r="I51" t="n">
-        <v>50569</v>
+        <v>10114</v>
       </c>
       <c r="J51" t="n">
-        <v>1005</v>
+        <v>201</v>
       </c>
       <c r="K51" t="n">
         <v>2.03</v>
@@ -7500,16 +7512,16 @@
         <v>878</v>
       </c>
       <c r="G52" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>28577</v>
+        <v>5196</v>
       </c>
       <c r="I52" t="n">
-        <v>28974</v>
+        <v>5268</v>
       </c>
       <c r="J52" t="n">
-        <v>397</v>
+        <v>72</v>
       </c>
       <c r="K52" t="n">
         <v>1.39</v>
@@ -7581,16 +7593,16 @@
         <v>3773.05</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>22858</v>
+        <v>3810</v>
       </c>
       <c r="I53" t="n">
-        <v>22638</v>
+        <v>3773</v>
       </c>
       <c r="J53" t="n">
-        <v>-220</v>
+        <v>-37</v>
       </c>
       <c r="K53" t="n">
         <v>-0.96</v>
@@ -7662,16 +7674,16 @@
         <v>1569.15</v>
       </c>
       <c r="G54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H54" t="n">
-        <v>39668</v>
+        <v>7934</v>
       </c>
       <c r="I54" t="n">
-        <v>39229</v>
+        <v>7846</v>
       </c>
       <c r="J54" t="n">
-        <v>-439</v>
+        <v>-88</v>
       </c>
       <c r="K54" t="n">
         <v>-1.11</v>
@@ -7743,16 +7755,16 @@
         <v>1232.25</v>
       </c>
       <c r="G55" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>24333</v>
+        <v>4056</v>
       </c>
       <c r="I55" t="n">
-        <v>22180</v>
+        <v>3697</v>
       </c>
       <c r="J55" t="n">
-        <v>-2153</v>
+        <v>-359</v>
       </c>
       <c r="K55" t="n">
         <v>-8.85</v>
@@ -7824,16 +7836,16 @@
         <v>693.95</v>
       </c>
       <c r="G56" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H56" t="n">
-        <v>39863</v>
+        <v>7666</v>
       </c>
       <c r="I56" t="n">
-        <v>36085</v>
+        <v>6940</v>
       </c>
       <c r="J56" t="n">
-        <v>-3778</v>
+        <v>-726</v>
       </c>
       <c r="K56" t="n">
         <v>-9.48</v>
@@ -7905,16 +7917,16 @@
         <v>837.7</v>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
-        <v>27873</v>
+        <v>5575</v>
       </c>
       <c r="I57" t="n">
-        <v>25131</v>
+        <v>5026</v>
       </c>
       <c r="J57" t="n">
-        <v>-2742</v>
+        <v>-548</v>
       </c>
       <c r="K57" t="n">
         <v>-9.84</v>
@@ -7986,16 +7998,16 @@
         <v>19.95</v>
       </c>
       <c r="G58" t="n">
-        <v>1790</v>
+        <v>358</v>
       </c>
       <c r="H58" t="n">
-        <v>39648</v>
+        <v>7930</v>
       </c>
       <c r="I58" t="n">
-        <v>35710</v>
+        <v>7142</v>
       </c>
       <c r="J58" t="n">
-        <v>-3938</v>
+        <v>-788</v>
       </c>
       <c r="K58" t="n">
         <v>-9.93</v>
@@ -8067,16 +8079,16 @@
         <v>3260.75</v>
       </c>
       <c r="G59" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>38148</v>
+        <v>7630</v>
       </c>
       <c r="I59" t="n">
-        <v>32608</v>
+        <v>6522</v>
       </c>
       <c r="J59" t="n">
-        <v>-5540</v>
+        <v>-1108</v>
       </c>
       <c r="K59" t="n">
         <v>-14.52</v>
@@ -8146,16 +8158,16 @@
         <v>1556.15</v>
       </c>
       <c r="G60" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>23869</v>
+        <v>3672</v>
       </c>
       <c r="I60" t="n">
-        <v>20230</v>
+        <v>3112</v>
       </c>
       <c r="J60" t="n">
-        <v>-3639</v>
+        <v>-560</v>
       </c>
       <c r="K60" t="n">
         <v>-15.24</v>
@@ -8227,16 +8239,16 @@
         <v>1491.65</v>
       </c>
       <c r="G61" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
-        <v>31639</v>
+        <v>5583</v>
       </c>
       <c r="I61" t="n">
-        <v>25358</v>
+        <v>4475</v>
       </c>
       <c r="J61" t="n">
-        <v>-6281</v>
+        <v>-1108</v>
       </c>
       <c r="K61" t="n">
         <v>-19.85</v>
@@ -8306,16 +8318,16 @@
         <v>32.7</v>
       </c>
       <c r="G62" t="n">
-        <v>819</v>
+        <v>163</v>
       </c>
       <c r="H62" t="n">
-        <v>22195</v>
+        <v>4417</v>
       </c>
       <c r="I62" t="n">
-        <v>26781</v>
+        <v>5330</v>
       </c>
       <c r="J62" t="n">
-        <v>4586</v>
+        <v>913</v>
       </c>
       <c r="K62" t="n">
         <v>20.66</v>
@@ -8387,16 +8399,16 @@
         <v>793.1</v>
       </c>
       <c r="G63" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H63" t="n">
-        <v>24982</v>
+        <v>4858</v>
       </c>
       <c r="I63" t="n">
-        <v>28552</v>
+        <v>5552</v>
       </c>
       <c r="J63" t="n">
-        <v>3569</v>
+        <v>694</v>
       </c>
       <c r="K63" t="n">
         <v>14.29</v>
@@ -8468,16 +8480,16 @@
         <v>955.15</v>
       </c>
       <c r="G64" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H64" t="n">
-        <v>35183</v>
+        <v>6702</v>
       </c>
       <c r="I64" t="n">
-        <v>40116</v>
+        <v>7641</v>
       </c>
       <c r="J64" t="n">
-        <v>4933</v>
+        <v>940</v>
       </c>
       <c r="K64" t="n">
         <v>14.02</v>
@@ -8549,16 +8561,16 @@
         <v>2014.85</v>
       </c>
       <c r="G65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H65" t="n">
-        <v>44299</v>
+        <v>8860</v>
       </c>
       <c r="I65" t="n">
-        <v>50371</v>
+        <v>10074</v>
       </c>
       <c r="J65" t="n">
-        <v>6072</v>
+        <v>1214</v>
       </c>
       <c r="K65" t="n">
         <v>13.71</v>
@@ -8711,16 +8723,16 @@
         <v>1238.75</v>
       </c>
       <c r="G67" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
-        <v>29804</v>
+        <v>5519</v>
       </c>
       <c r="I67" t="n">
-        <v>33446</v>
+        <v>6194</v>
       </c>
       <c r="J67" t="n">
-        <v>3642</v>
+        <v>674</v>
       </c>
       <c r="K67" t="n">
         <v>12.22</v>
@@ -8792,16 +8804,16 @@
         <v>157.2</v>
       </c>
       <c r="G68" t="n">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="H68" t="n">
-        <v>16023</v>
+        <v>3120</v>
       </c>
       <c r="I68" t="n">
-        <v>17764</v>
+        <v>3458</v>
       </c>
       <c r="J68" t="n">
-        <v>1740</v>
+        <v>339</v>
       </c>
       <c r="K68" t="n">
         <v>10.86</v>
@@ -8873,16 +8885,16 @@
         <v>21.35</v>
       </c>
       <c r="G69" t="n">
-        <v>1809</v>
+        <v>361</v>
       </c>
       <c r="H69" t="n">
-        <v>36090</v>
+        <v>7202</v>
       </c>
       <c r="I69" t="n">
-        <v>38622</v>
+        <v>7707</v>
       </c>
       <c r="J69" t="n">
-        <v>2533</v>
+        <v>505</v>
       </c>
       <c r="K69" t="n">
         <v>7.02</v>
@@ -8954,16 +8966,16 @@
         <v>966.05</v>
       </c>
       <c r="G70" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H70" t="n">
-        <v>42294</v>
+        <v>8275</v>
       </c>
       <c r="I70" t="n">
-        <v>44438</v>
+        <v>8694</v>
       </c>
       <c r="J70" t="n">
-        <v>2144</v>
+        <v>419</v>
       </c>
       <c r="K70" t="n">
         <v>5.07</v>
@@ -9035,16 +9047,16 @@
         <v>3200.3</v>
       </c>
       <c r="G71" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H71" t="n">
-        <v>58483</v>
+        <v>9234</v>
       </c>
       <c r="I71" t="n">
-        <v>60806</v>
+        <v>9601</v>
       </c>
       <c r="J71" t="n">
-        <v>2323</v>
+        <v>367</v>
       </c>
       <c r="K71" t="n">
         <v>3.97</v>
@@ -9116,16 +9128,16 @@
         <v>1010.7</v>
       </c>
       <c r="G72" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>26453</v>
+        <v>4899</v>
       </c>
       <c r="I72" t="n">
-        <v>27289</v>
+        <v>5054</v>
       </c>
       <c r="J72" t="n">
-        <v>836</v>
+        <v>155</v>
       </c>
       <c r="K72" t="n">
         <v>3.16</v>
@@ -9197,16 +9209,16 @@
         <v>1581.2</v>
       </c>
       <c r="G73" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H73" t="n">
-        <v>45505</v>
+        <v>7846</v>
       </c>
       <c r="I73" t="n">
-        <v>45855</v>
+        <v>7906</v>
       </c>
       <c r="J73" t="n">
-        <v>349</v>
+        <v>60</v>
       </c>
       <c r="K73" t="n">
         <v>0.77</v>
@@ -9278,16 +9290,16 @@
         <v>157.05</v>
       </c>
       <c r="G74" t="n">
-        <v>248</v>
+        <v>49</v>
       </c>
       <c r="H74" t="n">
-        <v>39144</v>
+        <v>7734</v>
       </c>
       <c r="I74" t="n">
-        <v>38948</v>
+        <v>7695</v>
       </c>
       <c r="J74" t="n">
-        <v>-196</v>
+        <v>-39</v>
       </c>
       <c r="K74" t="n">
         <v>-0.5</v>
@@ -9359,16 +9371,16 @@
         <v>83.95999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="H75" t="n">
-        <v>20723</v>
+        <v>4093</v>
       </c>
       <c r="I75" t="n">
-        <v>20402</v>
+        <v>4030</v>
       </c>
       <c r="J75" t="n">
-        <v>-321</v>
+        <v>-63</v>
       </c>
       <c r="K75" t="n">
         <v>-1.55</v>
@@ -9440,16 +9452,16 @@
         <v>3064.9</v>
       </c>
       <c r="G76" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>22825</v>
+        <v>3261</v>
       </c>
       <c r="I76" t="n">
-        <v>21454</v>
+        <v>3065</v>
       </c>
       <c r="J76" t="n">
-        <v>-1371</v>
+        <v>-196</v>
       </c>
       <c r="K76" t="n">
         <v>-6.01</v>
@@ -9521,16 +9533,16 @@
         <v>72.45</v>
       </c>
       <c r="G77" t="n">
-        <v>712</v>
+        <v>142</v>
       </c>
       <c r="H77" t="n">
-        <v>25632</v>
+        <v>5112</v>
       </c>
       <c r="I77" t="n">
-        <v>51584</v>
+        <v>10288</v>
       </c>
       <c r="J77" t="n">
-        <v>25952</v>
+        <v>5176</v>
       </c>
       <c r="K77" t="n">
         <v>101.25</v>
@@ -9602,16 +9614,16 @@
         <v>32.7</v>
       </c>
       <c r="G78" t="n">
-        <v>2850</v>
+        <v>570</v>
       </c>
       <c r="H78" t="n">
-        <v>60848</v>
+        <v>12170</v>
       </c>
       <c r="I78" t="n">
-        <v>93195</v>
+        <v>18639</v>
       </c>
       <c r="J78" t="n">
-        <v>32348</v>
+        <v>6470</v>
       </c>
       <c r="K78" t="n">
         <v>53.16</v>
@@ -9683,16 +9695,16 @@
         <v>125.72</v>
       </c>
       <c r="G79" t="n">
-        <v>378</v>
+        <v>75</v>
       </c>
       <c r="H79" t="n">
-        <v>31737</v>
+        <v>6297</v>
       </c>
       <c r="I79" t="n">
-        <v>47522</v>
+        <v>9429</v>
       </c>
       <c r="J79" t="n">
-        <v>15785</v>
+        <v>3132</v>
       </c>
       <c r="K79" t="n">
         <v>49.74</v>
@@ -9764,16 +9776,16 @@
         <v>80.05</v>
       </c>
       <c r="G80" t="n">
-        <v>429</v>
+        <v>85</v>
       </c>
       <c r="H80" t="n">
-        <v>28936</v>
+        <v>5733</v>
       </c>
       <c r="I80" t="n">
-        <v>34341</v>
+        <v>6804</v>
       </c>
       <c r="J80" t="n">
-        <v>5405</v>
+        <v>1071</v>
       </c>
       <c r="K80" t="n">
         <v>18.68</v>
@@ -9845,16 +9857,16 @@
         <v>1032.8</v>
       </c>
       <c r="G81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H81" t="n">
-        <v>23942</v>
+        <v>4788</v>
       </c>
       <c r="I81" t="n">
-        <v>25820</v>
+        <v>5164</v>
       </c>
       <c r="J81" t="n">
-        <v>1878</v>
+        <v>376</v>
       </c>
       <c r="K81" t="n">
         <v>7.84</v>
@@ -9926,16 +9938,16 @@
         <v>34.45</v>
       </c>
       <c r="G82" t="n">
-        <v>1134</v>
+        <v>226</v>
       </c>
       <c r="H82" t="n">
-        <v>37082</v>
+        <v>7390</v>
       </c>
       <c r="I82" t="n">
-        <v>39066</v>
+        <v>7786</v>
       </c>
       <c r="J82" t="n">
-        <v>1984</v>
+        <v>396</v>
       </c>
       <c r="K82" t="n">
         <v>5.35</v>
@@ -10007,16 +10019,16 @@
         <v>994.27</v>
       </c>
       <c r="G83" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H83" t="n">
-        <v>35744</v>
+        <v>6762</v>
       </c>
       <c r="I83" t="n">
-        <v>36788</v>
+        <v>6960</v>
       </c>
       <c r="J83" t="n">
-        <v>1044</v>
+        <v>198</v>
       </c>
       <c r="K83" t="n">
         <v>2.92</v>
@@ -10088,16 +10100,16 @@
         <v>3642.25</v>
       </c>
       <c r="G84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>28828</v>
+        <v>3604</v>
       </c>
       <c r="I84" t="n">
-        <v>29138</v>
+        <v>3642</v>
       </c>
       <c r="J84" t="n">
-        <v>310</v>
+        <v>39</v>
       </c>
       <c r="K84" t="n">
         <v>1.07</v>
@@ -10169,16 +10181,16 @@
         <v>796</v>
       </c>
       <c r="G85" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>26172</v>
+        <v>4759</v>
       </c>
       <c r="I85" t="n">
-        <v>26268</v>
+        <v>4776</v>
       </c>
       <c r="J85" t="n">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="K85" t="n">
         <v>0.37</v>
@@ -10250,16 +10262,16 @@
         <v>293.56</v>
       </c>
       <c r="G86" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="H86" t="n">
-        <v>38055</v>
+        <v>7611</v>
       </c>
       <c r="I86" t="n">
-        <v>38163</v>
+        <v>7633</v>
       </c>
       <c r="J86" t="n">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="K86" t="n">
         <v>0.28</v>
@@ -10331,16 +10343,16 @@
         <v>854.35</v>
       </c>
       <c r="G87" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>28011</v>
+        <v>5252</v>
       </c>
       <c r="I87" t="n">
-        <v>27339</v>
+        <v>5126</v>
       </c>
       <c r="J87" t="n">
-        <v>-671</v>
+        <v>-126</v>
       </c>
       <c r="K87" t="n">
         <v>-2.4</v>
@@ -10412,16 +10424,16 @@
         <v>1261.15</v>
       </c>
       <c r="G88" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H88" t="n">
-        <v>29289</v>
+        <v>5325</v>
       </c>
       <c r="I88" t="n">
-        <v>27745</v>
+        <v>5045</v>
       </c>
       <c r="J88" t="n">
-        <v>-1543</v>
+        <v>-281</v>
       </c>
       <c r="K88" t="n">
         <v>-5.27</v>
@@ -10493,16 +10505,16 @@
         <v>3031.35</v>
       </c>
       <c r="G89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>44804</v>
+        <v>6401</v>
       </c>
       <c r="I89" t="n">
-        <v>42439</v>
+        <v>6063</v>
       </c>
       <c r="J89" t="n">
-        <v>-2365</v>
+        <v>-338</v>
       </c>
       <c r="K89" t="n">
         <v>-5.28</v>
@@ -10574,16 +10586,16 @@
         <v>896.4</v>
       </c>
       <c r="G90" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H90" t="n">
-        <v>29310</v>
+        <v>5054</v>
       </c>
       <c r="I90" t="n">
-        <v>25996</v>
+        <v>4482</v>
       </c>
       <c r="J90" t="n">
-        <v>-3315</v>
+        <v>-572</v>
       </c>
       <c r="K90" t="n">
         <v>-11.31</v>
@@ -10653,16 +10665,16 @@
         <v>7829.05</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>17801</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>15658</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>-2143</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
         <v>-12.04</v>
@@ -10670,8 +10682,12 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-12</v>
+      </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10728,16 +10744,16 @@
         <v>350.46</v>
       </c>
       <c r="G92" t="n">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="H92" t="n">
-        <v>32879</v>
+        <v>6458</v>
       </c>
       <c r="I92" t="n">
-        <v>39252</v>
+        <v>7710</v>
       </c>
       <c r="J92" t="n">
-        <v>6373</v>
+        <v>1252</v>
       </c>
       <c r="K92" t="n">
         <v>19.38</v>
@@ -10809,16 +10825,16 @@
         <v>4286</v>
       </c>
       <c r="G93" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>32780</v>
+        <v>3642</v>
       </c>
       <c r="I93" t="n">
-        <v>38574</v>
+        <v>4286</v>
       </c>
       <c r="J93" t="n">
-        <v>5794</v>
+        <v>644</v>
       </c>
       <c r="K93" t="n">
         <v>17.67</v>
@@ -10890,16 +10906,16 @@
         <v>3312.5</v>
       </c>
       <c r="G94" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>32959</v>
+        <v>5993</v>
       </c>
       <c r="I94" t="n">
-        <v>36438</v>
+        <v>6625</v>
       </c>
       <c r="J94" t="n">
-        <v>3478</v>
+        <v>632</v>
       </c>
       <c r="K94" t="n">
         <v>10.55</v>
@@ -10971,16 +10987,16 @@
         <v>3340.6</v>
       </c>
       <c r="G95" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H95" t="n">
-        <v>48502</v>
+        <v>9094</v>
       </c>
       <c r="I95" t="n">
-        <v>53450</v>
+        <v>10022</v>
       </c>
       <c r="J95" t="n">
-        <v>4948</v>
+        <v>928</v>
       </c>
       <c r="K95" t="n">
         <v>10.2</v>
@@ -11052,16 +11068,16 @@
         <v>2288.5</v>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>18779</v>
+        <v>2087</v>
       </c>
       <c r="I96" t="n">
-        <v>20596</v>
+        <v>2288</v>
       </c>
       <c r="J96" t="n">
-        <v>1818</v>
+        <v>202</v>
       </c>
       <c r="K96" t="n">
         <v>9.68</v>
@@ -11133,16 +11149,16 @@
         <v>231.45</v>
       </c>
       <c r="G97" t="n">
-        <v>163</v>
+        <v>32</v>
       </c>
       <c r="H97" t="n">
-        <v>35518</v>
+        <v>6973</v>
       </c>
       <c r="I97" t="n">
-        <v>37726</v>
+        <v>7406</v>
       </c>
       <c r="J97" t="n">
-        <v>2209</v>
+        <v>434</v>
       </c>
       <c r="K97" t="n">
         <v>6.22</v>
@@ -11214,16 +11230,16 @@
         <v>842.45</v>
       </c>
       <c r="G98" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H98" t="n">
-        <v>19930</v>
+        <v>3986</v>
       </c>
       <c r="I98" t="n">
-        <v>21061</v>
+        <v>4212</v>
       </c>
       <c r="J98" t="n">
-        <v>1131</v>
+        <v>226</v>
       </c>
       <c r="K98" t="n">
         <v>5.68</v>
@@ -11295,16 +11311,16 @@
         <v>1587.65</v>
       </c>
       <c r="G99" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H99" t="n">
-        <v>51034</v>
+        <v>9279</v>
       </c>
       <c r="I99" t="n">
-        <v>52392</v>
+        <v>9526</v>
       </c>
       <c r="J99" t="n">
-        <v>1358</v>
+        <v>247</v>
       </c>
       <c r="K99" t="n">
         <v>2.66</v>
@@ -11376,16 +11392,16 @@
         <v>890.15</v>
       </c>
       <c r="G100" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H100" t="n">
-        <v>22623</v>
+        <v>4350</v>
       </c>
       <c r="I100" t="n">
-        <v>23144</v>
+        <v>4451</v>
       </c>
       <c r="J100" t="n">
-        <v>521</v>
+        <v>100</v>
       </c>
       <c r="K100" t="n">
         <v>2.3</v>
@@ -11457,16 +11473,16 @@
         <v>3241.65</v>
       </c>
       <c r="G101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>19269</v>
+        <v>3212</v>
       </c>
       <c r="I101" t="n">
-        <v>19450</v>
+        <v>3242</v>
       </c>
       <c r="J101" t="n">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="K101" t="n">
         <v>0.9399999999999999</v>
@@ -11538,16 +11554,16 @@
         <v>78</v>
       </c>
       <c r="G102" t="n">
-        <v>435</v>
+        <v>87</v>
       </c>
       <c r="H102" t="n">
-        <v>34822</v>
+        <v>6964</v>
       </c>
       <c r="I102" t="n">
-        <v>33930</v>
+        <v>6786</v>
       </c>
       <c r="J102" t="n">
-        <v>-892</v>
+        <v>-178</v>
       </c>
       <c r="K102" t="n">
         <v>-2.56</v>
@@ -11619,16 +11635,16 @@
         <v>771.1</v>
       </c>
       <c r="G103" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H103" t="n">
-        <v>34228</v>
+        <v>6368</v>
       </c>
       <c r="I103" t="n">
-        <v>33157</v>
+        <v>6169</v>
       </c>
       <c r="J103" t="n">
-        <v>-1071</v>
+        <v>-199</v>
       </c>
       <c r="K103" t="n">
         <v>-3.13</v>
@@ -11700,16 +11716,16 @@
         <v>1173.9</v>
       </c>
       <c r="G104" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H104" t="n">
-        <v>35312</v>
+        <v>6306</v>
       </c>
       <c r="I104" t="n">
-        <v>32869</v>
+        <v>5870</v>
       </c>
       <c r="J104" t="n">
-        <v>-2443</v>
+        <v>-436</v>
       </c>
       <c r="K104" t="n">
         <v>-6.92</v>
@@ -11781,16 +11797,16 @@
         <v>813.95</v>
       </c>
       <c r="G105" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
-        <v>40338</v>
+        <v>8068</v>
       </c>
       <c r="I105" t="n">
-        <v>36628</v>
+        <v>7326</v>
       </c>
       <c r="J105" t="n">
-        <v>-3710</v>
+        <v>-742</v>
       </c>
       <c r="K105" t="n">
         <v>-9.199999999999999</v>
@@ -11862,16 +11878,16 @@
         <v>1383.75</v>
       </c>
       <c r="G106" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>31493</v>
+        <v>4973</v>
       </c>
       <c r="I106" t="n">
-        <v>26291</v>
+        <v>4151</v>
       </c>
       <c r="J106" t="n">
-        <v>-5202</v>
+        <v>-821</v>
       </c>
       <c r="K106" t="n">
         <v>-16.52</v>
@@ -11943,16 +11959,16 @@
         <v>1356</v>
       </c>
       <c r="G107" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H107" t="n">
-        <v>33816</v>
+        <v>6545</v>
       </c>
       <c r="I107" t="n">
-        <v>42036</v>
+        <v>8136</v>
       </c>
       <c r="J107" t="n">
-        <v>8220</v>
+        <v>1591</v>
       </c>
       <c r="K107" t="n">
         <v>24.31</v>
@@ -12024,16 +12040,16 @@
         <v>3400</v>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>25081</v>
+        <v>2787</v>
       </c>
       <c r="I108" t="n">
-        <v>30600</v>
+        <v>3400</v>
       </c>
       <c r="J108" t="n">
-        <v>5519</v>
+        <v>613</v>
       </c>
       <c r="K108" t="n">
         <v>22.01</v>
@@ -12105,16 +12121,16 @@
         <v>1934.6</v>
       </c>
       <c r="G109" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>33341</v>
+        <v>6351</v>
       </c>
       <c r="I109" t="n">
-        <v>40627</v>
+        <v>7738</v>
       </c>
       <c r="J109" t="n">
-        <v>7286</v>
+        <v>1388</v>
       </c>
       <c r="K109" t="n">
         <v>21.85</v>
@@ -12186,16 +12202,16 @@
         <v>1659</v>
       </c>
       <c r="G110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H110" t="n">
-        <v>34815</v>
+        <v>6963</v>
       </c>
       <c r="I110" t="n">
-        <v>41475</v>
+        <v>8295</v>
       </c>
       <c r="J110" t="n">
-        <v>6660</v>
+        <v>1332</v>
       </c>
       <c r="K110" t="n">
         <v>19.13</v>
@@ -12267,16 +12283,16 @@
         <v>837</v>
       </c>
       <c r="G111" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H111" t="n">
-        <v>37357</v>
+        <v>7184</v>
       </c>
       <c r="I111" t="n">
-        <v>43524</v>
+        <v>8370</v>
       </c>
       <c r="J111" t="n">
-        <v>6167</v>
+        <v>1186</v>
       </c>
       <c r="K111" t="n">
         <v>16.51</v>
@@ -12348,16 +12364,16 @@
         <v>1809.7</v>
       </c>
       <c r="G112" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H112" t="n">
-        <v>42030</v>
+        <v>7783</v>
       </c>
       <c r="I112" t="n">
-        <v>48862</v>
+        <v>9048</v>
       </c>
       <c r="J112" t="n">
-        <v>6832</v>
+        <v>1265</v>
       </c>
       <c r="K112" t="n">
         <v>16.26</v>
@@ -12429,16 +12445,16 @@
         <v>3842.8</v>
       </c>
       <c r="G113" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H113" t="n">
-        <v>33125</v>
+        <v>6625</v>
       </c>
       <c r="I113" t="n">
-        <v>38428</v>
+        <v>7686</v>
       </c>
       <c r="J113" t="n">
-        <v>5303</v>
+        <v>1061</v>
       </c>
       <c r="K113" t="n">
         <v>16.01</v>
@@ -12510,16 +12526,16 @@
         <v>884.95</v>
       </c>
       <c r="G114" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H114" t="n">
-        <v>26988</v>
+        <v>5398</v>
       </c>
       <c r="I114" t="n">
-        <v>30973</v>
+        <v>6195</v>
       </c>
       <c r="J114" t="n">
-        <v>3985</v>
+        <v>797</v>
       </c>
       <c r="K114" t="n">
         <v>14.76</v>
@@ -12591,16 +12607,16 @@
         <v>9671</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>25863</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>29013</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>3150</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
         <v>12.18</v>
@@ -12672,16 +12688,16 @@
         <v>1309.5</v>
       </c>
       <c r="G116" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H116" t="n">
-        <v>35217</v>
+        <v>7043</v>
       </c>
       <c r="I116" t="n">
-        <v>39285</v>
+        <v>7857</v>
       </c>
       <c r="J116" t="n">
-        <v>4068</v>
+        <v>814</v>
       </c>
       <c r="K116" t="n">
         <v>11.55</v>
@@ -12753,16 +12769,16 @@
         <v>188.3</v>
       </c>
       <c r="G117" t="n">
-        <v>164</v>
+        <v>32</v>
       </c>
       <c r="H117" t="n">
-        <v>28831</v>
+        <v>5626</v>
       </c>
       <c r="I117" t="n">
-        <v>30881</v>
+        <v>6026</v>
       </c>
       <c r="J117" t="n">
-        <v>2050</v>
+        <v>400</v>
       </c>
       <c r="K117" t="n">
         <v>7.11</v>
@@ -12834,16 +12850,16 @@
         <v>197.38</v>
       </c>
       <c r="G118" t="n">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="H118" t="n">
-        <v>29587</v>
+        <v>5768</v>
       </c>
       <c r="I118" t="n">
-        <v>31383</v>
+        <v>6119</v>
       </c>
       <c r="J118" t="n">
-        <v>1797</v>
+        <v>350</v>
       </c>
       <c r="K118" t="n">
         <v>6.07</v>
@@ -12915,16 +12931,16 @@
         <v>1075</v>
       </c>
       <c r="G119" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H119" t="n">
-        <v>32534</v>
+        <v>6100</v>
       </c>
       <c r="I119" t="n">
-        <v>34400</v>
+        <v>6450</v>
       </c>
       <c r="J119" t="n">
-        <v>1866</v>
+        <v>350</v>
       </c>
       <c r="K119" t="n">
         <v>5.73</v>
@@ -12996,16 +13012,16 @@
         <v>1752.76</v>
       </c>
       <c r="G120" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H120" t="n">
-        <v>30790</v>
+        <v>5132</v>
       </c>
       <c r="I120" t="n">
-        <v>31550</v>
+        <v>5258</v>
       </c>
       <c r="J120" t="n">
-        <v>759</v>
+        <v>127</v>
       </c>
       <c r="K120" t="n">
         <v>2.47</v>
@@ -13077,16 +13093,16 @@
         <v>374</v>
       </c>
       <c r="G121" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="H121" t="n">
-        <v>39094</v>
+        <v>7745</v>
       </c>
       <c r="I121" t="n">
-        <v>39644</v>
+        <v>7854</v>
       </c>
       <c r="J121" t="n">
-        <v>550</v>
+        <v>109</v>
       </c>
       <c r="K121" t="n">
         <v>1.41</v>
@@ -13158,16 +13174,16 @@
         <v>242.05</v>
       </c>
       <c r="G122" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="H122" t="n">
-        <v>42368</v>
+        <v>8474</v>
       </c>
       <c r="I122" t="n">
-        <v>54461</v>
+        <v>10892</v>
       </c>
       <c r="J122" t="n">
-        <v>12094</v>
+        <v>2419</v>
       </c>
       <c r="K122" t="n">
         <v>28.54</v>
@@ -13239,16 +13255,16 @@
         <v>3186.25</v>
       </c>
       <c r="G123" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H123" t="n">
-        <v>51020</v>
+        <v>10204</v>
       </c>
       <c r="I123" t="n">
-        <v>63725</v>
+        <v>12745</v>
       </c>
       <c r="J123" t="n">
-        <v>12705</v>
+        <v>2541</v>
       </c>
       <c r="K123" t="n">
         <v>24.9</v>
@@ -13320,16 +13336,16 @@
         <v>2041.65</v>
       </c>
       <c r="G124" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H124" t="n">
-        <v>32575</v>
+        <v>5429</v>
       </c>
       <c r="I124" t="n">
-        <v>36750</v>
+        <v>6125</v>
       </c>
       <c r="J124" t="n">
-        <v>4175</v>
+        <v>696</v>
       </c>
       <c r="K124" t="n">
         <v>12.82</v>
@@ -13401,16 +13417,16 @@
         <v>1974.67</v>
       </c>
       <c r="G125" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H125" t="n">
-        <v>35055</v>
+        <v>7011</v>
       </c>
       <c r="I125" t="n">
-        <v>39493</v>
+        <v>7899</v>
       </c>
       <c r="J125" t="n">
-        <v>4438</v>
+        <v>888</v>
       </c>
       <c r="K125" t="n">
         <v>12.66</v>
@@ -13482,16 +13498,16 @@
         <v>10727.55</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>19342</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>21455</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>2113</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
         <v>10.92</v>
@@ -13563,16 +13579,16 @@
         <v>954.2</v>
       </c>
       <c r="G127" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H127" t="n">
-        <v>44248</v>
+        <v>8850</v>
       </c>
       <c r="I127" t="n">
-        <v>47710</v>
+        <v>9542</v>
       </c>
       <c r="J127" t="n">
-        <v>3462</v>
+        <v>692</v>
       </c>
       <c r="K127" t="n">
         <v>7.83</v>
@@ -13725,16 +13741,16 @@
         <v>3570.85</v>
       </c>
       <c r="G129" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>26754</v>
+        <v>3344</v>
       </c>
       <c r="I129" t="n">
-        <v>28567</v>
+        <v>3571</v>
       </c>
       <c r="J129" t="n">
-        <v>1813</v>
+        <v>227</v>
       </c>
       <c r="K129" t="n">
         <v>6.78</v>
@@ -13806,16 +13822,16 @@
         <v>1145.3</v>
       </c>
       <c r="G130" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H130" t="n">
-        <v>38700</v>
+        <v>7525</v>
       </c>
       <c r="I130" t="n">
-        <v>41231</v>
+        <v>8017</v>
       </c>
       <c r="J130" t="n">
-        <v>2531</v>
+        <v>492</v>
       </c>
       <c r="K130" t="n">
         <v>6.54</v>
@@ -13887,16 +13903,16 @@
         <v>205.53</v>
       </c>
       <c r="G131" t="n">
-        <v>176</v>
+        <v>35</v>
       </c>
       <c r="H131" t="n">
-        <v>34739</v>
+        <v>6908</v>
       </c>
       <c r="I131" t="n">
-        <v>36173</v>
+        <v>7194</v>
       </c>
       <c r="J131" t="n">
-        <v>1434</v>
+        <v>285</v>
       </c>
       <c r="K131" t="n">
         <v>4.13</v>
@@ -13968,16 +13984,16 @@
         <v>1177.72</v>
       </c>
       <c r="G132" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H132" t="n">
-        <v>23962</v>
+        <v>4564</v>
       </c>
       <c r="I132" t="n">
-        <v>24732</v>
+        <v>4711</v>
       </c>
       <c r="J132" t="n">
-        <v>770</v>
+        <v>147</v>
       </c>
       <c r="K132" t="n">
         <v>3.21</v>
@@ -14049,16 +14065,16 @@
         <v>951.3</v>
       </c>
       <c r="G133" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H133" t="n">
-        <v>37304</v>
+        <v>6696</v>
       </c>
       <c r="I133" t="n">
-        <v>37101</v>
+        <v>6659</v>
       </c>
       <c r="J133" t="n">
-        <v>-203</v>
+        <v>-36</v>
       </c>
       <c r="K133" t="n">
         <v>-0.54</v>
@@ -14130,16 +14146,16 @@
         <v>1624.85</v>
       </c>
       <c r="G134" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H134" t="n">
-        <v>26544</v>
+        <v>4977</v>
       </c>
       <c r="I134" t="n">
-        <v>25998</v>
+        <v>4875</v>
       </c>
       <c r="J134" t="n">
-        <v>-546</v>
+        <v>-102</v>
       </c>
       <c r="K134" t="n">
         <v>-2.06</v>
@@ -14211,16 +14227,16 @@
         <v>1230.03</v>
       </c>
       <c r="G135" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H135" t="n">
-        <v>23571</v>
+        <v>3928</v>
       </c>
       <c r="I135" t="n">
-        <v>22141</v>
+        <v>3690</v>
       </c>
       <c r="J135" t="n">
-        <v>-1430</v>
+        <v>-238</v>
       </c>
       <c r="K135" t="n">
         <v>-6.07</v>
@@ -14292,16 +14308,16 @@
         <v>3148.8</v>
       </c>
       <c r="G136" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>20400</v>
+        <v>3400</v>
       </c>
       <c r="I136" t="n">
-        <v>18893</v>
+        <v>3149</v>
       </c>
       <c r="J136" t="n">
-        <v>-1507</v>
+        <v>-251</v>
       </c>
       <c r="K136" t="n">
         <v>-7.39</v>
@@ -14373,16 +14389,16 @@
         <v>427.4</v>
       </c>
       <c r="G137" t="n">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="H137" t="n">
-        <v>40936</v>
+        <v>7933</v>
       </c>
       <c r="I137" t="n">
-        <v>55135</v>
+        <v>10685</v>
       </c>
       <c r="J137" t="n">
-        <v>14199</v>
+        <v>2752</v>
       </c>
       <c r="K137" t="n">
         <v>34.69</v>
@@ -14535,16 +14551,16 @@
         <v>9954.549999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>33476</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>39818</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>6342</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
         <v>18.95</v>
@@ -14616,16 +14632,16 @@
         <v>1394.13</v>
       </c>
       <c r="G140" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H140" t="n">
-        <v>29366</v>
+        <v>5873</v>
       </c>
       <c r="I140" t="n">
-        <v>34853</v>
+        <v>6971</v>
       </c>
       <c r="J140" t="n">
-        <v>5487</v>
+        <v>1097</v>
       </c>
       <c r="K140" t="n">
         <v>18.68</v>
@@ -14697,16 +14713,16 @@
         <v>26210.45</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>22307</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>26210</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>3903</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
         <v>17.5</v>
@@ -14778,16 +14794,16 @@
         <v>1329.35</v>
       </c>
       <c r="G142" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H142" t="n">
-        <v>35504</v>
+        <v>6872</v>
       </c>
       <c r="I142" t="n">
-        <v>41210</v>
+        <v>7976</v>
       </c>
       <c r="J142" t="n">
-        <v>5706</v>
+        <v>1104</v>
       </c>
       <c r="K142" t="n">
         <v>16.07</v>
@@ -14859,16 +14875,16 @@
         <v>1102.4</v>
       </c>
       <c r="G143" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H143" t="n">
-        <v>36260</v>
+        <v>6679</v>
       </c>
       <c r="I143" t="n">
-        <v>41891</v>
+        <v>7717</v>
       </c>
       <c r="J143" t="n">
-        <v>5632</v>
+        <v>1037</v>
       </c>
       <c r="K143" t="n">
         <v>15.53</v>
@@ -14940,16 +14956,16 @@
         <v>3758.85</v>
       </c>
       <c r="G144" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H144" t="n">
-        <v>32838</v>
+        <v>6568</v>
       </c>
       <c r="I144" t="n">
-        <v>37588</v>
+        <v>7518</v>
       </c>
       <c r="J144" t="n">
-        <v>4751</v>
+        <v>950</v>
       </c>
       <c r="K144" t="n">
         <v>14.47</v>
@@ -15021,16 +15037,16 @@
         <v>1377.13</v>
       </c>
       <c r="G145" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H145" t="n">
-        <v>25831</v>
+        <v>4920</v>
       </c>
       <c r="I145" t="n">
-        <v>28920</v>
+        <v>5509</v>
       </c>
       <c r="J145" t="n">
-        <v>3089</v>
+        <v>588</v>
       </c>
       <c r="K145" t="n">
         <v>11.96</v>
@@ -15102,16 +15118,16 @@
         <v>3903.8</v>
       </c>
       <c r="G146" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>28567</v>
+        <v>3571</v>
       </c>
       <c r="I146" t="n">
-        <v>31230</v>
+        <v>3904</v>
       </c>
       <c r="J146" t="n">
-        <v>2664</v>
+        <v>333</v>
       </c>
       <c r="K146" t="n">
         <v>9.32</v>
@@ -15183,16 +15199,16 @@
         <v>1273.78</v>
       </c>
       <c r="G147" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H147" t="n">
-        <v>29443</v>
+        <v>5889</v>
       </c>
       <c r="I147" t="n">
-        <v>31844</v>
+        <v>6369</v>
       </c>
       <c r="J147" t="n">
-        <v>2402</v>
+        <v>480</v>
       </c>
       <c r="K147" t="n">
         <v>8.16</v>
@@ -15264,16 +15280,16 @@
         <v>1009.85</v>
       </c>
       <c r="G148" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H148" t="n">
-        <v>39955</v>
+        <v>7610</v>
       </c>
       <c r="I148" t="n">
-        <v>42414</v>
+        <v>8079</v>
       </c>
       <c r="J148" t="n">
-        <v>2459</v>
+        <v>468</v>
       </c>
       <c r="K148" t="n">
         <v>6.15</v>
@@ -15345,16 +15361,16 @@
         <v>3273.9</v>
       </c>
       <c r="G149" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>25190</v>
+        <v>3149</v>
       </c>
       <c r="I149" t="n">
-        <v>26191</v>
+        <v>3274</v>
       </c>
       <c r="J149" t="n">
-        <v>1001</v>
+        <v>125</v>
       </c>
       <c r="K149" t="n">
         <v>3.97</v>
@@ -15426,16 +15442,16 @@
         <v>2573.2</v>
       </c>
       <c r="G150" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H150" t="n">
-        <v>28264</v>
+        <v>5139</v>
       </c>
       <c r="I150" t="n">
-        <v>28305</v>
+        <v>5146</v>
       </c>
       <c r="J150" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K150" t="n">
         <v>0.15</v>
@@ -15507,16 +15523,16 @@
         <v>10086.9</v>
       </c>
       <c r="G151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>21455</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>20174</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>-1281</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>-5.97</v>
@@ -15588,16 +15604,16 @@
         <v>404.95</v>
       </c>
       <c r="G152" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="H152" t="n">
-        <v>23810</v>
+        <v>4504</v>
       </c>
       <c r="I152" t="n">
-        <v>29966</v>
+        <v>5669</v>
       </c>
       <c r="J152" t="n">
-        <v>6157</v>
+        <v>1165</v>
       </c>
       <c r="K152" t="n">
         <v>25.86</v>
@@ -15669,16 +15685,16 @@
         <v>12405</v>
       </c>
       <c r="G153" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>40348</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>49620</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>9272</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
         <v>22.98</v>
@@ -15750,16 +15766,16 @@
         <v>1265.75</v>
       </c>
       <c r="G154" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H154" t="n">
-        <v>26458</v>
+        <v>4410</v>
       </c>
       <c r="I154" t="n">
-        <v>30378</v>
+        <v>5063</v>
       </c>
       <c r="J154" t="n">
-        <v>3920</v>
+        <v>653</v>
       </c>
       <c r="K154" t="n">
         <v>14.82</v>
@@ -15831,16 +15847,16 @@
         <v>1516.4</v>
       </c>
       <c r="G155" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H155" t="n">
-        <v>29246</v>
+        <v>5317</v>
       </c>
       <c r="I155" t="n">
-        <v>33361</v>
+        <v>6066</v>
       </c>
       <c r="J155" t="n">
-        <v>4115</v>
+        <v>748</v>
       </c>
       <c r="K155" t="n">
         <v>14.07</v>
@@ -15912,16 +15928,16 @@
         <v>2226.05</v>
       </c>
       <c r="G156" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H156" t="n">
-        <v>23111</v>
+        <v>4202</v>
       </c>
       <c r="I156" t="n">
-        <v>24487</v>
+        <v>4452</v>
       </c>
       <c r="J156" t="n">
-        <v>1376</v>
+        <v>250</v>
       </c>
       <c r="K156" t="n">
         <v>5.95</v>
@@ -15993,16 +16009,16 @@
         <v>1464.33</v>
       </c>
       <c r="G157" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H157" t="n">
-        <v>27883</v>
+        <v>5577</v>
       </c>
       <c r="I157" t="n">
-        <v>29287</v>
+        <v>5857</v>
       </c>
       <c r="J157" t="n">
-        <v>1404</v>
+        <v>281</v>
       </c>
       <c r="K157" t="n">
         <v>5.04</v>
@@ -16074,16 +16090,16 @@
         <v>1055.45</v>
       </c>
       <c r="G158" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H158" t="n">
-        <v>28276</v>
+        <v>5049</v>
       </c>
       <c r="I158" t="n">
-        <v>29553</v>
+        <v>5277</v>
       </c>
       <c r="J158" t="n">
-        <v>1277</v>
+        <v>228</v>
       </c>
       <c r="K158" t="n">
         <v>4.52</v>
@@ -16155,16 +16171,16 @@
         <v>3862</v>
       </c>
       <c r="G159" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>31230</v>
+        <v>3904</v>
       </c>
       <c r="I159" t="n">
-        <v>30896</v>
+        <v>3862</v>
       </c>
       <c r="J159" t="n">
-        <v>-334</v>
+        <v>-42</v>
       </c>
       <c r="K159" t="n">
         <v>-1.07</v>
@@ -16236,16 +16252,16 @@
         <v>1638.25</v>
       </c>
       <c r="G160" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H160" t="n">
-        <v>46497</v>
+        <v>8610</v>
       </c>
       <c r="I160" t="n">
-        <v>44233</v>
+        <v>8191</v>
       </c>
       <c r="J160" t="n">
-        <v>-2264</v>
+        <v>-419</v>
       </c>
       <c r="K160" t="n">
         <v>-4.87</v>
@@ -16392,16 +16408,16 @@
         <v>3525.1</v>
       </c>
       <c r="G162" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H162" t="n">
-        <v>37588</v>
+        <v>7518</v>
       </c>
       <c r="I162" t="n">
-        <v>35251</v>
+        <v>7050</v>
       </c>
       <c r="J162" t="n">
-        <v>-2338</v>
+        <v>-468</v>
       </c>
       <c r="K162" t="n">
         <v>-6.22</v>
@@ -16473,16 +16489,16 @@
         <v>4695</v>
       </c>
       <c r="G163" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>31064</v>
+        <v>5177</v>
       </c>
       <c r="I163" t="n">
-        <v>28170</v>
+        <v>4695</v>
       </c>
       <c r="J163" t="n">
-        <v>-2894</v>
+        <v>-482</v>
       </c>
       <c r="K163" t="n">
         <v>-9.32</v>
@@ -16554,16 +16570,16 @@
         <v>747.35</v>
       </c>
       <c r="G164" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H164" t="n">
-        <v>28438</v>
+        <v>5018</v>
       </c>
       <c r="I164" t="n">
-        <v>25410</v>
+        <v>4484</v>
       </c>
       <c r="J164" t="n">
-        <v>-3028</v>
+        <v>-534</v>
       </c>
       <c r="K164" t="n">
         <v>-10.65</v>
@@ -16635,16 +16651,16 @@
         <v>2214.8</v>
       </c>
       <c r="G165" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H165" t="n">
-        <v>41171</v>
+        <v>7720</v>
       </c>
       <c r="I165" t="n">
-        <v>35437</v>
+        <v>6644</v>
       </c>
       <c r="J165" t="n">
-        <v>-5734</v>
+        <v>-1075</v>
       </c>
       <c r="K165" t="n">
         <v>-13.93</v>
@@ -16714,16 +16730,16 @@
         <v>2807.7</v>
       </c>
       <c r="G166" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
-        <v>32739</v>
+        <v>6548</v>
       </c>
       <c r="I166" t="n">
-        <v>28077</v>
+        <v>5615</v>
       </c>
       <c r="J166" t="n">
-        <v>-4662</v>
+        <v>-932</v>
       </c>
       <c r="K166" t="n">
         <v>-14.24</v>
@@ -16795,16 +16811,16 @@
         <v>2743</v>
       </c>
       <c r="G167" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>20034</v>
+        <v>2226</v>
       </c>
       <c r="I167" t="n">
-        <v>24687</v>
+        <v>2743</v>
       </c>
       <c r="J167" t="n">
-        <v>4653</v>
+        <v>517</v>
       </c>
       <c r="K167" t="n">
         <v>23.22</v>
@@ -16876,16 +16892,16 @@
         <v>2727</v>
       </c>
       <c r="G168" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H168" t="n">
-        <v>35437</v>
+        <v>6644</v>
       </c>
       <c r="I168" t="n">
-        <v>43632</v>
+        <v>8181</v>
       </c>
       <c r="J168" t="n">
-        <v>8195</v>
+        <v>1537</v>
       </c>
       <c r="K168" t="n">
         <v>23.13</v>
@@ -16957,16 +16973,16 @@
         <v>11258.3</v>
       </c>
       <c r="G169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>18766</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>22517</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>3751</v>
+        <v>0</v>
       </c>
       <c r="K169" t="n">
         <v>19.99</v>
@@ -17038,16 +17054,16 @@
         <v>1248.65</v>
       </c>
       <c r="G170" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H170" t="n">
-        <v>24275</v>
+        <v>4222</v>
       </c>
       <c r="I170" t="n">
-        <v>28719</v>
+        <v>4995</v>
       </c>
       <c r="J170" t="n">
-        <v>4444</v>
+        <v>773</v>
       </c>
       <c r="K170" t="n">
         <v>18.3</v>
@@ -17119,16 +17135,16 @@
         <v>1926.85</v>
       </c>
       <c r="G171" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H171" t="n">
-        <v>44233</v>
+        <v>8191</v>
       </c>
       <c r="I171" t="n">
-        <v>52025</v>
+        <v>9634</v>
       </c>
       <c r="J171" t="n">
-        <v>7792</v>
+        <v>1443</v>
       </c>
       <c r="K171" t="n">
         <v>17.62</v>
@@ -17194,16 +17210,16 @@
         <v>1461.75</v>
       </c>
       <c r="G172" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H172" t="n">
-        <v>36707</v>
+        <v>6329</v>
       </c>
       <c r="I172" t="n">
-        <v>42391</v>
+        <v>7309</v>
       </c>
       <c r="J172" t="n">
-        <v>5684</v>
+        <v>980</v>
       </c>
       <c r="K172" t="n">
         <v>15.48</v>
@@ -17275,16 +17291,16 @@
         <v>446.08</v>
       </c>
       <c r="G173" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H173" t="n">
-        <v>46415</v>
+        <v>9283</v>
       </c>
       <c r="I173" t="n">
-        <v>53530</v>
+        <v>10706</v>
       </c>
       <c r="J173" t="n">
-        <v>7115</v>
+        <v>1423</v>
       </c>
       <c r="K173" t="n">
         <v>15.33</v>
@@ -17356,16 +17372,16 @@
         <v>1523.8</v>
       </c>
       <c r="G174" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H174" t="n">
-        <v>26871</v>
+        <v>5374</v>
       </c>
       <c r="I174" t="n">
-        <v>30476</v>
+        <v>6095</v>
       </c>
       <c r="J174" t="n">
-        <v>3605</v>
+        <v>721</v>
       </c>
       <c r="K174" t="n">
         <v>13.42</v>
@@ -17437,16 +17453,16 @@
         <v>1327.2</v>
       </c>
       <c r="G175" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H175" t="n">
-        <v>38126</v>
+        <v>7149</v>
       </c>
       <c r="I175" t="n">
-        <v>42470</v>
+        <v>7963</v>
       </c>
       <c r="J175" t="n">
-        <v>4345</v>
+        <v>815</v>
       </c>
       <c r="K175" t="n">
         <v>11.4</v>
@@ -17518,16 +17534,16 @@
         <v>4302.4</v>
       </c>
       <c r="G176" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>34758</v>
+        <v>3862</v>
       </c>
       <c r="I176" t="n">
-        <v>38722</v>
+        <v>4302</v>
       </c>
       <c r="J176" t="n">
-        <v>3964</v>
+        <v>440</v>
       </c>
       <c r="K176" t="n">
         <v>11.4</v>
@@ -17599,16 +17615,16 @@
         <v>1555.15</v>
       </c>
       <c r="G177" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H177" t="n">
-        <v>23429</v>
+        <v>4393</v>
       </c>
       <c r="I177" t="n">
-        <v>24882</v>
+        <v>4665</v>
       </c>
       <c r="J177" t="n">
-        <v>1453</v>
+        <v>272</v>
       </c>
       <c r="K177" t="n">
         <v>6.2</v>
@@ -17680,16 +17696,16 @@
         <v>2946.05</v>
       </c>
       <c r="G178" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H178" t="n">
-        <v>30885</v>
+        <v>5615</v>
       </c>
       <c r="I178" t="n">
-        <v>32407</v>
+        <v>5892</v>
       </c>
       <c r="J178" t="n">
-        <v>1522</v>
+        <v>277</v>
       </c>
       <c r="K178" t="n">
         <v>4.93</v>
@@ -17761,16 +17777,16 @@
         <v>1568.65</v>
       </c>
       <c r="G179" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H179" t="n">
-        <v>40943</v>
+        <v>7582</v>
       </c>
       <c r="I179" t="n">
-        <v>42354</v>
+        <v>7843</v>
       </c>
       <c r="J179" t="n">
-        <v>1411</v>
+        <v>261</v>
       </c>
       <c r="K179" t="n">
         <v>3.45</v>
@@ -17842,16 +17858,16 @@
         <v>364.32</v>
       </c>
       <c r="G180" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H180" t="n">
-        <v>25014</v>
+        <v>5003</v>
       </c>
       <c r="I180" t="n">
-        <v>25502</v>
+        <v>5100</v>
       </c>
       <c r="J180" t="n">
-        <v>488</v>
+        <v>98</v>
       </c>
       <c r="K180" t="n">
         <v>1.95</v>
@@ -17923,16 +17939,16 @@
         <v>12524.3</v>
       </c>
       <c r="G181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>37215</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>37573</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
         <v>0.96</v>
@@ -18004,16 +18020,16 @@
         <v>1910.35</v>
       </c>
       <c r="G182" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H182" t="n">
-        <v>26667</v>
+        <v>4706</v>
       </c>
       <c r="I182" t="n">
-        <v>32476</v>
+        <v>5731</v>
       </c>
       <c r="J182" t="n">
-        <v>5809</v>
+        <v>1025</v>
       </c>
       <c r="K182" t="n">
         <v>21.78</v>
@@ -18085,16 +18101,16 @@
         <v>4560.7</v>
       </c>
       <c r="G183" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H183" t="n">
-        <v>42188</v>
+        <v>7671</v>
       </c>
       <c r="I183" t="n">
-        <v>50168</v>
+        <v>9121</v>
       </c>
       <c r="J183" t="n">
-        <v>7979</v>
+        <v>1451</v>
       </c>
       <c r="K183" t="n">
         <v>18.91</v>
@@ -18166,16 +18182,16 @@
         <v>6982.9</v>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>19146</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>20949</v>
+        <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>1803</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
         <v>9.42</v>
@@ -18247,16 +18263,16 @@
         <v>1879.6</v>
       </c>
       <c r="G185" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H185" t="n">
-        <v>34066</v>
+        <v>5379</v>
       </c>
       <c r="I185" t="n">
-        <v>35712</v>
+        <v>5639</v>
       </c>
       <c r="J185" t="n">
-        <v>1646</v>
+        <v>260</v>
       </c>
       <c r="K185" t="n">
         <v>4.83</v>
@@ -18328,16 +18344,16 @@
         <v>840.9299999999999</v>
       </c>
       <c r="G186" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H186" t="n">
-        <v>38575</v>
+        <v>7233</v>
       </c>
       <c r="I186" t="n">
-        <v>40365</v>
+        <v>7568</v>
       </c>
       <c r="J186" t="n">
-        <v>1789</v>
+        <v>336</v>
       </c>
       <c r="K186" t="n">
         <v>4.64</v>
@@ -18409,16 +18425,16 @@
         <v>740.15</v>
       </c>
       <c r="G187" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H187" t="n">
-        <v>39523</v>
+        <v>7905</v>
       </c>
       <c r="I187" t="n">
-        <v>40708</v>
+        <v>8142</v>
       </c>
       <c r="J187" t="n">
-        <v>1185</v>
+        <v>237</v>
       </c>
       <c r="K187" t="n">
         <v>3</v>
@@ -18490,16 +18506,16 @@
         <v>457.5</v>
       </c>
       <c r="G188" t="n">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="H188" t="n">
-        <v>33902</v>
+        <v>6691</v>
       </c>
       <c r="I188" t="n">
-        <v>34770</v>
+        <v>6862</v>
       </c>
       <c r="J188" t="n">
-        <v>868</v>
+        <v>171</v>
       </c>
       <c r="K188" t="n">
         <v>2.56</v>
@@ -18571,16 +18587,16 @@
         <v>1348.22</v>
       </c>
       <c r="G189" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H189" t="n">
-        <v>27871</v>
+        <v>5309</v>
       </c>
       <c r="I189" t="n">
-        <v>28313</v>
+        <v>5393</v>
       </c>
       <c r="J189" t="n">
-        <v>441</v>
+        <v>84</v>
       </c>
       <c r="K189" t="n">
         <v>1.58</v>
@@ -18652,16 +18668,16 @@
         <v>1592</v>
       </c>
       <c r="G190" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H190" t="n">
-        <v>36050</v>
+        <v>6270</v>
       </c>
       <c r="I190" t="n">
-        <v>36616</v>
+        <v>6368</v>
       </c>
       <c r="J190" t="n">
-        <v>566</v>
+        <v>98</v>
       </c>
       <c r="K190" t="n">
         <v>1.57</v>
@@ -18733,16 +18749,16 @@
         <v>2992.15</v>
       </c>
       <c r="G191" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H191" t="n">
-        <v>29460</v>
+        <v>5892</v>
       </c>
       <c r="I191" t="n">
-        <v>29922</v>
+        <v>5984</v>
       </c>
       <c r="J191" t="n">
-        <v>461</v>
+        <v>92</v>
       </c>
       <c r="K191" t="n">
         <v>1.56</v>
@@ -18895,16 +18911,16 @@
         <v>2717.1</v>
       </c>
       <c r="G193" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H193" t="n">
-        <v>40905</v>
+        <v>8181</v>
       </c>
       <c r="I193" t="n">
-        <v>40756</v>
+        <v>8151</v>
       </c>
       <c r="J193" t="n">
-        <v>-148</v>
+        <v>-30</v>
       </c>
       <c r="K193" t="n">
         <v>-0.36</v>
@@ -18976,16 +18992,16 @@
         <v>4765.65</v>
       </c>
       <c r="G194" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>24254</v>
+        <v>4851</v>
       </c>
       <c r="I194" t="n">
-        <v>23828</v>
+        <v>4766</v>
       </c>
       <c r="J194" t="n">
-        <v>-425</v>
+        <v>-85</v>
       </c>
       <c r="K194" t="n">
         <v>-1.75</v>
@@ -19057,16 +19073,16 @@
         <v>1464.95</v>
       </c>
       <c r="G195" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H195" t="n">
-        <v>30476</v>
+        <v>6095</v>
       </c>
       <c r="I195" t="n">
-        <v>29299</v>
+        <v>5860</v>
       </c>
       <c r="J195" t="n">
-        <v>-1177</v>
+        <v>-235</v>
       </c>
       <c r="K195" t="n">
         <v>-3.86</v>
@@ -19138,16 +19154,16 @@
         <v>4123.05</v>
       </c>
       <c r="G196" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>30117</v>
+        <v>4302</v>
       </c>
       <c r="I196" t="n">
-        <v>28861</v>
+        <v>4123</v>
       </c>
       <c r="J196" t="n">
-        <v>-1255</v>
+        <v>-179</v>
       </c>
       <c r="K196" t="n">
         <v>-4.17</v>
@@ -19219,16 +19235,16 @@
         <v>5016.75</v>
       </c>
       <c r="G197" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H197" t="n">
-        <v>23828</v>
+        <v>4766</v>
       </c>
       <c r="I197" t="n">
-        <v>25084</v>
+        <v>5017</v>
       </c>
       <c r="J197" t="n">
-        <v>1256</v>
+        <v>251</v>
       </c>
       <c r="K197" t="n">
         <v>5.27</v>
@@ -19300,16 +19316,16 @@
         <v>25146</v>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>24325</v>
+        <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>25146</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>821</v>
+        <v>0</v>
       </c>
       <c r="K198" t="n">
         <v>3.37</v>
@@ -19381,16 +19397,16 @@
         <v>761.5</v>
       </c>
       <c r="G199" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H199" t="n">
-        <v>34047</v>
+        <v>6661</v>
       </c>
       <c r="I199" t="n">
-        <v>35029</v>
+        <v>6854</v>
       </c>
       <c r="J199" t="n">
-        <v>982</v>
+        <v>192</v>
       </c>
       <c r="K199" t="n">
         <v>2.88</v>
@@ -19462,16 +19478,16 @@
         <v>384.1</v>
       </c>
       <c r="G200" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H200" t="n">
-        <v>25820</v>
+        <v>4865</v>
       </c>
       <c r="I200" t="n">
-        <v>26503</v>
+        <v>4993</v>
       </c>
       <c r="J200" t="n">
-        <v>682</v>
+        <v>129</v>
       </c>
       <c r="K200" t="n">
         <v>2.64</v>
@@ -19543,16 +19559,16 @@
         <v>4077.8</v>
       </c>
       <c r="G201" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H201" t="n">
-        <v>28861</v>
+        <v>4123</v>
       </c>
       <c r="I201" t="n">
-        <v>28545</v>
+        <v>4078</v>
       </c>
       <c r="J201" t="n">
-        <v>-317</v>
+        <v>-45</v>
       </c>
       <c r="K201" t="n">
         <v>-1.1</v>
@@ -19624,16 +19640,16 @@
         <v>6780.85</v>
       </c>
       <c r="G202" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>27932</v>
+        <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>27123</v>
+        <v>0</v>
       </c>
       <c r="J202" t="n">
-        <v>-808</v>
+        <v>0</v>
       </c>
       <c r="K202" t="n">
         <v>-2.89</v>
@@ -19705,16 +19721,16 @@
         <v>1302.35</v>
       </c>
       <c r="G203" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H203" t="n">
-        <v>44491</v>
+        <v>8089</v>
       </c>
       <c r="I203" t="n">
-        <v>42978</v>
+        <v>7814</v>
       </c>
       <c r="J203" t="n">
-        <v>-1514</v>
+        <v>-275</v>
       </c>
       <c r="K203" t="n">
         <v>-3.4</v>
@@ -19786,16 +19802,16 @@
         <v>1813.3</v>
       </c>
       <c r="G204" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H204" t="n">
-        <v>26314</v>
+        <v>3759</v>
       </c>
       <c r="I204" t="n">
-        <v>25386</v>
+        <v>3627</v>
       </c>
       <c r="J204" t="n">
-        <v>-928</v>
+        <v>-133</v>
       </c>
       <c r="K204" t="n">
         <v>-3.53</v>
@@ -19867,16 +19883,16 @@
         <v>437.7</v>
       </c>
       <c r="G205" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="H205" t="n">
-        <v>30652</v>
+        <v>5948</v>
       </c>
       <c r="I205" t="n">
-        <v>29326</v>
+        <v>5690</v>
       </c>
       <c r="J205" t="n">
-        <v>-1327</v>
+        <v>-257</v>
       </c>
       <c r="K205" t="n">
         <v>-4.33</v>
@@ -19948,16 +19964,16 @@
         <v>1107</v>
       </c>
       <c r="G206" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H206" t="n">
-        <v>30553</v>
+        <v>5876</v>
       </c>
       <c r="I206" t="n">
-        <v>28782</v>
+        <v>5535</v>
       </c>
       <c r="J206" t="n">
-        <v>-1771</v>
+        <v>-341</v>
       </c>
       <c r="K206" t="n">
         <v>-5.8</v>
@@ -20029,16 +20045,16 @@
         <v>1778.25</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H207" t="n">
-        <v>42028</v>
+        <v>7641</v>
       </c>
       <c r="I207" t="n">
-        <v>39122</v>
+        <v>7113</v>
       </c>
       <c r="J207" t="n">
-        <v>-2906</v>
+        <v>-528</v>
       </c>
       <c r="K207" t="n">
         <v>-6.91</v>
@@ -20189,16 +20205,16 @@
         <v>1393.88</v>
       </c>
       <c r="G209" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H209" t="n">
-        <v>28656</v>
+        <v>4776</v>
       </c>
       <c r="I209" t="n">
-        <v>25090</v>
+        <v>4182</v>
       </c>
       <c r="J209" t="n">
-        <v>-3566</v>
+        <v>-594</v>
       </c>
       <c r="K209" t="n">
         <v>-12.44</v>
@@ -20270,16 +20286,16 @@
         <v>2280.55</v>
       </c>
       <c r="G210" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H210" t="n">
-        <v>26929</v>
+        <v>2992</v>
       </c>
       <c r="I210" t="n">
-        <v>20525</v>
+        <v>2281</v>
       </c>
       <c r="J210" t="n">
-        <v>-6404</v>
+        <v>-712</v>
       </c>
       <c r="K210" t="n">
         <v>-23.78</v>
@@ -20351,16 +20367,16 @@
         <v>578.35</v>
       </c>
       <c r="G211" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="H211" t="n">
-        <v>48487</v>
+        <v>9385</v>
       </c>
       <c r="I211" t="n">
-        <v>35858</v>
+        <v>6940</v>
       </c>
       <c r="J211" t="n">
-        <v>-12629</v>
+        <v>-2444</v>
       </c>
       <c r="K211" t="n">
         <v>-26.05</v>
@@ -20430,16 +20446,16 @@
         <v>958.4</v>
       </c>
       <c r="G212" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H212" t="n">
-        <v>31374</v>
+        <v>5779</v>
       </c>
       <c r="I212" t="n">
-        <v>36419</v>
+        <v>6709</v>
       </c>
       <c r="J212" t="n">
-        <v>5045</v>
+        <v>929</v>
       </c>
       <c r="K212" t="n">
         <v>16.08</v>
@@ -20511,16 +20527,16 @@
         <v>12159</v>
       </c>
       <c r="G213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>10624</v>
+        <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>12159</v>
+        <v>0</v>
       </c>
       <c r="J213" t="n">
-        <v>1535</v>
+        <v>0</v>
       </c>
       <c r="K213" t="n">
         <v>14.44</v>
@@ -20673,16 +20689,16 @@
         <v>1402.7</v>
       </c>
       <c r="G215" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H215" t="n">
-        <v>28358</v>
+        <v>4932</v>
       </c>
       <c r="I215" t="n">
-        <v>32262</v>
+        <v>5611</v>
       </c>
       <c r="J215" t="n">
-        <v>3904</v>
+        <v>679</v>
       </c>
       <c r="K215" t="n">
         <v>13.77</v>
@@ -20754,16 +20770,16 @@
         <v>1845.6</v>
       </c>
       <c r="G216" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H216" t="n">
-        <v>27900</v>
+        <v>4923</v>
       </c>
       <c r="I216" t="n">
-        <v>31375</v>
+        <v>5537</v>
       </c>
       <c r="J216" t="n">
-        <v>3476</v>
+        <v>613</v>
       </c>
       <c r="K216" t="n">
         <v>12.46</v>
@@ -20835,16 +20851,16 @@
         <v>1538.2</v>
       </c>
       <c r="G217" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H217" t="n">
-        <v>32059</v>
+        <v>5576</v>
       </c>
       <c r="I217" t="n">
-        <v>35379</v>
+        <v>6153</v>
       </c>
       <c r="J217" t="n">
-        <v>3319</v>
+        <v>577</v>
       </c>
       <c r="K217" t="n">
         <v>10.35</v>
@@ -20916,16 +20932,16 @@
         <v>1216.6</v>
       </c>
       <c r="G218" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H218" t="n">
-        <v>30996</v>
+        <v>5535</v>
       </c>
       <c r="I218" t="n">
-        <v>34065</v>
+        <v>6083</v>
       </c>
       <c r="J218" t="n">
-        <v>3069</v>
+        <v>548</v>
       </c>
       <c r="K218" t="n">
         <v>9.9</v>
@@ -20997,16 +21013,16 @@
         <v>7159.5</v>
       </c>
       <c r="G219" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>27123</v>
+        <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>28638</v>
+        <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>1515</v>
+        <v>0</v>
       </c>
       <c r="K219" t="n">
         <v>5.58</v>
@@ -21078,16 +21094,16 @@
         <v>1803.9</v>
       </c>
       <c r="G220" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H220" t="n">
-        <v>44456</v>
+        <v>8891</v>
       </c>
       <c r="I220" t="n">
-        <v>45098</v>
+        <v>9020</v>
       </c>
       <c r="J220" t="n">
-        <v>641</v>
+        <v>128</v>
       </c>
       <c r="K220" t="n">
         <v>1.44</v>
@@ -21159,16 +21175,16 @@
         <v>3382.6</v>
       </c>
       <c r="G221" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>20294</v>
+        <v>3382</v>
       </c>
       <c r="I221" t="n">
-        <v>20296</v>
+        <v>3383</v>
       </c>
       <c r="J221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K221" t="n">
         <v>0.01</v>
@@ -21240,16 +21256,16 @@
         <v>1301.6</v>
       </c>
       <c r="G222" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H222" t="n">
-        <v>20887</v>
+        <v>3916</v>
       </c>
       <c r="I222" t="n">
-        <v>20826</v>
+        <v>3905</v>
       </c>
       <c r="J222" t="n">
-        <v>-62</v>
+        <v>-12</v>
       </c>
       <c r="K222" t="n">
         <v>-0.29</v>
@@ -21319,16 +21335,16 @@
         <v>430.05</v>
       </c>
       <c r="G223" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="H223" t="n">
-        <v>33703</v>
+        <v>6566</v>
       </c>
       <c r="I223" t="n">
-        <v>33114</v>
+        <v>6451</v>
       </c>
       <c r="J223" t="n">
-        <v>-589</v>
+        <v>-115</v>
       </c>
       <c r="K223" t="n">
         <v>-1.75</v>
@@ -21400,16 +21416,16 @@
         <v>1200.5</v>
       </c>
       <c r="G224" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H224" t="n">
-        <v>39070</v>
+        <v>7814</v>
       </c>
       <c r="I224" t="n">
-        <v>36015</v>
+        <v>7203</v>
       </c>
       <c r="J224" t="n">
-        <v>-3056</v>
+        <v>-611</v>
       </c>
       <c r="K224" t="n">
         <v>-7.82</v>
@@ -21479,16 +21495,16 @@
         <v>2700</v>
       </c>
       <c r="G225" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H225" t="n">
-        <v>41854</v>
+        <v>5979</v>
       </c>
       <c r="I225" t="n">
-        <v>37800</v>
+        <v>5400</v>
       </c>
       <c r="J225" t="n">
-        <v>-4054</v>
+        <v>-579</v>
       </c>
       <c r="K225" t="n">
         <v>-9.69</v>
@@ -21554,16 +21570,16 @@
         <v>3401.6</v>
       </c>
       <c r="G226" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H226" t="n">
-        <v>36700</v>
+        <v>4078</v>
       </c>
       <c r="I226" t="n">
-        <v>30614</v>
+        <v>3402</v>
       </c>
       <c r="J226" t="n">
-        <v>-6086</v>
+        <v>-676</v>
       </c>
       <c r="K226" t="n">
         <v>-16.58</v>
@@ -21716,16 +21732,16 @@
         <v>1424.6</v>
       </c>
       <c r="G228" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H228" t="n">
-        <v>24730</v>
+        <v>3905</v>
       </c>
       <c r="I228" t="n">
-        <v>27067</v>
+        <v>4274</v>
       </c>
       <c r="J228" t="n">
-        <v>2337</v>
+        <v>369</v>
       </c>
       <c r="K228" t="n">
         <v>9.449999999999999</v>
@@ -21797,16 +21813,16 @@
         <v>3553.7</v>
       </c>
       <c r="G229" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H229" t="n">
-        <v>36576</v>
+        <v>6650</v>
       </c>
       <c r="I229" t="n">
-        <v>39091</v>
+        <v>7107</v>
       </c>
       <c r="J229" t="n">
-        <v>2515</v>
+        <v>457</v>
       </c>
       <c r="K229" t="n">
         <v>6.87</v>
@@ -21878,16 +21894,16 @@
         <v>12627</v>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>23788</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>25254</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>1466</v>
+        <v>0</v>
       </c>
       <c r="K230" t="n">
         <v>6.16</v>
@@ -21959,16 +21975,16 @@
         <v>1488.6</v>
       </c>
       <c r="G231" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H231" t="n">
-        <v>32262</v>
+        <v>5611</v>
       </c>
       <c r="I231" t="n">
-        <v>34238</v>
+        <v>5954</v>
       </c>
       <c r="J231" t="n">
-        <v>1976</v>
+        <v>344</v>
       </c>
       <c r="K231" t="n">
         <v>6.12</v>
@@ -22040,16 +22056,16 @@
         <v>3354.5</v>
       </c>
       <c r="G232" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H232" t="n">
-        <v>31713</v>
+        <v>6343</v>
       </c>
       <c r="I232" t="n">
-        <v>33545</v>
+        <v>6709</v>
       </c>
       <c r="J232" t="n">
-        <v>1832</v>
+        <v>366</v>
       </c>
       <c r="K232" t="n">
         <v>5.78</v>
@@ -22121,16 +22137,16 @@
         <v>1012.15</v>
       </c>
       <c r="G233" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H233" t="n">
-        <v>37378</v>
+        <v>6709</v>
       </c>
       <c r="I233" t="n">
-        <v>39474</v>
+        <v>7085</v>
       </c>
       <c r="J233" t="n">
-        <v>2096</v>
+        <v>376</v>
       </c>
       <c r="K233" t="n">
         <v>5.61</v>
@@ -22202,16 +22218,16 @@
         <v>32115</v>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>30705</v>
+        <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>32115</v>
+        <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>1410</v>
+        <v>0</v>
       </c>
       <c r="K234" t="n">
         <v>4.59</v>
@@ -22283,16 +22299,16 @@
         <v>1226.25</v>
       </c>
       <c r="G235" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H235" t="n">
-        <v>36498</v>
+        <v>7300</v>
       </c>
       <c r="I235" t="n">
-        <v>36788</v>
+        <v>7358</v>
       </c>
       <c r="J235" t="n">
-        <v>290</v>
+        <v>58</v>
       </c>
       <c r="K235" t="n">
         <v>0.79</v>
@@ -22364,16 +22380,16 @@
         <v>390.75</v>
       </c>
       <c r="G236" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H236" t="n">
-        <v>21992</v>
+        <v>4398</v>
       </c>
       <c r="I236" t="n">
-        <v>21491</v>
+        <v>4298</v>
       </c>
       <c r="J236" t="n">
-        <v>-500</v>
+        <v>-100</v>
       </c>
       <c r="K236" t="n">
         <v>-2.28</v>
@@ -22445,16 +22461,16 @@
         <v>414.95</v>
       </c>
       <c r="G237" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="H237" t="n">
-        <v>45585</v>
+        <v>9031</v>
       </c>
       <c r="I237" t="n">
-        <v>43985</v>
+        <v>8714</v>
       </c>
       <c r="J237" t="n">
-        <v>-1601</v>
+        <v>-317</v>
       </c>
       <c r="K237" t="n">
         <v>-3.51</v>
@@ -22526,16 +22542,16 @@
         <v>2375.4</v>
       </c>
       <c r="G238" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H238" t="n">
-        <v>24644</v>
+        <v>4929</v>
       </c>
       <c r="I238" t="n">
-        <v>23754</v>
+        <v>4751</v>
       </c>
       <c r="J238" t="n">
-        <v>-890</v>
+        <v>-178</v>
       </c>
       <c r="K238" t="n">
         <v>-3.61</v>
@@ -22607,16 +22623,16 @@
         <v>1459.45</v>
       </c>
       <c r="G239" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H239" t="n">
-        <v>33840</v>
+        <v>6153</v>
       </c>
       <c r="I239" t="n">
-        <v>32108</v>
+        <v>5838</v>
       </c>
       <c r="J239" t="n">
-        <v>-1732</v>
+        <v>-315</v>
       </c>
       <c r="K239" t="n">
         <v>-5.12</v>
@@ -22688,16 +22704,16 @@
         <v>3179.1</v>
       </c>
       <c r="G240" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H240" t="n">
-        <v>40819</v>
+        <v>6803</v>
       </c>
       <c r="I240" t="n">
-        <v>38149</v>
+        <v>6358</v>
       </c>
       <c r="J240" t="n">
-        <v>-2670</v>
+        <v>-445</v>
       </c>
       <c r="K240" t="n">
         <v>-6.54</v>
@@ -22769,16 +22785,16 @@
         <v>1682.5</v>
       </c>
       <c r="G241" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H241" t="n">
-        <v>28862</v>
+        <v>5412</v>
       </c>
       <c r="I241" t="n">
-        <v>26920</v>
+        <v>5048</v>
       </c>
       <c r="J241" t="n">
-        <v>-1942</v>
+        <v>-364</v>
       </c>
       <c r="K241" t="n">
         <v>-6.73</v>
@@ -22850,16 +22866,16 @@
         <v>16274</v>
       </c>
       <c r="G242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>25254</v>
+        <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>32548</v>
+        <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>7294</v>
+        <v>0</v>
       </c>
       <c r="K242" t="n">
         <v>28.88</v>
@@ -22931,16 +22947,16 @@
         <v>1584.4</v>
       </c>
       <c r="G243" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H243" t="n">
-        <v>27996</v>
+        <v>4420</v>
       </c>
       <c r="I243" t="n">
-        <v>30104</v>
+        <v>4753</v>
       </c>
       <c r="J243" t="n">
-        <v>2107</v>
+        <v>333</v>
       </c>
       <c r="K243" t="n">
         <v>7.53</v>
@@ -23093,16 +23109,16 @@
         <v>7837.5</v>
       </c>
       <c r="G245" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>22120</v>
+        <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>23512</v>
+        <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>1392</v>
+        <v>0</v>
       </c>
       <c r="K245" t="n">
         <v>6.29</v>
@@ -23174,16 +23190,16 @@
         <v>2501.6</v>
       </c>
       <c r="G246" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H246" t="n">
-        <v>30880</v>
+        <v>4751</v>
       </c>
       <c r="I246" t="n">
-        <v>32521</v>
+        <v>5003</v>
       </c>
       <c r="J246" t="n">
-        <v>1641</v>
+        <v>252</v>
       </c>
       <c r="K246" t="n">
         <v>5.31</v>
@@ -23255,16 +23271,16 @@
         <v>1282</v>
       </c>
       <c r="G247" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H247" t="n">
-        <v>30656</v>
+        <v>6131</v>
       </c>
       <c r="I247" t="n">
-        <v>32050</v>
+        <v>6410</v>
       </c>
       <c r="J247" t="n">
-        <v>1394</v>
+        <v>279</v>
       </c>
       <c r="K247" t="n">
         <v>4.55</v>
@@ -23336,16 +23352,16 @@
         <v>1507.1</v>
       </c>
       <c r="G248" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H248" t="n">
-        <v>54000</v>
+        <v>10216</v>
       </c>
       <c r="I248" t="n">
-        <v>55763</v>
+        <v>10550</v>
       </c>
       <c r="J248" t="n">
-        <v>1763</v>
+        <v>334</v>
       </c>
       <c r="K248" t="n">
         <v>3.26</v>
@@ -23417,16 +23433,16 @@
         <v>1283.6</v>
       </c>
       <c r="G249" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H249" t="n">
-        <v>26195</v>
+        <v>4990</v>
       </c>
       <c r="I249" t="n">
-        <v>26956</v>
+        <v>5134</v>
       </c>
       <c r="J249" t="n">
-        <v>760</v>
+        <v>145</v>
       </c>
       <c r="K249" t="n">
         <v>2.9</v>
@@ -23498,16 +23514,16 @@
         <v>394.05</v>
       </c>
       <c r="G250" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="H250" t="n">
-        <v>26180</v>
+        <v>5080</v>
       </c>
       <c r="I250" t="n">
-        <v>26401</v>
+        <v>5123</v>
       </c>
       <c r="J250" t="n">
-        <v>221</v>
+        <v>43</v>
       </c>
       <c r="K250" t="n">
         <v>0.84</v>
@@ -23579,16 +23595,16 @@
         <v>416.8</v>
       </c>
       <c r="G251" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H251" t="n">
-        <v>36516</v>
+        <v>7054</v>
       </c>
       <c r="I251" t="n">
-        <v>36678</v>
+        <v>7086</v>
       </c>
       <c r="J251" t="n">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="K251" t="n">
         <v>0.45</v>
@@ -23660,16 +23676,16 @@
         <v>994.75</v>
       </c>
       <c r="G252" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H252" t="n">
-        <v>32389</v>
+        <v>6073</v>
       </c>
       <c r="I252" t="n">
-        <v>31832</v>
+        <v>5968</v>
       </c>
       <c r="J252" t="n">
-        <v>-557</v>
+        <v>-104</v>
       </c>
       <c r="K252" t="n">
         <v>-1.72</v>
@@ -23741,16 +23757,16 @@
         <v>3063.2</v>
       </c>
       <c r="G253" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H253" t="n">
-        <v>38149</v>
+        <v>6358</v>
       </c>
       <c r="I253" t="n">
-        <v>36758</v>
+        <v>6126</v>
       </c>
       <c r="J253" t="n">
-        <v>-1391</v>
+        <v>-232</v>
       </c>
       <c r="K253" t="n">
         <v>-3.65</v>
@@ -23820,16 +23836,16 @@
         <v>1850.1</v>
       </c>
       <c r="G254" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H254" t="n">
-        <v>29250</v>
+        <v>5850</v>
       </c>
       <c r="I254" t="n">
-        <v>27752</v>
+        <v>5550</v>
       </c>
       <c r="J254" t="n">
-        <v>-1498</v>
+        <v>-300</v>
       </c>
       <c r="K254" t="n">
         <v>-5.12</v>
@@ -23899,16 +23915,16 @@
         <v>1377.7</v>
       </c>
       <c r="G255" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H255" t="n">
-        <v>31261</v>
+        <v>5954</v>
       </c>
       <c r="I255" t="n">
-        <v>28932</v>
+        <v>5511</v>
       </c>
       <c r="J255" t="n">
-        <v>-2329</v>
+        <v>-444</v>
       </c>
       <c r="K255" t="n">
         <v>-7.45</v>
@@ -24057,16 +24073,16 @@
         <v>1053.15</v>
       </c>
       <c r="G257" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H257" t="n">
-        <v>34371</v>
+        <v>6332</v>
       </c>
       <c r="I257" t="n">
-        <v>40020</v>
+        <v>7372</v>
       </c>
       <c r="J257" t="n">
-        <v>5649</v>
+        <v>1041</v>
       </c>
       <c r="K257" t="n">
         <v>16.43</v>
@@ -24138,16 +24154,16 @@
         <v>422.9</v>
       </c>
       <c r="G258" t="n">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="H258" t="n">
-        <v>35859</v>
+        <v>7093</v>
       </c>
       <c r="I258" t="n">
-        <v>38484</v>
+        <v>7612</v>
       </c>
       <c r="J258" t="n">
-        <v>2625</v>
+        <v>519</v>
       </c>
       <c r="K258" t="n">
         <v>7.32</v>
@@ -24219,16 +24235,16 @@
         <v>12589</v>
       </c>
       <c r="G259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>11918</v>
+        <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>12589</v>
+        <v>0</v>
       </c>
       <c r="J259" t="n">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="K259" t="n">
         <v>5.63</v>
@@ -24300,16 +24316,16 @@
         <v>7164.5</v>
       </c>
       <c r="G260" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H260" t="n">
-        <v>27360</v>
+        <v>0</v>
       </c>
       <c r="I260" t="n">
-        <v>28658</v>
+        <v>0</v>
       </c>
       <c r="J260" t="n">
-        <v>1298</v>
+        <v>0</v>
       </c>
       <c r="K260" t="n">
         <v>4.74</v>
@@ -24381,16 +24397,16 @@
         <v>745.8</v>
       </c>
       <c r="G261" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H261" t="n">
-        <v>42825</v>
+        <v>7984</v>
       </c>
       <c r="I261" t="n">
-        <v>44002</v>
+        <v>8204</v>
       </c>
       <c r="J261" t="n">
-        <v>1177</v>
+        <v>219</v>
       </c>
       <c r="K261" t="n">
         <v>2.75</v>
@@ -24462,16 +24478,16 @@
         <v>344.7</v>
       </c>
       <c r="G262" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="H262" t="n">
-        <v>31922</v>
+        <v>6113</v>
       </c>
       <c r="I262" t="n">
-        <v>32402</v>
+        <v>6205</v>
       </c>
       <c r="J262" t="n">
-        <v>479</v>
+        <v>92</v>
       </c>
       <c r="K262" t="n">
         <v>1.5</v>
@@ -24543,16 +24559,16 @@
         <v>247.95</v>
       </c>
       <c r="G263" t="n">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="H263" t="n">
-        <v>34930</v>
+        <v>6884</v>
       </c>
       <c r="I263" t="n">
-        <v>33969</v>
+        <v>6695</v>
       </c>
       <c r="J263" t="n">
-        <v>-960</v>
+        <v>-189</v>
       </c>
       <c r="K263" t="n">
         <v>-2.75</v>
@@ -24624,16 +24640,16 @@
         <v>1973.4</v>
       </c>
       <c r="G264" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H264" t="n">
-        <v>20293</v>
+        <v>4059</v>
       </c>
       <c r="I264" t="n">
-        <v>19734</v>
+        <v>3947</v>
       </c>
       <c r="J264" t="n">
-        <v>-559</v>
+        <v>-112</v>
       </c>
       <c r="K264" t="n">
         <v>-2.75</v>
@@ -24705,16 +24721,16 @@
         <v>3787.8</v>
       </c>
       <c r="G265" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H265" t="n">
-        <v>23429</v>
+        <v>3905</v>
       </c>
       <c r="I265" t="n">
-        <v>22727</v>
+        <v>3788</v>
       </c>
       <c r="J265" t="n">
-        <v>-703</v>
+        <v>-117</v>
       </c>
       <c r="K265" t="n">
         <v>-3</v>
@@ -24786,16 +24802,16 @@
         <v>1638.9</v>
       </c>
       <c r="G266" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H266" t="n">
-        <v>45873</v>
+        <v>8495</v>
       </c>
       <c r="I266" t="n">
-        <v>44250</v>
+        <v>8194</v>
       </c>
       <c r="J266" t="n">
-        <v>-1623</v>
+        <v>-300</v>
       </c>
       <c r="K266" t="n">
         <v>-3.54</v>
@@ -24867,16 +24883,16 @@
         <v>1447.2</v>
       </c>
       <c r="G267" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H267" t="n">
-        <v>46720</v>
+        <v>9043</v>
       </c>
       <c r="I267" t="n">
-        <v>44863</v>
+        <v>8683</v>
       </c>
       <c r="J267" t="n">
-        <v>-1857</v>
+        <v>-359</v>
       </c>
       <c r="K267" t="n">
         <v>-3.97</v>
@@ -24948,16 +24964,16 @@
         <v>1380.5</v>
       </c>
       <c r="G268" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H268" t="n">
-        <v>20322</v>
+        <v>2903</v>
       </c>
       <c r="I268" t="n">
-        <v>19327</v>
+        <v>2761</v>
       </c>
       <c r="J268" t="n">
-        <v>-995</v>
+        <v>-142</v>
       </c>
       <c r="K268" t="n">
         <v>-4.9</v>
@@ -25029,16 +25045,16 @@
         <v>926.4</v>
       </c>
       <c r="G269" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H269" t="n">
-        <v>32827</v>
+        <v>5968</v>
       </c>
       <c r="I269" t="n">
-        <v>30571</v>
+        <v>5558</v>
       </c>
       <c r="J269" t="n">
-        <v>-2256</v>
+        <v>-410</v>
       </c>
       <c r="K269" t="n">
         <v>-6.87</v>
@@ -25110,16 +25126,16 @@
         <v>1687.9</v>
       </c>
       <c r="G270" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H270" t="n">
-        <v>31452</v>
+        <v>5550</v>
       </c>
       <c r="I270" t="n">
-        <v>28694</v>
+        <v>5064</v>
       </c>
       <c r="J270" t="n">
-        <v>-2757</v>
+        <v>-487</v>
       </c>
       <c r="K270" t="n">
         <v>-8.77</v>
@@ -25191,16 +25207,16 @@
         <v>318.65</v>
       </c>
       <c r="G271" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H271" t="n">
-        <v>35845</v>
+        <v>7086</v>
       </c>
       <c r="I271" t="n">
-        <v>27404</v>
+        <v>5417</v>
       </c>
       <c r="J271" t="n">
-        <v>-8441</v>
+        <v>-1669</v>
       </c>
       <c r="K271" t="n">
         <v>-23.55</v>
@@ -25272,16 +25288,16 @@
         <v>318.35</v>
       </c>
       <c r="G272" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="H272" t="n">
-        <v>18313</v>
+        <v>3561</v>
       </c>
       <c r="I272" t="n">
-        <v>22921</v>
+        <v>4457</v>
       </c>
       <c r="J272" t="n">
-        <v>4608</v>
+        <v>896</v>
       </c>
       <c r="K272" t="n">
         <v>25.16</v>
@@ -25353,16 +25369,16 @@
         <v>299.55</v>
       </c>
       <c r="G273" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="H273" t="n">
-        <v>24299</v>
+        <v>4711</v>
       </c>
       <c r="I273" t="n">
-        <v>29356</v>
+        <v>5691</v>
       </c>
       <c r="J273" t="n">
-        <v>5057</v>
+        <v>980</v>
       </c>
       <c r="K273" t="n">
         <v>20.81</v>
@@ -25434,16 +25450,16 @@
         <v>399.15</v>
       </c>
       <c r="G274" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H274" t="n">
-        <v>18958</v>
+        <v>3792</v>
       </c>
       <c r="I274" t="n">
-        <v>21953</v>
+        <v>4391</v>
       </c>
       <c r="J274" t="n">
-        <v>2995</v>
+        <v>599</v>
       </c>
       <c r="K274" t="n">
         <v>15.8</v>
@@ -25515,16 +25531,16 @@
         <v>4385.2</v>
       </c>
       <c r="G275" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>35973</v>
+        <v>3997</v>
       </c>
       <c r="I275" t="n">
-        <v>39467</v>
+        <v>4385</v>
       </c>
       <c r="J275" t="n">
-        <v>3494</v>
+        <v>388</v>
       </c>
       <c r="K275" t="n">
         <v>9.710000000000001</v>
@@ -25596,16 +25612,16 @@
         <v>4014</v>
       </c>
       <c r="G276" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H276" t="n">
-        <v>41666</v>
+        <v>7576</v>
       </c>
       <c r="I276" t="n">
-        <v>44154</v>
+        <v>8028</v>
       </c>
       <c r="J276" t="n">
-        <v>2488</v>
+        <v>452</v>
       </c>
       <c r="K276" t="n">
         <v>5.97</v>
@@ -25677,16 +25693,16 @@
         <v>775</v>
       </c>
       <c r="G277" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H277" t="n">
-        <v>36544</v>
+        <v>6712</v>
       </c>
       <c r="I277" t="n">
-        <v>37975</v>
+        <v>6975</v>
       </c>
       <c r="J277" t="n">
-        <v>1431</v>
+        <v>263</v>
       </c>
       <c r="K277" t="n">
         <v>3.92</v>
@@ -25758,16 +25774,16 @@
         <v>1430.8</v>
       </c>
       <c r="G278" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H278" t="n">
-        <v>31752</v>
+        <v>5522</v>
       </c>
       <c r="I278" t="n">
-        <v>32908</v>
+        <v>5723</v>
       </c>
       <c r="J278" t="n">
-        <v>1157</v>
+        <v>201</v>
       </c>
       <c r="K278" t="n">
         <v>3.64</v>
@@ -25839,16 +25855,16 @@
         <v>1458.6</v>
       </c>
       <c r="G279" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H279" t="n">
-        <v>54097</v>
+        <v>9965</v>
       </c>
       <c r="I279" t="n">
-        <v>55427</v>
+        <v>10210</v>
       </c>
       <c r="J279" t="n">
-        <v>1330</v>
+        <v>245</v>
       </c>
       <c r="K279" t="n">
         <v>2.46</v>
@@ -25920,16 +25936,16 @@
         <v>1068.45</v>
       </c>
       <c r="G280" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H280" t="n">
-        <v>36860</v>
+        <v>7372</v>
       </c>
       <c r="I280" t="n">
-        <v>37396</v>
+        <v>7479</v>
       </c>
       <c r="J280" t="n">
-        <v>536</v>
+        <v>107</v>
       </c>
       <c r="K280" t="n">
         <v>1.45</v>
@@ -26001,16 +26017,16 @@
         <v>1886.8</v>
       </c>
       <c r="G281" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H281" t="n">
-        <v>37495</v>
+        <v>5920</v>
       </c>
       <c r="I281" t="n">
-        <v>35849</v>
+        <v>5660</v>
       </c>
       <c r="J281" t="n">
-        <v>-1645</v>
+        <v>-260</v>
       </c>
       <c r="K281" t="n">
         <v>-4.39</v>
@@ -26082,16 +26098,16 @@
         <v>1375.7</v>
       </c>
       <c r="G282" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H282" t="n">
-        <v>31838</v>
+        <v>5789</v>
       </c>
       <c r="I282" t="n">
-        <v>30265</v>
+        <v>5503</v>
       </c>
       <c r="J282" t="n">
-        <v>-1573</v>
+        <v>-286</v>
       </c>
       <c r="K282" t="n">
         <v>-4.94</v>
@@ -26163,16 +26179,16 @@
         <v>11586</v>
       </c>
       <c r="G283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H283" t="n">
-        <v>12589</v>
+        <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>11586</v>
+        <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>-1003</v>
+        <v>0</v>
       </c>
       <c r="K283" t="n">
         <v>-7.97</v>
@@ -26325,16 +26341,16 @@
         <v>539.55</v>
       </c>
       <c r="G285" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H285" t="n">
-        <v>20655</v>
+        <v>3645</v>
       </c>
       <c r="I285" t="n">
-        <v>18345</v>
+        <v>3237</v>
       </c>
       <c r="J285" t="n">
-        <v>-2310</v>
+        <v>-408</v>
       </c>
       <c r="K285" t="n">
         <v>-11.19</v>
@@ -26406,16 +26422,16 @@
         <v>771.7</v>
       </c>
       <c r="G286" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="H286" t="n">
-        <v>56510</v>
+        <v>11117</v>
       </c>
       <c r="I286" t="n">
-        <v>47074</v>
+        <v>9260</v>
       </c>
       <c r="J286" t="n">
-        <v>-9437</v>
+        <v>-1856</v>
       </c>
       <c r="K286" t="n">
         <v>-16.7</v>
@@ -26532,13 +26548,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D2" t="n">
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
         <v>-5.6</v>
@@ -26565,19 +26581,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>-5.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -26861,16 +26877,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C2" t="n">
         <v>12.6</v>
       </c>
       <c r="D2" t="n">
-        <v>563000</v>
+        <v>112600</v>
       </c>
       <c r="E2" t="n">
-        <v>559000</v>
+        <v>111800</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -26903,16 +26919,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>563000</v>
+        <v>112600</v>
       </c>
       <c r="C3" t="n">
         <v>-3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>542732</v>
+        <v>108546</v>
       </c>
       <c r="E3" t="n">
-        <v>561795</v>
+        <v>112359</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -26925,7 +26941,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.1</v>
+        <v>-10.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26945,16 +26961,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>542732</v>
+        <v>108546</v>
       </c>
       <c r="C4" t="n">
         <v>-1.9</v>
       </c>
       <c r="D4" t="n">
-        <v>532420</v>
+        <v>106484</v>
       </c>
       <c r="E4" t="n">
-        <v>572469</v>
+        <v>114494</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -26987,16 +27003,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>532420</v>
+        <v>106484</v>
       </c>
       <c r="C5" t="n">
         <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>530823</v>
+        <v>106165</v>
       </c>
       <c r="E5" t="n">
-        <v>509498</v>
+        <v>101900</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -27029,16 +27045,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>530823</v>
+        <v>106165</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>567980</v>
+        <v>113596</v>
       </c>
       <c r="E6" t="n">
-        <v>551786</v>
+        <v>110357</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27071,16 +27087,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>567980</v>
+        <v>113596</v>
       </c>
       <c r="C7" t="n">
         <v>14.8</v>
       </c>
       <c r="D7" t="n">
-        <v>652042</v>
+        <v>130408</v>
       </c>
       <c r="E7" t="n">
-        <v>568891</v>
+        <v>113778</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -27093,7 +27109,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.5</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27113,16 +27129,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>652042</v>
+        <v>130408</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>671603</v>
+        <v>134321</v>
       </c>
       <c r="E8" t="n">
-        <v>567184</v>
+        <v>113437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -27155,16 +27171,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>671603</v>
+        <v>134321</v>
       </c>
       <c r="C9" t="n">
         <v>13.2</v>
       </c>
       <c r="D9" t="n">
-        <v>760254</v>
+        <v>152051</v>
       </c>
       <c r="E9" t="n">
-        <v>618231</v>
+        <v>123646</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -27197,16 +27213,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>760254</v>
+        <v>152051</v>
       </c>
       <c r="C10" t="n">
         <v>9.1</v>
       </c>
       <c r="D10" t="n">
-        <v>829437</v>
+        <v>165887</v>
       </c>
       <c r="E10" t="n">
-        <v>628741</v>
+        <v>125748</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -27239,16 +27255,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>829437</v>
+        <v>165887</v>
       </c>
       <c r="C11" t="n">
         <v>13.6</v>
       </c>
       <c r="D11" t="n">
-        <v>942241</v>
+        <v>188448</v>
       </c>
       <c r="E11" t="n">
-        <v>703561</v>
+        <v>140712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -27281,16 +27297,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>942241</v>
+        <v>188448</v>
       </c>
       <c r="C12" t="n">
         <v>0.8</v>
       </c>
       <c r="D12" t="n">
-        <v>949779</v>
+        <v>189956</v>
       </c>
       <c r="E12" t="n">
-        <v>700043</v>
+        <v>140009</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -27323,16 +27339,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>949779</v>
+        <v>189956</v>
       </c>
       <c r="C13" t="n">
         <v>12.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1065652</v>
+        <v>213130</v>
       </c>
       <c r="E13" t="n">
-        <v>780548</v>
+        <v>156110</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -27365,16 +27381,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1065652</v>
+        <v>213130</v>
       </c>
       <c r="C14" t="n">
         <v>4.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1110409</v>
+        <v>222082</v>
       </c>
       <c r="E14" t="n">
-        <v>790696</v>
+        <v>158139</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -27407,16 +27423,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1110409</v>
+        <v>222082</v>
       </c>
       <c r="C15" t="n">
         <v>-6.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1039343</v>
+        <v>207869</v>
       </c>
       <c r="E15" t="n">
-        <v>742463</v>
+        <v>148493</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -27449,16 +27465,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1039343</v>
+        <v>207869</v>
       </c>
       <c r="C16" t="n">
         <v>3.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1073641</v>
+        <v>214728</v>
       </c>
       <c r="E16" t="n">
-        <v>771419</v>
+        <v>154284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -27491,16 +27507,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1073641</v>
+        <v>214728</v>
       </c>
       <c r="C17" t="n">
         <v>1.9</v>
       </c>
       <c r="D17" t="n">
-        <v>1094041</v>
+        <v>218808</v>
       </c>
       <c r="E17" t="n">
-        <v>802276</v>
+        <v>160455</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -27533,16 +27549,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1094041</v>
+        <v>218808</v>
       </c>
       <c r="C18" t="n">
         <v>2.7</v>
       </c>
       <c r="D18" t="n">
-        <v>1123580</v>
+        <v>224716</v>
       </c>
       <c r="E18" t="n">
-        <v>820728</v>
+        <v>164146</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -27575,16 +27591,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1123580</v>
+        <v>224716</v>
       </c>
       <c r="C19" t="n">
         <v>-1.6</v>
       </c>
       <c r="D19" t="n">
-        <v>1105602</v>
+        <v>221120</v>
       </c>
       <c r="E19" t="n">
-        <v>801031</v>
+        <v>160206</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -27617,16 +27633,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1105602</v>
+        <v>221120</v>
       </c>
       <c r="C20" t="n">
         <v>0.8</v>
       </c>
       <c r="D20" t="n">
-        <v>1114447</v>
+        <v>222889</v>
       </c>
       <c r="E20" t="n">
-        <v>763382</v>
+        <v>152676</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -27659,16 +27675,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C21" t="n">
         <v>122.9</v>
       </c>
       <c r="D21" t="n">
-        <v>1114447</v>
+        <v>222889</v>
       </c>
       <c r="E21" t="n">
-        <v>763382</v>
+        <v>152676</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -27714,12 +27730,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27729,12 +27745,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27744,12 +27760,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27759,12 +27775,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27774,12 +27790,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27789,12 +27805,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27819,12 +27835,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cement</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Market" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="About" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,12 +425,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TODAY</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -456,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -524,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -536,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TORNTPHARM (82)</t>
+          <t>APOLLOHOSP (81)</t>
         </is>
       </c>
     </row>
@@ -548,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (55)</t>
+          <t>ITC (56)</t>
         </is>
       </c>
     </row>
@@ -560,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SBILIFE, SUNPHARMA</t>
         </is>
       </c>
     </row>
@@ -572,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ICICIGI, TORNTPHARM</t>
         </is>
       </c>
     </row>
@@ -583,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -649,12 +637,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -700,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-14  /  2026-07-14</t>
+          <t>2026-07-17  /  2026-07-17</t>
         </is>
       </c>
     </row>
@@ -736,7 +724,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rs1L</t>
+          <t>Rs5L</t>
         </is>
       </c>
     </row>
@@ -748,7 +736,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs60,000 (60%)</t>
+          <t>Rs300,000 (60%)</t>
         </is>
       </c>
     </row>
@@ -760,7 +748,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs40,000 (40%)</t>
+          <t>Rs200,000 (40%)</t>
         </is>
       </c>
     </row>
@@ -772,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -816,7 +804,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs102,500</t>
+          <t>Rs512,500</t>
         </is>
       </c>
     </row>
@@ -828,7 +816,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rs120,400</t>
+          <t>Rs602,000</t>
         </is>
       </c>
     </row>
@@ -840,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rs91,600</t>
+          <t>Rs458,000</t>
         </is>
       </c>
     </row>
@@ -908,7 +896,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
+          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -920,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -932,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1136,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
+          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -1377,142 +1365,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Portfolio Suitability</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Suitability Breakdown</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Top Factor</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Weakest Factor</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>F: Historical</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>F: Technical/Trend</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>F: Risk/Vol</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>F: Sector</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F: Regime</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Buy Range</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Expected Range (hist)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Prob +ve</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Rec Confidence %</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Selected Because</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Not Evaluated</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Why This vs Alternatives</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1525,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +17 · Regime +9 · Sector +9 = 82</t>
+          <t>Risk/Vol +25 · Historical +19 · Trend/Tech +19 · Regime +9 · Sector +9 = 81</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1543,36 +1531,36 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>TORNTPHARM</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4967.1</v>
+        <v>8826</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4830 - 5104</t>
+          <t>8617 - 9035</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1586,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+21.9%)</t>
+          <t>Above 200-DMA (+14.8%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1603,21 +1591,21 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>35304</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>7.9</v>
+        <v>12.3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Healthcare name under the sector cap</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1627,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TORNTPHARM: 82; SUNPHARMA: 78, CIPLA: 76, BIOCON: 74</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 81; FORTIS: 72, MAXHEALTH: 69, LALPATHLAB: 63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+21.9%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +6.2%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.8%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1643,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +19 · Trend/Tech +18 · Regime +9 · Sector +9 = 80</t>
+          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +9 = 78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1661,58 +1649,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I3" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>8806</v>
+        <v>1932.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>8591 - 9021</t>
+          <t>1880 - 1986</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +14%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+14.8%)</t>
+          <t>Above 200-DMA (+10.0%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1721,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>23191</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>7.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Healthcare name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1745,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 80; FORTIS: 72, MAXHEALTH: 71, LALPATHLAB: 63</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 78; TORNTPHARM: 83, ABBOTINDIA: 78, ALKEM: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.8%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1761,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +6 = 75</t>
+          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +6 = 76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1782,13 +1770,13 @@
         <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H4" t="n">
         <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1804,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>845.3</v>
+        <v>844</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>825 - 865</t>
+          <t>824 - 864</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1826,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.5%)</t>
+          <t>Above 200-DMA (+10.1%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1839,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>5917</v>
+        <v>32072</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="X4" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1863,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 75; NESTLEIND: 76, UNITDSPR: 66, TATACONSUM: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 76; NESTLEIND: 76, UNITDSPR: 67, DABUR: 60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+10.5%) • outperforming Nifty • sector strength 65/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+10.1%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
@@ -1879,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +9 = 73</t>
+          <t>Risk/Vol +25 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +9 = 75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1900,7 +1888,7 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H5" t="n">
         <v>99</v>
@@ -1922,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2488.8</v>
+        <v>2443.2</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2427 - 2550</t>
+          <t>2382 - 2505</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1940,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+13.7%)</t>
+          <t>Above 200-DMA (+11.2%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1957,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>4978</v>
+        <v>26875</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1981,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 73; TORNTPHARM: 82, SUNPHARMA: 78, CIPLA: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 75; TORNTPHARM: 83, ABBOTINDIA: 78, SUNPHARMA: 78. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+13.7%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1997,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +4 = 73</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +4 = 74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2018,10 +2006,10 @@
         <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H6" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
         <v>35</v>
@@ -2040,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1397.6</v>
+        <v>1444.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1358 - 1438</t>
+          <t>1403 - 1486</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2062,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+3.9%)</t>
+          <t>Above 200-DMA (+7.3%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2075,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>2795</v>
+        <v>18776</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2099,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 73; LICI: 64, SBIN: 64, FEDERALBNK: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 74; FEDERALBNK: 66, SBIN: 65, KOTAKBANK: 63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.9%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -2115,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Regime +9 · Trend/Tech +8 · Sector +5 = 69</t>
+          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +6 = 71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2136,13 +2124,13 @@
         <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H7" t="n">
         <v>97</v>
       </c>
       <c r="I7" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2158,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1905.7</v>
+        <v>1908.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1853 - 1958</t>
+          <t>1856 - 1962</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2176,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.3%)</t>
+          <t>Below 200-DMA (-2.2%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2193,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>5717</v>
+        <v>24814</v>
       </c>
       <c r="W7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="X7" t="n">
-        <v>10.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2217,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 69; INDUSTOWER: 55, TATACOMM: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 71; INDUSTOWER: 57, TATACOMM: 51</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.3%) • sector strength 47/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.2%) • sector strength 65/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -2233,76 +2221,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +7 · Trend/Tech +4 = 69</t>
+          <t>Risk/Vol +22 · Trend/Tech +17 · Historical +14 · Regime +9 · Sector +8 = 70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>45</v>
+      </c>
+      <c r="G8" t="n">
         <v>84</v>
       </c>
-      <c r="G8" t="n">
-        <v>18</v>
-      </c>
       <c r="H8" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>353</v>
+        <v>1566.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>343 - 363</t>
+          <t>1517 - 1615</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.0%)</t>
+          <t>Above 200-DMA (+6.8%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2311,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>3530</v>
+        <v>23491</v>
       </c>
       <c r="W8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="X8" t="n">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2335,32 +2323,32 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 69; NHPC: 60, POWERGRID: 60, JSWENERGY: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 64, BALRAMCHIN: 61, DEEPAKNTR: 61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-1.0%) • sector strength 71/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+6.8%) • outperforming Nifty • sector strength 76/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +6 = 69</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2369,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I9" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1568</v>
+        <v>341.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1518 - 1618</t>
+          <t>332 - 351</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.0%)</t>
+          <t>Below 200-DMA (-4.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2429,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>1568</v>
+        <v>18460</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2453,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 69; NAVINFLUOR: 61, BALRAMCHIN: 59, DEEPAKNTR: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 57, NHPC: 54, TATAPOWER: 52</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+7.0%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.2%) • sector strength 24/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2469,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Sector +7 · Trend/Tech +4 = 60</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +7 · Sector +2 = 59</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2483,62 +2471,62 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>56</v>
       </c>
       <c r="G10" t="n">
+        <v>37</v>
+      </c>
+      <c r="H10" t="n">
+        <v>94</v>
+      </c>
+      <c r="I10" t="n">
         <v>18</v>
-      </c>
-      <c r="H10" t="n">
-        <v>92</v>
-      </c>
-      <c r="I10" t="n">
-        <v>71</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>284.6</v>
+        <v>1327.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>276 - 293</t>
+          <t>1288 - 1367</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1% to +7%</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.5%)</t>
+          <t>Below 200-DMA (-6.1%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2547,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>3131</v>
+        <v>25217</v>
       </c>
       <c r="W10" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="X10" t="n">
-        <v>5.4</v>
+        <v>8.5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2571,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 60; NTPC: 69, NHPC: 60, JSWENERGY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 59; GAIL: 61, IOC: 48, ONGC: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.5%) • sector strength 71/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-6.1%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2587,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +16 · Regime +9 · Trend/Tech +5 · Sector +4 = 58</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +2 = 57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2605,36 +2593,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H11" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1763.2</v>
+        <v>283.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1714 - 1813</t>
+          <t>275 - 292</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2652,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.0%)</t>
+          <t>Below 200-DMA (-0.9%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2665,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>5290</v>
+        <v>16162</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2689,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIGI: 58; ICICIBANK: 73, LICI: 64, SBIN: 64. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, NHPC: 54, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-6.0%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +7.7%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.9%) • sector strength 24/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2697,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +1 = 56</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Sector +6 · Trend/Tech +4 = 56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2719,50 +2707,50 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1295.2</v>
+        <v>280.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1256 - 1334</t>
+          <t>273 - 288</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-1% to +7%</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2770,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.5%)</t>
+          <t>Below 200-DMA (-17.3%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2783,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>3886</v>
+        <v>30596</v>
       </c>
       <c r="W12" t="n">
-        <v>3</v>
+        <v>109</v>
       </c>
       <c r="X12" t="n">
-        <v>8.4</v>
+        <v>10.2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2807,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 56; GAIL: 60, ONGC: 48, IGL: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 56; MARICO: 76, NESTLEIND: 76, UNITDSPR: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.5%) • sector strength 12/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.3%) • sector strength 59/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2823,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Sector +6 · Trend/Tech +3 = 55</t>
+          <t>Risk/Vol +23 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +4 = 56</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2837,62 +2825,62 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I13" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>280.3</v>
+        <v>1829.4</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>273 - 288</t>
+          <t>1775 - 1884</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.9%)</t>
+          <t>Below 200-DMA (-4.7%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2901,21 +2889,21 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>5045</v>
+        <v>18294</v>
       </c>
       <c r="W13" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="X13" t="n">
-        <v>8.699999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2925,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; NESTLEIND: 76, MARICO: 75, UNITDSPR: 66. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBILIFE: 56; ICICIBANK: 74, FEDERALBNK: 66, SBIN: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.9%) • sector strength 65/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-4.7%) • sector strength 35/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +0.0%</t>
         </is>
       </c>
     </row>
@@ -2949,77 +2937,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Start Rs</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>End Rs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Year Ret %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Beat Nifty</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cycles</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Win %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Losers</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Avg Return %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Median %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Best %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Worst %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
         </is>
@@ -3030,10 +3018,10 @@
         <v>2021</v>
       </c>
       <c r="B2" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C2" t="n">
-        <v>108546</v>
+        <v>542732</v>
       </c>
       <c r="D2" t="n">
         <v>8.5</v>
@@ -3071,7 +3059,7 @@
         <v>-14.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3480</v>
+        <v>43738</v>
       </c>
     </row>
     <row r="3">
@@ -3079,10 +3067,10 @@
         <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C3" t="n">
-        <v>120141</v>
+        <v>600703</v>
       </c>
       <c r="D3" t="n">
         <v>20.1</v>
@@ -3120,7 +3108,7 @@
         <v>-19.8</v>
       </c>
       <c r="O3" t="n">
-        <v>19532</v>
+        <v>93560</v>
       </c>
     </row>
     <row r="4">
@@ -3128,10 +3116,10 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C4" t="n">
-        <v>144506</v>
+        <v>722531</v>
       </c>
       <c r="D4" t="n">
         <v>44.5</v>
@@ -3169,7 +3157,7 @@
         <v>-16.5</v>
       </c>
       <c r="O4" t="n">
-        <v>30402</v>
+        <v>176947</v>
       </c>
     </row>
     <row r="5">
@@ -3177,10 +3165,10 @@
         <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C5" t="n">
-        <v>110305</v>
+        <v>551527</v>
       </c>
       <c r="D5" t="n">
         <v>10.3</v>
@@ -3218,7 +3206,7 @@
         <v>-26</v>
       </c>
       <c r="O5" t="n">
-        <v>7395</v>
+        <v>56158</v>
       </c>
     </row>
     <row r="6">
@@ -3226,10 +3214,10 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C6" t="n">
-        <v>106375</v>
+        <v>531876</v>
       </c>
       <c r="D6" t="n">
         <v>6.4</v>
@@ -3267,7 +3255,7 @@
         <v>-23.6</v>
       </c>
       <c r="O6" t="n">
-        <v>157</v>
+        <v>15954</v>
       </c>
     </row>
     <row r="7">
@@ -3275,10 +3263,10 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C7" t="n">
-        <v>100800</v>
+        <v>504000</v>
       </c>
       <c r="D7" t="n">
         <v>0.8</v>
@@ -3316,7 +3304,7 @@
         <v>-16.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1322</v>
+        <v>7126</v>
       </c>
     </row>
   </sheetData>
@@ -3334,107 +3322,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rec ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Buy Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Invested Rs</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Exit Value Rs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Contribution %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Max Profit %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Max Loss %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Captured %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAGR %</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Rank in Universe</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Why Picked</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3468,16 +3456,16 @@
         <v>22031.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>66945</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>88125</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>21180</v>
       </c>
       <c r="K2" t="n">
         <v>31.64</v>
@@ -3549,16 +3537,16 @@
         <v>4737.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>3618</v>
+        <v>32560</v>
       </c>
       <c r="I3" t="n">
-        <v>4737</v>
+        <v>42637</v>
       </c>
       <c r="J3" t="n">
-        <v>1120</v>
+        <v>10077</v>
       </c>
       <c r="K3" t="n">
         <v>30.95</v>
@@ -3630,16 +3618,16 @@
         <v>675.9</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>3136</v>
+        <v>16725</v>
       </c>
       <c r="I4" t="n">
-        <v>4055</v>
+        <v>21629</v>
       </c>
       <c r="J4" t="n">
-        <v>920</v>
+        <v>4904</v>
       </c>
       <c r="K4" t="n">
         <v>29.32</v>
@@ -3711,16 +3699,16 @@
         <v>3990.05</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>6439</v>
+        <v>32195</v>
       </c>
       <c r="I5" t="n">
-        <v>7980</v>
+        <v>39900</v>
       </c>
       <c r="J5" t="n">
-        <v>1541</v>
+        <v>7706</v>
       </c>
       <c r="K5" t="n">
         <v>23.93</v>
@@ -3792,16 +3780,16 @@
         <v>1834.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>3194</v>
+        <v>19162</v>
       </c>
       <c r="I6" t="n">
-        <v>3669</v>
+        <v>22016</v>
       </c>
       <c r="J6" t="n">
-        <v>476</v>
+        <v>2854</v>
       </c>
       <c r="K6" t="n">
         <v>14.89</v>
@@ -3873,16 +3861,16 @@
         <v>3730.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>3342</v>
+        <v>20049</v>
       </c>
       <c r="I7" t="n">
-        <v>3730</v>
+        <v>22381</v>
       </c>
       <c r="J7" t="n">
-        <v>389</v>
+        <v>2332</v>
       </c>
       <c r="K7" t="n">
         <v>11.63</v>
@@ -3954,16 +3942,16 @@
         <v>1208.63</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>3254</v>
+        <v>20607</v>
       </c>
       <c r="I8" t="n">
-        <v>3626</v>
+        <v>22964</v>
       </c>
       <c r="J8" t="n">
-        <v>372</v>
+        <v>2357</v>
       </c>
       <c r="K8" t="n">
         <v>11.44</v>
@@ -4035,16 +4023,16 @@
         <v>3921.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>7192</v>
+        <v>39554</v>
       </c>
       <c r="I9" t="n">
-        <v>7842</v>
+        <v>43132</v>
       </c>
       <c r="J9" t="n">
-        <v>651</v>
+        <v>3578</v>
       </c>
       <c r="K9" t="n">
         <v>9.050000000000001</v>
@@ -4116,16 +4104,16 @@
         <v>9740.799999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>35809</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>38963</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3154</v>
       </c>
       <c r="K10" t="n">
         <v>8.81</v>
@@ -4197,16 +4185,16 @@
         <v>2321.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>6524</v>
+        <v>34794</v>
       </c>
       <c r="I11" t="n">
-        <v>6965</v>
+        <v>37146</v>
       </c>
       <c r="J11" t="n">
-        <v>441</v>
+        <v>2351</v>
       </c>
       <c r="K11" t="n">
         <v>6.76</v>
@@ -4278,16 +4266,16 @@
         <v>1665.15</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>3121</v>
+        <v>20285</v>
       </c>
       <c r="I12" t="n">
-        <v>3330</v>
+        <v>21647</v>
       </c>
       <c r="J12" t="n">
-        <v>210</v>
+        <v>1362</v>
       </c>
       <c r="K12" t="n">
         <v>6.71</v>
@@ -4359,16 +4347,16 @@
         <v>729.45</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="H13" t="n">
-        <v>6858</v>
+        <v>34973</v>
       </c>
       <c r="I13" t="n">
-        <v>7294</v>
+        <v>37202</v>
       </c>
       <c r="J13" t="n">
-        <v>437</v>
+        <v>2229</v>
       </c>
       <c r="K13" t="n">
         <v>6.37</v>
@@ -4440,16 +4428,16 @@
         <v>1687.8</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H14" t="n">
-        <v>10249</v>
+        <v>58079</v>
       </c>
       <c r="I14" t="n">
-        <v>10127</v>
+        <v>57385</v>
       </c>
       <c r="J14" t="n">
-        <v>-122</v>
+        <v>-694</v>
       </c>
       <c r="K14" t="n">
         <v>-1.19</v>
@@ -4521,16 +4509,16 @@
         <v>178.85</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="H15" t="n">
-        <v>4002</v>
+        <v>20373</v>
       </c>
       <c r="I15" t="n">
-        <v>3935</v>
+        <v>20031</v>
       </c>
       <c r="J15" t="n">
-        <v>-67</v>
+        <v>-342</v>
       </c>
       <c r="K15" t="n">
         <v>-1.68</v>
@@ -4602,16 +4590,16 @@
         <v>1928.9</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>4228</v>
+        <v>29596</v>
       </c>
       <c r="I16" t="n">
-        <v>3858</v>
+        <v>27005</v>
       </c>
       <c r="J16" t="n">
-        <v>-370</v>
+        <v>-2591</v>
       </c>
       <c r="K16" t="n">
         <v>-8.76</v>
@@ -4683,16 +4671,16 @@
         <v>1898.45</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H17" t="n">
-        <v>4995</v>
+        <v>31638</v>
       </c>
       <c r="I17" t="n">
-        <v>5695</v>
+        <v>36071</v>
       </c>
       <c r="J17" t="n">
-        <v>700</v>
+        <v>4433</v>
       </c>
       <c r="K17" t="n">
         <v>14.01</v>
@@ -4764,16 +4752,16 @@
         <v>30.95</v>
       </c>
       <c r="G18" t="n">
-        <v>159</v>
+        <v>799</v>
       </c>
       <c r="H18" t="n">
-        <v>4516</v>
+        <v>22692</v>
       </c>
       <c r="I18" t="n">
-        <v>4921</v>
+        <v>24729</v>
       </c>
       <c r="J18" t="n">
-        <v>405</v>
+        <v>2037</v>
       </c>
       <c r="K18" t="n">
         <v>8.98</v>
@@ -4845,16 +4833,16 @@
         <v>31.2</v>
       </c>
       <c r="G19" t="n">
-        <v>142</v>
+        <v>714</v>
       </c>
       <c r="H19" t="n">
-        <v>4132</v>
+        <v>20777</v>
       </c>
       <c r="I19" t="n">
-        <v>4430</v>
+        <v>22277</v>
       </c>
       <c r="J19" t="n">
-        <v>298</v>
+        <v>1499</v>
       </c>
       <c r="K19" t="n">
         <v>7.22</v>
@@ -4926,16 +4914,16 @@
         <v>1626.05</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H20" t="n">
-        <v>7701</v>
+        <v>41588</v>
       </c>
       <c r="I20" t="n">
-        <v>8130</v>
+        <v>43903</v>
       </c>
       <c r="J20" t="n">
-        <v>429</v>
+        <v>2316</v>
       </c>
       <c r="K20" t="n">
         <v>5.57</v>
@@ -5007,16 +4995,16 @@
         <v>1236.98</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H21" t="n">
-        <v>6043</v>
+        <v>30216</v>
       </c>
       <c r="I21" t="n">
-        <v>6185</v>
+        <v>30924</v>
       </c>
       <c r="J21" t="n">
-        <v>142</v>
+        <v>709</v>
       </c>
       <c r="K21" t="n">
         <v>2.35</v>
@@ -5088,16 +5076,16 @@
         <v>3817.75</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>3730</v>
+        <v>26111</v>
       </c>
       <c r="I22" t="n">
-        <v>3818</v>
+        <v>26724</v>
       </c>
       <c r="J22" t="n">
-        <v>88</v>
+        <v>613</v>
       </c>
       <c r="K22" t="n">
         <v>2.35</v>
@@ -5169,16 +5157,16 @@
         <v>1209.4</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H23" t="n">
-        <v>6045</v>
+        <v>35062</v>
       </c>
       <c r="I23" t="n">
-        <v>6047</v>
+        <v>35073</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
         <v>0.03</v>
@@ -5250,16 +5238,16 @@
         <v>1091.18</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H24" t="n">
-        <v>6873</v>
+        <v>35513</v>
       </c>
       <c r="I24" t="n">
-        <v>6547</v>
+        <v>33827</v>
       </c>
       <c r="J24" t="n">
-        <v>-326</v>
+        <v>-1686</v>
       </c>
       <c r="K24" t="n">
         <v>-4.75</v>
@@ -5331,16 +5319,16 @@
         <v>9043.200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>19482</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>18086</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1395</v>
       </c>
       <c r="K25" t="n">
         <v>-7.16</v>
@@ -5412,16 +5400,16 @@
         <v>3617.55</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>7842</v>
+        <v>47053</v>
       </c>
       <c r="I26" t="n">
-        <v>7235</v>
+        <v>43411</v>
       </c>
       <c r="J26" t="n">
-        <v>-607</v>
+        <v>-3643</v>
       </c>
       <c r="K26" t="n">
         <v>-7.74</v>
@@ -5493,16 +5481,16 @@
         <v>650.5</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H27" t="n">
-        <v>7294</v>
+        <v>36472</v>
       </c>
       <c r="I27" t="n">
-        <v>6505</v>
+        <v>32525</v>
       </c>
       <c r="J27" t="n">
-        <v>-790</v>
+        <v>-3948</v>
       </c>
       <c r="K27" t="n">
         <v>-10.82</v>
@@ -5574,16 +5562,16 @@
         <v>1917.45</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>6541</v>
+        <v>37067</v>
       </c>
       <c r="I28" t="n">
-        <v>5752</v>
+        <v>32597</v>
       </c>
       <c r="J28" t="n">
-        <v>-789</v>
+        <v>-4470</v>
       </c>
       <c r="K28" t="n">
         <v>-12.06</v>
@@ -5649,16 +5637,16 @@
         <v>2476.6</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>2848</v>
+        <v>25632</v>
       </c>
       <c r="I29" t="n">
-        <v>2477</v>
+        <v>22289</v>
       </c>
       <c r="J29" t="n">
-        <v>-371</v>
+        <v>-3342</v>
       </c>
       <c r="K29" t="n">
         <v>-13.04</v>
@@ -5730,16 +5718,16 @@
         <v>1463.8</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H30" t="n">
-        <v>8439</v>
+        <v>43883</v>
       </c>
       <c r="I30" t="n">
-        <v>7319</v>
+        <v>38059</v>
       </c>
       <c r="J30" t="n">
-        <v>-1120</v>
+        <v>-5824</v>
       </c>
       <c r="K30" t="n">
         <v>-13.27</v>
@@ -5811,16 +5799,16 @@
         <v>3277.1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>3853</v>
+        <v>26968</v>
       </c>
       <c r="I31" t="n">
-        <v>3277</v>
+        <v>22940</v>
       </c>
       <c r="J31" t="n">
-        <v>-576</v>
+        <v>-4028</v>
       </c>
       <c r="K31" t="n">
         <v>-14.94</v>
@@ -5892,16 +5880,16 @@
         <v>3809.7</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>3277</v>
+        <v>19663</v>
       </c>
       <c r="I32" t="n">
-        <v>3810</v>
+        <v>22858</v>
       </c>
       <c r="J32" t="n">
-        <v>533</v>
+        <v>3196</v>
       </c>
       <c r="K32" t="n">
         <v>16.25</v>
@@ -5973,16 +5961,16 @@
         <v>1586.7</v>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H33" t="n">
-        <v>11710</v>
+        <v>62943</v>
       </c>
       <c r="I33" t="n">
-        <v>12694</v>
+        <v>68228</v>
       </c>
       <c r="J33" t="n">
-        <v>983</v>
+        <v>5285</v>
       </c>
       <c r="K33" t="n">
         <v>8.4</v>
@@ -6054,16 +6042,16 @@
         <v>804.13</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="H34" t="n">
-        <v>8358</v>
+        <v>43310</v>
       </c>
       <c r="I34" t="n">
-        <v>8845</v>
+        <v>45835</v>
       </c>
       <c r="J34" t="n">
-        <v>487</v>
+        <v>2525</v>
       </c>
       <c r="K34" t="n">
         <v>5.83</v>
@@ -6135,16 +6123,16 @@
         <v>1253.83</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H35" t="n">
-        <v>8659</v>
+        <v>44531</v>
       </c>
       <c r="I35" t="n">
-        <v>8777</v>
+        <v>45138</v>
       </c>
       <c r="J35" t="n">
-        <v>118</v>
+        <v>607</v>
       </c>
       <c r="K35" t="n">
         <v>1.36</v>
@@ -6216,16 +6204,16 @@
         <v>3814.8</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>3818</v>
+        <v>34360</v>
       </c>
       <c r="I36" t="n">
-        <v>3815</v>
+        <v>34333</v>
       </c>
       <c r="J36" t="n">
-        <v>-3</v>
+        <v>-27</v>
       </c>
       <c r="K36" t="n">
         <v>-0.08</v>
@@ -6297,16 +6285,16 @@
         <v>1861.1</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H37" t="n">
-        <v>5695</v>
+        <v>36071</v>
       </c>
       <c r="I37" t="n">
-        <v>5583</v>
+        <v>35361</v>
       </c>
       <c r="J37" t="n">
-        <v>-112</v>
+        <v>-710</v>
       </c>
       <c r="K37" t="n">
         <v>-1.97</v>
@@ -6378,16 +6366,16 @@
         <v>1836.05</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H38" t="n">
-        <v>3846</v>
+        <v>23074</v>
       </c>
       <c r="I38" t="n">
-        <v>3672</v>
+        <v>22033</v>
       </c>
       <c r="J38" t="n">
-        <v>-174</v>
+        <v>-1042</v>
       </c>
       <c r="K38" t="n">
         <v>-4.51</v>
@@ -6459,16 +6447,16 @@
         <v>828.65</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>3504</v>
+        <v>21024</v>
       </c>
       <c r="I39" t="n">
-        <v>3315</v>
+        <v>19888</v>
       </c>
       <c r="J39" t="n">
-        <v>-189</v>
+        <v>-1136</v>
       </c>
       <c r="K39" t="n">
         <v>-5.41</v>
@@ -6540,16 +6528,16 @@
         <v>2332.25</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>2477</v>
+        <v>22289</v>
       </c>
       <c r="I40" t="n">
-        <v>2332</v>
+        <v>20990</v>
       </c>
       <c r="J40" t="n">
-        <v>-144</v>
+        <v>-1299</v>
       </c>
       <c r="K40" t="n">
         <v>-5.83</v>
@@ -6702,16 +6690,16 @@
         <v>1701.8</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>7423</v>
+        <v>37115</v>
       </c>
       <c r="I42" t="n">
-        <v>6807</v>
+        <v>34036</v>
       </c>
       <c r="J42" t="n">
-        <v>-616</v>
+        <v>-3079</v>
       </c>
       <c r="K42" t="n">
         <v>-8.300000000000001</v>
@@ -6783,16 +6771,16 @@
         <v>901.16</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H43" t="n">
-        <v>8855</v>
+        <v>45259</v>
       </c>
       <c r="I43" t="n">
-        <v>8110</v>
+        <v>41453</v>
       </c>
       <c r="J43" t="n">
-        <v>-745</v>
+        <v>-3806</v>
       </c>
       <c r="K43" t="n">
         <v>-8.41</v>
@@ -6864,16 +6852,16 @@
         <v>199.6</v>
       </c>
       <c r="G44" t="n">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="H44" t="n">
-        <v>7220</v>
+        <v>36540</v>
       </c>
       <c r="I44" t="n">
-        <v>6587</v>
+        <v>33333</v>
       </c>
       <c r="J44" t="n">
-        <v>-634</v>
+        <v>-3206</v>
       </c>
       <c r="K44" t="n">
         <v>-8.779999999999999</v>
@@ -6945,16 +6933,16 @@
         <v>569.65</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H45" t="n">
-        <v>4554</v>
+        <v>24068</v>
       </c>
       <c r="I45" t="n">
-        <v>3988</v>
+        <v>21077</v>
       </c>
       <c r="J45" t="n">
-        <v>-566</v>
+        <v>-2991</v>
       </c>
       <c r="K45" t="n">
         <v>-12.43</v>
@@ -7026,16 +7014,16 @@
         <v>6726.15</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>15448</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>13452</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-1996</v>
       </c>
       <c r="K46" t="n">
         <v>-12.92</v>
@@ -7107,16 +7095,16 @@
         <v>2350.15</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H47" t="n">
-        <v>6807</v>
+        <v>39141</v>
       </c>
       <c r="I47" t="n">
-        <v>9401</v>
+        <v>54053</v>
       </c>
       <c r="J47" t="n">
-        <v>2593</v>
+        <v>14912</v>
       </c>
       <c r="K47" t="n">
         <v>38.1</v>
@@ -7188,16 +7176,16 @@
         <v>979.3</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H48" t="n">
-        <v>4944</v>
+        <v>27194</v>
       </c>
       <c r="I48" t="n">
-        <v>5876</v>
+        <v>32317</v>
       </c>
       <c r="J48" t="n">
-        <v>932</v>
+        <v>5123</v>
       </c>
       <c r="K48" t="n">
         <v>18.84</v>
@@ -7269,16 +7257,16 @@
         <v>220.95</v>
       </c>
       <c r="G49" t="n">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="H49" t="n">
-        <v>5190</v>
+        <v>26347</v>
       </c>
       <c r="I49" t="n">
-        <v>5745</v>
+        <v>29165</v>
       </c>
       <c r="J49" t="n">
-        <v>555</v>
+        <v>2818</v>
       </c>
       <c r="K49" t="n">
         <v>10.7</v>
@@ -7431,16 +7419,16 @@
         <v>919.4400000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H51" t="n">
-        <v>9913</v>
+        <v>49564</v>
       </c>
       <c r="I51" t="n">
-        <v>10114</v>
+        <v>50569</v>
       </c>
       <c r="J51" t="n">
-        <v>201</v>
+        <v>1005</v>
       </c>
       <c r="K51" t="n">
         <v>2.03</v>
@@ -7512,16 +7500,16 @@
         <v>878</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H52" t="n">
-        <v>5196</v>
+        <v>28577</v>
       </c>
       <c r="I52" t="n">
-        <v>5268</v>
+        <v>28974</v>
       </c>
       <c r="J52" t="n">
-        <v>72</v>
+        <v>397</v>
       </c>
       <c r="K52" t="n">
         <v>1.39</v>
@@ -7593,16 +7581,16 @@
         <v>3773.05</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>3810</v>
+        <v>22858</v>
       </c>
       <c r="I53" t="n">
-        <v>3773</v>
+        <v>22638</v>
       </c>
       <c r="J53" t="n">
-        <v>-37</v>
+        <v>-220</v>
       </c>
       <c r="K53" t="n">
         <v>-0.96</v>
@@ -7674,16 +7662,16 @@
         <v>1569.15</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H54" t="n">
-        <v>7934</v>
+        <v>39668</v>
       </c>
       <c r="I54" t="n">
-        <v>7846</v>
+        <v>39229</v>
       </c>
       <c r="J54" t="n">
-        <v>-88</v>
+        <v>-439</v>
       </c>
       <c r="K54" t="n">
         <v>-1.11</v>
@@ -7755,16 +7743,16 @@
         <v>1232.25</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H55" t="n">
-        <v>4056</v>
+        <v>24333</v>
       </c>
       <c r="I55" t="n">
-        <v>3697</v>
+        <v>22180</v>
       </c>
       <c r="J55" t="n">
-        <v>-359</v>
+        <v>-2153</v>
       </c>
       <c r="K55" t="n">
         <v>-8.85</v>
@@ -7836,16 +7824,16 @@
         <v>693.95</v>
       </c>
       <c r="G56" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H56" t="n">
-        <v>7666</v>
+        <v>39863</v>
       </c>
       <c r="I56" t="n">
-        <v>6940</v>
+        <v>36085</v>
       </c>
       <c r="J56" t="n">
-        <v>-726</v>
+        <v>-3778</v>
       </c>
       <c r="K56" t="n">
         <v>-9.48</v>
@@ -7917,16 +7905,16 @@
         <v>837.7</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H57" t="n">
-        <v>5575</v>
+        <v>27873</v>
       </c>
       <c r="I57" t="n">
-        <v>5026</v>
+        <v>25131</v>
       </c>
       <c r="J57" t="n">
-        <v>-548</v>
+        <v>-2742</v>
       </c>
       <c r="K57" t="n">
         <v>-9.84</v>
@@ -7998,16 +7986,16 @@
         <v>19.95</v>
       </c>
       <c r="G58" t="n">
-        <v>358</v>
+        <v>1790</v>
       </c>
       <c r="H58" t="n">
-        <v>7930</v>
+        <v>39648</v>
       </c>
       <c r="I58" t="n">
-        <v>7142</v>
+        <v>35710</v>
       </c>
       <c r="J58" t="n">
-        <v>-788</v>
+        <v>-3938</v>
       </c>
       <c r="K58" t="n">
         <v>-9.93</v>
@@ -8079,16 +8067,16 @@
         <v>3260.75</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>7630</v>
+        <v>38148</v>
       </c>
       <c r="I59" t="n">
-        <v>6522</v>
+        <v>32608</v>
       </c>
       <c r="J59" t="n">
-        <v>-1108</v>
+        <v>-5540</v>
       </c>
       <c r="K59" t="n">
         <v>-14.52</v>
@@ -8158,16 +8146,16 @@
         <v>1556.15</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H60" t="n">
-        <v>3672</v>
+        <v>23869</v>
       </c>
       <c r="I60" t="n">
-        <v>3112</v>
+        <v>20230</v>
       </c>
       <c r="J60" t="n">
-        <v>-560</v>
+        <v>-3639</v>
       </c>
       <c r="K60" t="n">
         <v>-15.24</v>
@@ -8239,16 +8227,16 @@
         <v>1491.65</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H61" t="n">
-        <v>5583</v>
+        <v>31639</v>
       </c>
       <c r="I61" t="n">
-        <v>4475</v>
+        <v>25358</v>
       </c>
       <c r="J61" t="n">
-        <v>-1108</v>
+        <v>-6281</v>
       </c>
       <c r="K61" t="n">
         <v>-19.85</v>
@@ -8318,16 +8306,16 @@
         <v>32.7</v>
       </c>
       <c r="G62" t="n">
-        <v>163</v>
+        <v>819</v>
       </c>
       <c r="H62" t="n">
-        <v>4417</v>
+        <v>22195</v>
       </c>
       <c r="I62" t="n">
-        <v>5330</v>
+        <v>26781</v>
       </c>
       <c r="J62" t="n">
-        <v>913</v>
+        <v>4586</v>
       </c>
       <c r="K62" t="n">
         <v>20.66</v>
@@ -8399,16 +8387,16 @@
         <v>793.1</v>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H63" t="n">
-        <v>4858</v>
+        <v>24982</v>
       </c>
       <c r="I63" t="n">
-        <v>5552</v>
+        <v>28552</v>
       </c>
       <c r="J63" t="n">
-        <v>694</v>
+        <v>3569</v>
       </c>
       <c r="K63" t="n">
         <v>14.29</v>
@@ -8480,16 +8468,16 @@
         <v>955.15</v>
       </c>
       <c r="G64" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H64" t="n">
-        <v>6702</v>
+        <v>35183</v>
       </c>
       <c r="I64" t="n">
-        <v>7641</v>
+        <v>40116</v>
       </c>
       <c r="J64" t="n">
-        <v>940</v>
+        <v>4933</v>
       </c>
       <c r="K64" t="n">
         <v>14.02</v>
@@ -8561,16 +8549,16 @@
         <v>2014.85</v>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H65" t="n">
-        <v>8860</v>
+        <v>44299</v>
       </c>
       <c r="I65" t="n">
-        <v>10074</v>
+        <v>50371</v>
       </c>
       <c r="J65" t="n">
-        <v>1214</v>
+        <v>6072</v>
       </c>
       <c r="K65" t="n">
         <v>13.71</v>
@@ -8723,16 +8711,16 @@
         <v>1238.75</v>
       </c>
       <c r="G67" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H67" t="n">
-        <v>5519</v>
+        <v>29804</v>
       </c>
       <c r="I67" t="n">
-        <v>6194</v>
+        <v>33446</v>
       </c>
       <c r="J67" t="n">
-        <v>674</v>
+        <v>3642</v>
       </c>
       <c r="K67" t="n">
         <v>12.22</v>
@@ -8804,16 +8792,16 @@
         <v>157.2</v>
       </c>
       <c r="G68" t="n">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="H68" t="n">
-        <v>3120</v>
+        <v>16023</v>
       </c>
       <c r="I68" t="n">
-        <v>3458</v>
+        <v>17764</v>
       </c>
       <c r="J68" t="n">
-        <v>339</v>
+        <v>1740</v>
       </c>
       <c r="K68" t="n">
         <v>10.86</v>
@@ -8885,16 +8873,16 @@
         <v>21.35</v>
       </c>
       <c r="G69" t="n">
-        <v>361</v>
+        <v>1809</v>
       </c>
       <c r="H69" t="n">
-        <v>7202</v>
+        <v>36090</v>
       </c>
       <c r="I69" t="n">
-        <v>7707</v>
+        <v>38622</v>
       </c>
       <c r="J69" t="n">
-        <v>505</v>
+        <v>2533</v>
       </c>
       <c r="K69" t="n">
         <v>7.02</v>
@@ -8966,16 +8954,16 @@
         <v>966.05</v>
       </c>
       <c r="G70" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H70" t="n">
-        <v>8275</v>
+        <v>42294</v>
       </c>
       <c r="I70" t="n">
-        <v>8694</v>
+        <v>44438</v>
       </c>
       <c r="J70" t="n">
-        <v>419</v>
+        <v>2144</v>
       </c>
       <c r="K70" t="n">
         <v>5.07</v>
@@ -9047,16 +9035,16 @@
         <v>3200.3</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H71" t="n">
-        <v>9234</v>
+        <v>58483</v>
       </c>
       <c r="I71" t="n">
-        <v>9601</v>
+        <v>60806</v>
       </c>
       <c r="J71" t="n">
-        <v>367</v>
+        <v>2323</v>
       </c>
       <c r="K71" t="n">
         <v>3.97</v>
@@ -9128,16 +9116,16 @@
         <v>1010.7</v>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H72" t="n">
-        <v>4899</v>
+        <v>26453</v>
       </c>
       <c r="I72" t="n">
-        <v>5054</v>
+        <v>27289</v>
       </c>
       <c r="J72" t="n">
-        <v>155</v>
+        <v>836</v>
       </c>
       <c r="K72" t="n">
         <v>3.16</v>
@@ -9209,16 +9197,16 @@
         <v>1581.2</v>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H73" t="n">
-        <v>7846</v>
+        <v>45505</v>
       </c>
       <c r="I73" t="n">
-        <v>7906</v>
+        <v>45855</v>
       </c>
       <c r="J73" t="n">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="K73" t="n">
         <v>0.77</v>
@@ -9290,16 +9278,16 @@
         <v>157.05</v>
       </c>
       <c r="G74" t="n">
-        <v>49</v>
+        <v>248</v>
       </c>
       <c r="H74" t="n">
-        <v>7734</v>
+        <v>39144</v>
       </c>
       <c r="I74" t="n">
-        <v>7695</v>
+        <v>38948</v>
       </c>
       <c r="J74" t="n">
-        <v>-39</v>
+        <v>-196</v>
       </c>
       <c r="K74" t="n">
         <v>-0.5</v>
@@ -9371,16 +9359,16 @@
         <v>83.95999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="H75" t="n">
-        <v>4093</v>
+        <v>20723</v>
       </c>
       <c r="I75" t="n">
-        <v>4030</v>
+        <v>20402</v>
       </c>
       <c r="J75" t="n">
-        <v>-63</v>
+        <v>-321</v>
       </c>
       <c r="K75" t="n">
         <v>-1.55</v>
@@ -9452,16 +9440,16 @@
         <v>3064.9</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H76" t="n">
-        <v>3261</v>
+        <v>22825</v>
       </c>
       <c r="I76" t="n">
-        <v>3065</v>
+        <v>21454</v>
       </c>
       <c r="J76" t="n">
-        <v>-196</v>
+        <v>-1371</v>
       </c>
       <c r="K76" t="n">
         <v>-6.01</v>
@@ -9533,16 +9521,16 @@
         <v>72.45</v>
       </c>
       <c r="G77" t="n">
-        <v>142</v>
+        <v>712</v>
       </c>
       <c r="H77" t="n">
-        <v>5112</v>
+        <v>25632</v>
       </c>
       <c r="I77" t="n">
-        <v>10288</v>
+        <v>51584</v>
       </c>
       <c r="J77" t="n">
-        <v>5176</v>
+        <v>25952</v>
       </c>
       <c r="K77" t="n">
         <v>101.25</v>
@@ -9614,16 +9602,16 @@
         <v>32.7</v>
       </c>
       <c r="G78" t="n">
-        <v>570</v>
+        <v>2850</v>
       </c>
       <c r="H78" t="n">
-        <v>12170</v>
+        <v>60848</v>
       </c>
       <c r="I78" t="n">
-        <v>18639</v>
+        <v>93195</v>
       </c>
       <c r="J78" t="n">
-        <v>6470</v>
+        <v>32348</v>
       </c>
       <c r="K78" t="n">
         <v>53.16</v>
@@ -9695,16 +9683,16 @@
         <v>125.72</v>
       </c>
       <c r="G79" t="n">
-        <v>75</v>
+        <v>378</v>
       </c>
       <c r="H79" t="n">
-        <v>6297</v>
+        <v>31737</v>
       </c>
       <c r="I79" t="n">
-        <v>9429</v>
+        <v>47522</v>
       </c>
       <c r="J79" t="n">
-        <v>3132</v>
+        <v>15785</v>
       </c>
       <c r="K79" t="n">
         <v>49.74</v>
@@ -9776,16 +9764,16 @@
         <v>80.05</v>
       </c>
       <c r="G80" t="n">
-        <v>85</v>
+        <v>429</v>
       </c>
       <c r="H80" t="n">
-        <v>5733</v>
+        <v>28936</v>
       </c>
       <c r="I80" t="n">
-        <v>6804</v>
+        <v>34341</v>
       </c>
       <c r="J80" t="n">
-        <v>1071</v>
+        <v>5405</v>
       </c>
       <c r="K80" t="n">
         <v>18.68</v>
@@ -9857,16 +9845,16 @@
         <v>1032.8</v>
       </c>
       <c r="G81" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H81" t="n">
-        <v>4788</v>
+        <v>23942</v>
       </c>
       <c r="I81" t="n">
-        <v>5164</v>
+        <v>25820</v>
       </c>
       <c r="J81" t="n">
-        <v>376</v>
+        <v>1878</v>
       </c>
       <c r="K81" t="n">
         <v>7.84</v>
@@ -9938,16 +9926,16 @@
         <v>34.45</v>
       </c>
       <c r="G82" t="n">
-        <v>226</v>
+        <v>1134</v>
       </c>
       <c r="H82" t="n">
-        <v>7390</v>
+        <v>37082</v>
       </c>
       <c r="I82" t="n">
-        <v>7786</v>
+        <v>39066</v>
       </c>
       <c r="J82" t="n">
-        <v>396</v>
+        <v>1984</v>
       </c>
       <c r="K82" t="n">
         <v>5.35</v>
@@ -10019,16 +10007,16 @@
         <v>994.27</v>
       </c>
       <c r="G83" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H83" t="n">
-        <v>6762</v>
+        <v>35744</v>
       </c>
       <c r="I83" t="n">
-        <v>6960</v>
+        <v>36788</v>
       </c>
       <c r="J83" t="n">
-        <v>198</v>
+        <v>1044</v>
       </c>
       <c r="K83" t="n">
         <v>2.92</v>
@@ -10100,16 +10088,16 @@
         <v>3642.25</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H84" t="n">
-        <v>3604</v>
+        <v>28828</v>
       </c>
       <c r="I84" t="n">
-        <v>3642</v>
+        <v>29138</v>
       </c>
       <c r="J84" t="n">
-        <v>39</v>
+        <v>310</v>
       </c>
       <c r="K84" t="n">
         <v>1.07</v>
@@ -10181,16 +10169,16 @@
         <v>796</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H85" t="n">
-        <v>4759</v>
+        <v>26172</v>
       </c>
       <c r="I85" t="n">
-        <v>4776</v>
+        <v>26268</v>
       </c>
       <c r="J85" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="K85" t="n">
         <v>0.37</v>
@@ -10262,16 +10250,16 @@
         <v>293.56</v>
       </c>
       <c r="G86" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="H86" t="n">
-        <v>7611</v>
+        <v>38055</v>
       </c>
       <c r="I86" t="n">
-        <v>7633</v>
+        <v>38163</v>
       </c>
       <c r="J86" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="K86" t="n">
         <v>0.28</v>
@@ -10343,16 +10331,16 @@
         <v>854.35</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H87" t="n">
-        <v>5252</v>
+        <v>28011</v>
       </c>
       <c r="I87" t="n">
-        <v>5126</v>
+        <v>27339</v>
       </c>
       <c r="J87" t="n">
-        <v>-126</v>
+        <v>-671</v>
       </c>
       <c r="K87" t="n">
         <v>-2.4</v>
@@ -10424,16 +10412,16 @@
         <v>1261.15</v>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H88" t="n">
-        <v>5325</v>
+        <v>29289</v>
       </c>
       <c r="I88" t="n">
-        <v>5045</v>
+        <v>27745</v>
       </c>
       <c r="J88" t="n">
-        <v>-281</v>
+        <v>-1543</v>
       </c>
       <c r="K88" t="n">
         <v>-5.27</v>
@@ -10505,16 +10493,16 @@
         <v>3031.35</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H89" t="n">
-        <v>6401</v>
+        <v>44804</v>
       </c>
       <c r="I89" t="n">
-        <v>6063</v>
+        <v>42439</v>
       </c>
       <c r="J89" t="n">
-        <v>-338</v>
+        <v>-2365</v>
       </c>
       <c r="K89" t="n">
         <v>-5.28</v>
@@ -10586,16 +10574,16 @@
         <v>896.4</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H90" t="n">
-        <v>5054</v>
+        <v>29310</v>
       </c>
       <c r="I90" t="n">
-        <v>4482</v>
+        <v>25996</v>
       </c>
       <c r="J90" t="n">
-        <v>-572</v>
+        <v>-3315</v>
       </c>
       <c r="K90" t="n">
         <v>-11.31</v>
@@ -10665,16 +10653,16 @@
         <v>7829.05</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>17801</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>15658</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>-2143</v>
       </c>
       <c r="K91" t="n">
         <v>-12.04</v>
@@ -10744,16 +10732,16 @@
         <v>350.46</v>
       </c>
       <c r="G92" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="H92" t="n">
-        <v>6458</v>
+        <v>32879</v>
       </c>
       <c r="I92" t="n">
-        <v>7710</v>
+        <v>39252</v>
       </c>
       <c r="J92" t="n">
-        <v>1252</v>
+        <v>6373</v>
       </c>
       <c r="K92" t="n">
         <v>19.38</v>
@@ -10825,16 +10813,16 @@
         <v>4286</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H93" t="n">
-        <v>3642</v>
+        <v>32780</v>
       </c>
       <c r="I93" t="n">
-        <v>4286</v>
+        <v>38574</v>
       </c>
       <c r="J93" t="n">
-        <v>644</v>
+        <v>5794</v>
       </c>
       <c r="K93" t="n">
         <v>17.67</v>
@@ -10906,16 +10894,16 @@
         <v>3312.5</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H94" t="n">
-        <v>5993</v>
+        <v>32959</v>
       </c>
       <c r="I94" t="n">
-        <v>6625</v>
+        <v>36438</v>
       </c>
       <c r="J94" t="n">
-        <v>632</v>
+        <v>3478</v>
       </c>
       <c r="K94" t="n">
         <v>10.55</v>
@@ -10987,16 +10975,16 @@
         <v>3340.6</v>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H95" t="n">
-        <v>9094</v>
+        <v>48502</v>
       </c>
       <c r="I95" t="n">
-        <v>10022</v>
+        <v>53450</v>
       </c>
       <c r="J95" t="n">
-        <v>928</v>
+        <v>4948</v>
       </c>
       <c r="K95" t="n">
         <v>10.2</v>
@@ -11068,16 +11056,16 @@
         <v>2288.5</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H96" t="n">
-        <v>2087</v>
+        <v>18779</v>
       </c>
       <c r="I96" t="n">
-        <v>2288</v>
+        <v>20596</v>
       </c>
       <c r="J96" t="n">
-        <v>202</v>
+        <v>1818</v>
       </c>
       <c r="K96" t="n">
         <v>9.68</v>
@@ -11149,16 +11137,16 @@
         <v>231.45</v>
       </c>
       <c r="G97" t="n">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="H97" t="n">
-        <v>6973</v>
+        <v>35518</v>
       </c>
       <c r="I97" t="n">
-        <v>7406</v>
+        <v>37726</v>
       </c>
       <c r="J97" t="n">
-        <v>434</v>
+        <v>2209</v>
       </c>
       <c r="K97" t="n">
         <v>6.22</v>
@@ -11230,16 +11218,16 @@
         <v>842.45</v>
       </c>
       <c r="G98" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H98" t="n">
-        <v>3986</v>
+        <v>19930</v>
       </c>
       <c r="I98" t="n">
-        <v>4212</v>
+        <v>21061</v>
       </c>
       <c r="J98" t="n">
-        <v>226</v>
+        <v>1131</v>
       </c>
       <c r="K98" t="n">
         <v>5.68</v>
@@ -11311,16 +11299,16 @@
         <v>1587.65</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H99" t="n">
-        <v>9279</v>
+        <v>51034</v>
       </c>
       <c r="I99" t="n">
-        <v>9526</v>
+        <v>52392</v>
       </c>
       <c r="J99" t="n">
-        <v>247</v>
+        <v>1358</v>
       </c>
       <c r="K99" t="n">
         <v>2.66</v>
@@ -11392,16 +11380,16 @@
         <v>890.15</v>
       </c>
       <c r="G100" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H100" t="n">
-        <v>4350</v>
+        <v>22623</v>
       </c>
       <c r="I100" t="n">
-        <v>4451</v>
+        <v>23144</v>
       </c>
       <c r="J100" t="n">
-        <v>100</v>
+        <v>521</v>
       </c>
       <c r="K100" t="n">
         <v>2.3</v>
@@ -11473,16 +11461,16 @@
         <v>3241.65</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H101" t="n">
-        <v>3212</v>
+        <v>19269</v>
       </c>
       <c r="I101" t="n">
-        <v>3242</v>
+        <v>19450</v>
       </c>
       <c r="J101" t="n">
-        <v>30</v>
+        <v>181</v>
       </c>
       <c r="K101" t="n">
         <v>0.9399999999999999</v>
@@ -11554,16 +11542,16 @@
         <v>78</v>
       </c>
       <c r="G102" t="n">
-        <v>87</v>
+        <v>435</v>
       </c>
       <c r="H102" t="n">
-        <v>6964</v>
+        <v>34822</v>
       </c>
       <c r="I102" t="n">
-        <v>6786</v>
+        <v>33930</v>
       </c>
       <c r="J102" t="n">
-        <v>-178</v>
+        <v>-892</v>
       </c>
       <c r="K102" t="n">
         <v>-2.56</v>
@@ -11635,16 +11623,16 @@
         <v>771.1</v>
       </c>
       <c r="G103" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H103" t="n">
-        <v>6368</v>
+        <v>34228</v>
       </c>
       <c r="I103" t="n">
-        <v>6169</v>
+        <v>33157</v>
       </c>
       <c r="J103" t="n">
-        <v>-199</v>
+        <v>-1071</v>
       </c>
       <c r="K103" t="n">
         <v>-3.13</v>
@@ -11716,16 +11704,16 @@
         <v>1173.9</v>
       </c>
       <c r="G104" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H104" t="n">
-        <v>6306</v>
+        <v>35312</v>
       </c>
       <c r="I104" t="n">
-        <v>5870</v>
+        <v>32869</v>
       </c>
       <c r="J104" t="n">
-        <v>-436</v>
+        <v>-2443</v>
       </c>
       <c r="K104" t="n">
         <v>-6.92</v>
@@ -11797,16 +11785,16 @@
         <v>813.95</v>
       </c>
       <c r="G105" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="H105" t="n">
-        <v>8068</v>
+        <v>40338</v>
       </c>
       <c r="I105" t="n">
-        <v>7326</v>
+        <v>36628</v>
       </c>
       <c r="J105" t="n">
-        <v>-742</v>
+        <v>-3710</v>
       </c>
       <c r="K105" t="n">
         <v>-9.199999999999999</v>
@@ -11878,16 +11866,16 @@
         <v>1383.75</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H106" t="n">
-        <v>4973</v>
+        <v>31493</v>
       </c>
       <c r="I106" t="n">
-        <v>4151</v>
+        <v>26291</v>
       </c>
       <c r="J106" t="n">
-        <v>-821</v>
+        <v>-5202</v>
       </c>
       <c r="K106" t="n">
         <v>-16.52</v>
@@ -11959,16 +11947,16 @@
         <v>1356</v>
       </c>
       <c r="G107" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H107" t="n">
-        <v>6545</v>
+        <v>33816</v>
       </c>
       <c r="I107" t="n">
-        <v>8136</v>
+        <v>42036</v>
       </c>
       <c r="J107" t="n">
-        <v>1591</v>
+        <v>8220</v>
       </c>
       <c r="K107" t="n">
         <v>24.31</v>
@@ -12040,16 +12028,16 @@
         <v>3400</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H108" t="n">
-        <v>2787</v>
+        <v>25081</v>
       </c>
       <c r="I108" t="n">
-        <v>3400</v>
+        <v>30600</v>
       </c>
       <c r="J108" t="n">
-        <v>613</v>
+        <v>5519</v>
       </c>
       <c r="K108" t="n">
         <v>22.01</v>
@@ -12121,16 +12109,16 @@
         <v>1934.6</v>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H109" t="n">
-        <v>6351</v>
+        <v>33341</v>
       </c>
       <c r="I109" t="n">
-        <v>7738</v>
+        <v>40627</v>
       </c>
       <c r="J109" t="n">
-        <v>1388</v>
+        <v>7286</v>
       </c>
       <c r="K109" t="n">
         <v>21.85</v>
@@ -12202,16 +12190,16 @@
         <v>1659</v>
       </c>
       <c r="G110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H110" t="n">
-        <v>6963</v>
+        <v>34815</v>
       </c>
       <c r="I110" t="n">
-        <v>8295</v>
+        <v>41475</v>
       </c>
       <c r="J110" t="n">
-        <v>1332</v>
+        <v>6660</v>
       </c>
       <c r="K110" t="n">
         <v>19.13</v>
@@ -12283,16 +12271,16 @@
         <v>837</v>
       </c>
       <c r="G111" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H111" t="n">
-        <v>7184</v>
+        <v>37357</v>
       </c>
       <c r="I111" t="n">
-        <v>8370</v>
+        <v>43524</v>
       </c>
       <c r="J111" t="n">
-        <v>1186</v>
+        <v>6167</v>
       </c>
       <c r="K111" t="n">
         <v>16.51</v>
@@ -12364,16 +12352,16 @@
         <v>1809.7</v>
       </c>
       <c r="G112" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H112" t="n">
-        <v>7783</v>
+        <v>42030</v>
       </c>
       <c r="I112" t="n">
-        <v>9048</v>
+        <v>48862</v>
       </c>
       <c r="J112" t="n">
-        <v>1265</v>
+        <v>6832</v>
       </c>
       <c r="K112" t="n">
         <v>16.26</v>
@@ -12445,16 +12433,16 @@
         <v>3842.8</v>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H113" t="n">
-        <v>6625</v>
+        <v>33125</v>
       </c>
       <c r="I113" t="n">
-        <v>7686</v>
+        <v>38428</v>
       </c>
       <c r="J113" t="n">
-        <v>1061</v>
+        <v>5303</v>
       </c>
       <c r="K113" t="n">
         <v>16.01</v>
@@ -12526,16 +12514,16 @@
         <v>884.95</v>
       </c>
       <c r="G114" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H114" t="n">
-        <v>5398</v>
+        <v>26988</v>
       </c>
       <c r="I114" t="n">
-        <v>6195</v>
+        <v>30973</v>
       </c>
       <c r="J114" t="n">
-        <v>797</v>
+        <v>3985</v>
       </c>
       <c r="K114" t="n">
         <v>14.76</v>
@@ -12607,16 +12595,16 @@
         <v>9671</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>25863</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>29013</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>3150</v>
       </c>
       <c r="K115" t="n">
         <v>12.18</v>
@@ -12688,16 +12676,16 @@
         <v>1309.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H116" t="n">
-        <v>7043</v>
+        <v>35217</v>
       </c>
       <c r="I116" t="n">
-        <v>7857</v>
+        <v>39285</v>
       </c>
       <c r="J116" t="n">
-        <v>814</v>
+        <v>4068</v>
       </c>
       <c r="K116" t="n">
         <v>11.55</v>
@@ -12769,16 +12757,16 @@
         <v>188.3</v>
       </c>
       <c r="G117" t="n">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="H117" t="n">
-        <v>5626</v>
+        <v>28831</v>
       </c>
       <c r="I117" t="n">
-        <v>6026</v>
+        <v>30881</v>
       </c>
       <c r="J117" t="n">
-        <v>400</v>
+        <v>2050</v>
       </c>
       <c r="K117" t="n">
         <v>7.11</v>
@@ -12850,16 +12838,16 @@
         <v>197.38</v>
       </c>
       <c r="G118" t="n">
-        <v>31</v>
+        <v>159</v>
       </c>
       <c r="H118" t="n">
-        <v>5768</v>
+        <v>29587</v>
       </c>
       <c r="I118" t="n">
-        <v>6119</v>
+        <v>31383</v>
       </c>
       <c r="J118" t="n">
-        <v>350</v>
+        <v>1797</v>
       </c>
       <c r="K118" t="n">
         <v>6.07</v>
@@ -12931,16 +12919,16 @@
         <v>1075</v>
       </c>
       <c r="G119" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H119" t="n">
-        <v>6100</v>
+        <v>32534</v>
       </c>
       <c r="I119" t="n">
-        <v>6450</v>
+        <v>34400</v>
       </c>
       <c r="J119" t="n">
-        <v>350</v>
+        <v>1866</v>
       </c>
       <c r="K119" t="n">
         <v>5.73</v>
@@ -13012,16 +13000,16 @@
         <v>1752.76</v>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H120" t="n">
-        <v>5132</v>
+        <v>30790</v>
       </c>
       <c r="I120" t="n">
-        <v>5258</v>
+        <v>31550</v>
       </c>
       <c r="J120" t="n">
-        <v>127</v>
+        <v>759</v>
       </c>
       <c r="K120" t="n">
         <v>2.47</v>
@@ -13093,16 +13081,16 @@
         <v>374</v>
       </c>
       <c r="G121" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H121" t="n">
-        <v>7745</v>
+        <v>39094</v>
       </c>
       <c r="I121" t="n">
-        <v>7854</v>
+        <v>39644</v>
       </c>
       <c r="J121" t="n">
-        <v>109</v>
+        <v>550</v>
       </c>
       <c r="K121" t="n">
         <v>1.41</v>
@@ -13174,16 +13162,16 @@
         <v>242.05</v>
       </c>
       <c r="G122" t="n">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="H122" t="n">
-        <v>8474</v>
+        <v>42368</v>
       </c>
       <c r="I122" t="n">
-        <v>10892</v>
+        <v>54461</v>
       </c>
       <c r="J122" t="n">
-        <v>2419</v>
+        <v>12094</v>
       </c>
       <c r="K122" t="n">
         <v>28.54</v>
@@ -13255,16 +13243,16 @@
         <v>3186.25</v>
       </c>
       <c r="G123" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H123" t="n">
-        <v>10204</v>
+        <v>51020</v>
       </c>
       <c r="I123" t="n">
-        <v>12745</v>
+        <v>63725</v>
       </c>
       <c r="J123" t="n">
-        <v>2541</v>
+        <v>12705</v>
       </c>
       <c r="K123" t="n">
         <v>24.9</v>
@@ -13336,16 +13324,16 @@
         <v>2041.65</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H124" t="n">
-        <v>5429</v>
+        <v>32575</v>
       </c>
       <c r="I124" t="n">
-        <v>6125</v>
+        <v>36750</v>
       </c>
       <c r="J124" t="n">
-        <v>696</v>
+        <v>4175</v>
       </c>
       <c r="K124" t="n">
         <v>12.82</v>
@@ -13417,16 +13405,16 @@
         <v>1974.67</v>
       </c>
       <c r="G125" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H125" t="n">
-        <v>7011</v>
+        <v>35055</v>
       </c>
       <c r="I125" t="n">
-        <v>7899</v>
+        <v>39493</v>
       </c>
       <c r="J125" t="n">
-        <v>888</v>
+        <v>4438</v>
       </c>
       <c r="K125" t="n">
         <v>12.66</v>
@@ -13498,16 +13486,16 @@
         <v>10727.55</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>19342</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>21455</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="K126" t="n">
         <v>10.92</v>
@@ -13579,16 +13567,16 @@
         <v>954.2</v>
       </c>
       <c r="G127" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H127" t="n">
-        <v>8850</v>
+        <v>44248</v>
       </c>
       <c r="I127" t="n">
-        <v>9542</v>
+        <v>47710</v>
       </c>
       <c r="J127" t="n">
-        <v>692</v>
+        <v>3462</v>
       </c>
       <c r="K127" t="n">
         <v>7.83</v>
@@ -13741,16 +13729,16 @@
         <v>3570.85</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H129" t="n">
-        <v>3344</v>
+        <v>26754</v>
       </c>
       <c r="I129" t="n">
-        <v>3571</v>
+        <v>28567</v>
       </c>
       <c r="J129" t="n">
-        <v>227</v>
+        <v>1813</v>
       </c>
       <c r="K129" t="n">
         <v>6.78</v>
@@ -13822,16 +13810,16 @@
         <v>1145.3</v>
       </c>
       <c r="G130" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H130" t="n">
-        <v>7525</v>
+        <v>38700</v>
       </c>
       <c r="I130" t="n">
-        <v>8017</v>
+        <v>41231</v>
       </c>
       <c r="J130" t="n">
-        <v>492</v>
+        <v>2531</v>
       </c>
       <c r="K130" t="n">
         <v>6.54</v>
@@ -13903,16 +13891,16 @@
         <v>205.53</v>
       </c>
       <c r="G131" t="n">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="H131" t="n">
-        <v>6908</v>
+        <v>34739</v>
       </c>
       <c r="I131" t="n">
-        <v>7194</v>
+        <v>36173</v>
       </c>
       <c r="J131" t="n">
-        <v>285</v>
+        <v>1434</v>
       </c>
       <c r="K131" t="n">
         <v>4.13</v>
@@ -13984,16 +13972,16 @@
         <v>1177.72</v>
       </c>
       <c r="G132" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H132" t="n">
-        <v>4564</v>
+        <v>23962</v>
       </c>
       <c r="I132" t="n">
-        <v>4711</v>
+        <v>24732</v>
       </c>
       <c r="J132" t="n">
-        <v>147</v>
+        <v>770</v>
       </c>
       <c r="K132" t="n">
         <v>3.21</v>
@@ -14065,16 +14053,16 @@
         <v>951.3</v>
       </c>
       <c r="G133" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H133" t="n">
-        <v>6696</v>
+        <v>37304</v>
       </c>
       <c r="I133" t="n">
-        <v>6659</v>
+        <v>37101</v>
       </c>
       <c r="J133" t="n">
-        <v>-36</v>
+        <v>-203</v>
       </c>
       <c r="K133" t="n">
         <v>-0.54</v>
@@ -14146,16 +14134,16 @@
         <v>1624.85</v>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H134" t="n">
-        <v>4977</v>
+        <v>26544</v>
       </c>
       <c r="I134" t="n">
-        <v>4875</v>
+        <v>25998</v>
       </c>
       <c r="J134" t="n">
-        <v>-102</v>
+        <v>-546</v>
       </c>
       <c r="K134" t="n">
         <v>-2.06</v>
@@ -14227,16 +14215,16 @@
         <v>1230.03</v>
       </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H135" t="n">
-        <v>3928</v>
+        <v>23571</v>
       </c>
       <c r="I135" t="n">
-        <v>3690</v>
+        <v>22141</v>
       </c>
       <c r="J135" t="n">
-        <v>-238</v>
+        <v>-1430</v>
       </c>
       <c r="K135" t="n">
         <v>-6.07</v>
@@ -14308,16 +14296,16 @@
         <v>3148.8</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H136" t="n">
-        <v>3400</v>
+        <v>20400</v>
       </c>
       <c r="I136" t="n">
-        <v>3149</v>
+        <v>18893</v>
       </c>
       <c r="J136" t="n">
-        <v>-251</v>
+        <v>-1507</v>
       </c>
       <c r="K136" t="n">
         <v>-7.39</v>
@@ -14389,16 +14377,16 @@
         <v>427.4</v>
       </c>
       <c r="G137" t="n">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="H137" t="n">
-        <v>7933</v>
+        <v>40936</v>
       </c>
       <c r="I137" t="n">
-        <v>10685</v>
+        <v>55135</v>
       </c>
       <c r="J137" t="n">
-        <v>2752</v>
+        <v>14199</v>
       </c>
       <c r="K137" t="n">
         <v>34.69</v>
@@ -14551,16 +14539,16 @@
         <v>9954.549999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>33476</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>39818</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>6342</v>
       </c>
       <c r="K139" t="n">
         <v>18.95</v>
@@ -14632,16 +14620,16 @@
         <v>1394.13</v>
       </c>
       <c r="G140" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H140" t="n">
-        <v>5873</v>
+        <v>29366</v>
       </c>
       <c r="I140" t="n">
-        <v>6971</v>
+        <v>34853</v>
       </c>
       <c r="J140" t="n">
-        <v>1097</v>
+        <v>5487</v>
       </c>
       <c r="K140" t="n">
         <v>18.68</v>
@@ -14713,16 +14701,16 @@
         <v>26210.45</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>22307</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>26210</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>3903</v>
       </c>
       <c r="K141" t="n">
         <v>17.5</v>
@@ -14794,16 +14782,16 @@
         <v>1329.35</v>
       </c>
       <c r="G142" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H142" t="n">
-        <v>6872</v>
+        <v>35504</v>
       </c>
       <c r="I142" t="n">
-        <v>7976</v>
+        <v>41210</v>
       </c>
       <c r="J142" t="n">
-        <v>1104</v>
+        <v>5706</v>
       </c>
       <c r="K142" t="n">
         <v>16.07</v>
@@ -14875,16 +14863,16 @@
         <v>1102.4</v>
       </c>
       <c r="G143" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H143" t="n">
-        <v>6679</v>
+        <v>36260</v>
       </c>
       <c r="I143" t="n">
-        <v>7717</v>
+        <v>41891</v>
       </c>
       <c r="J143" t="n">
-        <v>1037</v>
+        <v>5632</v>
       </c>
       <c r="K143" t="n">
         <v>15.53</v>
@@ -14956,16 +14944,16 @@
         <v>3758.85</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H144" t="n">
-        <v>6568</v>
+        <v>32838</v>
       </c>
       <c r="I144" t="n">
-        <v>7518</v>
+        <v>37588</v>
       </c>
       <c r="J144" t="n">
-        <v>950</v>
+        <v>4751</v>
       </c>
       <c r="K144" t="n">
         <v>14.47</v>
@@ -15037,16 +15025,16 @@
         <v>1377.13</v>
       </c>
       <c r="G145" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H145" t="n">
-        <v>4920</v>
+        <v>25831</v>
       </c>
       <c r="I145" t="n">
-        <v>5509</v>
+        <v>28920</v>
       </c>
       <c r="J145" t="n">
-        <v>588</v>
+        <v>3089</v>
       </c>
       <c r="K145" t="n">
         <v>11.96</v>
@@ -15118,16 +15106,16 @@
         <v>3903.8</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H146" t="n">
-        <v>3571</v>
+        <v>28567</v>
       </c>
       <c r="I146" t="n">
-        <v>3904</v>
+        <v>31230</v>
       </c>
       <c r="J146" t="n">
-        <v>333</v>
+        <v>2664</v>
       </c>
       <c r="K146" t="n">
         <v>9.32</v>
@@ -15199,16 +15187,16 @@
         <v>1273.78</v>
       </c>
       <c r="G147" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H147" t="n">
-        <v>5889</v>
+        <v>29443</v>
       </c>
       <c r="I147" t="n">
-        <v>6369</v>
+        <v>31844</v>
       </c>
       <c r="J147" t="n">
-        <v>480</v>
+        <v>2402</v>
       </c>
       <c r="K147" t="n">
         <v>8.16</v>
@@ -15280,16 +15268,16 @@
         <v>1009.85</v>
       </c>
       <c r="G148" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H148" t="n">
-        <v>7610</v>
+        <v>39955</v>
       </c>
       <c r="I148" t="n">
-        <v>8079</v>
+        <v>42414</v>
       </c>
       <c r="J148" t="n">
-        <v>468</v>
+        <v>2459</v>
       </c>
       <c r="K148" t="n">
         <v>6.15</v>
@@ -15361,16 +15349,16 @@
         <v>3273.9</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H149" t="n">
-        <v>3149</v>
+        <v>25190</v>
       </c>
       <c r="I149" t="n">
-        <v>3274</v>
+        <v>26191</v>
       </c>
       <c r="J149" t="n">
-        <v>125</v>
+        <v>1001</v>
       </c>
       <c r="K149" t="n">
         <v>3.97</v>
@@ -15442,16 +15430,16 @@
         <v>2573.2</v>
       </c>
       <c r="G150" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H150" t="n">
-        <v>5139</v>
+        <v>28264</v>
       </c>
       <c r="I150" t="n">
-        <v>5146</v>
+        <v>28305</v>
       </c>
       <c r="J150" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K150" t="n">
         <v>0.15</v>
@@ -15523,16 +15511,16 @@
         <v>10086.9</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>21455</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>20174</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>-1281</v>
       </c>
       <c r="K151" t="n">
         <v>-5.97</v>
@@ -15604,16 +15592,16 @@
         <v>404.95</v>
       </c>
       <c r="G152" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="H152" t="n">
-        <v>4504</v>
+        <v>23810</v>
       </c>
       <c r="I152" t="n">
-        <v>5669</v>
+        <v>29966</v>
       </c>
       <c r="J152" t="n">
-        <v>1165</v>
+        <v>6157</v>
       </c>
       <c r="K152" t="n">
         <v>25.86</v>
@@ -15685,16 +15673,16 @@
         <v>12405</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>40348</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>49620</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>9272</v>
       </c>
       <c r="K153" t="n">
         <v>22.98</v>
@@ -15766,16 +15754,16 @@
         <v>1265.75</v>
       </c>
       <c r="G154" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H154" t="n">
-        <v>4410</v>
+        <v>26458</v>
       </c>
       <c r="I154" t="n">
-        <v>5063</v>
+        <v>30378</v>
       </c>
       <c r="J154" t="n">
-        <v>653</v>
+        <v>3920</v>
       </c>
       <c r="K154" t="n">
         <v>14.82</v>
@@ -15847,16 +15835,16 @@
         <v>1516.4</v>
       </c>
       <c r="G155" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H155" t="n">
-        <v>5317</v>
+        <v>29246</v>
       </c>
       <c r="I155" t="n">
-        <v>6066</v>
+        <v>33361</v>
       </c>
       <c r="J155" t="n">
-        <v>748</v>
+        <v>4115</v>
       </c>
       <c r="K155" t="n">
         <v>14.07</v>
@@ -15928,16 +15916,16 @@
         <v>2226.05</v>
       </c>
       <c r="G156" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H156" t="n">
-        <v>4202</v>
+        <v>23111</v>
       </c>
       <c r="I156" t="n">
-        <v>4452</v>
+        <v>24487</v>
       </c>
       <c r="J156" t="n">
-        <v>250</v>
+        <v>1376</v>
       </c>
       <c r="K156" t="n">
         <v>5.95</v>
@@ -16009,16 +15997,16 @@
         <v>1464.33</v>
       </c>
       <c r="G157" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H157" t="n">
-        <v>5577</v>
+        <v>27883</v>
       </c>
       <c r="I157" t="n">
-        <v>5857</v>
+        <v>29287</v>
       </c>
       <c r="J157" t="n">
-        <v>281</v>
+        <v>1404</v>
       </c>
       <c r="K157" t="n">
         <v>5.04</v>
@@ -16090,16 +16078,16 @@
         <v>1055.45</v>
       </c>
       <c r="G158" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H158" t="n">
-        <v>5049</v>
+        <v>28276</v>
       </c>
       <c r="I158" t="n">
-        <v>5277</v>
+        <v>29553</v>
       </c>
       <c r="J158" t="n">
-        <v>228</v>
+        <v>1277</v>
       </c>
       <c r="K158" t="n">
         <v>4.52</v>
@@ -16171,16 +16159,16 @@
         <v>3862</v>
       </c>
       <c r="G159" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H159" t="n">
-        <v>3904</v>
+        <v>31230</v>
       </c>
       <c r="I159" t="n">
-        <v>3862</v>
+        <v>30896</v>
       </c>
       <c r="J159" t="n">
-        <v>-42</v>
+        <v>-334</v>
       </c>
       <c r="K159" t="n">
         <v>-1.07</v>
@@ -16252,16 +16240,16 @@
         <v>1638.25</v>
       </c>
       <c r="G160" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H160" t="n">
-        <v>8610</v>
+        <v>46497</v>
       </c>
       <c r="I160" t="n">
-        <v>8191</v>
+        <v>44233</v>
       </c>
       <c r="J160" t="n">
-        <v>-419</v>
+        <v>-2264</v>
       </c>
       <c r="K160" t="n">
         <v>-4.87</v>
@@ -16408,16 +16396,16 @@
         <v>3525.1</v>
       </c>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H162" t="n">
-        <v>7518</v>
+        <v>37588</v>
       </c>
       <c r="I162" t="n">
-        <v>7050</v>
+        <v>35251</v>
       </c>
       <c r="J162" t="n">
-        <v>-468</v>
+        <v>-2338</v>
       </c>
       <c r="K162" t="n">
         <v>-6.22</v>
@@ -16489,16 +16477,16 @@
         <v>4695</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H163" t="n">
-        <v>5177</v>
+        <v>31064</v>
       </c>
       <c r="I163" t="n">
-        <v>4695</v>
+        <v>28170</v>
       </c>
       <c r="J163" t="n">
-        <v>-482</v>
+        <v>-2894</v>
       </c>
       <c r="K163" t="n">
         <v>-9.32</v>
@@ -16570,16 +16558,16 @@
         <v>747.35</v>
       </c>
       <c r="G164" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H164" t="n">
-        <v>5018</v>
+        <v>28438</v>
       </c>
       <c r="I164" t="n">
-        <v>4484</v>
+        <v>25410</v>
       </c>
       <c r="J164" t="n">
-        <v>-534</v>
+        <v>-3028</v>
       </c>
       <c r="K164" t="n">
         <v>-10.65</v>
@@ -16651,16 +16639,16 @@
         <v>2214.8</v>
       </c>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H165" t="n">
-        <v>7720</v>
+        <v>41171</v>
       </c>
       <c r="I165" t="n">
-        <v>6644</v>
+        <v>35437</v>
       </c>
       <c r="J165" t="n">
-        <v>-1075</v>
+        <v>-5734</v>
       </c>
       <c r="K165" t="n">
         <v>-13.93</v>
@@ -16730,16 +16718,16 @@
         <v>2807.7</v>
       </c>
       <c r="G166" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H166" t="n">
-        <v>6548</v>
+        <v>32739</v>
       </c>
       <c r="I166" t="n">
-        <v>5615</v>
+        <v>28077</v>
       </c>
       <c r="J166" t="n">
-        <v>-932</v>
+        <v>-4662</v>
       </c>
       <c r="K166" t="n">
         <v>-14.24</v>
@@ -16811,16 +16799,16 @@
         <v>2743</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H167" t="n">
-        <v>2226</v>
+        <v>20034</v>
       </c>
       <c r="I167" t="n">
-        <v>2743</v>
+        <v>24687</v>
       </c>
       <c r="J167" t="n">
-        <v>517</v>
+        <v>4653</v>
       </c>
       <c r="K167" t="n">
         <v>23.22</v>
@@ -16892,16 +16880,16 @@
         <v>2727</v>
       </c>
       <c r="G168" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H168" t="n">
-        <v>6644</v>
+        <v>35437</v>
       </c>
       <c r="I168" t="n">
-        <v>8181</v>
+        <v>43632</v>
       </c>
       <c r="J168" t="n">
-        <v>1537</v>
+        <v>8195</v>
       </c>
       <c r="K168" t="n">
         <v>23.13</v>
@@ -16973,16 +16961,16 @@
         <v>11258.3</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>18766</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>22517</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>3751</v>
       </c>
       <c r="K169" t="n">
         <v>19.99</v>
@@ -17054,16 +17042,16 @@
         <v>1248.65</v>
       </c>
       <c r="G170" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H170" t="n">
-        <v>4222</v>
+        <v>24275</v>
       </c>
       <c r="I170" t="n">
-        <v>4995</v>
+        <v>28719</v>
       </c>
       <c r="J170" t="n">
-        <v>773</v>
+        <v>4444</v>
       </c>
       <c r="K170" t="n">
         <v>18.3</v>
@@ -17135,16 +17123,16 @@
         <v>1926.85</v>
       </c>
       <c r="G171" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H171" t="n">
-        <v>8191</v>
+        <v>44233</v>
       </c>
       <c r="I171" t="n">
-        <v>9634</v>
+        <v>52025</v>
       </c>
       <c r="J171" t="n">
-        <v>1443</v>
+        <v>7792</v>
       </c>
       <c r="K171" t="n">
         <v>17.62</v>
@@ -17210,16 +17198,16 @@
         <v>1461.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H172" t="n">
-        <v>6329</v>
+        <v>36707</v>
       </c>
       <c r="I172" t="n">
-        <v>7309</v>
+        <v>42391</v>
       </c>
       <c r="J172" t="n">
-        <v>980</v>
+        <v>5684</v>
       </c>
       <c r="K172" t="n">
         <v>15.48</v>
@@ -17291,16 +17279,16 @@
         <v>446.08</v>
       </c>
       <c r="G173" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="H173" t="n">
-        <v>9283</v>
+        <v>46415</v>
       </c>
       <c r="I173" t="n">
-        <v>10706</v>
+        <v>53530</v>
       </c>
       <c r="J173" t="n">
-        <v>1423</v>
+        <v>7115</v>
       </c>
       <c r="K173" t="n">
         <v>15.33</v>
@@ -17372,16 +17360,16 @@
         <v>1523.8</v>
       </c>
       <c r="G174" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H174" t="n">
-        <v>5374</v>
+        <v>26871</v>
       </c>
       <c r="I174" t="n">
-        <v>6095</v>
+        <v>30476</v>
       </c>
       <c r="J174" t="n">
-        <v>721</v>
+        <v>3605</v>
       </c>
       <c r="K174" t="n">
         <v>13.42</v>
@@ -17453,16 +17441,16 @@
         <v>1327.2</v>
       </c>
       <c r="G175" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H175" t="n">
-        <v>7149</v>
+        <v>38126</v>
       </c>
       <c r="I175" t="n">
-        <v>7963</v>
+        <v>42470</v>
       </c>
       <c r="J175" t="n">
-        <v>815</v>
+        <v>4345</v>
       </c>
       <c r="K175" t="n">
         <v>11.4</v>
@@ -17534,16 +17522,16 @@
         <v>4302.4</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H176" t="n">
-        <v>3862</v>
+        <v>34758</v>
       </c>
       <c r="I176" t="n">
-        <v>4302</v>
+        <v>38722</v>
       </c>
       <c r="J176" t="n">
-        <v>440</v>
+        <v>3964</v>
       </c>
       <c r="K176" t="n">
         <v>11.4</v>
@@ -17615,16 +17603,16 @@
         <v>1555.15</v>
       </c>
       <c r="G177" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H177" t="n">
-        <v>4393</v>
+        <v>23429</v>
       </c>
       <c r="I177" t="n">
-        <v>4665</v>
+        <v>24882</v>
       </c>
       <c r="J177" t="n">
-        <v>272</v>
+        <v>1453</v>
       </c>
       <c r="K177" t="n">
         <v>6.2</v>
@@ -17696,16 +17684,16 @@
         <v>2946.05</v>
       </c>
       <c r="G178" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H178" t="n">
-        <v>5615</v>
+        <v>30885</v>
       </c>
       <c r="I178" t="n">
-        <v>5892</v>
+        <v>32407</v>
       </c>
       <c r="J178" t="n">
-        <v>277</v>
+        <v>1522</v>
       </c>
       <c r="K178" t="n">
         <v>4.93</v>
@@ -17777,16 +17765,16 @@
         <v>1568.65</v>
       </c>
       <c r="G179" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H179" t="n">
-        <v>7582</v>
+        <v>40943</v>
       </c>
       <c r="I179" t="n">
-        <v>7843</v>
+        <v>42354</v>
       </c>
       <c r="J179" t="n">
-        <v>261</v>
+        <v>1411</v>
       </c>
       <c r="K179" t="n">
         <v>3.45</v>
@@ -17858,16 +17846,16 @@
         <v>364.32</v>
       </c>
       <c r="G180" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H180" t="n">
-        <v>5003</v>
+        <v>25014</v>
       </c>
       <c r="I180" t="n">
-        <v>5100</v>
+        <v>25502</v>
       </c>
       <c r="J180" t="n">
-        <v>98</v>
+        <v>488</v>
       </c>
       <c r="K180" t="n">
         <v>1.95</v>
@@ -17939,16 +17927,16 @@
         <v>12524.3</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>37215</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>37573</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="K181" t="n">
         <v>0.96</v>
@@ -18020,16 +18008,16 @@
         <v>1910.35</v>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H182" t="n">
-        <v>4706</v>
+        <v>26667</v>
       </c>
       <c r="I182" t="n">
-        <v>5731</v>
+        <v>32476</v>
       </c>
       <c r="J182" t="n">
-        <v>1025</v>
+        <v>5809</v>
       </c>
       <c r="K182" t="n">
         <v>21.78</v>
@@ -18101,16 +18089,16 @@
         <v>4560.7</v>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H183" t="n">
-        <v>7671</v>
+        <v>42188</v>
       </c>
       <c r="I183" t="n">
-        <v>9121</v>
+        <v>50168</v>
       </c>
       <c r="J183" t="n">
-        <v>1451</v>
+        <v>7979</v>
       </c>
       <c r="K183" t="n">
         <v>18.91</v>
@@ -18182,16 +18170,16 @@
         <v>6982.9</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>19146</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>20949</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>1803</v>
       </c>
       <c r="K184" t="n">
         <v>9.42</v>
@@ -18263,16 +18251,16 @@
         <v>1879.6</v>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H185" t="n">
-        <v>5379</v>
+        <v>34066</v>
       </c>
       <c r="I185" t="n">
-        <v>5639</v>
+        <v>35712</v>
       </c>
       <c r="J185" t="n">
-        <v>260</v>
+        <v>1646</v>
       </c>
       <c r="K185" t="n">
         <v>4.83</v>
@@ -18344,16 +18332,16 @@
         <v>840.9299999999999</v>
       </c>
       <c r="G186" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H186" t="n">
-        <v>7233</v>
+        <v>38575</v>
       </c>
       <c r="I186" t="n">
-        <v>7568</v>
+        <v>40365</v>
       </c>
       <c r="J186" t="n">
-        <v>336</v>
+        <v>1789</v>
       </c>
       <c r="K186" t="n">
         <v>4.64</v>
@@ -18425,16 +18413,16 @@
         <v>740.15</v>
       </c>
       <c r="G187" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H187" t="n">
-        <v>7905</v>
+        <v>39523</v>
       </c>
       <c r="I187" t="n">
-        <v>8142</v>
+        <v>40708</v>
       </c>
       <c r="J187" t="n">
-        <v>237</v>
+        <v>1185</v>
       </c>
       <c r="K187" t="n">
         <v>3</v>
@@ -18506,16 +18494,16 @@
         <v>457.5</v>
       </c>
       <c r="G188" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="H188" t="n">
-        <v>6691</v>
+        <v>33902</v>
       </c>
       <c r="I188" t="n">
-        <v>6862</v>
+        <v>34770</v>
       </c>
       <c r="J188" t="n">
-        <v>171</v>
+        <v>868</v>
       </c>
       <c r="K188" t="n">
         <v>2.56</v>
@@ -18587,16 +18575,16 @@
         <v>1348.22</v>
       </c>
       <c r="G189" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H189" t="n">
-        <v>5309</v>
+        <v>27871</v>
       </c>
       <c r="I189" t="n">
-        <v>5393</v>
+        <v>28313</v>
       </c>
       <c r="J189" t="n">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="K189" t="n">
         <v>1.58</v>
@@ -18668,16 +18656,16 @@
         <v>1592</v>
       </c>
       <c r="G190" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H190" t="n">
-        <v>6270</v>
+        <v>36050</v>
       </c>
       <c r="I190" t="n">
-        <v>6368</v>
+        <v>36616</v>
       </c>
       <c r="J190" t="n">
-        <v>98</v>
+        <v>566</v>
       </c>
       <c r="K190" t="n">
         <v>1.57</v>
@@ -18749,16 +18737,16 @@
         <v>2992.15</v>
       </c>
       <c r="G191" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H191" t="n">
-        <v>5892</v>
+        <v>29460</v>
       </c>
       <c r="I191" t="n">
-        <v>5984</v>
+        <v>29922</v>
       </c>
       <c r="J191" t="n">
-        <v>92</v>
+        <v>461</v>
       </c>
       <c r="K191" t="n">
         <v>1.56</v>
@@ -18911,16 +18899,16 @@
         <v>2717.1</v>
       </c>
       <c r="G193" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H193" t="n">
-        <v>8181</v>
+        <v>40905</v>
       </c>
       <c r="I193" t="n">
-        <v>8151</v>
+        <v>40756</v>
       </c>
       <c r="J193" t="n">
-        <v>-30</v>
+        <v>-148</v>
       </c>
       <c r="K193" t="n">
         <v>-0.36</v>
@@ -18992,16 +18980,16 @@
         <v>4765.65</v>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H194" t="n">
-        <v>4851</v>
+        <v>24254</v>
       </c>
       <c r="I194" t="n">
-        <v>4766</v>
+        <v>23828</v>
       </c>
       <c r="J194" t="n">
-        <v>-85</v>
+        <v>-425</v>
       </c>
       <c r="K194" t="n">
         <v>-1.75</v>
@@ -19073,16 +19061,16 @@
         <v>1464.95</v>
       </c>
       <c r="G195" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H195" t="n">
-        <v>6095</v>
+        <v>30476</v>
       </c>
       <c r="I195" t="n">
-        <v>5860</v>
+        <v>29299</v>
       </c>
       <c r="J195" t="n">
-        <v>-235</v>
+        <v>-1177</v>
       </c>
       <c r="K195" t="n">
         <v>-3.86</v>
@@ -19154,16 +19142,16 @@
         <v>4123.05</v>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H196" t="n">
-        <v>4302</v>
+        <v>30117</v>
       </c>
       <c r="I196" t="n">
-        <v>4123</v>
+        <v>28861</v>
       </c>
       <c r="J196" t="n">
-        <v>-179</v>
+        <v>-1255</v>
       </c>
       <c r="K196" t="n">
         <v>-4.17</v>
@@ -19235,16 +19223,16 @@
         <v>5016.75</v>
       </c>
       <c r="G197" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H197" t="n">
-        <v>4766</v>
+        <v>23828</v>
       </c>
       <c r="I197" t="n">
-        <v>5017</v>
+        <v>25084</v>
       </c>
       <c r="J197" t="n">
-        <v>251</v>
+        <v>1256</v>
       </c>
       <c r="K197" t="n">
         <v>5.27</v>
@@ -19316,16 +19304,16 @@
         <v>25146</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>24325</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>25146</v>
       </c>
       <c r="J198" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="K198" t="n">
         <v>3.37</v>
@@ -19397,16 +19385,16 @@
         <v>761.5</v>
       </c>
       <c r="G199" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H199" t="n">
-        <v>6661</v>
+        <v>34047</v>
       </c>
       <c r="I199" t="n">
-        <v>6854</v>
+        <v>35029</v>
       </c>
       <c r="J199" t="n">
-        <v>192</v>
+        <v>982</v>
       </c>
       <c r="K199" t="n">
         <v>2.88</v>
@@ -19478,16 +19466,16 @@
         <v>384.1</v>
       </c>
       <c r="G200" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H200" t="n">
-        <v>4865</v>
+        <v>25820</v>
       </c>
       <c r="I200" t="n">
-        <v>4993</v>
+        <v>26503</v>
       </c>
       <c r="J200" t="n">
-        <v>129</v>
+        <v>682</v>
       </c>
       <c r="K200" t="n">
         <v>2.64</v>
@@ -19559,16 +19547,16 @@
         <v>4077.8</v>
       </c>
       <c r="G201" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H201" t="n">
-        <v>4123</v>
+        <v>28861</v>
       </c>
       <c r="I201" t="n">
-        <v>4078</v>
+        <v>28545</v>
       </c>
       <c r="J201" t="n">
-        <v>-45</v>
+        <v>-317</v>
       </c>
       <c r="K201" t="n">
         <v>-1.1</v>
@@ -19640,16 +19628,16 @@
         <v>6780.85</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>27932</v>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>27123</v>
       </c>
       <c r="J202" t="n">
-        <v>0</v>
+        <v>-808</v>
       </c>
       <c r="K202" t="n">
         <v>-2.89</v>
@@ -19721,16 +19709,16 @@
         <v>1302.35</v>
       </c>
       <c r="G203" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H203" t="n">
-        <v>8089</v>
+        <v>44491</v>
       </c>
       <c r="I203" t="n">
-        <v>7814</v>
+        <v>42978</v>
       </c>
       <c r="J203" t="n">
-        <v>-275</v>
+        <v>-1514</v>
       </c>
       <c r="K203" t="n">
         <v>-3.4</v>
@@ -19802,16 +19790,16 @@
         <v>1813.3</v>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H204" t="n">
-        <v>3759</v>
+        <v>26314</v>
       </c>
       <c r="I204" t="n">
-        <v>3627</v>
+        <v>25386</v>
       </c>
       <c r="J204" t="n">
-        <v>-133</v>
+        <v>-928</v>
       </c>
       <c r="K204" t="n">
         <v>-3.53</v>
@@ -19883,16 +19871,16 @@
         <v>437.7</v>
       </c>
       <c r="G205" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H205" t="n">
-        <v>5948</v>
+        <v>30652</v>
       </c>
       <c r="I205" t="n">
-        <v>5690</v>
+        <v>29326</v>
       </c>
       <c r="J205" t="n">
-        <v>-257</v>
+        <v>-1327</v>
       </c>
       <c r="K205" t="n">
         <v>-4.33</v>
@@ -19964,16 +19952,16 @@
         <v>1107</v>
       </c>
       <c r="G206" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H206" t="n">
-        <v>5876</v>
+        <v>30553</v>
       </c>
       <c r="I206" t="n">
-        <v>5535</v>
+        <v>28782</v>
       </c>
       <c r="J206" t="n">
-        <v>-341</v>
+        <v>-1771</v>
       </c>
       <c r="K206" t="n">
         <v>-5.8</v>
@@ -20045,16 +20033,16 @@
         <v>1778.25</v>
       </c>
       <c r="G207" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H207" t="n">
-        <v>7641</v>
+        <v>42028</v>
       </c>
       <c r="I207" t="n">
-        <v>7113</v>
+        <v>39122</v>
       </c>
       <c r="J207" t="n">
-        <v>-528</v>
+        <v>-2906</v>
       </c>
       <c r="K207" t="n">
         <v>-6.91</v>
@@ -20205,16 +20193,16 @@
         <v>1393.88</v>
       </c>
       <c r="G209" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H209" t="n">
-        <v>4776</v>
+        <v>28656</v>
       </c>
       <c r="I209" t="n">
-        <v>4182</v>
+        <v>25090</v>
       </c>
       <c r="J209" t="n">
-        <v>-594</v>
+        <v>-3566</v>
       </c>
       <c r="K209" t="n">
         <v>-12.44</v>
@@ -20286,16 +20274,16 @@
         <v>2280.55</v>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H210" t="n">
-        <v>2992</v>
+        <v>26929</v>
       </c>
       <c r="I210" t="n">
-        <v>2281</v>
+        <v>20525</v>
       </c>
       <c r="J210" t="n">
-        <v>-712</v>
+        <v>-6404</v>
       </c>
       <c r="K210" t="n">
         <v>-23.78</v>
@@ -20367,16 +20355,16 @@
         <v>578.35</v>
       </c>
       <c r="G211" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="H211" t="n">
-        <v>9385</v>
+        <v>48487</v>
       </c>
       <c r="I211" t="n">
-        <v>6940</v>
+        <v>35858</v>
       </c>
       <c r="J211" t="n">
-        <v>-2444</v>
+        <v>-12629</v>
       </c>
       <c r="K211" t="n">
         <v>-26.05</v>
@@ -20446,16 +20434,16 @@
         <v>958.4</v>
       </c>
       <c r="G212" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H212" t="n">
-        <v>5779</v>
+        <v>31374</v>
       </c>
       <c r="I212" t="n">
-        <v>6709</v>
+        <v>36419</v>
       </c>
       <c r="J212" t="n">
-        <v>929</v>
+        <v>5045</v>
       </c>
       <c r="K212" t="n">
         <v>16.08</v>
@@ -20527,16 +20515,16 @@
         <v>12159</v>
       </c>
       <c r="G213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>10624</v>
       </c>
       <c r="I213" t="n">
-        <v>0</v>
+        <v>12159</v>
       </c>
       <c r="J213" t="n">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="K213" t="n">
         <v>14.44</v>
@@ -20689,16 +20677,16 @@
         <v>1402.7</v>
       </c>
       <c r="G215" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H215" t="n">
-        <v>4932</v>
+        <v>28358</v>
       </c>
       <c r="I215" t="n">
-        <v>5611</v>
+        <v>32262</v>
       </c>
       <c r="J215" t="n">
-        <v>679</v>
+        <v>3904</v>
       </c>
       <c r="K215" t="n">
         <v>13.77</v>
@@ -20770,16 +20758,16 @@
         <v>1845.6</v>
       </c>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H216" t="n">
-        <v>4923</v>
+        <v>27900</v>
       </c>
       <c r="I216" t="n">
-        <v>5537</v>
+        <v>31375</v>
       </c>
       <c r="J216" t="n">
-        <v>613</v>
+        <v>3476</v>
       </c>
       <c r="K216" t="n">
         <v>12.46</v>
@@ -20851,16 +20839,16 @@
         <v>1538.2</v>
       </c>
       <c r="G217" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H217" t="n">
-        <v>5576</v>
+        <v>32059</v>
       </c>
       <c r="I217" t="n">
-        <v>6153</v>
+        <v>35379</v>
       </c>
       <c r="J217" t="n">
-        <v>577</v>
+        <v>3319</v>
       </c>
       <c r="K217" t="n">
         <v>10.35</v>
@@ -20932,16 +20920,16 @@
         <v>1216.6</v>
       </c>
       <c r="G218" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H218" t="n">
-        <v>5535</v>
+        <v>30996</v>
       </c>
       <c r="I218" t="n">
-        <v>6083</v>
+        <v>34065</v>
       </c>
       <c r="J218" t="n">
-        <v>548</v>
+        <v>3069</v>
       </c>
       <c r="K218" t="n">
         <v>9.9</v>
@@ -21013,16 +21001,16 @@
         <v>7159.5</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>27123</v>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>28638</v>
       </c>
       <c r="J219" t="n">
-        <v>0</v>
+        <v>1515</v>
       </c>
       <c r="K219" t="n">
         <v>5.58</v>
@@ -21094,16 +21082,16 @@
         <v>1803.9</v>
       </c>
       <c r="G220" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H220" t="n">
-        <v>8891</v>
+        <v>44456</v>
       </c>
       <c r="I220" t="n">
-        <v>9020</v>
+        <v>45098</v>
       </c>
       <c r="J220" t="n">
-        <v>128</v>
+        <v>641</v>
       </c>
       <c r="K220" t="n">
         <v>1.44</v>
@@ -21175,16 +21163,16 @@
         <v>3382.6</v>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H221" t="n">
-        <v>3382</v>
+        <v>20294</v>
       </c>
       <c r="I221" t="n">
-        <v>3383</v>
+        <v>20296</v>
       </c>
       <c r="J221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K221" t="n">
         <v>0.01</v>
@@ -21256,16 +21244,16 @@
         <v>1301.6</v>
       </c>
       <c r="G222" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H222" t="n">
-        <v>3916</v>
+        <v>20887</v>
       </c>
       <c r="I222" t="n">
-        <v>3905</v>
+        <v>20826</v>
       </c>
       <c r="J222" t="n">
-        <v>-12</v>
+        <v>-62</v>
       </c>
       <c r="K222" t="n">
         <v>-0.29</v>
@@ -21335,16 +21323,16 @@
         <v>430.05</v>
       </c>
       <c r="G223" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="H223" t="n">
-        <v>6566</v>
+        <v>33703</v>
       </c>
       <c r="I223" t="n">
-        <v>6451</v>
+        <v>33114</v>
       </c>
       <c r="J223" t="n">
-        <v>-115</v>
+        <v>-589</v>
       </c>
       <c r="K223" t="n">
         <v>-1.75</v>
@@ -21416,16 +21404,16 @@
         <v>1200.5</v>
       </c>
       <c r="G224" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H224" t="n">
-        <v>7814</v>
+        <v>39070</v>
       </c>
       <c r="I224" t="n">
-        <v>7203</v>
+        <v>36015</v>
       </c>
       <c r="J224" t="n">
-        <v>-611</v>
+        <v>-3056</v>
       </c>
       <c r="K224" t="n">
         <v>-7.82</v>
@@ -21495,16 +21483,16 @@
         <v>2700</v>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H225" t="n">
-        <v>5979</v>
+        <v>41854</v>
       </c>
       <c r="I225" t="n">
-        <v>5400</v>
+        <v>37800</v>
       </c>
       <c r="J225" t="n">
-        <v>-579</v>
+        <v>-4054</v>
       </c>
       <c r="K225" t="n">
         <v>-9.69</v>
@@ -21570,16 +21558,16 @@
         <v>3401.6</v>
       </c>
       <c r="G226" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H226" t="n">
-        <v>4078</v>
+        <v>36700</v>
       </c>
       <c r="I226" t="n">
-        <v>3402</v>
+        <v>30614</v>
       </c>
       <c r="J226" t="n">
-        <v>-676</v>
+        <v>-6086</v>
       </c>
       <c r="K226" t="n">
         <v>-16.58</v>
@@ -21732,16 +21720,16 @@
         <v>1424.6</v>
       </c>
       <c r="G228" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H228" t="n">
-        <v>3905</v>
+        <v>24730</v>
       </c>
       <c r="I228" t="n">
-        <v>4274</v>
+        <v>27067</v>
       </c>
       <c r="J228" t="n">
-        <v>369</v>
+        <v>2337</v>
       </c>
       <c r="K228" t="n">
         <v>9.449999999999999</v>
@@ -21813,16 +21801,16 @@
         <v>3553.7</v>
       </c>
       <c r="G229" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H229" t="n">
-        <v>6650</v>
+        <v>36576</v>
       </c>
       <c r="I229" t="n">
-        <v>7107</v>
+        <v>39091</v>
       </c>
       <c r="J229" t="n">
-        <v>457</v>
+        <v>2515</v>
       </c>
       <c r="K229" t="n">
         <v>6.87</v>
@@ -21894,16 +21882,16 @@
         <v>12627</v>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>23788</v>
       </c>
       <c r="I230" t="n">
-        <v>0</v>
+        <v>25254</v>
       </c>
       <c r="J230" t="n">
-        <v>0</v>
+        <v>1466</v>
       </c>
       <c r="K230" t="n">
         <v>6.16</v>
@@ -21975,16 +21963,16 @@
         <v>1488.6</v>
       </c>
       <c r="G231" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H231" t="n">
-        <v>5611</v>
+        <v>32262</v>
       </c>
       <c r="I231" t="n">
-        <v>5954</v>
+        <v>34238</v>
       </c>
       <c r="J231" t="n">
-        <v>344</v>
+        <v>1976</v>
       </c>
       <c r="K231" t="n">
         <v>6.12</v>
@@ -22056,16 +22044,16 @@
         <v>3354.5</v>
       </c>
       <c r="G232" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H232" t="n">
-        <v>6343</v>
+        <v>31713</v>
       </c>
       <c r="I232" t="n">
-        <v>6709</v>
+        <v>33545</v>
       </c>
       <c r="J232" t="n">
-        <v>366</v>
+        <v>1832</v>
       </c>
       <c r="K232" t="n">
         <v>5.78</v>
@@ -22137,16 +22125,16 @@
         <v>1012.15</v>
       </c>
       <c r="G233" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H233" t="n">
-        <v>6709</v>
+        <v>37378</v>
       </c>
       <c r="I233" t="n">
-        <v>7085</v>
+        <v>39474</v>
       </c>
       <c r="J233" t="n">
-        <v>376</v>
+        <v>2096</v>
       </c>
       <c r="K233" t="n">
         <v>5.61</v>
@@ -22218,16 +22206,16 @@
         <v>32115</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H234" t="n">
-        <v>0</v>
+        <v>30705</v>
       </c>
       <c r="I234" t="n">
-        <v>0</v>
+        <v>32115</v>
       </c>
       <c r="J234" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="K234" t="n">
         <v>4.59</v>
@@ -22299,16 +22287,16 @@
         <v>1226.25</v>
       </c>
       <c r="G235" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H235" t="n">
-        <v>7300</v>
+        <v>36498</v>
       </c>
       <c r="I235" t="n">
-        <v>7358</v>
+        <v>36788</v>
       </c>
       <c r="J235" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="K235" t="n">
         <v>0.79</v>
@@ -22380,16 +22368,16 @@
         <v>390.75</v>
       </c>
       <c r="G236" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H236" t="n">
-        <v>4398</v>
+        <v>21992</v>
       </c>
       <c r="I236" t="n">
-        <v>4298</v>
+        <v>21491</v>
       </c>
       <c r="J236" t="n">
-        <v>-100</v>
+        <v>-500</v>
       </c>
       <c r="K236" t="n">
         <v>-2.28</v>
@@ -22461,16 +22449,16 @@
         <v>414.95</v>
       </c>
       <c r="G237" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H237" t="n">
-        <v>9031</v>
+        <v>45585</v>
       </c>
       <c r="I237" t="n">
-        <v>8714</v>
+        <v>43985</v>
       </c>
       <c r="J237" t="n">
-        <v>-317</v>
+        <v>-1601</v>
       </c>
       <c r="K237" t="n">
         <v>-3.51</v>
@@ -22542,16 +22530,16 @@
         <v>2375.4</v>
       </c>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H238" t="n">
-        <v>4929</v>
+        <v>24644</v>
       </c>
       <c r="I238" t="n">
-        <v>4751</v>
+        <v>23754</v>
       </c>
       <c r="J238" t="n">
-        <v>-178</v>
+        <v>-890</v>
       </c>
       <c r="K238" t="n">
         <v>-3.61</v>
@@ -22623,16 +22611,16 @@
         <v>1459.45</v>
       </c>
       <c r="G239" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H239" t="n">
-        <v>6153</v>
+        <v>33840</v>
       </c>
       <c r="I239" t="n">
-        <v>5838</v>
+        <v>32108</v>
       </c>
       <c r="J239" t="n">
-        <v>-315</v>
+        <v>-1732</v>
       </c>
       <c r="K239" t="n">
         <v>-5.12</v>
@@ -22704,16 +22692,16 @@
         <v>3179.1</v>
       </c>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H240" t="n">
-        <v>6803</v>
+        <v>40819</v>
       </c>
       <c r="I240" t="n">
-        <v>6358</v>
+        <v>38149</v>
       </c>
       <c r="J240" t="n">
-        <v>-445</v>
+        <v>-2670</v>
       </c>
       <c r="K240" t="n">
         <v>-6.54</v>
@@ -22785,16 +22773,16 @@
         <v>1682.5</v>
       </c>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H241" t="n">
-        <v>5412</v>
+        <v>28862</v>
       </c>
       <c r="I241" t="n">
-        <v>5048</v>
+        <v>26920</v>
       </c>
       <c r="J241" t="n">
-        <v>-364</v>
+        <v>-1942</v>
       </c>
       <c r="K241" t="n">
         <v>-6.73</v>
@@ -22866,16 +22854,16 @@
         <v>16274</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H242" t="n">
-        <v>0</v>
+        <v>25254</v>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>32548</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>7294</v>
       </c>
       <c r="K242" t="n">
         <v>28.88</v>
@@ -22947,16 +22935,16 @@
         <v>1584.4</v>
       </c>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H243" t="n">
-        <v>4420</v>
+        <v>27996</v>
       </c>
       <c r="I243" t="n">
-        <v>4753</v>
+        <v>30104</v>
       </c>
       <c r="J243" t="n">
-        <v>333</v>
+        <v>2107</v>
       </c>
       <c r="K243" t="n">
         <v>7.53</v>
@@ -23109,16 +23097,16 @@
         <v>7837.5</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H245" t="n">
-        <v>0</v>
+        <v>22120</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>23512</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="K245" t="n">
         <v>6.29</v>
@@ -23190,16 +23178,16 @@
         <v>2501.6</v>
       </c>
       <c r="G246" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H246" t="n">
-        <v>4751</v>
+        <v>30880</v>
       </c>
       <c r="I246" t="n">
-        <v>5003</v>
+        <v>32521</v>
       </c>
       <c r="J246" t="n">
-        <v>252</v>
+        <v>1641</v>
       </c>
       <c r="K246" t="n">
         <v>5.31</v>
@@ -23271,16 +23259,16 @@
         <v>1282</v>
       </c>
       <c r="G247" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H247" t="n">
-        <v>6131</v>
+        <v>30656</v>
       </c>
       <c r="I247" t="n">
-        <v>6410</v>
+        <v>32050</v>
       </c>
       <c r="J247" t="n">
-        <v>279</v>
+        <v>1394</v>
       </c>
       <c r="K247" t="n">
         <v>4.55</v>
@@ -23352,16 +23340,16 @@
         <v>1507.1</v>
       </c>
       <c r="G248" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H248" t="n">
-        <v>10216</v>
+        <v>54000</v>
       </c>
       <c r="I248" t="n">
-        <v>10550</v>
+        <v>55763</v>
       </c>
       <c r="J248" t="n">
-        <v>334</v>
+        <v>1763</v>
       </c>
       <c r="K248" t="n">
         <v>3.26</v>
@@ -23433,16 +23421,16 @@
         <v>1283.6</v>
       </c>
       <c r="G249" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H249" t="n">
-        <v>4990</v>
+        <v>26195</v>
       </c>
       <c r="I249" t="n">
-        <v>5134</v>
+        <v>26956</v>
       </c>
       <c r="J249" t="n">
-        <v>145</v>
+        <v>760</v>
       </c>
       <c r="K249" t="n">
         <v>2.9</v>
@@ -23514,16 +23502,16 @@
         <v>394.05</v>
       </c>
       <c r="G250" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H250" t="n">
-        <v>5080</v>
+        <v>26180</v>
       </c>
       <c r="I250" t="n">
-        <v>5123</v>
+        <v>26401</v>
       </c>
       <c r="J250" t="n">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="K250" t="n">
         <v>0.84</v>
@@ -23595,16 +23583,16 @@
         <v>416.8</v>
       </c>
       <c r="G251" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="H251" t="n">
-        <v>7054</v>
+        <v>36516</v>
       </c>
       <c r="I251" t="n">
-        <v>7086</v>
+        <v>36678</v>
       </c>
       <c r="J251" t="n">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="K251" t="n">
         <v>0.45</v>
@@ -23676,16 +23664,16 @@
         <v>994.75</v>
       </c>
       <c r="G252" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H252" t="n">
-        <v>6073</v>
+        <v>32389</v>
       </c>
       <c r="I252" t="n">
-        <v>5968</v>
+        <v>31832</v>
       </c>
       <c r="J252" t="n">
-        <v>-104</v>
+        <v>-557</v>
       </c>
       <c r="K252" t="n">
         <v>-1.72</v>
@@ -23757,16 +23745,16 @@
         <v>3063.2</v>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H253" t="n">
-        <v>6358</v>
+        <v>38149</v>
       </c>
       <c r="I253" t="n">
-        <v>6126</v>
+        <v>36758</v>
       </c>
       <c r="J253" t="n">
-        <v>-232</v>
+        <v>-1391</v>
       </c>
       <c r="K253" t="n">
         <v>-3.65</v>
@@ -23836,16 +23824,16 @@
         <v>1850.1</v>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H254" t="n">
-        <v>5850</v>
+        <v>29250</v>
       </c>
       <c r="I254" t="n">
-        <v>5550</v>
+        <v>27752</v>
       </c>
       <c r="J254" t="n">
-        <v>-300</v>
+        <v>-1498</v>
       </c>
       <c r="K254" t="n">
         <v>-5.12</v>
@@ -23915,16 +23903,16 @@
         <v>1377.7</v>
       </c>
       <c r="G255" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H255" t="n">
-        <v>5954</v>
+        <v>31261</v>
       </c>
       <c r="I255" t="n">
-        <v>5511</v>
+        <v>28932</v>
       </c>
       <c r="J255" t="n">
-        <v>-444</v>
+        <v>-2329</v>
       </c>
       <c r="K255" t="n">
         <v>-7.45</v>
@@ -24073,16 +24061,16 @@
         <v>1053.15</v>
       </c>
       <c r="G257" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H257" t="n">
-        <v>6332</v>
+        <v>34371</v>
       </c>
       <c r="I257" t="n">
-        <v>7372</v>
+        <v>40020</v>
       </c>
       <c r="J257" t="n">
-        <v>1041</v>
+        <v>5649</v>
       </c>
       <c r="K257" t="n">
         <v>16.43</v>
@@ -24154,16 +24142,16 @@
         <v>422.9</v>
       </c>
       <c r="G258" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H258" t="n">
-        <v>7093</v>
+        <v>35859</v>
       </c>
       <c r="I258" t="n">
-        <v>7612</v>
+        <v>38484</v>
       </c>
       <c r="J258" t="n">
-        <v>519</v>
+        <v>2625</v>
       </c>
       <c r="K258" t="n">
         <v>7.32</v>
@@ -24235,16 +24223,16 @@
         <v>12589</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" t="n">
-        <v>0</v>
+        <v>11918</v>
       </c>
       <c r="I259" t="n">
-        <v>0</v>
+        <v>12589</v>
       </c>
       <c r="J259" t="n">
-        <v>0</v>
+        <v>671</v>
       </c>
       <c r="K259" t="n">
         <v>5.63</v>
@@ -24316,16 +24304,16 @@
         <v>7164.5</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H260" t="n">
-        <v>0</v>
+        <v>27360</v>
       </c>
       <c r="I260" t="n">
-        <v>0</v>
+        <v>28658</v>
       </c>
       <c r="J260" t="n">
-        <v>0</v>
+        <v>1298</v>
       </c>
       <c r="K260" t="n">
         <v>4.74</v>
@@ -24397,16 +24385,16 @@
         <v>745.8</v>
       </c>
       <c r="G261" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="H261" t="n">
-        <v>7984</v>
+        <v>42825</v>
       </c>
       <c r="I261" t="n">
-        <v>8204</v>
+        <v>44002</v>
       </c>
       <c r="J261" t="n">
-        <v>219</v>
+        <v>1177</v>
       </c>
       <c r="K261" t="n">
         <v>2.75</v>
@@ -24478,16 +24466,16 @@
         <v>344.7</v>
       </c>
       <c r="G262" t="n">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="H262" t="n">
-        <v>6113</v>
+        <v>31922</v>
       </c>
       <c r="I262" t="n">
-        <v>6205</v>
+        <v>32402</v>
       </c>
       <c r="J262" t="n">
-        <v>92</v>
+        <v>479</v>
       </c>
       <c r="K262" t="n">
         <v>1.5</v>
@@ -24559,16 +24547,16 @@
         <v>247.95</v>
       </c>
       <c r="G263" t="n">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="H263" t="n">
-        <v>6884</v>
+        <v>34930</v>
       </c>
       <c r="I263" t="n">
-        <v>6695</v>
+        <v>33969</v>
       </c>
       <c r="J263" t="n">
-        <v>-189</v>
+        <v>-960</v>
       </c>
       <c r="K263" t="n">
         <v>-2.75</v>
@@ -24640,16 +24628,16 @@
         <v>1973.4</v>
       </c>
       <c r="G264" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H264" t="n">
-        <v>4059</v>
+        <v>20293</v>
       </c>
       <c r="I264" t="n">
-        <v>3947</v>
+        <v>19734</v>
       </c>
       <c r="J264" t="n">
-        <v>-112</v>
+        <v>-559</v>
       </c>
       <c r="K264" t="n">
         <v>-2.75</v>
@@ -24721,16 +24709,16 @@
         <v>3787.8</v>
       </c>
       <c r="G265" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H265" t="n">
-        <v>3905</v>
+        <v>23429</v>
       </c>
       <c r="I265" t="n">
-        <v>3788</v>
+        <v>22727</v>
       </c>
       <c r="J265" t="n">
-        <v>-117</v>
+        <v>-703</v>
       </c>
       <c r="K265" t="n">
         <v>-3</v>
@@ -24802,16 +24790,16 @@
         <v>1638.9</v>
       </c>
       <c r="G266" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H266" t="n">
-        <v>8495</v>
+        <v>45873</v>
       </c>
       <c r="I266" t="n">
-        <v>8194</v>
+        <v>44250</v>
       </c>
       <c r="J266" t="n">
-        <v>-300</v>
+        <v>-1623</v>
       </c>
       <c r="K266" t="n">
         <v>-3.54</v>
@@ -24883,16 +24871,16 @@
         <v>1447.2</v>
       </c>
       <c r="G267" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H267" t="n">
-        <v>9043</v>
+        <v>46720</v>
       </c>
       <c r="I267" t="n">
-        <v>8683</v>
+        <v>44863</v>
       </c>
       <c r="J267" t="n">
-        <v>-359</v>
+        <v>-1857</v>
       </c>
       <c r="K267" t="n">
         <v>-3.97</v>
@@ -24964,16 +24952,16 @@
         <v>1380.5</v>
       </c>
       <c r="G268" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H268" t="n">
-        <v>2903</v>
+        <v>20322</v>
       </c>
       <c r="I268" t="n">
-        <v>2761</v>
+        <v>19327</v>
       </c>
       <c r="J268" t="n">
-        <v>-142</v>
+        <v>-995</v>
       </c>
       <c r="K268" t="n">
         <v>-4.9</v>
@@ -25045,16 +25033,16 @@
         <v>926.4</v>
       </c>
       <c r="G269" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H269" t="n">
-        <v>5968</v>
+        <v>32827</v>
       </c>
       <c r="I269" t="n">
-        <v>5558</v>
+        <v>30571</v>
       </c>
       <c r="J269" t="n">
-        <v>-410</v>
+        <v>-2256</v>
       </c>
       <c r="K269" t="n">
         <v>-6.87</v>
@@ -25126,16 +25114,16 @@
         <v>1687.9</v>
       </c>
       <c r="G270" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H270" t="n">
-        <v>5550</v>
+        <v>31452</v>
       </c>
       <c r="I270" t="n">
-        <v>5064</v>
+        <v>28694</v>
       </c>
       <c r="J270" t="n">
-        <v>-487</v>
+        <v>-2757</v>
       </c>
       <c r="K270" t="n">
         <v>-8.77</v>
@@ -25207,16 +25195,16 @@
         <v>318.65</v>
       </c>
       <c r="G271" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="H271" t="n">
-        <v>7086</v>
+        <v>35845</v>
       </c>
       <c r="I271" t="n">
-        <v>5417</v>
+        <v>27404</v>
       </c>
       <c r="J271" t="n">
-        <v>-1669</v>
+        <v>-8441</v>
       </c>
       <c r="K271" t="n">
         <v>-23.55</v>
@@ -25288,16 +25276,16 @@
         <v>318.35</v>
       </c>
       <c r="G272" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="H272" t="n">
-        <v>3561</v>
+        <v>18313</v>
       </c>
       <c r="I272" t="n">
-        <v>4457</v>
+        <v>22921</v>
       </c>
       <c r="J272" t="n">
-        <v>896</v>
+        <v>4608</v>
       </c>
       <c r="K272" t="n">
         <v>25.16</v>
@@ -25369,16 +25357,16 @@
         <v>299.55</v>
       </c>
       <c r="G273" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H273" t="n">
-        <v>4711</v>
+        <v>24299</v>
       </c>
       <c r="I273" t="n">
-        <v>5691</v>
+        <v>29356</v>
       </c>
       <c r="J273" t="n">
-        <v>980</v>
+        <v>5057</v>
       </c>
       <c r="K273" t="n">
         <v>20.81</v>
@@ -25450,16 +25438,16 @@
         <v>399.15</v>
       </c>
       <c r="G274" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H274" t="n">
-        <v>3792</v>
+        <v>18958</v>
       </c>
       <c r="I274" t="n">
-        <v>4391</v>
+        <v>21953</v>
       </c>
       <c r="J274" t="n">
-        <v>599</v>
+        <v>2995</v>
       </c>
       <c r="K274" t="n">
         <v>15.8</v>
@@ -25531,16 +25519,16 @@
         <v>4385.2</v>
       </c>
       <c r="G275" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H275" t="n">
-        <v>3997</v>
+        <v>35973</v>
       </c>
       <c r="I275" t="n">
-        <v>4385</v>
+        <v>39467</v>
       </c>
       <c r="J275" t="n">
-        <v>388</v>
+        <v>3494</v>
       </c>
       <c r="K275" t="n">
         <v>9.710000000000001</v>
@@ -25612,16 +25600,16 @@
         <v>4014</v>
       </c>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H276" t="n">
-        <v>7576</v>
+        <v>41666</v>
       </c>
       <c r="I276" t="n">
-        <v>8028</v>
+        <v>44154</v>
       </c>
       <c r="J276" t="n">
-        <v>452</v>
+        <v>2488</v>
       </c>
       <c r="K276" t="n">
         <v>5.97</v>
@@ -25693,16 +25681,16 @@
         <v>775</v>
       </c>
       <c r="G277" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H277" t="n">
-        <v>6712</v>
+        <v>36544</v>
       </c>
       <c r="I277" t="n">
-        <v>6975</v>
+        <v>37975</v>
       </c>
       <c r="J277" t="n">
-        <v>263</v>
+        <v>1431</v>
       </c>
       <c r="K277" t="n">
         <v>3.92</v>
@@ -25774,16 +25762,16 @@
         <v>1430.8</v>
       </c>
       <c r="G278" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H278" t="n">
-        <v>5522</v>
+        <v>31752</v>
       </c>
       <c r="I278" t="n">
-        <v>5723</v>
+        <v>32908</v>
       </c>
       <c r="J278" t="n">
-        <v>201</v>
+        <v>1157</v>
       </c>
       <c r="K278" t="n">
         <v>3.64</v>
@@ -25855,16 +25843,16 @@
         <v>1458.6</v>
       </c>
       <c r="G279" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H279" t="n">
-        <v>9965</v>
+        <v>54097</v>
       </c>
       <c r="I279" t="n">
-        <v>10210</v>
+        <v>55427</v>
       </c>
       <c r="J279" t="n">
-        <v>245</v>
+        <v>1330</v>
       </c>
       <c r="K279" t="n">
         <v>2.46</v>
@@ -25936,16 +25924,16 @@
         <v>1068.45</v>
       </c>
       <c r="G280" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H280" t="n">
-        <v>7372</v>
+        <v>36860</v>
       </c>
       <c r="I280" t="n">
-        <v>7479</v>
+        <v>37396</v>
       </c>
       <c r="J280" t="n">
-        <v>107</v>
+        <v>536</v>
       </c>
       <c r="K280" t="n">
         <v>1.45</v>
@@ -26017,16 +26005,16 @@
         <v>1886.8</v>
       </c>
       <c r="G281" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H281" t="n">
-        <v>5920</v>
+        <v>37495</v>
       </c>
       <c r="I281" t="n">
-        <v>5660</v>
+        <v>35849</v>
       </c>
       <c r="J281" t="n">
-        <v>-260</v>
+        <v>-1645</v>
       </c>
       <c r="K281" t="n">
         <v>-4.39</v>
@@ -26098,16 +26086,16 @@
         <v>1375.7</v>
       </c>
       <c r="G282" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H282" t="n">
-        <v>5789</v>
+        <v>31838</v>
       </c>
       <c r="I282" t="n">
-        <v>5503</v>
+        <v>30265</v>
       </c>
       <c r="J282" t="n">
-        <v>-286</v>
+        <v>-1573</v>
       </c>
       <c r="K282" t="n">
         <v>-4.94</v>
@@ -26179,16 +26167,16 @@
         <v>11586</v>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H283" t="n">
-        <v>0</v>
+        <v>12589</v>
       </c>
       <c r="I283" t="n">
-        <v>0</v>
+        <v>11586</v>
       </c>
       <c r="J283" t="n">
-        <v>0</v>
+        <v>-1003</v>
       </c>
       <c r="K283" t="n">
         <v>-7.97</v>
@@ -26341,16 +26329,16 @@
         <v>539.55</v>
       </c>
       <c r="G285" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H285" t="n">
-        <v>3645</v>
+        <v>20655</v>
       </c>
       <c r="I285" t="n">
-        <v>3237</v>
+        <v>18345</v>
       </c>
       <c r="J285" t="n">
-        <v>-408</v>
+        <v>-2310</v>
       </c>
       <c r="K285" t="n">
         <v>-11.19</v>
@@ -26422,16 +26410,16 @@
         <v>771.7</v>
       </c>
       <c r="G286" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="H286" t="n">
-        <v>11117</v>
+        <v>56510</v>
       </c>
       <c r="I286" t="n">
-        <v>9260</v>
+        <v>47074</v>
       </c>
       <c r="J286" t="n">
-        <v>-1856</v>
+        <v>-9437</v>
       </c>
       <c r="K286" t="n">
         <v>-16.7</v>
@@ -26490,47 +26478,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Horizon</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Win Rate %</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Median Return %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Beat Nifty %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Worst Cycle %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sharpe (ann)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Chosen</t>
         </is>
@@ -26560,7 +26548,7 @@
         <v>-5.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -26626,7 +26614,7 @@
         <v>-6.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -26659,7 +26647,7 @@
         <v>-8.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -26819,52 +26807,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Start Rs</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>End Rs</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>If Nifty Rs</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Beat Nifty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Win Ratio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Largest Winner</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Largest Loser</t>
         </is>
@@ -26877,16 +26865,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C2" t="n">
         <v>12.6</v>
       </c>
       <c r="D2" t="n">
-        <v>112600</v>
+        <v>563000</v>
       </c>
       <c r="E2" t="n">
-        <v>111800</v>
+        <v>559000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -26919,16 +26907,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112600</v>
+        <v>563000</v>
       </c>
       <c r="C3" t="n">
         <v>-3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>108546</v>
+        <v>542732</v>
       </c>
       <c r="E3" t="n">
-        <v>112359</v>
+        <v>561795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -26961,16 +26949,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108546</v>
+        <v>542732</v>
       </c>
       <c r="C4" t="n">
         <v>-1.9</v>
       </c>
       <c r="D4" t="n">
-        <v>106484</v>
+        <v>532420</v>
       </c>
       <c r="E4" t="n">
-        <v>114494</v>
+        <v>572469</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -27003,16 +26991,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106484</v>
+        <v>532420</v>
       </c>
       <c r="C5" t="n">
         <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>106165</v>
+        <v>530823</v>
       </c>
       <c r="E5" t="n">
-        <v>101900</v>
+        <v>509498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -27045,16 +27033,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>106165</v>
+        <v>530823</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>113596</v>
+        <v>567980</v>
       </c>
       <c r="E6" t="n">
-        <v>110357</v>
+        <v>551786</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27087,16 +27075,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113596</v>
+        <v>567980</v>
       </c>
       <c r="C7" t="n">
         <v>14.8</v>
       </c>
       <c r="D7" t="n">
-        <v>130408</v>
+        <v>652042</v>
       </c>
       <c r="E7" t="n">
-        <v>113778</v>
+        <v>568891</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -27129,16 +27117,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>130408</v>
+        <v>652042</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>134321</v>
+        <v>671603</v>
       </c>
       <c r="E8" t="n">
-        <v>113437</v>
+        <v>567184</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -27171,16 +27159,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134321</v>
+        <v>671603</v>
       </c>
       <c r="C9" t="n">
         <v>13.2</v>
       </c>
       <c r="D9" t="n">
-        <v>152051</v>
+        <v>760254</v>
       </c>
       <c r="E9" t="n">
-        <v>123646</v>
+        <v>618231</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -27213,16 +27201,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152051</v>
+        <v>760254</v>
       </c>
       <c r="C10" t="n">
         <v>9.1</v>
       </c>
       <c r="D10" t="n">
-        <v>165887</v>
+        <v>829437</v>
       </c>
       <c r="E10" t="n">
-        <v>125748</v>
+        <v>628741</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -27255,16 +27243,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>165887</v>
+        <v>829437</v>
       </c>
       <c r="C11" t="n">
         <v>13.6</v>
       </c>
       <c r="D11" t="n">
-        <v>188448</v>
+        <v>942241</v>
       </c>
       <c r="E11" t="n">
-        <v>140712</v>
+        <v>703561</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -27297,16 +27285,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>188448</v>
+        <v>942241</v>
       </c>
       <c r="C12" t="n">
         <v>0.8</v>
       </c>
       <c r="D12" t="n">
-        <v>189956</v>
+        <v>949779</v>
       </c>
       <c r="E12" t="n">
-        <v>140009</v>
+        <v>700043</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -27339,16 +27327,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>189956</v>
+        <v>949779</v>
       </c>
       <c r="C13" t="n">
         <v>12.2</v>
       </c>
       <c r="D13" t="n">
-        <v>213130</v>
+        <v>1065652</v>
       </c>
       <c r="E13" t="n">
-        <v>156110</v>
+        <v>780548</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -27381,16 +27369,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>213130</v>
+        <v>1065652</v>
       </c>
       <c r="C14" t="n">
         <v>4.2</v>
       </c>
       <c r="D14" t="n">
-        <v>222082</v>
+        <v>1110409</v>
       </c>
       <c r="E14" t="n">
-        <v>158139</v>
+        <v>790696</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -27423,16 +27411,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>222082</v>
+        <v>1110409</v>
       </c>
       <c r="C15" t="n">
         <v>-6.4</v>
       </c>
       <c r="D15" t="n">
-        <v>207869</v>
+        <v>1039343</v>
       </c>
       <c r="E15" t="n">
-        <v>148493</v>
+        <v>742463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -27465,16 +27453,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>207869</v>
+        <v>1039343</v>
       </c>
       <c r="C16" t="n">
         <v>3.3</v>
       </c>
       <c r="D16" t="n">
-        <v>214728</v>
+        <v>1073641</v>
       </c>
       <c r="E16" t="n">
-        <v>154284</v>
+        <v>771419</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -27507,16 +27495,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>214728</v>
+        <v>1073641</v>
       </c>
       <c r="C17" t="n">
         <v>1.9</v>
       </c>
       <c r="D17" t="n">
-        <v>218808</v>
+        <v>1094041</v>
       </c>
       <c r="E17" t="n">
-        <v>160455</v>
+        <v>802276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -27549,16 +27537,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>218808</v>
+        <v>1094041</v>
       </c>
       <c r="C18" t="n">
         <v>2.7</v>
       </c>
       <c r="D18" t="n">
-        <v>224716</v>
+        <v>1123580</v>
       </c>
       <c r="E18" t="n">
-        <v>164146</v>
+        <v>820728</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -27591,16 +27579,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>224716</v>
+        <v>1123580</v>
       </c>
       <c r="C19" t="n">
         <v>-1.6</v>
       </c>
       <c r="D19" t="n">
-        <v>221120</v>
+        <v>1105602</v>
       </c>
       <c r="E19" t="n">
-        <v>160206</v>
+        <v>801031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -27633,16 +27621,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>221120</v>
+        <v>1105602</v>
       </c>
       <c r="C20" t="n">
         <v>0.8</v>
       </c>
       <c r="D20" t="n">
-        <v>222889</v>
+        <v>1114447</v>
       </c>
       <c r="E20" t="n">
-        <v>152676</v>
+        <v>763382</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -27675,16 +27663,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C21" t="n">
         <v>122.9</v>
       </c>
       <c r="D21" t="n">
-        <v>222889</v>
+        <v>1114447</v>
       </c>
       <c r="E21" t="n">
-        <v>152676</v>
+        <v>763382</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -27711,17 +27699,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>% of Capital</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Holdings</t>
         </is>
@@ -27735,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27750,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27765,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27775,42 +27763,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27820,7 +27808,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -27840,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27894,12 +27882,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (56)</t>
+          <t>ITC (55)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SBILIFE, SUNPHARMA</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ICICIGI, TORNTPHARM</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-17  /  2026-07-17</t>
+          <t>2026-07-20  /  2026-07-20</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -1537,10 +1537,10 @@
         <v>93</v>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8826</v>
+        <v>8868</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8617 - 9035</t>
+          <t>8660 - 9076</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+14.8%)</t>
+          <t>Above 200-DMA (+15.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35304</v>
+        <v>35472</v>
       </c>
       <c r="W2" t="n">
         <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.8%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+15.3%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +9 = 78</t>
+          <t>Risk/Vol +24 · Trend/Tech +19 · Historical +18 · Regime +9 · Sector +9 = 79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,13 +1652,13 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H3" t="n">
         <v>97</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1932.6</v>
+        <v>1940.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1880 - 1986</t>
+          <t>1888 - 1994</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.0%)</t>
+          <t>Above 200-DMA (+10.4%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23191</v>
+        <v>21348</v>
       </c>
       <c r="W3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X3" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 78; TORNTPHARM: 83, ABBOTINDIA: 78, ALKEM: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; TORNTPHARM: 84, ABBOTINDIA: 79, ALKEM: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.4%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +6 = 76</t>
+          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +5 = 75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1773,10 +1773,10 @@
         <v>90</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I4" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.1%)</t>
+          <t>Above 200-DMA (+10.0%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>32072</v>
+        <v>29540</v>
       </c>
       <c r="W4" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="X4" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 76; NESTLEIND: 76, UNITDSPR: 67, DABUR: 60</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 75; NESTLEIND: 75, UNITDSPR: 65, TATACONSUM: 59</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+10.1%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+10.0%) • outperforming Nifty • sector strength 53/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
@@ -1888,13 +1888,13 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
         <v>99</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2443.2</v>
+        <v>2456.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2382 - 2505</t>
+          <t>2395 - 2518</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.2%)</t>
+          <t>Above 200-DMA (+11.7%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>26875</v>
+        <v>24568</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 75; TORNTPHARM: 83, ABBOTINDIA: 78, SUNPHARMA: 78. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 75; TORNTPHARM: 84, ABBOTINDIA: 79, SUNPHARMA: 79. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.2%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.7%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +4 = 74</t>
+          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +8 = 73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,58 +2003,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1444.3</v>
+        <v>1931.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1403 - 1486</t>
+          <t>1877 - 1985</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>-3% to +15%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.3%)</t>
+          <t>Below 200-DMA (-1.0%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>18776</v>
+        <v>23174</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X6" t="n">
-        <v>6.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 74; FEDERALBNK: 66, SBIN: 65, KOTAKBANK: 63</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 73; INDUSTOWER: 60, TATACOMM: 54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-1.0%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +6 = 71</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +15 · Regime +9 · Sector +4 = 72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,58 +2121,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G7" t="n">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="H7" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I7" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1908.8</v>
+        <v>1444.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1856 - 1962</t>
+          <t>1403 - 1486</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.2%)</t>
+          <t>Above 200-DMA (+7.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>24814</v>
+        <v>18778</v>
       </c>
       <c r="W7" t="n">
         <v>13</v>
       </c>
       <c r="X7" t="n">
-        <v>8.300000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 71; INDUSTOWER: 57, TATACOMM: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 72; FEDERALBNK: 66, SBIN: 65, LICI: 64</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.2%) • sector strength 65/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Trend/Tech +17 · Historical +14 · Regime +9 · Sector +8 = 70</t>
+          <t>Risk/Vol +22 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 70</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2242,13 @@
         <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H8" t="n">
         <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1566.1</v>
+        <v>1567</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1517 - 1615</t>
+          <t>1518 - 1616</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.8%)</t>
+          <t>Above 200-DMA (+6.9%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>23491</v>
+        <v>21938</v>
       </c>
       <c r="W8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="X8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,27 +2323,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 64, BALRAMCHIN: 61, DEEPAKNTR: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, BALRAMCHIN: 61, SRF: 60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+6.8%) • outperforming Nifty • sector strength 76/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+6.9%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +2 = 65</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,7 +2360,7 @@
         <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H9" t="n">
         <v>96</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>341.9</v>
+        <v>346.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>332 - 351</t>
+          <t>337 - 356</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,34 +2400,34 @@
         </is>
       </c>
       <c r="Q9" t="n">
+        <v>72</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-3.0%)</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>41</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>24580</v>
+      </c>
+      <c r="W9" t="n">
         <v>71</v>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-4.2%)</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>34</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2 months (2M)</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="V9" t="n">
-        <v>18460</v>
-      </c>
-      <c r="W9" t="n">
-        <v>54</v>
-      </c>
       <c r="X9" t="n">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 57, NHPC: 54, TATAPOWER: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 63, POWERGRID: 56, TATAPOWER: 54</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.2%) • sector strength 24/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-3.0%) • sector strength 24/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1327.2</v>
+        <v>1335</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1288 - 1367</t>
+          <t>1295 - 1375</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.1%)</t>
+          <t>Below 200-DMA (-5.6%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>25217</v>
+        <v>20025</v>
       </c>
       <c r="W10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="X10" t="n">
-        <v>8.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 59; GAIL: 61, IOC: 48, ONGC: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 59; GAIL: 60, IOC: 48, IGL: 46. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-6.1%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-5.6%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +2 = 57</t>
+          <t>Risk/Vol +23 · Historical +16 · Regime +9 · Trend/Tech +6 · Sector +4 = 58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2593,36 +2593,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
         <v>93</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>283.5</v>
+        <v>1822</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>275 - 292</t>
+          <t>1768 - 1876</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.9%)</t>
+          <t>Below 200-DMA (-5.1%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>16162</v>
+        <v>16398</v>
       </c>
       <c r="W11" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="X11" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, NHPC: 54, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBILIFE: 58; ICICIBANK: 72, FEDERALBNK: 66, SBIN: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.9%) • sector strength 24/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.1%) • sector strength 35/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +0.0%</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Sector +6 · Trend/Tech +4 = 56</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +2 = 56</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2707,62 +2707,62 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="I12" t="n">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>280.7</v>
+        <v>285</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>273 - 288</t>
+          <t>276 - 294</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.3%)</t>
+          <t>Below 200-DMA (-0.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>30596</v>
+        <v>24225</v>
       </c>
       <c r="W12" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="X12" t="n">
-        <v>10.2</v>
+        <v>8.1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 56; MARICO: 76, NESTLEIND: 76, UNITDSPR: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 65, NHPC: 63, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.3%) • sector strength 59/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.4%) • sector strength 24/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +4 = 56</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Sector +5 · Trend/Tech +4 = 55</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2825,62 +2825,62 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1829.4</v>
+        <v>280.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1775 - 1884</t>
+          <t>273 - 288</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.7%)</t>
+          <t>Below 200-DMA (-17.2%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,21 +2889,21 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>18294</v>
+        <v>31696</v>
       </c>
       <c r="W13" t="n">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="X13" t="n">
-        <v>6.2</v>
+        <v>10.6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBILIFE: 56; ICICIBANK: 74, FEDERALBNK: 66, SBIN: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; MARICO: 75, NESTLEIND: 75, UNITDSPR: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-4.7%) • sector strength 35/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +0.0%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.2%) • sector strength 53/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27733,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27748,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27763,7 +27763,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -27772,33 +27772,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27823,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="History" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Market" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,13 +25,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,12 +53,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,12 +437,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TODAY</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -444,7 +456,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -512,7 +524,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -637,12 +649,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -688,7 +700,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-20  /  2026-07-20</t>
+          <t>2026-07-17  /  2026-07-17</t>
         </is>
       </c>
     </row>
@@ -724,7 +736,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rs5L</t>
+          <t>Rs1L</t>
         </is>
       </c>
     </row>
@@ -736,7 +748,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs300,000 (60%)</t>
+          <t>Rs60,000 (60%)</t>
         </is>
       </c>
     </row>
@@ -748,7 +760,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs200,000 (40%)</t>
+          <t>Rs40,000 (40%)</t>
         </is>
       </c>
     </row>
@@ -760,7 +772,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -804,7 +816,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs512,500</t>
+          <t>Rs102,500</t>
         </is>
       </c>
     </row>
@@ -816,7 +828,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rs602,000</t>
+          <t>Rs120,400</t>
         </is>
       </c>
     </row>
@@ -828,7 +840,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rs458,000</t>
+          <t>Rs91,600</t>
         </is>
       </c>
     </row>
@@ -896,7 +908,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
+          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -908,7 +920,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -920,7 +932,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1148,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
+          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -1365,142 +1377,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Portfolio Suitability</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Suitability Breakdown</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Top Factor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Weakest Factor</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>F: Historical</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>F: Technical/Trend</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>F: Risk/Vol</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>F: Sector</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>F: Regime</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Buy Range</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Expected Range (hist)</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Prob +ve</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Rec Confidence %</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Selected Because</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Not Evaluated</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Why This vs Alternatives</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1534,13 +1546,13 @@
         <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
         <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1568,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8868</v>
+        <v>8848.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8660 - 9076</t>
+          <t>8639 - 9058</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1590,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+15.3%)</t>
+          <t>Above 200-DMA (+15.1%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1603,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35472</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1620,7 +1632,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+15.3%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+15.1%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1643,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Trend/Tech +19 · Historical +18 · Regime +9 · Sector +9 = 79</t>
+          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +9 = 78</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,13 +1664,13 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H3" t="n">
         <v>97</v>
       </c>
       <c r="I3" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1686,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1940.7</v>
+        <v>1940.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1888 - 1994</t>
+          <t>1887 - 1994</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1704,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.4%)</t>
+          <t>Above 200-DMA (+10.5%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1721,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>21348</v>
+        <v>3881</v>
       </c>
       <c r="W3" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1745,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; TORNTPHARM: 84, ABBOTINDIA: 79, ALKEM: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 78; TORNTPHARM: 83, ABBOTINDIA: 78, ALKEM: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.4%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.5%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1782,7 @@
         <v>61</v>
       </c>
       <c r="G4" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H4" t="n">
         <v>99</v>
@@ -1792,11 +1804,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>844</v>
+        <v>830.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>824 - 864</t>
+          <t>811 - 850</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1826,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.0%)</t>
+          <t>Above 200-DMA (+8.3%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1839,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>29540</v>
+        <v>5812</v>
       </c>
       <c r="W4" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1863,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 75; NESTLEIND: 75, UNITDSPR: 65, TATACONSUM: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 75; NESTLEIND: 75, UNITDSPR: 65, HINDUNILVR: 59</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+10.0%) • outperforming Nifty • sector strength 53/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.3%) • outperforming Nifty • sector strength 53/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
         </is>
       </c>
     </row>
@@ -1888,13 +1900,13 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H5" t="n">
         <v>99</v>
       </c>
       <c r="I5" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1922,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2456.8</v>
+        <v>2447</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2395 - 2518</t>
+          <t>2386 - 2508</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1944,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.7%)</t>
+          <t>Above 200-DMA (+11.4%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1957,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>24568</v>
+        <v>4894</v>
       </c>
       <c r="W5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1981,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 75; TORNTPHARM: 84, ABBOTINDIA: 79, SUNPHARMA: 79. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 75; TORNTPHARM: 83, ABBOTINDIA: 78, SUNPHARMA: 78. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.7%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1997,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +8 = 73</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +4 = 74</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,58 +2015,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H6" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1931.2</v>
+        <v>1435.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1877 - 1985</t>
+          <t>1394 - 1476</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.0%)</t>
+          <t>Above 200-DMA (+6.7%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2075,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>23174</v>
+        <v>2870</v>
       </c>
       <c r="W6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>8.300000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2099,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 73; INDUSTOWER: 60, TATACOMM: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 74; FEDERALBNK: 70, SBIN: 65, LICI: 64</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-1.0%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.7%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2119,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +15 · Regime +9 · Sector +4 = 72</t>
+          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +7 = 72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,58 +2133,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="H7" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I7" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1444.5</v>
+        <v>1910.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1403 - 1486</t>
+          <t>1858 - 1964</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>-3% to +15%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.3%)</t>
+          <t>Below 200-DMA (-2.1%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2193,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>18778</v>
+        <v>3822</v>
       </c>
       <c r="W7" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>6.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2217,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 72; FEDERALBNK: 66, SBIN: 65, LICI: 64</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 72; INDUSTOWER: 58, TATACOMM: 53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.1%) • sector strength 71/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2233,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 70</t>
+          <t>Risk/Vol +22 · Trend/Tech +17 · Historical +14 · Regime +9 · Sector +6 = 68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2254,13 @@
         <v>45</v>
       </c>
       <c r="G8" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H8" t="n">
         <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2276,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1567</v>
+        <v>1564.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1518 - 1616</t>
+          <t>1515 - 1614</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2298,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.9%)</t>
+          <t>Above 200-DMA (+6.7%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2311,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>21938</v>
+        <v>4694</v>
       </c>
       <c r="W8" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,27 +2335,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, BALRAMCHIN: 61, SRF: 60</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; NAVINFLUOR: 61, BALRAMCHIN: 60, DEEPAKNTR: 59</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+6.9%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+6.7%) • outperforming Nifty • sector strength 65/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +2 = 65</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2372,13 @@
         <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
         <v>96</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2394,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>346.2</v>
+        <v>341.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>337 - 356</t>
+          <t>332 - 351</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2416,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.0%)</t>
+          <t>Below 200-DMA (-4.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2429,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>24580</v>
+        <v>3417</v>
       </c>
       <c r="W9" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="X9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2453,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 63, POWERGRID: 56, TATAPOWER: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 57, NHPC: 55, TATAPOWER: 53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-3.0%) • sector strength 24/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.2%) • sector strength 29/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2500,11 +2512,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1335</v>
+        <v>1321.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1295 - 1375</t>
+          <t>1282 - 1360</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2534,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.6%)</t>
+          <t>Below 200-DMA (-6.6%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2547,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>20025</v>
+        <v>3964</v>
       </c>
       <c r="W10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="X10" t="n">
-        <v>6.7</v>
+        <v>8.5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2571,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 59; GAIL: 60, IOC: 48, IGL: 46. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 59; GAIL: 60, IOC: 48, ONGC: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-5.6%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-6.6%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2608,7 @@
         <v>54</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H11" t="n">
         <v>93</v>
@@ -2618,11 +2630,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1822</v>
+        <v>1812.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1768 - 1876</t>
+          <t>1759 - 1867</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2652,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.1%)</t>
+          <t>Below 200-DMA (-5.6%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2665,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>16398</v>
+        <v>3625</v>
       </c>
       <c r="W11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2689,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBILIFE: 58; ICICIBANK: 72, FEDERALBNK: 66, SBIN: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBILIFE: 58; ICICIBANK: 74, FEDERALBNK: 70, SBIN: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.1%) • sector strength 35/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +0.0%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.6%) • sector strength 35/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +0.0%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2705,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +2 = 56</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +3 = 57</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2720,7 +2732,7 @@
         <v>93</v>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2736,11 +2748,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>285</v>
+        <v>282.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>276 - 294</t>
+          <t>274 - 291</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2766,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.4%)</t>
+          <t>Below 200-DMA (-1.2%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2783,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>24225</v>
+        <v>3108</v>
       </c>
       <c r="W12" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="X12" t="n">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2807,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 65, NHPC: 63, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 64, NHPC: 55, TATAPOWER: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.4%) • sector strength 24/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-1.2%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2844,7 @@
         <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
         <v>98</v>
@@ -2854,11 +2866,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>280.5</v>
+        <v>279.6</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>273 - 288</t>
+          <t>272 - 287</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2888,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.2%)</t>
+          <t>Below 200-DMA (-17.6%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2901,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>31696</v>
+        <v>5872</v>
       </c>
       <c r="W13" t="n">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="X13" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2918,7 +2930,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.2%) • sector strength 53/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.6%) • sector strength 53/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2937,77 +2949,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Start Rs</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>End Rs</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Year Ret %</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Beat Nifty</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Cycles</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Win %</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Losers</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Avg Return %</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Median %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Best %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Worst %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
         </is>
@@ -3018,10 +3030,10 @@
         <v>2021</v>
       </c>
       <c r="B2" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C2" t="n">
-        <v>542732</v>
+        <v>108546</v>
       </c>
       <c r="D2" t="n">
         <v>8.5</v>
@@ -3059,7 +3071,7 @@
         <v>-14.9</v>
       </c>
       <c r="O2" t="n">
-        <v>43738</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="3">
@@ -3067,10 +3079,10 @@
         <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C3" t="n">
-        <v>600703</v>
+        <v>120141</v>
       </c>
       <c r="D3" t="n">
         <v>20.1</v>
@@ -3108,7 +3120,7 @@
         <v>-19.8</v>
       </c>
       <c r="O3" t="n">
-        <v>93560</v>
+        <v>19532</v>
       </c>
     </row>
     <row r="4">
@@ -3116,10 +3128,10 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C4" t="n">
-        <v>722531</v>
+        <v>144506</v>
       </c>
       <c r="D4" t="n">
         <v>44.5</v>
@@ -3157,7 +3169,7 @@
         <v>-16.5</v>
       </c>
       <c r="O4" t="n">
-        <v>176947</v>
+        <v>30402</v>
       </c>
     </row>
     <row r="5">
@@ -3165,10 +3177,10 @@
         <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C5" t="n">
-        <v>551527</v>
+        <v>110305</v>
       </c>
       <c r="D5" t="n">
         <v>10.3</v>
@@ -3206,7 +3218,7 @@
         <v>-26</v>
       </c>
       <c r="O5" t="n">
-        <v>56158</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="6">
@@ -3214,10 +3226,10 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C6" t="n">
-        <v>531876</v>
+        <v>106375</v>
       </c>
       <c r="D6" t="n">
         <v>6.4</v>
@@ -3255,7 +3267,7 @@
         <v>-23.6</v>
       </c>
       <c r="O6" t="n">
-        <v>15954</v>
+        <v>157</v>
       </c>
     </row>
     <row r="7">
@@ -3263,10 +3275,10 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C7" t="n">
-        <v>504000</v>
+        <v>100800</v>
       </c>
       <c r="D7" t="n">
         <v>0.8</v>
@@ -3304,7 +3316,7 @@
         <v>-16.7</v>
       </c>
       <c r="O7" t="n">
-        <v>7126</v>
+        <v>1322</v>
       </c>
     </row>
   </sheetData>
@@ -3322,107 +3334,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Rec ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Buy Price</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Invested Rs</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Exit Value Rs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Contribution %</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Max Profit %</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Max Loss %</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Captured %</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CAGR %</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Rank in Universe</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Why Picked</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3456,16 +3468,16 @@
         <v>22031.2</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>66945</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>88125</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>21180</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>31.64</v>
@@ -3537,16 +3549,16 @@
         <v>4737.4</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>32560</v>
+        <v>3618</v>
       </c>
       <c r="I3" t="n">
-        <v>42637</v>
+        <v>4737</v>
       </c>
       <c r="J3" t="n">
-        <v>10077</v>
+        <v>1120</v>
       </c>
       <c r="K3" t="n">
         <v>30.95</v>
@@ -3618,16 +3630,16 @@
         <v>675.9</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>16725</v>
+        <v>3136</v>
       </c>
       <c r="I4" t="n">
-        <v>21629</v>
+        <v>4055</v>
       </c>
       <c r="J4" t="n">
-        <v>4904</v>
+        <v>920</v>
       </c>
       <c r="K4" t="n">
         <v>29.32</v>
@@ -3699,16 +3711,16 @@
         <v>3990.05</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>32195</v>
+        <v>6439</v>
       </c>
       <c r="I5" t="n">
-        <v>39900</v>
+        <v>7980</v>
       </c>
       <c r="J5" t="n">
-        <v>7706</v>
+        <v>1541</v>
       </c>
       <c r="K5" t="n">
         <v>23.93</v>
@@ -3780,16 +3792,16 @@
         <v>1834.7</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>19162</v>
+        <v>3194</v>
       </c>
       <c r="I6" t="n">
-        <v>22016</v>
+        <v>3669</v>
       </c>
       <c r="J6" t="n">
-        <v>2854</v>
+        <v>476</v>
       </c>
       <c r="K6" t="n">
         <v>14.89</v>
@@ -3861,16 +3873,16 @@
         <v>3730.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>20049</v>
+        <v>3342</v>
       </c>
       <c r="I7" t="n">
-        <v>22381</v>
+        <v>3730</v>
       </c>
       <c r="J7" t="n">
-        <v>2332</v>
+        <v>389</v>
       </c>
       <c r="K7" t="n">
         <v>11.63</v>
@@ -3942,16 +3954,16 @@
         <v>1208.63</v>
       </c>
       <c r="G8" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>20607</v>
+        <v>3254</v>
       </c>
       <c r="I8" t="n">
-        <v>22964</v>
+        <v>3626</v>
       </c>
       <c r="J8" t="n">
-        <v>2357</v>
+        <v>372</v>
       </c>
       <c r="K8" t="n">
         <v>11.44</v>
@@ -4023,16 +4035,16 @@
         <v>3921.1</v>
       </c>
       <c r="G9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>39554</v>
+        <v>7192</v>
       </c>
       <c r="I9" t="n">
-        <v>43132</v>
+        <v>7842</v>
       </c>
       <c r="J9" t="n">
-        <v>3578</v>
+        <v>651</v>
       </c>
       <c r="K9" t="n">
         <v>9.050000000000001</v>
@@ -4104,16 +4116,16 @@
         <v>9740.799999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>35809</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>38963</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3154</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>8.81</v>
@@ -4185,16 +4197,16 @@
         <v>2321.6</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>34794</v>
+        <v>6524</v>
       </c>
       <c r="I11" t="n">
-        <v>37146</v>
+        <v>6965</v>
       </c>
       <c r="J11" t="n">
-        <v>2351</v>
+        <v>441</v>
       </c>
       <c r="K11" t="n">
         <v>6.76</v>
@@ -4266,16 +4278,16 @@
         <v>1665.15</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>20285</v>
+        <v>3121</v>
       </c>
       <c r="I12" t="n">
-        <v>21647</v>
+        <v>3330</v>
       </c>
       <c r="J12" t="n">
-        <v>1362</v>
+        <v>210</v>
       </c>
       <c r="K12" t="n">
         <v>6.71</v>
@@ -4347,16 +4359,16 @@
         <v>729.45</v>
       </c>
       <c r="G13" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
-        <v>34973</v>
+        <v>6858</v>
       </c>
       <c r="I13" t="n">
-        <v>37202</v>
+        <v>7294</v>
       </c>
       <c r="J13" t="n">
-        <v>2229</v>
+        <v>437</v>
       </c>
       <c r="K13" t="n">
         <v>6.37</v>
@@ -4428,16 +4440,16 @@
         <v>1687.8</v>
       </c>
       <c r="G14" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>58079</v>
+        <v>10249</v>
       </c>
       <c r="I14" t="n">
-        <v>57385</v>
+        <v>10127</v>
       </c>
       <c r="J14" t="n">
-        <v>-694</v>
+        <v>-122</v>
       </c>
       <c r="K14" t="n">
         <v>-1.19</v>
@@ -4509,16 +4521,16 @@
         <v>178.85</v>
       </c>
       <c r="G15" t="n">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>20373</v>
+        <v>4002</v>
       </c>
       <c r="I15" t="n">
-        <v>20031</v>
+        <v>3935</v>
       </c>
       <c r="J15" t="n">
-        <v>-342</v>
+        <v>-67</v>
       </c>
       <c r="K15" t="n">
         <v>-1.68</v>
@@ -4590,16 +4602,16 @@
         <v>1928.9</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>29596</v>
+        <v>4228</v>
       </c>
       <c r="I16" t="n">
-        <v>27005</v>
+        <v>3858</v>
       </c>
       <c r="J16" t="n">
-        <v>-2591</v>
+        <v>-370</v>
       </c>
       <c r="K16" t="n">
         <v>-8.76</v>
@@ -4671,16 +4683,16 @@
         <v>1898.45</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>31638</v>
+        <v>4995</v>
       </c>
       <c r="I17" t="n">
-        <v>36071</v>
+        <v>5695</v>
       </c>
       <c r="J17" t="n">
-        <v>4433</v>
+        <v>700</v>
       </c>
       <c r="K17" t="n">
         <v>14.01</v>
@@ -4752,16 +4764,16 @@
         <v>30.95</v>
       </c>
       <c r="G18" t="n">
-        <v>799</v>
+        <v>159</v>
       </c>
       <c r="H18" t="n">
-        <v>22692</v>
+        <v>4516</v>
       </c>
       <c r="I18" t="n">
-        <v>24729</v>
+        <v>4921</v>
       </c>
       <c r="J18" t="n">
-        <v>2037</v>
+        <v>405</v>
       </c>
       <c r="K18" t="n">
         <v>8.98</v>
@@ -4833,16 +4845,16 @@
         <v>31.2</v>
       </c>
       <c r="G19" t="n">
-        <v>714</v>
+        <v>142</v>
       </c>
       <c r="H19" t="n">
-        <v>20777</v>
+        <v>4132</v>
       </c>
       <c r="I19" t="n">
-        <v>22277</v>
+        <v>4430</v>
       </c>
       <c r="J19" t="n">
-        <v>1499</v>
+        <v>298</v>
       </c>
       <c r="K19" t="n">
         <v>7.22</v>
@@ -4914,16 +4926,16 @@
         <v>1626.05</v>
       </c>
       <c r="G20" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>41588</v>
+        <v>7701</v>
       </c>
       <c r="I20" t="n">
-        <v>43903</v>
+        <v>8130</v>
       </c>
       <c r="J20" t="n">
-        <v>2316</v>
+        <v>429</v>
       </c>
       <c r="K20" t="n">
         <v>5.57</v>
@@ -4995,16 +5007,16 @@
         <v>1236.98</v>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H21" t="n">
-        <v>30216</v>
+        <v>6043</v>
       </c>
       <c r="I21" t="n">
-        <v>30924</v>
+        <v>6185</v>
       </c>
       <c r="J21" t="n">
-        <v>709</v>
+        <v>142</v>
       </c>
       <c r="K21" t="n">
         <v>2.35</v>
@@ -5076,16 +5088,16 @@
         <v>3817.75</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>26111</v>
+        <v>3730</v>
       </c>
       <c r="I22" t="n">
-        <v>26724</v>
+        <v>3818</v>
       </c>
       <c r="J22" t="n">
-        <v>613</v>
+        <v>88</v>
       </c>
       <c r="K22" t="n">
         <v>2.35</v>
@@ -5157,16 +5169,16 @@
         <v>1209.4</v>
       </c>
       <c r="G23" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H23" t="n">
-        <v>35062</v>
+        <v>6045</v>
       </c>
       <c r="I23" t="n">
-        <v>35073</v>
+        <v>6047</v>
       </c>
       <c r="J23" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>0.03</v>
@@ -5238,16 +5250,16 @@
         <v>1091.18</v>
       </c>
       <c r="G24" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>35513</v>
+        <v>6873</v>
       </c>
       <c r="I24" t="n">
-        <v>33827</v>
+        <v>6547</v>
       </c>
       <c r="J24" t="n">
-        <v>-1686</v>
+        <v>-326</v>
       </c>
       <c r="K24" t="n">
         <v>-4.75</v>
@@ -5319,16 +5331,16 @@
         <v>9043.200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>19482</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>18086</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-1395</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>-7.16</v>
@@ -5400,16 +5412,16 @@
         <v>3617.55</v>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>47053</v>
+        <v>7842</v>
       </c>
       <c r="I26" t="n">
-        <v>43411</v>
+        <v>7235</v>
       </c>
       <c r="J26" t="n">
-        <v>-3643</v>
+        <v>-607</v>
       </c>
       <c r="K26" t="n">
         <v>-7.74</v>
@@ -5481,16 +5493,16 @@
         <v>650.5</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>36472</v>
+        <v>7294</v>
       </c>
       <c r="I27" t="n">
-        <v>32525</v>
+        <v>6505</v>
       </c>
       <c r="J27" t="n">
-        <v>-3948</v>
+        <v>-790</v>
       </c>
       <c r="K27" t="n">
         <v>-10.82</v>
@@ -5562,16 +5574,16 @@
         <v>1917.45</v>
       </c>
       <c r="G28" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
-        <v>37067</v>
+        <v>6541</v>
       </c>
       <c r="I28" t="n">
-        <v>32597</v>
+        <v>5752</v>
       </c>
       <c r="J28" t="n">
-        <v>-4470</v>
+        <v>-789</v>
       </c>
       <c r="K28" t="n">
         <v>-12.06</v>
@@ -5637,16 +5649,16 @@
         <v>2476.6</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>25632</v>
+        <v>2848</v>
       </c>
       <c r="I29" t="n">
-        <v>22289</v>
+        <v>2477</v>
       </c>
       <c r="J29" t="n">
-        <v>-3342</v>
+        <v>-371</v>
       </c>
       <c r="K29" t="n">
         <v>-13.04</v>
@@ -5718,16 +5730,16 @@
         <v>1463.8</v>
       </c>
       <c r="G30" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
-        <v>43883</v>
+        <v>8439</v>
       </c>
       <c r="I30" t="n">
-        <v>38059</v>
+        <v>7319</v>
       </c>
       <c r="J30" t="n">
-        <v>-5824</v>
+        <v>-1120</v>
       </c>
       <c r="K30" t="n">
         <v>-13.27</v>
@@ -5799,16 +5811,16 @@
         <v>3277.1</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>26968</v>
+        <v>3853</v>
       </c>
       <c r="I31" t="n">
-        <v>22940</v>
+        <v>3277</v>
       </c>
       <c r="J31" t="n">
-        <v>-4028</v>
+        <v>-576</v>
       </c>
       <c r="K31" t="n">
         <v>-14.94</v>
@@ -5880,16 +5892,16 @@
         <v>3809.7</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>19663</v>
+        <v>3277</v>
       </c>
       <c r="I32" t="n">
-        <v>22858</v>
+        <v>3810</v>
       </c>
       <c r="J32" t="n">
-        <v>3196</v>
+        <v>533</v>
       </c>
       <c r="K32" t="n">
         <v>16.25</v>
@@ -5961,16 +5973,16 @@
         <v>1586.7</v>
       </c>
       <c r="G33" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>62943</v>
+        <v>11710</v>
       </c>
       <c r="I33" t="n">
-        <v>68228</v>
+        <v>12694</v>
       </c>
       <c r="J33" t="n">
-        <v>5285</v>
+        <v>983</v>
       </c>
       <c r="K33" t="n">
         <v>8.4</v>
@@ -6042,16 +6054,16 @@
         <v>804.13</v>
       </c>
       <c r="G34" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>43310</v>
+        <v>8358</v>
       </c>
       <c r="I34" t="n">
-        <v>45835</v>
+        <v>8845</v>
       </c>
       <c r="J34" t="n">
-        <v>2525</v>
+        <v>487</v>
       </c>
       <c r="K34" t="n">
         <v>5.83</v>
@@ -6123,16 +6135,16 @@
         <v>1253.83</v>
       </c>
       <c r="G35" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>44531</v>
+        <v>8659</v>
       </c>
       <c r="I35" t="n">
-        <v>45138</v>
+        <v>8777</v>
       </c>
       <c r="J35" t="n">
-        <v>607</v>
+        <v>118</v>
       </c>
       <c r="K35" t="n">
         <v>1.36</v>
@@ -6204,16 +6216,16 @@
         <v>3814.8</v>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>34360</v>
+        <v>3818</v>
       </c>
       <c r="I36" t="n">
-        <v>34333</v>
+        <v>3815</v>
       </c>
       <c r="J36" t="n">
-        <v>-27</v>
+        <v>-3</v>
       </c>
       <c r="K36" t="n">
         <v>-0.08</v>
@@ -6285,16 +6297,16 @@
         <v>1861.1</v>
       </c>
       <c r="G37" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>36071</v>
+        <v>5695</v>
       </c>
       <c r="I37" t="n">
-        <v>35361</v>
+        <v>5583</v>
       </c>
       <c r="J37" t="n">
-        <v>-710</v>
+        <v>-112</v>
       </c>
       <c r="K37" t="n">
         <v>-1.97</v>
@@ -6366,16 +6378,16 @@
         <v>1836.05</v>
       </c>
       <c r="G38" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
-        <v>23074</v>
+        <v>3846</v>
       </c>
       <c r="I38" t="n">
-        <v>22033</v>
+        <v>3672</v>
       </c>
       <c r="J38" t="n">
-        <v>-1042</v>
+        <v>-174</v>
       </c>
       <c r="K38" t="n">
         <v>-4.51</v>
@@ -6447,16 +6459,16 @@
         <v>828.65</v>
       </c>
       <c r="G39" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>21024</v>
+        <v>3504</v>
       </c>
       <c r="I39" t="n">
-        <v>19888</v>
+        <v>3315</v>
       </c>
       <c r="J39" t="n">
-        <v>-1136</v>
+        <v>-189</v>
       </c>
       <c r="K39" t="n">
         <v>-5.41</v>
@@ -6528,16 +6540,16 @@
         <v>2332.25</v>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>22289</v>
+        <v>2477</v>
       </c>
       <c r="I40" t="n">
-        <v>20990</v>
+        <v>2332</v>
       </c>
       <c r="J40" t="n">
-        <v>-1299</v>
+        <v>-144</v>
       </c>
       <c r="K40" t="n">
         <v>-5.83</v>
@@ -6690,16 +6702,16 @@
         <v>1701.8</v>
       </c>
       <c r="G42" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>37115</v>
+        <v>7423</v>
       </c>
       <c r="I42" t="n">
-        <v>34036</v>
+        <v>6807</v>
       </c>
       <c r="J42" t="n">
-        <v>-3079</v>
+        <v>-616</v>
       </c>
       <c r="K42" t="n">
         <v>-8.300000000000001</v>
@@ -6771,16 +6783,16 @@
         <v>901.16</v>
       </c>
       <c r="G43" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>45259</v>
+        <v>8855</v>
       </c>
       <c r="I43" t="n">
-        <v>41453</v>
+        <v>8110</v>
       </c>
       <c r="J43" t="n">
-        <v>-3806</v>
+        <v>-745</v>
       </c>
       <c r="K43" t="n">
         <v>-8.41</v>
@@ -6852,16 +6864,16 @@
         <v>199.6</v>
       </c>
       <c r="G44" t="n">
-        <v>167</v>
+        <v>33</v>
       </c>
       <c r="H44" t="n">
-        <v>36540</v>
+        <v>7220</v>
       </c>
       <c r="I44" t="n">
-        <v>33333</v>
+        <v>6587</v>
       </c>
       <c r="J44" t="n">
-        <v>-3206</v>
+        <v>-634</v>
       </c>
       <c r="K44" t="n">
         <v>-8.779999999999999</v>
@@ -6933,16 +6945,16 @@
         <v>569.65</v>
       </c>
       <c r="G45" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>24068</v>
+        <v>4554</v>
       </c>
       <c r="I45" t="n">
-        <v>21077</v>
+        <v>3988</v>
       </c>
       <c r="J45" t="n">
-        <v>-2991</v>
+        <v>-566</v>
       </c>
       <c r="K45" t="n">
         <v>-12.43</v>
@@ -7014,16 +7026,16 @@
         <v>6726.15</v>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>15448</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>13452</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>-1996</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>-12.92</v>
@@ -7095,16 +7107,16 @@
         <v>2350.15</v>
       </c>
       <c r="G47" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>39141</v>
+        <v>6807</v>
       </c>
       <c r="I47" t="n">
-        <v>54053</v>
+        <v>9401</v>
       </c>
       <c r="J47" t="n">
-        <v>14912</v>
+        <v>2593</v>
       </c>
       <c r="K47" t="n">
         <v>38.1</v>
@@ -7176,16 +7188,16 @@
         <v>979.3</v>
       </c>
       <c r="G48" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H48" t="n">
-        <v>27194</v>
+        <v>4944</v>
       </c>
       <c r="I48" t="n">
-        <v>32317</v>
+        <v>5876</v>
       </c>
       <c r="J48" t="n">
-        <v>5123</v>
+        <v>932</v>
       </c>
       <c r="K48" t="n">
         <v>18.84</v>
@@ -7257,16 +7269,16 @@
         <v>220.95</v>
       </c>
       <c r="G49" t="n">
-        <v>132</v>
+        <v>26</v>
       </c>
       <c r="H49" t="n">
-        <v>26347</v>
+        <v>5190</v>
       </c>
       <c r="I49" t="n">
-        <v>29165</v>
+        <v>5745</v>
       </c>
       <c r="J49" t="n">
-        <v>2818</v>
+        <v>555</v>
       </c>
       <c r="K49" t="n">
         <v>10.7</v>
@@ -7419,16 +7431,16 @@
         <v>919.4400000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>49564</v>
+        <v>9913</v>
       </c>
       <c r="I51" t="n">
-        <v>50569</v>
+        <v>10114</v>
       </c>
       <c r="J51" t="n">
-        <v>1005</v>
+        <v>201</v>
       </c>
       <c r="K51" t="n">
         <v>2.03</v>
@@ -7500,16 +7512,16 @@
         <v>878</v>
       </c>
       <c r="G52" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H52" t="n">
-        <v>28577</v>
+        <v>5196</v>
       </c>
       <c r="I52" t="n">
-        <v>28974</v>
+        <v>5268</v>
       </c>
       <c r="J52" t="n">
-        <v>397</v>
+        <v>72</v>
       </c>
       <c r="K52" t="n">
         <v>1.39</v>
@@ -7581,16 +7593,16 @@
         <v>3773.05</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>22858</v>
+        <v>3810</v>
       </c>
       <c r="I53" t="n">
-        <v>22638</v>
+        <v>3773</v>
       </c>
       <c r="J53" t="n">
-        <v>-220</v>
+        <v>-37</v>
       </c>
       <c r="K53" t="n">
         <v>-0.96</v>
@@ -7662,16 +7674,16 @@
         <v>1569.15</v>
       </c>
       <c r="G54" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H54" t="n">
-        <v>39668</v>
+        <v>7934</v>
       </c>
       <c r="I54" t="n">
-        <v>39229</v>
+        <v>7846</v>
       </c>
       <c r="J54" t="n">
-        <v>-439</v>
+        <v>-88</v>
       </c>
       <c r="K54" t="n">
         <v>-1.11</v>
@@ -7743,16 +7755,16 @@
         <v>1232.25</v>
       </c>
       <c r="G55" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>24333</v>
+        <v>4056</v>
       </c>
       <c r="I55" t="n">
-        <v>22180</v>
+        <v>3697</v>
       </c>
       <c r="J55" t="n">
-        <v>-2153</v>
+        <v>-359</v>
       </c>
       <c r="K55" t="n">
         <v>-8.85</v>
@@ -7824,16 +7836,16 @@
         <v>693.95</v>
       </c>
       <c r="G56" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H56" t="n">
-        <v>39863</v>
+        <v>7666</v>
       </c>
       <c r="I56" t="n">
-        <v>36085</v>
+        <v>6940</v>
       </c>
       <c r="J56" t="n">
-        <v>-3778</v>
+        <v>-726</v>
       </c>
       <c r="K56" t="n">
         <v>-9.48</v>
@@ -7905,16 +7917,16 @@
         <v>837.7</v>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H57" t="n">
-        <v>27873</v>
+        <v>5575</v>
       </c>
       <c r="I57" t="n">
-        <v>25131</v>
+        <v>5026</v>
       </c>
       <c r="J57" t="n">
-        <v>-2742</v>
+        <v>-548</v>
       </c>
       <c r="K57" t="n">
         <v>-9.84</v>
@@ -7986,16 +7998,16 @@
         <v>19.95</v>
       </c>
       <c r="G58" t="n">
-        <v>1790</v>
+        <v>358</v>
       </c>
       <c r="H58" t="n">
-        <v>39648</v>
+        <v>7930</v>
       </c>
       <c r="I58" t="n">
-        <v>35710</v>
+        <v>7142</v>
       </c>
       <c r="J58" t="n">
-        <v>-3938</v>
+        <v>-788</v>
       </c>
       <c r="K58" t="n">
         <v>-9.93</v>
@@ -8067,16 +8079,16 @@
         <v>3260.75</v>
       </c>
       <c r="G59" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>38148</v>
+        <v>7630</v>
       </c>
       <c r="I59" t="n">
-        <v>32608</v>
+        <v>6522</v>
       </c>
       <c r="J59" t="n">
-        <v>-5540</v>
+        <v>-1108</v>
       </c>
       <c r="K59" t="n">
         <v>-14.52</v>
@@ -8146,16 +8158,16 @@
         <v>1556.15</v>
       </c>
       <c r="G60" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H60" t="n">
-        <v>23869</v>
+        <v>3672</v>
       </c>
       <c r="I60" t="n">
-        <v>20230</v>
+        <v>3112</v>
       </c>
       <c r="J60" t="n">
-        <v>-3639</v>
+        <v>-560</v>
       </c>
       <c r="K60" t="n">
         <v>-15.24</v>
@@ -8227,16 +8239,16 @@
         <v>1491.65</v>
       </c>
       <c r="G61" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
-        <v>31639</v>
+        <v>5583</v>
       </c>
       <c r="I61" t="n">
-        <v>25358</v>
+        <v>4475</v>
       </c>
       <c r="J61" t="n">
-        <v>-6281</v>
+        <v>-1108</v>
       </c>
       <c r="K61" t="n">
         <v>-19.85</v>
@@ -8306,16 +8318,16 @@
         <v>32.7</v>
       </c>
       <c r="G62" t="n">
-        <v>819</v>
+        <v>163</v>
       </c>
       <c r="H62" t="n">
-        <v>22195</v>
+        <v>4417</v>
       </c>
       <c r="I62" t="n">
-        <v>26781</v>
+        <v>5330</v>
       </c>
       <c r="J62" t="n">
-        <v>4586</v>
+        <v>913</v>
       </c>
       <c r="K62" t="n">
         <v>20.66</v>
@@ -8387,16 +8399,16 @@
         <v>793.1</v>
       </c>
       <c r="G63" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H63" t="n">
-        <v>24982</v>
+        <v>4858</v>
       </c>
       <c r="I63" t="n">
-        <v>28552</v>
+        <v>5552</v>
       </c>
       <c r="J63" t="n">
-        <v>3569</v>
+        <v>694</v>
       </c>
       <c r="K63" t="n">
         <v>14.29</v>
@@ -8468,16 +8480,16 @@
         <v>955.15</v>
       </c>
       <c r="G64" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H64" t="n">
-        <v>35183</v>
+        <v>6702</v>
       </c>
       <c r="I64" t="n">
-        <v>40116</v>
+        <v>7641</v>
       </c>
       <c r="J64" t="n">
-        <v>4933</v>
+        <v>940</v>
       </c>
       <c r="K64" t="n">
         <v>14.02</v>
@@ -8549,16 +8561,16 @@
         <v>2014.85</v>
       </c>
       <c r="G65" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H65" t="n">
-        <v>44299</v>
+        <v>8860</v>
       </c>
       <c r="I65" t="n">
-        <v>50371</v>
+        <v>10074</v>
       </c>
       <c r="J65" t="n">
-        <v>6072</v>
+        <v>1214</v>
       </c>
       <c r="K65" t="n">
         <v>13.71</v>
@@ -8711,16 +8723,16 @@
         <v>1238.75</v>
       </c>
       <c r="G67" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H67" t="n">
-        <v>29804</v>
+        <v>5519</v>
       </c>
       <c r="I67" t="n">
-        <v>33446</v>
+        <v>6194</v>
       </c>
       <c r="J67" t="n">
-        <v>3642</v>
+        <v>674</v>
       </c>
       <c r="K67" t="n">
         <v>12.22</v>
@@ -8792,16 +8804,16 @@
         <v>157.2</v>
       </c>
       <c r="G68" t="n">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="H68" t="n">
-        <v>16023</v>
+        <v>3120</v>
       </c>
       <c r="I68" t="n">
-        <v>17764</v>
+        <v>3458</v>
       </c>
       <c r="J68" t="n">
-        <v>1740</v>
+        <v>339</v>
       </c>
       <c r="K68" t="n">
         <v>10.86</v>
@@ -8873,16 +8885,16 @@
         <v>21.35</v>
       </c>
       <c r="G69" t="n">
-        <v>1809</v>
+        <v>361</v>
       </c>
       <c r="H69" t="n">
-        <v>36090</v>
+        <v>7202</v>
       </c>
       <c r="I69" t="n">
-        <v>38622</v>
+        <v>7707</v>
       </c>
       <c r="J69" t="n">
-        <v>2533</v>
+        <v>505</v>
       </c>
       <c r="K69" t="n">
         <v>7.02</v>
@@ -8954,16 +8966,16 @@
         <v>966.05</v>
       </c>
       <c r="G70" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H70" t="n">
-        <v>42294</v>
+        <v>8275</v>
       </c>
       <c r="I70" t="n">
-        <v>44438</v>
+        <v>8694</v>
       </c>
       <c r="J70" t="n">
-        <v>2144</v>
+        <v>419</v>
       </c>
       <c r="K70" t="n">
         <v>5.07</v>
@@ -9035,16 +9047,16 @@
         <v>3200.3</v>
       </c>
       <c r="G71" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H71" t="n">
-        <v>58483</v>
+        <v>9234</v>
       </c>
       <c r="I71" t="n">
-        <v>60806</v>
+        <v>9601</v>
       </c>
       <c r="J71" t="n">
-        <v>2323</v>
+        <v>367</v>
       </c>
       <c r="K71" t="n">
         <v>3.97</v>
@@ -9116,16 +9128,16 @@
         <v>1010.7</v>
       </c>
       <c r="G72" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H72" t="n">
-        <v>26453</v>
+        <v>4899</v>
       </c>
       <c r="I72" t="n">
-        <v>27289</v>
+        <v>5054</v>
       </c>
       <c r="J72" t="n">
-        <v>836</v>
+        <v>155</v>
       </c>
       <c r="K72" t="n">
         <v>3.16</v>
@@ -9197,16 +9209,16 @@
         <v>1581.2</v>
       </c>
       <c r="G73" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H73" t="n">
-        <v>45505</v>
+        <v>7846</v>
       </c>
       <c r="I73" t="n">
-        <v>45855</v>
+        <v>7906</v>
       </c>
       <c r="J73" t="n">
-        <v>349</v>
+        <v>60</v>
       </c>
       <c r="K73" t="n">
         <v>0.77</v>
@@ -9278,16 +9290,16 @@
         <v>157.05</v>
       </c>
       <c r="G74" t="n">
-        <v>248</v>
+        <v>49</v>
       </c>
       <c r="H74" t="n">
-        <v>39144</v>
+        <v>7734</v>
       </c>
       <c r="I74" t="n">
-        <v>38948</v>
+        <v>7695</v>
       </c>
       <c r="J74" t="n">
-        <v>-196</v>
+        <v>-39</v>
       </c>
       <c r="K74" t="n">
         <v>-0.5</v>
@@ -9359,16 +9371,16 @@
         <v>83.95999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>243</v>
+        <v>48</v>
       </c>
       <c r="H75" t="n">
-        <v>20723</v>
+        <v>4093</v>
       </c>
       <c r="I75" t="n">
-        <v>20402</v>
+        <v>4030</v>
       </c>
       <c r="J75" t="n">
-        <v>-321</v>
+        <v>-63</v>
       </c>
       <c r="K75" t="n">
         <v>-1.55</v>
@@ -9440,16 +9452,16 @@
         <v>3064.9</v>
       </c>
       <c r="G76" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>22825</v>
+        <v>3261</v>
       </c>
       <c r="I76" t="n">
-        <v>21454</v>
+        <v>3065</v>
       </c>
       <c r="J76" t="n">
-        <v>-1371</v>
+        <v>-196</v>
       </c>
       <c r="K76" t="n">
         <v>-6.01</v>
@@ -9521,16 +9533,16 @@
         <v>72.45</v>
       </c>
       <c r="G77" t="n">
-        <v>712</v>
+        <v>142</v>
       </c>
       <c r="H77" t="n">
-        <v>25632</v>
+        <v>5112</v>
       </c>
       <c r="I77" t="n">
-        <v>51584</v>
+        <v>10288</v>
       </c>
       <c r="J77" t="n">
-        <v>25952</v>
+        <v>5176</v>
       </c>
       <c r="K77" t="n">
         <v>101.25</v>
@@ -9602,16 +9614,16 @@
         <v>32.7</v>
       </c>
       <c r="G78" t="n">
-        <v>2850</v>
+        <v>570</v>
       </c>
       <c r="H78" t="n">
-        <v>60848</v>
+        <v>12170</v>
       </c>
       <c r="I78" t="n">
-        <v>93195</v>
+        <v>18639</v>
       </c>
       <c r="J78" t="n">
-        <v>32348</v>
+        <v>6470</v>
       </c>
       <c r="K78" t="n">
         <v>53.16</v>
@@ -9683,16 +9695,16 @@
         <v>125.72</v>
       </c>
       <c r="G79" t="n">
-        <v>378</v>
+        <v>75</v>
       </c>
       <c r="H79" t="n">
-        <v>31737</v>
+        <v>6297</v>
       </c>
       <c r="I79" t="n">
-        <v>47522</v>
+        <v>9429</v>
       </c>
       <c r="J79" t="n">
-        <v>15785</v>
+        <v>3132</v>
       </c>
       <c r="K79" t="n">
         <v>49.74</v>
@@ -9764,16 +9776,16 @@
         <v>80.05</v>
       </c>
       <c r="G80" t="n">
-        <v>429</v>
+        <v>85</v>
       </c>
       <c r="H80" t="n">
-        <v>28936</v>
+        <v>5733</v>
       </c>
       <c r="I80" t="n">
-        <v>34341</v>
+        <v>6804</v>
       </c>
       <c r="J80" t="n">
-        <v>5405</v>
+        <v>1071</v>
       </c>
       <c r="K80" t="n">
         <v>18.68</v>
@@ -9845,16 +9857,16 @@
         <v>1032.8</v>
       </c>
       <c r="G81" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H81" t="n">
-        <v>23942</v>
+        <v>4788</v>
       </c>
       <c r="I81" t="n">
-        <v>25820</v>
+        <v>5164</v>
       </c>
       <c r="J81" t="n">
-        <v>1878</v>
+        <v>376</v>
       </c>
       <c r="K81" t="n">
         <v>7.84</v>
@@ -9926,16 +9938,16 @@
         <v>34.45</v>
       </c>
       <c r="G82" t="n">
-        <v>1134</v>
+        <v>226</v>
       </c>
       <c r="H82" t="n">
-        <v>37082</v>
+        <v>7390</v>
       </c>
       <c r="I82" t="n">
-        <v>39066</v>
+        <v>7786</v>
       </c>
       <c r="J82" t="n">
-        <v>1984</v>
+        <v>396</v>
       </c>
       <c r="K82" t="n">
         <v>5.35</v>
@@ -10007,16 +10019,16 @@
         <v>994.27</v>
       </c>
       <c r="G83" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H83" t="n">
-        <v>35744</v>
+        <v>6762</v>
       </c>
       <c r="I83" t="n">
-        <v>36788</v>
+        <v>6960</v>
       </c>
       <c r="J83" t="n">
-        <v>1044</v>
+        <v>198</v>
       </c>
       <c r="K83" t="n">
         <v>2.92</v>
@@ -10088,16 +10100,16 @@
         <v>3642.25</v>
       </c>
       <c r="G84" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>28828</v>
+        <v>3604</v>
       </c>
       <c r="I84" t="n">
-        <v>29138</v>
+        <v>3642</v>
       </c>
       <c r="J84" t="n">
-        <v>310</v>
+        <v>39</v>
       </c>
       <c r="K84" t="n">
         <v>1.07</v>
@@ -10169,16 +10181,16 @@
         <v>796</v>
       </c>
       <c r="G85" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H85" t="n">
-        <v>26172</v>
+        <v>4759</v>
       </c>
       <c r="I85" t="n">
-        <v>26268</v>
+        <v>4776</v>
       </c>
       <c r="J85" t="n">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="K85" t="n">
         <v>0.37</v>
@@ -10250,16 +10262,16 @@
         <v>293.56</v>
       </c>
       <c r="G86" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="H86" t="n">
-        <v>38055</v>
+        <v>7611</v>
       </c>
       <c r="I86" t="n">
-        <v>38163</v>
+        <v>7633</v>
       </c>
       <c r="J86" t="n">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="K86" t="n">
         <v>0.28</v>
@@ -10331,16 +10343,16 @@
         <v>854.35</v>
       </c>
       <c r="G87" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>28011</v>
+        <v>5252</v>
       </c>
       <c r="I87" t="n">
-        <v>27339</v>
+        <v>5126</v>
       </c>
       <c r="J87" t="n">
-        <v>-671</v>
+        <v>-126</v>
       </c>
       <c r="K87" t="n">
         <v>-2.4</v>
@@ -10412,16 +10424,16 @@
         <v>1261.15</v>
       </c>
       <c r="G88" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H88" t="n">
-        <v>29289</v>
+        <v>5325</v>
       </c>
       <c r="I88" t="n">
-        <v>27745</v>
+        <v>5045</v>
       </c>
       <c r="J88" t="n">
-        <v>-1543</v>
+        <v>-281</v>
       </c>
       <c r="K88" t="n">
         <v>-5.27</v>
@@ -10493,16 +10505,16 @@
         <v>3031.35</v>
       </c>
       <c r="G89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H89" t="n">
-        <v>44804</v>
+        <v>6401</v>
       </c>
       <c r="I89" t="n">
-        <v>42439</v>
+        <v>6063</v>
       </c>
       <c r="J89" t="n">
-        <v>-2365</v>
+        <v>-338</v>
       </c>
       <c r="K89" t="n">
         <v>-5.28</v>
@@ -10574,16 +10586,16 @@
         <v>896.4</v>
       </c>
       <c r="G90" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H90" t="n">
-        <v>29310</v>
+        <v>5054</v>
       </c>
       <c r="I90" t="n">
-        <v>25996</v>
+        <v>4482</v>
       </c>
       <c r="J90" t="n">
-        <v>-3315</v>
+        <v>-572</v>
       </c>
       <c r="K90" t="n">
         <v>-11.31</v>
@@ -10653,16 +10665,16 @@
         <v>7829.05</v>
       </c>
       <c r="G91" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>17801</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>15658</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>-2143</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
         <v>-12.04</v>
@@ -10732,16 +10744,16 @@
         <v>350.46</v>
       </c>
       <c r="G92" t="n">
-        <v>112</v>
+        <v>22</v>
       </c>
       <c r="H92" t="n">
-        <v>32879</v>
+        <v>6458</v>
       </c>
       <c r="I92" t="n">
-        <v>39252</v>
+        <v>7710</v>
       </c>
       <c r="J92" t="n">
-        <v>6373</v>
+        <v>1252</v>
       </c>
       <c r="K92" t="n">
         <v>19.38</v>
@@ -10813,16 +10825,16 @@
         <v>4286</v>
       </c>
       <c r="G93" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>32780</v>
+        <v>3642</v>
       </c>
       <c r="I93" t="n">
-        <v>38574</v>
+        <v>4286</v>
       </c>
       <c r="J93" t="n">
-        <v>5794</v>
+        <v>644</v>
       </c>
       <c r="K93" t="n">
         <v>17.67</v>
@@ -10894,16 +10906,16 @@
         <v>3312.5</v>
       </c>
       <c r="G94" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
-        <v>32959</v>
+        <v>5993</v>
       </c>
       <c r="I94" t="n">
-        <v>36438</v>
+        <v>6625</v>
       </c>
       <c r="J94" t="n">
-        <v>3478</v>
+        <v>632</v>
       </c>
       <c r="K94" t="n">
         <v>10.55</v>
@@ -10975,16 +10987,16 @@
         <v>3340.6</v>
       </c>
       <c r="G95" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H95" t="n">
-        <v>48502</v>
+        <v>9094</v>
       </c>
       <c r="I95" t="n">
-        <v>53450</v>
+        <v>10022</v>
       </c>
       <c r="J95" t="n">
-        <v>4948</v>
+        <v>928</v>
       </c>
       <c r="K95" t="n">
         <v>10.2</v>
@@ -11056,16 +11068,16 @@
         <v>2288.5</v>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>18779</v>
+        <v>2087</v>
       </c>
       <c r="I96" t="n">
-        <v>20596</v>
+        <v>2288</v>
       </c>
       <c r="J96" t="n">
-        <v>1818</v>
+        <v>202</v>
       </c>
       <c r="K96" t="n">
         <v>9.68</v>
@@ -11137,16 +11149,16 @@
         <v>231.45</v>
       </c>
       <c r="G97" t="n">
-        <v>163</v>
+        <v>32</v>
       </c>
       <c r="H97" t="n">
-        <v>35518</v>
+        <v>6973</v>
       </c>
       <c r="I97" t="n">
-        <v>37726</v>
+        <v>7406</v>
       </c>
       <c r="J97" t="n">
-        <v>2209</v>
+        <v>434</v>
       </c>
       <c r="K97" t="n">
         <v>6.22</v>
@@ -11218,16 +11230,16 @@
         <v>842.45</v>
       </c>
       <c r="G98" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H98" t="n">
-        <v>19930</v>
+        <v>3986</v>
       </c>
       <c r="I98" t="n">
-        <v>21061</v>
+        <v>4212</v>
       </c>
       <c r="J98" t="n">
-        <v>1131</v>
+        <v>226</v>
       </c>
       <c r="K98" t="n">
         <v>5.68</v>
@@ -11299,16 +11311,16 @@
         <v>1587.65</v>
       </c>
       <c r="G99" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H99" t="n">
-        <v>51034</v>
+        <v>9279</v>
       </c>
       <c r="I99" t="n">
-        <v>52392</v>
+        <v>9526</v>
       </c>
       <c r="J99" t="n">
-        <v>1358</v>
+        <v>247</v>
       </c>
       <c r="K99" t="n">
         <v>2.66</v>
@@ -11380,16 +11392,16 @@
         <v>890.15</v>
       </c>
       <c r="G100" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H100" t="n">
-        <v>22623</v>
+        <v>4350</v>
       </c>
       <c r="I100" t="n">
-        <v>23144</v>
+        <v>4451</v>
       </c>
       <c r="J100" t="n">
-        <v>521</v>
+        <v>100</v>
       </c>
       <c r="K100" t="n">
         <v>2.3</v>
@@ -11461,16 +11473,16 @@
         <v>3241.65</v>
       </c>
       <c r="G101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>19269</v>
+        <v>3212</v>
       </c>
       <c r="I101" t="n">
-        <v>19450</v>
+        <v>3242</v>
       </c>
       <c r="J101" t="n">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="K101" t="n">
         <v>0.9399999999999999</v>
@@ -11542,16 +11554,16 @@
         <v>78</v>
       </c>
       <c r="G102" t="n">
-        <v>435</v>
+        <v>87</v>
       </c>
       <c r="H102" t="n">
-        <v>34822</v>
+        <v>6964</v>
       </c>
       <c r="I102" t="n">
-        <v>33930</v>
+        <v>6786</v>
       </c>
       <c r="J102" t="n">
-        <v>-892</v>
+        <v>-178</v>
       </c>
       <c r="K102" t="n">
         <v>-2.56</v>
@@ -11623,16 +11635,16 @@
         <v>771.1</v>
       </c>
       <c r="G103" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="H103" t="n">
-        <v>34228</v>
+        <v>6368</v>
       </c>
       <c r="I103" t="n">
-        <v>33157</v>
+        <v>6169</v>
       </c>
       <c r="J103" t="n">
-        <v>-1071</v>
+        <v>-199</v>
       </c>
       <c r="K103" t="n">
         <v>-3.13</v>
@@ -11704,16 +11716,16 @@
         <v>1173.9</v>
       </c>
       <c r="G104" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H104" t="n">
-        <v>35312</v>
+        <v>6306</v>
       </c>
       <c r="I104" t="n">
-        <v>32869</v>
+        <v>5870</v>
       </c>
       <c r="J104" t="n">
-        <v>-2443</v>
+        <v>-436</v>
       </c>
       <c r="K104" t="n">
         <v>-6.92</v>
@@ -11785,16 +11797,16 @@
         <v>813.95</v>
       </c>
       <c r="G105" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="H105" t="n">
-        <v>40338</v>
+        <v>8068</v>
       </c>
       <c r="I105" t="n">
-        <v>36628</v>
+        <v>7326</v>
       </c>
       <c r="J105" t="n">
-        <v>-3710</v>
+        <v>-742</v>
       </c>
       <c r="K105" t="n">
         <v>-9.199999999999999</v>
@@ -11866,16 +11878,16 @@
         <v>1383.75</v>
       </c>
       <c r="G106" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>31493</v>
+        <v>4973</v>
       </c>
       <c r="I106" t="n">
-        <v>26291</v>
+        <v>4151</v>
       </c>
       <c r="J106" t="n">
-        <v>-5202</v>
+        <v>-821</v>
       </c>
       <c r="K106" t="n">
         <v>-16.52</v>
@@ -11947,16 +11959,16 @@
         <v>1356</v>
       </c>
       <c r="G107" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H107" t="n">
-        <v>33816</v>
+        <v>6545</v>
       </c>
       <c r="I107" t="n">
-        <v>42036</v>
+        <v>8136</v>
       </c>
       <c r="J107" t="n">
-        <v>8220</v>
+        <v>1591</v>
       </c>
       <c r="K107" t="n">
         <v>24.31</v>
@@ -12028,16 +12040,16 @@
         <v>3400</v>
       </c>
       <c r="G108" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>25081</v>
+        <v>2787</v>
       </c>
       <c r="I108" t="n">
-        <v>30600</v>
+        <v>3400</v>
       </c>
       <c r="J108" t="n">
-        <v>5519</v>
+        <v>613</v>
       </c>
       <c r="K108" t="n">
         <v>22.01</v>
@@ -12109,16 +12121,16 @@
         <v>1934.6</v>
       </c>
       <c r="G109" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>33341</v>
+        <v>6351</v>
       </c>
       <c r="I109" t="n">
-        <v>40627</v>
+        <v>7738</v>
       </c>
       <c r="J109" t="n">
-        <v>7286</v>
+        <v>1388</v>
       </c>
       <c r="K109" t="n">
         <v>21.85</v>
@@ -12190,16 +12202,16 @@
         <v>1659</v>
       </c>
       <c r="G110" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H110" t="n">
-        <v>34815</v>
+        <v>6963</v>
       </c>
       <c r="I110" t="n">
-        <v>41475</v>
+        <v>8295</v>
       </c>
       <c r="J110" t="n">
-        <v>6660</v>
+        <v>1332</v>
       </c>
       <c r="K110" t="n">
         <v>19.13</v>
@@ -12271,16 +12283,16 @@
         <v>837</v>
       </c>
       <c r="G111" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="H111" t="n">
-        <v>37357</v>
+        <v>7184</v>
       </c>
       <c r="I111" t="n">
-        <v>43524</v>
+        <v>8370</v>
       </c>
       <c r="J111" t="n">
-        <v>6167</v>
+        <v>1186</v>
       </c>
       <c r="K111" t="n">
         <v>16.51</v>
@@ -12352,16 +12364,16 @@
         <v>1809.7</v>
       </c>
       <c r="G112" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H112" t="n">
-        <v>42030</v>
+        <v>7783</v>
       </c>
       <c r="I112" t="n">
-        <v>48862</v>
+        <v>9048</v>
       </c>
       <c r="J112" t="n">
-        <v>6832</v>
+        <v>1265</v>
       </c>
       <c r="K112" t="n">
         <v>16.26</v>
@@ -12433,16 +12445,16 @@
         <v>3842.8</v>
       </c>
       <c r="G113" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H113" t="n">
-        <v>33125</v>
+        <v>6625</v>
       </c>
       <c r="I113" t="n">
-        <v>38428</v>
+        <v>7686</v>
       </c>
       <c r="J113" t="n">
-        <v>5303</v>
+        <v>1061</v>
       </c>
       <c r="K113" t="n">
         <v>16.01</v>
@@ -12514,16 +12526,16 @@
         <v>884.95</v>
       </c>
       <c r="G114" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H114" t="n">
-        <v>26988</v>
+        <v>5398</v>
       </c>
       <c r="I114" t="n">
-        <v>30973</v>
+        <v>6195</v>
       </c>
       <c r="J114" t="n">
-        <v>3985</v>
+        <v>797</v>
       </c>
       <c r="K114" t="n">
         <v>14.76</v>
@@ -12595,16 +12607,16 @@
         <v>9671</v>
       </c>
       <c r="G115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>25863</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>29013</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>3150</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
         <v>12.18</v>
@@ -12676,16 +12688,16 @@
         <v>1309.5</v>
       </c>
       <c r="G116" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H116" t="n">
-        <v>35217</v>
+        <v>7043</v>
       </c>
       <c r="I116" t="n">
-        <v>39285</v>
+        <v>7857</v>
       </c>
       <c r="J116" t="n">
-        <v>4068</v>
+        <v>814</v>
       </c>
       <c r="K116" t="n">
         <v>11.55</v>
@@ -12757,16 +12769,16 @@
         <v>188.3</v>
       </c>
       <c r="G117" t="n">
-        <v>164</v>
+        <v>32</v>
       </c>
       <c r="H117" t="n">
-        <v>28831</v>
+        <v>5626</v>
       </c>
       <c r="I117" t="n">
-        <v>30881</v>
+        <v>6026</v>
       </c>
       <c r="J117" t="n">
-        <v>2050</v>
+        <v>400</v>
       </c>
       <c r="K117" t="n">
         <v>7.11</v>
@@ -12838,16 +12850,16 @@
         <v>197.38</v>
       </c>
       <c r="G118" t="n">
-        <v>159</v>
+        <v>31</v>
       </c>
       <c r="H118" t="n">
-        <v>29587</v>
+        <v>5768</v>
       </c>
       <c r="I118" t="n">
-        <v>31383</v>
+        <v>6119</v>
       </c>
       <c r="J118" t="n">
-        <v>1797</v>
+        <v>350</v>
       </c>
       <c r="K118" t="n">
         <v>6.07</v>
@@ -12919,16 +12931,16 @@
         <v>1075</v>
       </c>
       <c r="G119" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H119" t="n">
-        <v>32534</v>
+        <v>6100</v>
       </c>
       <c r="I119" t="n">
-        <v>34400</v>
+        <v>6450</v>
       </c>
       <c r="J119" t="n">
-        <v>1866</v>
+        <v>350</v>
       </c>
       <c r="K119" t="n">
         <v>5.73</v>
@@ -13000,16 +13012,16 @@
         <v>1752.76</v>
       </c>
       <c r="G120" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H120" t="n">
-        <v>30790</v>
+        <v>5132</v>
       </c>
       <c r="I120" t="n">
-        <v>31550</v>
+        <v>5258</v>
       </c>
       <c r="J120" t="n">
-        <v>759</v>
+        <v>127</v>
       </c>
       <c r="K120" t="n">
         <v>2.47</v>
@@ -13081,16 +13093,16 @@
         <v>374</v>
       </c>
       <c r="G121" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="H121" t="n">
-        <v>39094</v>
+        <v>7745</v>
       </c>
       <c r="I121" t="n">
-        <v>39644</v>
+        <v>7854</v>
       </c>
       <c r="J121" t="n">
-        <v>550</v>
+        <v>109</v>
       </c>
       <c r="K121" t="n">
         <v>1.41</v>
@@ -13162,16 +13174,16 @@
         <v>242.05</v>
       </c>
       <c r="G122" t="n">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="H122" t="n">
-        <v>42368</v>
+        <v>8474</v>
       </c>
       <c r="I122" t="n">
-        <v>54461</v>
+        <v>10892</v>
       </c>
       <c r="J122" t="n">
-        <v>12094</v>
+        <v>2419</v>
       </c>
       <c r="K122" t="n">
         <v>28.54</v>
@@ -13243,16 +13255,16 @@
         <v>3186.25</v>
       </c>
       <c r="G123" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H123" t="n">
-        <v>51020</v>
+        <v>10204</v>
       </c>
       <c r="I123" t="n">
-        <v>63725</v>
+        <v>12745</v>
       </c>
       <c r="J123" t="n">
-        <v>12705</v>
+        <v>2541</v>
       </c>
       <c r="K123" t="n">
         <v>24.9</v>
@@ -13324,16 +13336,16 @@
         <v>2041.65</v>
       </c>
       <c r="G124" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H124" t="n">
-        <v>32575</v>
+        <v>5429</v>
       </c>
       <c r="I124" t="n">
-        <v>36750</v>
+        <v>6125</v>
       </c>
       <c r="J124" t="n">
-        <v>4175</v>
+        <v>696</v>
       </c>
       <c r="K124" t="n">
         <v>12.82</v>
@@ -13405,16 +13417,16 @@
         <v>1974.67</v>
       </c>
       <c r="G125" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H125" t="n">
-        <v>35055</v>
+        <v>7011</v>
       </c>
       <c r="I125" t="n">
-        <v>39493</v>
+        <v>7899</v>
       </c>
       <c r="J125" t="n">
-        <v>4438</v>
+        <v>888</v>
       </c>
       <c r="K125" t="n">
         <v>12.66</v>
@@ -13486,16 +13498,16 @@
         <v>10727.55</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>19342</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>21455</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>2113</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
         <v>10.92</v>
@@ -13567,16 +13579,16 @@
         <v>954.2</v>
       </c>
       <c r="G127" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H127" t="n">
-        <v>44248</v>
+        <v>8850</v>
       </c>
       <c r="I127" t="n">
-        <v>47710</v>
+        <v>9542</v>
       </c>
       <c r="J127" t="n">
-        <v>3462</v>
+        <v>692</v>
       </c>
       <c r="K127" t="n">
         <v>7.83</v>
@@ -13729,16 +13741,16 @@
         <v>3570.85</v>
       </c>
       <c r="G129" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>26754</v>
+        <v>3344</v>
       </c>
       <c r="I129" t="n">
-        <v>28567</v>
+        <v>3571</v>
       </c>
       <c r="J129" t="n">
-        <v>1813</v>
+        <v>227</v>
       </c>
       <c r="K129" t="n">
         <v>6.78</v>
@@ -13810,16 +13822,16 @@
         <v>1145.3</v>
       </c>
       <c r="G130" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="H130" t="n">
-        <v>38700</v>
+        <v>7525</v>
       </c>
       <c r="I130" t="n">
-        <v>41231</v>
+        <v>8017</v>
       </c>
       <c r="J130" t="n">
-        <v>2531</v>
+        <v>492</v>
       </c>
       <c r="K130" t="n">
         <v>6.54</v>
@@ -13891,16 +13903,16 @@
         <v>205.53</v>
       </c>
       <c r="G131" t="n">
-        <v>176</v>
+        <v>35</v>
       </c>
       <c r="H131" t="n">
-        <v>34739</v>
+        <v>6908</v>
       </c>
       <c r="I131" t="n">
-        <v>36173</v>
+        <v>7194</v>
       </c>
       <c r="J131" t="n">
-        <v>1434</v>
+        <v>285</v>
       </c>
       <c r="K131" t="n">
         <v>4.13</v>
@@ -13972,16 +13984,16 @@
         <v>1177.72</v>
       </c>
       <c r="G132" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H132" t="n">
-        <v>23962</v>
+        <v>4564</v>
       </c>
       <c r="I132" t="n">
-        <v>24732</v>
+        <v>4711</v>
       </c>
       <c r="J132" t="n">
-        <v>770</v>
+        <v>147</v>
       </c>
       <c r="K132" t="n">
         <v>3.21</v>
@@ -14053,16 +14065,16 @@
         <v>951.3</v>
       </c>
       <c r="G133" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H133" t="n">
-        <v>37304</v>
+        <v>6696</v>
       </c>
       <c r="I133" t="n">
-        <v>37101</v>
+        <v>6659</v>
       </c>
       <c r="J133" t="n">
-        <v>-203</v>
+        <v>-36</v>
       </c>
       <c r="K133" t="n">
         <v>-0.54</v>
@@ -14134,16 +14146,16 @@
         <v>1624.85</v>
       </c>
       <c r="G134" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H134" t="n">
-        <v>26544</v>
+        <v>4977</v>
       </c>
       <c r="I134" t="n">
-        <v>25998</v>
+        <v>4875</v>
       </c>
       <c r="J134" t="n">
-        <v>-546</v>
+        <v>-102</v>
       </c>
       <c r="K134" t="n">
         <v>-2.06</v>
@@ -14215,16 +14227,16 @@
         <v>1230.03</v>
       </c>
       <c r="G135" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H135" t="n">
-        <v>23571</v>
+        <v>3928</v>
       </c>
       <c r="I135" t="n">
-        <v>22141</v>
+        <v>3690</v>
       </c>
       <c r="J135" t="n">
-        <v>-1430</v>
+        <v>-238</v>
       </c>
       <c r="K135" t="n">
         <v>-6.07</v>
@@ -14296,16 +14308,16 @@
         <v>3148.8</v>
       </c>
       <c r="G136" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>20400</v>
+        <v>3400</v>
       </c>
       <c r="I136" t="n">
-        <v>18893</v>
+        <v>3149</v>
       </c>
       <c r="J136" t="n">
-        <v>-1507</v>
+        <v>-251</v>
       </c>
       <c r="K136" t="n">
         <v>-7.39</v>
@@ -14377,16 +14389,16 @@
         <v>427.4</v>
       </c>
       <c r="G137" t="n">
-        <v>129</v>
+        <v>25</v>
       </c>
       <c r="H137" t="n">
-        <v>40936</v>
+        <v>7933</v>
       </c>
       <c r="I137" t="n">
-        <v>55135</v>
+        <v>10685</v>
       </c>
       <c r="J137" t="n">
-        <v>14199</v>
+        <v>2752</v>
       </c>
       <c r="K137" t="n">
         <v>34.69</v>
@@ -14539,16 +14551,16 @@
         <v>9954.549999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>33476</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>39818</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>6342</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
         <v>18.95</v>
@@ -14620,16 +14632,16 @@
         <v>1394.13</v>
       </c>
       <c r="G140" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H140" t="n">
-        <v>29366</v>
+        <v>5873</v>
       </c>
       <c r="I140" t="n">
-        <v>34853</v>
+        <v>6971</v>
       </c>
       <c r="J140" t="n">
-        <v>5487</v>
+        <v>1097</v>
       </c>
       <c r="K140" t="n">
         <v>18.68</v>
@@ -14701,16 +14713,16 @@
         <v>26210.45</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>22307</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>26210</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>3903</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
         <v>17.5</v>
@@ -14782,16 +14794,16 @@
         <v>1329.35</v>
       </c>
       <c r="G142" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H142" t="n">
-        <v>35504</v>
+        <v>6872</v>
       </c>
       <c r="I142" t="n">
-        <v>41210</v>
+        <v>7976</v>
       </c>
       <c r="J142" t="n">
-        <v>5706</v>
+        <v>1104</v>
       </c>
       <c r="K142" t="n">
         <v>16.07</v>
@@ -14863,16 +14875,16 @@
         <v>1102.4</v>
       </c>
       <c r="G143" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H143" t="n">
-        <v>36260</v>
+        <v>6679</v>
       </c>
       <c r="I143" t="n">
-        <v>41891</v>
+        <v>7717</v>
       </c>
       <c r="J143" t="n">
-        <v>5632</v>
+        <v>1037</v>
       </c>
       <c r="K143" t="n">
         <v>15.53</v>
@@ -14944,16 +14956,16 @@
         <v>3758.85</v>
       </c>
       <c r="G144" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H144" t="n">
-        <v>32838</v>
+        <v>6568</v>
       </c>
       <c r="I144" t="n">
-        <v>37588</v>
+        <v>7518</v>
       </c>
       <c r="J144" t="n">
-        <v>4751</v>
+        <v>950</v>
       </c>
       <c r="K144" t="n">
         <v>14.47</v>
@@ -15025,16 +15037,16 @@
         <v>1377.13</v>
       </c>
       <c r="G145" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H145" t="n">
-        <v>25831</v>
+        <v>4920</v>
       </c>
       <c r="I145" t="n">
-        <v>28920</v>
+        <v>5509</v>
       </c>
       <c r="J145" t="n">
-        <v>3089</v>
+        <v>588</v>
       </c>
       <c r="K145" t="n">
         <v>11.96</v>
@@ -15106,16 +15118,16 @@
         <v>3903.8</v>
       </c>
       <c r="G146" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>28567</v>
+        <v>3571</v>
       </c>
       <c r="I146" t="n">
-        <v>31230</v>
+        <v>3904</v>
       </c>
       <c r="J146" t="n">
-        <v>2664</v>
+        <v>333</v>
       </c>
       <c r="K146" t="n">
         <v>9.32</v>
@@ -15187,16 +15199,16 @@
         <v>1273.78</v>
       </c>
       <c r="G147" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H147" t="n">
-        <v>29443</v>
+        <v>5889</v>
       </c>
       <c r="I147" t="n">
-        <v>31844</v>
+        <v>6369</v>
       </c>
       <c r="J147" t="n">
-        <v>2402</v>
+        <v>480</v>
       </c>
       <c r="K147" t="n">
         <v>8.16</v>
@@ -15268,16 +15280,16 @@
         <v>1009.85</v>
       </c>
       <c r="G148" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="H148" t="n">
-        <v>39955</v>
+        <v>7610</v>
       </c>
       <c r="I148" t="n">
-        <v>42414</v>
+        <v>8079</v>
       </c>
       <c r="J148" t="n">
-        <v>2459</v>
+        <v>468</v>
       </c>
       <c r="K148" t="n">
         <v>6.15</v>
@@ -15349,16 +15361,16 @@
         <v>3273.9</v>
       </c>
       <c r="G149" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>25190</v>
+        <v>3149</v>
       </c>
       <c r="I149" t="n">
-        <v>26191</v>
+        <v>3274</v>
       </c>
       <c r="J149" t="n">
-        <v>1001</v>
+        <v>125</v>
       </c>
       <c r="K149" t="n">
         <v>3.97</v>
@@ -15430,16 +15442,16 @@
         <v>2573.2</v>
       </c>
       <c r="G150" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H150" t="n">
-        <v>28264</v>
+        <v>5139</v>
       </c>
       <c r="I150" t="n">
-        <v>28305</v>
+        <v>5146</v>
       </c>
       <c r="J150" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K150" t="n">
         <v>0.15</v>
@@ -15511,16 +15523,16 @@
         <v>10086.9</v>
       </c>
       <c r="G151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>21455</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>20174</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>-1281</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>-5.97</v>
@@ -15592,16 +15604,16 @@
         <v>404.95</v>
       </c>
       <c r="G152" t="n">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="H152" t="n">
-        <v>23810</v>
+        <v>4504</v>
       </c>
       <c r="I152" t="n">
-        <v>29966</v>
+        <v>5669</v>
       </c>
       <c r="J152" t="n">
-        <v>6157</v>
+        <v>1165</v>
       </c>
       <c r="K152" t="n">
         <v>25.86</v>
@@ -15673,16 +15685,16 @@
         <v>12405</v>
       </c>
       <c r="G153" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>40348</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>49620</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>9272</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
         <v>22.98</v>
@@ -15754,16 +15766,16 @@
         <v>1265.75</v>
       </c>
       <c r="G154" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="H154" t="n">
-        <v>26458</v>
+        <v>4410</v>
       </c>
       <c r="I154" t="n">
-        <v>30378</v>
+        <v>5063</v>
       </c>
       <c r="J154" t="n">
-        <v>3920</v>
+        <v>653</v>
       </c>
       <c r="K154" t="n">
         <v>14.82</v>
@@ -15835,16 +15847,16 @@
         <v>1516.4</v>
       </c>
       <c r="G155" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H155" t="n">
-        <v>29246</v>
+        <v>5317</v>
       </c>
       <c r="I155" t="n">
-        <v>33361</v>
+        <v>6066</v>
       </c>
       <c r="J155" t="n">
-        <v>4115</v>
+        <v>748</v>
       </c>
       <c r="K155" t="n">
         <v>14.07</v>
@@ -15916,16 +15928,16 @@
         <v>2226.05</v>
       </c>
       <c r="G156" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H156" t="n">
-        <v>23111</v>
+        <v>4202</v>
       </c>
       <c r="I156" t="n">
-        <v>24487</v>
+        <v>4452</v>
       </c>
       <c r="J156" t="n">
-        <v>1376</v>
+        <v>250</v>
       </c>
       <c r="K156" t="n">
         <v>5.95</v>
@@ -15997,16 +16009,16 @@
         <v>1464.33</v>
       </c>
       <c r="G157" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H157" t="n">
-        <v>27883</v>
+        <v>5577</v>
       </c>
       <c r="I157" t="n">
-        <v>29287</v>
+        <v>5857</v>
       </c>
       <c r="J157" t="n">
-        <v>1404</v>
+        <v>281</v>
       </c>
       <c r="K157" t="n">
         <v>5.04</v>
@@ -16078,16 +16090,16 @@
         <v>1055.45</v>
       </c>
       <c r="G158" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H158" t="n">
-        <v>28276</v>
+        <v>5049</v>
       </c>
       <c r="I158" t="n">
-        <v>29553</v>
+        <v>5277</v>
       </c>
       <c r="J158" t="n">
-        <v>1277</v>
+        <v>228</v>
       </c>
       <c r="K158" t="n">
         <v>4.52</v>
@@ -16159,16 +16171,16 @@
         <v>3862</v>
       </c>
       <c r="G159" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H159" t="n">
-        <v>31230</v>
+        <v>3904</v>
       </c>
       <c r="I159" t="n">
-        <v>30896</v>
+        <v>3862</v>
       </c>
       <c r="J159" t="n">
-        <v>-334</v>
+        <v>-42</v>
       </c>
       <c r="K159" t="n">
         <v>-1.07</v>
@@ -16240,16 +16252,16 @@
         <v>1638.25</v>
       </c>
       <c r="G160" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H160" t="n">
-        <v>46497</v>
+        <v>8610</v>
       </c>
       <c r="I160" t="n">
-        <v>44233</v>
+        <v>8191</v>
       </c>
       <c r="J160" t="n">
-        <v>-2264</v>
+        <v>-419</v>
       </c>
       <c r="K160" t="n">
         <v>-4.87</v>
@@ -16396,16 +16408,16 @@
         <v>3525.1</v>
       </c>
       <c r="G162" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H162" t="n">
-        <v>37588</v>
+        <v>7518</v>
       </c>
       <c r="I162" t="n">
-        <v>35251</v>
+        <v>7050</v>
       </c>
       <c r="J162" t="n">
-        <v>-2338</v>
+        <v>-468</v>
       </c>
       <c r="K162" t="n">
         <v>-6.22</v>
@@ -16477,16 +16489,16 @@
         <v>4695</v>
       </c>
       <c r="G163" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>31064</v>
+        <v>5177</v>
       </c>
       <c r="I163" t="n">
-        <v>28170</v>
+        <v>4695</v>
       </c>
       <c r="J163" t="n">
-        <v>-2894</v>
+        <v>-482</v>
       </c>
       <c r="K163" t="n">
         <v>-9.32</v>
@@ -16558,16 +16570,16 @@
         <v>747.35</v>
       </c>
       <c r="G164" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H164" t="n">
-        <v>28438</v>
+        <v>5018</v>
       </c>
       <c r="I164" t="n">
-        <v>25410</v>
+        <v>4484</v>
       </c>
       <c r="J164" t="n">
-        <v>-3028</v>
+        <v>-534</v>
       </c>
       <c r="K164" t="n">
         <v>-10.65</v>
@@ -16639,16 +16651,16 @@
         <v>2214.8</v>
       </c>
       <c r="G165" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H165" t="n">
-        <v>41171</v>
+        <v>7720</v>
       </c>
       <c r="I165" t="n">
-        <v>35437</v>
+        <v>6644</v>
       </c>
       <c r="J165" t="n">
-        <v>-5734</v>
+        <v>-1075</v>
       </c>
       <c r="K165" t="n">
         <v>-13.93</v>
@@ -16718,16 +16730,16 @@
         <v>2807.7</v>
       </c>
       <c r="G166" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H166" t="n">
-        <v>32739</v>
+        <v>6548</v>
       </c>
       <c r="I166" t="n">
-        <v>28077</v>
+        <v>5615</v>
       </c>
       <c r="J166" t="n">
-        <v>-4662</v>
+        <v>-932</v>
       </c>
       <c r="K166" t="n">
         <v>-14.24</v>
@@ -16799,16 +16811,16 @@
         <v>2743</v>
       </c>
       <c r="G167" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>20034</v>
+        <v>2226</v>
       </c>
       <c r="I167" t="n">
-        <v>24687</v>
+        <v>2743</v>
       </c>
       <c r="J167" t="n">
-        <v>4653</v>
+        <v>517</v>
       </c>
       <c r="K167" t="n">
         <v>23.22</v>
@@ -16880,16 +16892,16 @@
         <v>2727</v>
       </c>
       <c r="G168" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H168" t="n">
-        <v>35437</v>
+        <v>6644</v>
       </c>
       <c r="I168" t="n">
-        <v>43632</v>
+        <v>8181</v>
       </c>
       <c r="J168" t="n">
-        <v>8195</v>
+        <v>1537</v>
       </c>
       <c r="K168" t="n">
         <v>23.13</v>
@@ -16961,16 +16973,16 @@
         <v>11258.3</v>
       </c>
       <c r="G169" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>18766</v>
+        <v>0</v>
       </c>
       <c r="I169" t="n">
-        <v>22517</v>
+        <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>3751</v>
+        <v>0</v>
       </c>
       <c r="K169" t="n">
         <v>19.99</v>
@@ -17042,16 +17054,16 @@
         <v>1248.65</v>
       </c>
       <c r="G170" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H170" t="n">
-        <v>24275</v>
+        <v>4222</v>
       </c>
       <c r="I170" t="n">
-        <v>28719</v>
+        <v>4995</v>
       </c>
       <c r="J170" t="n">
-        <v>4444</v>
+        <v>773</v>
       </c>
       <c r="K170" t="n">
         <v>18.3</v>
@@ -17123,16 +17135,16 @@
         <v>1926.85</v>
       </c>
       <c r="G171" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H171" t="n">
-        <v>44233</v>
+        <v>8191</v>
       </c>
       <c r="I171" t="n">
-        <v>52025</v>
+        <v>9634</v>
       </c>
       <c r="J171" t="n">
-        <v>7792</v>
+        <v>1443</v>
       </c>
       <c r="K171" t="n">
         <v>17.62</v>
@@ -17198,16 +17210,16 @@
         <v>1461.75</v>
       </c>
       <c r="G172" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="H172" t="n">
-        <v>36707</v>
+        <v>6329</v>
       </c>
       <c r="I172" t="n">
-        <v>42391</v>
+        <v>7309</v>
       </c>
       <c r="J172" t="n">
-        <v>5684</v>
+        <v>980</v>
       </c>
       <c r="K172" t="n">
         <v>15.48</v>
@@ -17279,16 +17291,16 @@
         <v>446.08</v>
       </c>
       <c r="G173" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H173" t="n">
-        <v>46415</v>
+        <v>9283</v>
       </c>
       <c r="I173" t="n">
-        <v>53530</v>
+        <v>10706</v>
       </c>
       <c r="J173" t="n">
-        <v>7115</v>
+        <v>1423</v>
       </c>
       <c r="K173" t="n">
         <v>15.33</v>
@@ -17360,16 +17372,16 @@
         <v>1523.8</v>
       </c>
       <c r="G174" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H174" t="n">
-        <v>26871</v>
+        <v>5374</v>
       </c>
       <c r="I174" t="n">
-        <v>30476</v>
+        <v>6095</v>
       </c>
       <c r="J174" t="n">
-        <v>3605</v>
+        <v>721</v>
       </c>
       <c r="K174" t="n">
         <v>13.42</v>
@@ -17441,16 +17453,16 @@
         <v>1327.2</v>
       </c>
       <c r="G175" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H175" t="n">
-        <v>38126</v>
+        <v>7149</v>
       </c>
       <c r="I175" t="n">
-        <v>42470</v>
+        <v>7963</v>
       </c>
       <c r="J175" t="n">
-        <v>4345</v>
+        <v>815</v>
       </c>
       <c r="K175" t="n">
         <v>11.4</v>
@@ -17522,16 +17534,16 @@
         <v>4302.4</v>
       </c>
       <c r="G176" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H176" t="n">
-        <v>34758</v>
+        <v>3862</v>
       </c>
       <c r="I176" t="n">
-        <v>38722</v>
+        <v>4302</v>
       </c>
       <c r="J176" t="n">
-        <v>3964</v>
+        <v>440</v>
       </c>
       <c r="K176" t="n">
         <v>11.4</v>
@@ -17603,16 +17615,16 @@
         <v>1555.15</v>
       </c>
       <c r="G177" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H177" t="n">
-        <v>23429</v>
+        <v>4393</v>
       </c>
       <c r="I177" t="n">
-        <v>24882</v>
+        <v>4665</v>
       </c>
       <c r="J177" t="n">
-        <v>1453</v>
+        <v>272</v>
       </c>
       <c r="K177" t="n">
         <v>6.2</v>
@@ -17684,16 +17696,16 @@
         <v>2946.05</v>
       </c>
       <c r="G178" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H178" t="n">
-        <v>30885</v>
+        <v>5615</v>
       </c>
       <c r="I178" t="n">
-        <v>32407</v>
+        <v>5892</v>
       </c>
       <c r="J178" t="n">
-        <v>1522</v>
+        <v>277</v>
       </c>
       <c r="K178" t="n">
         <v>4.93</v>
@@ -17765,16 +17777,16 @@
         <v>1568.65</v>
       </c>
       <c r="G179" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H179" t="n">
-        <v>40943</v>
+        <v>7582</v>
       </c>
       <c r="I179" t="n">
-        <v>42354</v>
+        <v>7843</v>
       </c>
       <c r="J179" t="n">
-        <v>1411</v>
+        <v>261</v>
       </c>
       <c r="K179" t="n">
         <v>3.45</v>
@@ -17846,16 +17858,16 @@
         <v>364.32</v>
       </c>
       <c r="G180" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="H180" t="n">
-        <v>25014</v>
+        <v>5003</v>
       </c>
       <c r="I180" t="n">
-        <v>25502</v>
+        <v>5100</v>
       </c>
       <c r="J180" t="n">
-        <v>488</v>
+        <v>98</v>
       </c>
       <c r="K180" t="n">
         <v>1.95</v>
@@ -17927,16 +17939,16 @@
         <v>12524.3</v>
       </c>
       <c r="G181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>37215</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>37573</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
         <v>0.96</v>
@@ -18008,16 +18020,16 @@
         <v>1910.35</v>
       </c>
       <c r="G182" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H182" t="n">
-        <v>26667</v>
+        <v>4706</v>
       </c>
       <c r="I182" t="n">
-        <v>32476</v>
+        <v>5731</v>
       </c>
       <c r="J182" t="n">
-        <v>5809</v>
+        <v>1025</v>
       </c>
       <c r="K182" t="n">
         <v>21.78</v>
@@ -18089,16 +18101,16 @@
         <v>4560.7</v>
       </c>
       <c r="G183" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H183" t="n">
-        <v>42188</v>
+        <v>7671</v>
       </c>
       <c r="I183" t="n">
-        <v>50168</v>
+        <v>9121</v>
       </c>
       <c r="J183" t="n">
-        <v>7979</v>
+        <v>1451</v>
       </c>
       <c r="K183" t="n">
         <v>18.91</v>
@@ -18170,16 +18182,16 @@
         <v>6982.9</v>
       </c>
       <c r="G184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>19146</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>20949</v>
+        <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>1803</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
         <v>9.42</v>
@@ -18251,16 +18263,16 @@
         <v>1879.6</v>
       </c>
       <c r="G185" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H185" t="n">
-        <v>34066</v>
+        <v>5379</v>
       </c>
       <c r="I185" t="n">
-        <v>35712</v>
+        <v>5639</v>
       </c>
       <c r="J185" t="n">
-        <v>1646</v>
+        <v>260</v>
       </c>
       <c r="K185" t="n">
         <v>4.83</v>
@@ -18332,16 +18344,16 @@
         <v>840.9299999999999</v>
       </c>
       <c r="G186" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="H186" t="n">
-        <v>38575</v>
+        <v>7233</v>
       </c>
       <c r="I186" t="n">
-        <v>40365</v>
+        <v>7568</v>
       </c>
       <c r="J186" t="n">
-        <v>1789</v>
+        <v>336</v>
       </c>
       <c r="K186" t="n">
         <v>4.64</v>
@@ -18413,16 +18425,16 @@
         <v>740.15</v>
       </c>
       <c r="G187" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H187" t="n">
-        <v>39523</v>
+        <v>7905</v>
       </c>
       <c r="I187" t="n">
-        <v>40708</v>
+        <v>8142</v>
       </c>
       <c r="J187" t="n">
-        <v>1185</v>
+        <v>237</v>
       </c>
       <c r="K187" t="n">
         <v>3</v>
@@ -18494,16 +18506,16 @@
         <v>457.5</v>
       </c>
       <c r="G188" t="n">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="H188" t="n">
-        <v>33902</v>
+        <v>6691</v>
       </c>
       <c r="I188" t="n">
-        <v>34770</v>
+        <v>6862</v>
       </c>
       <c r="J188" t="n">
-        <v>868</v>
+        <v>171</v>
       </c>
       <c r="K188" t="n">
         <v>2.56</v>
@@ -18575,16 +18587,16 @@
         <v>1348.22</v>
       </c>
       <c r="G189" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H189" t="n">
-        <v>27871</v>
+        <v>5309</v>
       </c>
       <c r="I189" t="n">
-        <v>28313</v>
+        <v>5393</v>
       </c>
       <c r="J189" t="n">
-        <v>441</v>
+        <v>84</v>
       </c>
       <c r="K189" t="n">
         <v>1.58</v>
@@ -18656,16 +18668,16 @@
         <v>1592</v>
       </c>
       <c r="G190" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H190" t="n">
-        <v>36050</v>
+        <v>6270</v>
       </c>
       <c r="I190" t="n">
-        <v>36616</v>
+        <v>6368</v>
       </c>
       <c r="J190" t="n">
-        <v>566</v>
+        <v>98</v>
       </c>
       <c r="K190" t="n">
         <v>1.57</v>
@@ -18737,16 +18749,16 @@
         <v>2992.15</v>
       </c>
       <c r="G191" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H191" t="n">
-        <v>29460</v>
+        <v>5892</v>
       </c>
       <c r="I191" t="n">
-        <v>29922</v>
+        <v>5984</v>
       </c>
       <c r="J191" t="n">
-        <v>461</v>
+        <v>92</v>
       </c>
       <c r="K191" t="n">
         <v>1.56</v>
@@ -18899,16 +18911,16 @@
         <v>2717.1</v>
       </c>
       <c r="G193" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H193" t="n">
-        <v>40905</v>
+        <v>8181</v>
       </c>
       <c r="I193" t="n">
-        <v>40756</v>
+        <v>8151</v>
       </c>
       <c r="J193" t="n">
-        <v>-148</v>
+        <v>-30</v>
       </c>
       <c r="K193" t="n">
         <v>-0.36</v>
@@ -18980,16 +18992,16 @@
         <v>4765.65</v>
       </c>
       <c r="G194" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>24254</v>
+        <v>4851</v>
       </c>
       <c r="I194" t="n">
-        <v>23828</v>
+        <v>4766</v>
       </c>
       <c r="J194" t="n">
-        <v>-425</v>
+        <v>-85</v>
       </c>
       <c r="K194" t="n">
         <v>-1.75</v>
@@ -19061,16 +19073,16 @@
         <v>1464.95</v>
       </c>
       <c r="G195" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H195" t="n">
-        <v>30476</v>
+        <v>6095</v>
       </c>
       <c r="I195" t="n">
-        <v>29299</v>
+        <v>5860</v>
       </c>
       <c r="J195" t="n">
-        <v>-1177</v>
+        <v>-235</v>
       </c>
       <c r="K195" t="n">
         <v>-3.86</v>
@@ -19142,16 +19154,16 @@
         <v>4123.05</v>
       </c>
       <c r="G196" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>30117</v>
+        <v>4302</v>
       </c>
       <c r="I196" t="n">
-        <v>28861</v>
+        <v>4123</v>
       </c>
       <c r="J196" t="n">
-        <v>-1255</v>
+        <v>-179</v>
       </c>
       <c r="K196" t="n">
         <v>-4.17</v>
@@ -19223,16 +19235,16 @@
         <v>5016.75</v>
       </c>
       <c r="G197" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H197" t="n">
-        <v>23828</v>
+        <v>4766</v>
       </c>
       <c r="I197" t="n">
-        <v>25084</v>
+        <v>5017</v>
       </c>
       <c r="J197" t="n">
-        <v>1256</v>
+        <v>251</v>
       </c>
       <c r="K197" t="n">
         <v>5.27</v>
@@ -19304,16 +19316,16 @@
         <v>25146</v>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>24325</v>
+        <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>25146</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>821</v>
+        <v>0</v>
       </c>
       <c r="K198" t="n">
         <v>3.37</v>
@@ -19385,16 +19397,16 @@
         <v>761.5</v>
       </c>
       <c r="G199" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="H199" t="n">
-        <v>34047</v>
+        <v>6661</v>
       </c>
       <c r="I199" t="n">
-        <v>35029</v>
+        <v>6854</v>
       </c>
       <c r="J199" t="n">
-        <v>982</v>
+        <v>192</v>
       </c>
       <c r="K199" t="n">
         <v>2.88</v>
@@ -19466,16 +19478,16 @@
         <v>384.1</v>
       </c>
       <c r="G200" t="n">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="H200" t="n">
-        <v>25820</v>
+        <v>4865</v>
       </c>
       <c r="I200" t="n">
-        <v>26503</v>
+        <v>4993</v>
       </c>
       <c r="J200" t="n">
-        <v>682</v>
+        <v>129</v>
       </c>
       <c r="K200" t="n">
         <v>2.64</v>
@@ -19547,16 +19559,16 @@
         <v>4077.8</v>
       </c>
       <c r="G201" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H201" t="n">
-        <v>28861</v>
+        <v>4123</v>
       </c>
       <c r="I201" t="n">
-        <v>28545</v>
+        <v>4078</v>
       </c>
       <c r="J201" t="n">
-        <v>-317</v>
+        <v>-45</v>
       </c>
       <c r="K201" t="n">
         <v>-1.1</v>
@@ -19628,16 +19640,16 @@
         <v>6780.85</v>
       </c>
       <c r="G202" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>27932</v>
+        <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>27123</v>
+        <v>0</v>
       </c>
       <c r="J202" t="n">
-        <v>-808</v>
+        <v>0</v>
       </c>
       <c r="K202" t="n">
         <v>-2.89</v>
@@ -19709,16 +19721,16 @@
         <v>1302.35</v>
       </c>
       <c r="G203" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H203" t="n">
-        <v>44491</v>
+        <v>8089</v>
       </c>
       <c r="I203" t="n">
-        <v>42978</v>
+        <v>7814</v>
       </c>
       <c r="J203" t="n">
-        <v>-1514</v>
+        <v>-275</v>
       </c>
       <c r="K203" t="n">
         <v>-3.4</v>
@@ -19790,16 +19802,16 @@
         <v>1813.3</v>
       </c>
       <c r="G204" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H204" t="n">
-        <v>26314</v>
+        <v>3759</v>
       </c>
       <c r="I204" t="n">
-        <v>25386</v>
+        <v>3627</v>
       </c>
       <c r="J204" t="n">
-        <v>-928</v>
+        <v>-133</v>
       </c>
       <c r="K204" t="n">
         <v>-3.53</v>
@@ -19871,16 +19883,16 @@
         <v>437.7</v>
       </c>
       <c r="G205" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="H205" t="n">
-        <v>30652</v>
+        <v>5948</v>
       </c>
       <c r="I205" t="n">
-        <v>29326</v>
+        <v>5690</v>
       </c>
       <c r="J205" t="n">
-        <v>-1327</v>
+        <v>-257</v>
       </c>
       <c r="K205" t="n">
         <v>-4.33</v>
@@ -19952,16 +19964,16 @@
         <v>1107</v>
       </c>
       <c r="G206" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="H206" t="n">
-        <v>30553</v>
+        <v>5876</v>
       </c>
       <c r="I206" t="n">
-        <v>28782</v>
+        <v>5535</v>
       </c>
       <c r="J206" t="n">
-        <v>-1771</v>
+        <v>-341</v>
       </c>
       <c r="K206" t="n">
         <v>-5.8</v>
@@ -20033,16 +20045,16 @@
         <v>1778.25</v>
       </c>
       <c r="G207" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H207" t="n">
-        <v>42028</v>
+        <v>7641</v>
       </c>
       <c r="I207" t="n">
-        <v>39122</v>
+        <v>7113</v>
       </c>
       <c r="J207" t="n">
-        <v>-2906</v>
+        <v>-528</v>
       </c>
       <c r="K207" t="n">
         <v>-6.91</v>
@@ -20193,16 +20205,16 @@
         <v>1393.88</v>
       </c>
       <c r="G209" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H209" t="n">
-        <v>28656</v>
+        <v>4776</v>
       </c>
       <c r="I209" t="n">
-        <v>25090</v>
+        <v>4182</v>
       </c>
       <c r="J209" t="n">
-        <v>-3566</v>
+        <v>-594</v>
       </c>
       <c r="K209" t="n">
         <v>-12.44</v>
@@ -20274,16 +20286,16 @@
         <v>2280.55</v>
       </c>
       <c r="G210" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H210" t="n">
-        <v>26929</v>
+        <v>2992</v>
       </c>
       <c r="I210" t="n">
-        <v>20525</v>
+        <v>2281</v>
       </c>
       <c r="J210" t="n">
-        <v>-6404</v>
+        <v>-712</v>
       </c>
       <c r="K210" t="n">
         <v>-23.78</v>
@@ -20355,16 +20367,16 @@
         <v>578.35</v>
       </c>
       <c r="G211" t="n">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="H211" t="n">
-        <v>48487</v>
+        <v>9385</v>
       </c>
       <c r="I211" t="n">
-        <v>35858</v>
+        <v>6940</v>
       </c>
       <c r="J211" t="n">
-        <v>-12629</v>
+        <v>-2444</v>
       </c>
       <c r="K211" t="n">
         <v>-26.05</v>
@@ -20434,16 +20446,16 @@
         <v>958.4</v>
       </c>
       <c r="G212" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H212" t="n">
-        <v>31374</v>
+        <v>5779</v>
       </c>
       <c r="I212" t="n">
-        <v>36419</v>
+        <v>6709</v>
       </c>
       <c r="J212" t="n">
-        <v>5045</v>
+        <v>929</v>
       </c>
       <c r="K212" t="n">
         <v>16.08</v>
@@ -20515,16 +20527,16 @@
         <v>12159</v>
       </c>
       <c r="G213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>10624</v>
+        <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>12159</v>
+        <v>0</v>
       </c>
       <c r="J213" t="n">
-        <v>1535</v>
+        <v>0</v>
       </c>
       <c r="K213" t="n">
         <v>14.44</v>
@@ -20677,16 +20689,16 @@
         <v>1402.7</v>
       </c>
       <c r="G215" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H215" t="n">
-        <v>28358</v>
+        <v>4932</v>
       </c>
       <c r="I215" t="n">
-        <v>32262</v>
+        <v>5611</v>
       </c>
       <c r="J215" t="n">
-        <v>3904</v>
+        <v>679</v>
       </c>
       <c r="K215" t="n">
         <v>13.77</v>
@@ -20758,16 +20770,16 @@
         <v>1845.6</v>
       </c>
       <c r="G216" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H216" t="n">
-        <v>27900</v>
+        <v>4923</v>
       </c>
       <c r="I216" t="n">
-        <v>31375</v>
+        <v>5537</v>
       </c>
       <c r="J216" t="n">
-        <v>3476</v>
+        <v>613</v>
       </c>
       <c r="K216" t="n">
         <v>12.46</v>
@@ -20839,16 +20851,16 @@
         <v>1538.2</v>
       </c>
       <c r="G217" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H217" t="n">
-        <v>32059</v>
+        <v>5576</v>
       </c>
       <c r="I217" t="n">
-        <v>35379</v>
+        <v>6153</v>
       </c>
       <c r="J217" t="n">
-        <v>3319</v>
+        <v>577</v>
       </c>
       <c r="K217" t="n">
         <v>10.35</v>
@@ -20920,16 +20932,16 @@
         <v>1216.6</v>
       </c>
       <c r="G218" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="H218" t="n">
-        <v>30996</v>
+        <v>5535</v>
       </c>
       <c r="I218" t="n">
-        <v>34065</v>
+        <v>6083</v>
       </c>
       <c r="J218" t="n">
-        <v>3069</v>
+        <v>548</v>
       </c>
       <c r="K218" t="n">
         <v>9.9</v>
@@ -21001,16 +21013,16 @@
         <v>7159.5</v>
       </c>
       <c r="G219" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>27123</v>
+        <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>28638</v>
+        <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>1515</v>
+        <v>0</v>
       </c>
       <c r="K219" t="n">
         <v>5.58</v>
@@ -21082,16 +21094,16 @@
         <v>1803.9</v>
       </c>
       <c r="G220" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H220" t="n">
-        <v>44456</v>
+        <v>8891</v>
       </c>
       <c r="I220" t="n">
-        <v>45098</v>
+        <v>9020</v>
       </c>
       <c r="J220" t="n">
-        <v>641</v>
+        <v>128</v>
       </c>
       <c r="K220" t="n">
         <v>1.44</v>
@@ -21163,16 +21175,16 @@
         <v>3382.6</v>
       </c>
       <c r="G221" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>20294</v>
+        <v>3382</v>
       </c>
       <c r="I221" t="n">
-        <v>20296</v>
+        <v>3383</v>
       </c>
       <c r="J221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K221" t="n">
         <v>0.01</v>
@@ -21244,16 +21256,16 @@
         <v>1301.6</v>
       </c>
       <c r="G222" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H222" t="n">
-        <v>20887</v>
+        <v>3916</v>
       </c>
       <c r="I222" t="n">
-        <v>20826</v>
+        <v>3905</v>
       </c>
       <c r="J222" t="n">
-        <v>-62</v>
+        <v>-12</v>
       </c>
       <c r="K222" t="n">
         <v>-0.29</v>
@@ -21323,16 +21335,16 @@
         <v>430.05</v>
       </c>
       <c r="G223" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="H223" t="n">
-        <v>33703</v>
+        <v>6566</v>
       </c>
       <c r="I223" t="n">
-        <v>33114</v>
+        <v>6451</v>
       </c>
       <c r="J223" t="n">
-        <v>-589</v>
+        <v>-115</v>
       </c>
       <c r="K223" t="n">
         <v>-1.75</v>
@@ -21404,16 +21416,16 @@
         <v>1200.5</v>
       </c>
       <c r="G224" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H224" t="n">
-        <v>39070</v>
+        <v>7814</v>
       </c>
       <c r="I224" t="n">
-        <v>36015</v>
+        <v>7203</v>
       </c>
       <c r="J224" t="n">
-        <v>-3056</v>
+        <v>-611</v>
       </c>
       <c r="K224" t="n">
         <v>-7.82</v>
@@ -21483,16 +21495,16 @@
         <v>2700</v>
       </c>
       <c r="G225" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H225" t="n">
-        <v>41854</v>
+        <v>5979</v>
       </c>
       <c r="I225" t="n">
-        <v>37800</v>
+        <v>5400</v>
       </c>
       <c r="J225" t="n">
-        <v>-4054</v>
+        <v>-579</v>
       </c>
       <c r="K225" t="n">
         <v>-9.69</v>
@@ -21558,16 +21570,16 @@
         <v>3401.6</v>
       </c>
       <c r="G226" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H226" t="n">
-        <v>36700</v>
+        <v>4078</v>
       </c>
       <c r="I226" t="n">
-        <v>30614</v>
+        <v>3402</v>
       </c>
       <c r="J226" t="n">
-        <v>-6086</v>
+        <v>-676</v>
       </c>
       <c r="K226" t="n">
         <v>-16.58</v>
@@ -21720,16 +21732,16 @@
         <v>1424.6</v>
       </c>
       <c r="G228" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H228" t="n">
-        <v>24730</v>
+        <v>3905</v>
       </c>
       <c r="I228" t="n">
-        <v>27067</v>
+        <v>4274</v>
       </c>
       <c r="J228" t="n">
-        <v>2337</v>
+        <v>369</v>
       </c>
       <c r="K228" t="n">
         <v>9.449999999999999</v>
@@ -21801,16 +21813,16 @@
         <v>3553.7</v>
       </c>
       <c r="G229" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H229" t="n">
-        <v>36576</v>
+        <v>6650</v>
       </c>
       <c r="I229" t="n">
-        <v>39091</v>
+        <v>7107</v>
       </c>
       <c r="J229" t="n">
-        <v>2515</v>
+        <v>457</v>
       </c>
       <c r="K229" t="n">
         <v>6.87</v>
@@ -21882,16 +21894,16 @@
         <v>12627</v>
       </c>
       <c r="G230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>23788</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
-        <v>25254</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>1466</v>
+        <v>0</v>
       </c>
       <c r="K230" t="n">
         <v>6.16</v>
@@ -21963,16 +21975,16 @@
         <v>1488.6</v>
       </c>
       <c r="G231" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H231" t="n">
-        <v>32262</v>
+        <v>5611</v>
       </c>
       <c r="I231" t="n">
-        <v>34238</v>
+        <v>5954</v>
       </c>
       <c r="J231" t="n">
-        <v>1976</v>
+        <v>344</v>
       </c>
       <c r="K231" t="n">
         <v>6.12</v>
@@ -22044,16 +22056,16 @@
         <v>3354.5</v>
       </c>
       <c r="G232" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H232" t="n">
-        <v>31713</v>
+        <v>6343</v>
       </c>
       <c r="I232" t="n">
-        <v>33545</v>
+        <v>6709</v>
       </c>
       <c r="J232" t="n">
-        <v>1832</v>
+        <v>366</v>
       </c>
       <c r="K232" t="n">
         <v>5.78</v>
@@ -22125,16 +22137,16 @@
         <v>1012.15</v>
       </c>
       <c r="G233" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="H233" t="n">
-        <v>37378</v>
+        <v>6709</v>
       </c>
       <c r="I233" t="n">
-        <v>39474</v>
+        <v>7085</v>
       </c>
       <c r="J233" t="n">
-        <v>2096</v>
+        <v>376</v>
       </c>
       <c r="K233" t="n">
         <v>5.61</v>
@@ -22206,16 +22218,16 @@
         <v>32115</v>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>30705</v>
+        <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>32115</v>
+        <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>1410</v>
+        <v>0</v>
       </c>
       <c r="K234" t="n">
         <v>4.59</v>
@@ -22287,16 +22299,16 @@
         <v>1226.25</v>
       </c>
       <c r="G235" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="H235" t="n">
-        <v>36498</v>
+        <v>7300</v>
       </c>
       <c r="I235" t="n">
-        <v>36788</v>
+        <v>7358</v>
       </c>
       <c r="J235" t="n">
-        <v>290</v>
+        <v>58</v>
       </c>
       <c r="K235" t="n">
         <v>0.79</v>
@@ -22368,16 +22380,16 @@
         <v>390.75</v>
       </c>
       <c r="G236" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H236" t="n">
-        <v>21992</v>
+        <v>4398</v>
       </c>
       <c r="I236" t="n">
-        <v>21491</v>
+        <v>4298</v>
       </c>
       <c r="J236" t="n">
-        <v>-500</v>
+        <v>-100</v>
       </c>
       <c r="K236" t="n">
         <v>-2.28</v>
@@ -22449,16 +22461,16 @@
         <v>414.95</v>
       </c>
       <c r="G237" t="n">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="H237" t="n">
-        <v>45585</v>
+        <v>9031</v>
       </c>
       <c r="I237" t="n">
-        <v>43985</v>
+        <v>8714</v>
       </c>
       <c r="J237" t="n">
-        <v>-1601</v>
+        <v>-317</v>
       </c>
       <c r="K237" t="n">
         <v>-3.51</v>
@@ -22530,16 +22542,16 @@
         <v>2375.4</v>
       </c>
       <c r="G238" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H238" t="n">
-        <v>24644</v>
+        <v>4929</v>
       </c>
       <c r="I238" t="n">
-        <v>23754</v>
+        <v>4751</v>
       </c>
       <c r="J238" t="n">
-        <v>-890</v>
+        <v>-178</v>
       </c>
       <c r="K238" t="n">
         <v>-3.61</v>
@@ -22611,16 +22623,16 @@
         <v>1459.45</v>
       </c>
       <c r="G239" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H239" t="n">
-        <v>33840</v>
+        <v>6153</v>
       </c>
       <c r="I239" t="n">
-        <v>32108</v>
+        <v>5838</v>
       </c>
       <c r="J239" t="n">
-        <v>-1732</v>
+        <v>-315</v>
       </c>
       <c r="K239" t="n">
         <v>-5.12</v>
@@ -22692,16 +22704,16 @@
         <v>3179.1</v>
       </c>
       <c r="G240" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H240" t="n">
-        <v>40819</v>
+        <v>6803</v>
       </c>
       <c r="I240" t="n">
-        <v>38149</v>
+        <v>6358</v>
       </c>
       <c r="J240" t="n">
-        <v>-2670</v>
+        <v>-445</v>
       </c>
       <c r="K240" t="n">
         <v>-6.54</v>
@@ -22773,16 +22785,16 @@
         <v>1682.5</v>
       </c>
       <c r="G241" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H241" t="n">
-        <v>28862</v>
+        <v>5412</v>
       </c>
       <c r="I241" t="n">
-        <v>26920</v>
+        <v>5048</v>
       </c>
       <c r="J241" t="n">
-        <v>-1942</v>
+        <v>-364</v>
       </c>
       <c r="K241" t="n">
         <v>-6.73</v>
@@ -22854,16 +22866,16 @@
         <v>16274</v>
       </c>
       <c r="G242" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>25254</v>
+        <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>32548</v>
+        <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>7294</v>
+        <v>0</v>
       </c>
       <c r="K242" t="n">
         <v>28.88</v>
@@ -22935,16 +22947,16 @@
         <v>1584.4</v>
       </c>
       <c r="G243" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H243" t="n">
-        <v>27996</v>
+        <v>4420</v>
       </c>
       <c r="I243" t="n">
-        <v>30104</v>
+        <v>4753</v>
       </c>
       <c r="J243" t="n">
-        <v>2107</v>
+        <v>333</v>
       </c>
       <c r="K243" t="n">
         <v>7.53</v>
@@ -23097,16 +23109,16 @@
         <v>7837.5</v>
       </c>
       <c r="G245" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>22120</v>
+        <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>23512</v>
+        <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>1392</v>
+        <v>0</v>
       </c>
       <c r="K245" t="n">
         <v>6.29</v>
@@ -23178,16 +23190,16 @@
         <v>2501.6</v>
       </c>
       <c r="G246" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H246" t="n">
-        <v>30880</v>
+        <v>4751</v>
       </c>
       <c r="I246" t="n">
-        <v>32521</v>
+        <v>5003</v>
       </c>
       <c r="J246" t="n">
-        <v>1641</v>
+        <v>252</v>
       </c>
       <c r="K246" t="n">
         <v>5.31</v>
@@ -23259,16 +23271,16 @@
         <v>1282</v>
       </c>
       <c r="G247" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="H247" t="n">
-        <v>30656</v>
+        <v>6131</v>
       </c>
       <c r="I247" t="n">
-        <v>32050</v>
+        <v>6410</v>
       </c>
       <c r="J247" t="n">
-        <v>1394</v>
+        <v>279</v>
       </c>
       <c r="K247" t="n">
         <v>4.55</v>
@@ -23340,16 +23352,16 @@
         <v>1507.1</v>
       </c>
       <c r="G248" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H248" t="n">
-        <v>54000</v>
+        <v>10216</v>
       </c>
       <c r="I248" t="n">
-        <v>55763</v>
+        <v>10550</v>
       </c>
       <c r="J248" t="n">
-        <v>1763</v>
+        <v>334</v>
       </c>
       <c r="K248" t="n">
         <v>3.26</v>
@@ -23421,16 +23433,16 @@
         <v>1283.6</v>
       </c>
       <c r="G249" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H249" t="n">
-        <v>26195</v>
+        <v>4990</v>
       </c>
       <c r="I249" t="n">
-        <v>26956</v>
+        <v>5134</v>
       </c>
       <c r="J249" t="n">
-        <v>760</v>
+        <v>145</v>
       </c>
       <c r="K249" t="n">
         <v>2.9</v>
@@ -23502,16 +23514,16 @@
         <v>394.05</v>
       </c>
       <c r="G250" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="H250" t="n">
-        <v>26180</v>
+        <v>5080</v>
       </c>
       <c r="I250" t="n">
-        <v>26401</v>
+        <v>5123</v>
       </c>
       <c r="J250" t="n">
-        <v>221</v>
+        <v>43</v>
       </c>
       <c r="K250" t="n">
         <v>0.84</v>
@@ -23583,16 +23595,16 @@
         <v>416.8</v>
       </c>
       <c r="G251" t="n">
-        <v>88</v>
+        <v>17</v>
       </c>
       <c r="H251" t="n">
-        <v>36516</v>
+        <v>7054</v>
       </c>
       <c r="I251" t="n">
-        <v>36678</v>
+        <v>7086</v>
       </c>
       <c r="J251" t="n">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="K251" t="n">
         <v>0.45</v>
@@ -23664,16 +23676,16 @@
         <v>994.75</v>
       </c>
       <c r="G252" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="H252" t="n">
-        <v>32389</v>
+        <v>6073</v>
       </c>
       <c r="I252" t="n">
-        <v>31832</v>
+        <v>5968</v>
       </c>
       <c r="J252" t="n">
-        <v>-557</v>
+        <v>-104</v>
       </c>
       <c r="K252" t="n">
         <v>-1.72</v>
@@ -23745,16 +23757,16 @@
         <v>3063.2</v>
       </c>
       <c r="G253" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H253" t="n">
-        <v>38149</v>
+        <v>6358</v>
       </c>
       <c r="I253" t="n">
-        <v>36758</v>
+        <v>6126</v>
       </c>
       <c r="J253" t="n">
-        <v>-1391</v>
+        <v>-232</v>
       </c>
       <c r="K253" t="n">
         <v>-3.65</v>
@@ -23824,16 +23836,16 @@
         <v>1850.1</v>
       </c>
       <c r="G254" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H254" t="n">
-        <v>29250</v>
+        <v>5850</v>
       </c>
       <c r="I254" t="n">
-        <v>27752</v>
+        <v>5550</v>
       </c>
       <c r="J254" t="n">
-        <v>-1498</v>
+        <v>-300</v>
       </c>
       <c r="K254" t="n">
         <v>-5.12</v>
@@ -23903,16 +23915,16 @@
         <v>1377.7</v>
       </c>
       <c r="G255" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="H255" t="n">
-        <v>31261</v>
+        <v>5954</v>
       </c>
       <c r="I255" t="n">
-        <v>28932</v>
+        <v>5511</v>
       </c>
       <c r="J255" t="n">
-        <v>-2329</v>
+        <v>-444</v>
       </c>
       <c r="K255" t="n">
         <v>-7.45</v>
@@ -24061,16 +24073,16 @@
         <v>1053.15</v>
       </c>
       <c r="G257" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H257" t="n">
-        <v>34371</v>
+        <v>6332</v>
       </c>
       <c r="I257" t="n">
-        <v>40020</v>
+        <v>7372</v>
       </c>
       <c r="J257" t="n">
-        <v>5649</v>
+        <v>1041</v>
       </c>
       <c r="K257" t="n">
         <v>16.43</v>
@@ -24142,16 +24154,16 @@
         <v>422.9</v>
       </c>
       <c r="G258" t="n">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="H258" t="n">
-        <v>35859</v>
+        <v>7093</v>
       </c>
       <c r="I258" t="n">
-        <v>38484</v>
+        <v>7612</v>
       </c>
       <c r="J258" t="n">
-        <v>2625</v>
+        <v>519</v>
       </c>
       <c r="K258" t="n">
         <v>7.32</v>
@@ -24223,16 +24235,16 @@
         <v>12589</v>
       </c>
       <c r="G259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>11918</v>
+        <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>12589</v>
+        <v>0</v>
       </c>
       <c r="J259" t="n">
-        <v>671</v>
+        <v>0</v>
       </c>
       <c r="K259" t="n">
         <v>5.63</v>
@@ -24304,16 +24316,16 @@
         <v>7164.5</v>
       </c>
       <c r="G260" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H260" t="n">
-        <v>27360</v>
+        <v>0</v>
       </c>
       <c r="I260" t="n">
-        <v>28658</v>
+        <v>0</v>
       </c>
       <c r="J260" t="n">
-        <v>1298</v>
+        <v>0</v>
       </c>
       <c r="K260" t="n">
         <v>4.74</v>
@@ -24385,16 +24397,16 @@
         <v>745.8</v>
       </c>
       <c r="G261" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H261" t="n">
-        <v>42825</v>
+        <v>7984</v>
       </c>
       <c r="I261" t="n">
-        <v>44002</v>
+        <v>8204</v>
       </c>
       <c r="J261" t="n">
-        <v>1177</v>
+        <v>219</v>
       </c>
       <c r="K261" t="n">
         <v>2.75</v>
@@ -24466,16 +24478,16 @@
         <v>344.7</v>
       </c>
       <c r="G262" t="n">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="H262" t="n">
-        <v>31922</v>
+        <v>6113</v>
       </c>
       <c r="I262" t="n">
-        <v>32402</v>
+        <v>6205</v>
       </c>
       <c r="J262" t="n">
-        <v>479</v>
+        <v>92</v>
       </c>
       <c r="K262" t="n">
         <v>1.5</v>
@@ -24547,16 +24559,16 @@
         <v>247.95</v>
       </c>
       <c r="G263" t="n">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="H263" t="n">
-        <v>34930</v>
+        <v>6884</v>
       </c>
       <c r="I263" t="n">
-        <v>33969</v>
+        <v>6695</v>
       </c>
       <c r="J263" t="n">
-        <v>-960</v>
+        <v>-189</v>
       </c>
       <c r="K263" t="n">
         <v>-2.75</v>
@@ -24628,16 +24640,16 @@
         <v>1973.4</v>
       </c>
       <c r="G264" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H264" t="n">
-        <v>20293</v>
+        <v>4059</v>
       </c>
       <c r="I264" t="n">
-        <v>19734</v>
+        <v>3947</v>
       </c>
       <c r="J264" t="n">
-        <v>-559</v>
+        <v>-112</v>
       </c>
       <c r="K264" t="n">
         <v>-2.75</v>
@@ -24709,16 +24721,16 @@
         <v>3787.8</v>
       </c>
       <c r="G265" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H265" t="n">
-        <v>23429</v>
+        <v>3905</v>
       </c>
       <c r="I265" t="n">
-        <v>22727</v>
+        <v>3788</v>
       </c>
       <c r="J265" t="n">
-        <v>-703</v>
+        <v>-117</v>
       </c>
       <c r="K265" t="n">
         <v>-3</v>
@@ -24790,16 +24802,16 @@
         <v>1638.9</v>
       </c>
       <c r="G266" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H266" t="n">
-        <v>45873</v>
+        <v>8495</v>
       </c>
       <c r="I266" t="n">
-        <v>44250</v>
+        <v>8194</v>
       </c>
       <c r="J266" t="n">
-        <v>-1623</v>
+        <v>-300</v>
       </c>
       <c r="K266" t="n">
         <v>-3.54</v>
@@ -24871,16 +24883,16 @@
         <v>1447.2</v>
       </c>
       <c r="G267" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="H267" t="n">
-        <v>46720</v>
+        <v>9043</v>
       </c>
       <c r="I267" t="n">
-        <v>44863</v>
+        <v>8683</v>
       </c>
       <c r="J267" t="n">
-        <v>-1857</v>
+        <v>-359</v>
       </c>
       <c r="K267" t="n">
         <v>-3.97</v>
@@ -24952,16 +24964,16 @@
         <v>1380.5</v>
       </c>
       <c r="G268" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H268" t="n">
-        <v>20322</v>
+        <v>2903</v>
       </c>
       <c r="I268" t="n">
-        <v>19327</v>
+        <v>2761</v>
       </c>
       <c r="J268" t="n">
-        <v>-995</v>
+        <v>-142</v>
       </c>
       <c r="K268" t="n">
         <v>-4.9</v>
@@ -25033,16 +25045,16 @@
         <v>926.4</v>
       </c>
       <c r="G269" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="H269" t="n">
-        <v>32827</v>
+        <v>5968</v>
       </c>
       <c r="I269" t="n">
-        <v>30571</v>
+        <v>5558</v>
       </c>
       <c r="J269" t="n">
-        <v>-2256</v>
+        <v>-410</v>
       </c>
       <c r="K269" t="n">
         <v>-6.87</v>
@@ -25114,16 +25126,16 @@
         <v>1687.9</v>
       </c>
       <c r="G270" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H270" t="n">
-        <v>31452</v>
+        <v>5550</v>
       </c>
       <c r="I270" t="n">
-        <v>28694</v>
+        <v>5064</v>
       </c>
       <c r="J270" t="n">
-        <v>-2757</v>
+        <v>-487</v>
       </c>
       <c r="K270" t="n">
         <v>-8.77</v>
@@ -25195,16 +25207,16 @@
         <v>318.65</v>
       </c>
       <c r="G271" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="H271" t="n">
-        <v>35845</v>
+        <v>7086</v>
       </c>
       <c r="I271" t="n">
-        <v>27404</v>
+        <v>5417</v>
       </c>
       <c r="J271" t="n">
-        <v>-8441</v>
+        <v>-1669</v>
       </c>
       <c r="K271" t="n">
         <v>-23.55</v>
@@ -25276,16 +25288,16 @@
         <v>318.35</v>
       </c>
       <c r="G272" t="n">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="H272" t="n">
-        <v>18313</v>
+        <v>3561</v>
       </c>
       <c r="I272" t="n">
-        <v>22921</v>
+        <v>4457</v>
       </c>
       <c r="J272" t="n">
-        <v>4608</v>
+        <v>896</v>
       </c>
       <c r="K272" t="n">
         <v>25.16</v>
@@ -25357,16 +25369,16 @@
         <v>299.55</v>
       </c>
       <c r="G273" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="H273" t="n">
-        <v>24299</v>
+        <v>4711</v>
       </c>
       <c r="I273" t="n">
-        <v>29356</v>
+        <v>5691</v>
       </c>
       <c r="J273" t="n">
-        <v>5057</v>
+        <v>980</v>
       </c>
       <c r="K273" t="n">
         <v>20.81</v>
@@ -25438,16 +25450,16 @@
         <v>399.15</v>
       </c>
       <c r="G274" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="H274" t="n">
-        <v>18958</v>
+        <v>3792</v>
       </c>
       <c r="I274" t="n">
-        <v>21953</v>
+        <v>4391</v>
       </c>
       <c r="J274" t="n">
-        <v>2995</v>
+        <v>599</v>
       </c>
       <c r="K274" t="n">
         <v>15.8</v>
@@ -25519,16 +25531,16 @@
         <v>4385.2</v>
       </c>
       <c r="G275" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>35973</v>
+        <v>3997</v>
       </c>
       <c r="I275" t="n">
-        <v>39467</v>
+        <v>4385</v>
       </c>
       <c r="J275" t="n">
-        <v>3494</v>
+        <v>388</v>
       </c>
       <c r="K275" t="n">
         <v>9.710000000000001</v>
@@ -25600,16 +25612,16 @@
         <v>4014</v>
       </c>
       <c r="G276" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H276" t="n">
-        <v>41666</v>
+        <v>7576</v>
       </c>
       <c r="I276" t="n">
-        <v>44154</v>
+        <v>8028</v>
       </c>
       <c r="J276" t="n">
-        <v>2488</v>
+        <v>452</v>
       </c>
       <c r="K276" t="n">
         <v>5.97</v>
@@ -25681,16 +25693,16 @@
         <v>775</v>
       </c>
       <c r="G277" t="n">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="H277" t="n">
-        <v>36544</v>
+        <v>6712</v>
       </c>
       <c r="I277" t="n">
-        <v>37975</v>
+        <v>6975</v>
       </c>
       <c r="J277" t="n">
-        <v>1431</v>
+        <v>263</v>
       </c>
       <c r="K277" t="n">
         <v>3.92</v>
@@ -25762,16 +25774,16 @@
         <v>1430.8</v>
       </c>
       <c r="G278" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H278" t="n">
-        <v>31752</v>
+        <v>5522</v>
       </c>
       <c r="I278" t="n">
-        <v>32908</v>
+        <v>5723</v>
       </c>
       <c r="J278" t="n">
-        <v>1157</v>
+        <v>201</v>
       </c>
       <c r="K278" t="n">
         <v>3.64</v>
@@ -25843,16 +25855,16 @@
         <v>1458.6</v>
       </c>
       <c r="G279" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="H279" t="n">
-        <v>54097</v>
+        <v>9965</v>
       </c>
       <c r="I279" t="n">
-        <v>55427</v>
+        <v>10210</v>
       </c>
       <c r="J279" t="n">
-        <v>1330</v>
+        <v>245</v>
       </c>
       <c r="K279" t="n">
         <v>2.46</v>
@@ -25924,16 +25936,16 @@
         <v>1068.45</v>
       </c>
       <c r="G280" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="H280" t="n">
-        <v>36860</v>
+        <v>7372</v>
       </c>
       <c r="I280" t="n">
-        <v>37396</v>
+        <v>7479</v>
       </c>
       <c r="J280" t="n">
-        <v>536</v>
+        <v>107</v>
       </c>
       <c r="K280" t="n">
         <v>1.45</v>
@@ -26005,16 +26017,16 @@
         <v>1886.8</v>
       </c>
       <c r="G281" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H281" t="n">
-        <v>37495</v>
+        <v>5920</v>
       </c>
       <c r="I281" t="n">
-        <v>35849</v>
+        <v>5660</v>
       </c>
       <c r="J281" t="n">
-        <v>-1645</v>
+        <v>-260</v>
       </c>
       <c r="K281" t="n">
         <v>-4.39</v>
@@ -26086,16 +26098,16 @@
         <v>1375.7</v>
       </c>
       <c r="G282" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H282" t="n">
-        <v>31838</v>
+        <v>5789</v>
       </c>
       <c r="I282" t="n">
-        <v>30265</v>
+        <v>5503</v>
       </c>
       <c r="J282" t="n">
-        <v>-1573</v>
+        <v>-286</v>
       </c>
       <c r="K282" t="n">
         <v>-4.94</v>
@@ -26167,16 +26179,16 @@
         <v>11586</v>
       </c>
       <c r="G283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H283" t="n">
-        <v>12589</v>
+        <v>0</v>
       </c>
       <c r="I283" t="n">
-        <v>11586</v>
+        <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>-1003</v>
+        <v>0</v>
       </c>
       <c r="K283" t="n">
         <v>-7.97</v>
@@ -26329,16 +26341,16 @@
         <v>539.55</v>
       </c>
       <c r="G285" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H285" t="n">
-        <v>20655</v>
+        <v>3645</v>
       </c>
       <c r="I285" t="n">
-        <v>18345</v>
+        <v>3237</v>
       </c>
       <c r="J285" t="n">
-        <v>-2310</v>
+        <v>-408</v>
       </c>
       <c r="K285" t="n">
         <v>-11.19</v>
@@ -26410,16 +26422,16 @@
         <v>771.7</v>
       </c>
       <c r="G286" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="H286" t="n">
-        <v>56510</v>
+        <v>11117</v>
       </c>
       <c r="I286" t="n">
-        <v>47074</v>
+        <v>9260</v>
       </c>
       <c r="J286" t="n">
-        <v>-9437</v>
+        <v>-1856</v>
       </c>
       <c r="K286" t="n">
         <v>-16.7</v>
@@ -26478,47 +26490,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Horizon</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Win Rate %</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Median Return %</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Beat Nifty %</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Worst Cycle %</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sharpe (ann)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Chosen</t>
         </is>
@@ -26548,7 +26560,7 @@
         <v>-5.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -26614,7 +26626,7 @@
         <v>-6.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -26647,7 +26659,7 @@
         <v>-8.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -26807,52 +26819,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Start Rs</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>End Rs</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>If Nifty Rs</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Beat Nifty</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Win Ratio</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Largest Winner</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Largest Loser</t>
         </is>
@@ -26865,16 +26877,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C2" t="n">
         <v>12.6</v>
       </c>
       <c r="D2" t="n">
-        <v>563000</v>
+        <v>112600</v>
       </c>
       <c r="E2" t="n">
-        <v>559000</v>
+        <v>111800</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -26907,16 +26919,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>563000</v>
+        <v>112600</v>
       </c>
       <c r="C3" t="n">
         <v>-3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>542732</v>
+        <v>108546</v>
       </c>
       <c r="E3" t="n">
-        <v>561795</v>
+        <v>112359</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -26949,16 +26961,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>542732</v>
+        <v>108546</v>
       </c>
       <c r="C4" t="n">
         <v>-1.9</v>
       </c>
       <c r="D4" t="n">
-        <v>532420</v>
+        <v>106484</v>
       </c>
       <c r="E4" t="n">
-        <v>572469</v>
+        <v>114494</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -26991,16 +27003,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>532420</v>
+        <v>106484</v>
       </c>
       <c r="C5" t="n">
         <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>530823</v>
+        <v>106165</v>
       </c>
       <c r="E5" t="n">
-        <v>509498</v>
+        <v>101900</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -27033,16 +27045,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>530823</v>
+        <v>106165</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>567980</v>
+        <v>113596</v>
       </c>
       <c r="E6" t="n">
-        <v>551786</v>
+        <v>110357</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27075,16 +27087,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>567980</v>
+        <v>113596</v>
       </c>
       <c r="C7" t="n">
         <v>14.8</v>
       </c>
       <c r="D7" t="n">
-        <v>652042</v>
+        <v>130408</v>
       </c>
       <c r="E7" t="n">
-        <v>568891</v>
+        <v>113778</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -27117,16 +27129,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>652042</v>
+        <v>130408</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>671603</v>
+        <v>134321</v>
       </c>
       <c r="E8" t="n">
-        <v>567184</v>
+        <v>113437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -27159,16 +27171,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>671603</v>
+        <v>134321</v>
       </c>
       <c r="C9" t="n">
         <v>13.2</v>
       </c>
       <c r="D9" t="n">
-        <v>760254</v>
+        <v>152051</v>
       </c>
       <c r="E9" t="n">
-        <v>618231</v>
+        <v>123646</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -27201,16 +27213,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>760254</v>
+        <v>152051</v>
       </c>
       <c r="C10" t="n">
         <v>9.1</v>
       </c>
       <c r="D10" t="n">
-        <v>829437</v>
+        <v>165887</v>
       </c>
       <c r="E10" t="n">
-        <v>628741</v>
+        <v>125748</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -27243,16 +27255,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>829437</v>
+        <v>165887</v>
       </c>
       <c r="C11" t="n">
         <v>13.6</v>
       </c>
       <c r="D11" t="n">
-        <v>942241</v>
+        <v>188448</v>
       </c>
       <c r="E11" t="n">
-        <v>703561</v>
+        <v>140712</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -27285,16 +27297,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>942241</v>
+        <v>188448</v>
       </c>
       <c r="C12" t="n">
         <v>0.8</v>
       </c>
       <c r="D12" t="n">
-        <v>949779</v>
+        <v>189956</v>
       </c>
       <c r="E12" t="n">
-        <v>700043</v>
+        <v>140009</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -27327,16 +27339,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>949779</v>
+        <v>189956</v>
       </c>
       <c r="C13" t="n">
         <v>12.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1065652</v>
+        <v>213130</v>
       </c>
       <c r="E13" t="n">
-        <v>780548</v>
+        <v>156110</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -27369,16 +27381,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1065652</v>
+        <v>213130</v>
       </c>
       <c r="C14" t="n">
         <v>4.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1110409</v>
+        <v>222082</v>
       </c>
       <c r="E14" t="n">
-        <v>790696</v>
+        <v>158139</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -27411,16 +27423,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1110409</v>
+        <v>222082</v>
       </c>
       <c r="C15" t="n">
         <v>-6.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1039343</v>
+        <v>207869</v>
       </c>
       <c r="E15" t="n">
-        <v>742463</v>
+        <v>148493</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -27453,16 +27465,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1039343</v>
+        <v>207869</v>
       </c>
       <c r="C16" t="n">
         <v>3.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1073641</v>
+        <v>214728</v>
       </c>
       <c r="E16" t="n">
-        <v>771419</v>
+        <v>154284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -27495,16 +27507,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1073641</v>
+        <v>214728</v>
       </c>
       <c r="C17" t="n">
         <v>1.9</v>
       </c>
       <c r="D17" t="n">
-        <v>1094041</v>
+        <v>218808</v>
       </c>
       <c r="E17" t="n">
-        <v>802276</v>
+        <v>160455</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -27537,16 +27549,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1094041</v>
+        <v>218808</v>
       </c>
       <c r="C18" t="n">
         <v>2.7</v>
       </c>
       <c r="D18" t="n">
-        <v>1123580</v>
+        <v>224716</v>
       </c>
       <c r="E18" t="n">
-        <v>820728</v>
+        <v>164146</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -27579,16 +27591,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1123580</v>
+        <v>224716</v>
       </c>
       <c r="C19" t="n">
         <v>-1.6</v>
       </c>
       <c r="D19" t="n">
-        <v>1105602</v>
+        <v>221120</v>
       </c>
       <c r="E19" t="n">
-        <v>801031</v>
+        <v>160206</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -27621,16 +27633,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1105602</v>
+        <v>221120</v>
       </c>
       <c r="C20" t="n">
         <v>0.8</v>
       </c>
       <c r="D20" t="n">
-        <v>1114447</v>
+        <v>222889</v>
       </c>
       <c r="E20" t="n">
-        <v>763382</v>
+        <v>152676</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -27663,16 +27675,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="C21" t="n">
         <v>122.9</v>
       </c>
       <c r="D21" t="n">
-        <v>1114447</v>
+        <v>222889</v>
       </c>
       <c r="E21" t="n">
-        <v>763382</v>
+        <v>152676</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -27699,17 +27711,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>% of Capital</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Holdings</t>
         </is>
@@ -27723,7 +27735,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27745,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27760,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27763,7 +27775,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -27772,33 +27784,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27820,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27835,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27882,12 +27894,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Market" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="About" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,16 +25,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,21 +50,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,12 +425,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TODAY</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -456,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -501,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -548,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (55)</t>
+          <t>BRITANNIA (50)</t>
         </is>
       </c>
     </row>
@@ -560,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BRITANNIA, IRCTC, KOTAKBANK</t>
         </is>
       </c>
     </row>
@@ -572,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MARICO, PIDILITIND, SBILIFE</t>
         </is>
       </c>
     </row>
@@ -583,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -649,12 +637,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -700,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-17  /  2026-07-17</t>
+          <t>2026-07-22  /  2026-07-22</t>
         </is>
       </c>
     </row>
@@ -736,7 +724,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rs1L</t>
+          <t>Rs5L</t>
         </is>
       </c>
     </row>
@@ -748,7 +736,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rs60,000 (60%)</t>
+          <t>Rs300,000 (60%)</t>
         </is>
       </c>
     </row>
@@ -760,7 +748,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rs40,000 (40%)</t>
+          <t>Rs200,000 (40%)</t>
         </is>
       </c>
     </row>
@@ -772,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -816,7 +804,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs102,500</t>
+          <t>Rs512,500</t>
         </is>
       </c>
     </row>
@@ -828,7 +816,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rs120,400</t>
+          <t>Rs602,000</t>
         </is>
       </c>
     </row>
@@ -840,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rs91,600</t>
+          <t>Rs458,000</t>
         </is>
       </c>
     </row>
@@ -908,7 +896,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
+          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -932,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1136,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rs1L -&gt; Rs222,889 (2.23x)</t>
+          <t>Rs5L -&gt; Rs1,114,447 (2.23x)</t>
         </is>
       </c>
     </row>
@@ -1377,142 +1365,142 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Portfolio Suitability</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Suitability Breakdown</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Top Factor</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Weakest Factor</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>F: Historical</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>F: Technical/Trend</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>F: Risk/Vol</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>F: Sector</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>F: Regime</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Buy Range</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Expected Range (hist)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Prob +ve</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Rec Confidence %</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Recommended Holding</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Allocation Rs</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Weight %</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Selected Because</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Not Evaluated</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Why This vs Alternatives</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Why</t>
         </is>
@@ -1546,10 +1534,10 @@
         <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I2" t="n">
         <v>94</v>
@@ -1568,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8848.5</v>
+        <v>8905</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8639 - 9058</t>
+          <t>8696 - 9114</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1590,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+15.1%)</t>
+          <t>Above 200-DMA (+15.5%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1603,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>35620</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>12.3</v>
+        <v>14.1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1627,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — APOLLOHOSP: 81; FORTIS: 72, MAXHEALTH: 69, LALPATHLAB: 63</t>
+          <t>No same-sector peer in the universe.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+15.1%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+15.5%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1643,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +9 = 78</t>
+          <t>Risk/Vol +24 · Trend/Tech +19 · Historical +18 · Regime +9 · Sector +9 = 79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1664,10 +1652,10 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H3" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I3" t="n">
         <v>88</v>
@@ -1686,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1940.5</v>
+        <v>1941.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1887 - 1994</t>
+          <t>1888 - 1995</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1704,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.5%)</t>
+          <t>Above 200-DMA (+10.2%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1721,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>3881</v>
+        <v>23299</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1745,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 78; TORNTPHARM: 83, ABBOTINDIA: 78, ALKEM: 76. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; LUPIN: 74, ZYDUSLIFE: 74, BIOCON: 73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.5%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.2%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1761,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +5 = 75</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +6 = 76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1779,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I4" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>830.3</v>
+        <v>1450.7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>811 - 850</t>
+          <t>1409 - 1492</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.3%)</t>
+          <t>Above 200-DMA (+7.7%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1839,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>5812</v>
+        <v>18859</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X4" t="n">
-        <v>10.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1863,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — MARICO: 75; NESTLEIND: 75, UNITDSPR: 65, HINDUNILVR: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; FEDERALBNK: 69, LICI: 66, SBIN: 65</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • above 200-dma (+8.3%) • outperforming Nifty • sector strength 53/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +3.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.7%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1879,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +9 = 75</t>
+          <t>Risk/Vol +24 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +9 = 74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1900,10 +1888,10 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H5" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I5" t="n">
         <v>88</v>
@@ -1922,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2447</v>
+        <v>2446.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2386 - 2508</t>
+          <t>2384 - 2509</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1940,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.4%)</t>
+          <t>Above 200-DMA (+11.0%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1957,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>4894</v>
+        <v>26913</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1981,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 75; TORNTPHARM: 83, ABBOTINDIA: 78, SUNPHARMA: 78. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 74; SUNPHARMA: 79, ZYDUSLIFE: 74, BIOCON: 73. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.4%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1997,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +4 = 74</t>
+          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +8 = 73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2015,58 +2003,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G6" t="n">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1435.2</v>
+        <v>1942.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1394 - 1476</t>
+          <t>1889 - 1997</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>-3% to +15%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.7%)</t>
+          <t>Below 200-DMA (-0.4%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2075,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>2870</v>
+        <v>25256</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="X6" t="n">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2099,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 74; FEDERALBNK: 70, SBIN: 65, LICI: 64</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 73; TATACOMM: 55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.7%) • outperforming Nifty • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-0.4%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -2115,76 +2103,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +7 = 72</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +4 · Trend/Tech +3 = 65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I7" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1910.9</v>
+        <v>347.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1858 - 1964</t>
+          <t>338 - 357</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.1%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2193,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>3822</v>
+        <v>29872</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="X7" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2217,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 72; INDUSTOWER: 58, TATACOMM: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 66, POWERGRID: 58, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.1%) • sector strength 71/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-2.7%) • sector strength 41/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Trend/Tech +17 · Historical +14 · Regime +9 · Sector +6 = 68</t>
+          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +6 · Sector +6 = 62</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2251,54 +2239,54 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
         <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>1564.6</v>
+        <v>383</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1515 - 1614</t>
+          <t>371 - 395</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.7%)</t>
+          <t>Below 200-DMA (-5.4%)</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -2311,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>4694</v>
+        <v>22977</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="X8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2335,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; NAVINFLUOR: 61, BALRAMCHIN: 60, DEEPAKNTR: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 62; ICICIBANK: 76, FEDERALBNK: 69, LICI: 66. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+6.7%) • outperforming Nifty • sector strength 65/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.4%) • sector strength 59/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2351,16 +2339,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +7 · Sector +4 = 60</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2369,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H9" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>341.7</v>
+        <v>1299.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>332 - 351</t>
+          <t>1261 - 1338</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1% to +7%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.2%)</t>
+          <t>Below 200-DMA (-8.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2429,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>3417</v>
+        <v>16888</v>
       </c>
       <c r="W9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="X9" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2453,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 57, NHPC: 55, TATAPOWER: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 60; IOC: 50, OIL: 48, ONGC: 48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.2%) • sector strength 29/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.1%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2469,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +7 · Sector +2 = 59</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +4 = 58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2490,55 +2478,55 @@
         <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I10" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1321.2</v>
+        <v>285.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1282 - 1360</t>
+          <t>277 - 294</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-1% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.6%)</t>
+          <t>Below 200-DMA (-0.3%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2547,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>3964</v>
+        <v>22816</v>
       </c>
       <c r="W10" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="X10" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2571,27 +2559,27 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 59; GAIL: 60, IOC: 48, ONGC: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NHPC: 66, NTPC: 65, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-6.6%) • sector strength 18/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.3%) • sector strength 41/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +16 · Regime +9 · Trend/Tech +6 · Sector +4 = 58</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2605,58 +2593,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1812.7</v>
+        <v>279.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1759 - 1867</t>
+          <t>272 - 287</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.6%)</t>
+          <t>Below 200-DMA (-17.1%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2665,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>3625</v>
+        <v>22380</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="X11" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2689,27 +2677,27 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBILIFE: 58; ICICIBANK: 74, FEDERALBNK: 70, SBIN: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; TATACONSUM: 55, COLPAL: 51, DABUR: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.6%) • sector strength 35/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +0.0%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 12/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +3 = 57</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +5 · Sector +5 = 53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2723,36 +2711,36 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I12" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>282.5</v>
+        <v>497.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>274 - 291</t>
+          <t>482 - 513</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2766,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.2%)</t>
+          <t>Below 200-DMA (-17.5%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2783,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>3108</v>
+        <v>14928</v>
       </c>
       <c r="W12" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2807,27 +2795,27 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 64, NHPC: 55, TATAPOWER: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 60, INDIGO: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-1.2%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.5%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Sector +5 · Trend/Tech +4 = 55</t>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +6 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2837,27 +2825,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="H13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I13" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2866,33 +2854,33 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>279.6</v>
+        <v>5450.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>272 - 287</t>
+          <t>5307 - 5594</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.6%)</t>
+          <t>Below 200-DMA (-4.8%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2901,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>5872</v>
+        <v>27252</v>
       </c>
       <c r="W13" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="X13" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2925,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; MARICO: 75, NESTLEIND: 75, UNITDSPR: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; TATACONSUM: 55, COLPAL: 51, DABUR: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.6%) • sector strength 53/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.8%) • sector strength 12/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2949,77 +2937,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Start Rs</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>End Rs</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Year Ret %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Beat Nifty</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Cycles</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Picks</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Win %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Winners</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Losers</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Avg Return %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Median %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Best %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Worst %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
         </is>
@@ -3030,10 +3018,10 @@
         <v>2021</v>
       </c>
       <c r="B2" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C2" t="n">
-        <v>108546</v>
+        <v>542732</v>
       </c>
       <c r="D2" t="n">
         <v>8.5</v>
@@ -3071,7 +3059,7 @@
         <v>-14.9</v>
       </c>
       <c r="O2" t="n">
-        <v>3480</v>
+        <v>43738</v>
       </c>
     </row>
     <row r="3">
@@ -3079,10 +3067,10 @@
         <v>2022</v>
       </c>
       <c r="B3" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C3" t="n">
-        <v>120141</v>
+        <v>600703</v>
       </c>
       <c r="D3" t="n">
         <v>20.1</v>
@@ -3120,7 +3108,7 @@
         <v>-19.8</v>
       </c>
       <c r="O3" t="n">
-        <v>19532</v>
+        <v>93560</v>
       </c>
     </row>
     <row r="4">
@@ -3128,10 +3116,10 @@
         <v>2023</v>
       </c>
       <c r="B4" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C4" t="n">
-        <v>144506</v>
+        <v>722531</v>
       </c>
       <c r="D4" t="n">
         <v>44.5</v>
@@ -3169,7 +3157,7 @@
         <v>-16.5</v>
       </c>
       <c r="O4" t="n">
-        <v>30402</v>
+        <v>176947</v>
       </c>
     </row>
     <row r="5">
@@ -3177,10 +3165,10 @@
         <v>2024</v>
       </c>
       <c r="B5" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C5" t="n">
-        <v>110305</v>
+        <v>551527</v>
       </c>
       <c r="D5" t="n">
         <v>10.3</v>
@@ -3218,7 +3206,7 @@
         <v>-26</v>
       </c>
       <c r="O5" t="n">
-        <v>7395</v>
+        <v>56158</v>
       </c>
     </row>
     <row r="6">
@@ -3226,10 +3214,10 @@
         <v>2025</v>
       </c>
       <c r="B6" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C6" t="n">
-        <v>106375</v>
+        <v>531876</v>
       </c>
       <c r="D6" t="n">
         <v>6.4</v>
@@ -3267,7 +3255,7 @@
         <v>-23.6</v>
       </c>
       <c r="O6" t="n">
-        <v>157</v>
+        <v>15954</v>
       </c>
     </row>
     <row r="7">
@@ -3275,10 +3263,10 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C7" t="n">
-        <v>100800</v>
+        <v>504000</v>
       </c>
       <c r="D7" t="n">
         <v>0.8</v>
@@ -3316,7 +3304,7 @@
         <v>-16.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1322</v>
+        <v>7126</v>
       </c>
     </row>
   </sheetData>
@@ -3334,107 +3322,107 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Rec ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Buy Price</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Shares</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Invested Rs</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Exit Value Rs</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Profit Rs</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Contribution %</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Max Profit %</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Max Loss %</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Captured %</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CAGR %</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Holding Days</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Rank in Universe</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Why Picked</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3468,16 +3456,16 @@
         <v>22031.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>66945</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>88125</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>21180</v>
       </c>
       <c r="K2" t="n">
         <v>31.64</v>
@@ -3549,16 +3537,16 @@
         <v>4737.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>3618</v>
+        <v>32560</v>
       </c>
       <c r="I3" t="n">
-        <v>4737</v>
+        <v>42637</v>
       </c>
       <c r="J3" t="n">
-        <v>1120</v>
+        <v>10077</v>
       </c>
       <c r="K3" t="n">
         <v>30.95</v>
@@ -3630,16 +3618,16 @@
         <v>675.9</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H4" t="n">
-        <v>3136</v>
+        <v>16725</v>
       </c>
       <c r="I4" t="n">
-        <v>4055</v>
+        <v>21629</v>
       </c>
       <c r="J4" t="n">
-        <v>920</v>
+        <v>4904</v>
       </c>
       <c r="K4" t="n">
         <v>29.32</v>
@@ -3711,16 +3699,16 @@
         <v>3990.05</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>6439</v>
+        <v>32195</v>
       </c>
       <c r="I5" t="n">
-        <v>7980</v>
+        <v>39900</v>
       </c>
       <c r="J5" t="n">
-        <v>1541</v>
+        <v>7706</v>
       </c>
       <c r="K5" t="n">
         <v>23.93</v>
@@ -3792,16 +3780,16 @@
         <v>1834.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
-        <v>3194</v>
+        <v>19162</v>
       </c>
       <c r="I6" t="n">
-        <v>3669</v>
+        <v>22016</v>
       </c>
       <c r="J6" t="n">
-        <v>476</v>
+        <v>2854</v>
       </c>
       <c r="K6" t="n">
         <v>14.89</v>
@@ -3873,16 +3861,16 @@
         <v>3730.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>3342</v>
+        <v>20049</v>
       </c>
       <c r="I7" t="n">
-        <v>3730</v>
+        <v>22381</v>
       </c>
       <c r="J7" t="n">
-        <v>389</v>
+        <v>2332</v>
       </c>
       <c r="K7" t="n">
         <v>11.63</v>
@@ -3954,16 +3942,16 @@
         <v>1208.63</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H8" t="n">
-        <v>3254</v>
+        <v>20607</v>
       </c>
       <c r="I8" t="n">
-        <v>3626</v>
+        <v>22964</v>
       </c>
       <c r="J8" t="n">
-        <v>372</v>
+        <v>2357</v>
       </c>
       <c r="K8" t="n">
         <v>11.44</v>
@@ -4035,16 +4023,16 @@
         <v>3921.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>7192</v>
+        <v>39554</v>
       </c>
       <c r="I9" t="n">
-        <v>7842</v>
+        <v>43132</v>
       </c>
       <c r="J9" t="n">
-        <v>651</v>
+        <v>3578</v>
       </c>
       <c r="K9" t="n">
         <v>9.050000000000001</v>
@@ -4116,16 +4104,16 @@
         <v>9740.799999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>35809</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>38963</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3154</v>
       </c>
       <c r="K10" t="n">
         <v>8.81</v>
@@ -4197,16 +4185,16 @@
         <v>2321.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>6524</v>
+        <v>34794</v>
       </c>
       <c r="I11" t="n">
-        <v>6965</v>
+        <v>37146</v>
       </c>
       <c r="J11" t="n">
-        <v>441</v>
+        <v>2351</v>
       </c>
       <c r="K11" t="n">
         <v>6.76</v>
@@ -4278,16 +4266,16 @@
         <v>1665.15</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>3121</v>
+        <v>20285</v>
       </c>
       <c r="I12" t="n">
-        <v>3330</v>
+        <v>21647</v>
       </c>
       <c r="J12" t="n">
-        <v>210</v>
+        <v>1362</v>
       </c>
       <c r="K12" t="n">
         <v>6.71</v>
@@ -4359,16 +4347,16 @@
         <v>729.45</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="H13" t="n">
-        <v>6858</v>
+        <v>34973</v>
       </c>
       <c r="I13" t="n">
-        <v>7294</v>
+        <v>37202</v>
       </c>
       <c r="J13" t="n">
-        <v>437</v>
+        <v>2229</v>
       </c>
       <c r="K13" t="n">
         <v>6.37</v>
@@ -4440,16 +4428,16 @@
         <v>1687.8</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H14" t="n">
-        <v>10249</v>
+        <v>58079</v>
       </c>
       <c r="I14" t="n">
-        <v>10127</v>
+        <v>57385</v>
       </c>
       <c r="J14" t="n">
-        <v>-122</v>
+        <v>-694</v>
       </c>
       <c r="K14" t="n">
         <v>-1.19</v>
@@ -4521,16 +4509,16 @@
         <v>178.85</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="H15" t="n">
-        <v>4002</v>
+        <v>20373</v>
       </c>
       <c r="I15" t="n">
-        <v>3935</v>
+        <v>20031</v>
       </c>
       <c r="J15" t="n">
-        <v>-67</v>
+        <v>-342</v>
       </c>
       <c r="K15" t="n">
         <v>-1.68</v>
@@ -4602,16 +4590,16 @@
         <v>1928.9</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>4228</v>
+        <v>29596</v>
       </c>
       <c r="I16" t="n">
-        <v>3858</v>
+        <v>27005</v>
       </c>
       <c r="J16" t="n">
-        <v>-370</v>
+        <v>-2591</v>
       </c>
       <c r="K16" t="n">
         <v>-8.76</v>
@@ -4683,16 +4671,16 @@
         <v>1898.45</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H17" t="n">
-        <v>4995</v>
+        <v>31638</v>
       </c>
       <c r="I17" t="n">
-        <v>5695</v>
+        <v>36071</v>
       </c>
       <c r="J17" t="n">
-        <v>700</v>
+        <v>4433</v>
       </c>
       <c r="K17" t="n">
         <v>14.01</v>
@@ -4764,16 +4752,16 @@
         <v>30.95</v>
       </c>
       <c r="G18" t="n">
-        <v>159</v>
+        <v>799</v>
       </c>
       <c r="H18" t="n">
-        <v>4516</v>
+        <v>22692</v>
       </c>
       <c r="I18" t="n">
-        <v>4921</v>
+        <v>24729</v>
       </c>
       <c r="J18" t="n">
-        <v>405</v>
+        <v>2037</v>
       </c>
       <c r="K18" t="n">
         <v>8.98</v>
@@ -4845,16 +4833,16 @@
         <v>31.2</v>
       </c>
       <c r="G19" t="n">
-        <v>142</v>
+        <v>714</v>
       </c>
       <c r="H19" t="n">
-        <v>4132</v>
+        <v>20777</v>
       </c>
       <c r="I19" t="n">
-        <v>4430</v>
+        <v>22277</v>
       </c>
       <c r="J19" t="n">
-        <v>298</v>
+        <v>1499</v>
       </c>
       <c r="K19" t="n">
         <v>7.22</v>
@@ -4926,16 +4914,16 @@
         <v>1626.05</v>
       </c>
       <c r="G20" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H20" t="n">
-        <v>7701</v>
+        <v>41588</v>
       </c>
       <c r="I20" t="n">
-        <v>8130</v>
+        <v>43903</v>
       </c>
       <c r="J20" t="n">
-        <v>429</v>
+        <v>2316</v>
       </c>
       <c r="K20" t="n">
         <v>5.57</v>
@@ -5007,16 +4995,16 @@
         <v>1236.98</v>
       </c>
       <c r="G21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H21" t="n">
-        <v>6043</v>
+        <v>30216</v>
       </c>
       <c r="I21" t="n">
-        <v>6185</v>
+        <v>30924</v>
       </c>
       <c r="J21" t="n">
-        <v>142</v>
+        <v>709</v>
       </c>
       <c r="K21" t="n">
         <v>2.35</v>
@@ -5088,16 +5076,16 @@
         <v>3817.75</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>3730</v>
+        <v>26111</v>
       </c>
       <c r="I22" t="n">
-        <v>3818</v>
+        <v>26724</v>
       </c>
       <c r="J22" t="n">
-        <v>88</v>
+        <v>613</v>
       </c>
       <c r="K22" t="n">
         <v>2.35</v>
@@ -5169,16 +5157,16 @@
         <v>1209.4</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H23" t="n">
-        <v>6045</v>
+        <v>35062</v>
       </c>
       <c r="I23" t="n">
-        <v>6047</v>
+        <v>35073</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
         <v>0.03</v>
@@ -5250,16 +5238,16 @@
         <v>1091.18</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H24" t="n">
-        <v>6873</v>
+        <v>35513</v>
       </c>
       <c r="I24" t="n">
-        <v>6547</v>
+        <v>33827</v>
       </c>
       <c r="J24" t="n">
-        <v>-326</v>
+        <v>-1686</v>
       </c>
       <c r="K24" t="n">
         <v>-4.75</v>
@@ -5331,16 +5319,16 @@
         <v>9043.200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>19482</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>18086</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1395</v>
       </c>
       <c r="K25" t="n">
         <v>-7.16</v>
@@ -5412,16 +5400,16 @@
         <v>3617.55</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>7842</v>
+        <v>47053</v>
       </c>
       <c r="I26" t="n">
-        <v>7235</v>
+        <v>43411</v>
       </c>
       <c r="J26" t="n">
-        <v>-607</v>
+        <v>-3643</v>
       </c>
       <c r="K26" t="n">
         <v>-7.74</v>
@@ -5493,16 +5481,16 @@
         <v>650.5</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H27" t="n">
-        <v>7294</v>
+        <v>36472</v>
       </c>
       <c r="I27" t="n">
-        <v>6505</v>
+        <v>32525</v>
       </c>
       <c r="J27" t="n">
-        <v>-790</v>
+        <v>-3948</v>
       </c>
       <c r="K27" t="n">
         <v>-10.82</v>
@@ -5574,16 +5562,16 @@
         <v>1917.45</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>6541</v>
+        <v>37067</v>
       </c>
       <c r="I28" t="n">
-        <v>5752</v>
+        <v>32597</v>
       </c>
       <c r="J28" t="n">
-        <v>-789</v>
+        <v>-4470</v>
       </c>
       <c r="K28" t="n">
         <v>-12.06</v>
@@ -5649,16 +5637,16 @@
         <v>2476.6</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>2848</v>
+        <v>25632</v>
       </c>
       <c r="I29" t="n">
-        <v>2477</v>
+        <v>22289</v>
       </c>
       <c r="J29" t="n">
-        <v>-371</v>
+        <v>-3342</v>
       </c>
       <c r="K29" t="n">
         <v>-13.04</v>
@@ -5730,16 +5718,16 @@
         <v>1463.8</v>
       </c>
       <c r="G30" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H30" t="n">
-        <v>8439</v>
+        <v>43883</v>
       </c>
       <c r="I30" t="n">
-        <v>7319</v>
+        <v>38059</v>
       </c>
       <c r="J30" t="n">
-        <v>-1120</v>
+        <v>-5824</v>
       </c>
       <c r="K30" t="n">
         <v>-13.27</v>
@@ -5811,16 +5799,16 @@
         <v>3277.1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>3853</v>
+        <v>26968</v>
       </c>
       <c r="I31" t="n">
-        <v>3277</v>
+        <v>22940</v>
       </c>
       <c r="J31" t="n">
-        <v>-576</v>
+        <v>-4028</v>
       </c>
       <c r="K31" t="n">
         <v>-14.94</v>
@@ -5892,16 +5880,16 @@
         <v>3809.7</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>3277</v>
+        <v>19663</v>
       </c>
       <c r="I32" t="n">
-        <v>3810</v>
+        <v>22858</v>
       </c>
       <c r="J32" t="n">
-        <v>533</v>
+        <v>3196</v>
       </c>
       <c r="K32" t="n">
         <v>16.25</v>
@@ -5973,16 +5961,16 @@
         <v>1586.7</v>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H33" t="n">
-        <v>11710</v>
+        <v>62943</v>
       </c>
       <c r="I33" t="n">
-        <v>12694</v>
+        <v>68228</v>
       </c>
       <c r="J33" t="n">
-        <v>983</v>
+        <v>5285</v>
       </c>
       <c r="K33" t="n">
         <v>8.4</v>
@@ -6054,16 +6042,16 @@
         <v>804.13</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="H34" t="n">
-        <v>8358</v>
+        <v>43310</v>
       </c>
       <c r="I34" t="n">
-        <v>8845</v>
+        <v>45835</v>
       </c>
       <c r="J34" t="n">
-        <v>487</v>
+        <v>2525</v>
       </c>
       <c r="K34" t="n">
         <v>5.83</v>
@@ -6135,16 +6123,16 @@
         <v>1253.83</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H35" t="n">
-        <v>8659</v>
+        <v>44531</v>
       </c>
       <c r="I35" t="n">
-        <v>8777</v>
+        <v>45138</v>
       </c>
       <c r="J35" t="n">
-        <v>118</v>
+        <v>607</v>
       </c>
       <c r="K35" t="n">
         <v>1.36</v>
@@ -6216,16 +6204,16 @@
         <v>3814.8</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>3818</v>
+        <v>34360</v>
       </c>
       <c r="I36" t="n">
-        <v>3815</v>
+        <v>34333</v>
       </c>
       <c r="J36" t="n">
-        <v>-3</v>
+        <v>-27</v>
       </c>
       <c r="K36" t="n">
         <v>-0.08</v>
@@ -6297,16 +6285,16 @@
         <v>1861.1</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H37" t="n">
-        <v>5695</v>
+        <v>36071</v>
       </c>
       <c r="I37" t="n">
-        <v>5583</v>
+        <v>35361</v>
       </c>
       <c r="J37" t="n">
-        <v>-112</v>
+        <v>-710</v>
       </c>
       <c r="K37" t="n">
         <v>-1.97</v>
@@ -6378,16 +6366,16 @@
         <v>1836.05</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H38" t="n">
-        <v>3846</v>
+        <v>23074</v>
       </c>
       <c r="I38" t="n">
-        <v>3672</v>
+        <v>22033</v>
       </c>
       <c r="J38" t="n">
-        <v>-174</v>
+        <v>-1042</v>
       </c>
       <c r="K38" t="n">
         <v>-4.51</v>
@@ -6459,16 +6447,16 @@
         <v>828.65</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>3504</v>
+        <v>21024</v>
       </c>
       <c r="I39" t="n">
-        <v>3315</v>
+        <v>19888</v>
       </c>
       <c r="J39" t="n">
-        <v>-189</v>
+        <v>-1136</v>
       </c>
       <c r="K39" t="n">
         <v>-5.41</v>
@@ -6540,16 +6528,16 @@
         <v>2332.25</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>2477</v>
+        <v>22289</v>
       </c>
       <c r="I40" t="n">
-        <v>2332</v>
+        <v>20990</v>
       </c>
       <c r="J40" t="n">
-        <v>-144</v>
+        <v>-1299</v>
       </c>
       <c r="K40" t="n">
         <v>-5.83</v>
@@ -6702,16 +6690,16 @@
         <v>1701.8</v>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>7423</v>
+        <v>37115</v>
       </c>
       <c r="I42" t="n">
-        <v>6807</v>
+        <v>34036</v>
       </c>
       <c r="J42" t="n">
-        <v>-616</v>
+        <v>-3079</v>
       </c>
       <c r="K42" t="n">
         <v>-8.300000000000001</v>
@@ -6783,16 +6771,16 @@
         <v>901.16</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H43" t="n">
-        <v>8855</v>
+        <v>45259</v>
       </c>
       <c r="I43" t="n">
-        <v>8110</v>
+        <v>41453</v>
       </c>
       <c r="J43" t="n">
-        <v>-745</v>
+        <v>-3806</v>
       </c>
       <c r="K43" t="n">
         <v>-8.41</v>
@@ -6864,16 +6852,16 @@
         <v>199.6</v>
       </c>
       <c r="G44" t="n">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="H44" t="n">
-        <v>7220</v>
+        <v>36540</v>
       </c>
       <c r="I44" t="n">
-        <v>6587</v>
+        <v>33333</v>
       </c>
       <c r="J44" t="n">
-        <v>-634</v>
+        <v>-3206</v>
       </c>
       <c r="K44" t="n">
         <v>-8.779999999999999</v>
@@ -6945,16 +6933,16 @@
         <v>569.65</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H45" t="n">
-        <v>4554</v>
+        <v>24068</v>
       </c>
       <c r="I45" t="n">
-        <v>3988</v>
+        <v>21077</v>
       </c>
       <c r="J45" t="n">
-        <v>-566</v>
+        <v>-2991</v>
       </c>
       <c r="K45" t="n">
         <v>-12.43</v>
@@ -7026,16 +7014,16 @@
         <v>6726.15</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>15448</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>13452</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>-1996</v>
       </c>
       <c r="K46" t="n">
         <v>-12.92</v>
@@ -7107,16 +7095,16 @@
         <v>2350.15</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H47" t="n">
-        <v>6807</v>
+        <v>39141</v>
       </c>
       <c r="I47" t="n">
-        <v>9401</v>
+        <v>54053</v>
       </c>
       <c r="J47" t="n">
-        <v>2593</v>
+        <v>14912</v>
       </c>
       <c r="K47" t="n">
         <v>38.1</v>
@@ -7188,16 +7176,16 @@
         <v>979.3</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H48" t="n">
-        <v>4944</v>
+        <v>27194</v>
       </c>
       <c r="I48" t="n">
-        <v>5876</v>
+        <v>32317</v>
       </c>
       <c r="J48" t="n">
-        <v>932</v>
+        <v>5123</v>
       </c>
       <c r="K48" t="n">
         <v>18.84</v>
@@ -7269,16 +7257,16 @@
         <v>220.95</v>
       </c>
       <c r="G49" t="n">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="H49" t="n">
-        <v>5190</v>
+        <v>26347</v>
       </c>
       <c r="I49" t="n">
-        <v>5745</v>
+        <v>29165</v>
       </c>
       <c r="J49" t="n">
-        <v>555</v>
+        <v>2818</v>
       </c>
       <c r="K49" t="n">
         <v>10.7</v>
@@ -7431,16 +7419,16 @@
         <v>919.4400000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H51" t="n">
-        <v>9913</v>
+        <v>49564</v>
       </c>
       <c r="I51" t="n">
-        <v>10114</v>
+        <v>50569</v>
       </c>
       <c r="J51" t="n">
-        <v>201</v>
+        <v>1005</v>
       </c>
       <c r="K51" t="n">
         <v>2.03</v>
@@ -7512,16 +7500,16 @@
         <v>878</v>
       </c>
       <c r="G52" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H52" t="n">
-        <v>5196</v>
+        <v>28577</v>
       </c>
       <c r="I52" t="n">
-        <v>5268</v>
+        <v>28974</v>
       </c>
       <c r="J52" t="n">
-        <v>72</v>
+        <v>397</v>
       </c>
       <c r="K52" t="n">
         <v>1.39</v>
@@ -7593,16 +7581,16 @@
         <v>3773.05</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>3810</v>
+        <v>22858</v>
       </c>
       <c r="I53" t="n">
-        <v>3773</v>
+        <v>22638</v>
       </c>
       <c r="J53" t="n">
-        <v>-37</v>
+        <v>-220</v>
       </c>
       <c r="K53" t="n">
         <v>-0.96</v>
@@ -7674,16 +7662,16 @@
         <v>1569.15</v>
       </c>
       <c r="G54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H54" t="n">
-        <v>7934</v>
+        <v>39668</v>
       </c>
       <c r="I54" t="n">
-        <v>7846</v>
+        <v>39229</v>
       </c>
       <c r="J54" t="n">
-        <v>-88</v>
+        <v>-439</v>
       </c>
       <c r="K54" t="n">
         <v>-1.11</v>
@@ -7755,16 +7743,16 @@
         <v>1232.25</v>
       </c>
       <c r="G55" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H55" t="n">
-        <v>4056</v>
+        <v>24333</v>
       </c>
       <c r="I55" t="n">
-        <v>3697</v>
+        <v>22180</v>
       </c>
       <c r="J55" t="n">
-        <v>-359</v>
+        <v>-2153</v>
       </c>
       <c r="K55" t="n">
         <v>-8.85</v>
@@ -7836,16 +7824,16 @@
         <v>693.95</v>
       </c>
       <c r="G56" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H56" t="n">
-        <v>7666</v>
+        <v>39863</v>
       </c>
       <c r="I56" t="n">
-        <v>6940</v>
+        <v>36085</v>
       </c>
       <c r="J56" t="n">
-        <v>-726</v>
+        <v>-3778</v>
       </c>
       <c r="K56" t="n">
         <v>-9.48</v>
@@ -7917,16 +7905,16 @@
         <v>837.7</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H57" t="n">
-        <v>5575</v>
+        <v>27873</v>
       </c>
       <c r="I57" t="n">
-        <v>5026</v>
+        <v>25131</v>
       </c>
       <c r="J57" t="n">
-        <v>-548</v>
+        <v>-2742</v>
       </c>
       <c r="K57" t="n">
         <v>-9.84</v>
@@ -7998,16 +7986,16 @@
         <v>19.95</v>
       </c>
       <c r="G58" t="n">
-        <v>358</v>
+        <v>1790</v>
       </c>
       <c r="H58" t="n">
-        <v>7930</v>
+        <v>39648</v>
       </c>
       <c r="I58" t="n">
-        <v>7142</v>
+        <v>35710</v>
       </c>
       <c r="J58" t="n">
-        <v>-788</v>
+        <v>-3938</v>
       </c>
       <c r="K58" t="n">
         <v>-9.93</v>
@@ -8079,16 +8067,16 @@
         <v>3260.75</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>7630</v>
+        <v>38148</v>
       </c>
       <c r="I59" t="n">
-        <v>6522</v>
+        <v>32608</v>
       </c>
       <c r="J59" t="n">
-        <v>-1108</v>
+        <v>-5540</v>
       </c>
       <c r="K59" t="n">
         <v>-14.52</v>
@@ -8158,16 +8146,16 @@
         <v>1556.15</v>
       </c>
       <c r="G60" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H60" t="n">
-        <v>3672</v>
+        <v>23869</v>
       </c>
       <c r="I60" t="n">
-        <v>3112</v>
+        <v>20230</v>
       </c>
       <c r="J60" t="n">
-        <v>-560</v>
+        <v>-3639</v>
       </c>
       <c r="K60" t="n">
         <v>-15.24</v>
@@ -8239,16 +8227,16 @@
         <v>1491.65</v>
       </c>
       <c r="G61" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H61" t="n">
-        <v>5583</v>
+        <v>31639</v>
       </c>
       <c r="I61" t="n">
-        <v>4475</v>
+        <v>25358</v>
       </c>
       <c r="J61" t="n">
-        <v>-1108</v>
+        <v>-6281</v>
       </c>
       <c r="K61" t="n">
         <v>-19.85</v>
@@ -8318,16 +8306,16 @@
         <v>32.7</v>
       </c>
       <c r="G62" t="n">
-        <v>163</v>
+        <v>819</v>
       </c>
       <c r="H62" t="n">
-        <v>4417</v>
+        <v>22195</v>
       </c>
       <c r="I62" t="n">
-        <v>5330</v>
+        <v>26781</v>
       </c>
       <c r="J62" t="n">
-        <v>913</v>
+        <v>4586</v>
       </c>
       <c r="K62" t="n">
         <v>20.66</v>
@@ -8399,16 +8387,16 @@
         <v>793.1</v>
       </c>
       <c r="G63" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H63" t="n">
-        <v>4858</v>
+        <v>24982</v>
       </c>
       <c r="I63" t="n">
-        <v>5552</v>
+        <v>28552</v>
       </c>
       <c r="J63" t="n">
-        <v>694</v>
+        <v>3569</v>
       </c>
       <c r="K63" t="n">
         <v>14.29</v>
@@ -8480,16 +8468,16 @@
         <v>955.15</v>
       </c>
       <c r="G64" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H64" t="n">
-        <v>6702</v>
+        <v>35183</v>
       </c>
       <c r="I64" t="n">
-        <v>7641</v>
+        <v>40116</v>
       </c>
       <c r="J64" t="n">
-        <v>940</v>
+        <v>4933</v>
       </c>
       <c r="K64" t="n">
         <v>14.02</v>
@@ -8561,16 +8549,16 @@
         <v>2014.85</v>
       </c>
       <c r="G65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H65" t="n">
-        <v>8860</v>
+        <v>44299</v>
       </c>
       <c r="I65" t="n">
-        <v>10074</v>
+        <v>50371</v>
       </c>
       <c r="J65" t="n">
-        <v>1214</v>
+        <v>6072</v>
       </c>
       <c r="K65" t="n">
         <v>13.71</v>
@@ -8723,16 +8711,16 @@
         <v>1238.75</v>
       </c>
       <c r="G67" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H67" t="n">
-        <v>5519</v>
+        <v>29804</v>
       </c>
       <c r="I67" t="n">
-        <v>6194</v>
+        <v>33446</v>
       </c>
       <c r="J67" t="n">
-        <v>674</v>
+        <v>3642</v>
       </c>
       <c r="K67" t="n">
         <v>12.22</v>
@@ -8804,16 +8792,16 @@
         <v>157.2</v>
       </c>
       <c r="G68" t="n">
-        <v>22</v>
+        <v>113</v>
       </c>
       <c r="H68" t="n">
-        <v>3120</v>
+        <v>16023</v>
       </c>
       <c r="I68" t="n">
-        <v>3458</v>
+        <v>17764</v>
       </c>
       <c r="J68" t="n">
-        <v>339</v>
+        <v>1740</v>
       </c>
       <c r="K68" t="n">
         <v>10.86</v>
@@ -8885,16 +8873,16 @@
         <v>21.35</v>
       </c>
       <c r="G69" t="n">
-        <v>361</v>
+        <v>1809</v>
       </c>
       <c r="H69" t="n">
-        <v>7202</v>
+        <v>36090</v>
       </c>
       <c r="I69" t="n">
-        <v>7707</v>
+        <v>38622</v>
       </c>
       <c r="J69" t="n">
-        <v>505</v>
+        <v>2533</v>
       </c>
       <c r="K69" t="n">
         <v>7.02</v>
@@ -8966,16 +8954,16 @@
         <v>966.05</v>
       </c>
       <c r="G70" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H70" t="n">
-        <v>8275</v>
+        <v>42294</v>
       </c>
       <c r="I70" t="n">
-        <v>8694</v>
+        <v>44438</v>
       </c>
       <c r="J70" t="n">
-        <v>419</v>
+        <v>2144</v>
       </c>
       <c r="K70" t="n">
         <v>5.07</v>
@@ -9047,16 +9035,16 @@
         <v>3200.3</v>
       </c>
       <c r="G71" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H71" t="n">
-        <v>9234</v>
+        <v>58483</v>
       </c>
       <c r="I71" t="n">
-        <v>9601</v>
+        <v>60806</v>
       </c>
       <c r="J71" t="n">
-        <v>367</v>
+        <v>2323</v>
       </c>
       <c r="K71" t="n">
         <v>3.97</v>
@@ -9128,16 +9116,16 @@
         <v>1010.7</v>
       </c>
       <c r="G72" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H72" t="n">
-        <v>4899</v>
+        <v>26453</v>
       </c>
       <c r="I72" t="n">
-        <v>5054</v>
+        <v>27289</v>
       </c>
       <c r="J72" t="n">
-        <v>155</v>
+        <v>836</v>
       </c>
       <c r="K72" t="n">
         <v>3.16</v>
@@ -9209,16 +9197,16 @@
         <v>1581.2</v>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H73" t="n">
-        <v>7846</v>
+        <v>45505</v>
       </c>
       <c r="I73" t="n">
-        <v>7906</v>
+        <v>45855</v>
       </c>
       <c r="J73" t="n">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="K73" t="n">
         <v>0.77</v>
@@ -9290,16 +9278,16 @@
         <v>157.05</v>
       </c>
       <c r="G74" t="n">
-        <v>49</v>
+        <v>248</v>
       </c>
       <c r="H74" t="n">
-        <v>7734</v>
+        <v>39144</v>
       </c>
       <c r="I74" t="n">
-        <v>7695</v>
+        <v>38948</v>
       </c>
       <c r="J74" t="n">
-        <v>-39</v>
+        <v>-196</v>
       </c>
       <c r="K74" t="n">
         <v>-0.5</v>
@@ -9371,16 +9359,16 @@
         <v>83.95999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="H75" t="n">
-        <v>4093</v>
+        <v>20723</v>
       </c>
       <c r="I75" t="n">
-        <v>4030</v>
+        <v>20402</v>
       </c>
       <c r="J75" t="n">
-        <v>-63</v>
+        <v>-321</v>
       </c>
       <c r="K75" t="n">
         <v>-1.55</v>
@@ -9452,16 +9440,16 @@
         <v>3064.9</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H76" t="n">
-        <v>3261</v>
+        <v>22825</v>
       </c>
       <c r="I76" t="n">
-        <v>3065</v>
+        <v>21454</v>
       </c>
       <c r="J76" t="n">
-        <v>-196</v>
+        <v>-1371</v>
       </c>
       <c r="K76" t="n">
         <v>-6.01</v>
@@ -9533,16 +9521,16 @@
         <v>72.45</v>
       </c>
       <c r="G77" t="n">
-        <v>142</v>
+        <v>712</v>
       </c>
       <c r="H77" t="n">
-        <v>5112</v>
+        <v>25632</v>
       </c>
       <c r="I77" t="n">
-        <v>10288</v>
+        <v>51584</v>
       </c>
       <c r="J77" t="n">
-        <v>5176</v>
+        <v>25952</v>
       </c>
       <c r="K77" t="n">
         <v>101.25</v>
@@ -9614,16 +9602,16 @@
         <v>32.7</v>
       </c>
       <c r="G78" t="n">
-        <v>570</v>
+        <v>2850</v>
       </c>
       <c r="H78" t="n">
-        <v>12170</v>
+        <v>60848</v>
       </c>
       <c r="I78" t="n">
-        <v>18639</v>
+        <v>93195</v>
       </c>
       <c r="J78" t="n">
-        <v>6470</v>
+        <v>32348</v>
       </c>
       <c r="K78" t="n">
         <v>53.16</v>
@@ -9695,16 +9683,16 @@
         <v>125.72</v>
       </c>
       <c r="G79" t="n">
-        <v>75</v>
+        <v>378</v>
       </c>
       <c r="H79" t="n">
-        <v>6297</v>
+        <v>31737</v>
       </c>
       <c r="I79" t="n">
-        <v>9429</v>
+        <v>47522</v>
       </c>
       <c r="J79" t="n">
-        <v>3132</v>
+        <v>15785</v>
       </c>
       <c r="K79" t="n">
         <v>49.74</v>
@@ -9776,16 +9764,16 @@
         <v>80.05</v>
       </c>
       <c r="G80" t="n">
-        <v>85</v>
+        <v>429</v>
       </c>
       <c r="H80" t="n">
-        <v>5733</v>
+        <v>28936</v>
       </c>
       <c r="I80" t="n">
-        <v>6804</v>
+        <v>34341</v>
       </c>
       <c r="J80" t="n">
-        <v>1071</v>
+        <v>5405</v>
       </c>
       <c r="K80" t="n">
         <v>18.68</v>
@@ -9857,16 +9845,16 @@
         <v>1032.8</v>
       </c>
       <c r="G81" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H81" t="n">
-        <v>4788</v>
+        <v>23942</v>
       </c>
       <c r="I81" t="n">
-        <v>5164</v>
+        <v>25820</v>
       </c>
       <c r="J81" t="n">
-        <v>376</v>
+        <v>1878</v>
       </c>
       <c r="K81" t="n">
         <v>7.84</v>
@@ -9938,16 +9926,16 @@
         <v>34.45</v>
       </c>
       <c r="G82" t="n">
-        <v>226</v>
+        <v>1134</v>
       </c>
       <c r="H82" t="n">
-        <v>7390</v>
+        <v>37082</v>
       </c>
       <c r="I82" t="n">
-        <v>7786</v>
+        <v>39066</v>
       </c>
       <c r="J82" t="n">
-        <v>396</v>
+        <v>1984</v>
       </c>
       <c r="K82" t="n">
         <v>5.35</v>
@@ -10019,16 +10007,16 @@
         <v>994.27</v>
       </c>
       <c r="G83" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H83" t="n">
-        <v>6762</v>
+        <v>35744</v>
       </c>
       <c r="I83" t="n">
-        <v>6960</v>
+        <v>36788</v>
       </c>
       <c r="J83" t="n">
-        <v>198</v>
+        <v>1044</v>
       </c>
       <c r="K83" t="n">
         <v>2.92</v>
@@ -10100,16 +10088,16 @@
         <v>3642.25</v>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H84" t="n">
-        <v>3604</v>
+        <v>28828</v>
       </c>
       <c r="I84" t="n">
-        <v>3642</v>
+        <v>29138</v>
       </c>
       <c r="J84" t="n">
-        <v>39</v>
+        <v>310</v>
       </c>
       <c r="K84" t="n">
         <v>1.07</v>
@@ -10181,16 +10169,16 @@
         <v>796</v>
       </c>
       <c r="G85" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H85" t="n">
-        <v>4759</v>
+        <v>26172</v>
       </c>
       <c r="I85" t="n">
-        <v>4776</v>
+        <v>26268</v>
       </c>
       <c r="J85" t="n">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="K85" t="n">
         <v>0.37</v>
@@ -10262,16 +10250,16 @@
         <v>293.56</v>
       </c>
       <c r="G86" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="H86" t="n">
-        <v>7611</v>
+        <v>38055</v>
       </c>
       <c r="I86" t="n">
-        <v>7633</v>
+        <v>38163</v>
       </c>
       <c r="J86" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="K86" t="n">
         <v>0.28</v>
@@ -10343,16 +10331,16 @@
         <v>854.35</v>
       </c>
       <c r="G87" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H87" t="n">
-        <v>5252</v>
+        <v>28011</v>
       </c>
       <c r="I87" t="n">
-        <v>5126</v>
+        <v>27339</v>
       </c>
       <c r="J87" t="n">
-        <v>-126</v>
+        <v>-671</v>
       </c>
       <c r="K87" t="n">
         <v>-2.4</v>
@@ -10424,16 +10412,16 @@
         <v>1261.15</v>
       </c>
       <c r="G88" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H88" t="n">
-        <v>5325</v>
+        <v>29289</v>
       </c>
       <c r="I88" t="n">
-        <v>5045</v>
+        <v>27745</v>
       </c>
       <c r="J88" t="n">
-        <v>-281</v>
+        <v>-1543</v>
       </c>
       <c r="K88" t="n">
         <v>-5.27</v>
@@ -10505,16 +10493,16 @@
         <v>3031.35</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H89" t="n">
-        <v>6401</v>
+        <v>44804</v>
       </c>
       <c r="I89" t="n">
-        <v>6063</v>
+        <v>42439</v>
       </c>
       <c r="J89" t="n">
-        <v>-338</v>
+        <v>-2365</v>
       </c>
       <c r="K89" t="n">
         <v>-5.28</v>
@@ -10586,16 +10574,16 @@
         <v>896.4</v>
       </c>
       <c r="G90" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H90" t="n">
-        <v>5054</v>
+        <v>29310</v>
       </c>
       <c r="I90" t="n">
-        <v>4482</v>
+        <v>25996</v>
       </c>
       <c r="J90" t="n">
-        <v>-572</v>
+        <v>-3315</v>
       </c>
       <c r="K90" t="n">
         <v>-11.31</v>
@@ -10665,16 +10653,16 @@
         <v>7829.05</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>17801</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>15658</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>-2143</v>
       </c>
       <c r="K91" t="n">
         <v>-12.04</v>
@@ -10744,16 +10732,16 @@
         <v>350.46</v>
       </c>
       <c r="G92" t="n">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="H92" t="n">
-        <v>6458</v>
+        <v>32879</v>
       </c>
       <c r="I92" t="n">
-        <v>7710</v>
+        <v>39252</v>
       </c>
       <c r="J92" t="n">
-        <v>1252</v>
+        <v>6373</v>
       </c>
       <c r="K92" t="n">
         <v>19.38</v>
@@ -10825,16 +10813,16 @@
         <v>4286</v>
       </c>
       <c r="G93" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H93" t="n">
-        <v>3642</v>
+        <v>32780</v>
       </c>
       <c r="I93" t="n">
-        <v>4286</v>
+        <v>38574</v>
       </c>
       <c r="J93" t="n">
-        <v>644</v>
+        <v>5794</v>
       </c>
       <c r="K93" t="n">
         <v>17.67</v>
@@ -10906,16 +10894,16 @@
         <v>3312.5</v>
       </c>
       <c r="G94" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H94" t="n">
-        <v>5993</v>
+        <v>32959</v>
       </c>
       <c r="I94" t="n">
-        <v>6625</v>
+        <v>36438</v>
       </c>
       <c r="J94" t="n">
-        <v>632</v>
+        <v>3478</v>
       </c>
       <c r="K94" t="n">
         <v>10.55</v>
@@ -10987,16 +10975,16 @@
         <v>3340.6</v>
       </c>
       <c r="G95" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H95" t="n">
-        <v>9094</v>
+        <v>48502</v>
       </c>
       <c r="I95" t="n">
-        <v>10022</v>
+        <v>53450</v>
       </c>
       <c r="J95" t="n">
-        <v>928</v>
+        <v>4948</v>
       </c>
       <c r="K95" t="n">
         <v>10.2</v>
@@ -11068,16 +11056,16 @@
         <v>2288.5</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H96" t="n">
-        <v>2087</v>
+        <v>18779</v>
       </c>
       <c r="I96" t="n">
-        <v>2288</v>
+        <v>20596</v>
       </c>
       <c r="J96" t="n">
-        <v>202</v>
+        <v>1818</v>
       </c>
       <c r="K96" t="n">
         <v>9.68</v>
@@ -11149,16 +11137,16 @@
         <v>231.45</v>
       </c>
       <c r="G97" t="n">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="H97" t="n">
-        <v>6973</v>
+        <v>35518</v>
       </c>
       <c r="I97" t="n">
-        <v>7406</v>
+        <v>37726</v>
       </c>
       <c r="J97" t="n">
-        <v>434</v>
+        <v>2209</v>
       </c>
       <c r="K97" t="n">
         <v>6.22</v>
@@ -11230,16 +11218,16 @@
         <v>842.45</v>
       </c>
       <c r="G98" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H98" t="n">
-        <v>3986</v>
+        <v>19930</v>
       </c>
       <c r="I98" t="n">
-        <v>4212</v>
+        <v>21061</v>
       </c>
       <c r="J98" t="n">
-        <v>226</v>
+        <v>1131</v>
       </c>
       <c r="K98" t="n">
         <v>5.68</v>
@@ -11311,16 +11299,16 @@
         <v>1587.65</v>
       </c>
       <c r="G99" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H99" t="n">
-        <v>9279</v>
+        <v>51034</v>
       </c>
       <c r="I99" t="n">
-        <v>9526</v>
+        <v>52392</v>
       </c>
       <c r="J99" t="n">
-        <v>247</v>
+        <v>1358</v>
       </c>
       <c r="K99" t="n">
         <v>2.66</v>
@@ -11392,16 +11380,16 @@
         <v>890.15</v>
       </c>
       <c r="G100" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H100" t="n">
-        <v>4350</v>
+        <v>22623</v>
       </c>
       <c r="I100" t="n">
-        <v>4451</v>
+        <v>23144</v>
       </c>
       <c r="J100" t="n">
-        <v>100</v>
+        <v>521</v>
       </c>
       <c r="K100" t="n">
         <v>2.3</v>
@@ -11473,16 +11461,16 @@
         <v>3241.65</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H101" t="n">
-        <v>3212</v>
+        <v>19269</v>
       </c>
       <c r="I101" t="n">
-        <v>3242</v>
+        <v>19450</v>
       </c>
       <c r="J101" t="n">
-        <v>30</v>
+        <v>181</v>
       </c>
       <c r="K101" t="n">
         <v>0.9399999999999999</v>
@@ -11554,16 +11542,16 @@
         <v>78</v>
       </c>
       <c r="G102" t="n">
-        <v>87</v>
+        <v>435</v>
       </c>
       <c r="H102" t="n">
-        <v>6964</v>
+        <v>34822</v>
       </c>
       <c r="I102" t="n">
-        <v>6786</v>
+        <v>33930</v>
       </c>
       <c r="J102" t="n">
-        <v>-178</v>
+        <v>-892</v>
       </c>
       <c r="K102" t="n">
         <v>-2.56</v>
@@ -11635,16 +11623,16 @@
         <v>771.1</v>
       </c>
       <c r="G103" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H103" t="n">
-        <v>6368</v>
+        <v>34228</v>
       </c>
       <c r="I103" t="n">
-        <v>6169</v>
+        <v>33157</v>
       </c>
       <c r="J103" t="n">
-        <v>-199</v>
+        <v>-1071</v>
       </c>
       <c r="K103" t="n">
         <v>-3.13</v>
@@ -11716,16 +11704,16 @@
         <v>1173.9</v>
       </c>
       <c r="G104" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H104" t="n">
-        <v>6306</v>
+        <v>35312</v>
       </c>
       <c r="I104" t="n">
-        <v>5870</v>
+        <v>32869</v>
       </c>
       <c r="J104" t="n">
-        <v>-436</v>
+        <v>-2443</v>
       </c>
       <c r="K104" t="n">
         <v>-6.92</v>
@@ -11797,16 +11785,16 @@
         <v>813.95</v>
       </c>
       <c r="G105" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="H105" t="n">
-        <v>8068</v>
+        <v>40338</v>
       </c>
       <c r="I105" t="n">
-        <v>7326</v>
+        <v>36628</v>
       </c>
       <c r="J105" t="n">
-        <v>-742</v>
+        <v>-3710</v>
       </c>
       <c r="K105" t="n">
         <v>-9.199999999999999</v>
@@ -11878,16 +11866,16 @@
         <v>1383.75</v>
       </c>
       <c r="G106" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H106" t="n">
-        <v>4973</v>
+        <v>31493</v>
       </c>
       <c r="I106" t="n">
-        <v>4151</v>
+        <v>26291</v>
       </c>
       <c r="J106" t="n">
-        <v>-821</v>
+        <v>-5202</v>
       </c>
       <c r="K106" t="n">
         <v>-16.52</v>
@@ -11959,16 +11947,16 @@
         <v>1356</v>
       </c>
       <c r="G107" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H107" t="n">
-        <v>6545</v>
+        <v>33816</v>
       </c>
       <c r="I107" t="n">
-        <v>8136</v>
+        <v>42036</v>
       </c>
       <c r="J107" t="n">
-        <v>1591</v>
+        <v>8220</v>
       </c>
       <c r="K107" t="n">
         <v>24.31</v>
@@ -12040,16 +12028,16 @@
         <v>3400</v>
       </c>
       <c r="G108" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H108" t="n">
-        <v>2787</v>
+        <v>25081</v>
       </c>
       <c r="I108" t="n">
-        <v>3400</v>
+        <v>30600</v>
       </c>
       <c r="J108" t="n">
-        <v>613</v>
+        <v>5519</v>
       </c>
       <c r="K108" t="n">
         <v>22.01</v>
@@ -12121,16 +12109,16 @@
         <v>1934.6</v>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H109" t="n">
-        <v>6351</v>
+        <v>33341</v>
       </c>
       <c r="I109" t="n">
-        <v>7738</v>
+        <v>40627</v>
       </c>
       <c r="J109" t="n">
-        <v>1388</v>
+        <v>7286</v>
       </c>
       <c r="K109" t="n">
         <v>21.85</v>
@@ -12202,16 +12190,16 @@
         <v>1659</v>
       </c>
       <c r="G110" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H110" t="n">
-        <v>6963</v>
+        <v>34815</v>
       </c>
       <c r="I110" t="n">
-        <v>8295</v>
+        <v>41475</v>
       </c>
       <c r="J110" t="n">
-        <v>1332</v>
+        <v>6660</v>
       </c>
       <c r="K110" t="n">
         <v>19.13</v>
@@ -12283,16 +12271,16 @@
         <v>837</v>
       </c>
       <c r="G111" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="H111" t="n">
-        <v>7184</v>
+        <v>37357</v>
       </c>
       <c r="I111" t="n">
-        <v>8370</v>
+        <v>43524</v>
       </c>
       <c r="J111" t="n">
-        <v>1186</v>
+        <v>6167</v>
       </c>
       <c r="K111" t="n">
         <v>16.51</v>
@@ -12364,16 +12352,16 @@
         <v>1809.7</v>
       </c>
       <c r="G112" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H112" t="n">
-        <v>7783</v>
+        <v>42030</v>
       </c>
       <c r="I112" t="n">
-        <v>9048</v>
+        <v>48862</v>
       </c>
       <c r="J112" t="n">
-        <v>1265</v>
+        <v>6832</v>
       </c>
       <c r="K112" t="n">
         <v>16.26</v>
@@ -12445,16 +12433,16 @@
         <v>3842.8</v>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H113" t="n">
-        <v>6625</v>
+        <v>33125</v>
       </c>
       <c r="I113" t="n">
-        <v>7686</v>
+        <v>38428</v>
       </c>
       <c r="J113" t="n">
-        <v>1061</v>
+        <v>5303</v>
       </c>
       <c r="K113" t="n">
         <v>16.01</v>
@@ -12526,16 +12514,16 @@
         <v>884.95</v>
       </c>
       <c r="G114" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H114" t="n">
-        <v>5398</v>
+        <v>26988</v>
       </c>
       <c r="I114" t="n">
-        <v>6195</v>
+        <v>30973</v>
       </c>
       <c r="J114" t="n">
-        <v>797</v>
+        <v>3985</v>
       </c>
       <c r="K114" t="n">
         <v>14.76</v>
@@ -12607,16 +12595,16 @@
         <v>9671</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>25863</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>29013</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>3150</v>
       </c>
       <c r="K115" t="n">
         <v>12.18</v>
@@ -12688,16 +12676,16 @@
         <v>1309.5</v>
       </c>
       <c r="G116" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H116" t="n">
-        <v>7043</v>
+        <v>35217</v>
       </c>
       <c r="I116" t="n">
-        <v>7857</v>
+        <v>39285</v>
       </c>
       <c r="J116" t="n">
-        <v>814</v>
+        <v>4068</v>
       </c>
       <c r="K116" t="n">
         <v>11.55</v>
@@ -12769,16 +12757,16 @@
         <v>188.3</v>
       </c>
       <c r="G117" t="n">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="H117" t="n">
-        <v>5626</v>
+        <v>28831</v>
       </c>
       <c r="I117" t="n">
-        <v>6026</v>
+        <v>30881</v>
       </c>
       <c r="J117" t="n">
-        <v>400</v>
+        <v>2050</v>
       </c>
       <c r="K117" t="n">
         <v>7.11</v>
@@ -12850,16 +12838,16 @@
         <v>197.38</v>
       </c>
       <c r="G118" t="n">
-        <v>31</v>
+        <v>159</v>
       </c>
       <c r="H118" t="n">
-        <v>5768</v>
+        <v>29587</v>
       </c>
       <c r="I118" t="n">
-        <v>6119</v>
+        <v>31383</v>
       </c>
       <c r="J118" t="n">
-        <v>350</v>
+        <v>1797</v>
       </c>
       <c r="K118" t="n">
         <v>6.07</v>
@@ -12931,16 +12919,16 @@
         <v>1075</v>
       </c>
       <c r="G119" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H119" t="n">
-        <v>6100</v>
+        <v>32534</v>
       </c>
       <c r="I119" t="n">
-        <v>6450</v>
+        <v>34400</v>
       </c>
       <c r="J119" t="n">
-        <v>350</v>
+        <v>1866</v>
       </c>
       <c r="K119" t="n">
         <v>5.73</v>
@@ -13012,16 +13000,16 @@
         <v>1752.76</v>
       </c>
       <c r="G120" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H120" t="n">
-        <v>5132</v>
+        <v>30790</v>
       </c>
       <c r="I120" t="n">
-        <v>5258</v>
+        <v>31550</v>
       </c>
       <c r="J120" t="n">
-        <v>127</v>
+        <v>759</v>
       </c>
       <c r="K120" t="n">
         <v>2.47</v>
@@ -13093,16 +13081,16 @@
         <v>374</v>
       </c>
       <c r="G121" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H121" t="n">
-        <v>7745</v>
+        <v>39094</v>
       </c>
       <c r="I121" t="n">
-        <v>7854</v>
+        <v>39644</v>
       </c>
       <c r="J121" t="n">
-        <v>109</v>
+        <v>550</v>
       </c>
       <c r="K121" t="n">
         <v>1.41</v>
@@ -13174,16 +13162,16 @@
         <v>242.05</v>
       </c>
       <c r="G122" t="n">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="H122" t="n">
-        <v>8474</v>
+        <v>42368</v>
       </c>
       <c r="I122" t="n">
-        <v>10892</v>
+        <v>54461</v>
       </c>
       <c r="J122" t="n">
-        <v>2419</v>
+        <v>12094</v>
       </c>
       <c r="K122" t="n">
         <v>28.54</v>
@@ -13255,16 +13243,16 @@
         <v>3186.25</v>
       </c>
       <c r="G123" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H123" t="n">
-        <v>10204</v>
+        <v>51020</v>
       </c>
       <c r="I123" t="n">
-        <v>12745</v>
+        <v>63725</v>
       </c>
       <c r="J123" t="n">
-        <v>2541</v>
+        <v>12705</v>
       </c>
       <c r="K123" t="n">
         <v>24.9</v>
@@ -13336,16 +13324,16 @@
         <v>2041.65</v>
       </c>
       <c r="G124" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H124" t="n">
-        <v>5429</v>
+        <v>32575</v>
       </c>
       <c r="I124" t="n">
-        <v>6125</v>
+        <v>36750</v>
       </c>
       <c r="J124" t="n">
-        <v>696</v>
+        <v>4175</v>
       </c>
       <c r="K124" t="n">
         <v>12.82</v>
@@ -13417,16 +13405,16 @@
         <v>1974.67</v>
       </c>
       <c r="G125" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H125" t="n">
-        <v>7011</v>
+        <v>35055</v>
       </c>
       <c r="I125" t="n">
-        <v>7899</v>
+        <v>39493</v>
       </c>
       <c r="J125" t="n">
-        <v>888</v>
+        <v>4438</v>
       </c>
       <c r="K125" t="n">
         <v>12.66</v>
@@ -13498,16 +13486,16 @@
         <v>10727.55</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>19342</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>21455</v>
       </c>
       <c r="J126" t="n">
-        <v>0</v>
+        <v>2113</v>
       </c>
       <c r="K126" t="n">
         <v>10.92</v>
@@ -13579,16 +13567,16 @@
         <v>954.2</v>
       </c>
       <c r="G127" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H127" t="n">
-        <v>8850</v>
+        <v>44248</v>
       </c>
       <c r="I127" t="n">
-        <v>9542</v>
+        <v>47710</v>
       </c>
       <c r="J127" t="n">
-        <v>692</v>
+        <v>3462</v>
       </c>
       <c r="K127" t="n">
         <v>7.83</v>
@@ -13741,16 +13729,16 @@
         <v>3570.85</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H129" t="n">
-        <v>3344</v>
+        <v>26754</v>
       </c>
       <c r="I129" t="n">
-        <v>3571</v>
+        <v>28567</v>
       </c>
       <c r="J129" t="n">
-        <v>227</v>
+        <v>1813</v>
       </c>
       <c r="K129" t="n">
         <v>6.78</v>
@@ -13822,16 +13810,16 @@
         <v>1145.3</v>
       </c>
       <c r="G130" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="H130" t="n">
-        <v>7525</v>
+        <v>38700</v>
       </c>
       <c r="I130" t="n">
-        <v>8017</v>
+        <v>41231</v>
       </c>
       <c r="J130" t="n">
-        <v>492</v>
+        <v>2531</v>
       </c>
       <c r="K130" t="n">
         <v>6.54</v>
@@ -13903,16 +13891,16 @@
         <v>205.53</v>
       </c>
       <c r="G131" t="n">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="H131" t="n">
-        <v>6908</v>
+        <v>34739</v>
       </c>
       <c r="I131" t="n">
-        <v>7194</v>
+        <v>36173</v>
       </c>
       <c r="J131" t="n">
-        <v>285</v>
+        <v>1434</v>
       </c>
       <c r="K131" t="n">
         <v>4.13</v>
@@ -13984,16 +13972,16 @@
         <v>1177.72</v>
       </c>
       <c r="G132" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H132" t="n">
-        <v>4564</v>
+        <v>23962</v>
       </c>
       <c r="I132" t="n">
-        <v>4711</v>
+        <v>24732</v>
       </c>
       <c r="J132" t="n">
-        <v>147</v>
+        <v>770</v>
       </c>
       <c r="K132" t="n">
         <v>3.21</v>
@@ -14065,16 +14053,16 @@
         <v>951.3</v>
       </c>
       <c r="G133" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H133" t="n">
-        <v>6696</v>
+        <v>37304</v>
       </c>
       <c r="I133" t="n">
-        <v>6659</v>
+        <v>37101</v>
       </c>
       <c r="J133" t="n">
-        <v>-36</v>
+        <v>-203</v>
       </c>
       <c r="K133" t="n">
         <v>-0.54</v>
@@ -14146,16 +14134,16 @@
         <v>1624.85</v>
       </c>
       <c r="G134" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H134" t="n">
-        <v>4977</v>
+        <v>26544</v>
       </c>
       <c r="I134" t="n">
-        <v>4875</v>
+        <v>25998</v>
       </c>
       <c r="J134" t="n">
-        <v>-102</v>
+        <v>-546</v>
       </c>
       <c r="K134" t="n">
         <v>-2.06</v>
@@ -14227,16 +14215,16 @@
         <v>1230.03</v>
       </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H135" t="n">
-        <v>3928</v>
+        <v>23571</v>
       </c>
       <c r="I135" t="n">
-        <v>3690</v>
+        <v>22141</v>
       </c>
       <c r="J135" t="n">
-        <v>-238</v>
+        <v>-1430</v>
       </c>
       <c r="K135" t="n">
         <v>-6.07</v>
@@ -14308,16 +14296,16 @@
         <v>3148.8</v>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H136" t="n">
-        <v>3400</v>
+        <v>20400</v>
       </c>
       <c r="I136" t="n">
-        <v>3149</v>
+        <v>18893</v>
       </c>
       <c r="J136" t="n">
-        <v>-251</v>
+        <v>-1507</v>
       </c>
       <c r="K136" t="n">
         <v>-7.39</v>
@@ -14389,16 +14377,16 @@
         <v>427.4</v>
       </c>
       <c r="G137" t="n">
-        <v>25</v>
+        <v>129</v>
       </c>
       <c r="H137" t="n">
-        <v>7933</v>
+        <v>40936</v>
       </c>
       <c r="I137" t="n">
-        <v>10685</v>
+        <v>55135</v>
       </c>
       <c r="J137" t="n">
-        <v>2752</v>
+        <v>14199</v>
       </c>
       <c r="K137" t="n">
         <v>34.69</v>
@@ -14551,16 +14539,16 @@
         <v>9954.549999999999</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>33476</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>39818</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>6342</v>
       </c>
       <c r="K139" t="n">
         <v>18.95</v>
@@ -14632,16 +14620,16 @@
         <v>1394.13</v>
       </c>
       <c r="G140" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H140" t="n">
-        <v>5873</v>
+        <v>29366</v>
       </c>
       <c r="I140" t="n">
-        <v>6971</v>
+        <v>34853</v>
       </c>
       <c r="J140" t="n">
-        <v>1097</v>
+        <v>5487</v>
       </c>
       <c r="K140" t="n">
         <v>18.68</v>
@@ -14713,16 +14701,16 @@
         <v>26210.45</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>22307</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>26210</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>3903</v>
       </c>
       <c r="K141" t="n">
         <v>17.5</v>
@@ -14794,16 +14782,16 @@
         <v>1329.35</v>
       </c>
       <c r="G142" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H142" t="n">
-        <v>6872</v>
+        <v>35504</v>
       </c>
       <c r="I142" t="n">
-        <v>7976</v>
+        <v>41210</v>
       </c>
       <c r="J142" t="n">
-        <v>1104</v>
+        <v>5706</v>
       </c>
       <c r="K142" t="n">
         <v>16.07</v>
@@ -14875,16 +14863,16 @@
         <v>1102.4</v>
       </c>
       <c r="G143" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H143" t="n">
-        <v>6679</v>
+        <v>36260</v>
       </c>
       <c r="I143" t="n">
-        <v>7717</v>
+        <v>41891</v>
       </c>
       <c r="J143" t="n">
-        <v>1037</v>
+        <v>5632</v>
       </c>
       <c r="K143" t="n">
         <v>15.53</v>
@@ -14956,16 +14944,16 @@
         <v>3758.85</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H144" t="n">
-        <v>6568</v>
+        <v>32838</v>
       </c>
       <c r="I144" t="n">
-        <v>7518</v>
+        <v>37588</v>
       </c>
       <c r="J144" t="n">
-        <v>950</v>
+        <v>4751</v>
       </c>
       <c r="K144" t="n">
         <v>14.47</v>
@@ -15037,16 +15025,16 @@
         <v>1377.13</v>
       </c>
       <c r="G145" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H145" t="n">
-        <v>4920</v>
+        <v>25831</v>
       </c>
       <c r="I145" t="n">
-        <v>5509</v>
+        <v>28920</v>
       </c>
       <c r="J145" t="n">
-        <v>588</v>
+        <v>3089</v>
       </c>
       <c r="K145" t="n">
         <v>11.96</v>
@@ -15118,16 +15106,16 @@
         <v>3903.8</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H146" t="n">
-        <v>3571</v>
+        <v>28567</v>
       </c>
       <c r="I146" t="n">
-        <v>3904</v>
+        <v>31230</v>
       </c>
       <c r="J146" t="n">
-        <v>333</v>
+        <v>2664</v>
       </c>
       <c r="K146" t="n">
         <v>9.32</v>
@@ -15199,16 +15187,16 @@
         <v>1273.78</v>
       </c>
       <c r="G147" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H147" t="n">
-        <v>5889</v>
+        <v>29443</v>
       </c>
       <c r="I147" t="n">
-        <v>6369</v>
+        <v>31844</v>
       </c>
       <c r="J147" t="n">
-        <v>480</v>
+        <v>2402</v>
       </c>
       <c r="K147" t="n">
         <v>8.16</v>
@@ -15280,16 +15268,16 @@
         <v>1009.85</v>
       </c>
       <c r="G148" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="H148" t="n">
-        <v>7610</v>
+        <v>39955</v>
       </c>
       <c r="I148" t="n">
-        <v>8079</v>
+        <v>42414</v>
       </c>
       <c r="J148" t="n">
-        <v>468</v>
+        <v>2459</v>
       </c>
       <c r="K148" t="n">
         <v>6.15</v>
@@ -15361,16 +15349,16 @@
         <v>3273.9</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H149" t="n">
-        <v>3149</v>
+        <v>25190</v>
       </c>
       <c r="I149" t="n">
-        <v>3274</v>
+        <v>26191</v>
       </c>
       <c r="J149" t="n">
-        <v>125</v>
+        <v>1001</v>
       </c>
       <c r="K149" t="n">
         <v>3.97</v>
@@ -15442,16 +15430,16 @@
         <v>2573.2</v>
       </c>
       <c r="G150" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H150" t="n">
-        <v>5139</v>
+        <v>28264</v>
       </c>
       <c r="I150" t="n">
-        <v>5146</v>
+        <v>28305</v>
       </c>
       <c r="J150" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K150" t="n">
         <v>0.15</v>
@@ -15523,16 +15511,16 @@
         <v>10086.9</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>21455</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>20174</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>-1281</v>
       </c>
       <c r="K151" t="n">
         <v>-5.97</v>
@@ -15604,16 +15592,16 @@
         <v>404.95</v>
       </c>
       <c r="G152" t="n">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="H152" t="n">
-        <v>4504</v>
+        <v>23810</v>
       </c>
       <c r="I152" t="n">
-        <v>5669</v>
+        <v>29966</v>
       </c>
       <c r="J152" t="n">
-        <v>1165</v>
+        <v>6157</v>
       </c>
       <c r="K152" t="n">
         <v>25.86</v>
@@ -15685,16 +15673,16 @@
         <v>12405</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>40348</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>49620</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>9272</v>
       </c>
       <c r="K153" t="n">
         <v>22.98</v>
@@ -15766,16 +15754,16 @@
         <v>1265.75</v>
       </c>
       <c r="G154" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="H154" t="n">
-        <v>4410</v>
+        <v>26458</v>
       </c>
       <c r="I154" t="n">
-        <v>5063</v>
+        <v>30378</v>
       </c>
       <c r="J154" t="n">
-        <v>653</v>
+        <v>3920</v>
       </c>
       <c r="K154" t="n">
         <v>14.82</v>
@@ -15847,16 +15835,16 @@
         <v>1516.4</v>
       </c>
       <c r="G155" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H155" t="n">
-        <v>5317</v>
+        <v>29246</v>
       </c>
       <c r="I155" t="n">
-        <v>6066</v>
+        <v>33361</v>
       </c>
       <c r="J155" t="n">
-        <v>748</v>
+        <v>4115</v>
       </c>
       <c r="K155" t="n">
         <v>14.07</v>
@@ -15928,16 +15916,16 @@
         <v>2226.05</v>
       </c>
       <c r="G156" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H156" t="n">
-        <v>4202</v>
+        <v>23111</v>
       </c>
       <c r="I156" t="n">
-        <v>4452</v>
+        <v>24487</v>
       </c>
       <c r="J156" t="n">
-        <v>250</v>
+        <v>1376</v>
       </c>
       <c r="K156" t="n">
         <v>5.95</v>
@@ -16009,16 +15997,16 @@
         <v>1464.33</v>
       </c>
       <c r="G157" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H157" t="n">
-        <v>5577</v>
+        <v>27883</v>
       </c>
       <c r="I157" t="n">
-        <v>5857</v>
+        <v>29287</v>
       </c>
       <c r="J157" t="n">
-        <v>281</v>
+        <v>1404</v>
       </c>
       <c r="K157" t="n">
         <v>5.04</v>
@@ -16090,16 +16078,16 @@
         <v>1055.45</v>
       </c>
       <c r="G158" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H158" t="n">
-        <v>5049</v>
+        <v>28276</v>
       </c>
       <c r="I158" t="n">
-        <v>5277</v>
+        <v>29553</v>
       </c>
       <c r="J158" t="n">
-        <v>228</v>
+        <v>1277</v>
       </c>
       <c r="K158" t="n">
         <v>4.52</v>
@@ -16171,16 +16159,16 @@
         <v>3862</v>
       </c>
       <c r="G159" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H159" t="n">
-        <v>3904</v>
+        <v>31230</v>
       </c>
       <c r="I159" t="n">
-        <v>3862</v>
+        <v>30896</v>
       </c>
       <c r="J159" t="n">
-        <v>-42</v>
+        <v>-334</v>
       </c>
       <c r="K159" t="n">
         <v>-1.07</v>
@@ -16252,16 +16240,16 @@
         <v>1638.25</v>
       </c>
       <c r="G160" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H160" t="n">
-        <v>8610</v>
+        <v>46497</v>
       </c>
       <c r="I160" t="n">
-        <v>8191</v>
+        <v>44233</v>
       </c>
       <c r="J160" t="n">
-        <v>-419</v>
+        <v>-2264</v>
       </c>
       <c r="K160" t="n">
         <v>-4.87</v>
@@ -16408,16 +16396,16 @@
         <v>3525.1</v>
       </c>
       <c r="G162" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H162" t="n">
-        <v>7518</v>
+        <v>37588</v>
       </c>
       <c r="I162" t="n">
-        <v>7050</v>
+        <v>35251</v>
       </c>
       <c r="J162" t="n">
-        <v>-468</v>
+        <v>-2338</v>
       </c>
       <c r="K162" t="n">
         <v>-6.22</v>
@@ -16489,16 +16477,16 @@
         <v>4695</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H163" t="n">
-        <v>5177</v>
+        <v>31064</v>
       </c>
       <c r="I163" t="n">
-        <v>4695</v>
+        <v>28170</v>
       </c>
       <c r="J163" t="n">
-        <v>-482</v>
+        <v>-2894</v>
       </c>
       <c r="K163" t="n">
         <v>-9.32</v>
@@ -16570,16 +16558,16 @@
         <v>747.35</v>
       </c>
       <c r="G164" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H164" t="n">
-        <v>5018</v>
+        <v>28438</v>
       </c>
       <c r="I164" t="n">
-        <v>4484</v>
+        <v>25410</v>
       </c>
       <c r="J164" t="n">
-        <v>-534</v>
+        <v>-3028</v>
       </c>
       <c r="K164" t="n">
         <v>-10.65</v>
@@ -16651,16 +16639,16 @@
         <v>2214.8</v>
       </c>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H165" t="n">
-        <v>7720</v>
+        <v>41171</v>
       </c>
       <c r="I165" t="n">
-        <v>6644</v>
+        <v>35437</v>
       </c>
       <c r="J165" t="n">
-        <v>-1075</v>
+        <v>-5734</v>
       </c>
       <c r="K165" t="n">
         <v>-13.93</v>
@@ -16730,16 +16718,16 @@
         <v>2807.7</v>
       </c>
       <c r="G166" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H166" t="n">
-        <v>6548</v>
+        <v>32739</v>
       </c>
       <c r="I166" t="n">
-        <v>5615</v>
+        <v>28077</v>
       </c>
       <c r="J166" t="n">
-        <v>-932</v>
+        <v>-4662</v>
       </c>
       <c r="K166" t="n">
         <v>-14.24</v>
@@ -16811,16 +16799,16 @@
         <v>2743</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H167" t="n">
-        <v>2226</v>
+        <v>20034</v>
       </c>
       <c r="I167" t="n">
-        <v>2743</v>
+        <v>24687</v>
       </c>
       <c r="J167" t="n">
-        <v>517</v>
+        <v>4653</v>
       </c>
       <c r="K167" t="n">
         <v>23.22</v>
@@ -16892,16 +16880,16 @@
         <v>2727</v>
       </c>
       <c r="G168" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H168" t="n">
-        <v>6644</v>
+        <v>35437</v>
       </c>
       <c r="I168" t="n">
-        <v>8181</v>
+        <v>43632</v>
       </c>
       <c r="J168" t="n">
-        <v>1537</v>
+        <v>8195</v>
       </c>
       <c r="K168" t="n">
         <v>23.13</v>
@@ -16973,16 +16961,16 @@
         <v>11258.3</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H169" t="n">
-        <v>0</v>
+        <v>18766</v>
       </c>
       <c r="I169" t="n">
-        <v>0</v>
+        <v>22517</v>
       </c>
       <c r="J169" t="n">
-        <v>0</v>
+        <v>3751</v>
       </c>
       <c r="K169" t="n">
         <v>19.99</v>
@@ -17054,16 +17042,16 @@
         <v>1248.65</v>
       </c>
       <c r="G170" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H170" t="n">
-        <v>4222</v>
+        <v>24275</v>
       </c>
       <c r="I170" t="n">
-        <v>4995</v>
+        <v>28719</v>
       </c>
       <c r="J170" t="n">
-        <v>773</v>
+        <v>4444</v>
       </c>
       <c r="K170" t="n">
         <v>18.3</v>
@@ -17135,16 +17123,16 @@
         <v>1926.85</v>
       </c>
       <c r="G171" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H171" t="n">
-        <v>8191</v>
+        <v>44233</v>
       </c>
       <c r="I171" t="n">
-        <v>9634</v>
+        <v>52025</v>
       </c>
       <c r="J171" t="n">
-        <v>1443</v>
+        <v>7792</v>
       </c>
       <c r="K171" t="n">
         <v>17.62</v>
@@ -17210,16 +17198,16 @@
         <v>1461.75</v>
       </c>
       <c r="G172" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H172" t="n">
-        <v>6329</v>
+        <v>36707</v>
       </c>
       <c r="I172" t="n">
-        <v>7309</v>
+        <v>42391</v>
       </c>
       <c r="J172" t="n">
-        <v>980</v>
+        <v>5684</v>
       </c>
       <c r="K172" t="n">
         <v>15.48</v>
@@ -17291,16 +17279,16 @@
         <v>446.08</v>
       </c>
       <c r="G173" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="H173" t="n">
-        <v>9283</v>
+        <v>46415</v>
       </c>
       <c r="I173" t="n">
-        <v>10706</v>
+        <v>53530</v>
       </c>
       <c r="J173" t="n">
-        <v>1423</v>
+        <v>7115</v>
       </c>
       <c r="K173" t="n">
         <v>15.33</v>
@@ -17372,16 +17360,16 @@
         <v>1523.8</v>
       </c>
       <c r="G174" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H174" t="n">
-        <v>5374</v>
+        <v>26871</v>
       </c>
       <c r="I174" t="n">
-        <v>6095</v>
+        <v>30476</v>
       </c>
       <c r="J174" t="n">
-        <v>721</v>
+        <v>3605</v>
       </c>
       <c r="K174" t="n">
         <v>13.42</v>
@@ -17453,16 +17441,16 @@
         <v>1327.2</v>
       </c>
       <c r="G175" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H175" t="n">
-        <v>7149</v>
+        <v>38126</v>
       </c>
       <c r="I175" t="n">
-        <v>7963</v>
+        <v>42470</v>
       </c>
       <c r="J175" t="n">
-        <v>815</v>
+        <v>4345</v>
       </c>
       <c r="K175" t="n">
         <v>11.4</v>
@@ -17534,16 +17522,16 @@
         <v>4302.4</v>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H176" t="n">
-        <v>3862</v>
+        <v>34758</v>
       </c>
       <c r="I176" t="n">
-        <v>4302</v>
+        <v>38722</v>
       </c>
       <c r="J176" t="n">
-        <v>440</v>
+        <v>3964</v>
       </c>
       <c r="K176" t="n">
         <v>11.4</v>
@@ -17615,16 +17603,16 @@
         <v>1555.15</v>
       </c>
       <c r="G177" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H177" t="n">
-        <v>4393</v>
+        <v>23429</v>
       </c>
       <c r="I177" t="n">
-        <v>4665</v>
+        <v>24882</v>
       </c>
       <c r="J177" t="n">
-        <v>272</v>
+        <v>1453</v>
       </c>
       <c r="K177" t="n">
         <v>6.2</v>
@@ -17696,16 +17684,16 @@
         <v>2946.05</v>
       </c>
       <c r="G178" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H178" t="n">
-        <v>5615</v>
+        <v>30885</v>
       </c>
       <c r="I178" t="n">
-        <v>5892</v>
+        <v>32407</v>
       </c>
       <c r="J178" t="n">
-        <v>277</v>
+        <v>1522</v>
       </c>
       <c r="K178" t="n">
         <v>4.93</v>
@@ -17777,16 +17765,16 @@
         <v>1568.65</v>
       </c>
       <c r="G179" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H179" t="n">
-        <v>7582</v>
+        <v>40943</v>
       </c>
       <c r="I179" t="n">
-        <v>7843</v>
+        <v>42354</v>
       </c>
       <c r="J179" t="n">
-        <v>261</v>
+        <v>1411</v>
       </c>
       <c r="K179" t="n">
         <v>3.45</v>
@@ -17858,16 +17846,16 @@
         <v>364.32</v>
       </c>
       <c r="G180" t="n">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="H180" t="n">
-        <v>5003</v>
+        <v>25014</v>
       </c>
       <c r="I180" t="n">
-        <v>5100</v>
+        <v>25502</v>
       </c>
       <c r="J180" t="n">
-        <v>98</v>
+        <v>488</v>
       </c>
       <c r="K180" t="n">
         <v>1.95</v>
@@ -17939,16 +17927,16 @@
         <v>12524.3</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>37215</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>37573</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="K181" t="n">
         <v>0.96</v>
@@ -18020,16 +18008,16 @@
         <v>1910.35</v>
       </c>
       <c r="G182" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H182" t="n">
-        <v>4706</v>
+        <v>26667</v>
       </c>
       <c r="I182" t="n">
-        <v>5731</v>
+        <v>32476</v>
       </c>
       <c r="J182" t="n">
-        <v>1025</v>
+        <v>5809</v>
       </c>
       <c r="K182" t="n">
         <v>21.78</v>
@@ -18101,16 +18089,16 @@
         <v>4560.7</v>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H183" t="n">
-        <v>7671</v>
+        <v>42188</v>
       </c>
       <c r="I183" t="n">
-        <v>9121</v>
+        <v>50168</v>
       </c>
       <c r="J183" t="n">
-        <v>1451</v>
+        <v>7979</v>
       </c>
       <c r="K183" t="n">
         <v>18.91</v>
@@ -18182,16 +18170,16 @@
         <v>6982.9</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>19146</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>20949</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>1803</v>
       </c>
       <c r="K184" t="n">
         <v>9.42</v>
@@ -18263,16 +18251,16 @@
         <v>1879.6</v>
       </c>
       <c r="G185" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H185" t="n">
-        <v>5379</v>
+        <v>34066</v>
       </c>
       <c r="I185" t="n">
-        <v>5639</v>
+        <v>35712</v>
       </c>
       <c r="J185" t="n">
-        <v>260</v>
+        <v>1646</v>
       </c>
       <c r="K185" t="n">
         <v>4.83</v>
@@ -18344,16 +18332,16 @@
         <v>840.9299999999999</v>
       </c>
       <c r="G186" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H186" t="n">
-        <v>7233</v>
+        <v>38575</v>
       </c>
       <c r="I186" t="n">
-        <v>7568</v>
+        <v>40365</v>
       </c>
       <c r="J186" t="n">
-        <v>336</v>
+        <v>1789</v>
       </c>
       <c r="K186" t="n">
         <v>4.64</v>
@@ -18425,16 +18413,16 @@
         <v>740.15</v>
       </c>
       <c r="G187" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H187" t="n">
-        <v>7905</v>
+        <v>39523</v>
       </c>
       <c r="I187" t="n">
-        <v>8142</v>
+        <v>40708</v>
       </c>
       <c r="J187" t="n">
-        <v>237</v>
+        <v>1185</v>
       </c>
       <c r="K187" t="n">
         <v>3</v>
@@ -18506,16 +18494,16 @@
         <v>457.5</v>
       </c>
       <c r="G188" t="n">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="H188" t="n">
-        <v>6691</v>
+        <v>33902</v>
       </c>
       <c r="I188" t="n">
-        <v>6862</v>
+        <v>34770</v>
       </c>
       <c r="J188" t="n">
-        <v>171</v>
+        <v>868</v>
       </c>
       <c r="K188" t="n">
         <v>2.56</v>
@@ -18587,16 +18575,16 @@
         <v>1348.22</v>
       </c>
       <c r="G189" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H189" t="n">
-        <v>5309</v>
+        <v>27871</v>
       </c>
       <c r="I189" t="n">
-        <v>5393</v>
+        <v>28313</v>
       </c>
       <c r="J189" t="n">
-        <v>84</v>
+        <v>441</v>
       </c>
       <c r="K189" t="n">
         <v>1.58</v>
@@ -18668,16 +18656,16 @@
         <v>1592</v>
       </c>
       <c r="G190" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H190" t="n">
-        <v>6270</v>
+        <v>36050</v>
       </c>
       <c r="I190" t="n">
-        <v>6368</v>
+        <v>36616</v>
       </c>
       <c r="J190" t="n">
-        <v>98</v>
+        <v>566</v>
       </c>
       <c r="K190" t="n">
         <v>1.57</v>
@@ -18749,16 +18737,16 @@
         <v>2992.15</v>
       </c>
       <c r="G191" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H191" t="n">
-        <v>5892</v>
+        <v>29460</v>
       </c>
       <c r="I191" t="n">
-        <v>5984</v>
+        <v>29922</v>
       </c>
       <c r="J191" t="n">
-        <v>92</v>
+        <v>461</v>
       </c>
       <c r="K191" t="n">
         <v>1.56</v>
@@ -18911,16 +18899,16 @@
         <v>2717.1</v>
       </c>
       <c r="G193" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H193" t="n">
-        <v>8181</v>
+        <v>40905</v>
       </c>
       <c r="I193" t="n">
-        <v>8151</v>
+        <v>40756</v>
       </c>
       <c r="J193" t="n">
-        <v>-30</v>
+        <v>-148</v>
       </c>
       <c r="K193" t="n">
         <v>-0.36</v>
@@ -18992,16 +18980,16 @@
         <v>4765.65</v>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H194" t="n">
-        <v>4851</v>
+        <v>24254</v>
       </c>
       <c r="I194" t="n">
-        <v>4766</v>
+        <v>23828</v>
       </c>
       <c r="J194" t="n">
-        <v>-85</v>
+        <v>-425</v>
       </c>
       <c r="K194" t="n">
         <v>-1.75</v>
@@ -19073,16 +19061,16 @@
         <v>1464.95</v>
       </c>
       <c r="G195" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H195" t="n">
-        <v>6095</v>
+        <v>30476</v>
       </c>
       <c r="I195" t="n">
-        <v>5860</v>
+        <v>29299</v>
       </c>
       <c r="J195" t="n">
-        <v>-235</v>
+        <v>-1177</v>
       </c>
       <c r="K195" t="n">
         <v>-3.86</v>
@@ -19154,16 +19142,16 @@
         <v>4123.05</v>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H196" t="n">
-        <v>4302</v>
+        <v>30117</v>
       </c>
       <c r="I196" t="n">
-        <v>4123</v>
+        <v>28861</v>
       </c>
       <c r="J196" t="n">
-        <v>-179</v>
+        <v>-1255</v>
       </c>
       <c r="K196" t="n">
         <v>-4.17</v>
@@ -19235,16 +19223,16 @@
         <v>5016.75</v>
       </c>
       <c r="G197" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H197" t="n">
-        <v>4766</v>
+        <v>23828</v>
       </c>
       <c r="I197" t="n">
-        <v>5017</v>
+        <v>25084</v>
       </c>
       <c r="J197" t="n">
-        <v>251</v>
+        <v>1256</v>
       </c>
       <c r="K197" t="n">
         <v>5.27</v>
@@ -19316,16 +19304,16 @@
         <v>25146</v>
       </c>
       <c r="G198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>24325</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>25146</v>
       </c>
       <c r="J198" t="n">
-        <v>0</v>
+        <v>821</v>
       </c>
       <c r="K198" t="n">
         <v>3.37</v>
@@ -19397,16 +19385,16 @@
         <v>761.5</v>
       </c>
       <c r="G199" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H199" t="n">
-        <v>6661</v>
+        <v>34047</v>
       </c>
       <c r="I199" t="n">
-        <v>6854</v>
+        <v>35029</v>
       </c>
       <c r="J199" t="n">
-        <v>192</v>
+        <v>982</v>
       </c>
       <c r="K199" t="n">
         <v>2.88</v>
@@ -19478,16 +19466,16 @@
         <v>384.1</v>
       </c>
       <c r="G200" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="H200" t="n">
-        <v>4865</v>
+        <v>25820</v>
       </c>
       <c r="I200" t="n">
-        <v>4993</v>
+        <v>26503</v>
       </c>
       <c r="J200" t="n">
-        <v>129</v>
+        <v>682</v>
       </c>
       <c r="K200" t="n">
         <v>2.64</v>
@@ -19559,16 +19547,16 @@
         <v>4077.8</v>
       </c>
       <c r="G201" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H201" t="n">
-        <v>4123</v>
+        <v>28861</v>
       </c>
       <c r="I201" t="n">
-        <v>4078</v>
+        <v>28545</v>
       </c>
       <c r="J201" t="n">
-        <v>-45</v>
+        <v>-317</v>
       </c>
       <c r="K201" t="n">
         <v>-1.1</v>
@@ -19640,16 +19628,16 @@
         <v>6780.85</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>27932</v>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>27123</v>
       </c>
       <c r="J202" t="n">
-        <v>0</v>
+        <v>-808</v>
       </c>
       <c r="K202" t="n">
         <v>-2.89</v>
@@ -19721,16 +19709,16 @@
         <v>1302.35</v>
       </c>
       <c r="G203" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H203" t="n">
-        <v>8089</v>
+        <v>44491</v>
       </c>
       <c r="I203" t="n">
-        <v>7814</v>
+        <v>42978</v>
       </c>
       <c r="J203" t="n">
-        <v>-275</v>
+        <v>-1514</v>
       </c>
       <c r="K203" t="n">
         <v>-3.4</v>
@@ -19802,16 +19790,16 @@
         <v>1813.3</v>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H204" t="n">
-        <v>3759</v>
+        <v>26314</v>
       </c>
       <c r="I204" t="n">
-        <v>3627</v>
+        <v>25386</v>
       </c>
       <c r="J204" t="n">
-        <v>-133</v>
+        <v>-928</v>
       </c>
       <c r="K204" t="n">
         <v>-3.53</v>
@@ -19883,16 +19871,16 @@
         <v>437.7</v>
       </c>
       <c r="G205" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H205" t="n">
-        <v>5948</v>
+        <v>30652</v>
       </c>
       <c r="I205" t="n">
-        <v>5690</v>
+        <v>29326</v>
       </c>
       <c r="J205" t="n">
-        <v>-257</v>
+        <v>-1327</v>
       </c>
       <c r="K205" t="n">
         <v>-4.33</v>
@@ -19964,16 +19952,16 @@
         <v>1107</v>
       </c>
       <c r="G206" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H206" t="n">
-        <v>5876</v>
+        <v>30553</v>
       </c>
       <c r="I206" t="n">
-        <v>5535</v>
+        <v>28782</v>
       </c>
       <c r="J206" t="n">
-        <v>-341</v>
+        <v>-1771</v>
       </c>
       <c r="K206" t="n">
         <v>-5.8</v>
@@ -20045,16 +20033,16 @@
         <v>1778.25</v>
       </c>
       <c r="G207" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H207" t="n">
-        <v>7641</v>
+        <v>42028</v>
       </c>
       <c r="I207" t="n">
-        <v>7113</v>
+        <v>39122</v>
       </c>
       <c r="J207" t="n">
-        <v>-528</v>
+        <v>-2906</v>
       </c>
       <c r="K207" t="n">
         <v>-6.91</v>
@@ -20205,16 +20193,16 @@
         <v>1393.88</v>
       </c>
       <c r="G209" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H209" t="n">
-        <v>4776</v>
+        <v>28656</v>
       </c>
       <c r="I209" t="n">
-        <v>4182</v>
+        <v>25090</v>
       </c>
       <c r="J209" t="n">
-        <v>-594</v>
+        <v>-3566</v>
       </c>
       <c r="K209" t="n">
         <v>-12.44</v>
@@ -20286,16 +20274,16 @@
         <v>2280.55</v>
       </c>
       <c r="G210" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H210" t="n">
-        <v>2992</v>
+        <v>26929</v>
       </c>
       <c r="I210" t="n">
-        <v>2281</v>
+        <v>20525</v>
       </c>
       <c r="J210" t="n">
-        <v>-712</v>
+        <v>-6404</v>
       </c>
       <c r="K210" t="n">
         <v>-23.78</v>
@@ -20367,16 +20355,16 @@
         <v>578.35</v>
       </c>
       <c r="G211" t="n">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="H211" t="n">
-        <v>9385</v>
+        <v>48487</v>
       </c>
       <c r="I211" t="n">
-        <v>6940</v>
+        <v>35858</v>
       </c>
       <c r="J211" t="n">
-        <v>-2444</v>
+        <v>-12629</v>
       </c>
       <c r="K211" t="n">
         <v>-26.05</v>
@@ -20446,16 +20434,16 @@
         <v>958.4</v>
       </c>
       <c r="G212" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H212" t="n">
-        <v>5779</v>
+        <v>31374</v>
       </c>
       <c r="I212" t="n">
-        <v>6709</v>
+        <v>36419</v>
       </c>
       <c r="J212" t="n">
-        <v>929</v>
+        <v>5045</v>
       </c>
       <c r="K212" t="n">
         <v>16.08</v>
@@ -20527,16 +20515,16 @@
         <v>12159</v>
       </c>
       <c r="G213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H213" t="n">
-        <v>0</v>
+        <v>10624</v>
       </c>
       <c r="I213" t="n">
-        <v>0</v>
+        <v>12159</v>
       </c>
       <c r="J213" t="n">
-        <v>0</v>
+        <v>1535</v>
       </c>
       <c r="K213" t="n">
         <v>14.44</v>
@@ -20689,16 +20677,16 @@
         <v>1402.7</v>
       </c>
       <c r="G215" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H215" t="n">
-        <v>4932</v>
+        <v>28358</v>
       </c>
       <c r="I215" t="n">
-        <v>5611</v>
+        <v>32262</v>
       </c>
       <c r="J215" t="n">
-        <v>679</v>
+        <v>3904</v>
       </c>
       <c r="K215" t="n">
         <v>13.77</v>
@@ -20770,16 +20758,16 @@
         <v>1845.6</v>
       </c>
       <c r="G216" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H216" t="n">
-        <v>4923</v>
+        <v>27900</v>
       </c>
       <c r="I216" t="n">
-        <v>5537</v>
+        <v>31375</v>
       </c>
       <c r="J216" t="n">
-        <v>613</v>
+        <v>3476</v>
       </c>
       <c r="K216" t="n">
         <v>12.46</v>
@@ -20851,16 +20839,16 @@
         <v>1538.2</v>
       </c>
       <c r="G217" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H217" t="n">
-        <v>5576</v>
+        <v>32059</v>
       </c>
       <c r="I217" t="n">
-        <v>6153</v>
+        <v>35379</v>
       </c>
       <c r="J217" t="n">
-        <v>577</v>
+        <v>3319</v>
       </c>
       <c r="K217" t="n">
         <v>10.35</v>
@@ -20932,16 +20920,16 @@
         <v>1216.6</v>
       </c>
       <c r="G218" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H218" t="n">
-        <v>5535</v>
+        <v>30996</v>
       </c>
       <c r="I218" t="n">
-        <v>6083</v>
+        <v>34065</v>
       </c>
       <c r="J218" t="n">
-        <v>548</v>
+        <v>3069</v>
       </c>
       <c r="K218" t="n">
         <v>9.9</v>
@@ -21013,16 +21001,16 @@
         <v>7159.5</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>27123</v>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>28638</v>
       </c>
       <c r="J219" t="n">
-        <v>0</v>
+        <v>1515</v>
       </c>
       <c r="K219" t="n">
         <v>5.58</v>
@@ -21094,16 +21082,16 @@
         <v>1803.9</v>
       </c>
       <c r="G220" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H220" t="n">
-        <v>8891</v>
+        <v>44456</v>
       </c>
       <c r="I220" t="n">
-        <v>9020</v>
+        <v>45098</v>
       </c>
       <c r="J220" t="n">
-        <v>128</v>
+        <v>641</v>
       </c>
       <c r="K220" t="n">
         <v>1.44</v>
@@ -21175,16 +21163,16 @@
         <v>3382.6</v>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H221" t="n">
-        <v>3382</v>
+        <v>20294</v>
       </c>
       <c r="I221" t="n">
-        <v>3383</v>
+        <v>20296</v>
       </c>
       <c r="J221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K221" t="n">
         <v>0.01</v>
@@ -21256,16 +21244,16 @@
         <v>1301.6</v>
       </c>
       <c r="G222" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H222" t="n">
-        <v>3916</v>
+        <v>20887</v>
       </c>
       <c r="I222" t="n">
-        <v>3905</v>
+        <v>20826</v>
       </c>
       <c r="J222" t="n">
-        <v>-12</v>
+        <v>-62</v>
       </c>
       <c r="K222" t="n">
         <v>-0.29</v>
@@ -21335,16 +21323,16 @@
         <v>430.05</v>
       </c>
       <c r="G223" t="n">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="H223" t="n">
-        <v>6566</v>
+        <v>33703</v>
       </c>
       <c r="I223" t="n">
-        <v>6451</v>
+        <v>33114</v>
       </c>
       <c r="J223" t="n">
-        <v>-115</v>
+        <v>-589</v>
       </c>
       <c r="K223" t="n">
         <v>-1.75</v>
@@ -21416,16 +21404,16 @@
         <v>1200.5</v>
       </c>
       <c r="G224" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H224" t="n">
-        <v>7814</v>
+        <v>39070</v>
       </c>
       <c r="I224" t="n">
-        <v>7203</v>
+        <v>36015</v>
       </c>
       <c r="J224" t="n">
-        <v>-611</v>
+        <v>-3056</v>
       </c>
       <c r="K224" t="n">
         <v>-7.82</v>
@@ -21495,16 +21483,16 @@
         <v>2700</v>
       </c>
       <c r="G225" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H225" t="n">
-        <v>5979</v>
+        <v>41854</v>
       </c>
       <c r="I225" t="n">
-        <v>5400</v>
+        <v>37800</v>
       </c>
       <c r="J225" t="n">
-        <v>-579</v>
+        <v>-4054</v>
       </c>
       <c r="K225" t="n">
         <v>-9.69</v>
@@ -21570,16 +21558,16 @@
         <v>3401.6</v>
       </c>
       <c r="G226" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H226" t="n">
-        <v>4078</v>
+        <v>36700</v>
       </c>
       <c r="I226" t="n">
-        <v>3402</v>
+        <v>30614</v>
       </c>
       <c r="J226" t="n">
-        <v>-676</v>
+        <v>-6086</v>
       </c>
       <c r="K226" t="n">
         <v>-16.58</v>
@@ -21732,16 +21720,16 @@
         <v>1424.6</v>
       </c>
       <c r="G228" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H228" t="n">
-        <v>3905</v>
+        <v>24730</v>
       </c>
       <c r="I228" t="n">
-        <v>4274</v>
+        <v>27067</v>
       </c>
       <c r="J228" t="n">
-        <v>369</v>
+        <v>2337</v>
       </c>
       <c r="K228" t="n">
         <v>9.449999999999999</v>
@@ -21813,16 +21801,16 @@
         <v>3553.7</v>
       </c>
       <c r="G229" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H229" t="n">
-        <v>6650</v>
+        <v>36576</v>
       </c>
       <c r="I229" t="n">
-        <v>7107</v>
+        <v>39091</v>
       </c>
       <c r="J229" t="n">
-        <v>457</v>
+        <v>2515</v>
       </c>
       <c r="K229" t="n">
         <v>6.87</v>
@@ -21894,16 +21882,16 @@
         <v>12627</v>
       </c>
       <c r="G230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>23788</v>
       </c>
       <c r="I230" t="n">
-        <v>0</v>
+        <v>25254</v>
       </c>
       <c r="J230" t="n">
-        <v>0</v>
+        <v>1466</v>
       </c>
       <c r="K230" t="n">
         <v>6.16</v>
@@ -21975,16 +21963,16 @@
         <v>1488.6</v>
       </c>
       <c r="G231" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H231" t="n">
-        <v>5611</v>
+        <v>32262</v>
       </c>
       <c r="I231" t="n">
-        <v>5954</v>
+        <v>34238</v>
       </c>
       <c r="J231" t="n">
-        <v>344</v>
+        <v>1976</v>
       </c>
       <c r="K231" t="n">
         <v>6.12</v>
@@ -22056,16 +22044,16 @@
         <v>3354.5</v>
       </c>
       <c r="G232" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H232" t="n">
-        <v>6343</v>
+        <v>31713</v>
       </c>
       <c r="I232" t="n">
-        <v>6709</v>
+        <v>33545</v>
       </c>
       <c r="J232" t="n">
-        <v>366</v>
+        <v>1832</v>
       </c>
       <c r="K232" t="n">
         <v>5.78</v>
@@ -22137,16 +22125,16 @@
         <v>1012.15</v>
       </c>
       <c r="G233" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H233" t="n">
-        <v>6709</v>
+        <v>37378</v>
       </c>
       <c r="I233" t="n">
-        <v>7085</v>
+        <v>39474</v>
       </c>
       <c r="J233" t="n">
-        <v>376</v>
+        <v>2096</v>
       </c>
       <c r="K233" t="n">
         <v>5.61</v>
@@ -22218,16 +22206,16 @@
         <v>32115</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H234" t="n">
-        <v>0</v>
+        <v>30705</v>
       </c>
       <c r="I234" t="n">
-        <v>0</v>
+        <v>32115</v>
       </c>
       <c r="J234" t="n">
-        <v>0</v>
+        <v>1410</v>
       </c>
       <c r="K234" t="n">
         <v>4.59</v>
@@ -22299,16 +22287,16 @@
         <v>1226.25</v>
       </c>
       <c r="G235" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="H235" t="n">
-        <v>7300</v>
+        <v>36498</v>
       </c>
       <c r="I235" t="n">
-        <v>7358</v>
+        <v>36788</v>
       </c>
       <c r="J235" t="n">
-        <v>58</v>
+        <v>290</v>
       </c>
       <c r="K235" t="n">
         <v>0.79</v>
@@ -22380,16 +22368,16 @@
         <v>390.75</v>
       </c>
       <c r="G236" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H236" t="n">
-        <v>4398</v>
+        <v>21992</v>
       </c>
       <c r="I236" t="n">
-        <v>4298</v>
+        <v>21491</v>
       </c>
       <c r="J236" t="n">
-        <v>-100</v>
+        <v>-500</v>
       </c>
       <c r="K236" t="n">
         <v>-2.28</v>
@@ -22461,16 +22449,16 @@
         <v>414.95</v>
       </c>
       <c r="G237" t="n">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="H237" t="n">
-        <v>9031</v>
+        <v>45585</v>
       </c>
       <c r="I237" t="n">
-        <v>8714</v>
+        <v>43985</v>
       </c>
       <c r="J237" t="n">
-        <v>-317</v>
+        <v>-1601</v>
       </c>
       <c r="K237" t="n">
         <v>-3.51</v>
@@ -22542,16 +22530,16 @@
         <v>2375.4</v>
       </c>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H238" t="n">
-        <v>4929</v>
+        <v>24644</v>
       </c>
       <c r="I238" t="n">
-        <v>4751</v>
+        <v>23754</v>
       </c>
       <c r="J238" t="n">
-        <v>-178</v>
+        <v>-890</v>
       </c>
       <c r="K238" t="n">
         <v>-3.61</v>
@@ -22623,16 +22611,16 @@
         <v>1459.45</v>
       </c>
       <c r="G239" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H239" t="n">
-        <v>6153</v>
+        <v>33840</v>
       </c>
       <c r="I239" t="n">
-        <v>5838</v>
+        <v>32108</v>
       </c>
       <c r="J239" t="n">
-        <v>-315</v>
+        <v>-1732</v>
       </c>
       <c r="K239" t="n">
         <v>-5.12</v>
@@ -22704,16 +22692,16 @@
         <v>3179.1</v>
       </c>
       <c r="G240" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H240" t="n">
-        <v>6803</v>
+        <v>40819</v>
       </c>
       <c r="I240" t="n">
-        <v>6358</v>
+        <v>38149</v>
       </c>
       <c r="J240" t="n">
-        <v>-445</v>
+        <v>-2670</v>
       </c>
       <c r="K240" t="n">
         <v>-6.54</v>
@@ -22785,16 +22773,16 @@
         <v>1682.5</v>
       </c>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H241" t="n">
-        <v>5412</v>
+        <v>28862</v>
       </c>
       <c r="I241" t="n">
-        <v>5048</v>
+        <v>26920</v>
       </c>
       <c r="J241" t="n">
-        <v>-364</v>
+        <v>-1942</v>
       </c>
       <c r="K241" t="n">
         <v>-6.73</v>
@@ -22866,16 +22854,16 @@
         <v>16274</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H242" t="n">
-        <v>0</v>
+        <v>25254</v>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>32548</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>7294</v>
       </c>
       <c r="K242" t="n">
         <v>28.88</v>
@@ -22947,16 +22935,16 @@
         <v>1584.4</v>
       </c>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H243" t="n">
-        <v>4420</v>
+        <v>27996</v>
       </c>
       <c r="I243" t="n">
-        <v>4753</v>
+        <v>30104</v>
       </c>
       <c r="J243" t="n">
-        <v>333</v>
+        <v>2107</v>
       </c>
       <c r="K243" t="n">
         <v>7.53</v>
@@ -23109,16 +23097,16 @@
         <v>7837.5</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H245" t="n">
-        <v>0</v>
+        <v>22120</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>23512</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>1392</v>
       </c>
       <c r="K245" t="n">
         <v>6.29</v>
@@ -23190,16 +23178,16 @@
         <v>2501.6</v>
       </c>
       <c r="G246" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H246" t="n">
-        <v>4751</v>
+        <v>30880</v>
       </c>
       <c r="I246" t="n">
-        <v>5003</v>
+        <v>32521</v>
       </c>
       <c r="J246" t="n">
-        <v>252</v>
+        <v>1641</v>
       </c>
       <c r="K246" t="n">
         <v>5.31</v>
@@ -23271,16 +23259,16 @@
         <v>1282</v>
       </c>
       <c r="G247" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H247" t="n">
-        <v>6131</v>
+        <v>30656</v>
       </c>
       <c r="I247" t="n">
-        <v>6410</v>
+        <v>32050</v>
       </c>
       <c r="J247" t="n">
-        <v>279</v>
+        <v>1394</v>
       </c>
       <c r="K247" t="n">
         <v>4.55</v>
@@ -23352,16 +23340,16 @@
         <v>1507.1</v>
       </c>
       <c r="G248" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="H248" t="n">
-        <v>10216</v>
+        <v>54000</v>
       </c>
       <c r="I248" t="n">
-        <v>10550</v>
+        <v>55763</v>
       </c>
       <c r="J248" t="n">
-        <v>334</v>
+        <v>1763</v>
       </c>
       <c r="K248" t="n">
         <v>3.26</v>
@@ -23433,16 +23421,16 @@
         <v>1283.6</v>
       </c>
       <c r="G249" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H249" t="n">
-        <v>4990</v>
+        <v>26195</v>
       </c>
       <c r="I249" t="n">
-        <v>5134</v>
+        <v>26956</v>
       </c>
       <c r="J249" t="n">
-        <v>145</v>
+        <v>760</v>
       </c>
       <c r="K249" t="n">
         <v>2.9</v>
@@ -23514,16 +23502,16 @@
         <v>394.05</v>
       </c>
       <c r="G250" t="n">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="H250" t="n">
-        <v>5080</v>
+        <v>26180</v>
       </c>
       <c r="I250" t="n">
-        <v>5123</v>
+        <v>26401</v>
       </c>
       <c r="J250" t="n">
-        <v>43</v>
+        <v>221</v>
       </c>
       <c r="K250" t="n">
         <v>0.84</v>
@@ -23595,16 +23583,16 @@
         <v>416.8</v>
       </c>
       <c r="G251" t="n">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="H251" t="n">
-        <v>7054</v>
+        <v>36516</v>
       </c>
       <c r="I251" t="n">
-        <v>7086</v>
+        <v>36678</v>
       </c>
       <c r="J251" t="n">
-        <v>31</v>
+        <v>163</v>
       </c>
       <c r="K251" t="n">
         <v>0.45</v>
@@ -23676,16 +23664,16 @@
         <v>994.75</v>
       </c>
       <c r="G252" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H252" t="n">
-        <v>6073</v>
+        <v>32389</v>
       </c>
       <c r="I252" t="n">
-        <v>5968</v>
+        <v>31832</v>
       </c>
       <c r="J252" t="n">
-        <v>-104</v>
+        <v>-557</v>
       </c>
       <c r="K252" t="n">
         <v>-1.72</v>
@@ -23757,16 +23745,16 @@
         <v>3063.2</v>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H253" t="n">
-        <v>6358</v>
+        <v>38149</v>
       </c>
       <c r="I253" t="n">
-        <v>6126</v>
+        <v>36758</v>
       </c>
       <c r="J253" t="n">
-        <v>-232</v>
+        <v>-1391</v>
       </c>
       <c r="K253" t="n">
         <v>-3.65</v>
@@ -23836,16 +23824,16 @@
         <v>1850.1</v>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H254" t="n">
-        <v>5850</v>
+        <v>29250</v>
       </c>
       <c r="I254" t="n">
-        <v>5550</v>
+        <v>27752</v>
       </c>
       <c r="J254" t="n">
-        <v>-300</v>
+        <v>-1498</v>
       </c>
       <c r="K254" t="n">
         <v>-5.12</v>
@@ -23915,16 +23903,16 @@
         <v>1377.7</v>
       </c>
       <c r="G255" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="H255" t="n">
-        <v>5954</v>
+        <v>31261</v>
       </c>
       <c r="I255" t="n">
-        <v>5511</v>
+        <v>28932</v>
       </c>
       <c r="J255" t="n">
-        <v>-444</v>
+        <v>-2329</v>
       </c>
       <c r="K255" t="n">
         <v>-7.45</v>
@@ -24073,16 +24061,16 @@
         <v>1053.15</v>
       </c>
       <c r="G257" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H257" t="n">
-        <v>6332</v>
+        <v>34371</v>
       </c>
       <c r="I257" t="n">
-        <v>7372</v>
+        <v>40020</v>
       </c>
       <c r="J257" t="n">
-        <v>1041</v>
+        <v>5649</v>
       </c>
       <c r="K257" t="n">
         <v>16.43</v>
@@ -24154,16 +24142,16 @@
         <v>422.9</v>
       </c>
       <c r="G258" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="H258" t="n">
-        <v>7093</v>
+        <v>35859</v>
       </c>
       <c r="I258" t="n">
-        <v>7612</v>
+        <v>38484</v>
       </c>
       <c r="J258" t="n">
-        <v>519</v>
+        <v>2625</v>
       </c>
       <c r="K258" t="n">
         <v>7.32</v>
@@ -24235,16 +24223,16 @@
         <v>12589</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" t="n">
-        <v>0</v>
+        <v>11918</v>
       </c>
       <c r="I259" t="n">
-        <v>0</v>
+        <v>12589</v>
       </c>
       <c r="J259" t="n">
-        <v>0</v>
+        <v>671</v>
       </c>
       <c r="K259" t="n">
         <v>5.63</v>
@@ -24316,16 +24304,16 @@
         <v>7164.5</v>
       </c>
       <c r="G260" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H260" t="n">
-        <v>0</v>
+        <v>27360</v>
       </c>
       <c r="I260" t="n">
-        <v>0</v>
+        <v>28658</v>
       </c>
       <c r="J260" t="n">
-        <v>0</v>
+        <v>1298</v>
       </c>
       <c r="K260" t="n">
         <v>4.74</v>
@@ -24397,16 +24385,16 @@
         <v>745.8</v>
       </c>
       <c r="G261" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="H261" t="n">
-        <v>7984</v>
+        <v>42825</v>
       </c>
       <c r="I261" t="n">
-        <v>8204</v>
+        <v>44002</v>
       </c>
       <c r="J261" t="n">
-        <v>219</v>
+        <v>1177</v>
       </c>
       <c r="K261" t="n">
         <v>2.75</v>
@@ -24478,16 +24466,16 @@
         <v>344.7</v>
       </c>
       <c r="G262" t="n">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="H262" t="n">
-        <v>6113</v>
+        <v>31922</v>
       </c>
       <c r="I262" t="n">
-        <v>6205</v>
+        <v>32402</v>
       </c>
       <c r="J262" t="n">
-        <v>92</v>
+        <v>479</v>
       </c>
       <c r="K262" t="n">
         <v>1.5</v>
@@ -24559,16 +24547,16 @@
         <v>247.95</v>
       </c>
       <c r="G263" t="n">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="H263" t="n">
-        <v>6884</v>
+        <v>34930</v>
       </c>
       <c r="I263" t="n">
-        <v>6695</v>
+        <v>33969</v>
       </c>
       <c r="J263" t="n">
-        <v>-189</v>
+        <v>-960</v>
       </c>
       <c r="K263" t="n">
         <v>-2.75</v>
@@ -24640,16 +24628,16 @@
         <v>1973.4</v>
       </c>
       <c r="G264" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H264" t="n">
-        <v>4059</v>
+        <v>20293</v>
       </c>
       <c r="I264" t="n">
-        <v>3947</v>
+        <v>19734</v>
       </c>
       <c r="J264" t="n">
-        <v>-112</v>
+        <v>-559</v>
       </c>
       <c r="K264" t="n">
         <v>-2.75</v>
@@ -24721,16 +24709,16 @@
         <v>3787.8</v>
       </c>
       <c r="G265" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H265" t="n">
-        <v>3905</v>
+        <v>23429</v>
       </c>
       <c r="I265" t="n">
-        <v>3788</v>
+        <v>22727</v>
       </c>
       <c r="J265" t="n">
-        <v>-117</v>
+        <v>-703</v>
       </c>
       <c r="K265" t="n">
         <v>-3</v>
@@ -24802,16 +24790,16 @@
         <v>1638.9</v>
       </c>
       <c r="G266" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H266" t="n">
-        <v>8495</v>
+        <v>45873</v>
       </c>
       <c r="I266" t="n">
-        <v>8194</v>
+        <v>44250</v>
       </c>
       <c r="J266" t="n">
-        <v>-300</v>
+        <v>-1623</v>
       </c>
       <c r="K266" t="n">
         <v>-3.54</v>
@@ -24883,16 +24871,16 @@
         <v>1447.2</v>
       </c>
       <c r="G267" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H267" t="n">
-        <v>9043</v>
+        <v>46720</v>
       </c>
       <c r="I267" t="n">
-        <v>8683</v>
+        <v>44863</v>
       </c>
       <c r="J267" t="n">
-        <v>-359</v>
+        <v>-1857</v>
       </c>
       <c r="K267" t="n">
         <v>-3.97</v>
@@ -24964,16 +24952,16 @@
         <v>1380.5</v>
       </c>
       <c r="G268" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H268" t="n">
-        <v>2903</v>
+        <v>20322</v>
       </c>
       <c r="I268" t="n">
-        <v>2761</v>
+        <v>19327</v>
       </c>
       <c r="J268" t="n">
-        <v>-142</v>
+        <v>-995</v>
       </c>
       <c r="K268" t="n">
         <v>-4.9</v>
@@ -25045,16 +25033,16 @@
         <v>926.4</v>
       </c>
       <c r="G269" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H269" t="n">
-        <v>5968</v>
+        <v>32827</v>
       </c>
       <c r="I269" t="n">
-        <v>5558</v>
+        <v>30571</v>
       </c>
       <c r="J269" t="n">
-        <v>-410</v>
+        <v>-2256</v>
       </c>
       <c r="K269" t="n">
         <v>-6.87</v>
@@ -25126,16 +25114,16 @@
         <v>1687.9</v>
       </c>
       <c r="G270" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H270" t="n">
-        <v>5550</v>
+        <v>31452</v>
       </c>
       <c r="I270" t="n">
-        <v>5064</v>
+        <v>28694</v>
       </c>
       <c r="J270" t="n">
-        <v>-487</v>
+        <v>-2757</v>
       </c>
       <c r="K270" t="n">
         <v>-8.77</v>
@@ -25207,16 +25195,16 @@
         <v>318.65</v>
       </c>
       <c r="G271" t="n">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="H271" t="n">
-        <v>7086</v>
+        <v>35845</v>
       </c>
       <c r="I271" t="n">
-        <v>5417</v>
+        <v>27404</v>
       </c>
       <c r="J271" t="n">
-        <v>-1669</v>
+        <v>-8441</v>
       </c>
       <c r="K271" t="n">
         <v>-23.55</v>
@@ -25288,16 +25276,16 @@
         <v>318.35</v>
       </c>
       <c r="G272" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="H272" t="n">
-        <v>3561</v>
+        <v>18313</v>
       </c>
       <c r="I272" t="n">
-        <v>4457</v>
+        <v>22921</v>
       </c>
       <c r="J272" t="n">
-        <v>896</v>
+        <v>4608</v>
       </c>
       <c r="K272" t="n">
         <v>25.16</v>
@@ -25369,16 +25357,16 @@
         <v>299.55</v>
       </c>
       <c r="G273" t="n">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="H273" t="n">
-        <v>4711</v>
+        <v>24299</v>
       </c>
       <c r="I273" t="n">
-        <v>5691</v>
+        <v>29356</v>
       </c>
       <c r="J273" t="n">
-        <v>980</v>
+        <v>5057</v>
       </c>
       <c r="K273" t="n">
         <v>20.81</v>
@@ -25450,16 +25438,16 @@
         <v>399.15</v>
       </c>
       <c r="G274" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="H274" t="n">
-        <v>3792</v>
+        <v>18958</v>
       </c>
       <c r="I274" t="n">
-        <v>4391</v>
+        <v>21953</v>
       </c>
       <c r="J274" t="n">
-        <v>599</v>
+        <v>2995</v>
       </c>
       <c r="K274" t="n">
         <v>15.8</v>
@@ -25531,16 +25519,16 @@
         <v>4385.2</v>
       </c>
       <c r="G275" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H275" t="n">
-        <v>3997</v>
+        <v>35973</v>
       </c>
       <c r="I275" t="n">
-        <v>4385</v>
+        <v>39467</v>
       </c>
       <c r="J275" t="n">
-        <v>388</v>
+        <v>3494</v>
       </c>
       <c r="K275" t="n">
         <v>9.710000000000001</v>
@@ -25612,16 +25600,16 @@
         <v>4014</v>
       </c>
       <c r="G276" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H276" t="n">
-        <v>7576</v>
+        <v>41666</v>
       </c>
       <c r="I276" t="n">
-        <v>8028</v>
+        <v>44154</v>
       </c>
       <c r="J276" t="n">
-        <v>452</v>
+        <v>2488</v>
       </c>
       <c r="K276" t="n">
         <v>5.97</v>
@@ -25693,16 +25681,16 @@
         <v>775</v>
       </c>
       <c r="G277" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="H277" t="n">
-        <v>6712</v>
+        <v>36544</v>
       </c>
       <c r="I277" t="n">
-        <v>6975</v>
+        <v>37975</v>
       </c>
       <c r="J277" t="n">
-        <v>263</v>
+        <v>1431</v>
       </c>
       <c r="K277" t="n">
         <v>3.92</v>
@@ -25774,16 +25762,16 @@
         <v>1430.8</v>
       </c>
       <c r="G278" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H278" t="n">
-        <v>5522</v>
+        <v>31752</v>
       </c>
       <c r="I278" t="n">
-        <v>5723</v>
+        <v>32908</v>
       </c>
       <c r="J278" t="n">
-        <v>201</v>
+        <v>1157</v>
       </c>
       <c r="K278" t="n">
         <v>3.64</v>
@@ -25855,16 +25843,16 @@
         <v>1458.6</v>
       </c>
       <c r="G279" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="H279" t="n">
-        <v>9965</v>
+        <v>54097</v>
       </c>
       <c r="I279" t="n">
-        <v>10210</v>
+        <v>55427</v>
       </c>
       <c r="J279" t="n">
-        <v>245</v>
+        <v>1330</v>
       </c>
       <c r="K279" t="n">
         <v>2.46</v>
@@ -25936,16 +25924,16 @@
         <v>1068.45</v>
       </c>
       <c r="G280" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="H280" t="n">
-        <v>7372</v>
+        <v>36860</v>
       </c>
       <c r="I280" t="n">
-        <v>7479</v>
+        <v>37396</v>
       </c>
       <c r="J280" t="n">
-        <v>107</v>
+        <v>536</v>
       </c>
       <c r="K280" t="n">
         <v>1.45</v>
@@ -26017,16 +26005,16 @@
         <v>1886.8</v>
       </c>
       <c r="G281" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H281" t="n">
-        <v>5920</v>
+        <v>37495</v>
       </c>
       <c r="I281" t="n">
-        <v>5660</v>
+        <v>35849</v>
       </c>
       <c r="J281" t="n">
-        <v>-260</v>
+        <v>-1645</v>
       </c>
       <c r="K281" t="n">
         <v>-4.39</v>
@@ -26098,16 +26086,16 @@
         <v>1375.7</v>
       </c>
       <c r="G282" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H282" t="n">
-        <v>5789</v>
+        <v>31838</v>
       </c>
       <c r="I282" t="n">
-        <v>5503</v>
+        <v>30265</v>
       </c>
       <c r="J282" t="n">
-        <v>-286</v>
+        <v>-1573</v>
       </c>
       <c r="K282" t="n">
         <v>-4.94</v>
@@ -26179,16 +26167,16 @@
         <v>11586</v>
       </c>
       <c r="G283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H283" t="n">
-        <v>0</v>
+        <v>12589</v>
       </c>
       <c r="I283" t="n">
-        <v>0</v>
+        <v>11586</v>
       </c>
       <c r="J283" t="n">
-        <v>0</v>
+        <v>-1003</v>
       </c>
       <c r="K283" t="n">
         <v>-7.97</v>
@@ -26341,16 +26329,16 @@
         <v>539.55</v>
       </c>
       <c r="G285" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="H285" t="n">
-        <v>3645</v>
+        <v>20655</v>
       </c>
       <c r="I285" t="n">
-        <v>3237</v>
+        <v>18345</v>
       </c>
       <c r="J285" t="n">
-        <v>-408</v>
+        <v>-2310</v>
       </c>
       <c r="K285" t="n">
         <v>-11.19</v>
@@ -26422,16 +26410,16 @@
         <v>771.7</v>
       </c>
       <c r="G286" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="H286" t="n">
-        <v>11117</v>
+        <v>56510</v>
       </c>
       <c r="I286" t="n">
-        <v>9260</v>
+        <v>47074</v>
       </c>
       <c r="J286" t="n">
-        <v>-1856</v>
+        <v>-9437</v>
       </c>
       <c r="K286" t="n">
         <v>-16.7</v>
@@ -26490,47 +26478,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Horizon</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Win Rate %</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Median Return %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Beat Nifty %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Worst Cycle %</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sharpe (ann)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Chosen</t>
         </is>
@@ -26560,7 +26548,7 @@
         <v>-5.6</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -26626,7 +26614,7 @@
         <v>-6.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -26659,7 +26647,7 @@
         <v>-8.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -26819,52 +26807,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Start Rs</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Return %</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>End Rs</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>If Nifty Rs</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Beat Nifty</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Win Ratio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Largest Winner</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Largest Loser</t>
         </is>
@@ -26877,16 +26865,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C2" t="n">
         <v>12.6</v>
       </c>
       <c r="D2" t="n">
-        <v>112600</v>
+        <v>563000</v>
       </c>
       <c r="E2" t="n">
-        <v>111800</v>
+        <v>559000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -26919,16 +26907,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112600</v>
+        <v>563000</v>
       </c>
       <c r="C3" t="n">
         <v>-3.6</v>
       </c>
       <c r="D3" t="n">
-        <v>108546</v>
+        <v>542732</v>
       </c>
       <c r="E3" t="n">
-        <v>112359</v>
+        <v>561795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -26961,16 +26949,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>108546</v>
+        <v>542732</v>
       </c>
       <c r="C4" t="n">
         <v>-1.9</v>
       </c>
       <c r="D4" t="n">
-        <v>106484</v>
+        <v>532420</v>
       </c>
       <c r="E4" t="n">
-        <v>114494</v>
+        <v>572469</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -27003,16 +26991,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>106484</v>
+        <v>532420</v>
       </c>
       <c r="C5" t="n">
         <v>-0.3</v>
       </c>
       <c r="D5" t="n">
-        <v>106165</v>
+        <v>530823</v>
       </c>
       <c r="E5" t="n">
-        <v>101900</v>
+        <v>509498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -27045,16 +27033,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>106165</v>
+        <v>530823</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>113596</v>
+        <v>567980</v>
       </c>
       <c r="E6" t="n">
-        <v>110357</v>
+        <v>551786</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27087,16 +27075,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113596</v>
+        <v>567980</v>
       </c>
       <c r="C7" t="n">
         <v>14.8</v>
       </c>
       <c r="D7" t="n">
-        <v>130408</v>
+        <v>652042</v>
       </c>
       <c r="E7" t="n">
-        <v>113778</v>
+        <v>568891</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -27129,16 +27117,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>130408</v>
+        <v>652042</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>134321</v>
+        <v>671603</v>
       </c>
       <c r="E8" t="n">
-        <v>113437</v>
+        <v>567184</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -27171,16 +27159,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>134321</v>
+        <v>671603</v>
       </c>
       <c r="C9" t="n">
         <v>13.2</v>
       </c>
       <c r="D9" t="n">
-        <v>152051</v>
+        <v>760254</v>
       </c>
       <c r="E9" t="n">
-        <v>123646</v>
+        <v>618231</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -27213,16 +27201,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>152051</v>
+        <v>760254</v>
       </c>
       <c r="C10" t="n">
         <v>9.1</v>
       </c>
       <c r="D10" t="n">
-        <v>165887</v>
+        <v>829437</v>
       </c>
       <c r="E10" t="n">
-        <v>125748</v>
+        <v>628741</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -27255,16 +27243,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>165887</v>
+        <v>829437</v>
       </c>
       <c r="C11" t="n">
         <v>13.6</v>
       </c>
       <c r="D11" t="n">
-        <v>188448</v>
+        <v>942241</v>
       </c>
       <c r="E11" t="n">
-        <v>140712</v>
+        <v>703561</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -27297,16 +27285,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>188448</v>
+        <v>942241</v>
       </c>
       <c r="C12" t="n">
         <v>0.8</v>
       </c>
       <c r="D12" t="n">
-        <v>189956</v>
+        <v>949779</v>
       </c>
       <c r="E12" t="n">
-        <v>140009</v>
+        <v>700043</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -27339,16 +27327,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>189956</v>
+        <v>949779</v>
       </c>
       <c r="C13" t="n">
         <v>12.2</v>
       </c>
       <c r="D13" t="n">
-        <v>213130</v>
+        <v>1065652</v>
       </c>
       <c r="E13" t="n">
-        <v>156110</v>
+        <v>780548</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -27381,16 +27369,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>213130</v>
+        <v>1065652</v>
       </c>
       <c r="C14" t="n">
         <v>4.2</v>
       </c>
       <c r="D14" t="n">
-        <v>222082</v>
+        <v>1110409</v>
       </c>
       <c r="E14" t="n">
-        <v>158139</v>
+        <v>790696</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -27423,16 +27411,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>222082</v>
+        <v>1110409</v>
       </c>
       <c r="C15" t="n">
         <v>-6.4</v>
       </c>
       <c r="D15" t="n">
-        <v>207869</v>
+        <v>1039343</v>
       </c>
       <c r="E15" t="n">
-        <v>148493</v>
+        <v>742463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -27465,16 +27453,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>207869</v>
+        <v>1039343</v>
       </c>
       <c r="C16" t="n">
         <v>3.3</v>
       </c>
       <c r="D16" t="n">
-        <v>214728</v>
+        <v>1073641</v>
       </c>
       <c r="E16" t="n">
-        <v>154284</v>
+        <v>771419</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -27507,16 +27495,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>214728</v>
+        <v>1073641</v>
       </c>
       <c r="C17" t="n">
         <v>1.9</v>
       </c>
       <c r="D17" t="n">
-        <v>218808</v>
+        <v>1094041</v>
       </c>
       <c r="E17" t="n">
-        <v>160455</v>
+        <v>802276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -27549,16 +27537,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>218808</v>
+        <v>1094041</v>
       </c>
       <c r="C18" t="n">
         <v>2.7</v>
       </c>
       <c r="D18" t="n">
-        <v>224716</v>
+        <v>1123580</v>
       </c>
       <c r="E18" t="n">
-        <v>164146</v>
+        <v>820728</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -27591,16 +27579,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>224716</v>
+        <v>1123580</v>
       </c>
       <c r="C19" t="n">
         <v>-1.6</v>
       </c>
       <c r="D19" t="n">
-        <v>221120</v>
+        <v>1105602</v>
       </c>
       <c r="E19" t="n">
-        <v>160206</v>
+        <v>801031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -27633,16 +27621,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>221120</v>
+        <v>1105602</v>
       </c>
       <c r="C20" t="n">
         <v>0.8</v>
       </c>
       <c r="D20" t="n">
-        <v>222889</v>
+        <v>1114447</v>
       </c>
       <c r="E20" t="n">
-        <v>152676</v>
+        <v>763382</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -27675,16 +27663,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="C21" t="n">
         <v>122.9</v>
       </c>
       <c r="D21" t="n">
-        <v>222889</v>
+        <v>1114447</v>
       </c>
       <c r="E21" t="n">
-        <v>152676</v>
+        <v>763382</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -27711,17 +27699,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>% of Capital</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Holdings</t>
         </is>
@@ -27730,12 +27718,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27750,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27760,12 +27748,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27780,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27790,12 +27778,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27805,12 +27793,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27820,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27835,12 +27823,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27894,12 +27882,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRITANNIA (50)</t>
+          <t>BRITANNIA (51)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BRITANNIA, IRCTC, KOTAKBANK</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MARICO, PIDILITIND, SBILIFE</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-22  /  2026-07-22</t>
+          <t>2026-07-23  /  2026-07-23</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.5%</t>
+          <t>+2.6%</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rs512,500</t>
+          <t>Rs513,000</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>64</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H2" t="n">
         <v>99</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8905</v>
+        <v>8910</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8696 - 9114</t>
+          <t>8701 - 9119</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35620</v>
+        <v>35640</v>
       </c>
       <c r="W2" t="n">
         <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H3" t="n">
         <v>96</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1941.6</v>
+        <v>1936.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1888 - 1995</t>
+          <t>1883 - 1989</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.2%)</t>
+          <t>Above 200-DMA (+9.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23299</v>
+        <v>23234</v>
       </c>
       <c r="W3" t="n">
         <v>12</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; LUPIN: 74, ZYDUSLIFE: 74, BIOCON: 73</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; ZYDUSLIFE: 74, BIOCON: 73, LUPIN: 72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.2%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="n">
         <v>94</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1450.7</v>
+        <v>1442.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1409 - 1492</t>
+          <t>1401 - 1483</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.7%)</t>
+          <t>Above 200-DMA (+7.1%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>18859</v>
+        <v>15864</v>
       </c>
       <c r="W4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; FEDERALBNK: 69, LICI: 66, SBIN: 65</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; FEDERALBNK: 69, SBIN: 67, LICI: 64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.7%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.1%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +9 = 74</t>
+          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +10 · Regime +9 · Sector +8 = 74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,54 +1885,54 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Telecom</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2446.6</v>
+        <v>1948.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2384 - 2509</t>
+          <t>1894 - 2003</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3% to +15%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.0%)</t>
+          <t>Below 200-DMA (-0.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>26913</v>
+        <v>25333</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X5" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 74; SUNPHARMA: 79, ZYDUSLIFE: 74, BIOCON: 73. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 74; TATACOMM: 55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.0%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-0.1%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +8 = 73</t>
+          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +9 = 72</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2003,58 +2003,58 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G6" t="n">
         <v>76</v>
       </c>
-      <c r="G6" t="n">
-        <v>46</v>
-      </c>
       <c r="H6" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I6" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1942.8</v>
+        <v>2398</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1889 - 1997</t>
+          <t>2336 - 2460</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.4%)</t>
+          <t>Above 200-DMA (+8.7%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>25256</v>
+        <v>26378</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 73; TATACOMM: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 72; SUNPHARMA: 79, ZYDUSLIFE: 74, BIOCON: 73. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-0.4%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.7%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,41 +2103,41 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +4 · Trend/Tech +3 = 65</t>
+          <t>Risk/Vol +22 · Historical +17 · Trend/Tech +14 · Regime +9 · Sector +4 = 66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="H7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>347.4</v>
+        <v>289.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>338 - 357</t>
+          <t>280 - 298</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Above 200-DMA (+1.1%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>29872</v>
+        <v>22558</v>
       </c>
       <c r="W7" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="X7" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,70 +2205,70 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 66, POWERGRID: 58, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 66; NHPC: 66, NTPC: 65, JSWENERGY: 58</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-2.7%) • sector strength 41/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+1.1%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +6 · Sector +6 = 62</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +4 · Trend/Tech +3 = 65</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I8" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>383</v>
+        <v>348.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>371 - 395</t>
+          <t>339 - 358</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.4%)</t>
+          <t>Below 200-DMA (-2.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>22977</v>
+        <v>30333</v>
       </c>
       <c r="W8" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="X8" t="n">
-        <v>7.7</v>
+        <v>10.2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 62; ICICIBANK: 76, FEDERALBNK: 69, LICI: 66. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 66, POWERGRID: 66, JSWENERGY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.4%) • sector strength 59/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-2.3%) • sector strength 35/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +7 · Sector +4 = 60</t>
+          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +7 · Sector +6 = 63</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1299.1</v>
+        <v>381</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1261 - 1338</t>
+          <t>370 - 392</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-1% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.1%)</t>
+          <t>Below 200-DMA (-5.9%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>16888</v>
+        <v>15238</v>
       </c>
       <c r="W9" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="X9" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 60; IOC: 50, OIL: 48, ONGC: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 63; ICICIBANK: 76, FEDERALBNK: 69, SBIN: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.1%) • sector strength 35/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.9%) • sector strength 59/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +4 = 58</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +7 · Sector +4 = 60</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,10 +2478,10 @@
         <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H10" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" t="n">
         <v>41</v>
@@ -2491,42 +2491,42 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>285.2</v>
+        <v>1283.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>277 - 294</t>
+          <t>1245 - 1322</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-1% to +7%</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.3%)</t>
+          <t>Below 200-DMA (-9.1%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>22816</v>
+        <v>16684</v>
       </c>
       <c r="W10" t="n">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="X10" t="n">
-        <v>7.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NHPC: 66, NTPC: 65, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 60; IOC: 51, ONGC: 49, OIL: 47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.3%) • sector strength 41/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.1%) • sector strength 41/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
         <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
         <v>98</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>279.8</v>
+        <v>280.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>272 - 287</t>
+          <t>273 - 288</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.1%)</t>
+          <t>Below 200-DMA (-16.7%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>22380</v>
+        <v>30035</v>
       </c>
       <c r="W11" t="n">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="X11" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; TATACONSUM: 55, COLPAL: 51, DABUR: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; COLPAL: 58, TATACONSUM: 55, BRITANNIA: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 12/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.7%) • sector strength 12/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +5 · Sector +5 = 53</t>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +7 · Sector +1 = 51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2711,36 +2711,36 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="H12" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I12" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>497.6</v>
+        <v>5484.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>482 - 513</t>
+          <t>5340 - 5629</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.5%)</t>
+          <t>Below 200-DMA (-4.2%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14928</v>
+        <v>27422</v>
       </c>
       <c r="W12" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>10.1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 60, INDIGO: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; COLPAL: 58, TATACONSUM: 55, GODREJCP: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.5%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.2%) • sector strength 12/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +6 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +5 · Trend/Tech +3 = 51</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2825,40 +2825,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5450.5</v>
+        <v>491.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5307 - 5594</t>
+          <t>476 - 507</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.8%)</t>
+          <t>Below 200-DMA (-18.3%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,21 +2889,21 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>27252</v>
+        <v>15738</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="X13" t="n">
-        <v>9.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; TATACONSUM: 55, COLPAL: 51, DABUR: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 60, INDIGO: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.8%) • sector strength 12/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-18.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -26602,10 +26602,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E4" t="n">
         <v>59</v>
@@ -26638,7 +26638,7 @@
         <v>67</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="E5" t="n">
         <v>67</v>
@@ -26672,13 +26672,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" t="n">
         <v>2.6</v>
       </c>
       <c r="E6" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>-7.9</v>
@@ -26705,13 +26705,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D7" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>-13.3</v>
@@ -26738,13 +26738,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
         <v>-8.699999999999999</v>
@@ -26771,13 +26771,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D9" t="n">
         <v>6.8</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F9" t="n">
         <v>-5.5</v>
@@ -27718,12 +27718,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27733,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27748,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-23  /  2026-07-23</t>
+          <t>2026-07-24  /  2026-07-24</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8910</v>
+        <v>8854.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8701 - 9119</t>
+          <t>8647 - 9062</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+15.5%)</t>
+          <t>Above 200-DMA (+14.7%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35640</v>
+        <v>35418</v>
       </c>
       <c r="W2" t="n">
         <v>4</v>
       </c>
       <c r="X2" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+15.5%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.7%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
         </is>
       </c>
     </row>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1936.2</v>
+        <v>1953.6</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1883 - 1989</t>
+          <t>1901 - 2007</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+9.8%)</t>
+          <t>Above 200-DMA (+10.7%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23234</v>
+        <v>23443</v>
       </c>
       <c r="W3" t="n">
         <v>12</v>
       </c>
       <c r="X3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; ZYDUSLIFE: 74, BIOCON: 73, LUPIN: 72</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; CIPLA: 75, ZYDUSLIFE: 74, BIOCON: 73</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.8%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.7%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +6 = 76</t>
+          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +6 = 77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,7 +1770,7 @@
         <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" t="n">
         <v>94</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1442.2</v>
+        <v>1428.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1401 - 1483</t>
+          <t>1388 - 1469</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.1%)</t>
+          <t>Above 200-DMA (+6.0%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>15864</v>
+        <v>15711</v>
       </c>
       <c r="W4" t="n">
         <v>11</v>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; FEDERALBNK: 69, SBIN: 67, LICI: 64</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; FEDERALBNK: 69, KOTAKBANK: 66, YESBANK: 63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.1%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.0%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +10 · Regime +9 · Sector +8 = 74</t>
+          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +8 = 73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,7 +1888,7 @@
         <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H5" t="n">
         <v>94</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1948.7</v>
+        <v>1901.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1894 - 2003</t>
+          <t>1848 - 1955</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.1%)</t>
+          <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>25333</v>
+        <v>24720</v>
       </c>
       <c r="W5" t="n">
         <v>13</v>
       </c>
       <c r="X5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 74; TATACOMM: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 73; TATACOMM: 54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-0.1%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H6" t="n">
         <v>98</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2398</v>
+        <v>2376.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2336 - 2460</t>
+          <t>2315 - 2437</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.7%)</t>
+          <t>Above 200-DMA (+7.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,11 +2063,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>26378</v>
+        <v>26138</v>
       </c>
       <c r="W6" t="n">
         <v>11</v>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 72; SUNPHARMA: 79, ZYDUSLIFE: 74, BIOCON: 73. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 72; SUNPHARMA: 79, CIPLA: 75, ZYDUSLIFE: 74. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.7%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.6%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +17 · Trend/Tech +14 · Regime +9 · Sector +4 = 66</t>
+          <t>Risk/Vol +23 · Historical +17 · Trend/Tech +14 · Regime +9 · Sector +3 = 66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2127,10 +2127,10 @@
         <v>69</v>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>289.2</v>
+        <v>288.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>280 - 298</t>
+          <t>280 - 297</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+1.1%)</t>
+          <t>Above 200-DMA (+0.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,11 +2181,11 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>22558</v>
+        <v>22480</v>
       </c>
       <c r="W7" t="n">
         <v>78</v>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 66; NHPC: 66, NTPC: 65, JSWENERGY: 58</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 66; NHPC: 65, NTPC: 64, JSWENERGY: 57</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • above 200-dma (+1.1%) • sector strength 35/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • above 200-dma (+0.7%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2221,54 +2221,54 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +4 · Trend/Tech +3 = 65</t>
+          <t>Risk/Vol +23 · Historical +19 · Trend/Tech +9 · Regime +9 · Sector +6 = 66</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="H8" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>348.6</v>
+        <v>383</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>339 - 358</t>
+          <t>372 - 394</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.3%)</t>
+          <t>Below 200-DMA (-5.4%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>30333</v>
+        <v>15320</v>
       </c>
       <c r="W8" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="X8" t="n">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 66, POWERGRID: 66, JSWENERGY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 66; ICICIBANK: 77, FEDERALBNK: 69, YESBANK: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-2.3%) • sector strength 35/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.4%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2339,16 +2339,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +7 · Sector +6 = 63</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2357,36 +2357,36 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G9" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>381</v>
+        <v>347</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>370 - 392</t>
+          <t>337 - 356</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.9%)</t>
+          <t>Below 200-DMA (-2.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>15238</v>
+        <v>30532</v>
       </c>
       <c r="W9" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="X9" t="n">
-        <v>5.2</v>
+        <v>10.2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 63; ICICIBANK: 76, FEDERALBNK: 69, SBIN: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 66, NHPC: 65, JSWENERGY: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.9%) • sector strength 59/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-2.8%) • sector strength 29/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +7 · Sector +4 = 60</t>
+          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +4 = 58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,7 +2478,7 @@
         <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
         <v>92</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1283.4</v>
+        <v>1268.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1245 - 1322</t>
+          <t>1231 - 1306</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.1%)</t>
+          <t>Below 200-DMA (-10.2%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>16684</v>
+        <v>24100</v>
       </c>
       <c r="W10" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="X10" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 60; IOC: 51, ONGC: 49, OIL: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 58; ONGC: 52, OIL: 50, IOC: 48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.1%) • sector strength 41/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-10.2%) • sector strength 41/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
         <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" t="n">
         <v>98</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>280.7</v>
+        <v>281</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>273 - 288</t>
+          <t>274 - 288</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.7%)</t>
+          <t>Below 200-DMA (-16.5%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>30035</v>
+        <v>30343</v>
       </c>
       <c r="W11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; COLPAL: 58, TATACONSUM: 55, BRITANNIA: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; TATACONSUM: 54, BRITANNIA: 51, COLPAL: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.7%) • sector strength 12/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.5%) • sector strength 12/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" t="n">
         <v>97</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>5484.5</v>
+        <v>5354</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5340 - 5629</t>
+          <t>5213 - 5495</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.2%)</t>
+          <t>Below 200-DMA (-6.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>27422</v>
+        <v>21416</v>
       </c>
       <c r="W12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X12" t="n">
-        <v>10.1</v>
+        <v>7.4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; COLPAL: 58, TATACONSUM: 55, GODREJCP: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; TATACONSUM: 54, ITC: 51, COLPAL: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.2%) • sector strength 12/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-6.4%) • sector strength 12/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
         <v>88</v>
       </c>
       <c r="I13" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>491.8</v>
+        <v>491.7</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>476 - 507</t>
+          <t>477 - 507</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-18.3%)</t>
+          <t>Below 200-DMA (-18.2%)</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>15738</v>
+        <v>16718</v>
       </c>
       <c r="W13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="X13" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 60, INDIGO: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 60, INDIGO: 41. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-18.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-18.2%) • sector strength 53/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27718,12 +27718,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27733,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APOLLOHOSP (81)</t>
+          <t>SUNPHARMA (77)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRITANNIA (51)</t>
+          <t>COALINDIA (50)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>BEL, COALINDIA, PIDILITIND, TATAPOWER</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APOLLOHOSP, BHARTIARTL, POWERGRID, RELIANCE</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-24  /  2026-07-24</t>
+          <t>2026-07-29  /  2026-07-29</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +19 · Trend/Tech +19 · Regime +9 · Sector +9 = 81</t>
+          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +8 = 77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1531,58 +1531,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H2" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I2" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>8854.5</v>
+        <v>1974</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8647 - 9062</t>
+          <t>1921 - 2027</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +14%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+14.7%)</t>
+          <t>Above 200-DMA (+11.5%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35418</v>
+        <v>35532</v>
       </c>
       <c r="W2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="X2" t="n">
-        <v>14.1</v>
+        <v>12.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Healthcare name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>No same-sector peer in the universe.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 77; CIPLA: 74, LUPIN: 73, ZYDUSLIFE: 70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Healthcare holding (low vol) • above 200-dma (+14.7%) • outperforming Nifty • sector strength 94/100 • regime cautious (partial deploy) • 4 similar past recs: 75% positive, median +5.9%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.5%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Trend/Tech +19 · Historical +18 · Regime +9 · Sector +9 = 79</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +7 = 77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1649,58 +1649,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1953.6</v>
+        <v>1440.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1901 - 2007</t>
+          <t>1399 - 1481</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-4% to +14%</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.7%)</t>
+          <t>Above 200-DMA (+6.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>23443</v>
+        <v>15841</v>
       </c>
       <c r="W3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X3" t="n">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 79; CIPLA: 75, ZYDUSLIFE: 74, BIOCON: 73</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; FEDERALBNK: 68, BAJAJFINSV: 67, LICI: 65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.7%) • outperforming Nifty • sector strength 88/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.8%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +6 = 77</t>
+          <t>Risk/Vol +24 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +8 = 73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I4" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1428.3</v>
+        <v>2443.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1388 - 1469</t>
+          <t>2380 - 2507</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.0%)</t>
+          <t>Above 200-DMA (+10.3%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>15711</v>
+        <v>31764</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X4" t="n">
-        <v>5.6</v>
+        <v>10.9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; FEDERALBNK: 69, KOTAKBANK: 66, YESBANK: 63</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 73; SUNPHARMA: 77, CIPLA: 74, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.0%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.3%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +23 · Trend/Tech +9 · Regime +9 · Sector +8 = 73</t>
+          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +9 = 71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,58 +1885,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1901.5</v>
+        <v>1619.4</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1848 - 1955</t>
+          <t>1568 - 1671</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-3% to +15%</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.6%)</t>
+          <t>Above 200-DMA (+10.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>24720</v>
+        <v>21052</v>
       </c>
       <c r="W5" t="n">
         <v>13</v>
       </c>
       <c r="X5" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Telecom name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BHARTIARTL: 73; TATACOMM: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 71; NAVINFLUOR: 64, CHAMBLFERT: 55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Telecom holding (low vol) • below 200-dma (-2.6%) • outperforming Nifty • sector strength 82/100 • regime cautious (partial deploy) • 13 similar past recs: 69% positive, median +12.5%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.1%) • outperforming Nifty • sector strength 87/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +9 = 72</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +4 · Sector +3 = 65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2003,36 +2003,36 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="H6" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2376.2</v>
+        <v>342.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2315 - 2437</t>
+          <t>333 - 352</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.6%)</t>
+          <t>Below 200-DMA (-4.1%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>26138</v>
+        <v>26026</v>
       </c>
       <c r="W6" t="n">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="X6" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 72; SUNPHARMA: 79, CIPLA: 75, ZYDUSLIFE: 74. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; POWERGRID: 56, JSWENERGY: 54, NHPC: 54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.6%) • sector strength 88/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.1%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Trend/Tech +14 · Regime +9 · Sector +3 = 66</t>
+          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Sector +7 · Trend/Tech +6 = 63</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>288.2</v>
+        <v>388.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>280 - 297</t>
+          <t>377 - 400</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+0.7%)</t>
+          <t>Below 200-DMA (-3.9%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>22480</v>
+        <v>15532</v>
       </c>
       <c r="W7" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="X7" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 66; NHPC: 65, NTPC: 64, JSWENERGY: 57</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 63; ICICIBANK: 77, FEDERALBNK: 68, BAJAJFINSV: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • above 200-dma (+0.7%) • sector strength 29/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.9%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +19 · Trend/Tech +9 · Regime +9 · Sector +6 = 66</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,46 +2239,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>383</v>
+        <v>287.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>372 - 394</t>
+          <t>280 - 294</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.4%)</t>
+          <t>Below 200-DMA (-14.1%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>15320</v>
+        <v>24412</v>
       </c>
       <c r="W8" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="X8" t="n">
-        <v>5.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,32 +2323,32 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 66; ICICIBANK: 77, FEDERALBNK: 69, YESBANK: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; BRITANNIA: 52, DABUR: 51, HINDUNILVR: 50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-5.4%) • outperforming Nifty • sector strength 59/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.1%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
+          <t>Risk/Vol +23 · Historical +15 · Regime +9 · Trend/Tech +4 · Sector +3 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2357,23 +2357,23 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>347</v>
+        <v>373.5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>337 - 356</t>
+          <t>363 - 384</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.8%)</t>
+          <t>Below 200-DMA (-4.5%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>30532</v>
+        <v>22039</v>
       </c>
       <c r="W9" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="X9" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,27 +2441,27 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 66, NHPC: 65, JSWENERGY: 57. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NTPC: 65, POWERGRID: 56, JSWENERGY: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-2.8%) • sector strength 29/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.5%) • sector strength 27/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +4 = 58</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +3 = 53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2471,62 +2471,62 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I10" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1268.4</v>
+        <v>383.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1231 - 1306</t>
+          <t>372 - 396</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-1% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.2%)</t>
+          <t>Below 200-DMA (-8.7%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>24100</v>
+        <v>23031</v>
       </c>
       <c r="W10" t="n">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="X10" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — RELIANCE: 58; ONGC: 52, OIL: 50, IOC: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 60, POLYCAB: 55, KEI: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-10.2%) • sector strength 41/100 • regime cautious (partial deploy) • 8 similar past recs: 62% positive, median +4.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.7%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2575,76 +2575,76 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>51</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 51</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>44</v>
-      </c>
       <c r="G11" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>281</v>
+        <v>410.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>274 - 288</t>
+          <t>398 - 423</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.5%)</t>
+          <t>Below 200-DMA (-3.5%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>30343</v>
+        <v>29966</v>
       </c>
       <c r="W11" t="n">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="X11" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 51; TATACONSUM: 54, BRITANNIA: 51, COLPAL: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 43, HINDZINC: 38</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.5%) • sector strength 12/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.5%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +7 · Sector +1 = 51</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +6 · Trend/Tech +5 = 54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2707,40 +2707,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="H12" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>5354</v>
+        <v>493.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>5213 - 5495</t>
+          <t>479 - 509</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.4%)</t>
+          <t>Below 200-DMA (-17.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>21416</v>
+        <v>17276</v>
       </c>
       <c r="W12" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="X12" t="n">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; TATACONSUM: 54, ITC: 51, COLPAL: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60, INDIGO: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-6.4%) • sector strength 12/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.4%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +5 · Trend/Tech +3 = 51</t>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +7 · Sector +2 = 52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2825,40 +2825,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="H13" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I13" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>491.7</v>
+        <v>5560.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>477 - 507</t>
+          <t>5415 - 5706</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-18.2%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,21 +2889,21 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>16718</v>
+        <v>27802</v>
       </c>
       <c r="W13" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>10.6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 60, INDIGO: 41. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 55, DABUR: 51, HINDUNILVR: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-18.2%) • sector strength 53/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-2.7%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27718,12 +27718,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27748,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27763,42 +27763,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Telecom</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COALINDIA (50)</t>
+          <t>COALINDIA (49)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BEL, COALINDIA, PIDILITIND, TATAPOWER</t>
+          <t>POWERGRID</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>APOLLOHOSP, BHARTIARTL, POWERGRID, RELIANCE</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-29  /  2026-07-29</t>
+          <t>2026-07-30  /  2026-07-30</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +8 = 77</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +9 = 77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I2" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1974</v>
+        <v>1989.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1921 - 2027</t>
+          <t>1936 - 2044</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.5%)</t>
+          <t>Above 200-DMA (+12.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35532</v>
+        <v>35818</v>
       </c>
       <c r="W2" t="n">
         <v>18</v>
       </c>
       <c r="X2" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 77; CIPLA: 74, LUPIN: 73, ZYDUSLIFE: 70</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 77; CIPLA: 75, LUPIN: 74, ZYDUSLIFE: 71</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+11.5%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+12.3%) • outperforming Nifty • sector strength 87/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1652,10 +1652,10 @@
         <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
         <v>67</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1440.1</v>
+        <v>1437.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1399 - 1481</t>
+          <t>1397 - 1478</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.8%)</t>
+          <t>Above 200-DMA (+6.6%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15841</v>
+        <v>15817</v>
       </c>
       <c r="W3" t="n">
         <v>11</v>
       </c>
       <c r="X3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; FEDERALBNK: 68, BAJAJFINSV: 67, LICI: 65</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; FEDERALBNK: 69, BAJAJFINSV: 68, KOTAKBANK: 65</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.8%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.6%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +8 = 73</t>
+          <t>Risk/Vol +24 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +9 = 74</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1773,10 +1773,10 @@
         <v>86</v>
       </c>
       <c r="H4" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I4" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2443.4</v>
+        <v>2447</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2380 - 2507</t>
+          <t>2383 - 2511</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>31764</v>
+        <v>31811</v>
       </c>
       <c r="W4" t="n">
         <v>13</v>
       </c>
       <c r="X4" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 73; SUNPHARMA: 77, CIPLA: 74, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 74; SUNPHARMA: 77, CIPLA: 75, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.3%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.3%) • outperforming Nifty • sector strength 87/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +9 = 71</t>
+          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,13 +1888,13 @@
         <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
         <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1619.4</v>
+        <v>1629.9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1568 - 1671</t>
+          <t>1578 - 1682</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.1%)</t>
+          <t>Above 200-DMA (+10.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>21052</v>
+        <v>19559</v>
       </c>
       <c r="W5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 71; NAVINFLUOR: 64, CHAMBLFERT: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 62, CHAMBLFERT: 54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.1%) • outperforming Nifty • sector strength 87/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +4 · Sector +3 = 65</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +3 = 66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,7 +2006,7 @@
         <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
         <v>95</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>342.5</v>
+        <v>343.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>333 - 352</t>
+          <t>334 - 353</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.1%)</t>
+          <t>Below 200-DMA (-3.8%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>26026</v>
+        <v>25419</v>
       </c>
       <c r="W6" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; POWERGRID: 56, JSWENERGY: 54, NHPC: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 66; POWERGRID: 58, JSWENERGY: 56, TATAPOWER: 53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.1%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Sector +7 · Trend/Tech +6 = 63</t>
+          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +8 · Sector +7 = 65</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I7" t="n">
         <v>67</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>388.3</v>
+        <v>390.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>377 - 400</t>
+          <t>379 - 402</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.9%)</t>
+          <t>Below 200-DMA (-3.4%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>15532</v>
+        <v>14828</v>
       </c>
       <c r="W7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="X7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 63; ICICIBANK: 77, FEDERALBNK: 68, BAJAJFINSV: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 77, FEDERALBNK: 69, BAJAJFINSV: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.9%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.4%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +2 = 55</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +3 = 58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>287.2</v>
+        <v>282.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>280 - 294</t>
+          <t>275 - 290</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.1%)</t>
+          <t>Below 200-DMA (-1.1%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>24412</v>
+        <v>25457</v>
       </c>
       <c r="W8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="X8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 55; BRITANNIA: 52, DABUR: 51, HINDUNILVR: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 66, JSWENERGY: 56, TATAPOWER: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.1%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-1.1%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +15 · Regime +9 · Trend/Tech +4 · Sector +3 = 54</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>373.5</v>
+        <v>286.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>363 - 384</t>
+          <t>279 - 293</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.5%)</t>
+          <t>Below 200-DMA (-14.3%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>22039</v>
+        <v>24331</v>
       </c>
       <c r="W9" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="X9" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATAPOWER: 54; NTPC: 65, POWERGRID: 56, JSWENERGY: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 52, DABUR: 50, HINDUNILVR: 50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.5%) • sector strength 27/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.3%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2481,10 +2481,10 @@
         <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>383.9</v>
+        <v>387.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>372 - 396</t>
+          <t>375 - 400</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.7%)</t>
+          <t>Below 200-DMA (-7.8%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>23031</v>
+        <v>23253</v>
       </c>
       <c r="W10" t="n">
         <v>60</v>
       </c>
       <c r="X10" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 60, POLYCAB: 55, KEI: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 61, POLYCAB: 56, KEI: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-8.7%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.8%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +2 · Sector +1 = 49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2596,7 +2596,7 @@
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
         <v>87</v>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>410.5</v>
+        <v>410</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.5%)</t>
+          <t>Below 200-DMA (-3.7%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>29966</v>
+        <v>30344</v>
       </c>
       <c r="W11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 43, HINDZINC: 38</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 49; TATASTEEL: 47, SAIL: 43, HINDZINC: 39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.5%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.7%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H12" t="n">
         <v>88</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>493.6</v>
+        <v>496</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>479 - 509</t>
+          <t>481 - 511</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.4%)</t>
+          <t>Below 200-DMA (-16.8%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>17276</v>
+        <v>16864</v>
       </c>
       <c r="W12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.4%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.8%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2832,10 +2832,10 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I13" t="n">
         <v>20</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5560.5</v>
+        <v>5517.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5415 - 5706</t>
+          <t>5375 - 5660</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-3.4%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,11 +2889,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>27802</v>
+        <v>27588</v>
       </c>
       <c r="W13" t="n">
         <v>5</v>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 55, DABUR: 51, HINDUNILVR: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 54, DABUR: 50, HINDUNILVR: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-2.7%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-3.4%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -26542,7 +26542,7 @@
         <v>0.6</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
         <v>-5.6</v>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C8" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SUNPHARMA (77)</t>
+          <t>ICICIBANK (77)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COALINDIA (49)</t>
+          <t>BRITANNIA (50)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-30  /  2026-07-30</t>
+          <t>2026-07-31  /  2026-07-31</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +18 · Regime +9 · Sector +9 = 77</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +7 = 77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1531,58 +1531,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1989.9</v>
+        <v>1438.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1936 - 2044</t>
+          <t>1399 - 1478</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-4% to +14%</t>
+          <t>+2% to +8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+12.3%)</t>
+          <t>Above 200-DMA (+6.6%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,21 +1591,21 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>35818</v>
+        <v>15824</v>
       </c>
       <c r="W2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="X2" t="n">
-        <v>12.3</v>
+        <v>5.5</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 77; CIPLA: 75, LUPIN: 74, ZYDUSLIFE: 71</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; BAJAJFINSV: 69, SBIN: 69, FEDERALBNK: 68</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+12.3%) • outperforming Nifty • sector strength 87/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.6%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +7 = 77</t>
+          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +16 · Regime +9 · Sector +8 = 75</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1649,58 +1649,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H3" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I3" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1437.9</v>
+        <v>2014.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1397 - 1478</t>
+          <t>1963 - 2067</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>+2% to +8%</t>
+          <t>-4% to +14%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.6%)</t>
+          <t>Above 200-DMA (+13.6%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>15817</v>
+        <v>38281</v>
       </c>
       <c r="W3" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="X3" t="n">
-        <v>5.6</v>
+        <v>13.1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; FEDERALBNK: 69, BAJAJFINSV: 68, KOTAKBANK: 65</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 75; CIPLA: 74, ZYDUSLIFE: 72, LUPIN: 71</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.6%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+13.6%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +9 = 74</t>
+          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +8 = 71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="H4" t="n">
         <v>96</v>
       </c>
       <c r="I4" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2447</v>
+        <v>2417</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2383 - 2511</t>
+          <t>2355 - 2479</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.3%)</t>
+          <t>Above 200-DMA (+8.8%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>31811</v>
+        <v>31421</v>
       </c>
       <c r="W4" t="n">
         <v>13</v>
       </c>
       <c r="X4" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 74; SUNPHARMA: 77, CIPLA: 75, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 71; SUNPHARMA: 75, CIPLA: 74, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.3%) • outperforming Nifty • sector strength 87/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.8%) • sector strength 80/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
+          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +7 = 69</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>81</v>
       </c>
       <c r="I5" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1629.9</v>
+        <v>1625.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1578 - 1682</t>
+          <t>1574 - 1677</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.8%)</t>
+          <t>Above 200-DMA (+10.4%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>19559</v>
+        <v>19506</v>
       </c>
       <c r="W5" t="n">
         <v>12</v>
       </c>
       <c r="X5" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 62, CHAMBLFERT: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 69; NAVINFLUOR: 62, CHAMBLFERT: 53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.4%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +3 = 66</t>
+          <t>Historical +25 · Risk/Vol +23 · Regime +9 · Trend/Tech +5 · Sector +3 = 65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2009,10 +2009,10 @@
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>343.5</v>
+        <v>345.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>334 - 353</t>
+          <t>337 - 355</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,11 +2046,11 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.8%)</t>
+          <t>Below 200-DMA (-3.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>25419</v>
+        <v>25931</v>
       </c>
       <c r="W6" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="X6" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 66; POWERGRID: 58, JSWENERGY: 56, TATAPOWER: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; POWERGRID: 58, JSWENERGY: 56, NHPC: 54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-3.2%) • sector strength 33/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
         <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
         <v>89</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>390.2</v>
+        <v>389.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>379 - 402</t>
+          <t>378 - 401</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.4%)</t>
+          <t>Below 200-DMA (-3.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>14828</v>
+        <v>14793</v>
       </c>
       <c r="W7" t="n">
         <v>38</v>
       </c>
       <c r="X7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 77, FEDERALBNK: 69, BAJAJFINSV: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 77, BAJAJFINSV: 69, SBIN: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.4%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.6%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2245,10 +2245,10 @@
         <v>25</v>
       </c>
       <c r="H8" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>282.9</v>
+        <v>285.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>275 - 290</t>
+          <t>279 - 293</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.1%)</t>
+          <t>Below 200-DMA (-0.1%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>25457</v>
+        <v>27732</v>
       </c>
       <c r="W8" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="X8" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 66, JSWENERGY: 56, TATAPOWER: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 65, JSWENERGY: 56, NHPC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-1.1%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.1%) • sector strength 33/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +2 = 54</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" t="n">
         <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>286.2</v>
+        <v>282.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>279 - 293</t>
+          <t>276 - 290</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.3%)</t>
+          <t>Below 200-DMA (-15.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>24331</v>
+        <v>23198</v>
       </c>
       <c r="W9" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="X9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 52, DABUR: 50, HINDUNILVR: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; BRITANNIA: 50, DABUR: 49, HINDUNILVR: 49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.3%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.1%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>387.5</v>
+        <v>388.7</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>375 - 400</t>
+          <t>377 - 401</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.8%)</t>
+          <t>Below 200-DMA (-7.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>23253</v>
+        <v>22933</v>
       </c>
       <c r="W10" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="X10" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 61, POLYCAB: 56, KEI: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 61, POLYCAB: 57, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.8%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.5%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +2 · Sector +1 = 49</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +2 · Sector +2 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2602,7 +2602,7 @@
         <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>410</v>
+        <v>411.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>398 - 423</t>
+          <t>399 - 424</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.7%)</t>
+          <t>Below 200-DMA (-3.4%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,14 +2653,14 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>30344</v>
+        <v>30025</v>
       </c>
       <c r="W11" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="X11" t="n">
         <v>10.1</v>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 49; TATASTEEL: 47, SAIL: 43, HINDZINC: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 48, SAIL: 43, HINDZINC: 40</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.7%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.4%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H12" t="n">
         <v>88</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>496</v>
+        <v>494.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>481 - 511</t>
+          <t>479 - 509</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.8%)</t>
+          <t>Below 200-DMA (-17.0%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>16864</v>
+        <v>16314</v>
       </c>
       <c r="W12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X12" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60, INDIGO: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.8%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.0%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +7 · Sector +2 = 52</t>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +6 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,13 +2832,13 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H13" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5517.5</v>
+        <v>5406</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5375 - 5660</t>
+          <t>5265 - 5547</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.4%)</t>
+          <t>Below 200-DMA (-5.3%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>27588</v>
+        <v>27030</v>
       </c>
       <c r="W13" t="n">
         <v>5</v>
       </c>
       <c r="X13" t="n">
-        <v>10.6</v>
+        <v>9.9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 54, DABUR: 50, HINDUNILVR: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 53, DABUR: 49, HINDUNILVR: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-3.4%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-5.3%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27733,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27748,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRITANNIA (50)</t>
+          <t>COALINDIA (49)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31  /  2026-07-31</t>
+          <t>2026-08-03  /  2026-08-03</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.02</t>
         </is>
       </c>
     </row>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1438.5</v>
+        <v>1448.3</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1399 - 1478</t>
+          <t>1408 - 1488</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.6%)</t>
+          <t>Above 200-DMA (+7.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>15824</v>
+        <v>15931</v>
       </c>
       <c r="W2" t="n">
         <v>11</v>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; BAJAJFINSV: 69, SBIN: 69, FEDERALBNK: 68</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 69, FEDERALBNK: 68, BAJAJFINSV: 66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.6%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +18 · Trend/Tech +16 · Regime +9 · Sector +8 = 75</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +7 = 74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,13 +1652,13 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>2014.8</v>
+        <v>1942.9</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1963 - 2067</t>
+          <t>1891 - 1995</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+13.6%)</t>
+          <t>Above 200-DMA (+9.5%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>38281</v>
+        <v>36915</v>
       </c>
       <c r="W3" t="n">
         <v>19</v>
       </c>
       <c r="X3" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 75; CIPLA: 74, ZYDUSLIFE: 72, LUPIN: 71</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 73, ZYDUSLIFE: 71, LUPIN: 69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+13.6%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.5%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +8 = 71</t>
+          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,13 +1767,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="H4" t="n">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="I4" t="n">
         <v>80</v>
@@ -1783,42 +1783,42 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2417</v>
+        <v>1633.8</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2355 - 2479</t>
+          <t>1582 - 1686</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.8%)</t>
+          <t>Above 200-DMA (+10.9%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>31421</v>
+        <v>19606</v>
       </c>
       <c r="W4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X4" t="n">
-        <v>10.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 71; SUNPHARMA: 75, CIPLA: 74, ZYDUSLIFE: 72. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.8%) • sector strength 80/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.9%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +7 = 69</t>
+          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +14 · Regime +9 · Sector +7 = 69</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
+        <v>70</v>
+      </c>
+      <c r="H5" t="n">
         <v>95</v>
-      </c>
-      <c r="H5" t="n">
-        <v>81</v>
       </c>
       <c r="I5" t="n">
         <v>73</v>
@@ -1901,42 +1901,42 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1625.5</v>
+        <v>2398</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1574 - 1677</t>
+          <t>2336 - 2460</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.4%)</t>
+          <t>Above 200-DMA (+7.9%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>19506</v>
+        <v>31174</v>
       </c>
       <c r="W5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="X5" t="n">
-        <v>6.5</v>
+        <v>10.9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 69; NAVINFLUOR: 62, CHAMBLFERT: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 73, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.4%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.9%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +23 · Regime +9 · Trend/Tech +5 · Sector +3 = 65</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +3 = 66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2009,10 +2009,10 @@
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>345.8</v>
+        <v>347.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>337 - 355</t>
+          <t>339 - 357</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.2%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>25931</v>
+        <v>27109</v>
       </c>
       <c r="W6" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X6" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; POWERGRID: 58, JSWENERGY: 56, NHPC: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 66; NHPC: 63, POWERGRID: 59, JSWENERGY: 55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-3.2%) • sector strength 33/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-2.7%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +8 · Sector +7 = 65</t>
+          <t>Risk/Vol +22 · Historical +19 · Trend/Tech +9 · Regime +9 · Sector +7 = 66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H7" t="n">
         <v>89</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>389.3</v>
+        <v>392.7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>378 - 401</t>
+          <t>381 - 404</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.6%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,14 +2181,14 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>14793</v>
+        <v>14530</v>
       </c>
       <c r="W7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="X7" t="n">
         <v>4.9</v>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 77, BAJAJFINSV: 69, SBIN: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 66; ICICIBANK: 77, SBIN: 69, FEDERALBNK: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.6%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.7%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +3 = 58</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +3 = 59</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2242,13 @@
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>27732</v>
+        <v>28876</v>
       </c>
       <c r="W8" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="X8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 65, JSWENERGY: 56, NHPC: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 59; NTPC: 66, NHPC: 63, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.1%) • sector strength 33/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.1%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 53</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +3 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,62 +2353,62 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>282.9</v>
+        <v>390.3</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>276 - 290</t>
+          <t>378 - 402</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.1%)</t>
+          <t>Below 200-DMA (-7.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23198</v>
+        <v>23418</v>
       </c>
       <c r="W9" t="n">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="X9" t="n">
         <v>7.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; BRITANNIA: 50, DABUR: 49, HINDUNILVR: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 62, POLYCAB: 57, KEI: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.1%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.1%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +3 = 53</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2471,62 +2471,62 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="H10" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I10" t="n">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>388.7</v>
+        <v>291.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>377 - 401</t>
+          <t>284 - 299</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.5%)</t>
+          <t>Below 200-DMA (-12.3%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>22933</v>
+        <v>21892</v>
       </c>
       <c r="W10" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="X10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 61, POLYCAB: 57, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; BRITANNIA: 50, DABUR: 50, HINDUNILVR: 48</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.5%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.3%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +2 · Sector +2 = 50</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +2 · Sector +1 = 49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2599,10 +2599,10 @@
         <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>411.3</v>
+        <v>414.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>399 - 424</t>
+          <t>402 - 427</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.4%)</t>
+          <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>30025</v>
+        <v>30692</v>
       </c>
       <c r="W11" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="X11" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 48, SAIL: 43, HINDZINC: 40</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 49; TATASTEEL: 47, SAIL: 42, HINDZINC: 39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.4%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.6%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2714,10 +2714,10 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I12" t="n">
         <v>60</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>494.4</v>
+        <v>501.4</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>479 - 509</t>
+          <t>486 - 517</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.0%)</t>
+          <t>Below 200-DMA (-15.6%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>16314</v>
+        <v>16045</v>
       </c>
       <c r="W12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-17.0%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-15.6%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2832,7 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" t="n">
         <v>94</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5406</v>
+        <v>5452</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5265 - 5547</t>
+          <t>5310 - 5594</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.3%)</t>
+          <t>Below 200-DMA (-4.5%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,11 +2889,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>27030</v>
+        <v>27260</v>
       </c>
       <c r="W13" t="n">
         <v>5</v>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 53, DABUR: 49, HINDUNILVR: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 53, DABUR: 50, HINDUNILVR: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-5.3%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.5%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="C8" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (77)</t>
+          <t>ICICIBANK (78)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COALINDIA (49)</t>
+          <t>BRITANNIA (50)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-03  /  2026-08-03</t>
+          <t>2026-08-04  /  2026-08-04</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +7 = 77</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +19 · Regime +9 · Sector +7 = 78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1448.3</v>
+        <v>1449.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1408 - 1488</t>
+          <t>1410 - 1489</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.3%)</t>
+          <t>Above 200-DMA (+7.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>15931</v>
+        <v>15944</v>
       </c>
       <c r="W2" t="n">
         <v>11</v>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 69, FEDERALBNK: 68, BAJAJFINSV: 66</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; SBIN: 69, FEDERALBNK: 68, BAJAJFINSV: 67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.4%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1942.9</v>
+        <v>1955.3</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1891 - 1995</t>
+          <t>1903 - 2008</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+9.5%)</t>
+          <t>Above 200-DMA (+10.1%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>36915</v>
+        <v>37151</v>
       </c>
       <c r="W3" t="n">
         <v>19</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.5%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.1%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1633.8</v>
+        <v>1642.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1582 - 1686</t>
+          <t>1590 - 1695</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.9%)</t>
+          <t>Above 200-DMA (+11.5%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,11 +1827,11 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>19606</v>
+        <v>19710</v>
       </c>
       <c r="W4" t="n">
         <v>12</v>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 62, CHAMBLFERT: 54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.9%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+11.5%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1888,10 +1888,10 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H5" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I5" t="n">
         <v>73</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2398</v>
+        <v>2383.9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2336 - 2460</t>
+          <t>2323 - 2445</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.9%)</t>
+          <t>Above 200-DMA (+7.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,11 +1945,11 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>31174</v>
+        <v>30991</v>
       </c>
       <c r="W5" t="n">
         <v>13</v>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.9%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.1%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +3 = 66</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +2 = 65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2012,7 +2012,7 @@
         <v>96</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>347.5</v>
+        <v>347.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>339 - 357</t>
+          <t>338 - 356</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-2.8%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,11 +2063,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>27109</v>
+        <v>27086</v>
       </c>
       <c r="W6" t="n">
         <v>78</v>
@@ -2087,27 +2087,27 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 66; NHPC: 63, POWERGRID: 59, JSWENERGY: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 61, POWERGRID: 58, JSWENERGY: 54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-2.7%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-2.8%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Trend/Tech +9 · Regime +9 · Sector +7 = 66</t>
+          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +7 · Sector +7 = 64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>64</v>
       </c>
       <c r="G7" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="H7" t="n">
         <v>89</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>392.7</v>
+        <v>397</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>381 - 404</t>
+          <t>385 - 409</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-1.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,14 +2181,14 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>14530</v>
+        <v>14292</v>
       </c>
       <c r="W7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="X7" t="n">
         <v>4.9</v>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 66; ICICIBANK: 77, SBIN: 69, FEDERALBNK: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 64; ICICIBANK: 78, SBIN: 69, FEDERALBNK: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.7%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.6%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +3 = 59</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +2 = 58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2242,13 @@
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8" t="n">
         <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,11 +2299,11 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>28876</v>
+        <v>28871</v>
       </c>
       <c r="W8" t="n">
         <v>101</v>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 59; NTPC: 66, NHPC: 63, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 65, NHPC: 61, JSWENERGY: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.1%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.1%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>390.3</v>
+        <v>389.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.1%)</t>
+          <t>Below 200-DMA (-7.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23418</v>
+        <v>23391</v>
       </c>
       <c r="W9" t="n">
         <v>60</v>
       </c>
       <c r="X9" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 62, POLYCAB: 57, KEI: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 60, POLYCAB: 55, KEI: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.1%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.2%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 53</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,13 +2478,13 @@
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H10" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>291.9</v>
+        <v>284.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>284 - 299</t>
+          <t>277 - 292</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.3%)</t>
+          <t>Below 200-DMA (-14.3%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>21892</v>
+        <v>29340</v>
       </c>
       <c r="W10" t="n">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="X10" t="n">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; BRITANNIA: 50, DABUR: 50, HINDUNILVR: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; BRITANNIA: 50, HINDUNILVR: 48, DABUR: 47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.3%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.3%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +2 · Sector +1 = 49</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2596,13 +2596,13 @@
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
         <v>88</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>414.8</v>
+        <v>415.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>402 - 427</t>
+          <t>403 - 428</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>30692</v>
+        <v>30721</v>
       </c>
       <c r="W11" t="n">
         <v>74</v>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 49; TATASTEEL: 47, SAIL: 42, HINDZINC: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 42, HINDZINC: 41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.6%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.6%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
         <v>87</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>501.4</v>
+        <v>507.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>486 - 517</t>
+          <t>492 - 523</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.6%)</t>
+          <t>Below 200-DMA (-14.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>16045</v>
+        <v>16253</v>
       </c>
       <c r="W12" t="n">
         <v>32</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60, INDIGO: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-15.6%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-14.4%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2832,13 +2832,13 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" t="n">
         <v>94</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5452</v>
+        <v>5454.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5310 - 5594</t>
+          <t>5312 - 5597</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.5%)</t>
+          <t>Below 200-DMA (-4.4%)</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>27260</v>
+        <v>16364</v>
       </c>
       <c r="W13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 53, DABUR: 50, HINDUNILVR: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 52, HINDUNILVR: 48, DABUR: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.5%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.4%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRITANNIA (50)</t>
+          <t>COALINDIA (50)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-04  /  2026-08-04</t>
+          <t>2026-08-05  /  2026-08-05</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1449.5</v>
+        <v>1454.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1410 - 1489</t>
+          <t>1415 - 1495</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.4%)</t>
+          <t>Above 200-DMA (+7.7%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>15944</v>
+        <v>14546</v>
       </c>
       <c r="W2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="X2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.4%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.7%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1955.3</v>
+        <v>1964</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1903 - 2008</t>
+          <t>1911 - 2017</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.1%)</t>
+          <t>Above 200-DMA (+10.5%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>37151</v>
+        <v>35352</v>
       </c>
       <c r="W3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 73, ZYDUSLIFE: 71, LUPIN: 69</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 72, ZYDUSLIFE: 69, LUPIN: 68</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.1%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.5%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,10 +1770,10 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I4" t="n">
         <v>80</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1642.5</v>
+        <v>1620</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1590 - 1695</t>
+          <t>1569 - 1671</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.5%)</t>
+          <t>Above 200-DMA (+9.9%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>19710</v>
+        <v>17820</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 62, CHAMBLFERT: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 62</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+11.5%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+9.9%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +14 · Regime +9 · Sector +7 = 69</t>
+          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +13 · Regime +9 · Sector +7 = 68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,10 +1888,10 @@
         <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H5" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="I5" t="n">
         <v>73</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2383.9</v>
+        <v>2410</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2323 - 2445</t>
+          <t>2349 - 2471</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.1%)</t>
+          <t>Above 200-DMA (+8.2%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>30991</v>
+        <v>33740</v>
       </c>
       <c r="W5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X5" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 73, ZYDUSLIFE: 71. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 68; SUNPHARMA: 74, CIPLA: 72, ZYDUSLIFE: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.1%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.2%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2009,7 @@
         <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>347.2</v>
+        <v>343.6</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>338 - 356</t>
+          <t>335 - 353</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.8%)</t>
+          <t>Below 200-DMA (-3.8%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>27086</v>
+        <v>26117</v>
       </c>
       <c r="W6" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="X6" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 61, POWERGRID: 58, JSWENERGY: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 62, POWERGRID: 57, JSWENERGY: 54</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-2.8%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>385 - 409</t>
+          <t>386 - 410</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.6%)</t>
+          <t>Below 200-DMA (-1.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>14292</v>
+        <v>13930</v>
       </c>
       <c r="W7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X7" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.6%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.3%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +2 = 58</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +2 = 57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,10 +2242,10 @@
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I8" t="n">
         <v>20</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>285.9</v>
+        <v>283.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>279 - 293</t>
+          <t>276 - 290</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,11 +2286,11 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.1%)</t>
+          <t>Below 200-DMA (-0.9%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>28871</v>
+        <v>28057</v>
       </c>
       <c r="W8" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="X8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 65, NHPC: 61, JSWENERGY: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 65, NHPC: 62, JSWENERGY: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.1%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-0.9%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +3 = 53</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,62 +2353,62 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>389.9</v>
+        <v>289</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>378 - 402</t>
+          <t>282 - 296</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.2%)</t>
+          <t>Below 200-DMA (-12.9%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23391</v>
+        <v>37570</v>
       </c>
       <c r="W9" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="X9" t="n">
-        <v>7.9</v>
+        <v>12.6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 60, POLYCAB: 55, KEI: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 51, HINDUNILVR: 48, DABUR: 47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.2%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.9%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 52</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +3 = 53</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2471,62 +2471,62 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>284.9</v>
+        <v>391.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>277 - 292</t>
+          <t>379 - 404</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.3%)</t>
+          <t>Below 200-DMA (-6.8%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>29340</v>
+        <v>21141</v>
       </c>
       <c r="W10" t="n">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="X10" t="n">
-        <v>9.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; BRITANNIA: 50, HINDUNILVR: 48, DABUR: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 60, POLYCAB: 57, KEI: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.3%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-6.8%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
         <v>88</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>415.1</v>
+        <v>417.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>403 - 428</t>
+          <t>405 - 430</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.6%)</t>
+          <t>Below 200-DMA (-2.0%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>30721</v>
+        <v>29650</v>
       </c>
       <c r="W11" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="X11" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 42, HINDZINC: 41</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 43, HINDZINC: 38</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.6%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.0%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
         <v>87</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>507.9</v>
+        <v>510.2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>492 - 523</t>
+          <t>495 - 526</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.4%)</t>
+          <t>Below 200-DMA (-13.9%)</t>
         </is>
       </c>
       <c r="S12" t="n">
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>16253</v>
+        <v>15818</v>
       </c>
       <c r="W12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60, INDIGO: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 62, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-14.4%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-13.9%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +6 · Sector +1 = 50</t>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +7 · Sector +1 = 51</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,7 +2832,7 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H13" t="n">
         <v>94</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5454.5</v>
+        <v>5478</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5312 - 5597</t>
+          <t>5335 - 5621</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.4%)</t>
+          <t>Below 200-DMA (-3.9%)</t>
         </is>
       </c>
       <c r="S13" t="n">
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>16364</v>
+        <v>16434</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 52, HINDUNILVR: 48, DABUR: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; ITC: 54, HINDUNILVR: 48, DABUR: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.4%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-3.9%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27733,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27748,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27763,31 +27763,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COALINDIA (50)</t>
+          <t>BRITANNIA (50)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-05  /  2026-08-05</t>
+          <t>2026-08-06  /  2026-08-06</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1454.6</v>
+        <v>1449.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1415 - 1495</t>
+          <t>1410 - 1489</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.7%)</t>
+          <t>Above 200-DMA (+7.3%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>14546</v>
+        <v>14496</v>
       </c>
       <c r="W2" t="n">
         <v>10</v>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; SBIN: 69, FEDERALBNK: 68, BAJAJFINSV: 67</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; SBIN: 71, FEDERALBNK: 68, BAJAJFINSV: 66</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.7%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1964</v>
+        <v>1949</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1911 - 2017</t>
+          <t>1897 - 2001</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.5%)</t>
+          <t>Above 200-DMA (+9.5%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>35352</v>
+        <v>35082</v>
       </c>
       <c r="W3" t="n">
         <v>18</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 72, ZYDUSLIFE: 69, LUPIN: 68</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 72, LUPIN: 70, ZYDUSLIFE: 70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+10.5%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.5%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
+          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +7 = 70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="I4" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1620</v>
+        <v>2390.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1569 - 1671</t>
+          <t>2329 - 2451</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+9.9%)</t>
+          <t>Above 200-DMA (+7.2%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>17820</v>
+        <v>33466</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="X4" t="n">
-        <v>6.2</v>
+        <v>11.6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 70; SUNPHARMA: 74, CIPLA: 72, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+9.9%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.2%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +13 · Regime +9 · Sector +7 = 68</t>
+          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,58 +1885,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2410</v>
+        <v>1657</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2349 - 2471</t>
+          <t>1604 - 1710</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.2%)</t>
+          <t>Above 200-DMA (+12.4%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>33740</v>
+        <v>18227</v>
       </c>
       <c r="W5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>11.7</v>
+        <v>6.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 68; SUNPHARMA: 74, CIPLA: 72, ZYDUSLIFE: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 62</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.2%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+12.4%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +2 = 65</t>
+          <t>Risk/Vol +22 · Historical +19 · Trend/Tech +9 · Regime +9 · Sector +7 = 66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2003,36 +2003,36 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>343.6</v>
+        <v>397.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>335 - 353</t>
+          <t>386 - 409</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.8%)</t>
+          <t>Below 200-DMA (-1.5%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>26117</v>
+        <v>14299</v>
       </c>
       <c r="W6" t="n">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="X6" t="n">
-        <v>8.699999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 65; NHPC: 62, POWERGRID: 57, JSWENERGY: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 66; ICICIBANK: 78, SBIN: 71, FEDERALBNK: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.5%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +7 · Sector +7 = 64</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +1 = 64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2121,36 +2121,36 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H7" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I7" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>398</v>
+        <v>346.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>386 - 410</t>
+          <t>338 - 356</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.3%)</t>
+          <t>Below 200-DMA (-2.9%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>13930</v>
+        <v>26364</v>
       </c>
       <c r="W7" t="n">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="X7" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 64; ICICIBANK: 78, SBIN: 69, FEDERALBNK: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 56, JSWENERGY: 54, NHPC: 53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.3%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-2.9%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +2 = 57</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +1 = 56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2242,13 @@
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H8" t="n">
         <v>98</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>283.4</v>
+        <v>276.8</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>276 - 290</t>
+          <t>270 - 284</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.9%)</t>
+          <t>Below 200-DMA (-3.2%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>28057</v>
+        <v>27957</v>
       </c>
       <c r="W8" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="X8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 65, NHPC: 62, JSWENERGY: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, JSWENERGY: 54, NHPC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-0.9%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-3.2%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H9" t="n">
         <v>99</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>289</v>
+        <v>285.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>282 - 296</t>
+          <t>279 - 293</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.9%)</t>
+          <t>Below 200-DMA (-13.7%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>37570</v>
+        <v>37154</v>
       </c>
       <c r="W9" t="n">
         <v>130</v>
       </c>
       <c r="X9" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 51, HINDUNILVR: 48, DABUR: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 50, DABUR: 49, HINDUNILVR: 49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-12.9%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.7%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +5 · Trend/Tech +3 = 53</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +4 · Trend/Tech +3 = 52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,13 +2478,13 @@
         <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
         <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>391.5</v>
+        <v>390</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>379 - 404</t>
+          <t>378 - 402</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.8%)</t>
+          <t>Below 200-DMA (-7.1%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>21141</v>
+        <v>21453</v>
       </c>
       <c r="W10" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X10" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 53; HAL: 60, POLYCAB: 57, KEI: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 52; HAL: 59, POLYCAB: 55, KEI: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-6.8%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.1%) • sector strength 40/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2602,7 +2602,7 @@
         <v>88</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>417.6</v>
+        <v>414</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>405 - 430</t>
+          <t>401 - 427</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.0%)</t>
+          <t>Below 200-DMA (-2.9%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>29650</v>
+        <v>29398</v>
       </c>
       <c r="W11" t="n">
         <v>71</v>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 43, HINDZINC: 38</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; TATASTEEL: 56, HINDZINC: 47, SAIL: 42. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.0%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.9%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2714,10 +2714,10 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H12" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I12" t="n">
         <v>60</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>510.2</v>
+        <v>510.9</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.9%)</t>
+          <t>Below 200-DMA (-13.6%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,11 +2771,11 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>15818</v>
+        <v>15836</v>
       </c>
       <c r="W12" t="n">
         <v>31</v>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 62, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 58, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-13.9%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-13.6%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +7 · Sector +1 = 51</t>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +6 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,7 +2832,7 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H13" t="n">
         <v>94</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5478</v>
+        <v>5429</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5335 - 5621</t>
+          <t>5287 - 5571</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.9%)</t>
+          <t>Below 200-DMA (-4.8%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>16434</v>
+        <v>16287</v>
       </c>
       <c r="W13" t="n">
         <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 51; ITC: 54, HINDUNILVR: 48, DABUR: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 54, DABUR: 49, HINDUNILVR: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-3.9%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.8%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -26569,13 +26569,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
         <v>-5.9</v>
@@ -27763,22 +27763,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -27787,7 +27787,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-06  /  2026-08-06</t>
+          <t>2026-08-07  /  2026-08-06</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (78)</t>
+          <t>ICICIBANK (76)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRITANNIA (50)</t>
+          <t>BRITANNIA (52)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-07  /  2026-08-06</t>
+          <t>2026-08-10  /  2026-08-07</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +19 · Regime +9 · Sector +7 = 78</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +7 = 76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1449.6</v>
+        <v>1421</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1410 - 1489</t>
+          <t>1382 - 1460</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.3%)</t>
+          <t>Above 200-DMA (+5.2%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>14496</v>
+        <v>15631</v>
       </c>
       <c r="W2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; SBIN: 71, FEDERALBNK: 68, BAJAJFINSV: 66</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, FEDERALBNK: 70, BAJAJFINSV: 67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+7.3%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1897 - 2001</t>
+          <t>1893 - 1997</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+9.5%)</t>
+          <t>Above 200-DMA (+9.2%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>35082</v>
+        <v>35010</v>
       </c>
       <c r="W3" t="n">
         <v>18</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 72, LUPIN: 70, ZYDUSLIFE: 70</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 72, ZYDUSLIFE: 70, LUPIN: 69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.5%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.2%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +15 · Regime +9 · Sector +7 = 70</t>
+          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H4" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="I4" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2390.4</v>
+        <v>1660</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2329 - 2451</t>
+          <t>1607 - 1713</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.2%)</t>
+          <t>Above 200-DMA (+12.5%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>33466</v>
+        <v>11620</v>
       </c>
       <c r="W4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>11.6</v>
+        <v>4.2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 70; SUNPHARMA: 74, CIPLA: 72, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 54</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.2%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+12.5%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
+          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +14 · Regime +9 · Sector +7 = 69</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,58 +1885,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1657</v>
+        <v>2363.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1604 - 1710</t>
+          <t>2303 - 2424</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+12.4%)</t>
+          <t>Above 200-DMA (+5.9%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>18227</v>
+        <v>33089</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="X5" t="n">
-        <v>6.1</v>
+        <v>11.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 72, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+12.4%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.9%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Trend/Tech +9 · Regime +9 · Sector +7 = 66</t>
+          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +8 · Sector +7 = 65</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,7 +2006,7 @@
         <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
         <v>89</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>397.2</v>
+        <v>390.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>386 - 409</t>
+          <t>379 - 402</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.5%)</t>
+          <t>Below 200-DMA (-3.0%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>14299</v>
+        <v>23054</v>
       </c>
       <c r="W6" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="X6" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 66; ICICIBANK: 78, SBIN: 71, FEDERALBNK: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 76, SBIN: 74, FEDERALBNK: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-1.5%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.0%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +5 · Sector +1 = 64</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +4 · Sector +2 = 64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>84</v>
       </c>
       <c r="G7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
         <v>95</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>346.9</v>
+        <v>342.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>338 - 356</t>
+          <t>334 - 351</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2168,11 +2168,11 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.9%)</t>
+          <t>Below 200-DMA (-4.1%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>26364</v>
+        <v>26372</v>
       </c>
       <c r="W7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="X7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 56, JSWENERGY: 54, NHPC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 55, JSWENERGY: 54, TATAPOWER: 54</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-2.9%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.1%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +5 · Sector +1 = 56</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,36 +2239,36 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H8" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>276.8</v>
+        <v>401</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>270 - 284</t>
+          <t>388 - 414</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.2%)</t>
+          <t>Below 200-DMA (-4.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>27957</v>
+        <v>14035</v>
       </c>
       <c r="W8" t="n">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="X8" t="n">
-        <v>9.300000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, JSWENERGY: 54, NHPC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 60, POLYCAB: 56, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-3.2%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-4.5%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 54</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>285.8</v>
+        <v>271.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>279 - 293</t>
+          <t>265 - 278</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.7%)</t>
+          <t>Below 200-DMA (-5.0%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>37154</v>
+        <v>27703</v>
       </c>
       <c r="W9" t="n">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="X9" t="n">
-        <v>12.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 50, DABUR: 49, HINDUNILVR: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 55; NTPC: 64, JSWENERGY: 54, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.7%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.0%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +4 · Trend/Tech +3 = 52</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2471,62 +2471,62 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>390</v>
+        <v>286.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>378 - 402</t>
+          <t>279 - 293</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.1%)</t>
+          <t>Below 200-DMA (-13.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>21453</v>
+        <v>37193</v>
       </c>
       <c r="W10" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="X10" t="n">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 52; HAL: 59, POLYCAB: 55, KEI: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 52, HINDUNILVR: 49, DABUR: 46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-7.1%) • sector strength 40/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.5%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +4 · Sector +3 = 53</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2596,13 +2596,13 @@
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>414</v>
+        <v>415.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>401 - 427</t>
+          <t>403 - 428</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.9%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,11 +2653,11 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>29398</v>
+        <v>29483</v>
       </c>
       <c r="W11" t="n">
         <v>71</v>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; TATASTEEL: 56, HINDZINC: 47, SAIL: 42. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 53; TATASTEEL: 49, HINDZINC: 48, SAIL: 44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.9%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.7%) • sector strength 27/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +6 · Trend/Tech +5 = 54</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +6 = 55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2707,14 +2707,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H12" t="n">
         <v>86</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>510.9</v>
+        <v>520</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>495 - 526</t>
+          <t>504 - 536</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.6%)</t>
+          <t>Below 200-DMA (-11.9%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>15836</v>
+        <v>14559</v>
       </c>
       <c r="W12" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X12" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 58, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 55; DELHIVERY: 60, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-13.6%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-11.9%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +6 · Sector +1 = 50</t>
+          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +8 · Sector +1 = 52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,13 +2832,13 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H13" t="n">
         <v>94</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5429</v>
+        <v>5510</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5287 - 5571</t>
+          <t>5366 - 5654</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.8%)</t>
+          <t>Below 200-DMA (-3.3%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>16287</v>
+        <v>22040</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X13" t="n">
-        <v>7.2</v>
+        <v>8.9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 50; ITC: 54, DABUR: 49, HINDUNILVR: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 54, HINDUNILVR: 49, DABUR: 46. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-4.8%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-3.3%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27793,12 +27793,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27823,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (76)</t>
+          <t>ICICIBANK (75)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BRITANNIA (52)</t>
+          <t>ONGC (50)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ONGC, ZYDUSLIFE</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PIDILITIND, SUNPHARMA</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-10  /  2026-08-07</t>
+          <t>2026-08-11  /  2026-08-10</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.0%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +7 = 76</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +7 = 75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1421</v>
+        <v>1431.8</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1382 - 1460</t>
+          <t>1392 - 1472</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+5.2%)</t>
+          <t>Above 200-DMA (+6.0%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>15631</v>
+        <v>15750</v>
       </c>
       <c r="W2" t="n">
         <v>11</v>
       </c>
       <c r="X2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, FEDERALBNK: 70, BAJAJFINSV: 67</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 75; SBIN: 74, FEDERALBNK: 70, BAJAJFINSV: 67</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.2%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.0%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +7 = 74</t>
+          <t>Risk/Vol +22 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +7 = 70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1649,23 +1649,23 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="I3" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1674,33 +1674,33 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1945</v>
+        <v>1119</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1893 - 1997</t>
+          <t>1086 - 1152</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-4% to +14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+9.2%)</t>
+          <t>Above 200-DMA (+14.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>35010</v>
+        <v>20142</v>
       </c>
       <c r="W3" t="n">
         <v>18</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 72, ZYDUSLIFE: 70, LUPIN: 69</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ZYDUSLIFE: 70; LUPIN: 69, AJANTPHARM: 66, DRREDDY: 50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+9.2%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+14.8%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1749,76 +1749,76 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>69</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +14 · Regime +9 · Sector +7 = 69</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="n">
         <v>70</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Risk/Vol +20 · Trend/Tech +19 · Historical +14 · Regime +9 · Sector +8 = 70</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>45</v>
-      </c>
-      <c r="G4" t="n">
-        <v>94</v>
-      </c>
       <c r="H4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I4" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1660</v>
+        <v>2300</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1607 - 1713</t>
+          <t>2240 - 2360</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+12.5%)</t>
+          <t>Above 200-DMA (+3.0%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>11620</v>
+        <v>25300</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 70; NAVINFLUOR: 63, CHAMBLFERT: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; ZYDUSLIFE: 70, AJANTPHARM: 66, DRREDDY: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+12.5%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+3.0%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +14 · Regime +9 · Sector +7 = 69</t>
+          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +8 · Sector +7 = 65</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="G5" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I5" t="n">
         <v>73</v>
@@ -1901,20 +1901,20 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2363.5</v>
+        <v>393.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2303 - 2424</t>
+          <t>382 - 405</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+5.9%)</t>
+          <t>Below 200-DMA (-2.3%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>33089</v>
+        <v>15346</v>
       </c>
       <c r="W5" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,32 +1969,32 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 72, ZYDUSLIFE: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 75, SBIN: 74, FEDERALBNK: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+5.9%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.3%) • sector strength 73/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +8 · Sector +7 = 65</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +1 = 62</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2003,36 +2003,36 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I6" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>390.8</v>
+        <v>340.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>379 - 402</t>
+          <t>332 - 349</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.0%)</t>
+          <t>Below 200-DMA (-4.7%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>23054</v>
+        <v>37450</v>
       </c>
       <c r="W6" t="n">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="X6" t="n">
-        <v>7.8</v>
+        <v>12.6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 76, SBIN: 74, FEDERALBNK: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 62; POWERGRID: 54, JSWENERGY: 53, TATAPOWER: 52</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-3.0%) • sector strength 67/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.7%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +4 · Sector +2 = 64</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2121,36 +2121,36 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" t="n">
         <v>84</v>
       </c>
-      <c r="G7" t="n">
-        <v>22</v>
-      </c>
-      <c r="H7" t="n">
-        <v>95</v>
-      </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>342.5</v>
+        <v>404.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>334 - 351</t>
+          <t>392 - 417</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.1%)</t>
+          <t>Below 200-DMA (-3.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>26372</v>
+        <v>14152</v>
       </c>
       <c r="W7" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="X7" t="n">
-        <v>8.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,70 +2205,70 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 55, JSWENERGY: 54, TATAPOWER: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 59, KEI: 51, MAZDOCK: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.1%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.7%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>54</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +1 = 54</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>56</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 56</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>50</v>
-      </c>
       <c r="G8" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="I8" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>401</v>
+        <v>270.1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>388 - 414</t>
+          <t>263 - 277</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.5%)</t>
+          <t>Below 200-DMA (-5.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>14035</v>
+        <v>37274</v>
       </c>
       <c r="W8" t="n">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="X8" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 60, POLYCAB: 56, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 54; NTPC: 62, JSWENERGY: 53, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-4.5%) • sector strength 47/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.5%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +2 = 55</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H9" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>271.6</v>
+        <v>282.6</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>265 - 278</t>
+          <t>276 - 290</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.0%)</t>
+          <t>Below 200-DMA (-14.3%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>27703</v>
+        <v>31091</v>
       </c>
       <c r="W9" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="X9" t="n">
-        <v>9.300000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 55; NTPC: 64, JSWENERGY: 54, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 52, DABUR: 49, HINDUNILVR: 48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.0%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.3%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 54</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>286.1</v>
+        <v>411</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>279 - 293</t>
+          <t>399 - 423</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-13.5%)</t>
+          <t>Below 200-DMA (-3.7%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>37193</v>
+        <v>27126</v>
       </c>
       <c r="W10" t="n">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="X10" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 52, HINDUNILVR: 49, DABUR: 46</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; TATASTEEL: 48, HINDZINC: 47, SAIL: 44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-13.5%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.7%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2575,31 +2575,31 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Sector +3 · Trend/Tech +2 = 50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Trend/Tech</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>53</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +4 · Sector +3 = 53</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>51</v>
-      </c>
       <c r="G11" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="I11" t="n">
         <v>27</v>
@@ -2609,20 +2609,20 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>415.2</v>
+        <v>239.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>403 - 428</t>
+          <t>232 - 248</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-7.4%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>29483</v>
+        <v>29980</v>
       </c>
       <c r="W11" t="n">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="X11" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 53; TATASTEEL: 49, HINDZINC: 48, SAIL: 44</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 50; OIL: 51, IOC: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.7%) • sector strength 27/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.4%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +6 = 55</t>
+          <t>Risk/Vol +21 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2714,13 +2714,13 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H12" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I12" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>520</v>
+        <v>522.2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>504 - 536</t>
+          <t>506 - 538</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.9%)</t>
+          <t>Below 200-DMA (-11.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14559</v>
+        <v>14623</v>
       </c>
       <c r="W12" t="n">
         <v>28</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 55; DELHIVERY: 60, INDIGO: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-11.9%) • sector strength 60/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-11.4%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +10 · Regime +9 · Trend/Tech +8 · Sector +1 = 52</t>
+          <t>Risk/Vol +23 · Historical +10 · Trend/Tech +9 · Regime +9 · Sector +1 = 52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,13 +2832,13 @@
         <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H13" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5510</v>
+        <v>5623.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5366 - 5654</t>
+          <t>5477 - 5770</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.3%)</t>
+          <t>Below 200-DMA (-1.3%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>22040</v>
+        <v>22494</v>
       </c>
       <c r="W13" t="n">
         <v>4</v>
       </c>
       <c r="X13" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 54, HINDUNILVR: 49, DABUR: 46. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 54, DABUR: 49, HINDUNILVR: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-3.3%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-1.3%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -3554,15 +3554,9 @@
       <c r="L3" t="n">
         <v>2.12</v>
       </c>
-      <c r="M3" t="n">
-        <v>38</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>81</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>194.1</v>
       </c>
@@ -3959,15 +3953,9 @@
       <c r="L8" t="n">
         <v>0.47</v>
       </c>
-      <c r="M8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>88</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>54.2</v>
       </c>
@@ -4121,15 +4109,9 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>88</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -4445,15 +4427,9 @@
       <c r="L14" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-21</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>-4.7</v>
       </c>
@@ -4607,15 +4583,9 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-331</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -4769,15 +4739,9 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>61</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -5012,15 +4976,9 @@
       <c r="L21" t="n">
         <v>0.14</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>67</v>
-      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5174,15 +5132,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-7</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0.1</v>
       </c>
@@ -5336,15 +5288,9 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-64</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5735,15 +5681,9 @@
       <c r="L30" t="n">
         <v>-1.18</v>
       </c>
-      <c r="M30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-16.1</v>
-      </c>
-      <c r="O30" t="n">
-        <v>-1221</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
         <v>-43.4</v>
       </c>
@@ -5978,15 +5918,9 @@
       <c r="L33" t="n">
         <v>1.08</v>
       </c>
-      <c r="M33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-4.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>100</v>
-      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
         <v>38.1</v>
       </c>
@@ -6140,15 +6074,9 @@
       <c r="L35" t="n">
         <v>0.12</v>
       </c>
-      <c r="M35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>12</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>5.6</v>
       </c>
@@ -6626,15 +6554,9 @@
       <c r="L41" t="n">
         <v>-0.27</v>
       </c>
-      <c r="M41" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-702</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>-27.3</v>
       </c>
@@ -6707,15 +6629,9 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>-157</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -7112,15 +7028,9 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>97</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -7355,15 +7265,9 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>55</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -7679,15 +7583,9 @@
       <c r="L54" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M54" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N54" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="O54" t="n">
-        <v>-26</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
         <v>-4.4</v>
       </c>
@@ -7760,15 +7658,9 @@
       <c r="L55" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>-243</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
         <v>-31</v>
       </c>
@@ -7922,15 +7814,9 @@
       <c r="L57" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="M57" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-609</v>
-      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
         <v>-33.9</v>
       </c>
@@ -8323,15 +8209,9 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="n">
-        <v>93</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -8485,15 +8365,9 @@
       <c r="L64" t="n">
         <v>0.99</v>
       </c>
-      <c r="M64" t="n">
-        <v>14</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" t="n">
-        <v>100</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" t="n">
         <v>69</v>
       </c>
@@ -8647,15 +8521,9 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>49</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -9133,15 +9001,9 @@
       <c r="L72" t="n">
         <v>0.17</v>
       </c>
-      <c r="M72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O72" t="n">
-        <v>29</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
         <v>13.3</v>
       </c>
@@ -9214,15 +9076,9 @@
       <c r="L73" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M73" t="n">
-        <v>7</v>
-      </c>
-      <c r="N73" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="O73" t="n">
-        <v>11</v>
-      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
       <c r="P73" t="n">
         <v>3.1</v>
       </c>
@@ -9943,15 +9799,9 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="N82" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="O82" t="n">
-        <v>21</v>
-      </c>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -10429,15 +10279,9 @@
       <c r="L88" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M88" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="O88" t="n">
-        <v>-128</v>
-      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
         <v>-19.5</v>
       </c>
@@ -10591,12 +10435,8 @@
       <c r="L90" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-12.5</v>
-      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>-38.1</v>
@@ -10670,12 +10510,8 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-12</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -11721,15 +11557,9 @@
       <c r="L104" t="n">
         <v>-0.49</v>
       </c>
-      <c r="M104" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="O104" t="n">
-        <v>-581</v>
-      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
         <v>-24.9</v>
       </c>
@@ -11802,15 +11632,9 @@
       <c r="L105" t="n">
         <v>-0.75</v>
       </c>
-      <c r="M105" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O105" t="n">
-        <v>-4582</v>
-      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
         <v>-32</v>
       </c>
@@ -11883,15 +11707,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -11964,15 +11782,9 @@
       <c r="L107" t="n">
         <v>1.65</v>
       </c>
-      <c r="M107" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N107" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="O107" t="n">
-        <v>99</v>
-      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
         <v>138.8</v>
       </c>
@@ -12369,15 +12181,9 @@
       <c r="L112" t="n">
         <v>1.4</v>
       </c>
-      <c r="M112" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N112" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O112" t="n">
-        <v>100</v>
-      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
       <c r="P112" t="n">
         <v>82.7</v>
       </c>
@@ -12612,15 +12418,9 @@
       <c r="L115" t="n">
         <v>0.72</v>
       </c>
-      <c r="M115" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N115" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O115" t="n">
-        <v>77</v>
-      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
       <c r="P115" t="n">
         <v>58.4</v>
       </c>
@@ -12693,15 +12493,9 @@
       <c r="L116" t="n">
         <v>0.83</v>
       </c>
-      <c r="M116" t="n">
-        <v>15</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>77</v>
-      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
         <v>54.8</v>
       </c>
@@ -12936,15 +12730,9 @@
       <c r="L119" t="n">
         <v>0.38</v>
       </c>
-      <c r="M119" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="N119" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="O119" t="n">
-        <v>97</v>
-      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
       <c r="P119" t="n">
         <v>25</v>
       </c>
@@ -13341,15 +13129,9 @@
       <c r="L124" t="n">
         <v>0.86</v>
       </c>
-      <c r="M124" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="N124" t="n">
-        <v>0</v>
-      </c>
-      <c r="O124" t="n">
-        <v>90</v>
-      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="n">
         <v>62</v>
       </c>
@@ -13503,15 +13285,9 @@
       <c r="L126" t="n">
         <v>0.61</v>
       </c>
-      <c r="M126" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N126" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="O126" t="n">
-        <v>100</v>
-      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
       <c r="P126" t="n">
         <v>51.4</v>
       </c>
@@ -13665,15 +13441,9 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>83</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -13827,15 +13597,9 @@
       <c r="L130" t="n">
         <v>0.52</v>
       </c>
-      <c r="M130" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="N130" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O130" t="n">
-        <v>81</v>
-      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
       <c r="P130" t="n">
         <v>28.8</v>
       </c>
@@ -14232,15 +13996,9 @@
       <c r="L135" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M135" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N135" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>-241</v>
-      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
       <c r="P135" t="n">
         <v>-22.2</v>
       </c>
@@ -14475,15 +14233,9 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N138" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O138" t="n">
-        <v>100</v>
-      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -14799,15 +14551,9 @@
       <c r="L142" t="n">
         <v>1.16</v>
       </c>
-      <c r="M142" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="N142" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O142" t="n">
-        <v>100</v>
-      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
       <c r="P142" t="n">
         <v>81.5</v>
       </c>
@@ -15042,15 +14788,9 @@
       <c r="L145" t="n">
         <v>0.64</v>
       </c>
-      <c r="M145" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N145" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="O145" t="n">
-        <v>94</v>
-      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
       <c r="P145" t="n">
         <v>57.1</v>
       </c>
@@ -15528,15 +15268,9 @@
       <c r="L151" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M151" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N151" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="O151" t="n">
-        <v>-1052</v>
-      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
       <c r="P151" t="n">
         <v>-21.8</v>
       </c>
@@ -15690,15 +15424,9 @@
       <c r="L153" t="n">
         <v>1.91</v>
       </c>
-      <c r="M153" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="N153" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="O153" t="n">
-        <v>83</v>
-      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
       <c r="P153" t="n">
         <v>128.7</v>
       </c>
@@ -15852,15 +15580,9 @@
       <c r="L155" t="n">
         <v>0.84</v>
       </c>
-      <c r="M155" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="N155" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="O155" t="n">
-        <v>62</v>
-      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
       <c r="P155" t="n">
         <v>69.3</v>
       </c>
@@ -16332,15 +16054,9 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O161" t="n">
-        <v>-46</v>
-      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -17782,15 +17498,9 @@
       <c r="L179" t="n">
         <v>0.29</v>
       </c>
-      <c r="M179" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N179" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="O179" t="n">
-        <v>64</v>
-      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
       <c r="P179" t="n">
         <v>14.5</v>
       </c>
@@ -17944,15 +17654,9 @@
       <c r="L181" t="n">
         <v>0.08</v>
       </c>
-      <c r="M181" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N181" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="O181" t="n">
-        <v>20</v>
-      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
       <c r="P181" t="n">
         <v>3.9</v>
       </c>
@@ -18025,15 +17729,9 @@
       <c r="L182" t="n">
         <v>1.21</v>
       </c>
-      <c r="M182" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="N182" t="n">
-        <v>0</v>
-      </c>
-      <c r="O182" t="n">
-        <v>90</v>
-      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
       <c r="P182" t="n">
         <v>119.9</v>
       </c>
@@ -18106,15 +17804,9 @@
       <c r="L183" t="n">
         <v>1.73</v>
       </c>
-      <c r="M183" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" t="n">
-        <v>81</v>
-      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
       <c r="P183" t="n">
         <v>99.90000000000001</v>
       </c>
@@ -18673,15 +18365,9 @@
       <c r="L190" t="n">
         <v>0.12</v>
       </c>
-      <c r="M190" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N190" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="O190" t="n">
-        <v>22</v>
-      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
       <c r="P190" t="n">
         <v>6.4</v>
       </c>
@@ -18835,15 +18521,9 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="n">
-        <v>11</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="n">
-        <v>9</v>
-      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -18997,15 +18677,9 @@
       <c r="L194" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M194" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N194" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="O194" t="n">
-        <v>-40</v>
-      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
       <c r="P194" t="n">
         <v>-6.8</v>
       </c>
@@ -19240,15 +18914,9 @@
       <c r="L197" t="n">
         <v>0.27</v>
       </c>
-      <c r="M197" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N197" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="O197" t="n">
-        <v>46</v>
-      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
       <c r="P197" t="n">
         <v>22.8</v>
       </c>
@@ -19321,15 +18989,9 @@
       <c r="L198" t="n">
         <v>0.27</v>
       </c>
-      <c r="M198" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N198" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O198" t="n">
-        <v>20</v>
-      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
       <c r="P198" t="n">
         <v>14.2</v>
       </c>
@@ -20050,12 +19712,8 @@
       <c r="L207" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="n">
-        <v>-9.199999999999999</v>
-      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="n">
         <v>-24.9</v>
@@ -20129,15 +19787,9 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N208" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="O208" t="n">
-        <v>-413</v>
-      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -20210,15 +19862,9 @@
       <c r="L209" t="n">
         <v>-0.72</v>
       </c>
-      <c r="M209" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N209" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="O209" t="n">
-        <v>-1358</v>
-      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
       <c r="P209" t="n">
         <v>-41.2</v>
       </c>
@@ -20372,12 +20018,8 @@
       <c r="L211" t="n">
         <v>-2.56</v>
       </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="n">
-        <v>-26.2</v>
-      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="n">
         <v>-70.09999999999999</v>
@@ -20613,15 +20255,9 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N214" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O214" t="n">
-        <v>100</v>
-      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -20856,15 +20492,9 @@
       <c r="L217" t="n">
         <v>0.68</v>
       </c>
-      <c r="M217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="N217" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="O217" t="n">
-        <v>100</v>
-      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
       <c r="P217" t="n">
         <v>48.3</v>
       </c>
@@ -21099,15 +20729,9 @@
       <c r="L220" t="n">
         <v>0.13</v>
       </c>
-      <c r="M220" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N220" t="n">
-        <v>-11.9</v>
-      </c>
-      <c r="O220" t="n">
-        <v>46</v>
-      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
       <c r="P220" t="n">
         <v>5.9</v>
       </c>
@@ -21656,15 +21280,9 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N227" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O227" t="n">
-        <v>89</v>
-      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -21899,15 +21517,9 @@
       <c r="L230" t="n">
         <v>0.4</v>
       </c>
-      <c r="M230" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="N230" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O230" t="n">
-        <v>67</v>
-      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
       <c r="P230" t="n">
         <v>27</v>
       </c>
@@ -22061,15 +21673,9 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N232" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O232" t="n">
-        <v>51</v>
-      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -22223,15 +21829,9 @@
       <c r="L234" t="n">
         <v>0.32</v>
       </c>
-      <c r="M234" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N234" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="O234" t="n">
-        <v>86</v>
-      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
       <c r="P234" t="n">
         <v>19.7</v>
       </c>
@@ -22628,15 +22228,9 @@
       <c r="L239" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M239" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N239" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="O239" t="n">
-        <v>-413</v>
-      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
       <c r="P239" t="n">
         <v>-19</v>
       </c>
@@ -22790,15 +22384,9 @@
       <c r="L241" t="n">
         <v>-0.39</v>
       </c>
-      <c r="M241" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="N241" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="O241" t="n">
-        <v>-322</v>
-      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
       <c r="P241" t="n">
         <v>-24.3</v>
       </c>
@@ -22871,15 +22459,9 @@
       <c r="L242" t="n">
         <v>1.88</v>
       </c>
-      <c r="M242" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="N242" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="O242" t="n">
-        <v>96</v>
-      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
       <c r="P242" t="n">
         <v>175.9</v>
       </c>
@@ -22952,15 +22534,9 @@
       <c r="L243" t="n">
         <v>0.42</v>
       </c>
-      <c r="M243" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N243" t="n">
-        <v>0</v>
-      </c>
-      <c r="O243" t="n">
-        <v>58</v>
-      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
       <c r="P243" t="n">
         <v>33.7</v>
       </c>
@@ -23033,15 +22609,9 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="N244" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="O244" t="n">
-        <v>83</v>
-      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -23357,15 +22927,9 @@
       <c r="L248" t="n">
         <v>0.35</v>
       </c>
-      <c r="M248" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="N248" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O248" t="n">
-        <v>46</v>
-      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
       <c r="P248" t="n">
         <v>13.7</v>
       </c>
@@ -23841,12 +23405,8 @@
       <c r="L254" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M254" t="n">
-        <v>0</v>
-      </c>
-      <c r="N254" t="n">
-        <v>-8.6</v>
-      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="n">
         <v>-19</v>
@@ -23999,12 +23559,8 @@
       <c r="L256" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M256" t="n">
-        <v>0</v>
-      </c>
-      <c r="N256" t="n">
-        <v>-10.6</v>
-      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
         <v>-36.1</v>
@@ -24321,15 +23877,9 @@
       <c r="L260" t="n">
         <v>0.29</v>
       </c>
-      <c r="M260" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N260" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O260" t="n">
-        <v>44</v>
-      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
       <c r="P260" t="n">
         <v>20.4</v>
       </c>
@@ -24807,15 +24357,9 @@
       <c r="L266" t="n">
         <v>-0.33</v>
       </c>
-      <c r="M266" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="N266" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="O266" t="n">
-        <v>-45</v>
-      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
       <c r="P266" t="n">
         <v>-13.4</v>
       </c>
@@ -24888,15 +24432,9 @@
       <c r="L267" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M267" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N267" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="O267" t="n">
-        <v>-777</v>
-      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
       <c r="P267" t="n">
         <v>-15</v>
       </c>
@@ -25131,15 +24669,9 @@
       <c r="L270" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M270" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N270" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O270" t="n">
-        <v>-255</v>
-      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
       <c r="P270" t="n">
         <v>-30.7</v>
       </c>
@@ -25860,15 +25392,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -26103,15 +25629,9 @@
       <c r="L282" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M282" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N282" t="n">
-        <v>-12</v>
-      </c>
-      <c r="O282" t="n">
-        <v>-103</v>
-      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
       <c r="P282" t="n">
         <v>-18.3</v>
       </c>
@@ -26265,15 +25785,9 @@
       <c r="L284" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M284" t="n">
-        <v>1</v>
-      </c>
-      <c r="N284" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="O284" t="n">
-        <v>-1163</v>
-      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
       <c r="P284" t="n">
         <v>-37.6</v>
       </c>
@@ -26929,7 +26443,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.7</v>
+        <v>-10.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26971,7 +26485,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-13.9</v>
+        <v>-14</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -27013,7 +26527,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-8.1</v>
+        <v>-10.4</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -27097,7 +26611,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27139,7 +26653,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -27181,7 +26695,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.7</v>
+        <v>-1.4</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -27223,7 +26737,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.4</v>
+        <v>-2.9</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -27265,7 +26779,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3.8</v>
+        <v>-4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -27307,7 +26821,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-2.9</v>
+        <v>-3.8</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -27349,7 +26863,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-3.6</v>
+        <v>-3.2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -27433,7 +26947,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.3</v>
+        <v>-7.4</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -27475,7 +26989,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.1</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -27517,7 +27031,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.3</v>
+        <v>-3.1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -27559,7 +27073,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-3.8</v>
+        <v>-5.1</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27601,7 +27115,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-4.2</v>
+        <v>-3.7</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -27643,7 +27157,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-12.6</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27718,12 +27232,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27252,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27262,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27768,7 +27282,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27778,12 +27292,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27793,12 +27307,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27322,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27337,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (75)</t>
+          <t>ICICIBANK (78)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ONGC (50)</t>
+          <t>HINDUNILVR (48)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ONGC, ZYDUSLIFE</t>
+          <t>HINDUNILVR, PIDILITIND, SUNPHARMA</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIDILITIND, SUNPHARMA</t>
+          <t>BRITANNIA, KOTAKBANK, ZYDUSLIFE</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-11  /  2026-08-10</t>
+          <t>2026-08-12  /  2026-08-11</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +7 = 75</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +8 = 78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1431.8</v>
+        <v>1429.6</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1392 - 1472</t>
+          <t>1390 - 1469</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.0%)</t>
+          <t>Above 200-DMA (+5.8%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>15750</v>
+        <v>20014</v>
       </c>
       <c r="W2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="X2" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 75; SBIN: 74, FEDERALBNK: 70, BAJAJFINSV: 67</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; SBIN: 74, BAJFINANCE: 61, YESBANK: 61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.0%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Trend/Tech +17 · Historical +15 · Regime +9 · Sector +7 = 70</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +7 = 74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1649,13 +1649,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
         <v>67</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1674,33 +1674,33 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1119</v>
+        <v>1942</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1086 - 1152</t>
+          <t>1890 - 1994</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +14%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+14.8%)</t>
+          <t>Above 200-DMA (+8.9%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>20142</v>
+        <v>27188</v>
       </c>
       <c r="W3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="X3" t="n">
-        <v>7</v>
+        <v>9.1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ZYDUSLIFE: 70; LUPIN: 69, AJANTPHARM: 66, DRREDDY: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 73, LUPIN: 69, ZYDUSLIFE: 69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+14.8%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.9%) • sector strength 67/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H4" t="n">
         <v>95</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2300</v>
+        <v>2278.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2240 - 2360</t>
+          <t>2219 - 2338</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+3.0%)</t>
+          <t>Above 200-DMA (+1.9%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>25300</v>
+        <v>27347</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X4" t="n">
-        <v>8.6</v>
+        <v>9.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; ZYDUSLIFE: 70, AJANTPHARM: 66, DRREDDY: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 73, ZYDUSLIFE: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+3.0%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+1.9%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +19 · Regime +9 · Trend/Tech +8 · Sector +7 = 65</t>
+          <t>Risk/Vol +20 · Trend/Tech +16 · Historical +14 · Regime +9 · Sector +7 = 66</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="I5" t="n">
         <v>73</v>
@@ -1901,42 +1901,42 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>393.5</v>
+        <v>1685.8</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>382 - 405</t>
+          <t>1632 - 1740</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.3%)</t>
+          <t>Above 200-DMA (+14.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>15346</v>
+        <v>20230</v>
       </c>
       <c r="W5" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — KOTAKBANK: 65; ICICIBANK: 75, SBIN: 74, FEDERALBNK: 70. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 66; CHAMBLFERT: 54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • below 200-dma (-2.3%) • sector strength 73/100 • regime cautious (partial deploy) • 3 similar past recs: 100% positive, median +1.9%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+14.1%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +1 = 62</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +3 · Trend/Tech +2 = 63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,20 +1999,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
         <v>96</v>
       </c>
       <c r="I6" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>340.5</v>
+        <v>338.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>332 - 349</t>
+          <t>330 - 347</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.7%)</t>
+          <t>Below 200-DMA (-5.3%)</t>
         </is>
       </c>
       <c r="S6" t="n">
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>37450</v>
+        <v>36553</v>
       </c>
       <c r="W6" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X6" t="n">
-        <v>12.6</v>
+        <v>12.2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 62; POWERGRID: 54, JSWENERGY: 53, TATAPOWER: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; JSWENERGY: 56, POWERGRID: 56, TATAPOWER: 55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.7%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 56</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>404.4</v>
+        <v>405.9</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>392 - 417</t>
+          <t>393 - 419</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.7%)</t>
+          <t>Below 200-DMA (-3.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>14152</v>
+        <v>14611</v>
       </c>
       <c r="W7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X7" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 59, KEI: 51, MAZDOCK: 47. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 58; HAL: 62, POLYCAB: 56, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.7%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +1 = 54</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2242,13 @@
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
         <v>97</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>270.1</v>
+        <v>268</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>263 - 277</t>
+          <t>261 - 275</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,11 +2282,11 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.5%)</t>
+          <t>Below 200-DMA (-6.2%)</t>
         </is>
       </c>
       <c r="S8" t="n">
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>37274</v>
+        <v>35905</v>
       </c>
       <c r="W8" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 54; NTPC: 62, JSWENERGY: 53, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 63, JSWENERGY: 56, TATAPOWER: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.5%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>282.6</v>
+        <v>279</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>276 - 290</t>
+          <t>272 - 286</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-14.3%)</t>
+          <t>Below 200-DMA (-15.3%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>31091</v>
+        <v>24273</v>
       </c>
       <c r="W9" t="n">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="X9" t="n">
-        <v>10.4</v>
+        <v>8.1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; BRITANNIA: 52, DABUR: 49, HINDUNILVR: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 48, HINDUNILVR: 48, PATANJALI: 45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-14.3%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.3%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2478,10 +2478,10 @@
         <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I10" t="n">
         <v>20</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>411</v>
+        <v>412.6</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>399 - 423</t>
+          <t>400 - 425</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.7%)</t>
+          <t>Below 200-DMA (-3.3%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>27126</v>
+        <v>26406</v>
       </c>
       <c r="W10" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; TATASTEEL: 48, HINDZINC: 47, SAIL: 44</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; TATASTEEL: 49, HINDZINC: 46, SAIL: 45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.7%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.3%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Sector +3 · Trend/Tech +2 = 50</t>
+          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2589,20 +2589,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>239.8</v>
+        <v>239.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>232 - 248</t>
+          <t>232 - 247</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.4%)</t>
+          <t>Below 200-DMA (-7.5%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>29980</v>
+        <v>28973</v>
       </c>
       <c r="W11" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 50; OIL: 51, IOC: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 48; IOC: 48, OIL: 47, GUJGASLTD: 33</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.4%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.5%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 53</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +4 = 53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2714,13 +2714,13 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="I12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>522.2</v>
+        <v>515</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>506 - 538</t>
+          <t>499 - 531</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-11.4%)</t>
+          <t>Below 200-DMA (-12.5%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14623</v>
+        <v>15451</v>
       </c>
       <c r="W12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-11.4%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-12.5%) • sector strength 40/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +10 · Trend/Tech +9 · Regime +9 · Sector +1 = 52</t>
+          <t>Risk/Vol +20 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2829,13 +2829,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="H13" t="n">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I13" t="n">
         <v>7</v>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>5623.5</v>
+        <v>2064.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5477 - 5770</t>
+          <t>1999 - 2130</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2872,15 +2872,15 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.3%)</t>
+          <t>Below 200-DMA (-9.1%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>22494</v>
+        <v>18584</v>
       </c>
       <c r="W13" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="X13" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BRITANNIA: 52; ITC: 54, DABUR: 49, HINDUNILVR: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 54, DABUR: 48, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-1.3%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 33% positive, median -7.7% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.1%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -3554,9 +3554,15 @@
       <c r="L3" t="n">
         <v>2.12</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>38</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>81</v>
+      </c>
       <c r="P3" t="n">
         <v>194.1</v>
       </c>
@@ -3710,15 +3716,9 @@
       <c r="L5" t="n">
         <v>1.6</v>
       </c>
-      <c r="M5" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>98</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>135.9</v>
       </c>
@@ -3953,9 +3953,15 @@
       <c r="L8" t="n">
         <v>0.47</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>88</v>
+      </c>
       <c r="P8" t="n">
         <v>54.2</v>
       </c>
@@ -4028,15 +4034,9 @@
       <c r="L9" t="n">
         <v>0.77</v>
       </c>
-      <c r="M9" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-5.3</v>
-      </c>
-      <c r="O9" t="n">
-        <v>62</v>
-      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>41.4</v>
       </c>
@@ -4427,9 +4427,15 @@
       <c r="L14" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-21</v>
+      </c>
       <c r="P14" t="n">
         <v>-4.7</v>
       </c>
@@ -4583,9 +4589,15 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-331</v>
+      </c>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -4739,9 +4751,15 @@
       <c r="L18" t="n">
         <v>0.41</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O18" t="n">
+        <v>61</v>
+      </c>
       <c r="P18" t="n">
         <v>41.1</v>
       </c>
@@ -4895,15 +4913,9 @@
       <c r="L20" t="n">
         <v>0.48</v>
       </c>
-      <c r="M20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-10.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>87</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>24.2</v>
       </c>
@@ -4976,9 +4988,15 @@
       <c r="L21" t="n">
         <v>0.14</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>67</v>
+      </c>
       <c r="P21" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5363,15 +5381,9 @@
       <c r="L26" t="n">
         <v>-0.73</v>
       </c>
-      <c r="M26" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-11.5</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-1734</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>-27.5</v>
       </c>
@@ -5681,9 +5693,15 @@
       <c r="L30" t="n">
         <v>-1.18</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-16.1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>-1221</v>
+      </c>
       <c r="P30" t="n">
         <v>-43.4</v>
       </c>
@@ -5756,15 +5774,9 @@
       <c r="L31" t="n">
         <v>-0.92</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-456</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
         <v>-47.7</v>
       </c>
@@ -5837,15 +5849,9 @@
       <c r="L32" t="n">
         <v>0.71</v>
       </c>
-      <c r="M32" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>100</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
         <v>82.59999999999999</v>
       </c>
@@ -5918,9 +5924,15 @@
       <c r="L33" t="n">
         <v>1.08</v>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-4.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>100</v>
+      </c>
       <c r="P33" t="n">
         <v>38.1</v>
       </c>
@@ -6074,9 +6086,15 @@
       <c r="L35" t="n">
         <v>0.12</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>12</v>
+      </c>
       <c r="P35" t="n">
         <v>5.6</v>
       </c>
@@ -6392,15 +6410,9 @@
       <c r="L39" t="n">
         <v>-0.23</v>
       </c>
-      <c r="M39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-22.2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>-322</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
         <v>-19.9</v>
       </c>
@@ -6629,9 +6641,15 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-157</v>
+      </c>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -6704,15 +6722,9 @@
       <c r="L43" t="n">
         <v>-0.76</v>
       </c>
-      <c r="M43" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="N43" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="O43" t="n">
-        <v>-642</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
         <v>-29.6</v>
       </c>
@@ -7028,9 +7040,15 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>97</v>
+      </c>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -7103,15 +7121,9 @@
       <c r="L48" t="n">
         <v>1.05</v>
       </c>
-      <c r="M48" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="O48" t="n">
-        <v>98</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>99.5</v>
       </c>
@@ -7340,15 +7352,9 @@
       <c r="L51" t="n">
         <v>0.2</v>
       </c>
-      <c r="M51" t="n">
-        <v>3</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="O51" t="n">
-        <v>68</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
         <v>8.4</v>
       </c>
@@ -7502,15 +7508,9 @@
       <c r="L53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="M53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-38</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
         <v>-3.8</v>
       </c>
@@ -7583,9 +7583,15 @@
       <c r="L54" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+      <c r="M54" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O54" t="n">
+        <v>-26</v>
+      </c>
       <c r="P54" t="n">
         <v>-4.4</v>
       </c>
@@ -7814,9 +7820,15 @@
       <c r="L57" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="M57" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N57" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="O57" t="n">
+        <v>-609</v>
+      </c>
       <c r="P57" t="n">
         <v>-33.9</v>
       </c>
@@ -8209,9 +8221,15 @@
       <c r="L62" t="n">
         <v>0.92</v>
       </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+      <c r="M62" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>93</v>
+      </c>
       <c r="P62" t="n">
         <v>112</v>
       </c>
@@ -8365,9 +8383,15 @@
       <c r="L64" t="n">
         <v>0.99</v>
       </c>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
+      <c r="M64" t="n">
+        <v>14</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>100</v>
+      </c>
       <c r="P64" t="n">
         <v>69</v>
       </c>
@@ -8839,15 +8863,9 @@
       <c r="L70" t="n">
         <v>0.43</v>
       </c>
-      <c r="M70" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="N70" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="O70" t="n">
-        <v>61</v>
-      </c>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
       <c r="P70" t="n">
         <v>21.9</v>
       </c>
@@ -8920,15 +8938,9 @@
       <c r="L71" t="n">
         <v>0.48</v>
       </c>
-      <c r="M71" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>51</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
         <v>16.9</v>
       </c>
@@ -9076,9 +9088,15 @@
       <c r="L73" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
+      <c r="M73" t="n">
+        <v>7</v>
+      </c>
+      <c r="N73" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="O73" t="n">
+        <v>11</v>
+      </c>
       <c r="P73" t="n">
         <v>3.1</v>
       </c>
@@ -9799,9 +9817,15 @@
       <c r="L82" t="n">
         <v>0.4</v>
       </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="M82" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="N82" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="O82" t="n">
+        <v>21</v>
+      </c>
       <c r="P82" t="n">
         <v>23.2</v>
       </c>
@@ -9874,15 +9898,9 @@
       <c r="L83" t="n">
         <v>0.21</v>
       </c>
-      <c r="M83" t="n">
-        <v>8</v>
-      </c>
-      <c r="N83" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="O83" t="n">
-        <v>36</v>
-      </c>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
       <c r="P83" t="n">
         <v>12.2</v>
       </c>
@@ -9955,15 +9973,9 @@
       <c r="L84" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M84" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N84" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>23</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
         <v>4.3</v>
       </c>
@@ -10279,9 +10291,15 @@
       <c r="L88" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-128</v>
+      </c>
       <c r="P88" t="n">
         <v>-19.5</v>
       </c>
@@ -10354,15 +10372,9 @@
       <c r="L89" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M89" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="O89" t="n">
-        <v>-153</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
         <v>-19.5</v>
       </c>
@@ -10666,15 +10678,9 @@
       <c r="L93" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="N93" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="O93" t="n">
-        <v>100</v>
-      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
         <v>91.7</v>
       </c>
@@ -10828,15 +10834,9 @@
       <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O95" t="n">
-        <v>82</v>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
         <v>47.5</v>
       </c>
@@ -11152,15 +11152,9 @@
       <c r="L99" t="n">
         <v>0.28</v>
       </c>
-      <c r="M99" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N99" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="O99" t="n">
-        <v>58</v>
-      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
       <c r="P99" t="n">
         <v>11.1</v>
       </c>
@@ -11557,9 +11551,15 @@
       <c r="L104" t="n">
         <v>-0.49</v>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>-581</v>
+      </c>
       <c r="P104" t="n">
         <v>-24.9</v>
       </c>
@@ -11857,15 +11857,9 @@
       <c r="L108" t="n">
         <v>1.21</v>
       </c>
-      <c r="M108" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>100</v>
-      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
       <c r="P108" t="n">
         <v>121.6</v>
       </c>
@@ -11938,15 +11932,9 @@
       <c r="L109" t="n">
         <v>1.48</v>
       </c>
-      <c r="M109" t="n">
-        <v>22</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="O109" t="n">
-        <v>99</v>
-      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
       <c r="P109" t="n">
         <v>120.4</v>
       </c>
@@ -12181,9 +12169,15 @@
       <c r="L112" t="n">
         <v>1.4</v>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O112" t="n">
+        <v>100</v>
+      </c>
       <c r="P112" t="n">
         <v>82.7</v>
       </c>
@@ -12418,9 +12412,15 @@
       <c r="L115" t="n">
         <v>0.72</v>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="N115" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O115" t="n">
+        <v>77</v>
+      </c>
       <c r="P115" t="n">
         <v>58.4</v>
       </c>
@@ -12493,9 +12493,15 @@
       <c r="L116" t="n">
         <v>0.83</v>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>15</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>77</v>
+      </c>
       <c r="P116" t="n">
         <v>54.8</v>
       </c>
@@ -12730,9 +12736,15 @@
       <c r="L119" t="n">
         <v>0.38</v>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="O119" t="n">
+        <v>97</v>
+      </c>
       <c r="P119" t="n">
         <v>25</v>
       </c>
@@ -12886,15 +12898,9 @@
       <c r="L121" t="n">
         <v>0.11</v>
       </c>
-      <c r="M121" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="N121" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="O121" t="n">
-        <v>15</v>
-      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
       <c r="P121" t="n">
         <v>5.8</v>
       </c>
@@ -13048,15 +13054,9 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O123" t="n">
-        <v>86</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -13129,9 +13129,15 @@
       <c r="L124" t="n">
         <v>0.86</v>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>90</v>
+      </c>
       <c r="P124" t="n">
         <v>62</v>
       </c>
@@ -13285,9 +13291,15 @@
       <c r="L126" t="n">
         <v>0.61</v>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O126" t="n">
+        <v>100</v>
+      </c>
       <c r="P126" t="n">
         <v>51.4</v>
       </c>
@@ -13597,9 +13609,15 @@
       <c r="L130" t="n">
         <v>0.52</v>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O130" t="n">
+        <v>81</v>
+      </c>
       <c r="P130" t="n">
         <v>28.8</v>
       </c>
@@ -13753,15 +13771,9 @@
       <c r="L132" t="n">
         <v>0.16</v>
       </c>
-      <c r="M132" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N132" t="n">
-        <v>-5.2</v>
-      </c>
-      <c r="O132" t="n">
-        <v>100</v>
-      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
       <c r="P132" t="n">
         <v>13.5</v>
       </c>
@@ -13996,9 +14008,15 @@
       <c r="L135" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-241</v>
+      </c>
       <c r="P135" t="n">
         <v>-22.2</v>
       </c>
@@ -14071,15 +14089,9 @@
       <c r="L136" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M136" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N136" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="O136" t="n">
-        <v>-173</v>
-      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
       <c r="P136" t="n">
         <v>-26.4</v>
       </c>
@@ -14551,9 +14563,15 @@
       <c r="L142" t="n">
         <v>1.16</v>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
+      <c r="M142" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="N142" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O142" t="n">
+        <v>100</v>
+      </c>
       <c r="P142" t="n">
         <v>81.5</v>
       </c>
@@ -14788,9 +14806,15 @@
       <c r="L145" t="n">
         <v>0.64</v>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="O145" t="n">
+        <v>94</v>
+      </c>
       <c r="P145" t="n">
         <v>57.1</v>
       </c>
@@ -14944,15 +14968,9 @@
       <c r="L147" t="n">
         <v>0.49</v>
       </c>
-      <c r="M147" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="N147" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="O147" t="n">
-        <v>50</v>
-      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
       <c r="P147" t="n">
         <v>36.9</v>
       </c>
@@ -15106,15 +15124,9 @@
       <c r="L149" t="n">
         <v>0.22</v>
       </c>
-      <c r="M149" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="N149" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="O149" t="n">
-        <v>49</v>
-      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
       <c r="P149" t="n">
         <v>16.9</v>
       </c>
@@ -15268,9 +15280,15 @@
       <c r="L151" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
+      <c r="M151" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="O151" t="n">
+        <v>-1052</v>
+      </c>
       <c r="P151" t="n">
         <v>-21.8</v>
       </c>
@@ -15424,9 +15442,15 @@
       <c r="L153" t="n">
         <v>1.91</v>
       </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
+      <c r="M153" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="O153" t="n">
+        <v>83</v>
+      </c>
       <c r="P153" t="n">
         <v>128.7</v>
       </c>
@@ -15580,9 +15604,15 @@
       <c r="L155" t="n">
         <v>0.84</v>
       </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="N155" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="O155" t="n">
+        <v>62</v>
+      </c>
       <c r="P155" t="n">
         <v>69.3</v>
       </c>
@@ -16210,15 +16240,9 @@
       <c r="L163" t="n">
         <v>-0.62</v>
       </c>
-      <c r="M163" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N163" t="n">
-        <v>-9.300000000000001</v>
-      </c>
-      <c r="O163" t="n">
-        <v>-2292</v>
-      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
       <c r="P163" t="n">
         <v>-32.4</v>
       </c>
@@ -16451,15 +16475,9 @@
       <c r="L166" t="n">
         <v>-0.93</v>
       </c>
-      <c r="M166" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N166" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="O166" t="n">
-        <v>-2027</v>
-      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
       <c r="P166" t="n">
         <v>-45.9</v>
       </c>
@@ -17417,15 +17435,9 @@
       <c r="L178" t="n">
         <v>0.33</v>
       </c>
-      <c r="M178" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="N178" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="O178" t="n">
-        <v>65</v>
-      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
       <c r="P178" t="n">
         <v>21.2</v>
       </c>
@@ -17498,9 +17510,15 @@
       <c r="L179" t="n">
         <v>0.29</v>
       </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
+      <c r="M179" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="N179" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="O179" t="n">
+        <v>64</v>
+      </c>
       <c r="P179" t="n">
         <v>14.5</v>
       </c>
@@ -17573,15 +17591,9 @@
       <c r="L180" t="n">
         <v>0.1</v>
       </c>
-      <c r="M180" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N180" t="n">
-        <v>-13.4</v>
-      </c>
-      <c r="O180" t="n">
-        <v>52</v>
-      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
       <c r="P180" t="n">
         <v>8</v>
       </c>
@@ -17654,9 +17666,15 @@
       <c r="L181" t="n">
         <v>0.08</v>
       </c>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
+      <c r="M181" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="O181" t="n">
+        <v>20</v>
+      </c>
       <c r="P181" t="n">
         <v>3.9</v>
       </c>
@@ -17729,9 +17747,15 @@
       <c r="L182" t="n">
         <v>1.21</v>
       </c>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
+      <c r="M182" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>90</v>
+      </c>
       <c r="P182" t="n">
         <v>119.9</v>
       </c>
@@ -18122,15 +18146,9 @@
       <c r="L187" t="n">
         <v>0.24</v>
       </c>
-      <c r="M187" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="N187" t="n">
-        <v>-4</v>
-      </c>
-      <c r="O187" t="n">
-        <v>25</v>
-      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
       <c r="P187" t="n">
         <v>12.6</v>
       </c>
@@ -18365,9 +18383,15 @@
       <c r="L190" t="n">
         <v>0.12</v>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N190" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="O190" t="n">
+        <v>22</v>
+      </c>
       <c r="P190" t="n">
         <v>6.4</v>
       </c>
@@ -18440,15 +18464,9 @@
       <c r="L191" t="n">
         <v>0.1</v>
       </c>
-      <c r="M191" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N191" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="O191" t="n">
-        <v>11</v>
-      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
       <c r="P191" t="n">
         <v>6.4</v>
       </c>
@@ -18677,9 +18695,15 @@
       <c r="L194" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="O194" t="n">
+        <v>-40</v>
+      </c>
       <c r="P194" t="n">
         <v>-6.8</v>
       </c>
@@ -18914,9 +18938,15 @@
       <c r="L197" t="n">
         <v>0.27</v>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N197" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="O197" t="n">
+        <v>46</v>
+      </c>
       <c r="P197" t="n">
         <v>22.8</v>
       </c>
@@ -19064,15 +19094,9 @@
       <c r="L199" t="n">
         <v>0.2</v>
       </c>
-      <c r="M199" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N199" t="n">
-        <v>-10.3</v>
-      </c>
-      <c r="O199" t="n">
-        <v>100</v>
-      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
       <c r="P199" t="n">
         <v>12</v>
       </c>
@@ -19145,15 +19169,9 @@
       <c r="L200" t="n">
         <v>0.14</v>
       </c>
-      <c r="M200" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N200" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O200" t="n">
-        <v>100</v>
-      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
       <c r="P200" t="n">
         <v>11</v>
       </c>
@@ -19631,15 +19649,9 @@
       <c r="L206" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M206" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N206" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="O206" t="n">
-        <v>-3098</v>
-      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
       <c r="P206" t="n">
         <v>-21.3</v>
       </c>
@@ -19712,8 +19724,12 @@
       <c r="L207" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="n">
+        <v>-9.199999999999999</v>
+      </c>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="n">
         <v>-24.9</v>
@@ -19862,9 +19878,15 @@
       <c r="L209" t="n">
         <v>-0.72</v>
       </c>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
+      <c r="M209" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N209" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="O209" t="n">
+        <v>-1358</v>
+      </c>
       <c r="P209" t="n">
         <v>-41.2</v>
       </c>
@@ -19937,15 +19959,9 @@
       <c r="L210" t="n">
         <v>-1.35</v>
       </c>
-      <c r="M210" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N210" t="n">
-        <v>-26</v>
-      </c>
-      <c r="O210" t="n">
-        <v>-1247</v>
-      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
       <c r="P210" t="n">
         <v>-66.2</v>
       </c>
@@ -20492,9 +20508,15 @@
       <c r="L217" t="n">
         <v>0.68</v>
       </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
+      <c r="M217" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="N217" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="O217" t="n">
+        <v>100</v>
+      </c>
       <c r="P217" t="n">
         <v>48.3</v>
       </c>
@@ -20567,15 +20589,9 @@
       <c r="L218" t="n">
         <v>0.63</v>
       </c>
-      <c r="M218" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="N218" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O218" t="n">
-        <v>100</v>
-      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
       <c r="P218" t="n">
         <v>45.9</v>
       </c>
@@ -20729,9 +20745,15 @@
       <c r="L220" t="n">
         <v>0.13</v>
       </c>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
+      <c r="M220" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N220" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="O220" t="n">
+        <v>46</v>
+      </c>
       <c r="P220" t="n">
         <v>5.9</v>
       </c>
@@ -21436,15 +21458,9 @@
       <c r="L229" t="n">
         <v>0.53</v>
       </c>
-      <c r="M229" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="N229" t="n">
-        <v>-5.9</v>
-      </c>
-      <c r="O229" t="n">
-        <v>100</v>
-      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
       <c r="P229" t="n">
         <v>30.4</v>
       </c>
@@ -21517,9 +21533,15 @@
       <c r="L230" t="n">
         <v>0.4</v>
       </c>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
+      <c r="M230" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="N230" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="O230" t="n">
+        <v>67</v>
+      </c>
       <c r="P230" t="n">
         <v>27</v>
       </c>
@@ -21673,9 +21695,15 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N232" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O232" t="n">
+        <v>51</v>
+      </c>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -21904,15 +21932,9 @@
       <c r="L235" t="n">
         <v>0.06</v>
       </c>
-      <c r="M235" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N235" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="O235" t="n">
-        <v>49</v>
-      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
       <c r="P235" t="n">
         <v>3.2</v>
       </c>
@@ -22147,15 +22169,9 @@
       <c r="L238" t="n">
         <v>-0.18</v>
       </c>
-      <c r="M238" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N238" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="O238" t="n">
-        <v>-258</v>
-      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
         <v>-13.7</v>
       </c>
@@ -22228,9 +22244,15 @@
       <c r="L239" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N239" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="O239" t="n">
+        <v>-413</v>
+      </c>
       <c r="P239" t="n">
         <v>-19</v>
       </c>
@@ -22384,9 +22406,15 @@
       <c r="L241" t="n">
         <v>-0.39</v>
       </c>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
+      <c r="M241" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N241" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="O241" t="n">
+        <v>-322</v>
+      </c>
       <c r="P241" t="n">
         <v>-24.3</v>
       </c>
@@ -22459,9 +22487,15 @@
       <c r="L242" t="n">
         <v>1.88</v>
       </c>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
+      <c r="M242" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="N242" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="O242" t="n">
+        <v>96</v>
+      </c>
       <c r="P242" t="n">
         <v>175.9</v>
       </c>
@@ -22534,9 +22568,15 @@
       <c r="L243" t="n">
         <v>0.42</v>
       </c>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
+      <c r="M243" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>58</v>
+      </c>
       <c r="P243" t="n">
         <v>33.7</v>
       </c>
@@ -22765,15 +22805,9 @@
       <c r="L246" t="n">
         <v>0.34</v>
       </c>
-      <c r="M246" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="N246" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="O246" t="n">
-        <v>59</v>
-      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
       <c r="P246" t="n">
         <v>23</v>
       </c>
@@ -22846,15 +22880,9 @@
       <c r="L247" t="n">
         <v>0.28</v>
       </c>
-      <c r="M247" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="N247" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="O247" t="n">
-        <v>88</v>
-      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
       <c r="P247" t="n">
         <v>19.5</v>
       </c>
@@ -22927,9 +22955,15 @@
       <c r="L248" t="n">
         <v>0.35</v>
       </c>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
+      <c r="M248" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N248" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O248" t="n">
+        <v>46</v>
+      </c>
       <c r="P248" t="n">
         <v>13.7</v>
       </c>
@@ -23877,9 +23911,15 @@
       <c r="L260" t="n">
         <v>0.29</v>
       </c>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
+      <c r="M260" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N260" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O260" t="n">
+        <v>44</v>
+      </c>
       <c r="P260" t="n">
         <v>20.4</v>
       </c>
@@ -23952,15 +23992,9 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N261" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O261" t="n">
-        <v>38</v>
-      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -24357,9 +24391,15 @@
       <c r="L266" t="n">
         <v>-0.33</v>
       </c>
-      <c r="M266" t="inlineStr"/>
-      <c r="N266" t="inlineStr"/>
-      <c r="O266" t="inlineStr"/>
+      <c r="M266" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N266" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="O266" t="n">
+        <v>-45</v>
+      </c>
       <c r="P266" t="n">
         <v>-13.4</v>
       </c>
@@ -24432,9 +24472,15 @@
       <c r="L267" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr"/>
+      <c r="M267" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N267" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="O267" t="n">
+        <v>-777</v>
+      </c>
       <c r="P267" t="n">
         <v>-15</v>
       </c>
@@ -25230,15 +25276,9 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="N277" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="O277" t="n">
-        <v>45</v>
-      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25629,9 +25669,15 @@
       <c r="L282" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr"/>
+      <c r="M282" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N282" t="n">
+        <v>-12</v>
+      </c>
+      <c r="O282" t="n">
+        <v>-103</v>
+      </c>
       <c r="P282" t="n">
         <v>-18.3</v>
       </c>
@@ -26401,7 +26447,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.9</v>
+        <v>-3.3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26443,7 +26489,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.1</v>
+        <v>-10.9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26485,7 +26531,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-14</v>
+        <v>-14.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26527,7 +26573,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-10.4</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26569,7 +26615,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.5</v>
+        <v>-5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26611,7 +26657,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-8.9</v>
+        <v>-11.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -26653,7 +26699,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-3.4</v>
+        <v>-2.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -26695,7 +26741,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -26737,7 +26783,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -26779,7 +26825,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-4</v>
+        <v>-4.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -26821,7 +26867,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-3.8</v>
+        <v>-2.6</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -26863,7 +26909,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-3.2</v>
+        <v>-3.7</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -26905,7 +26951,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.7</v>
+        <v>-4.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -26947,7 +26993,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.4</v>
+        <v>-5.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -26989,7 +27035,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-8.699999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -27073,7 +27119,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-5.1</v>
+        <v>-4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27115,7 +27161,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-3.7</v>
+        <v>-4.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -27157,7 +27203,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-12.6</v>
+        <v>-13</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27209,7 +27255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27237,7 +27283,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27247,12 +27293,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27262,12 +27308,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27277,27 +27323,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27307,12 +27353,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27322,12 +27368,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27337,12 +27383,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27352,32 +27398,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CASH (intentional)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>12 stocks / 8 sectors</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12 stocks / 9 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HINDUNILVR, PIDILITIND, SUNPHARMA</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BRITANNIA, KOTAKBANK, ZYDUSLIFE</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (78)</t>
+          <t>ICICIBANK (77)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-12  /  2026-08-11</t>
+          <t>2026-08-12  /  2026-08-12</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +8 = 78</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +7 = 77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>20014</v>
+        <v>18585</v>
       </c>
       <c r="W2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X2" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; SBIN: 74, BAJFINANCE: 61, YESBANK: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 73, YESBANK: 62, BAJFINANCE: 60</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.8%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.9%)</t>
+          <t>Above 200-DMA (+8.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>27188</v>
+        <v>25246</v>
       </c>
       <c r="W3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="X3" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 73, LUPIN: 69, ZYDUSLIFE: 69</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 71, LUPIN: 69, ZYDUSLIFE: 69</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.9%) • sector strength 67/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.8%) • sector strength 67/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H4" t="n">
         <v>95</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V4" t="n">
@@ -1837,7 +1837,7 @@
         <v>12</v>
       </c>
       <c r="X4" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 73, ZYDUSLIFE: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 71, ZYDUSLIFE: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +16 · Historical +14 · Regime +9 · Sector +7 = 66</t>
+          <t>Risk/Vol +20 · Trend/Tech +16 · Historical +14 · Regime +9 · Sector +8 = 67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1891,10 +1891,10 @@
         <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I5" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>20230</v>
+        <v>18544</v>
       </c>
       <c r="W5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 66; CHAMBLFERT: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 67; CHAMBLFERT: 55</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+14.1%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+14.1%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +3 · Trend/Tech +2 = 63</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
         <v>96</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>36553</v>
+        <v>36214</v>
       </c>
       <c r="W6" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="X6" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; JSWENERGY: 56, POWERGRID: 56, TATAPOWER: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; JSWENERGY: 56, POWERGRID: 56, TATAPOWER: 55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +6 = 58</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 56</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,36 +2121,36 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>405.9</v>
+        <v>268</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>393 - 419</t>
+          <t>261 - 275</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.3%)</t>
+          <t>Below 200-DMA (-6.2%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>14611</v>
+        <v>36977</v>
       </c>
       <c r="W7" t="n">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>12.4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 58; HAL: 62, POLYCAB: 56, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, JSWENERGY: 56, TATAPOWER: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 56</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,36 +2239,36 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>268</v>
+        <v>405.9</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>261 - 275</t>
+          <t>393 - 418</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.2%)</t>
+          <t>Below 200-DMA (-3.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>35905</v>
+        <v>14611</v>
       </c>
       <c r="W8" t="n">
-        <v>134</v>
+        <v>36</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 63, JSWENERGY: 56, TATAPOWER: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 61, POLYCAB: 56, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +6 · Sector +1 = 54</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H9" t="n">
         <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.3%)</t>
+          <t>Below 200-DMA (-15.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>24273</v>
+        <v>23715</v>
       </c>
       <c r="W9" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="X9" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 48, HINDUNILVR: 48, PATANJALI: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; DABUR: 48, HINDUNILVR: 48, PATANJALI: 45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.3%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.1%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2484,7 +2484,7 @@
         <v>89</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.3%)</t>
+          <t>Below 200-DMA (-3.4%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>26406</v>
+        <v>27232</v>
       </c>
       <c r="W10" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="X10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; TATASTEEL: 49, HINDZINC: 46, SAIL: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, HINDZINC: 45, SAIL: 41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.3%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.4%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +1 = 48</t>
+          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +2 = 49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2599,10 +2599,10 @@
         <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>28973</v>
+        <v>29931</v>
       </c>
       <c r="W11" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="X11" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 48; IOC: 48, OIL: 47, GUJGASLTD: 33</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 49; OIL: 49, IOC: 48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.5%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.5%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +4 = 53</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +5 · Trend/Tech +4 = 52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2707,20 +2707,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="H12" t="n">
         <v>88</v>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.5%)</t>
+          <t>Below 200-DMA (-12.3%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>15451</v>
+        <v>14936</v>
       </c>
       <c r="W12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="X12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 61. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-12.5%) • sector strength 40/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-12.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 48</t>
+          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,13 +2832,13 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1999 - 2130</t>
+          <t>2001 - 2128</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.1%)</t>
+          <t>Below 200-DMA (-9.0%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>18584</v>
+        <v>20649</v>
       </c>
       <c r="W13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X13" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 54, DABUR: 48, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 53, DABUR: 48, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.1%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.0%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -3716,9 +3716,15 @@
       <c r="L5" t="n">
         <v>1.6</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>98</v>
+      </c>
       <c r="P5" t="n">
         <v>135.9</v>
       </c>
@@ -4034,9 +4040,15 @@
       <c r="L9" t="n">
         <v>0.77</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="O9" t="n">
+        <v>62</v>
+      </c>
       <c r="P9" t="n">
         <v>41.4</v>
       </c>
@@ -4109,9 +4121,15 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>88</v>
+      </c>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -4913,9 +4931,15 @@
       <c r="L20" t="n">
         <v>0.48</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-10.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>87</v>
+      </c>
       <c r="P20" t="n">
         <v>24.2</v>
       </c>
@@ -5150,9 +5174,15 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
       <c r="P23" t="n">
         <v>0.1</v>
       </c>
@@ -5306,9 +5336,15 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-64</v>
+      </c>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5381,9 +5417,15 @@
       <c r="L26" t="n">
         <v>-0.73</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-1734</v>
+      </c>
       <c r="P26" t="n">
         <v>-27.5</v>
       </c>
@@ -5774,9 +5816,15 @@
       <c r="L31" t="n">
         <v>-0.92</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-456</v>
+      </c>
       <c r="P31" t="n">
         <v>-47.7</v>
       </c>
@@ -5849,9 +5897,15 @@
       <c r="L32" t="n">
         <v>0.71</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>100</v>
+      </c>
       <c r="P32" t="n">
         <v>82.59999999999999</v>
       </c>
@@ -6410,9 +6464,15 @@
       <c r="L39" t="n">
         <v>-0.23</v>
       </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="M39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-22.2</v>
+      </c>
+      <c r="O39" t="n">
+        <v>-322</v>
+      </c>
       <c r="P39" t="n">
         <v>-19.9</v>
       </c>
@@ -6566,9 +6626,15 @@
       <c r="L41" t="n">
         <v>-0.27</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-702</v>
+      </c>
       <c r="P41" t="n">
         <v>-27.3</v>
       </c>
@@ -6722,9 +6788,15 @@
       <c r="L43" t="n">
         <v>-0.76</v>
       </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="M43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>-642</v>
+      </c>
       <c r="P43" t="n">
         <v>-29.6</v>
       </c>
@@ -7121,9 +7193,15 @@
       <c r="L48" t="n">
         <v>1.05</v>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>98</v>
+      </c>
       <c r="P48" t="n">
         <v>99.5</v>
       </c>
@@ -7277,9 +7355,15 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>55</v>
+      </c>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -7352,9 +7436,15 @@
       <c r="L51" t="n">
         <v>0.2</v>
       </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>3</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="O51" t="n">
+        <v>68</v>
+      </c>
       <c r="P51" t="n">
         <v>8.4</v>
       </c>
@@ -7508,9 +7598,15 @@
       <c r="L53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-38</v>
+      </c>
       <c r="P53" t="n">
         <v>-3.8</v>
       </c>
@@ -7664,9 +7760,15 @@
       <c r="L55" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-243</v>
+      </c>
       <c r="P55" t="n">
         <v>-31</v>
       </c>
@@ -8545,9 +8647,15 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>49</v>
+      </c>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -8863,9 +8971,15 @@
       <c r="L70" t="n">
         <v>0.43</v>
       </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
+      <c r="M70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="N70" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="O70" t="n">
+        <v>61</v>
+      </c>
       <c r="P70" t="n">
         <v>21.9</v>
       </c>
@@ -8938,9 +9052,15 @@
       <c r="L71" t="n">
         <v>0.48</v>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="M71" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>51</v>
+      </c>
       <c r="P71" t="n">
         <v>16.9</v>
       </c>
@@ -9013,9 +9133,15 @@
       <c r="L72" t="n">
         <v>0.17</v>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>29</v>
+      </c>
       <c r="P72" t="n">
         <v>13.3</v>
       </c>
@@ -9898,9 +10024,15 @@
       <c r="L83" t="n">
         <v>0.21</v>
       </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="M83" t="n">
+        <v>8</v>
+      </c>
+      <c r="N83" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="O83" t="n">
+        <v>36</v>
+      </c>
       <c r="P83" t="n">
         <v>12.2</v>
       </c>
@@ -9973,9 +10105,15 @@
       <c r="L84" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>23</v>
+      </c>
       <c r="P84" t="n">
         <v>4.3</v>
       </c>
@@ -10372,9 +10510,15 @@
       <c r="L89" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-153</v>
+      </c>
       <c r="P89" t="n">
         <v>-19.5</v>
       </c>
@@ -10447,8 +10591,12 @@
       <c r="L90" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-12.5</v>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>-38.1</v>
@@ -10522,8 +10670,12 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-12</v>
+      </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10678,9 +10830,15 @@
       <c r="L93" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O93" t="n">
+        <v>100</v>
+      </c>
       <c r="P93" t="n">
         <v>91.7</v>
       </c>
@@ -10834,9 +10992,15 @@
       <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="M95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>82</v>
+      </c>
       <c r="P95" t="n">
         <v>47.5</v>
       </c>
@@ -11152,9 +11316,15 @@
       <c r="L99" t="n">
         <v>0.28</v>
       </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+      <c r="M99" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N99" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="O99" t="n">
+        <v>58</v>
+      </c>
       <c r="P99" t="n">
         <v>11.1</v>
       </c>
@@ -11632,9 +11802,15 @@
       <c r="L105" t="n">
         <v>-0.75</v>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="M105" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O105" t="n">
+        <v>-4582</v>
+      </c>
       <c r="P105" t="n">
         <v>-32</v>
       </c>
@@ -11707,9 +11883,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -11782,9 +11964,15 @@
       <c r="L107" t="n">
         <v>1.65</v>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O107" t="n">
+        <v>99</v>
+      </c>
       <c r="P107" t="n">
         <v>138.8</v>
       </c>
@@ -11857,9 +12045,15 @@
       <c r="L108" t="n">
         <v>1.21</v>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>100</v>
+      </c>
       <c r="P108" t="n">
         <v>121.6</v>
       </c>
@@ -11932,9 +12126,15 @@
       <c r="L109" t="n">
         <v>1.48</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>22</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O109" t="n">
+        <v>99</v>
+      </c>
       <c r="P109" t="n">
         <v>120.4</v>
       </c>
@@ -12898,9 +13098,15 @@
       <c r="L121" t="n">
         <v>0.11</v>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="O121" t="n">
+        <v>15</v>
+      </c>
       <c r="P121" t="n">
         <v>5.8</v>
       </c>
@@ -13054,9 +13260,15 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O123" t="n">
+        <v>86</v>
+      </c>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -13453,9 +13665,15 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>83</v>
+      </c>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -13771,9 +13989,15 @@
       <c r="L132" t="n">
         <v>0.16</v>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-5.2</v>
+      </c>
+      <c r="O132" t="n">
+        <v>100</v>
+      </c>
       <c r="P132" t="n">
         <v>13.5</v>
       </c>
@@ -14089,9 +14313,15 @@
       <c r="L136" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-173</v>
+      </c>
       <c r="P136" t="n">
         <v>-26.4</v>
       </c>
@@ -14245,9 +14475,15 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O138" t="n">
+        <v>100</v>
+      </c>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -14968,9 +15204,15 @@
       <c r="L147" t="n">
         <v>0.49</v>
       </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="M147" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="O147" t="n">
+        <v>50</v>
+      </c>
       <c r="P147" t="n">
         <v>36.9</v>
       </c>
@@ -15124,9 +15366,15 @@
       <c r="L149" t="n">
         <v>0.22</v>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O149" t="n">
+        <v>49</v>
+      </c>
       <c r="P149" t="n">
         <v>16.9</v>
       </c>
@@ -16084,9 +16332,15 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N161" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-46</v>
+      </c>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -16240,9 +16494,15 @@
       <c r="L163" t="n">
         <v>-0.62</v>
       </c>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
+      <c r="M163" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N163" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="O163" t="n">
+        <v>-2292</v>
+      </c>
       <c r="P163" t="n">
         <v>-32.4</v>
       </c>
@@ -16475,9 +16735,15 @@
       <c r="L166" t="n">
         <v>-0.93</v>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N166" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="O166" t="n">
+        <v>-2027</v>
+      </c>
       <c r="P166" t="n">
         <v>-45.9</v>
       </c>
@@ -17435,9 +17701,15 @@
       <c r="L178" t="n">
         <v>0.33</v>
       </c>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="O178" t="n">
+        <v>65</v>
+      </c>
       <c r="P178" t="n">
         <v>21.2</v>
       </c>
@@ -17591,9 +17863,15 @@
       <c r="L180" t="n">
         <v>0.1</v>
       </c>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
+      <c r="M180" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N180" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="O180" t="n">
+        <v>52</v>
+      </c>
       <c r="P180" t="n">
         <v>8</v>
       </c>
@@ -17828,9 +18106,15 @@
       <c r="L183" t="n">
         <v>1.73</v>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>81</v>
+      </c>
       <c r="P183" t="n">
         <v>99.90000000000001</v>
       </c>
@@ -18146,9 +18430,15 @@
       <c r="L187" t="n">
         <v>0.24</v>
       </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
+      <c r="M187" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="N187" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O187" t="n">
+        <v>25</v>
+      </c>
       <c r="P187" t="n">
         <v>12.6</v>
       </c>
@@ -18464,9 +18754,15 @@
       <c r="L191" t="n">
         <v>0.1</v>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="O191" t="n">
+        <v>11</v>
+      </c>
       <c r="P191" t="n">
         <v>6.4</v>
       </c>
@@ -18539,9 +18835,15 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>11</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>9</v>
+      </c>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -19019,9 +19321,15 @@
       <c r="L198" t="n">
         <v>0.27</v>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="O198" t="n">
+        <v>20</v>
+      </c>
       <c r="P198" t="n">
         <v>14.2</v>
       </c>
@@ -19094,9 +19402,15 @@
       <c r="L199" t="n">
         <v>0.2</v>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-10.3</v>
+      </c>
+      <c r="O199" t="n">
+        <v>100</v>
+      </c>
       <c r="P199" t="n">
         <v>12</v>
       </c>
@@ -19169,9 +19483,15 @@
       <c r="L200" t="n">
         <v>0.14</v>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
+      <c r="M200" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O200" t="n">
+        <v>100</v>
+      </c>
       <c r="P200" t="n">
         <v>11</v>
       </c>
@@ -19649,9 +19969,15 @@
       <c r="L206" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N206" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="O206" t="n">
+        <v>-3098</v>
+      </c>
       <c r="P206" t="n">
         <v>-21.3</v>
       </c>
@@ -19803,9 +20129,15 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-413</v>
+      </c>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -19959,9 +20291,15 @@
       <c r="L210" t="n">
         <v>-1.35</v>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
+      <c r="M210" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N210" t="n">
+        <v>-26</v>
+      </c>
+      <c r="O210" t="n">
+        <v>-1247</v>
+      </c>
       <c r="P210" t="n">
         <v>-66.2</v>
       </c>
@@ -20034,8 +20372,12 @@
       <c r="L211" t="n">
         <v>-2.56</v>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-26.2</v>
+      </c>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="n">
         <v>-70.09999999999999</v>
@@ -20271,9 +20613,15 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
+      <c r="M214" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O214" t="n">
+        <v>100</v>
+      </c>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -20589,9 +20937,15 @@
       <c r="L218" t="n">
         <v>0.63</v>
       </c>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
+      <c r="M218" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="N218" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O218" t="n">
+        <v>100</v>
+      </c>
       <c r="P218" t="n">
         <v>45.9</v>
       </c>
@@ -21302,9 +21656,15 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
+      <c r="M227" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>89</v>
+      </c>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -21458,9 +21818,15 @@
       <c r="L229" t="n">
         <v>0.53</v>
       </c>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
+      <c r="M229" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N229" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="O229" t="n">
+        <v>100</v>
+      </c>
       <c r="P229" t="n">
         <v>30.4</v>
       </c>
@@ -21857,9 +22223,15 @@
       <c r="L234" t="n">
         <v>0.32</v>
       </c>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N234" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="O234" t="n">
+        <v>86</v>
+      </c>
       <c r="P234" t="n">
         <v>19.7</v>
       </c>
@@ -21932,9 +22304,15 @@
       <c r="L235" t="n">
         <v>0.06</v>
       </c>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
+      <c r="M235" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N235" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="O235" t="n">
+        <v>49</v>
+      </c>
       <c r="P235" t="n">
         <v>3.2</v>
       </c>
@@ -22169,9 +22547,15 @@
       <c r="L238" t="n">
         <v>-0.18</v>
       </c>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N238" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="O238" t="n">
+        <v>-258</v>
+      </c>
       <c r="P238" t="n">
         <v>-13.7</v>
       </c>
@@ -22649,9 +23033,15 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N244" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="O244" t="n">
+        <v>83</v>
+      </c>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -22805,9 +23195,15 @@
       <c r="L246" t="n">
         <v>0.34</v>
       </c>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="N246" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="O246" t="n">
+        <v>59</v>
+      </c>
       <c r="P246" t="n">
         <v>23</v>
       </c>
@@ -22880,9 +23276,15 @@
       <c r="L247" t="n">
         <v>0.28</v>
       </c>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
+      <c r="M247" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N247" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="O247" t="n">
+        <v>88</v>
+      </c>
       <c r="P247" t="n">
         <v>19.5</v>
       </c>
@@ -23439,8 +23841,12 @@
       <c r="L254" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="n">
+        <v>-8.6</v>
+      </c>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="n">
         <v>-19</v>
@@ -23593,8 +23999,12 @@
       <c r="L256" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="n">
+        <v>-10.6</v>
+      </c>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
         <v>-36.1</v>
@@ -23992,9 +24402,15 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
+      <c r="M261" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N261" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O261" t="n">
+        <v>38</v>
+      </c>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -24715,9 +25131,15 @@
       <c r="L270" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
+      <c r="M270" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N270" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O270" t="n">
+        <v>-255</v>
+      </c>
       <c r="P270" t="n">
         <v>-30.7</v>
       </c>
@@ -25276,9 +25698,15 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N277" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="O277" t="n">
+        <v>45</v>
+      </c>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25432,9 +25860,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -25831,9 +26265,15 @@
       <c r="L284" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
+      <c r="M284" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="O284" t="n">
+        <v>-1163</v>
+      </c>
       <c r="P284" t="n">
         <v>-37.6</v>
       </c>
@@ -26447,7 +26887,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-3.3</v>
+        <v>-2.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26489,7 +26929,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.9</v>
+        <v>-10.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26531,7 +26971,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-14.1</v>
+        <v>-13.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26573,7 +27013,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-8.699999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26615,7 +27055,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-5</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26657,7 +27097,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-11.7</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -26699,7 +27139,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-2.7</v>
+        <v>-3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -26741,7 +27181,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -26783,7 +27223,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-3.1</v>
+        <v>-2.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -26825,7 +27265,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-4.2</v>
+        <v>-3.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -26867,7 +27307,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-2.6</v>
+        <v>-2.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -26909,7 +27349,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-3.7</v>
+        <v>-3.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -26951,7 +27391,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.3</v>
+        <v>-4.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -26993,7 +27433,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-5.5</v>
+        <v>-7.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -27035,7 +27475,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -27077,7 +27517,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.1</v>
+        <v>-3.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -27119,7 +27559,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27203,7 +27643,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-13</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27283,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27298,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27328,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27343,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27358,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27388,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C9" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (48)</t>
+          <t>ONGC (48)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-12  /  2026-08-12</t>
+          <t>2026-08-13  /  2026-08-12</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
         <v>80</v>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; JSWENERGY: 56, POWERGRID: 56, TATAPOWER: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; JSWENERGY: 56, POWERGRID: 56, TATAPOWER: 56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
         <v>97</v>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, JSWENERGY: 56, TATAPOWER: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, JSWENERGY: 56, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 53</t>
+          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +2 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2366,7 +2366,7 @@
         <v>99</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; DABUR: 48, HINDUNILVR: 48, PATANJALI: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 49, HINDUNILVR: 49, PATANJALI: 46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.1%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.1%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +2 = 49</t>
+          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2602,7 +2602,7 @@
         <v>81</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 49; OIL: 49, IOC: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 48; OIL: 49, IOC: 47, GUJGASLTD: 33. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.5%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.5%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 48</t>
+          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +2 = 49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2838,7 +2838,7 @@
         <v>86</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 53, DABUR: 48, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 54, DABUR: 49, PATANJALI: 46. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.0%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.0%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ONGC (48)</t>
+          <t>HINDUNILVR (48)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13  /  2026-08-12</t>
+          <t>2026-08-13  /  2026-08-13</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1429.6</v>
+        <v>1431.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1390 - 1469</t>
+          <t>1392 - 1471</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+5.8%)</t>
+          <t>Above 200-DMA (+6.0%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>18585</v>
+        <v>18612</v>
       </c>
       <c r="W2" t="n">
         <v>13</v>
       </c>
       <c r="X2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 73, YESBANK: 62, BAJFINANCE: 60</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 71, YESBANK: 62, PNB: 61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.8%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.0%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +17 · Regime +9 · Sector +7 = 74</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +16 · Regime +9 · Sector +7 = 73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1890 - 1994</t>
+          <t>1892 - 1996</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.8%)</t>
+          <t>Above 200-DMA (+8.9%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>25246</v>
+        <v>25272</v>
       </c>
       <c r="W3" t="n">
         <v>13</v>
       </c>
       <c r="X3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 74; CIPLA: 71, LUPIN: 69, ZYDUSLIFE: 69</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 73; CIPLA: 71, LUPIN: 69, ZYDUSLIFE: 68</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.8%) • sector strength 67/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.9%) • sector strength 67/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1770,7 @@
         <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H4" t="n">
         <v>95</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2278.9</v>
+        <v>2281</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2219 - 2338</t>
+          <t>2222 - 2340</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>27347</v>
+        <v>25091</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 74, CIPLA: 71, ZYDUSLIFE: 69. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 73, CIPLA: 71, ZYDUSLIFE: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1891,7 +1891,7 @@
         <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I5" t="n">
         <v>80</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1685.8</v>
+        <v>1701.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1632 - 1740</t>
+          <t>1647 - 1756</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+14.1%)</t>
+          <t>Above 200-DMA (+15.1%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>18544</v>
+        <v>18716</v>
       </c>
       <c r="W5" t="n">
         <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+14.1%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+15.1%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,11 +1985,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +3 · Trend/Tech +2 = 63</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,14 +1999,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
         <v>96</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>338.5</v>
+        <v>339.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>330 - 347</t>
+          <t>331 - 348</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.3%)</t>
+          <t>Below 200-DMA (-5.0%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>36214</v>
+        <v>34963</v>
       </c>
       <c r="W6" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="X6" t="n">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; JSWENERGY: 56, POWERGRID: 56, TATAPOWER: 56</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; JSWENERGY: 58, POWERGRID: 57, TATAPOWER: 55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.3%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.0%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 56</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,10 +2124,10 @@
         <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I7" t="n">
         <v>27</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>268</v>
+        <v>269.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>261 - 275</t>
+          <t>263 - 276</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.2%)</t>
+          <t>Below 200-DMA (-5.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>36977</v>
+        <v>42034</v>
       </c>
       <c r="W7" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="X7" t="n">
-        <v>12.4</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, JSWENERGY: 56, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, JSWENERGY: 58, TATAPOWER: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.2%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.6%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
         <v>84</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>405.9</v>
+        <v>405.7</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>14611</v>
+        <v>14200</v>
       </c>
       <c r="W8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 61, POLYCAB: 56, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 61, POLYCAB: 54, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +2 = 54</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2363,10 +2363,10 @@
         <v>27</v>
       </c>
       <c r="H9" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>279</v>
+        <v>276.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>272 - 286</t>
+          <t>269 - 283</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.1%)</t>
+          <t>Below 200-DMA (-15.8%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23715</v>
+        <v>23197</v>
       </c>
       <c r="W9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 54; DABUR: 49, HINDUNILVR: 49, PATANJALI: 46</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 48, HINDUNILVR: 48, PATANJALI: 45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.1%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.8%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
         <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
         <v>89</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>412.6</v>
+        <v>409.3</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>400 - 425</t>
+          <t>397 - 421</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.4%)</t>
+          <t>Below 200-DMA (-4.2%)</t>
         </is>
       </c>
       <c r="S10" t="n">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>27232</v>
+        <v>28651</v>
       </c>
       <c r="W10" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="X10" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, HINDZINC: 45, SAIL: 41</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, HINDZINC: 45, SAIL: 40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-3.4%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.2%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +1 = 48</t>
+          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +2 = 49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2602,7 +2602,7 @@
         <v>81</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>239.4</v>
+        <v>239.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.5%)</t>
+          <t>Below 200-DMA (-7.6%)</t>
         </is>
       </c>
       <c r="S11" t="n">
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>29931</v>
+        <v>29642</v>
       </c>
       <c r="W11" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X11" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 48; OIL: 49, IOC: 47, GUJGASLTD: 33. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 49; IOC: 48, OIL: 48</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.5%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.6%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +5 · Trend/Tech +4 = 52</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 54</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2707,14 +2707,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H12" t="n">
         <v>88</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>515</v>
+        <v>513.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>499 - 531</t>
+          <t>498 - 529</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.3%)</t>
+          <t>Below 200-DMA (-12.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14936</v>
+        <v>14379</v>
       </c>
       <c r="W12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X12" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 61. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-12.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-12.4%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +2 = 49</t>
+          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,13 +2832,13 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2064.9</v>
+        <v>2063</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2001 - 2128</t>
+          <t>2000 - 2126</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>20649</v>
+        <v>18567</v>
       </c>
       <c r="W13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 54, DABUR: 49, PATANJALI: 46. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 52, DABUR: 48, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.0%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.0%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27813,7 +27813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27828,7 +27828,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27843,7 +27843,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="C10" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="History" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Market" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="About" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TODAY" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Today's Recommendations" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Backtest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trade Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holding Options" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-13  /  2026-08-13</t>
+          <t>2026-08-14  /  2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>82</v>
       </c>
       <c r="H5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
         <v>80</v>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; JSWENERGY: 58, POWERGRID: 57, TATAPOWER: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; JSWENERGY: 58, POWERGRID: 57, TATAPOWER: 56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, JSWENERGY: 58, TATAPOWER: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, JSWENERGY: 58, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 49; IOC: 48, OIL: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 49; OIL: 49, IOC: 48, GUJGASLTD: 34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (77)</t>
+          <t>ICICIBANK (76)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (48)</t>
+          <t>HINDUNILVR (49)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-14  /  2026-08-13</t>
+          <t>2026-08-17  /  2026-08-14</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +7 = 77</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1431.7</v>
+        <v>1417</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1392 - 1471</t>
+          <t>1378 - 1456</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.0%)</t>
+          <t>Above 200-DMA (+4.8%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>18612</v>
+        <v>17004</v>
       </c>
       <c r="W2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X2" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 77; SBIN: 71, YESBANK: 62, PNB: 61</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, YESBANK: 63, PNB: 62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+6.0%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +16 · Regime +9 · Sector +7 = 73</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +14 · Regime +9 · Sector +6 = 70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,13 +1652,13 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1944</v>
+        <v>1930</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1892 - 1996</t>
+          <t>1878 - 1982</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1692,15 +1692,15 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.9%)</t>
+          <t>Above 200-DMA (+8.0%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,11 +1709,11 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>25272</v>
+        <v>25090</v>
       </c>
       <c r="W3" t="n">
         <v>13</v>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 73; CIPLA: 71, LUPIN: 69, ZYDUSLIFE: 68</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 70; CIPLA: 70, ZYDUSLIFE: 67, LUPIN: 59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.9%) • sector strength 67/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.0%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Trend/Tech +14 · Regime +9 · Sector +7 = 69</t>
+          <t>Risk/Vol +20 · Trend/Tech +16 · Historical +14 · Regime +9 · Sector +7 = 66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="H4" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="I4" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2281</v>
+        <v>1693</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2222 - 2340</t>
+          <t>1639 - 1747</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+1.9%)</t>
+          <t>Above 200-DMA (+14.4%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>25091</v>
+        <v>18623</v>
       </c>
       <c r="W4" t="n">
         <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>6.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,32 +1851,32 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 69; SUNPHARMA: 73, CIPLA: 71, ZYDUSLIFE: 68. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 66; CHAMBLFERT: 53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+1.9%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+14.4%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +16 · Historical +14 · Regime +9 · Sector +8 = 67</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1885,58 +1885,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1701.5</v>
+        <v>340</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1647 - 1756</t>
+          <t>331 - 349</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+15.1%)</t>
+          <t>Below 200-DMA (-4.8%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>18716</v>
+        <v>35020</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="X5" t="n">
-        <v>6.5</v>
+        <v>11.8</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 67; CHAMBLFERT: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; JSWENERGY: 58, POWERGRID: 57, TATAPOWER: 56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+15.1%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.8%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -1985,16 +1985,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Sector +3 · Trend/Tech +2 = 63</t>
+          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2003,36 +2003,36 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>339.5</v>
+        <v>2235</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>331 - 348</t>
+          <t>2176 - 2294</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.0%)</t>
+          <t>Below 200-DMA (-0.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>34963</v>
+        <v>24585</v>
       </c>
       <c r="W6" t="n">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="X6" t="n">
-        <v>11.8</v>
+        <v>8.9</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; JSWENERGY: 58, POWERGRID: 57, TATAPOWER: 56</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; CIPLA: 70, SUNPHARMA: 70, ZYDUSLIFE: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.0%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.2%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 57</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +7 = 59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2121,36 +2121,36 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>269.5</v>
+        <v>410.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>263 - 276</t>
+          <t>398 - 423</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.6%)</t>
+          <t>Below 200-DMA (-2.1%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>42034</v>
+        <v>20540</v>
       </c>
       <c r="W7" t="n">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>6.9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, JSWENERGY: 58, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 59; HAL: 64, POLYCAB: 57, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.6%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.1%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,54 +2221,54 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>57</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 57</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>56</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +6 · Sector +5 = 56</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>50</v>
-      </c>
       <c r="G8" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>405.7</v>
+        <v>266</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>393 - 418</t>
+          <t>260 - 272</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.3%)</t>
+          <t>Below 200-DMA (-6.8%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>14200</v>
+        <v>41504</v>
       </c>
       <c r="W8" t="n">
-        <v>35</v>
+        <v>156</v>
       </c>
       <c r="X8" t="n">
-        <v>4.8</v>
+        <v>13.8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 56; HAL: 61, POLYCAB: 54, KEI: 51. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 64, JSWENERGY: 58, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-3.3%) • sector strength 53/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.8%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>276.1</v>
+        <v>278.2</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>269 - 283</t>
+          <t>272 - 285</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.8%)</t>
+          <t>Below 200-DMA (-15.0%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,11 +2417,11 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23197</v>
+        <v>23369</v>
       </c>
       <c r="W9" t="n">
         <v>84</v>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 48, HINDUNILVR: 48, PATANJALI: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; HINDUNILVR: 49, DABUR: 46, PATANJALI: 45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.8%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.0%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +2 = 51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H10" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>409.3</v>
+        <v>236.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>397 - 421</t>
+          <t>229 - 244</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.2%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>28651</v>
+        <v>29314</v>
       </c>
       <c r="W10" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="X10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, HINDZINC: 45, SAIL: 40</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 49, OIL: 46, GUJGASLTD: 34</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.2%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.6%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +2 = 49</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2593,36 +2593,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>239.1</v>
+        <v>407.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>232 - 247</t>
+          <t>395 - 419</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.6%)</t>
+          <t>Below 200-DMA (-4.7%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>29642</v>
+        <v>28497</v>
       </c>
       <c r="W11" t="n">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="X11" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 49; OIL: 49, IOC: 48, GUJGASLTD: 34</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 42, HINDZINC: 39</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.6%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.7%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 54</t>
+          <t>Risk/Vol +21 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +3 = 51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2714,13 +2714,13 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H12" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I12" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>513.5</v>
+        <v>497.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>498 - 529</t>
+          <t>482 - 513</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-12.4%)</t>
+          <t>Below 200-DMA (-15.0%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,14 +2771,14 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14379</v>
+        <v>14428</v>
       </c>
       <c r="W12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X12" t="n">
         <v>4.9</v>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 54; DELHIVERY: 60. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-12.4%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-15.0%) • sector strength 33/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 48</t>
+          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2835,7 +2835,7 @@
         <v>18</v>
       </c>
       <c r="H13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" t="n">
         <v>13</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2063</v>
+        <v>2077</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2000 - 2126</t>
+          <t>2013 - 2141</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.0%)</t>
+          <t>Below 200-DMA (-8.2%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>18567</v>
+        <v>14539</v>
       </c>
       <c r="W13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 52, DABUR: 48, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 52, DABUR: 46, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.0%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-8.2%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27793,12 +27793,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27823,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27838,7 +27838,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (49)</t>
+          <t>HINDUNILVR (47)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-17  /  2026-08-14</t>
+          <t>2026-08-18  /  2026-08-18</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1378 - 1456</t>
+          <t>1373 - 1451</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+4.8%)</t>
+          <t>Above 200-DMA (+4.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>17004</v>
+        <v>16944</v>
       </c>
       <c r="W2" t="n">
         <v>12</v>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, YESBANK: 63, PNB: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, PNB: 65, YESBANK: 62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.4%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +14 · Regime +9 · Sector +6 = 70</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +13 · Regime +9 · Sector +6 = 69</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1930</v>
+        <v>1875.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1878 - 1982</t>
+          <t>1824 - 1926</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+8.0%)</t>
+          <t>Above 200-DMA (+4.8%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>25090</v>
+        <v>24376</v>
       </c>
       <c r="W3" t="n">
         <v>13</v>
       </c>
       <c r="X3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 70; CIPLA: 70, ZYDUSLIFE: 67, LUPIN: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 69; CIPLA: 67, ZYDUSLIFE: 65, LUPIN: 59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+8.0%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+4.8%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +16 · Historical +14 · Regime +9 · Sector +7 = 66</t>
+          <t>Risk/Vol +20 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 68</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1770,13 +1770,13 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H4" t="n">
         <v>81</v>
       </c>
       <c r="I4" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1693</v>
+        <v>1674</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1639 - 1747</t>
+          <t>1621 - 1727</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1810,15 +1810,15 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+14.4%)</t>
+          <t>Above 200-DMA (+13.0%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,14 +1827,14 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>18623</v>
+        <v>20088</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X4" t="n">
         <v>6.7</v>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 66; CHAMBLFERT: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 51</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+14.4%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+13.0%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>340</v>
+        <v>337.1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>331 - 349</t>
+          <t>329 - 346</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.8%)</t>
+          <t>Below 200-DMA (-5.6%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>35020</v>
+        <v>35058</v>
       </c>
       <c r="W5" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="X5" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; JSWENERGY: 58, POWERGRID: 57, TATAPOWER: 56</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 56, JSWENERGY: 55, TATAPOWER: 54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.8%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.6%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
         <v>95</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2176 - 2294</t>
+          <t>2173 - 2291</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.2%)</t>
+          <t>Below 200-DMA (-0.5%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,11 +2063,11 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>24585</v>
+        <v>24552</v>
       </c>
       <c r="W6" t="n">
         <v>11</v>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; CIPLA: 70, SUNPHARMA: 70, ZYDUSLIFE: 67. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 69, CIPLA: 67, ZYDUSLIFE: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.2%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.5%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +7 = 59</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,20 +2117,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I7" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>410.8</v>
+        <v>412</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>398 - 423</t>
+          <t>399 - 425</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.1%)</t>
+          <t>Below 200-DMA (-1.8%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>20540</v>
+        <v>20600</v>
       </c>
       <c r="W7" t="n">
         <v>50</v>
       </c>
       <c r="X7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 59; HAL: 64, POLYCAB: 57, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 58; HAL: 65, POLYCAB: 56, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.1%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-1.8%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 57</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +2 = 56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2242,13 +2242,13 @@
         <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
         <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>260 - 272</t>
+          <t>262 - 274</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.8%)</t>
+          <t>Below 200-DMA (-6.0%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,17 +2299,17 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>41504</v>
+        <v>41004</v>
       </c>
       <c r="W8" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="X8" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 64, JSWENERGY: 58, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 63, JSWENERGY: 55, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.8%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.0%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +5 · Sector +1 = 52</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +3 = 54</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
+        <v>21</v>
+      </c>
+      <c r="H9" t="n">
+        <v>88</v>
+      </c>
+      <c r="I9" t="n">
         <v>27</v>
-      </c>
-      <c r="H9" t="n">
-        <v>97</v>
-      </c>
-      <c r="I9" t="n">
-        <v>13</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>278.2</v>
+        <v>239.5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>272 - 285</t>
+          <t>232 - 247</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.0%)</t>
+          <t>Below 200-DMA (-7.4%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>23369</v>
+        <v>30416</v>
       </c>
       <c r="W9" t="n">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="X9" t="n">
-        <v>7.8</v>
+        <v>10.2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; HINDUNILVR: 49, DABUR: 46, PATANJALI: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 54; IOC: 50, OIL: 50</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.0%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.4%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2457,54 +2457,54 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>52</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +1 = 52</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>51</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Risk/Vol +20 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +2 = 51</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>53</v>
-      </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>236.4</v>
+        <v>406.9</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>229 - 244</t>
+          <t>395 - 419</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Below 200-DMA (-4.8%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>29314</v>
+        <v>28076</v>
       </c>
       <c r="W10" t="n">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="X10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; IOC: 49, OIL: 46, GUJGASLTD: 34</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 52; TATASTEEL: 48, SAIL: 41, HINDZINC: 39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.6%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.8%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -2609,42 +2609,42 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>407.1</v>
+        <v>270</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>395 - 419</t>
+          <t>264 - 276</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.7%)</t>
+          <t>Below 200-DMA (-17.1%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>28497</v>
+        <v>23760</v>
       </c>
       <c r="W11" t="n">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="X11" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 47, SAIL: 42, HINDZINC: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; DABUR: 47, HINDUNILVR: 47, PATANJALI: 45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.7%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +3 = 51</t>
+          <t>Risk/Vol +20 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2717,10 +2717,10 @@
         <v>29</v>
       </c>
       <c r="H12" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>497.5</v>
+        <v>493</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>482 - 513</t>
+          <t>478 - 508</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.0%)</t>
+          <t>Below 200-DMA (-15.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14428</v>
+        <v>14298</v>
       </c>
       <c r="W12" t="n">
         <v>29</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-15.0%) • sector strength 33/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-15.4%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 49</t>
+          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 47</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,13 +2832,13 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2077</v>
+        <v>2035</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2013 - 2141</t>
+          <t>1973 - 2097</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2872,15 +2872,15 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.2%)</t>
+          <t>Below 200-DMA (-9.9%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,11 +2889,11 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>14539</v>
+        <v>14245</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 52, DABUR: 46, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 47; ITC: 50, DABUR: 47, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-8.2%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.9%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="C7" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (47)</t>
+          <t>HINDUNILVR (48)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-18  /  2026-08-18</t>
+          <t>2026-08-19  /  2026-08-18</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 56, JSWENERGY: 55, TATAPOWER: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 57, JSWENERGY: 56, TATAPOWER: 56</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.6%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.6%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
         <v>95</v>
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +2 = 56</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2248,7 +2248,7 @@
         <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 63, JSWENERGY: 55, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 64, JSWENERGY: 56, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.0%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.0%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +3 = 54</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +2 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2360,13 +2360,13 @@
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H9" t="n">
         <v>88</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 54; IOC: 50, OIL: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; OIL: 50, IOC: 49, GUJGASLTD: 34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.4%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.4%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 52; TATASTEEL: 48, SAIL: 41, HINDZINC: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 52; TATASTEEL: 48, SAIL: 42, HINDZINC: 39</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -2596,7 +2596,7 @@
         <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
         <v>97</v>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; DABUR: 47, HINDUNILVR: 47, PATANJALI: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; HINDUNILVR: 48, DABUR: 47, PATANJALI: 45</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 47</t>
+          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,7 +2832,7 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H13" t="n">
         <v>84</v>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 47; ITC: 50, DABUR: 47, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 50, DABUR: 47, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (76)</t>
+          <t>ICICIBANK (74)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (48)</t>
+          <t>HINDUNILVR (49)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 12-stock risk-managed portfolio</t>
+          <t>Hold a 11-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-19  /  2026-08-18</t>
+          <t>2026-08-20  /  2026-08-19</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 76</t>
+          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +7 = 74</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1537,10 +1537,10 @@
         <v>81</v>
       </c>
       <c r="H2" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="I2" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1412</v>
+        <v>1402</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1373 - 1451</t>
+          <t>1363 - 1441</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+4.4%)</t>
+          <t>Above 200-DMA (+3.7%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>16944</v>
+        <v>23834</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X2" t="n">
-        <v>5.9</v>
+        <v>8.1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, PNB: 65, YESBANK: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 74; SBIN: 73, PNB: 63, YESBANK: 62</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.4%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.7%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,11 +1631,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +13 · Regime +9 · Sector +6 = 69</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +14 · Regime +9 · Sector +6 = 70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1652,13 +1652,13 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I3" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1875.1</v>
+        <v>1900</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1824 - 1926</t>
+          <t>1848 - 1952</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+4.8%)</t>
+          <t>Above 200-DMA (+6.1%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>24376</v>
+        <v>22800</v>
       </c>
       <c r="W3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X3" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,32 +1733,32 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 69; CIPLA: 67, ZYDUSLIFE: 65, LUPIN: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 70; LUPIN: 59, DRREDDY: 50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+4.8%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.1%) • sector strength 57/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 68</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1767,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="I4" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1674</v>
+        <v>336.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1621 - 1727</t>
+          <t>328 - 345</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+13.0%)</t>
+          <t>Below 200-DMA (-5.8%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>20088</v>
+        <v>22549</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="X4" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 55, TATAPOWER: 54, NHPC: 53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+13.0%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.8%) • sector strength 21/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -1867,54 +1867,54 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
+          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>337.1</v>
+        <v>2225</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>329 - 346</t>
+          <t>2166 - 2284</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.6%)</t>
+          <t>Below 200-DMA (-0.9%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>35058</v>
+        <v>28925</v>
       </c>
       <c r="W5" t="n">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="X5" t="n">
-        <v>11.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 57, JSWENERGY: 56, TATAPOWER: 56</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 70, DRREDDY: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.6%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.9%) • sector strength 57/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +8 · Trend/Tech +6 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2006,33 +2006,33 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2232</v>
+        <v>409.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2173 - 2291</t>
+          <t>397 - 422</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.5%)</t>
+          <t>Below 200-DMA (-2.5%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>24552</v>
+        <v>28644</v>
       </c>
       <c r="W6" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="X6" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 69, CIPLA: 67, ZYDUSLIFE: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 59; HAL: 66, KEI: 54, MAZDOCK: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.5%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.5%) • sector strength 79/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 58</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +2 = 55</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="I7" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>412</v>
+        <v>263.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>399 - 425</t>
+          <t>257 - 270</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.8%)</t>
+          <t>Below 200-DMA (-7.6%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>20600</v>
+        <v>25032</v>
       </c>
       <c r="W7" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="X7" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 58; HAL: 65, POLYCAB: 56, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 55; NTPC: 63, TATAPOWER: 54, NHPC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-1.8%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 21/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 57</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +3 = 52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,58 +2239,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>262 - 274</t>
+          <t>261 - 273</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.0%)</t>
+          <t>Below 200-DMA (-17.8%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>41004</v>
+        <v>32046</v>
       </c>
       <c r="W8" t="n">
-        <v>153</v>
+        <v>120</v>
       </c>
       <c r="X8" t="n">
-        <v>13.7</v>
+        <v>10.7</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 64, JSWENERGY: 56, TATAPOWER: 56. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 49, HINDUNILVR: 49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-6.0%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.8%) • sector strength 29/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +2 = 53</t>
+          <t>Risk/Vol +21 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +1 = 51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2363,10 +2363,10 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>239.5</v>
+        <v>238</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>232 - 247</t>
+          <t>231 - 245</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.4%)</t>
+          <t>Below 200-DMA (-7.9%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>30416</v>
+        <v>35462</v>
       </c>
       <c r="W9" t="n">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="X9" t="n">
-        <v>10.2</v>
+        <v>11.9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; OIL: 50, IOC: 49, GUJGASLTD: 34</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; OIL: 48, IOC: 46, GUJGASLTD: 33</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.4%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.9%) • sector strength 14/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +1 = 52</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2478,13 +2478,13 @@
         <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H10" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
@@ -2500,11 +2500,11 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>406.9</v>
+        <v>400</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>395 - 419</t>
+          <t>388 - 412</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.8%)</t>
+          <t>Below 200-DMA (-6.4%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>28076</v>
+        <v>36800</v>
       </c>
       <c r="W10" t="n">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="X10" t="n">
-        <v>9.4</v>
+        <v>12.4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -2559,92 +2559,92 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 52; TATASTEEL: 48, SAIL: 42, HINDZINC: 39</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 49, SAIL: 43, HINDZINC: 40</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-4.8%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.4%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>52</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Risk/Vol +20 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 52</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G11" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" t="n">
+        <v>81</v>
+      </c>
+      <c r="I11" t="n">
         <v>50</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>44</v>
-      </c>
-      <c r="G11" t="n">
-        <v>14</v>
-      </c>
-      <c r="H11" t="n">
-        <v>97</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>270</v>
+        <v>488.4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>264 - 276</t>
+          <t>473 - 503</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.1%)</t>
+          <t>Below 200-DMA (-16.1%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>23760</v>
+        <v>20511</v>
       </c>
       <c r="W11" t="n">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; HINDUNILVR: 48, DABUR: 47, PATANJALI: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.1%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.1%) • sector strength 50/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 52</t>
+          <t>Risk/Vol +20 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +3 = 49</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2711,36 +2711,36 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H12" t="n">
         <v>82</v>
       </c>
       <c r="I12" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>493</v>
+        <v>2020.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>478 - 508</t>
+          <t>1959 - 2082</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2754,15 +2754,15 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.4%)</t>
+          <t>Below 200-DMA (-10.4%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>14298</v>
+        <v>18186</v>
       </c>
       <c r="W12" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2795,130 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 52, DABUR: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-15.4%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>48</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 48</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Risk/Vol</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>42</v>
-      </c>
-      <c r="G13" t="n">
-        <v>18</v>
-      </c>
-      <c r="H13" t="n">
-        <v>84</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" t="n">
-        <v>60</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>2035</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>1973 - 2097</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>65</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-9.9%)</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>35</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2 months (2M)</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>14245</v>
-      </c>
-      <c r="W13" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Fundamentals · Earnings · News · Flows</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 50, DABUR: 47, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.9%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.4%) • sector strength 29/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -3473,15 +3355,9 @@
       <c r="L2" t="n">
         <v>4.34</v>
       </c>
-      <c r="M2" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>100</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>200.3</v>
       </c>
@@ -3554,15 +3430,9 @@
       <c r="L3" t="n">
         <v>2.12</v>
       </c>
-      <c r="M3" t="n">
-        <v>38</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>81</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>194.1</v>
       </c>
@@ -3716,15 +3586,9 @@
       <c r="L5" t="n">
         <v>1.6</v>
       </c>
-      <c r="M5" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O5" t="n">
-        <v>98</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>135.9</v>
       </c>
@@ -3959,15 +3823,9 @@
       <c r="L8" t="n">
         <v>0.47</v>
       </c>
-      <c r="M8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>88</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>54.2</v>
       </c>
@@ -4202,15 +4060,9 @@
       <c r="L11" t="n">
         <v>0.49</v>
       </c>
-      <c r="M11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-9.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>92</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>29.9</v>
       </c>
@@ -4526,15 +4378,9 @@
       <c r="L15" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="M15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-13.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-39</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>-6.6</v>
       </c>
@@ -4607,15 +4453,9 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-9.1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-331</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -5012,15 +4852,9 @@
       <c r="L21" t="n">
         <v>0.14</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-8.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>67</v>
-      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5816,15 +5650,9 @@
       <c r="L31" t="n">
         <v>-0.92</v>
       </c>
-      <c r="M31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="O31" t="n">
-        <v>-456</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
         <v>-47.7</v>
       </c>
@@ -5897,15 +5725,9 @@
       <c r="L32" t="n">
         <v>0.71</v>
       </c>
-      <c r="M32" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="O32" t="n">
-        <v>100</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
         <v>82.59999999999999</v>
       </c>
@@ -6140,15 +5962,9 @@
       <c r="L35" t="n">
         <v>0.12</v>
       </c>
-      <c r="M35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="O35" t="n">
-        <v>12</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
         <v>5.6</v>
       </c>
@@ -6626,15 +6442,9 @@
       <c r="L41" t="n">
         <v>-0.27</v>
       </c>
-      <c r="M41" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-19.4</v>
-      </c>
-      <c r="O41" t="n">
-        <v>-702</v>
-      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
         <v>-27.3</v>
       </c>
@@ -6707,15 +6517,9 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>-157</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -7112,15 +6916,9 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>97</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -7193,15 +6991,9 @@
       <c r="L48" t="n">
         <v>1.05</v>
       </c>
-      <c r="M48" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="O48" t="n">
-        <v>98</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>99.5</v>
       </c>
@@ -7355,15 +7147,9 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>55</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -7598,15 +7384,9 @@
       <c r="L53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="M53" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-38</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
         <v>-3.8</v>
       </c>
@@ -7760,15 +7540,9 @@
       <c r="L55" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N55" t="n">
-        <v>-18.1</v>
-      </c>
-      <c r="O55" t="n">
-        <v>-243</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
         <v>-31</v>
       </c>
@@ -8566,15 +8340,9 @@
       <c r="L65" t="n">
         <v>1.25</v>
       </c>
-      <c r="M65" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="N65" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" t="n">
-        <v>66</v>
-      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="n">
         <v>67.2</v>
       </c>
@@ -8647,15 +8415,9 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="N66" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" t="n">
-        <v>49</v>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -8809,15 +8571,9 @@
       <c r="L68" t="n">
         <v>0.35</v>
       </c>
-      <c r="M68" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="N68" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" t="n">
-        <v>46</v>
-      </c>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="n">
         <v>51</v>
       </c>
@@ -9052,15 +8808,9 @@
       <c r="L71" t="n">
         <v>0.48</v>
       </c>
-      <c r="M71" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="N71" t="n">
-        <v>-5.5</v>
-      </c>
-      <c r="O71" t="n">
-        <v>51</v>
-      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" t="n">
         <v>16.9</v>
       </c>
@@ -9133,15 +8883,9 @@
       <c r="L72" t="n">
         <v>0.17</v>
       </c>
-      <c r="M72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N72" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="O72" t="n">
-        <v>29</v>
-      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="n">
         <v>13.3</v>
       </c>
@@ -10105,15 +9849,9 @@
       <c r="L84" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M84" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N84" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>23</v>
-      </c>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
       <c r="P84" t="n">
         <v>4.3</v>
       </c>
@@ -10429,15 +10167,9 @@
       <c r="L88" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M88" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>-6.5</v>
-      </c>
-      <c r="O88" t="n">
-        <v>-128</v>
-      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
       <c r="P88" t="n">
         <v>-19.5</v>
       </c>
@@ -10510,15 +10242,9 @@
       <c r="L89" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M89" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N89" t="n">
-        <v>-6.3</v>
-      </c>
-      <c r="O89" t="n">
-        <v>-153</v>
-      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
       <c r="P89" t="n">
         <v>-19.5</v>
       </c>
@@ -10591,12 +10317,8 @@
       <c r="L90" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
-        <v>-12.5</v>
-      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>-38.1</v>
@@ -10830,15 +10552,9 @@
       <c r="L93" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="N93" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="O93" t="n">
-        <v>100</v>
-      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
       <c r="P93" t="n">
         <v>91.7</v>
       </c>
@@ -10992,15 +10708,9 @@
       <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="N95" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O95" t="n">
-        <v>82</v>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
       <c r="P95" t="n">
         <v>47.5</v>
       </c>
@@ -11721,15 +11431,9 @@
       <c r="L104" t="n">
         <v>-0.49</v>
       </c>
-      <c r="M104" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N104" t="n">
-        <v>-10.1</v>
-      </c>
-      <c r="O104" t="n">
-        <v>-581</v>
-      </c>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
       <c r="P104" t="n">
         <v>-24.9</v>
       </c>
@@ -11802,15 +11506,9 @@
       <c r="L105" t="n">
         <v>-0.75</v>
       </c>
-      <c r="M105" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N105" t="n">
-        <v>-16</v>
-      </c>
-      <c r="O105" t="n">
-        <v>-4582</v>
-      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
       <c r="P105" t="n">
         <v>-32</v>
       </c>
@@ -11883,15 +11581,9 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="n">
-        <v>1</v>
-      </c>
-      <c r="N106" t="n">
-        <v>-17.4</v>
-      </c>
-      <c r="O106" t="n">
-        <v>-1645</v>
-      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -11964,15 +11656,9 @@
       <c r="L107" t="n">
         <v>1.65</v>
       </c>
-      <c r="M107" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N107" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="O107" t="n">
-        <v>99</v>
-      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
       <c r="P107" t="n">
         <v>138.8</v>
       </c>
@@ -12288,15 +11974,9 @@
       <c r="L111" t="n">
         <v>1.23</v>
       </c>
-      <c r="M111" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N111" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="O111" t="n">
-        <v>81</v>
-      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
       <c r="P111" t="n">
         <v>84.3</v>
       </c>
@@ -12693,15 +12373,9 @@
       <c r="L116" t="n">
         <v>0.83</v>
       </c>
-      <c r="M116" t="n">
-        <v>15</v>
-      </c>
-      <c r="N116" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" t="n">
-        <v>77</v>
-      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
       <c r="P116" t="n">
         <v>54.8</v>
       </c>
@@ -13017,15 +12691,9 @@
       <c r="L120" t="n">
         <v>0.15</v>
       </c>
-      <c r="M120" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N120" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O120" t="n">
-        <v>56</v>
-      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
       <c r="P120" t="n">
         <v>10.3</v>
       </c>
@@ -13422,15 +13090,9 @@
       <c r="L125" t="n">
         <v>0.89</v>
       </c>
-      <c r="M125" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N125" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="O125" t="n">
-        <v>92</v>
-      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
       <c r="P125" t="n">
         <v>61.1</v>
       </c>
@@ -13665,15 +13327,9 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>83</v>
-      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -14232,15 +13888,9 @@
       <c r="L135" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M135" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N135" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="O135" t="n">
-        <v>-241</v>
-      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
       <c r="P135" t="n">
         <v>-22.2</v>
       </c>
@@ -14475,15 +14125,9 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="N138" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="O138" t="n">
-        <v>100</v>
-      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -14718,15 +14362,9 @@
       <c r="L141" t="n">
         <v>1.18</v>
       </c>
-      <c r="M141" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N141" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O141" t="n">
-        <v>100</v>
-      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
       <c r="P141" t="n">
         <v>90.59999999999999</v>
       </c>
@@ -15042,15 +14680,9 @@
       <c r="L145" t="n">
         <v>0.64</v>
       </c>
-      <c r="M145" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="N145" t="n">
-        <v>-6.7</v>
-      </c>
-      <c r="O145" t="n">
-        <v>94</v>
-      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
       <c r="P145" t="n">
         <v>57.1</v>
       </c>
@@ -15933,15 +15565,9 @@
       <c r="L156" t="n">
         <v>0.29</v>
       </c>
-      <c r="M156" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="N156" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="O156" t="n">
-        <v>61</v>
-      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
       <c r="P156" t="n">
         <v>26</v>
       </c>
@@ -16332,15 +15958,9 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="N161" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O161" t="n">
-        <v>-46</v>
-      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -16816,15 +16436,9 @@
       <c r="L167" t="n">
         <v>1.03</v>
       </c>
-      <c r="M167" t="n">
-        <v>27.7</v>
-      </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" t="n">
-        <v>84</v>
-      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
       <c r="P167" t="n">
         <v>130.5</v>
       </c>
@@ -18187,15 +17801,9 @@
       <c r="L184" t="n">
         <v>0.44</v>
       </c>
-      <c r="M184" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="N184" t="n">
-        <v>0</v>
-      </c>
-      <c r="O184" t="n">
-        <v>71</v>
-      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
       <c r="P184" t="n">
         <v>43.3</v>
       </c>
@@ -18673,15 +18281,9 @@
       <c r="L190" t="n">
         <v>0.12</v>
       </c>
-      <c r="M190" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N190" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="O190" t="n">
-        <v>22</v>
-      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
       <c r="P190" t="n">
         <v>6.4</v>
       </c>
@@ -18835,15 +18437,9 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="n">
-        <v>11</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="n">
-        <v>9</v>
-      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -18997,15 +18593,9 @@
       <c r="L194" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M194" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N194" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="O194" t="n">
-        <v>-40</v>
-      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
       <c r="P194" t="n">
         <v>-6.8</v>
       </c>
@@ -19240,15 +18830,9 @@
       <c r="L197" t="n">
         <v>0.27</v>
       </c>
-      <c r="M197" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N197" t="n">
-        <v>-3.7</v>
-      </c>
-      <c r="O197" t="n">
-        <v>46</v>
-      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
       <c r="P197" t="n">
         <v>22.8</v>
       </c>
@@ -19321,15 +18905,9 @@
       <c r="L198" t="n">
         <v>0.27</v>
       </c>
-      <c r="M198" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="N198" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="O198" t="n">
-        <v>20</v>
-      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr"/>
       <c r="P198" t="n">
         <v>14.2</v>
       </c>
@@ -19645,15 +19223,9 @@
       <c r="L202" t="n">
         <v>-0.19</v>
       </c>
-      <c r="M202" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N202" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="O202" t="n">
-        <v>-44</v>
-      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
       <c r="P202" t="n">
         <v>-11.1</v>
       </c>
@@ -20129,15 +19701,9 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N208" t="n">
-        <v>-12.7</v>
-      </c>
-      <c r="O208" t="n">
-        <v>-413</v>
-      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -20210,15 +19776,9 @@
       <c r="L209" t="n">
         <v>-0.72</v>
       </c>
-      <c r="M209" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="N209" t="n">
-        <v>-12.5</v>
-      </c>
-      <c r="O209" t="n">
-        <v>-1358</v>
-      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
       <c r="P209" t="n">
         <v>-41.2</v>
       </c>
@@ -20372,12 +19932,8 @@
       <c r="L211" t="n">
         <v>-2.56</v>
       </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="n">
-        <v>-26.2</v>
-      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="n">
         <v>-70.09999999999999</v>
@@ -20613,15 +20169,9 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N214" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O214" t="n">
-        <v>100</v>
-      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -20856,15 +20406,9 @@
       <c r="L217" t="n">
         <v>0.68</v>
       </c>
-      <c r="M217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="N217" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="O217" t="n">
-        <v>100</v>
-      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
       <c r="P217" t="n">
         <v>48.3</v>
       </c>
@@ -21018,15 +20562,9 @@
       <c r="L219" t="n">
         <v>0.35</v>
       </c>
-      <c r="M219" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="N219" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="O219" t="n">
-        <v>100</v>
-      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
       <c r="P219" t="n">
         <v>24.3</v>
       </c>
@@ -21656,15 +21194,9 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="N227" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O227" t="n">
-        <v>89</v>
-      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -22061,15 +21593,9 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="N232" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O232" t="n">
-        <v>51</v>
-      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -22223,15 +21749,9 @@
       <c r="L234" t="n">
         <v>0.32</v>
       </c>
-      <c r="M234" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="N234" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="O234" t="n">
-        <v>86</v>
-      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
       <c r="P234" t="n">
         <v>19.7</v>
       </c>
@@ -22628,15 +22148,9 @@
       <c r="L239" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M239" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="N239" t="n">
-        <v>-5.1</v>
-      </c>
-      <c r="O239" t="n">
-        <v>-413</v>
-      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
       <c r="P239" t="n">
         <v>-19</v>
       </c>
@@ -22952,15 +22466,9 @@
       <c r="L243" t="n">
         <v>0.42</v>
       </c>
-      <c r="M243" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N243" t="n">
-        <v>0</v>
-      </c>
-      <c r="O243" t="n">
-        <v>58</v>
-      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
       <c r="P243" t="n">
         <v>33.7</v>
       </c>
@@ -23033,15 +22541,9 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="N244" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="O244" t="n">
-        <v>83</v>
-      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -23114,15 +22616,9 @@
       <c r="L245" t="n">
         <v>0.36</v>
       </c>
-      <c r="M245" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="N245" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="O245" t="n">
-        <v>73</v>
-      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
       <c r="P245" t="n">
         <v>27.6</v>
       </c>
@@ -23357,15 +22853,9 @@
       <c r="L248" t="n">
         <v>0.35</v>
       </c>
-      <c r="M248" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="N248" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O248" t="n">
-        <v>46</v>
-      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
       <c r="P248" t="n">
         <v>13.7</v>
       </c>
@@ -23999,12 +23489,8 @@
       <c r="L256" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M256" t="n">
-        <v>0</v>
-      </c>
-      <c r="N256" t="n">
-        <v>-10.6</v>
-      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
         <v>-36.1</v>
@@ -24321,15 +23807,9 @@
       <c r="L260" t="n">
         <v>0.29</v>
       </c>
-      <c r="M260" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N260" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O260" t="n">
-        <v>44</v>
-      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
       <c r="P260" t="n">
         <v>20.4</v>
       </c>
@@ -24402,15 +23882,9 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N261" t="n">
-        <v>-2.1</v>
-      </c>
-      <c r="O261" t="n">
-        <v>38</v>
-      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -24888,15 +24362,9 @@
       <c r="L267" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M267" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N267" t="n">
-        <v>-5.7</v>
-      </c>
-      <c r="O267" t="n">
-        <v>-777</v>
-      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
       <c r="P267" t="n">
         <v>-15</v>
       </c>
@@ -25698,15 +25166,9 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="N277" t="n">
-        <v>-3.4</v>
-      </c>
-      <c r="O277" t="n">
-        <v>45</v>
-      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25860,15 +25322,9 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="N279" t="n">
-        <v>0</v>
-      </c>
-      <c r="O279" t="n">
-        <v>10</v>
-      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -26103,15 +25559,9 @@
       <c r="L282" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M282" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="N282" t="n">
-        <v>-12</v>
-      </c>
-      <c r="O282" t="n">
-        <v>-103</v>
-      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
       <c r="P282" t="n">
         <v>-18.3</v>
       </c>
@@ -26265,15 +25715,9 @@
       <c r="L284" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M284" t="n">
-        <v>1</v>
-      </c>
-      <c r="N284" t="n">
-        <v>-16.5</v>
-      </c>
-      <c r="O284" t="n">
-        <v>-1163</v>
-      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
       <c r="P284" t="n">
         <v>-37.6</v>
       </c>
@@ -26887,7 +26331,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.9</v>
+        <v>-3.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26929,7 +26373,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.7</v>
+        <v>-10.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26971,7 +26415,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-13.9</v>
+        <v>-12.8</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -27013,7 +26457,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-8.1</v>
+        <v>-12.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -27055,7 +26499,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.5</v>
+        <v>-5.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -27097,7 +26541,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10.7</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -27181,7 +26625,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.7</v>
+        <v>-1.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -27223,7 +26667,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -27265,7 +26709,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3.8</v>
+        <v>-4.2</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -27349,7 +26793,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-3.6</v>
+        <v>-3.3</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -27391,7 +26835,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.7</v>
+        <v>-4.3</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -27433,7 +26877,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.3</v>
+        <v>-7.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -27475,7 +26919,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9.1</v>
+        <v>-9</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -27601,7 +27045,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-4.2</v>
+        <v>-4.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -27643,7 +27087,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-11.8</v>
+        <v>-13</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27695,7 +27139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27718,12 +27162,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27177,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27748,12 +27192,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27763,12 +27207,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27778,12 +27222,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27242,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27252,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27267,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27838,47 +27282,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>CASH (intentional)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>12 stocks / 9 sectors</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>11 stocks / 8 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (74)</t>
+          <t>ICICIBANK (76)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (49)</t>
+          <t>ITC (50)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PIDILITIND, SBIN</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hold a 11-stock risk-managed portfolio</t>
+          <t>Hold a 12-stock risk-managed portfolio</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-20  /  2026-08-19</t>
+          <t>2026-08-21  /  2026-08-20</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.0%</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +7 = 74</t>
+          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +8 = 76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H2" t="n">
         <v>89</v>
       </c>
       <c r="I2" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1402</v>
+        <v>1411.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1363 - 1441</t>
+          <t>1373 - 1451</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+3.7%)</t>
+          <t>Above 200-DMA (+4.4%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>23834</v>
+        <v>15531</v>
       </c>
       <c r="W2" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="X2" t="n">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 74; SBIN: 73, PNB: 63, YESBANK: 62</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, IDFCFIRSTB: 65, PNB: 63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+3.7%) • outperforming Nifty • sector strength 71/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.4%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +14 · Regime +9 · Sector +6 = 70</t>
+          <t>Historical +20 · Risk/Vol +19 · Trend/Tech +18 · Regime +9 · Sector +8 = 74</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1649,58 +1649,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="I3" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1900</v>
+        <v>1048</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1848 - 1952</t>
+          <t>1014 - 1082</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-4% to +14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.1%)</t>
+          <t>Above 200-DMA (+1.3%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,21 +1709,21 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>22800</v>
+        <v>17816</v>
       </c>
       <c r="W3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="X3" t="n">
-        <v>8.1</v>
+        <v>5.9</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,32 +1733,32 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 70; LUPIN: 59, DRREDDY: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 74; ICICIBANK: 76, IDFCFIRSTB: 65, PNB: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.1%) • sector strength 57/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+1.3%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +14 · Regime +9 · Sector +6 = 70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1767,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="H4" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>336.5</v>
+        <v>1904</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>328 - 345</t>
+          <t>1852 - 1956</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +14%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.8%)</t>
+          <t>Above 200-DMA (+6.3%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>22549</v>
+        <v>34272</v>
       </c>
       <c r="W4" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="X4" t="n">
-        <v>7.5</v>
+        <v>11.6</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,27 +1851,27 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 55, TATAPOWER: 54, NHPC: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 70; CIPLA: 66, ZYDUSLIFE: 66, LUPIN: 59</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.8%) • sector strength 21/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.3%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
+          <t>Risk/Vol +20 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1881,62 +1881,62 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>2225</v>
+        <v>1660</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2166 - 2284</t>
+          <t>1607 - 1713</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-0.9%)</t>
+          <t>Above 200-DMA (+12.0%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,21 +1945,21 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>28925</v>
+        <v>11620</v>
       </c>
       <c r="W5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X5" t="n">
-        <v>9.699999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 70, DRREDDY: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 51</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-0.9%) • sector strength 57/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+12.0%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1985,54 +1985,54 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +8 · Trend/Tech +6 = 59</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I6" t="n">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>409.2</v>
+        <v>337.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>397 - 422</t>
+          <t>329 - 346</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,15 +2046,15 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.5%)</t>
+          <t>Below 200-DMA (-5.5%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>28644</v>
+        <v>27675</v>
       </c>
       <c r="W6" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="X6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 59; HAL: 66, KEI: 54, MAZDOCK: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 56, TATAPOWER: 56, JSWENERGY: 55</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.5%) • sector strength 79/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.5%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +2 = 55</t>
+          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="H7" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>263.5</v>
+        <v>2201.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>257 - 270</t>
+          <t>2144 - 2259</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.6%)</t>
+          <t>Below 200-DMA (-2.0%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>25032</v>
+        <v>24216</v>
       </c>
       <c r="W7" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="X7" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 55; NTPC: 63, TATAPOWER: 54, NHPC: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 70, CIPLA: 66, ZYDUSLIFE: 66. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.6%) • sector strength 21/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-2.0%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +3 = 52</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,62 +2235,62 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>267</v>
+        <v>409.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>261 - 273</t>
+          <t>397 - 422</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-17.8%)</t>
+          <t>Below 200-DMA (-2.4%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>32046</v>
+        <v>15148</v>
       </c>
       <c r="W8" t="n">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="X8" t="n">
-        <v>10.7</v>
+        <v>5.1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; DABUR: 49, HINDUNILVR: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 64, MAZDOCK: 50, AMBER: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-17.8%) • sector strength 29/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.4%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +1 = 51</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 56</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,36 +2357,36 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="I9" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>238</v>
+        <v>264.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>231 - 245</t>
+          <t>259 - 271</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.9%)</t>
+          <t>Below 200-DMA (-7.1%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>35462</v>
+        <v>39455</v>
       </c>
       <c r="W9" t="n">
         <v>149</v>
       </c>
       <c r="X9" t="n">
-        <v>11.9</v>
+        <v>13.2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; OIL: 48, IOC: 46, GUJGASLTD: 33</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, TATAPOWER: 56, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.9%) • sector strength 14/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.1%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +1 = 52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H10" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>400</v>
+        <v>238.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>388 - 412</t>
+          <t>231 - 246</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-6.4%)</t>
+          <t>Below 200-DMA (-7.7%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>36800</v>
+        <v>32674</v>
       </c>
       <c r="W10" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="X10" t="n">
-        <v>12.4</v>
+        <v>11</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,27 +2559,27 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; TATASTEEL: 49, SAIL: 43, HINDZINC: 40</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 52; OIL: 48, IOC: 45, GUJGASLTD: 33</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.4%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.7%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 52</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2593,36 +2593,36 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>488.4</v>
+        <v>402.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>473 - 503</t>
+          <t>391 - 414</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.1%)</t>
+          <t>Below 200-DMA (-5.8%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>20511</v>
+        <v>30590</v>
       </c>
       <c r="W11" t="n">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="X11" t="n">
-        <v>6.8</v>
+        <v>10.2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,27 +2677,27 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; HINDZINC: 49, TATASTEEL: 48, SAIL: 44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.1%) • sector strength 50/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.8%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +3 = 49</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2711,23 +2711,23 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="I12" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2736,71 +2736,189 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>2020.7</v>
+        <v>271.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1959 - 2082</t>
+          <t>265 - 278</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
+          <t>-4% to +3%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>70</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-16.2%)</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>39</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2 months (2M)</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>31511</v>
+      </c>
+      <c r="W12" t="n">
+        <v>116</v>
+      </c>
+      <c r="X12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Fundamentals · Earnings · News · Flows</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; DABUR: 47, PATANJALI: 44</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>53</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Risk/Vol +21 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 53</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>40</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="n">
+        <v>83</v>
+      </c>
+      <c r="I13" t="n">
+        <v>47</v>
+      </c>
+      <c r="J13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>485.9</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>471 - 501</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q12" t="n">
-        <v>65</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Below 200-DMA (-10.4%)</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="Q13" t="n">
+        <v>67</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Below 200-DMA (-16.3%)</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>44</v>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>2 months (2M)</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>18186</v>
-      </c>
-      <c r="W12" t="n">
-        <v>9</v>
-      </c>
-      <c r="X12" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>14577</v>
+      </c>
+      <c r="W13" t="n">
+        <v>30</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Fundamentals · Earnings · News · Flows</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 52, DABUR: 49. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.4%) • sector strength 29/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -3355,9 +3473,15 @@
       <c r="L2" t="n">
         <v>4.34</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>100</v>
+      </c>
       <c r="P2" t="n">
         <v>200.3</v>
       </c>
@@ -3586,9 +3710,15 @@
       <c r="L5" t="n">
         <v>1.6</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>98</v>
+      </c>
       <c r="P5" t="n">
         <v>135.9</v>
       </c>
@@ -3661,15 +3791,9 @@
       <c r="L6" t="n">
         <v>0.6</v>
       </c>
-      <c r="M6" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>99</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>74.2</v>
       </c>
@@ -3823,9 +3947,15 @@
       <c r="L8" t="n">
         <v>0.47</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>13</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>88</v>
+      </c>
       <c r="P8" t="n">
         <v>54.2</v>
       </c>
@@ -3979,15 +4109,9 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>88</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -4060,9 +4184,15 @@
       <c r="L11" t="n">
         <v>0.49</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>92</v>
+      </c>
       <c r="P11" t="n">
         <v>29.9</v>
       </c>
@@ -4378,9 +4508,15 @@
       <c r="L15" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-39</v>
+      </c>
       <c r="P15" t="n">
         <v>-6.6</v>
       </c>
@@ -4852,9 +4988,15 @@
       <c r="L21" t="n">
         <v>0.14</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-8.9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>67</v>
+      </c>
       <c r="P21" t="n">
         <v>9.699999999999999</v>
       </c>
@@ -5170,15 +5312,9 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-14.8</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-64</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5488,15 +5624,9 @@
       <c r="L29" t="n">
         <v>-0.71</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-17.6</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-465</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
         <v>-42.8</v>
       </c>
@@ -5962,9 +6092,15 @@
       <c r="L35" t="n">
         <v>0.12</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>12</v>
+      </c>
       <c r="P35" t="n">
         <v>5.6</v>
       </c>
@@ -6361,15 +6497,9 @@
       <c r="L40" t="n">
         <v>-0.29</v>
       </c>
-      <c r="M40" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-11.2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>-46</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
         <v>-21.4</v>
       </c>
@@ -6991,9 +7121,15 @@
       <c r="L48" t="n">
         <v>1.05</v>
       </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="M48" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="O48" t="n">
+        <v>98</v>
+      </c>
       <c r="P48" t="n">
         <v>99.5</v>
       </c>
@@ -7303,15 +7439,9 @@
       <c r="L52" t="n">
         <v>0.08</v>
       </c>
-      <c r="M52" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="O52" t="n">
-        <v>60</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
         <v>5.7</v>
       </c>
@@ -8340,9 +8470,15 @@
       <c r="L65" t="n">
         <v>1.25</v>
       </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="M65" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" t="n">
+        <v>66</v>
+      </c>
       <c r="P65" t="n">
         <v>67.2</v>
       </c>
@@ -8490,15 +8626,9 @@
       <c r="L67" t="n">
         <v>0.74</v>
       </c>
-      <c r="M67" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="N67" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="O67" t="n">
-        <v>85</v>
-      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
       <c r="P67" t="n">
         <v>58.6</v>
       </c>
@@ -8571,9 +8701,15 @@
       <c r="L68" t="n">
         <v>0.35</v>
       </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="M68" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" t="n">
+        <v>46</v>
+      </c>
       <c r="P68" t="n">
         <v>51</v>
       </c>
@@ -8808,9 +8944,15 @@
       <c r="L71" t="n">
         <v>0.48</v>
       </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
+      <c r="M71" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N71" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="O71" t="n">
+        <v>51</v>
+      </c>
       <c r="P71" t="n">
         <v>16.9</v>
       </c>
@@ -8883,9 +9025,15 @@
       <c r="L72" t="n">
         <v>0.17</v>
       </c>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="O72" t="n">
+        <v>29</v>
+      </c>
       <c r="P72" t="n">
         <v>13.3</v>
       </c>
@@ -9606,15 +9754,9 @@
       <c r="L81" t="n">
         <v>0.38</v>
       </c>
-      <c r="M81" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="N81" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O81" t="n">
-        <v>42</v>
-      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
       <c r="P81" t="n">
         <v>35.2</v>
       </c>
@@ -10086,15 +10228,9 @@
       <c r="L87" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M87" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="N87" t="n">
-        <v>-3.2</v>
-      </c>
-      <c r="O87" t="n">
-        <v>-49</v>
-      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
       <c r="P87" t="n">
         <v>-9.300000000000001</v>
       </c>
@@ -10167,9 +10303,15 @@
       <c r="L88" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="M88" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="O88" t="n">
+        <v>-128</v>
+      </c>
       <c r="P88" t="n">
         <v>-19.5</v>
       </c>
@@ -10242,9 +10384,15 @@
       <c r="L89" t="n">
         <v>-0.48</v>
       </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="M89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="O89" t="n">
+        <v>-153</v>
+      </c>
       <c r="P89" t="n">
         <v>-19.5</v>
       </c>
@@ -10317,8 +10465,12 @@
       <c r="L90" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-12.5</v>
+      </c>
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="n">
         <v>-38.1</v>
@@ -10392,12 +10544,8 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
-        <v>-12</v>
-      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10708,9 +10856,15 @@
       <c r="L95" t="n">
         <v>1</v>
       </c>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
+      <c r="M95" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>82</v>
+      </c>
       <c r="P95" t="n">
         <v>47.5</v>
       </c>
@@ -11431,9 +11585,15 @@
       <c r="L104" t="n">
         <v>-0.49</v>
       </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>-581</v>
+      </c>
       <c r="P104" t="n">
         <v>-24.9</v>
       </c>
@@ -11506,9 +11666,15 @@
       <c r="L105" t="n">
         <v>-0.75</v>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+      <c r="M105" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-16</v>
+      </c>
+      <c r="O105" t="n">
+        <v>-4582</v>
+      </c>
       <c r="P105" t="n">
         <v>-32</v>
       </c>
@@ -11731,15 +11897,9 @@
       <c r="L108" t="n">
         <v>1.21</v>
       </c>
-      <c r="M108" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="N108" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" t="n">
-        <v>100</v>
-      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
       <c r="P108" t="n">
         <v>121.6</v>
       </c>
@@ -11893,15 +12053,9 @@
       <c r="L110" t="n">
         <v>1.35</v>
       </c>
-      <c r="M110" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="N110" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" t="n">
-        <v>88</v>
-      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
       <c r="P110" t="n">
         <v>101.4</v>
       </c>
@@ -11974,9 +12128,15 @@
       <c r="L111" t="n">
         <v>1.23</v>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="M111" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="O111" t="n">
+        <v>81</v>
+      </c>
       <c r="P111" t="n">
         <v>84.3</v>
       </c>
@@ -12373,9 +12533,15 @@
       <c r="L116" t="n">
         <v>0.83</v>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>15</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" t="n">
+        <v>77</v>
+      </c>
       <c r="P116" t="n">
         <v>54.8</v>
       </c>
@@ -12928,15 +13094,9 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="N123" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="O123" t="n">
-        <v>86</v>
-      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -13807,15 +13967,9 @@
       <c r="L134" t="n">
         <v>-0.11</v>
       </c>
-      <c r="M134" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N134" t="n">
-        <v>-4.2</v>
-      </c>
-      <c r="O134" t="n">
-        <v>-32</v>
-      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
       <c r="P134" t="n">
         <v>-8</v>
       </c>
@@ -13888,9 +14042,15 @@
       <c r="L135" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-241</v>
+      </c>
       <c r="P135" t="n">
         <v>-22.2</v>
       </c>
@@ -13963,15 +14123,9 @@
       <c r="L136" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M136" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N136" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="O136" t="n">
-        <v>-173</v>
-      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
       <c r="P136" t="n">
         <v>-26.4</v>
       </c>
@@ -14362,9 +14516,15 @@
       <c r="L141" t="n">
         <v>1.18</v>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O141" t="n">
+        <v>100</v>
+      </c>
       <c r="P141" t="n">
         <v>90.59999999999999</v>
       </c>
@@ -14680,9 +14840,15 @@
       <c r="L145" t="n">
         <v>0.64</v>
       </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
+      <c r="M145" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="O145" t="n">
+        <v>94</v>
+      </c>
       <c r="P145" t="n">
         <v>57.1</v>
       </c>
@@ -14998,15 +15164,9 @@
       <c r="L149" t="n">
         <v>0.22</v>
       </c>
-      <c r="M149" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="N149" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="O149" t="n">
-        <v>49</v>
-      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
       <c r="P149" t="n">
         <v>16.9</v>
       </c>
@@ -15079,15 +15239,9 @@
       <c r="L150" t="n">
         <v>0.01</v>
       </c>
-      <c r="M150" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N150" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="O150" t="n">
-        <v>4</v>
-      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
       <c r="P150" t="n">
         <v>0.6</v>
       </c>
@@ -15883,9 +16037,15 @@
       <c r="L160" t="n">
         <v>-0.46</v>
       </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
+      <c r="M160" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N160" t="n">
+        <v>-14.7</v>
+      </c>
+      <c r="O160" t="n">
+        <v>-593</v>
+      </c>
       <c r="P160" t="n">
         <v>-18.1</v>
       </c>
@@ -16276,12 +16436,8 @@
       <c r="L165" t="n">
         <v>-1.2</v>
       </c>
-      <c r="M165" t="n">
-        <v>0</v>
-      </c>
-      <c r="N165" t="n">
-        <v>-14.7</v>
-      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="n">
         <v>-45.1</v>
@@ -16355,15 +16511,9 @@
       <c r="L166" t="n">
         <v>-0.93</v>
       </c>
-      <c r="M166" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N166" t="n">
-        <v>-14.6</v>
-      </c>
-      <c r="O166" t="n">
-        <v>-2027</v>
-      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
       <c r="P166" t="n">
         <v>-45.9</v>
       </c>
@@ -16511,15 +16661,9 @@
       <c r="L168" t="n">
         <v>1.7</v>
       </c>
-      <c r="M168" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" t="n">
-        <v>98</v>
-      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
       <c r="P168" t="n">
         <v>129.9</v>
       </c>
@@ -16754,9 +16898,15 @@
       <c r="L171" t="n">
         <v>1.61</v>
       </c>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
+      <c r="M171" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="N171" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O171" t="n">
+        <v>87</v>
+      </c>
       <c r="P171" t="n">
         <v>91.40000000000001</v>
       </c>
@@ -16991,15 +17141,9 @@
       <c r="L174" t="n">
         <v>0.72</v>
       </c>
-      <c r="M174" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="N174" t="n">
-        <v>-3.3</v>
-      </c>
-      <c r="O174" t="n">
-        <v>91</v>
-      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
       <c r="P174" t="n">
         <v>65.5</v>
       </c>
@@ -17072,15 +17216,9 @@
       <c r="L175" t="n">
         <v>0.88</v>
       </c>
-      <c r="M175" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="N175" t="n">
-        <v>-3.8</v>
-      </c>
-      <c r="O175" t="n">
-        <v>81</v>
-      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
       <c r="P175" t="n">
         <v>54</v>
       </c>
@@ -17315,15 +17453,9 @@
       <c r="L178" t="n">
         <v>0.33</v>
       </c>
-      <c r="M178" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="N178" t="n">
-        <v>-3.5</v>
-      </c>
-      <c r="O178" t="n">
-        <v>65</v>
-      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
       <c r="P178" t="n">
         <v>21.2</v>
       </c>
@@ -17720,15 +17852,9 @@
       <c r="L183" t="n">
         <v>1.73</v>
       </c>
-      <c r="M183" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="N183" t="n">
-        <v>0</v>
-      </c>
-      <c r="O183" t="n">
-        <v>81</v>
-      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
       <c r="P183" t="n">
         <v>99.90000000000001</v>
       </c>
@@ -18200,15 +18326,9 @@
       <c r="L189" t="n">
         <v>0.09</v>
       </c>
-      <c r="M189" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N189" t="n">
-        <v>-2</v>
-      </c>
-      <c r="O189" t="n">
-        <v>25</v>
-      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
       <c r="P189" t="n">
         <v>6.5</v>
       </c>
@@ -18281,9 +18401,15 @@
       <c r="L190" t="n">
         <v>0.12</v>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N190" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="O190" t="n">
+        <v>22</v>
+      </c>
       <c r="P190" t="n">
         <v>6.4</v>
       </c>
@@ -18356,15 +18482,9 @@
       <c r="L191" t="n">
         <v>0.1</v>
       </c>
-      <c r="M191" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N191" t="n">
-        <v>-1.7</v>
-      </c>
-      <c r="O191" t="n">
-        <v>11</v>
-      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
       <c r="P191" t="n">
         <v>6.4</v>
       </c>
@@ -18512,15 +18632,9 @@
       <c r="L193" t="n">
         <v>-0.03</v>
       </c>
-      <c r="M193" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N193" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="O193" t="n">
-        <v>-3</v>
-      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
       <c r="P193" t="n">
         <v>-1.4</v>
       </c>
@@ -18668,15 +18782,9 @@
       <c r="L195" t="n">
         <v>-0.25</v>
       </c>
-      <c r="M195" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="N195" t="n">
-        <v>-11.1</v>
-      </c>
-      <c r="O195" t="n">
-        <v>-60</v>
-      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
       <c r="P195" t="n">
         <v>-14.6</v>
       </c>
@@ -19298,15 +19406,9 @@
       <c r="L203" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M203" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N203" t="n">
-        <v>-11.6</v>
-      </c>
-      <c r="O203" t="n">
-        <v>-111</v>
-      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
       <c r="P203" t="n">
         <v>-12.9</v>
       </c>
@@ -19776,9 +19878,15 @@
       <c r="L209" t="n">
         <v>-0.72</v>
       </c>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
+      <c r="M209" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N209" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="O209" t="n">
+        <v>-1358</v>
+      </c>
       <c r="P209" t="n">
         <v>-41.2</v>
       </c>
@@ -19851,15 +19959,9 @@
       <c r="L210" t="n">
         <v>-1.35</v>
       </c>
-      <c r="M210" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N210" t="n">
-        <v>-26</v>
-      </c>
-      <c r="O210" t="n">
-        <v>-1247</v>
-      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
       <c r="P210" t="n">
         <v>-66.2</v>
       </c>
@@ -19932,8 +20034,12 @@
       <c r="L211" t="n">
         <v>-2.56</v>
       </c>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>-26.2</v>
+      </c>
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="n">
         <v>-70.09999999999999</v>
@@ -20406,9 +20512,15 @@
       <c r="L217" t="n">
         <v>0.68</v>
       </c>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
+      <c r="M217" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="N217" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="O217" t="n">
+        <v>100</v>
+      </c>
       <c r="P217" t="n">
         <v>48.3</v>
       </c>
@@ -20959,12 +21071,8 @@
       <c r="L224" t="n">
         <v>-0.61</v>
       </c>
-      <c r="M224" t="n">
-        <v>0</v>
-      </c>
-      <c r="N224" t="n">
-        <v>-16.5</v>
-      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="n">
         <v>-27.8</v>
@@ -22067,15 +22175,9 @@
       <c r="L238" t="n">
         <v>-0.18</v>
       </c>
-      <c r="M238" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N238" t="n">
-        <v>-10.4</v>
-      </c>
-      <c r="O238" t="n">
-        <v>-258</v>
-      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
       <c r="P238" t="n">
         <v>-13.7</v>
       </c>
@@ -22148,9 +22250,15 @@
       <c r="L239" t="n">
         <v>-0.36</v>
       </c>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
+      <c r="M239" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N239" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="O239" t="n">
+        <v>-413</v>
+      </c>
       <c r="P239" t="n">
         <v>-19</v>
       </c>
@@ -22466,9 +22574,15 @@
       <c r="L243" t="n">
         <v>0.42</v>
       </c>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
+      <c r="M243" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>58</v>
+      </c>
       <c r="P243" t="n">
         <v>33.7</v>
       </c>
@@ -22691,15 +22805,9 @@
       <c r="L246" t="n">
         <v>0.34</v>
       </c>
-      <c r="M246" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="N246" t="n">
-        <v>-2.4</v>
-      </c>
-      <c r="O246" t="n">
-        <v>59</v>
-      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
       <c r="P246" t="n">
         <v>23</v>
       </c>
@@ -22853,9 +22961,15 @@
       <c r="L248" t="n">
         <v>0.35</v>
       </c>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
+      <c r="M248" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N248" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O248" t="n">
+        <v>46</v>
+      </c>
       <c r="P248" t="n">
         <v>13.7</v>
       </c>
@@ -22928,15 +23042,9 @@
       <c r="L249" t="n">
         <v>0.16</v>
       </c>
-      <c r="M249" t="n">
-        <v>6</v>
-      </c>
-      <c r="N249" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="O249" t="n">
-        <v>48</v>
-      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
       <c r="P249" t="n">
         <v>12.1</v>
       </c>
@@ -23331,12 +23439,8 @@
       <c r="L254" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M254" t="n">
-        <v>0</v>
-      </c>
-      <c r="N254" t="n">
-        <v>-8.6</v>
-      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="n">
         <v>-19</v>
@@ -24362,9 +24466,15 @@
       <c r="L267" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M267" t="inlineStr"/>
-      <c r="N267" t="inlineStr"/>
-      <c r="O267" t="inlineStr"/>
+      <c r="M267" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N267" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="O267" t="n">
+        <v>-777</v>
+      </c>
       <c r="P267" t="n">
         <v>-15</v>
       </c>
@@ -24599,15 +24709,9 @@
       <c r="L270" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M270" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N270" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="O270" t="n">
-        <v>-255</v>
-      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
       <c r="P270" t="n">
         <v>-30.7</v>
       </c>
@@ -25559,9 +25663,15 @@
       <c r="L282" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M282" t="inlineStr"/>
-      <c r="N282" t="inlineStr"/>
-      <c r="O282" t="inlineStr"/>
+      <c r="M282" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="N282" t="n">
+        <v>-12</v>
+      </c>
+      <c r="O282" t="n">
+        <v>-103</v>
+      </c>
       <c r="P282" t="n">
         <v>-18.3</v>
       </c>
@@ -26331,7 +26441,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-3.4</v>
+        <v>-2.7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26373,7 +26483,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-10.5</v>
+        <v>-8.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26415,7 +26525,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-12.8</v>
+        <v>-13.3</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26457,7 +26567,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-12.1</v>
+        <v>-11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26499,7 +26609,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-5.2</v>
+        <v>-4.1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26541,7 +26651,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-10.7</v>
+        <v>-10.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -26625,7 +26735,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -26667,7 +26777,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.7</v>
+        <v>-2.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -26709,7 +26819,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-4.2</v>
+        <v>-3.9</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -26751,7 +26861,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-2.9</v>
+        <v>-2</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -26793,7 +26903,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-3.3</v>
+        <v>-5.1</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -26835,7 +26945,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.3</v>
+        <v>-4.6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -26877,7 +26987,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-7.9</v>
+        <v>-8.1</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -26961,7 +27071,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.3</v>
+        <v>-3.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -27003,7 +27113,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-3.8</v>
+        <v>-3.6</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27045,7 +27155,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-4.5</v>
+        <v>-4.3</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -27139,7 +27249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27162,12 +27272,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27177,12 +27287,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27192,12 +27302,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27207,12 +27317,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27222,12 +27332,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27237,12 +27347,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27252,12 +27362,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27272,7 +27382,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27282,32 +27392,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CASH (intentional)</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>CASH (intentional)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>11 stocks / 8 sectors</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>12 stocks / 9 sectors</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -500,7 +500,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2M (2 months)</t>
+          <t>3M (3 months)</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (76)</t>
+          <t>ICICIBANK (75)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ITC (50)</t>
+          <t>HINDUNILVR (48)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PIDILITIND, SBIN</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>SBIN</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21  /  2026-08-20</t>
+          <t>2026-08-24  /  2026-08-24</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2M (2 months)</t>
+          <t>3M (3 months)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>66%</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rs602,000</t>
+          <t>Rs596,500</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rs458,000</t>
+          <t>Rs460,500</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2 months (63 trading days)</t>
+          <t>3 months (63 trading days)</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +17 · Regime +9 · Sector +8 = 76</t>
+          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,10 +1534,10 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I2" t="n">
         <v>80</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1411.9</v>
+        <v>1420.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1373 - 1451</t>
+          <t>1382 - 1459</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,30 +1578,30 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+4.4%)</t>
+          <t>Above 200-DMA (+5.0%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>15531</v>
+        <v>17046</v>
       </c>
       <c r="W2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, IDFCFIRSTB: 65, PNB: 63</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 75; SBIN: 74, IDFCFIRSTB: 66, LICI: 65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.4%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.0%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1631,99 +1631,99 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>71</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +15 · Regime +9 · Sector +6 = 71</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Risk/Vol</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>59</v>
+      </c>
+      <c r="G3" t="n">
         <v>74</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Historical +20 · Risk/Vol +19 · Trend/Tech +18 · Regime +9 · Sector +8 = 74</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Historical</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>65</v>
-      </c>
-      <c r="G3" t="n">
-        <v>90</v>
-      </c>
       <c r="H3" t="n">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1048</v>
+        <v>1902.4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1014 - 1082</t>
+          <t>1851 - 1954</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +14%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+1.3%)</t>
+          <t>Above 200-DMA (+6.1%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>17816</v>
+        <v>34243</v>
       </c>
       <c r="W3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="X3" t="n">
-        <v>5.9</v>
+        <v>11.7</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Financials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SBIN: 74; ICICIBANK: 76, IDFCFIRSTB: 65, PNB: 63. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 71; CIPLA: 66, ZYDUSLIFE: 65, LUPIN: 59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+1.3%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 2 similar past recs: 100% positive, median +8.9%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.1%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +18 · Trend/Tech +14 · Regime +9 · Sector +6 = 70</t>
+          <t>Risk/Vol +20 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 68</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,46 +1767,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I4" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1904</v>
+        <v>1646</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1852 - 1956</t>
+          <t>1593 - 1699</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-4% to +14%</t>
+          <t>-5% to +7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1814,34 +1814,34 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.3%)</t>
+          <t>Above 200-DMA (+10.9%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>34272</v>
+        <v>18106</v>
       </c>
       <c r="W4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>11.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,32 +1851,32 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 70; CIPLA: 66, ZYDUSLIFE: 66, LUPIN: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.3%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.9%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 68</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Risk/Vol</t>
+          <t>Historical</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1885,81 +1885,81 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1660</v>
+        <v>340.7</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>1607 - 1713</t>
+          <t>332 - 349</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+12.0%)</t>
+          <t>Below 200-DMA (-4.6%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>11620</v>
+        <v>27937</v>
       </c>
       <c r="W5" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="X5" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 51</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 57, NHPC: 53, TATAPOWER: 53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+12.0%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.6%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -1985,54 +1985,54 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
+          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Historical</t>
+          <t>Risk/Vol</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
         <v>95</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>337.5</v>
+        <v>2199.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>329 - 346</t>
+          <t>2142 - 2257</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2046,38 +2046,38 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.5%)</t>
+          <t>Below 200-DMA (-2.2%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>27675</v>
+        <v>24198</v>
       </c>
       <c r="W6" t="n">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="X6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Historical + Risk/Vol strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 56, TATAPOWER: 56, JSWENERGY: 55</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 71, CIPLA: 66, ZYDUSLIFE: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.5%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-2.2%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +2 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>2201.5</v>
+        <v>274</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2144 - 2259</t>
+          <t>268 - 280</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,38 +2164,38 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.0%)</t>
+          <t>Below 200-DMA (-3.8%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>24216</v>
+        <v>37538</v>
       </c>
       <c r="W7" t="n">
-        <v>11</v>
+        <v>137</v>
       </c>
       <c r="X7" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 70, CIPLA: 66, ZYDUSLIFE: 66. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, NHPC: 53, TATAPOWER: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-2.0%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2242,13 +2242,13 @@
         <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8" t="n">
         <v>84</v>
       </c>
       <c r="I8" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
@@ -2264,11 +2264,11 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>409.4</v>
+        <v>414.3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>397 - 422</t>
+          <t>402 - 427</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2286,30 +2286,30 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.4%)</t>
+          <t>Below 200-DMA (-1.3%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>15148</v>
+        <v>20301</v>
       </c>
       <c r="W8" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="X8" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -2323,27 +2323,27 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 64, MAZDOCK: 50, AMBER: 48. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 64, POLYCAB: 56, KEI: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.4%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-1.3%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +3 · Sector +3 = 56</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Sector +3 · Trend/Tech +2 = 52</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,17 +2353,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="I9" t="n">
         <v>27</v>
@@ -2373,20 +2373,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>264.8</v>
+        <v>237</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>259 - 271</t>
+          <t>230 - 244</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,38 +2400,38 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.1%)</t>
+          <t>Below 200-DMA (-8.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>39455</v>
+        <v>32232</v>
       </c>
       <c r="W9" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="X9" t="n">
-        <v>13.2</v>
+        <v>10.8</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 56; NTPC: 64, TATAPOWER: 56, JSWENERGY: 55. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 52; OIL: 52, IOC: 46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-7.1%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.2%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +4 · Sector +1 = 52</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I10" t="n">
         <v>13</v>
@@ -2491,20 +2491,20 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>238.5</v>
+        <v>406</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>231 - 246</t>
+          <t>394 - 418</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,34 +2522,34 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-7.7%)</t>
+          <t>Below 200-DMA (-5.0%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>32674</v>
+        <v>30856</v>
       </c>
       <c r="W10" t="n">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 52; OIL: 48, IOC: 45, GUJGASLTD: 33</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-7.7%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.0%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2593,81 +2593,81 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>402.5</v>
+        <v>270.6</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>391 - 414</t>
+          <t>264 - 277</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.8%)</t>
+          <t>Below 200-DMA (-16.2%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>30590</v>
+        <v>22460</v>
       </c>
       <c r="W11" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="X11" t="n">
-        <v>10.2</v>
+        <v>7.5</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,27 +2677,27 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; HINDZINC: 49, TATASTEEL: 48, SAIL: 44</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; HINDUNILVR: 48, DABUR: 47, PATANJALI: 43</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.8%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ACCUMULATE</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +5 · Trend/Tech +3 = 51</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2707,85 +2707,85 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="J12" t="n">
         <v>60</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>271.6</v>
+        <v>484.2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>265 - 278</t>
+          <t>470 - 499</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.2%)</t>
+          <t>Below 200-DMA (-16.3%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>31511</v>
+        <v>15010</v>
       </c>
       <c r="W12" t="n">
-        <v>116</v>
+        <v>31</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; DABUR: 47, PATANJALI: 44</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +12 · Regime +9 · Trend/Tech +6 · Sector +5 = 53</t>
+          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2829,36 +2829,36 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I13" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>485.9</v>
+        <v>2019.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>471 - 501</t>
+          <t>1959 - 2081</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2872,38 +2872,38 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.3%)</t>
+          <t>Below 200-DMA (-10.2%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2 months (2M)</t>
+          <t>3 months (3M)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>14577</v>
+        <v>14139</v>
       </c>
       <c r="W13" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Transport name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 53; DELHIVERY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 50, DABUR: 47, PATANJALI: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.2%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -3554,9 +3554,15 @@
       <c r="L3" t="n">
         <v>2.12</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>38</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>81</v>
+      </c>
       <c r="P3" t="n">
         <v>194.1</v>
       </c>
@@ -3791,9 +3797,15 @@
       <c r="L6" t="n">
         <v>0.6</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>99</v>
+      </c>
       <c r="P6" t="n">
         <v>74.2</v>
       </c>
@@ -4109,9 +4121,15 @@
       <c r="L10" t="n">
         <v>0.7</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>88</v>
+      </c>
       <c r="P10" t="n">
         <v>40.2</v>
       </c>
@@ -4589,9 +4607,15 @@
       <c r="L16" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-9.1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-331</v>
+      </c>
       <c r="P16" t="n">
         <v>-30.7</v>
       </c>
@@ -5312,9 +5336,15 @@
       <c r="L25" t="n">
         <v>-0.35</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-14.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-64</v>
+      </c>
       <c r="P25" t="n">
         <v>-25.7</v>
       </c>
@@ -5624,9 +5654,15 @@
       <c r="L29" t="n">
         <v>-0.71</v>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-17.6</v>
+      </c>
+      <c r="O29" t="n">
+        <v>-465</v>
+      </c>
       <c r="P29" t="n">
         <v>-42.8</v>
       </c>
@@ -5780,9 +5816,15 @@
       <c r="L31" t="n">
         <v>-0.92</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>-456</v>
+      </c>
       <c r="P31" t="n">
         <v>-47.7</v>
       </c>
@@ -5855,9 +5897,15 @@
       <c r="L32" t="n">
         <v>0.71</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>100</v>
+      </c>
       <c r="P32" t="n">
         <v>82.59999999999999</v>
       </c>
@@ -6497,9 +6545,15 @@
       <c r="L40" t="n">
         <v>-0.29</v>
       </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-11.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-46</v>
+      </c>
       <c r="P40" t="n">
         <v>-21.4</v>
       </c>
@@ -6572,9 +6626,15 @@
       <c r="L41" t="n">
         <v>-0.27</v>
       </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>-702</v>
+      </c>
       <c r="P41" t="n">
         <v>-27.3</v>
       </c>
@@ -6647,9 +6707,15 @@
       <c r="L42" t="n">
         <v>-0.63</v>
       </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>-157</v>
+      </c>
       <c r="P42" t="n">
         <v>-29.3</v>
       </c>
@@ -7046,9 +7112,15 @@
       <c r="L47" t="n">
         <v>3.05</v>
       </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+      <c r="M47" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>97</v>
+      </c>
       <c r="P47" t="n">
         <v>263.7</v>
       </c>
@@ -7283,9 +7355,15 @@
       <c r="L50" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+      <c r="M50" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N50" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>55</v>
+      </c>
       <c r="P50" t="n">
         <v>36.5</v>
       </c>
@@ -7439,9 +7517,15 @@
       <c r="L52" t="n">
         <v>0.08</v>
       </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="M52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N52" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="O52" t="n">
+        <v>60</v>
+      </c>
       <c r="P52" t="n">
         <v>5.7</v>
       </c>
@@ -7514,9 +7598,15 @@
       <c r="L53" t="n">
         <v>-0.05</v>
       </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N53" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="O53" t="n">
+        <v>-38</v>
+      </c>
       <c r="P53" t="n">
         <v>-3.8</v>
       </c>
@@ -7670,9 +7760,15 @@
       <c r="L55" t="n">
         <v>-0.43</v>
       </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
+      <c r="M55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N55" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="O55" t="n">
+        <v>-243</v>
+      </c>
       <c r="P55" t="n">
         <v>-31</v>
       </c>
@@ -8551,9 +8647,15 @@
       <c r="L66" t="n">
         <v>0.77</v>
       </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
+      <c r="M66" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>49</v>
+      </c>
       <c r="P66" t="n">
         <v>63.2</v>
       </c>
@@ -8626,9 +8728,15 @@
       <c r="L67" t="n">
         <v>0.74</v>
       </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="M67" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="O67" t="n">
+        <v>85</v>
+      </c>
       <c r="P67" t="n">
         <v>58.6</v>
       </c>
@@ -9754,9 +9862,15 @@
       <c r="L81" t="n">
         <v>0.38</v>
       </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="M81" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="N81" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>42</v>
+      </c>
       <c r="P81" t="n">
         <v>35.2</v>
       </c>
@@ -9991,9 +10105,15 @@
       <c r="L84" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="M84" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="N84" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>23</v>
+      </c>
       <c r="P84" t="n">
         <v>4.3</v>
       </c>
@@ -10228,9 +10348,15 @@
       <c r="L87" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="M87" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>-49</v>
+      </c>
       <c r="P87" t="n">
         <v>-9.300000000000001</v>
       </c>
@@ -10544,8 +10670,12 @@
       <c r="L91" t="n">
         <v>-0.59</v>
       </c>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-12</v>
+      </c>
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="n">
         <v>-40.1</v>
@@ -10700,9 +10830,15 @@
       <c r="L93" t="n">
         <v>1.23</v>
       </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+      <c r="M93" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O93" t="n">
+        <v>100</v>
+      </c>
       <c r="P93" t="n">
         <v>91.7</v>
       </c>
@@ -11747,9 +11883,15 @@
       <c r="L106" t="n">
         <v>-1.05</v>
       </c>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-17.4</v>
+      </c>
+      <c r="O106" t="n">
+        <v>-1645</v>
+      </c>
       <c r="P106" t="n">
         <v>-51.4</v>
       </c>
@@ -11822,9 +11964,15 @@
       <c r="L107" t="n">
         <v>1.65</v>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="O107" t="n">
+        <v>99</v>
+      </c>
       <c r="P107" t="n">
         <v>138.8</v>
       </c>
@@ -11897,9 +12045,15 @@
       <c r="L108" t="n">
         <v>1.21</v>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="n">
+        <v>100</v>
+      </c>
       <c r="P108" t="n">
         <v>121.6</v>
       </c>
@@ -12053,9 +12207,15 @@
       <c r="L110" t="n">
         <v>1.35</v>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" t="n">
+        <v>88</v>
+      </c>
       <c r="P110" t="n">
         <v>101.4</v>
       </c>
@@ -12857,9 +13017,15 @@
       <c r="L120" t="n">
         <v>0.15</v>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="O120" t="n">
+        <v>56</v>
+      </c>
       <c r="P120" t="n">
         <v>10.3</v>
       </c>
@@ -13094,9 +13260,15 @@
       <c r="L123" t="n">
         <v>2.63</v>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="O123" t="n">
+        <v>86</v>
+      </c>
       <c r="P123" t="n">
         <v>143.4</v>
       </c>
@@ -13250,9 +13422,15 @@
       <c r="L125" t="n">
         <v>0.89</v>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O125" t="n">
+        <v>92</v>
+      </c>
       <c r="P125" t="n">
         <v>61.1</v>
       </c>
@@ -13487,9 +13665,15 @@
       <c r="L128" t="n">
         <v>0.37</v>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>83</v>
+      </c>
       <c r="P128" t="n">
         <v>35</v>
       </c>
@@ -13967,9 +14151,15 @@
       <c r="L134" t="n">
         <v>-0.11</v>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="O134" t="n">
+        <v>-32</v>
+      </c>
       <c r="P134" t="n">
         <v>-8</v>
       </c>
@@ -14123,9 +14313,15 @@
       <c r="L136" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-7.4</v>
+      </c>
+      <c r="O136" t="n">
+        <v>-173</v>
+      </c>
       <c r="P136" t="n">
         <v>-26.4</v>
       </c>
@@ -14279,9 +14475,15 @@
       <c r="L138" t="n">
         <v>1.71</v>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="O138" t="n">
+        <v>100</v>
+      </c>
       <c r="P138" t="n">
         <v>140.6</v>
       </c>
@@ -15164,9 +15366,15 @@
       <c r="L149" t="n">
         <v>0.22</v>
       </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="M149" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="O149" t="n">
+        <v>49</v>
+      </c>
       <c r="P149" t="n">
         <v>16.9</v>
       </c>
@@ -15239,9 +15447,15 @@
       <c r="L150" t="n">
         <v>0.01</v>
       </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
+      <c r="M150" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N150" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O150" t="n">
+        <v>4</v>
+      </c>
       <c r="P150" t="n">
         <v>0.6</v>
       </c>
@@ -15719,9 +15933,15 @@
       <c r="L156" t="n">
         <v>0.29</v>
       </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
+      <c r="M156" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="N156" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="O156" t="n">
+        <v>61</v>
+      </c>
       <c r="P156" t="n">
         <v>26</v>
       </c>
@@ -16037,15 +16257,9 @@
       <c r="L160" t="n">
         <v>-0.46</v>
       </c>
-      <c r="M160" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N160" t="n">
-        <v>-14.7</v>
-      </c>
-      <c r="O160" t="n">
-        <v>-593</v>
-      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
       <c r="P160" t="n">
         <v>-18.1</v>
       </c>
@@ -16118,9 +16332,15 @@
       <c r="L161" t="n">
         <v>-0.38</v>
       </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
+      <c r="M161" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="N161" t="n">
+        <v>-5</v>
+      </c>
+      <c r="O161" t="n">
+        <v>-46</v>
+      </c>
       <c r="P161" t="n">
         <v>-18.5</v>
       </c>
@@ -16436,8 +16656,12 @@
       <c r="L165" t="n">
         <v>-1.2</v>
       </c>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>-14.7</v>
+      </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="n">
         <v>-45.1</v>
@@ -16511,9 +16735,15 @@
       <c r="L166" t="n">
         <v>-0.93</v>
       </c>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
+      <c r="M166" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N166" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="O166" t="n">
+        <v>-2027</v>
+      </c>
       <c r="P166" t="n">
         <v>-45.9</v>
       </c>
@@ -16586,9 +16816,15 @@
       <c r="L167" t="n">
         <v>1.03</v>
       </c>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
+      <c r="M167" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>84</v>
+      </c>
       <c r="P167" t="n">
         <v>130.5</v>
       </c>
@@ -16661,9 +16897,15 @@
       <c r="L168" t="n">
         <v>1.7</v>
       </c>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
+      <c r="M168" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>98</v>
+      </c>
       <c r="P168" t="n">
         <v>129.9</v>
       </c>
@@ -16898,15 +17140,9 @@
       <c r="L171" t="n">
         <v>1.61</v>
       </c>
-      <c r="M171" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="N171" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="O171" t="n">
-        <v>87</v>
-      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
       <c r="P171" t="n">
         <v>91.40000000000001</v>
       </c>
@@ -17141,9 +17377,15 @@
       <c r="L174" t="n">
         <v>0.72</v>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
+      <c r="M174" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="N174" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="O174" t="n">
+        <v>91</v>
+      </c>
       <c r="P174" t="n">
         <v>65.5</v>
       </c>
@@ -17216,9 +17458,15 @@
       <c r="L175" t="n">
         <v>0.88</v>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="O175" t="n">
+        <v>81</v>
+      </c>
       <c r="P175" t="n">
         <v>54</v>
       </c>
@@ -17453,9 +17701,15 @@
       <c r="L178" t="n">
         <v>0.33</v>
       </c>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="O178" t="n">
+        <v>65</v>
+      </c>
       <c r="P178" t="n">
         <v>21.2</v>
       </c>
@@ -17852,9 +18106,15 @@
       <c r="L183" t="n">
         <v>1.73</v>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>81</v>
+      </c>
       <c r="P183" t="n">
         <v>99.90000000000001</v>
       </c>
@@ -17927,9 +18187,15 @@
       <c r="L184" t="n">
         <v>0.44</v>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>71</v>
+      </c>
       <c r="P184" t="n">
         <v>43.3</v>
       </c>
@@ -18326,9 +18592,15 @@
       <c r="L189" t="n">
         <v>0.09</v>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N189" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O189" t="n">
+        <v>25</v>
+      </c>
       <c r="P189" t="n">
         <v>6.5</v>
       </c>
@@ -18482,9 +18754,15 @@
       <c r="L191" t="n">
         <v>0.1</v>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="O191" t="n">
+        <v>11</v>
+      </c>
       <c r="P191" t="n">
         <v>6.4</v>
       </c>
@@ -18557,9 +18835,15 @@
       <c r="L192" t="n">
         <v>0.05</v>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>11</v>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>9</v>
+      </c>
       <c r="P192" t="n">
         <v>4.2</v>
       </c>
@@ -18632,9 +18916,15 @@
       <c r="L193" t="n">
         <v>-0.03</v>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
+      <c r="M193" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N193" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="O193" t="n">
+        <v>-3</v>
+      </c>
       <c r="P193" t="n">
         <v>-1.4</v>
       </c>
@@ -18707,9 +18997,15 @@
       <c r="L194" t="n">
         <v>-0.09</v>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N194" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="O194" t="n">
+        <v>-40</v>
+      </c>
       <c r="P194" t="n">
         <v>-6.8</v>
       </c>
@@ -18782,9 +19078,15 @@
       <c r="L195" t="n">
         <v>-0.25</v>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="N195" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="O195" t="n">
+        <v>-60</v>
+      </c>
       <c r="P195" t="n">
         <v>-14.6</v>
       </c>
@@ -18938,9 +19240,15 @@
       <c r="L197" t="n">
         <v>0.27</v>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N197" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="O197" t="n">
+        <v>46</v>
+      </c>
       <c r="P197" t="n">
         <v>22.8</v>
       </c>
@@ -19013,9 +19321,15 @@
       <c r="L198" t="n">
         <v>0.27</v>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="O198" t="n">
+        <v>20</v>
+      </c>
       <c r="P198" t="n">
         <v>14.2</v>
       </c>
@@ -19331,9 +19645,15 @@
       <c r="L202" t="n">
         <v>-0.19</v>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
+      <c r="M202" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N202" t="n">
+        <v>-4.2</v>
+      </c>
+      <c r="O202" t="n">
+        <v>-44</v>
+      </c>
       <c r="P202" t="n">
         <v>-11.1</v>
       </c>
@@ -19406,9 +19726,15 @@
       <c r="L203" t="n">
         <v>-0.31</v>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N203" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="O203" t="n">
+        <v>-111</v>
+      </c>
       <c r="P203" t="n">
         <v>-12.9</v>
       </c>
@@ -19803,9 +20129,15 @@
       <c r="L208" t="n">
         <v>-0.64</v>
       </c>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
+      <c r="M208" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N208" t="n">
+        <v>-12.7</v>
+      </c>
+      <c r="O208" t="n">
+        <v>-413</v>
+      </c>
       <c r="P208" t="n">
         <v>-40.3</v>
       </c>
@@ -19959,9 +20291,15 @@
       <c r="L210" t="n">
         <v>-1.35</v>
       </c>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
+      <c r="M210" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N210" t="n">
+        <v>-26</v>
+      </c>
+      <c r="O210" t="n">
+        <v>-1247</v>
+      </c>
       <c r="P210" t="n">
         <v>-66.2</v>
       </c>
@@ -20275,9 +20613,15 @@
       <c r="L214" t="n">
         <v>1.4</v>
       </c>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
+      <c r="M214" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N214" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O214" t="n">
+        <v>100</v>
+      </c>
       <c r="P214" t="n">
         <v>70</v>
       </c>
@@ -20674,9 +21018,15 @@
       <c r="L219" t="n">
         <v>0.35</v>
       </c>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
+      <c r="M219" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N219" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="O219" t="n">
+        <v>100</v>
+      </c>
       <c r="P219" t="n">
         <v>24.3</v>
       </c>
@@ -21071,8 +21421,12 @@
       <c r="L224" t="n">
         <v>-0.61</v>
       </c>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>-16.5</v>
+      </c>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="n">
         <v>-27.8</v>
@@ -21302,9 +21656,15 @@
       <c r="L227" t="n">
         <v>0.86</v>
       </c>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
+      <c r="M227" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="N227" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O227" t="n">
+        <v>89</v>
+      </c>
       <c r="P227" t="n">
         <v>77.3</v>
       </c>
@@ -21701,9 +22061,15 @@
       <c r="L232" t="n">
         <v>0.38</v>
       </c>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
+      <c r="M232" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="N232" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O232" t="n">
+        <v>51</v>
+      </c>
       <c r="P232" t="n">
         <v>25.2</v>
       </c>
@@ -21857,9 +22223,15 @@
       <c r="L234" t="n">
         <v>0.32</v>
       </c>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
+      <c r="M234" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N234" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="O234" t="n">
+        <v>86</v>
+      </c>
       <c r="P234" t="n">
         <v>19.7</v>
       </c>
@@ -22175,9 +22547,15 @@
       <c r="L238" t="n">
         <v>-0.18</v>
       </c>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
+      <c r="M238" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N238" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="O238" t="n">
+        <v>-258</v>
+      </c>
       <c r="P238" t="n">
         <v>-13.7</v>
       </c>
@@ -22655,9 +23033,15 @@
       <c r="L244" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
+      <c r="M244" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N244" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="O244" t="n">
+        <v>83</v>
+      </c>
       <c r="P244" t="n">
         <v>30.3</v>
       </c>
@@ -22730,9 +23114,15 @@
       <c r="L245" t="n">
         <v>0.36</v>
       </c>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
+      <c r="M245" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N245" t="n">
+        <v>-3.9</v>
+      </c>
+      <c r="O245" t="n">
+        <v>73</v>
+      </c>
       <c r="P245" t="n">
         <v>27.6</v>
       </c>
@@ -22805,9 +23195,15 @@
       <c r="L246" t="n">
         <v>0.34</v>
       </c>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
+      <c r="M246" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="N246" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="O246" t="n">
+        <v>59</v>
+      </c>
       <c r="P246" t="n">
         <v>23</v>
       </c>
@@ -23042,9 +23438,15 @@
       <c r="L249" t="n">
         <v>0.16</v>
       </c>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
+      <c r="M249" t="n">
+        <v>6</v>
+      </c>
+      <c r="N249" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="O249" t="n">
+        <v>48</v>
+      </c>
       <c r="P249" t="n">
         <v>12.1</v>
       </c>
@@ -23439,8 +23841,12 @@
       <c r="L254" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M254" t="inlineStr"/>
-      <c r="N254" t="inlineStr"/>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="n">
+        <v>-8.6</v>
+      </c>
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="n">
         <v>-19</v>
@@ -23593,8 +23999,12 @@
       <c r="L256" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M256" t="inlineStr"/>
-      <c r="N256" t="inlineStr"/>
+      <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="n">
+        <v>-10.6</v>
+      </c>
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="n">
         <v>-36.1</v>
@@ -23911,9 +24321,15 @@
       <c r="L260" t="n">
         <v>0.29</v>
       </c>
-      <c r="M260" t="inlineStr"/>
-      <c r="N260" t="inlineStr"/>
-      <c r="O260" t="inlineStr"/>
+      <c r="M260" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="N260" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O260" t="n">
+        <v>44</v>
+      </c>
       <c r="P260" t="n">
         <v>20.4</v>
       </c>
@@ -23986,9 +24402,15 @@
       <c r="L261" t="n">
         <v>0.24</v>
       </c>
-      <c r="M261" t="inlineStr"/>
-      <c r="N261" t="inlineStr"/>
-      <c r="O261" t="inlineStr"/>
+      <c r="M261" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N261" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="O261" t="n">
+        <v>38</v>
+      </c>
       <c r="P261" t="n">
         <v>11.5</v>
       </c>
@@ -24709,9 +25131,15 @@
       <c r="L270" t="n">
         <v>-0.57</v>
       </c>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
+      <c r="M270" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N270" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="O270" t="n">
+        <v>-255</v>
+      </c>
       <c r="P270" t="n">
         <v>-30.7</v>
       </c>
@@ -25270,9 +25698,15 @@
       <c r="L277" t="n">
         <v>0.29</v>
       </c>
-      <c r="M277" t="inlineStr"/>
-      <c r="N277" t="inlineStr"/>
-      <c r="O277" t="inlineStr"/>
+      <c r="M277" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="N277" t="n">
+        <v>-3.4</v>
+      </c>
+      <c r="O277" t="n">
+        <v>45</v>
+      </c>
       <c r="P277" t="n">
         <v>16.6</v>
       </c>
@@ -25426,9 +25860,15 @@
       <c r="L279" t="n">
         <v>0.27</v>
       </c>
-      <c r="M279" t="inlineStr"/>
-      <c r="N279" t="inlineStr"/>
-      <c r="O279" t="inlineStr"/>
+      <c r="M279" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>10</v>
+      </c>
       <c r="P279" t="n">
         <v>10.2</v>
       </c>
@@ -25825,9 +26265,15 @@
       <c r="L284" t="n">
         <v>-0.53</v>
       </c>
-      <c r="M284" t="inlineStr"/>
-      <c r="N284" t="inlineStr"/>
-      <c r="O284" t="inlineStr"/>
+      <c r="M284" t="n">
+        <v>1</v>
+      </c>
+      <c r="N284" t="n">
+        <v>-16.5</v>
+      </c>
+      <c r="O284" t="n">
+        <v>-1163</v>
+      </c>
       <c r="P284" t="n">
         <v>-37.6</v>
       </c>
@@ -26156,19 +26602,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F4" t="n">
         <v>-6.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -26189,30 +26635,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
         <v>-8.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>&lt;-- engine pick (regime)</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26226,13 +26668,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" t="n">
         <v>2.6</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
         <v>-7.9</v>
@@ -26245,7 +26687,11 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>&lt;-- engine pick (regime)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26259,10 +26705,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D7" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="E7" t="n">
         <v>67</v>
@@ -26292,10 +26738,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="E8" t="n">
         <v>67</v>
@@ -26325,23 +26771,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.5</v>
+        <v>-7.6</v>
       </c>
       <c r="G9" t="n">
         <v>0.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -26441,7 +26887,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-2.7</v>
+        <v>-2.9</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -26483,7 +26929,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-8.6</v>
+        <v>-10.7</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -26525,7 +26971,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-13.3</v>
+        <v>-13.9</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -26567,7 +27013,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-11</v>
+        <v>-8.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -26609,7 +27055,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-4.1</v>
+        <v>-4.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -26651,7 +27097,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-10.3</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -26735,7 +27181,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-1.5</v>
+        <v>-1.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -26777,7 +27223,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -26819,7 +27265,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -26861,7 +27307,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-2</v>
+        <v>-2.9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -26903,7 +27349,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-5.1</v>
+        <v>-3.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -26945,7 +27391,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-4.6</v>
+        <v>-4.7</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -26987,7 +27433,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-8.1</v>
+        <v>-7.3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -27029,7 +27475,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-9</v>
+        <v>-9.1</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -27071,7 +27517,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -27113,7 +27559,7 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-3.6</v>
+        <v>-3.8</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -27155,7 +27601,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -27197,7 +27643,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>-13</v>
+        <v>-11.8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -27277,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27292,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27302,12 +27748,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27322,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27332,12 +27778,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27347,12 +27793,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27362,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27377,12 +27823,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27392,12 +27838,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -27622,7 +28068,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chosen by choose_horizon() from the backtested Horizon Matrix, REGIME-CONDITIONAL: risk-off favours a strong SHORT horizon (de-risk fast), risk-on lets it run longer. Today: 2M. The full menu of horizons (1W-1Y) with win rates is on this sheet so you can pick a shorter commitment. Per-STOCK horizons are NOT offered (small-sample skill ~random).</t>
+          <t>Chosen by choose_horizon() from the backtested Horizon Matrix, REGIME-CONDITIONAL: risk-off favours a strong SHORT horizon (de-risk fast), risk-on lets it run longer. Today: 3M. The full menu of horizons (1W-1Y) with win rates is on this sheet so you can pick a shorter commitment. Per-STOCK horizons are NOT offered (small-sample skill ~random).</t>
         </is>
       </c>
     </row>
@@ -27798,7 +28244,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HISTORICALLY TESTED — all horizons backtested · best = 2M</t>
+          <t>HISTORICALLY TESTED — all horizons backtested · best = 3M</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (75)</t>
+          <t>ICICIBANK (76)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-24  /  2026-08-24</t>
+          <t>2026-08-25  /  2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 75</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,10 +1534,10 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I2" t="n">
         <v>80</v>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 75; SBIN: 74, IDFCFIRSTB: 66, LICI: 65</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, IDFCFIRSTB: 65, LICI: 65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 57, NHPC: 53, TATAPOWER: 53</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 58, NHPC: 54, TATAPOWER: 54</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.6%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.6%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +2 = 57</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +3 = 58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2130,7 +2130,7 @@
         <v>99</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, NHPC: 53, TATAPOWER: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 64, NHPC: 54, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Sector +3 · Trend/Tech +2 = 52</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,40 +2353,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>237</v>
+        <v>406</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>230 - 244</t>
+          <t>394 - 418</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.2%)</t>
+          <t>Below 200-DMA (-5.0%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32232</v>
+        <v>30856</v>
       </c>
       <c r="W9" t="n">
-        <v>136</v>
+        <v>76</v>
       </c>
       <c r="X9" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 52; OIL: 52, IOC: 46</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; HINDZINC: 49, TATASTEEL: 47, SAIL: 43</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.2%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.0%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>406</v>
+        <v>237</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>394 - 418</t>
+          <t>230 - 244</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.0%)</t>
+          <t>Below 200-DMA (-8.2%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2539,17 +2539,17 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>30856</v>
+        <v>32232</v>
       </c>
       <c r="W10" t="n">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="X10" t="n">
-        <v>10.3</v>
+        <v>10.8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 42</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 50; OIL: 50, IOC: 44, GUJGASLTD: 31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.0%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.2%) • sector strength 7/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
         <v>97</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
         <v>85</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.2%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.2%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (76)</t>
+          <t>ICICIBANK (75)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25  /  2026-08-24</t>
+          <t>2026-08-25  /  2026-08-25</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 76</t>
+          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,10 +1534,10 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H2" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I2" t="n">
         <v>80</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1420.5</v>
+        <v>1417.9</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1382 - 1459</t>
+          <t>1379 - 1457</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+5.0%)</t>
+          <t>Above 200-DMA (+4.8%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>17046</v>
+        <v>19851</v>
       </c>
       <c r="W2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="X2" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, IDFCFIRSTB: 65, LICI: 65</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 75; IDFCFIRSTB: 65, LICI: 65, PNB: 65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.0%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1902.4</v>
+        <v>1912.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1851 - 1954</t>
+          <t>1861 - 1964</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.1%)</t>
+          <t>Above 200-DMA (+6.6%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>34243</v>
+        <v>34429</v>
       </c>
       <c r="W3" t="n">
         <v>18</v>
       </c>
       <c r="X3" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 71; CIPLA: 66, ZYDUSLIFE: 65, LUPIN: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 71; CIPLA: 66, ZYDUSLIFE: 64, LUPIN: 59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.1%) • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.6%) • outperforming Nifty • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,13 +1770,13 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" t="n">
         <v>81</v>
       </c>
       <c r="I4" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1646</v>
+        <v>1654.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1593 - 1699</t>
+          <t>1602 - 1708</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+10.9%)</t>
+          <t>Above 200-DMA (+11.4%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>18106</v>
+        <v>19859</v>
       </c>
       <c r="W4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X4" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+10.9%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+11.4%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +3 = 64</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>340.7</v>
+        <v>338</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>332 - 349</t>
+          <t>330 - 346</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1928,15 +1928,15 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.6%)</t>
+          <t>Below 200-DMA (-5.4%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>27937</v>
+        <v>22308</v>
       </c>
       <c r="W5" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="X5" t="n">
-        <v>9.4</v>
+        <v>7.5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 64; POWERGRID: 58, NHPC: 54, TATAPOWER: 54</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 57, NHPC: 53, TATAPOWER: 52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.6%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.4%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
         <v>95</v>
@@ -2028,11 +2028,11 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2199.8</v>
+        <v>2175.4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2142 - 2257</t>
+          <t>2119 - 2232</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.2%)</t>
+          <t>Below 200-DMA (-3.3%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>24198</v>
+        <v>28280</v>
       </c>
       <c r="W6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X6" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 71, CIPLA: 66, ZYDUSLIFE: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 71, CIPLA: 66, ZYDUSLIFE: 64. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-2.2%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Pharma holding (low vol) • below 200-dma (-3.3%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +3 = 58</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H7" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>274</v>
+        <v>408.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>268 - 280</t>
+          <t>396 - 421</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.8%)</t>
+          <t>Below 200-DMA (-2.7%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>37538</v>
+        <v>25315</v>
       </c>
       <c r="W7" t="n">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 64, NHPC: 54, TATAPOWER: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 66, POLYCAB: 55, KEI: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-3.8%) • sector strength 27/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.7%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 57</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +2 = 57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,40 +2235,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G8" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I8" t="n">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>414.3</v>
+        <v>270.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>402 - 427</t>
+          <t>264 - 277</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.3%)</t>
+          <t>Below 200-DMA (-5.1%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>20301</v>
+        <v>23778</v>
       </c>
       <c r="W8" t="n">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="X8" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 64, POLYCAB: 56, KEI: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, NHPC: 53, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-1.3%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-5.1%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2339,11 +2339,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +2 = 51</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Sector +4 · Trend/Tech +2 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,40 +2353,40 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H9" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>406</v>
+        <v>235.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>394 - 418</t>
+          <t>229 - 243</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2400,15 +2400,15 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.0%)</t>
+          <t>Below 200-DMA (-8.6%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>30856</v>
+        <v>32785</v>
       </c>
       <c r="W9" t="n">
-        <v>76</v>
+        <v>139</v>
       </c>
       <c r="X9" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 51; HINDZINC: 49, TATASTEEL: 47, SAIL: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; OIL: 52, IOC: 48</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.0%) • sector strength 20/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.6%) • sector strength 40/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +2 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>237</v>
+        <v>405.8</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>230 - 244</t>
+          <t>394 - 418</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2522,11 +2522,11 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.2%)</t>
+          <t>Below 200-DMA (-5.1%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>32232</v>
+        <v>31247</v>
       </c>
       <c r="W10" t="n">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="X10" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 50; OIL: 50, IOC: 44, GUJGASLTD: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 42</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.2%) • sector strength 7/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.1%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
         <v>97</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>270.6</v>
+        <v>268</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>264 - 277</t>
+          <t>262 - 274</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2640,11 +2640,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.2%)</t>
+          <t>Below 200-DMA (-16.8%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>22460</v>
+        <v>23048</v>
       </c>
       <c r="W11" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="X11" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 13/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.8%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2693,11 +2693,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +5 · Trend/Tech +3 = 51</t>
+          <t>Risk/Vol +22 · Historical +12 · Regime +9 · Sector +5 · Trend/Tech +4 = 52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2714,7 +2714,7 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" t="n">
         <v>88</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>484.2</v>
+        <v>483.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>470 - 499</t>
+          <t>469 - 498</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.3%)</t>
+          <t>Below 200-DMA (-16.2%)</t>
         </is>
       </c>
       <c r="S12" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>15010</v>
+        <v>18373</v>
       </c>
       <c r="W12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 51; DELHIVERY: 59. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.3%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk Transport holding (low vol) • below 200-dma (-16.2%) • sector strength 47/100 • regime cautious (partial deploy) • 1 similar past recs: 0% positive, median -11.2% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -2835,10 +2835,10 @@
         <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2019.9</v>
+        <v>2019.3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1959 - 2081</t>
+          <t>1958 - 2081</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.2%)</t>
+          <t>Below 200-DMA (-10.1%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>14139</v>
+        <v>14135</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.2%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.1%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27718,12 +27718,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27733,12 +27733,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27798,7 +27798,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27823,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27843,7 +27843,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C10" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (75)</t>
+          <t>ICICIBANK (76)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (48)</t>
+          <t>HINDUNILVR (49)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-25  /  2026-08-25</t>
+          <t>2026-08-26  /  2026-08-26</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.98</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 75</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,10 +1534,10 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I2" t="n">
         <v>80</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1417.9</v>
+        <v>1422.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1379 - 1457</t>
+          <t>1384 - 1461</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1578,11 +1578,11 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+4.8%)</t>
+          <t>Above 200-DMA (+5.1%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>19851</v>
+        <v>28454</v>
       </c>
       <c r="W2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="X2" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 75; IDFCFIRSTB: 65, LICI: 65, PNB: 65</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, IDFCFIRSTB: 65, LICI: 65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+4.8%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1912.7</v>
+        <v>1922</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1861 - 1964</t>
+          <t>1871 - 1973</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+6.6%)</t>
+          <t>Above 200-DMA (+7.1%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>34429</v>
+        <v>36518</v>
       </c>
       <c r="W3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X3" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 71; CIPLA: 66, ZYDUSLIFE: 64, LUPIN: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 71; CIPLA: 66, ZYDUSLIFE: 65, LUPIN: 59</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.6%) • outperforming Nifty • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.1%) • outperforming Nifty • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1770,13 +1770,13 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
         <v>81</v>
       </c>
       <c r="I4" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1654.9</v>
+        <v>1651.1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1602 - 1708</t>
+          <t>1599 - 1703</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1814,11 +1814,11 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.4%)</t>
+          <t>Above 200-DMA (+11.1%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>19859</v>
+        <v>14860</v>
       </c>
       <c r="W4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="X4" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+11.4%) • outperforming Nifty • sector strength 73/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+11.1%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +1 = 62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,13 +1888,13 @@
         <v>84</v>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
         <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>338</v>
+        <v>339.9</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>330 - 346</t>
+          <t>331 - 348</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.4%)</t>
+          <t>Below 200-DMA (-4.9%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>22308</v>
+        <v>21071</v>
       </c>
       <c r="W5" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="X5" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 57, NHPC: 53, TATAPOWER: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 62; POWERGRID: 58, NHPC: 52, TATAPOWER: 50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.4%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.9%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
         <v>95</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2175.4</v>
+        <v>2175.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>28280</v>
+        <v>26106</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="X6" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 71, CIPLA: 66, ZYDUSLIFE: 64. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 71, CIPLA: 66, ZYDUSLIFE: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 57</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +1 = 58</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2117,40 +2117,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H7" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="I7" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>408.3</v>
+        <v>271</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>396 - 421</t>
+          <t>265 - 277</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-2.7%)</t>
+          <t>Below 200-DMA (-4.8%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,21 +2181,21 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>25315</v>
+        <v>22764</v>
       </c>
       <c r="W7" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="X7" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 66, POLYCAB: 55, KEI: 54. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 62, NHPC: 52, TATAPOWER: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.7%) • sector strength 67/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.8%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +4 · Sector +2 = 57</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 57</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2235,40 +2235,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Trend/Tech</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="H8" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="I8" t="n">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>270.2</v>
+        <v>413.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>264 - 277</t>
+          <t>401 - 426</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.1%)</t>
+          <t>Below 200-DMA (-1.5%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>23778</v>
+        <v>21076</v>
       </c>
       <c r="W8" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Power name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 63, NHPC: 53, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 66, POLYCAB: 55, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-5.1%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-1.5%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Sector +4 · Trend/Tech +2 = 53</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +3 · Sector +3 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2353,20 +2353,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
         <v>86</v>
       </c>
       <c r="I9" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>235.9</v>
+        <v>234</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>229 - 243</t>
+          <t>227 - 241</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-8.6%)</t>
+          <t>Below 200-DMA (-9.3%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>32785</v>
+        <v>33696</v>
       </c>
       <c r="W9" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; OIL: 52, IOC: 48</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; OIL: 51, IOC: 47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-8.6%) • sector strength 40/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.3%) • sector strength 33/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +2 = 52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H10" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>405.8</v>
+        <v>271.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>394 - 418</t>
+          <t>265 - 278</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.1%)</t>
+          <t>Below 200-DMA (-15.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>31247</v>
+        <v>22526</v>
       </c>
       <c r="W10" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="X10" t="n">
-        <v>10.4</v>
+        <v>7.5</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 42</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; HINDUNILVR: 49, DABUR: 48, PATANJALI: 44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.1%) • sector strength 13/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2593,13 +2593,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
@@ -2609,42 +2609,42 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>268</v>
+        <v>404</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>262 - 274</t>
+          <t>392 - 416</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-16.8%)</t>
+          <t>Below 200-DMA (-5.6%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,21 +2653,21 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>23048</v>
+        <v>32320</v>
       </c>
       <c r="W11" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="X11" t="n">
-        <v>7.7</v>
+        <v>10.8</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 50; HINDUNILVR: 48, DABUR: 47, PATANJALI: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 42</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.8%) • sector strength 7/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.6%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
@@ -2714,10 +2714,10 @@
         <v>40</v>
       </c>
       <c r="G12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I12" t="n">
         <v>47</v>
@@ -2736,11 +2736,11 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>483.5</v>
+        <v>482.5</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>469 - 498</t>
+          <t>469 - 496</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2771,17 +2771,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>18373</v>
+        <v>19302</v>
       </c>
       <c r="W12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="X12" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — IRCTC: 52; DELHIVERY: 58. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +1 = 48</t>
+          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +2 = 49</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2832,13 +2832,13 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2854,11 +2854,11 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2019.3</v>
+        <v>2024.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1958 - 2081</t>
+          <t>1963 - 2085</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2876,11 +2876,11 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-10.1%)</t>
+          <t>Below 200-DMA (-9.8%)</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>14135</v>
+        <v>14169</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 48; ITC: 50, DABUR: 47, PATANJALI: 43. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 52, DABUR: 48, PATANJALI: 44. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-10.1%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.8%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -27738,7 +27738,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -27783,7 +27783,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -27793,12 +27793,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -27808,12 +27808,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -27823,12 +27823,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -27838,12 +27838,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C10" t="n">

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (49)</t>
+          <t>HINDUNILVR (50)</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-26  /  2026-08-26</t>
+          <t>2026-08-27  /  2026-08-26</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +1 = 62</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1894,7 +1894,7 @@
         <v>96</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 62; POWERGRID: 58, NHPC: 52, TATAPOWER: 50</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 59, NHPC: 53, TATAPOWER: 52</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.9%) • sector strength 13/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.9%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +1 = 58</t>
+          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +2 = 59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2124,13 +2124,13 @@
         <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" t="n">
         <v>99</v>
       </c>
       <c r="I7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 58; NTPC: 62, NHPC: 52, TATAPOWER: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 59; NTPC: 63, NHPC: 53, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.8%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-4.8%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +3 · Sector +3 = 53</t>
+          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +3 = 53</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2357,58 +2357,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I9" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>234</v>
+        <v>271.4</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>227 - 241</t>
+          <t>265 - 278</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-4% to +3%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.3%)</t>
+          <t>Below 200-DMA (-15.5%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2421,17 +2421,17 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>33696</v>
+        <v>22526</v>
       </c>
       <c r="W9" t="n">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="X9" t="n">
-        <v>11.3</v>
+        <v>7.5</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; OIL: 51, IOC: 47</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; HINDUNILVR: 50, DABUR: 49, PATANJALI: 45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.3%) • sector strength 33/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 27/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +2 = 52</t>
+          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +3 · Sector +1 = 51</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,58 +2475,58 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="I10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>271.4</v>
+        <v>234</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>265 - 278</t>
+          <t>227 - 241</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-4% to +3%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.5%)</t>
+          <t>Below 200-DMA (-9.3%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2539,17 +2539,17 @@
         </is>
       </c>
       <c r="V10" t="n">
-        <v>22526</v>
+        <v>33696</v>
       </c>
       <c r="W10" t="n">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="X10" t="n">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility FMCG name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 52; HINDUNILVR: 49, DABUR: 48, PATANJALI: 44</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; OIL: 50, IOC: 45, GUJGASLTD: 31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 20/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.3%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 42</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 43</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -2811,11 +2811,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +2 = 49</t>
+          <t>Risk/Vol +21 · Historical +13 · Regime +9 · Trend/Tech +4 · Sector +3 = 50</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2838,7 +2838,7 @@
         <v>85</v>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2913,12 +2913,12 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 49; ITC: 52, DABUR: 48, PATANJALI: 44. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — HINDUNILVR: 50; ITC: 53, DABUR: 49, PATANJALI: 45. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.8%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-9.8%) • sector strength 27/100 • regime cautious (partial deploy) • 4 similar past recs: 50% positive, median -0.1% • HELD FOR DIVERSIFICATION despite weak historical analogue — sized by risk, not conviction</t>
         </is>
       </c>
     </row>

--- a/reports/AEGIS_LATEST.xlsx
+++ b/reports/AEGIS_LATEST.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK (76)</t>
+          <t>ICICIBANK (78)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HINDUNILVR (50)</t>
+          <t>DABUR (49)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CIPLA, DABUR, TATASTEEL</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HINDUNILVR, LUPIN, PIDILITIND</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -688,7 +688,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-27  /  2026-08-26</t>
+          <t>2026-08-28  /  2026-08-28</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.97</t>
         </is>
       </c>
     </row>
@@ -1513,11 +1513,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +16 · Regime +9 · Sector +8 = 76</t>
+          <t>Risk/Vol +23 · Historical +20 · Trend/Tech +18 · Regime +9 · Sector +8 = 78</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1534,13 +1534,13 @@
         <v>66</v>
       </c>
       <c r="G2" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="H2" t="n">
         <v>92</v>
       </c>
       <c r="I2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J2" t="n">
         <v>60</v>
@@ -1556,11 +1556,11 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>1422.7</v>
+        <v>1432</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1384 - 1461</t>
+          <t>1393 - 1471</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -1574,15 +1574,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+5.1%)</t>
+          <t>Above 200-DMA (+5.7%)</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -1591,17 +1591,17 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V2" t="n">
-        <v>28454</v>
+        <v>25776</v>
       </c>
       <c r="W2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="X2" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 76; SBIN: 74, IDFCFIRSTB: 65, LICI: 65</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ICICIBANK: 78; SBIN: 71, PNB: 66, IDFCFIRSTB: 65</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.1%) • outperforming Nifty • sector strength 80/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
+          <t>Low-risk Financials holding (low vol) • above 200-dma (+5.7%) • outperforming Nifty • sector strength 79/100 • regime cautious (partial deploy) • 8 similar past recs: 75% positive, median +5.3%</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1652,13 @@
         <v>59</v>
       </c>
       <c r="G3" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
@@ -1674,11 +1674,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1922</v>
+        <v>1912</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1871 - 1973</t>
+          <t>1862 - 1962</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1696,11 +1696,11 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+7.1%)</t>
+          <t>Above 200-DMA (+6.4%)</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1709,17 +1709,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V3" t="n">
-        <v>36518</v>
+        <v>24856</v>
       </c>
       <c r="W3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 71; CIPLA: 66, ZYDUSLIFE: 65, LUPIN: 59</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — SUNPHARMA: 71; CIPLA: 66, ZYDUSLIFE: 64, DRREDDY: 50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • above 200-dma (+7.1%) • outperforming Nifty • sector strength 60/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+6.4%) • sector strength 64/100 • regime cautious (partial deploy) • 12 similar past recs: 67% positive, median +4.6%</t>
         </is>
       </c>
     </row>
@@ -1749,11 +1749,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Risk/Vol +20 · Trend/Tech +18 · Historical +14 · Regime +9 · Sector +7 = 68</t>
+          <t>Risk/Vol +20 · Historical +17 · Trend/Tech +14 · Regime +9 · Sector +6 = 66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1767,58 +1767,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="H4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="J4" t="n">
         <v>60</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1651.1</v>
+        <v>1413.5</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1599 - 1703</t>
+          <t>1371 - 1456</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-5% to +7%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Above 200-DMA (+11.1%)</t>
+          <t>Above 200-DMA (+1.2%)</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1827,21 +1827,21 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V4" t="n">
-        <v>14860</v>
+        <v>19789</v>
       </c>
       <c r="W4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="X4" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Risk/Vol + Trend/Tech strongest; chosen as a lowest-volatility Chemicals name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — PIDILITIND: 68; CHAMBLFERT: 49</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — CIPLA: 66; SUNPHARMA: 71, ZYDUSLIFE: 64, DRREDDY: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Low-risk Chemicals holding (low vol) • above 200-dma (+11.1%) • outperforming Nifty • sector strength 67/100 • regime cautious (partial deploy) • 15 similar past recs: 53% positive, median +1.4%</t>
+          <t>Low-risk Pharma holding (low vol) • above 200-dma (+1.2%) • sector strength 64/100 • regime cautious (partial deploy) • 1 similar past recs: 100% positive, median +7.5%</t>
         </is>
       </c>
     </row>
@@ -1867,11 +1867,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +2 = 63</t>
+          <t>Historical +25 · Risk/Vol +24 · Regime +9 · Trend/Tech +3 · Sector +1 = 62</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1891,10 +1891,10 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I5" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -1910,11 +1910,11 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>339.9</v>
+        <v>330.5</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>331 - 348</t>
+          <t>322 - 339</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1932,11 +1932,11 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.9%)</t>
+          <t>Below 200-DMA (-7.5%)</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1945,17 +1945,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V5" t="n">
-        <v>21071</v>
+        <v>33386</v>
       </c>
       <c r="W5" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="X5" t="n">
-        <v>7.1</v>
+        <v>11.2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 63; POWERGRID: 59, NHPC: 53, TATAPOWER: 52</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — NTPC: 62; POWERGRID: 57, NHPC: 52, JSWENERGY: 50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.9%) • sector strength 20/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-7.5%) • sector strength 7/100 • regime cautious (partial deploy) • 4 similar past recs: 100% positive, median +11.5%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Risk/Vol +24 · Historical +15 · Regime +9 · Sector +6 · Trend/Tech +5 = 59</t>
+          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Trend/Tech +7 · Sector +7 = 59</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1999,40 +1999,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trend/Tech</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="H6" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="I6" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J6" t="n">
         <v>60</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2175.5</v>
+        <v>408.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2119 - 2232</t>
+          <t>397 - 421</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2050,11 +2050,11 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-3.3%)</t>
+          <t>Below 200-DMA (-2.6%)</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -2063,21 +2063,21 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V6" t="n">
-        <v>26106</v>
+        <v>16759</v>
       </c>
       <c r="W6" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="X6" t="n">
-        <v>9.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Pharma name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — LUPIN: 59; SUNPHARMA: 71, CIPLA: 66, ZYDUSLIFE: 65. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 59; HAL: 66, KEI: 55, MAZDOCK: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Low-risk Pharma holding (low vol) • below 200-dma (-3.3%) • sector strength 60/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Industrials holding (low vol) • below 200-dma (-2.6%) • sector strength 71/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk/Vol +25 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +2 = 59</t>
+          <t>Risk/Vol +24 · Historical +17 · Regime +9 · Trend/Tech +6 · Sector +1 = 57</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2127,10 +2127,10 @@
         <v>29</v>
       </c>
       <c r="H7" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="J7" t="n">
         <v>60</v>
@@ -2146,11 +2146,11 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>271</v>
+        <v>266.5</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>265 - 277</t>
+          <t>260 - 273</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -2164,15 +2164,15 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-4.8%)</t>
+          <t>Below 200-DMA (-6.3%)</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -2181,17 +2181,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V7" t="n">
-        <v>22764</v>
+        <v>36784</v>
       </c>
       <c r="W7" t="n">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="X7" t="n">
-        <v>7.7</v>
+        <v>12.3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -2205,27 +2205,27 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 59; NTPC: 63, NHPC: 53, TATAPOWER: 52. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — POWERGRID: 57; NTPC: 62, NHPC: 52, JSWENERGY: 50. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Low-risk Power holding (low vol) • below 200-dma (-4.8%) • sector strength 20/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
+          <t>Low-risk Power holding (low vol) • below 200-dma (-6.3%) • sector strength 7/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +12.3%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>ACCUMULATE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Risk/Vol +21 · Historical +15 · Regime +9 · Sector +7 · Trend/Tech +5 = 57</t>
+          <t>Risk/Vol +21 · Historical +16 · Regime +9 · Sector +4 · Trend/Tech +3 = 53</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2239,36 +2239,36 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G8" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I8" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="J8" t="n">
         <v>60</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>413.2</v>
+        <v>232.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>401 - 426</t>
+          <t>225 - 239</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2282,15 +2282,15 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-1.5%)</t>
+          <t>Below 200-DMA (-9.9%)</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V8" t="n">
-        <v>21076</v>
+        <v>29046</v>
       </c>
       <c r="W8" t="n">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="X8" t="n">
-        <v>7.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Industrials name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — BEL: 57; HAL: 66, POLYCAB: 55, KEI: 53. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 53; OIL: 52, IOC: 50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Low-risk Industrials holding (low vol) • below 200-dma (-1.5%) • sector strength 73/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
+          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.9%) • sector strength 43/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
         <v>97</v>
       </c>
       <c r="I9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J9" t="n">
         <v>60</v>
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>271.4</v>
+        <v>268.1</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>265 - 278</t>
+          <t>262 - 275</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -2404,11 +2404,11 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-15.5%)</t>
+          <t>Below 200-DMA (-16.2%)</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2417,17 +2417,17 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V9" t="n">
-        <v>22526</v>
+        <v>24133</v>
       </c>
       <c r="W9" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="X9" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -2441,12 +2441,12 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; HINDUNILVR: 50, DABUR: 49, PATANJALI: 45</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ITC: 53; DABUR: 49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Low-risk FMCG holding (low vol) • below 200-dma (-15.5%) • sector strength 27/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
+          <t>Low-risk FMCG holding (low vol) • below 200-dma (-16.2%) • sector strength 29/100 • regime cautious (partial deploy) • 9 similar past recs: 56% positive, median +0.3%</t>
         </is>
       </c>
     </row>
@@ -2457,11 +2457,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +16 · Regime +9 · Trend/Tech +3 · Sector +1 = 51</t>
+          <t>Risk/Vol +20 · Historical +15 · Regime +9 · Trend/Tech +5 · Sector +1 = 50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2475,36 +2475,36 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="H10" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J10" t="n">
         <v>60</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>234</v>
+        <v>187.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>227 - 241</t>
+          <t>182 - 193</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -2518,15 +2518,15 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-9.3%)</t>
+          <t>Below 200-DMA (-2.5%)</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2535,21 +2535,21 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V10" t="n">
-        <v>33696</v>
+        <v>15559</v>
       </c>
       <c r="W10" t="n">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="X10" t="n">
-        <v>11.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Energy name under the sector cap</t>
+          <t>Risk/Vol + Historical strongest; chosen as a lowest-volatility Metal name under the sector cap</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — ONGC: 51; OIL: 50, IOC: 45, GUJGASLTD: 31</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — TATASTEEL: 50; COALINDIA: 49, HINDZINC: 49, SAIL: 41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Low-risk Energy holding (low vol) • below 200-dma (-9.3%) • sector strength 13/100 • regime cautious (partial deploy) • 2 similar past recs: 50% positive, median +9.0%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-2.5%) • sector strength 14/100 • regime cautious (partial deploy) • no historical analogue yet (&lt;3 obs)</t>
         </is>
       </c>
     </row>
@@ -2575,11 +2575,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +3 · Sector +1 = 50</t>
+          <t>Risk/Vol +22 · Historical +15 · Regime +9 · Trend/Tech +2 · Sector +1 = 49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2596,13 +2596,13 @@
         <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H11" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
         <v>60</v>
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>404</v>
+        <v>402.5</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>392 - 416</t>
+          <t>391 - 414</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -2636,15 +2636,15 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Below 200-DMA (-5.6%)</t>
+          <t>Below 200-DMA (-6.0%)</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2653,17 +2653,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>32320</v>
+        <v>26971</v>
       </c>
       <c r="W11" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="X11" t="n">
-        <v>10.8</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -2677,27 +2677,27 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 50; HINDZINC: 48, TATASTEEL: 46, SAIL: 43</t>
+          <t>Picked by lowest-vol + sector cap (the validated rule). Evidence scores — COALINDIA: 49; TATASTEEL: 50, HINDZINC: 49, SAIL: 41. Note: a peer scores higher but is higher-vol or cap-excluded — Evidence Score is context, not the selector.</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Low-risk Metal holding (low vol) • below 200-dma (-5.6%) • sector strength 7/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
+          <t>Low-risk Metal holding (low vol) • below 200-dma (-6.0%) • sector strength 14/100 • regime cautious (partial deploy) • 3 similar past recs: 67% positive, median +0.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WATCH</t>
+    